--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D52ECA6-7612-419B-A67C-7A9F968AA141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2F1C62-F02E-4DC1-81AD-F27F18CFC416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4135" uniqueCount="2673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4167" uniqueCount="2698">
   <si>
     <t>Пароль</t>
   </si>
@@ -8053,6 +8053,81 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/49C-i-rm3_n6Qg</t>
+  </si>
+  <si>
+    <t>13/09/26/10:00</t>
+  </si>
+  <si>
+    <t>37593</t>
+  </si>
+  <si>
+    <t>70112</t>
+  </si>
+  <si>
+    <t>42938</t>
+  </si>
+  <si>
+    <t>13/09/26/12:30</t>
+  </si>
+  <si>
+    <t>72137</t>
+  </si>
+  <si>
+    <t>01133</t>
+  </si>
+  <si>
+    <t>32857</t>
+  </si>
+  <si>
+    <t>88755</t>
+  </si>
+  <si>
+    <t>13/09/26/15:00</t>
+  </si>
+  <si>
+    <t>50320</t>
+  </si>
+  <si>
+    <t>36125</t>
+  </si>
+  <si>
+    <t>39173</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/wKpZLaqoVUY6Eg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/D1VjdbSf1ciZwg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/hb6wy0BBx-ptHQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/UwobLamdBFay1A</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/beqUkzqgBcfphw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/a8qe1nzzQSCpvQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/3IfgzvQ7lyCfKQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/JhMkOTkzXMLl1A</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/v0PXA9HaKjS73w</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/-UgyhSh5NJfJxA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/QmRQmt8RImP7ow</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/oFSidzVfBlg42Q</t>
   </si>
 </sst>
 </file>
@@ -31857,14 +31932,24 @@
     <row r="1299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1299" s="7"/>
       <c r="B1299" s="17"/>
-      <c r="C1299" s="2"/>
-      <c r="D1299" s="2"/>
-      <c r="E1299" s="2"/>
-      <c r="F1299" s="2"/>
+      <c r="C1299" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1299" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1299" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1299" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1299" s="2"/>
     </row>
     <row r="1300" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1300" s="7"/>
+      <c r="A1300" s="40" t="s">
+        <v>2673</v>
+      </c>
       <c r="B1300" s="17"/>
       <c r="C1300" s="2"/>
       <c r="D1300" s="2"/>
@@ -31873,34 +31958,56 @@
       <c r="G1300" s="2"/>
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1301" s="7"/>
-      <c r="B1301" s="17"/>
-      <c r="C1301" s="2"/>
+      <c r="A1301" s="7" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B1301" s="17">
+        <v>79525837593</v>
+      </c>
+      <c r="C1301" s="2" t="s">
+        <v>2691</v>
+      </c>
       <c r="D1301" s="2"/>
       <c r="E1301" s="2"/>
       <c r="F1301" s="2"/>
       <c r="G1301" s="2"/>
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1302" s="7"/>
-      <c r="B1302" s="17"/>
-      <c r="C1302" s="2"/>
-      <c r="D1302" s="2"/>
+      <c r="A1302" s="7" t="s">
+        <v>2675</v>
+      </c>
+      <c r="B1302" s="17">
+        <v>79183870112</v>
+      </c>
+      <c r="C1302" s="2" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D1302" s="2" t="s">
+        <v>2689</v>
+      </c>
       <c r="E1302" s="2"/>
       <c r="F1302" s="2"/>
       <c r="G1302" s="2"/>
     </row>
     <row r="1303" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1303" s="7"/>
-      <c r="B1303" s="17"/>
+      <c r="A1303" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B1303" s="17">
+        <v>79182842938</v>
+      </c>
       <c r="C1303" s="2"/>
-      <c r="D1303" s="2"/>
+      <c r="D1303" s="2" t="s">
+        <v>2690</v>
+      </c>
       <c r="E1303" s="2"/>
       <c r="F1303" s="2"/>
       <c r="G1303" s="2"/>
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1304" s="7"/>
+      <c r="A1304" s="40" t="s">
+        <v>2677</v>
+      </c>
       <c r="B1304" s="17"/>
       <c r="C1304" s="2"/>
       <c r="D1304" s="2"/>
@@ -31909,43 +32016,77 @@
       <c r="G1304" s="2"/>
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1305" s="7"/>
-      <c r="B1305" s="17"/>
-      <c r="C1305" s="2"/>
-      <c r="D1305" s="2"/>
-      <c r="E1305" s="2"/>
-      <c r="F1305" s="2"/>
+      <c r="A1305" s="7" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B1305" s="17">
+        <v>79183772137</v>
+      </c>
+      <c r="C1305" s="2" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D1305" s="2" t="s">
+        <v>2692</v>
+      </c>
+      <c r="E1305" s="2" t="s">
+        <v>2688</v>
+      </c>
+      <c r="F1305" s="2" t="s">
+        <v>2686</v>
+      </c>
       <c r="G1305" s="2"/>
     </row>
     <row r="1306" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1306" s="7"/>
-      <c r="B1306" s="17"/>
+      <c r="A1306" s="7" t="s">
+        <v>2679</v>
+      </c>
+      <c r="B1306" s="17">
+        <v>79897201133</v>
+      </c>
       <c r="C1306" s="2"/>
       <c r="D1306" s="2"/>
-      <c r="E1306" s="2"/>
-      <c r="F1306" s="2"/>
+      <c r="E1306" s="2" t="s">
+        <v>2688</v>
+      </c>
+      <c r="F1306" s="2" t="s">
+        <v>2687</v>
+      </c>
       <c r="G1306" s="2"/>
     </row>
     <row r="1307" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1307" s="7"/>
-      <c r="B1307" s="17"/>
+      <c r="A1307" s="7" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B1307" s="17">
+        <v>79615332857</v>
+      </c>
       <c r="C1307" s="2"/>
-      <c r="D1307" s="2"/>
+      <c r="D1307" s="2" t="s">
+        <v>2693</v>
+      </c>
       <c r="E1307" s="2"/>
       <c r="F1307" s="2"/>
       <c r="G1307" s="2"/>
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1308" s="7"/>
-      <c r="B1308" s="17"/>
+      <c r="A1308" s="7" t="s">
+        <v>2681</v>
+      </c>
+      <c r="B1308" s="17">
+        <v>79184188755</v>
+      </c>
       <c r="C1308" s="2"/>
-      <c r="D1308" s="2"/>
+      <c r="D1308" s="2" t="s">
+        <v>2693</v>
+      </c>
       <c r="E1308" s="2"/>
       <c r="F1308" s="2"/>
       <c r="G1308" s="2"/>
     </row>
     <row r="1309" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1309" s="7"/>
+      <c r="A1309" s="40" t="s">
+        <v>2682</v>
+      </c>
       <c r="B1309" s="17"/>
       <c r="C1309" s="2"/>
       <c r="D1309" s="2"/>
@@ -31954,28 +32095,46 @@
       <c r="G1309" s="2"/>
     </row>
     <row r="1310" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1310" s="7"/>
-      <c r="B1310" s="17"/>
+      <c r="A1310" s="7" t="s">
+        <v>2683</v>
+      </c>
+      <c r="B1310" s="17">
+        <v>79034550320</v>
+      </c>
       <c r="C1310" s="2"/>
-      <c r="D1310" s="2"/>
+      <c r="D1310" s="2" t="s">
+        <v>2695</v>
+      </c>
       <c r="E1310" s="2"/>
       <c r="F1310" s="2"/>
       <c r="G1310" s="2"/>
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1311" s="7"/>
-      <c r="B1311" s="17"/>
-      <c r="C1311" s="2"/>
+      <c r="A1311" s="7" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B1311" s="17">
+        <v>79497336125</v>
+      </c>
+      <c r="C1311" s="2" t="s">
+        <v>2697</v>
+      </c>
       <c r="D1311" s="2"/>
       <c r="E1311" s="2"/>
       <c r="F1311" s="2"/>
       <c r="G1311" s="2"/>
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1312" s="7"/>
-      <c r="B1312" s="17"/>
+      <c r="A1312" s="7" t="s">
+        <v>2685</v>
+      </c>
+      <c r="B1312" s="17">
+        <v>79676739173</v>
+      </c>
       <c r="C1312" s="2"/>
-      <c r="D1312" s="2"/>
+      <c r="D1312" s="2" t="s">
+        <v>2696</v>
+      </c>
       <c r="E1312" s="2"/>
       <c r="F1312" s="2"/>
       <c r="G1312" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2F1C62-F02E-4DC1-81AD-F27F18CFC416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA33043-F04E-4B5D-99C0-8CEE660D1580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4167" uniqueCount="2698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4181" uniqueCount="2708">
   <si>
     <t>Пароль</t>
   </si>
@@ -8128,6 +8128,36 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/oFSidzVfBlg42Q</t>
+  </si>
+  <si>
+    <t>14/09/26/10:00</t>
+  </si>
+  <si>
+    <t>67815</t>
+  </si>
+  <si>
+    <t>00394</t>
+  </si>
+  <si>
+    <t>05403</t>
+  </si>
+  <si>
+    <t>46088</t>
+  </si>
+  <si>
+    <t>14/09/26/12:30</t>
+  </si>
+  <si>
+    <t>83258</t>
+  </si>
+  <si>
+    <t>14/09/26/15:00</t>
+  </si>
+  <si>
+    <t>17570</t>
+  </si>
+  <si>
+    <t>33313</t>
   </si>
 </sst>
 </file>
@@ -32142,14 +32172,24 @@
     <row r="1313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1313" s="7"/>
       <c r="B1313" s="17"/>
-      <c r="C1313" s="2"/>
-      <c r="D1313" s="2"/>
-      <c r="E1313" s="2"/>
-      <c r="F1313" s="2"/>
+      <c r="C1313" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1313" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1313" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1313" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1313" s="2"/>
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1314" s="7"/>
+      <c r="A1314" s="40" t="s">
+        <v>2698</v>
+      </c>
       <c r="B1314" s="17"/>
       <c r="C1314" s="2"/>
       <c r="D1314" s="2"/>
@@ -32158,8 +32198,12 @@
       <c r="G1314" s="2"/>
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1315" s="7"/>
-      <c r="B1315" s="17"/>
+      <c r="A1315" s="7" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B1315" s="17">
+        <v>79183767815</v>
+      </c>
       <c r="C1315" s="2"/>
       <c r="D1315" s="2"/>
       <c r="E1315" s="2"/>
@@ -32167,8 +32211,9 @@
       <c r="G1315" s="2"/>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1316" s="7"/>
-      <c r="B1316" s="17"/>
+      <c r="A1316" s="40" t="s">
+        <v>2703</v>
+      </c>
       <c r="C1316" s="2"/>
       <c r="D1316" s="2"/>
       <c r="E1316" s="2"/>
@@ -32176,8 +32221,12 @@
       <c r="G1316" s="2"/>
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1317" s="7"/>
-      <c r="B1317" s="17"/>
+      <c r="A1317" s="7" t="s">
+        <v>2700</v>
+      </c>
+      <c r="B1317" s="17">
+        <v>79528700394</v>
+      </c>
       <c r="C1317" s="2"/>
       <c r="D1317" s="2"/>
       <c r="E1317" s="2"/>
@@ -32185,8 +32234,12 @@
       <c r="G1317" s="2"/>
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1318" s="7"/>
-      <c r="B1318" s="17"/>
+      <c r="A1318" s="7" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B1318" s="17">
+        <v>79054305403</v>
+      </c>
       <c r="C1318" s="2"/>
       <c r="D1318" s="2"/>
       <c r="E1318" s="2"/>
@@ -32194,8 +32247,12 @@
       <c r="G1318" s="2"/>
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1319" s="7"/>
-      <c r="B1319" s="17"/>
+      <c r="A1319" s="7" t="s">
+        <v>2702</v>
+      </c>
+      <c r="B1319" s="17">
+        <v>79064046088</v>
+      </c>
       <c r="C1319" s="2"/>
       <c r="D1319" s="2"/>
       <c r="E1319" s="2"/>
@@ -32203,8 +32260,12 @@
       <c r="G1319" s="2"/>
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1320" s="7"/>
-      <c r="B1320" s="17"/>
+      <c r="A1320" s="7" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B1320" s="17">
+        <v>79284483258</v>
+      </c>
       <c r="C1320" s="2"/>
       <c r="D1320" s="2"/>
       <c r="E1320" s="2"/>
@@ -32212,7 +32273,9 @@
       <c r="G1320" s="2"/>
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1321" s="7"/>
+      <c r="A1321" s="40" t="s">
+        <v>2705</v>
+      </c>
       <c r="B1321" s="17"/>
       <c r="C1321" s="2"/>
       <c r="D1321" s="2"/>
@@ -32221,18 +32284,24 @@
       <c r="G1321" s="2"/>
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1322" s="7"/>
-      <c r="B1322" s="17"/>
-      <c r="C1322" s="2"/>
+      <c r="A1322" s="7" t="s">
+        <v>2706</v>
+      </c>
+      <c r="B1322">
+        <v>79081817570</v>
+      </c>
       <c r="D1322" s="2"/>
       <c r="E1322" s="2"/>
       <c r="F1322" s="2"/>
       <c r="G1322" s="2"/>
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1323" s="7"/>
-      <c r="B1323" s="17"/>
-      <c r="C1323" s="2"/>
+      <c r="A1323" s="7" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B1323">
+        <v>79045033313</v>
+      </c>
       <c r="D1323" s="2"/>
       <c r="E1323" s="2"/>
       <c r="F1323" s="2"/>
@@ -32240,8 +32309,6 @@
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1324" s="7"/>
-      <c r="B1324" s="17"/>
-      <c r="C1324" s="2"/>
       <c r="D1324" s="2"/>
       <c r="E1324" s="2"/>
       <c r="F1324" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA33043-F04E-4B5D-99C0-8CEE660D1580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86D3B85-9F31-4365-BDED-9B3DB10CBAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4181" uniqueCount="2708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4192" uniqueCount="2716">
   <si>
     <t>Пароль</t>
   </si>
@@ -8158,6 +8158,30 @@
   </si>
   <si>
     <t>33313</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/hk6EMpC7P4E0Bw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/cYXpV2VFqwFMLg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/ZDjevD6mX2Luww</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/39jlmYAXMUCNvw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/ZqmFYitgM6LYRQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/fNX3bTxGntW17A</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/0OycK_Ox6bJKsA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/b_6pEh0bEqhgVQ</t>
   </si>
 </sst>
 </file>
@@ -32205,9 +32229,15 @@
         <v>79183767815</v>
       </c>
       <c r="C1315" s="2"/>
-      <c r="D1315" s="2"/>
-      <c r="E1315" s="2"/>
-      <c r="F1315" s="2"/>
+      <c r="D1315" s="2" t="s">
+        <v>2708</v>
+      </c>
+      <c r="E1315" s="2" t="s">
+        <v>2713</v>
+      </c>
+      <c r="F1315" s="2" t="s">
+        <v>2712</v>
+      </c>
       <c r="G1315" s="2"/>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
@@ -32227,7 +32257,9 @@
       <c r="B1317" s="17">
         <v>79528700394</v>
       </c>
-      <c r="C1317" s="2"/>
+      <c r="C1317" s="2" t="s">
+        <v>2710</v>
+      </c>
       <c r="D1317" s="2"/>
       <c r="E1317" s="2"/>
       <c r="F1317" s="2"/>
@@ -32240,7 +32272,9 @@
       <c r="B1318" s="17">
         <v>79054305403</v>
       </c>
-      <c r="C1318" s="2"/>
+      <c r="C1318" s="2" t="s">
+        <v>2710</v>
+      </c>
       <c r="D1318" s="2"/>
       <c r="E1318" s="2"/>
       <c r="F1318" s="2"/>
@@ -32254,7 +32288,9 @@
         <v>79064046088</v>
       </c>
       <c r="C1319" s="2"/>
-      <c r="D1319" s="2"/>
+      <c r="D1319" s="2" t="s">
+        <v>2709</v>
+      </c>
       <c r="E1319" s="2"/>
       <c r="F1319" s="2"/>
       <c r="G1319" s="2"/>
@@ -32266,8 +32302,12 @@
       <c r="B1320" s="17">
         <v>79284483258</v>
       </c>
-      <c r="C1320" s="2"/>
-      <c r="D1320" s="2"/>
+      <c r="C1320" s="2" t="s">
+        <v>2710</v>
+      </c>
+      <c r="D1320" s="2" t="s">
+        <v>2709</v>
+      </c>
       <c r="E1320" s="2"/>
       <c r="F1320" s="2"/>
       <c r="G1320" s="2"/>
@@ -32290,6 +32330,9 @@
       <c r="B1322">
         <v>79081817570</v>
       </c>
+      <c r="C1322" t="s">
+        <v>2711</v>
+      </c>
       <c r="D1322" s="2"/>
       <c r="E1322" s="2"/>
       <c r="F1322" s="2"/>
@@ -32303,8 +32346,12 @@
         <v>79045033313</v>
       </c>
       <c r="D1323" s="2"/>
-      <c r="E1323" s="2"/>
-      <c r="F1323" s="2"/>
+      <c r="E1323" s="2" t="s">
+        <v>2715</v>
+      </c>
+      <c r="F1323" s="2" t="s">
+        <v>2714</v>
+      </c>
       <c r="G1323" s="2"/>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86D3B85-9F31-4365-BDED-9B3DB10CBAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5354D0EF-52C6-49EE-8C81-A4B70DF17CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4192" uniqueCount="2716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4215" uniqueCount="2728">
   <si>
     <t>Пароль</t>
   </si>
@@ -8182,6 +8182,42 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/b_6pEh0bEqhgVQ</t>
+  </si>
+  <si>
+    <t>15/09/26/12:30</t>
+  </si>
+  <si>
+    <t>95666</t>
+  </si>
+  <si>
+    <t>48554</t>
+  </si>
+  <si>
+    <t>22752</t>
+  </si>
+  <si>
+    <t>16/09/26/10:00</t>
+  </si>
+  <si>
+    <t>33991</t>
+  </si>
+  <si>
+    <t>76368</t>
+  </si>
+  <si>
+    <t>16/09/26/12:30</t>
+  </si>
+  <si>
+    <t>71997</t>
+  </si>
+  <si>
+    <t>83714</t>
+  </si>
+  <si>
+    <t>93944</t>
+  </si>
+  <si>
+    <t>45546</t>
   </si>
 </sst>
 </file>
@@ -32355,41 +32391,69 @@
       <c r="G1323" s="2"/>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1324" s="7"/>
+      <c r="A1324" s="40" t="s">
+        <v>2716</v>
+      </c>
       <c r="D1324" s="2"/>
       <c r="E1324" s="2"/>
       <c r="F1324" s="2"/>
       <c r="G1324" s="2"/>
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1325" s="7"/>
-      <c r="B1325" s="17"/>
-      <c r="C1325" s="2"/>
+      <c r="A1325" s="7" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B1325" s="17">
+        <v>79186195666</v>
+      </c>
+      <c r="C1325" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="D1325" s="2"/>
-      <c r="E1325" s="2"/>
-      <c r="F1325" s="2"/>
+      <c r="E1325" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="F1325" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="G1325" s="2"/>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1326" s="7"/>
-      <c r="B1326" s="17"/>
+      <c r="A1326" s="7" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B1326" s="17">
+        <v>79780648554</v>
+      </c>
       <c r="C1326" s="2"/>
       <c r="D1326" s="2"/>
-      <c r="E1326" s="2"/>
-      <c r="F1326" s="2"/>
+      <c r="E1326" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="F1326" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="G1326" s="2"/>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1327" s="7"/>
-      <c r="B1327" s="17"/>
+      <c r="A1327" s="7" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B1327" s="17">
+        <v>79493022752</v>
+      </c>
       <c r="C1327" s="2"/>
-      <c r="D1327" s="2"/>
+      <c r="D1327" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="E1327" s="2"/>
       <c r="F1327" s="2"/>
       <c r="G1327" s="2"/>
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1328" s="7"/>
+      <c r="A1328" s="40" t="s">
+        <v>2720</v>
+      </c>
       <c r="B1328" s="17"/>
       <c r="C1328" s="2"/>
       <c r="D1328" s="2"/>
@@ -32398,17 +32462,27 @@
       <c r="G1328" s="2"/>
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1329" s="7"/>
-      <c r="B1329" s="17"/>
+      <c r="A1329" s="7" t="s">
+        <v>2721</v>
+      </c>
+      <c r="B1329" s="17">
+        <v>79085033991</v>
+      </c>
       <c r="C1329" s="2"/>
-      <c r="D1329" s="2"/>
+      <c r="D1329" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="E1329" s="2"/>
       <c r="F1329" s="2"/>
       <c r="G1329" s="2"/>
     </row>
     <row r="1330" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1330" s="7"/>
-      <c r="B1330" s="17"/>
+      <c r="A1330" s="7" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B1330" s="17">
+        <v>79282576368</v>
+      </c>
       <c r="C1330" s="2"/>
       <c r="D1330" s="2"/>
       <c r="E1330" s="2"/>
@@ -32416,7 +32490,9 @@
       <c r="G1330" s="2"/>
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1331" s="7"/>
+      <c r="A1331" s="40" t="s">
+        <v>2723</v>
+      </c>
       <c r="B1331" s="17"/>
       <c r="C1331" s="2"/>
       <c r="D1331" s="2"/>
@@ -32425,36 +32501,60 @@
       <c r="G1331" s="2"/>
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1332" s="7"/>
-      <c r="B1332" s="17"/>
-      <c r="C1332" s="2"/>
+      <c r="A1332" s="7" t="s">
+        <v>2724</v>
+      </c>
+      <c r="B1332" s="17">
+        <v>79054871997</v>
+      </c>
+      <c r="C1332" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="D1332" s="2"/>
       <c r="E1332" s="2"/>
       <c r="F1332" s="2"/>
       <c r="G1332" s="2"/>
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1333" s="7"/>
-      <c r="B1333" s="17"/>
+      <c r="A1333" s="7" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B1333" s="17">
+        <v>79193683714</v>
+      </c>
       <c r="C1333" s="2"/>
-      <c r="D1333" s="2"/>
+      <c r="D1333" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="E1333" s="2"/>
       <c r="F1333" s="2"/>
       <c r="G1333" s="2"/>
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1334" s="7"/>
-      <c r="B1334" s="17"/>
+      <c r="A1334" s="7" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B1334" s="17">
+        <v>79586493944</v>
+      </c>
       <c r="C1334" s="2"/>
-      <c r="D1334" s="2"/>
+      <c r="D1334" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="E1334" s="2"/>
       <c r="F1334" s="2"/>
       <c r="G1334" s="2"/>
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1335" s="7"/>
-      <c r="B1335" s="17"/>
-      <c r="C1335" s="2"/>
+      <c r="A1335" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="B1335" s="17">
+        <v>79780045546</v>
+      </c>
+      <c r="C1335" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="D1335" s="2"/>
       <c r="E1335" s="2"/>
       <c r="F1335" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF8143B-CBE2-4762-9AE1-29B03D315130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656B46BD-EE31-4C15-862E-705F01F4862E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8428" uniqueCount="2724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4214" uniqueCount="2732">
   <si>
     <t>Пароль</t>
   </si>
@@ -5295,9 +5295,6 @@
     <t>https://disk.yandex.ru/i/rbgqc_ta4pF-qg</t>
   </si>
   <si>
-    <t>53012</t>
-  </si>
-  <si>
     <t>20/08/26/10:00</t>
   </si>
   <si>
@@ -8206,6 +8203,33 @@
   </si>
   <si>
     <t>/?06758</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/fax7jYYqvSppAA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/A20SKLqnywkIwg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/IE_MZmonyocm-g</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/d3UTvbBpVHdgHA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/QrdUWpmS7gL1Hw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/5Fh_cRghsUflaA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/wznLDcPEZokKiQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/z3Hi2ecWsKhuUA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/P1cyniJFzuwCaw</t>
   </si>
 </sst>
 </file>
@@ -20459,7 +20483,7 @@
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" s="34" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="B646" s="35">
         <v>79263873911</v>
@@ -20475,7 +20499,7 @@
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" s="34" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="B647" s="35">
         <v>79384091479</v>
@@ -20491,7 +20515,7 @@
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" s="34" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B648" s="35">
         <v>79996939443</v>
@@ -20511,7 +20535,7 @@
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" s="19" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="B649" s="42">
         <v>79045249791</v>
@@ -20557,7 +20581,7 @@
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" s="34" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="B651" s="35">
         <v>79097598620</v>
@@ -20573,7 +20597,7 @@
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" s="34" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="B652" s="35">
         <v>79889439795</v>
@@ -20597,7 +20621,7 @@
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" s="34" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="B653" s="35">
         <v>79064143240</v>
@@ -20621,7 +20645,7 @@
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" s="34" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="B654" s="35">
         <v>79160773755</v>
@@ -20645,7 +20669,7 @@
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" s="34" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B655" s="35">
         <v>79265583230</v>
@@ -20669,7 +20693,7 @@
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" s="34" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="B656" s="35">
         <v>79198916190</v>
@@ -20687,7 +20711,7 @@
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" s="34" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="B657" s="35">
         <v>79094523993</v>
@@ -20707,7 +20731,7 @@
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" s="34" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="B658" s="35">
         <v>79275559989</v>
@@ -20727,7 +20751,7 @@
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" s="34" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B659" s="35">
         <v>79819649756</v>
@@ -20747,7 +20771,7 @@
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" s="34" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B660" s="35">
         <v>79275944640</v>
@@ -20767,7 +20791,7 @@
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" s="34" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="B661" s="35">
         <v>79286639177</v>
@@ -20811,7 +20835,7 @@
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" s="34" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B663" s="35">
         <v>79508413494</v>
@@ -20833,7 +20857,7 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" s="34" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B664" s="35">
         <v>79381137254</v>
@@ -20855,7 +20879,7 @@
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" s="34" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B665" s="35">
         <v>79186033939</v>
@@ -20877,7 +20901,7 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" s="34" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B666" s="35">
         <v>79189238531</v>
@@ -20899,7 +20923,7 @@
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" s="34" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B667" s="35">
         <v>79289686846</v>
@@ -20945,7 +20969,7 @@
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" s="34" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B669" s="35">
         <v>79881316452</v>
@@ -20961,7 +20985,7 @@
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" s="34" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B670" s="35">
         <v>79182136397</v>
@@ -20977,7 +21001,7 @@
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" s="34" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B671" s="35">
         <v>79185215394</v>
@@ -20993,7 +21017,7 @@
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" s="34" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B672" s="35">
         <v>79183508554</v>
@@ -21009,7 +21033,7 @@
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" s="19" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B673" s="42">
         <v>79883167580</v>
@@ -21027,7 +21051,7 @@
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" s="19" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B674" s="42">
         <v>79165690999</v>
@@ -21095,7 +21119,7 @@
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" s="34" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B677" s="41">
         <v>79081994332</v>
@@ -21111,7 +21135,7 @@
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" s="34" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B678" s="41">
         <v>79183168414</v>
@@ -21129,7 +21153,7 @@
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" s="34" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B679" s="41">
         <v>79187581965</v>
@@ -21145,7 +21169,7 @@
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" s="34" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B680" s="41">
         <v>79186240090</v>
@@ -21161,7 +21185,7 @@
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" s="34" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B681" s="41">
         <v>79034580987</v>
@@ -21177,7 +21201,7 @@
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" s="34" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B682" s="41">
         <v>79615252918</v>
@@ -21195,7 +21219,7 @@
     </row>
     <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" s="34" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B683" s="41">
         <v>79183178886</v>
@@ -21211,7 +21235,7 @@
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" s="34" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B684" s="41">
         <v>79183125885</v>
@@ -21229,7 +21253,7 @@
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" s="34" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B685" s="41">
         <v>79281924307</v>
@@ -21245,7 +21269,7 @@
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" s="34" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B686" s="41">
         <v>79180776694</v>
@@ -21261,7 +21285,7 @@
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" s="34" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B687" s="41">
         <v>79183201419</v>
@@ -21297,7 +21321,7 @@
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" s="34" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B689" s="41">
         <v>79183607310</v>
@@ -21313,7 +21337,7 @@
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A690" s="34" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B690" s="41">
         <v>79186874312</v>
@@ -21329,7 +21353,7 @@
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A691" s="34" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B691" s="41">
         <v>79604769229</v>
@@ -21347,7 +21371,7 @@
     </row>
     <row r="692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A692" s="34" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B692" s="41">
         <v>79034665752</v>
@@ -21365,7 +21389,7 @@
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" s="19" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B693" s="42">
         <v>79114539442</v>
@@ -21409,7 +21433,7 @@
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A695" s="34" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B695" s="41">
         <v>79255188793</v>
@@ -21429,7 +21453,7 @@
     </row>
     <row r="696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A696" s="34" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B696" s="41">
         <v>79185559591</v>
@@ -21447,7 +21471,7 @@
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" s="34" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B697" s="41">
         <v>79507592181</v>
@@ -21479,7 +21503,7 @@
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" s="34" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B699" s="41">
         <v>79200786301</v>
@@ -21495,7 +21519,7 @@
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A700" s="34" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B700" s="41">
         <v>79115503818</v>
@@ -21511,7 +21535,7 @@
     </row>
     <row r="701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A701" s="34" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B701" s="41">
         <v>79185024513</v>
@@ -21553,7 +21577,7 @@
     </row>
     <row r="703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A703" s="19" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B703" s="42">
         <v>79189161966</v>
@@ -21571,7 +21595,7 @@
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" s="34" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B704" s="41">
         <v>79185235426</v>
@@ -21587,7 +21611,7 @@
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" s="34" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B705" s="41">
         <v>79281427880</v>
@@ -21603,7 +21627,7 @@
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" s="34" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B706" s="41">
         <v>79689895325</v>
@@ -21619,7 +21643,7 @@
     </row>
     <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" s="34" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B707" s="41">
         <v>79054742719</v>
@@ -21637,7 +21661,7 @@
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" s="34" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B708" s="41">
         <v>79180269799</v>
@@ -21655,7 +21679,7 @@
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" s="34" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B709" s="41">
         <v>79129993888</v>
@@ -21697,7 +21721,7 @@
     </row>
     <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" s="34" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B711" s="41">
         <v>79284254870</v>
@@ -21715,7 +21739,7 @@
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" s="34" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B712" s="41">
         <v>79286257438</v>
@@ -21737,7 +21761,7 @@
     </row>
     <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" s="34" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B713" s="41">
         <v>79151193826</v>
@@ -21839,7 +21863,7 @@
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" s="34" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="B718" s="35">
         <v>79882471155</v>
@@ -21881,7 +21905,7 @@
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" s="34" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="B720" s="41">
         <v>79129386464</v>
@@ -21899,7 +21923,7 @@
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" s="34" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="B721" s="41">
         <v>79892622268</v>
@@ -21915,7 +21939,7 @@
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A722" s="34" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="B722" s="41">
         <v>79295621524</v>
@@ -21931,7 +21955,7 @@
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A723" s="34" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="B723" s="41">
         <v>79964053359</v>
@@ -21951,7 +21975,7 @@
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A724" s="34" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="B724" s="41">
         <v>79055976162</v>
@@ -21971,7 +21995,7 @@
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A725" s="34" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="B725" s="41">
         <v>79494308129</v>
@@ -21989,7 +22013,7 @@
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A726" s="34" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="B726" s="41">
         <v>79281088703</v>
@@ -22005,7 +22029,7 @@
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A727" s="34" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="B727" s="41">
         <v>79184357363</v>
@@ -22045,7 +22069,7 @@
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A729" s="34" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="B729" s="41">
         <v>79180215006</v>
@@ -22063,7 +22087,7 @@
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A730" s="34" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="B730" s="41">
         <v>79186207263</v>
@@ -22083,7 +22107,7 @@
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A731" s="34" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="B731" s="41">
         <v>79167870593</v>
@@ -22101,7 +22125,7 @@
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A732" s="34" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="B732" s="41">
         <v>79175018147</v>
@@ -22119,7 +22143,7 @@
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A733" s="34" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="B733" s="41">
         <v>79821035052</v>
@@ -22137,7 +22161,7 @@
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A734" s="34" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="B734" s="41">
         <v>79628563044</v>
@@ -22155,7 +22179,7 @@
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A735" s="34" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="B735" s="41">
         <v>79044540208</v>
@@ -22195,14 +22219,14 @@
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A737" s="34" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="B737" s="41">
         <v>79284321002</v>
       </c>
       <c r="C737" s="33"/>
       <c r="D737" s="33" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E737" s="33"/>
       <c r="F737" s="33"/>
@@ -22211,7 +22235,7 @@
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A738" s="34" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="B738" s="41">
         <v>79034020303</v>
@@ -22233,7 +22257,7 @@
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A739" s="34" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="B739" s="41">
         <v>79192264623</v>
@@ -22255,7 +22279,7 @@
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A740" s="34" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="B740" s="41">
         <v>79086846536</v>
@@ -22271,7 +22295,7 @@
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A741" s="34" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B741" s="41">
         <v>79002293262</v>
@@ -22287,7 +22311,7 @@
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A742" s="34" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="B742" s="41">
         <v>79287714786</v>
@@ -22303,7 +22327,7 @@
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A743" s="34" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="B743" s="41">
         <v>79102888222</v>
@@ -22319,7 +22343,7 @@
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A744" s="34" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="B744" s="41">
         <v>79897292002</v>
@@ -22335,7 +22359,7 @@
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A745" s="34" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="B745" s="41">
         <v>79787641608</v>
@@ -22357,7 +22381,7 @@
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A746" s="34" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="B746" s="41">
         <v>79898090353</v>
@@ -22379,7 +22403,7 @@
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A747" s="34" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="B747" s="41">
         <v>79282045454</v>
@@ -22401,7 +22425,7 @@
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A748" s="34" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="B748" s="41">
         <v>79198999382</v>
@@ -22423,7 +22447,7 @@
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" s="19" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="B749" s="42">
         <v>79494022984</v>
@@ -22483,7 +22507,7 @@
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A752" s="34" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="B752" s="41">
         <v>79809565909</v>
@@ -22501,7 +22525,7 @@
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" s="34" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="B753" s="41">
         <v>79536931038</v>
@@ -22523,7 +22547,7 @@
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" s="34" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="B754" s="41">
         <v>79182668274</v>
@@ -22545,7 +22569,7 @@
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" s="34" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="B755" s="41">
         <v>79183223371</v>
@@ -22563,7 +22587,7 @@
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756" s="34" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="B756" s="41">
         <v>79180909877</v>
@@ -22579,7 +22603,7 @@
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" s="34" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="B757" s="41">
         <v>79284631547</v>
@@ -22595,7 +22619,7 @@
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758" s="34" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="B758" s="41">
         <v>79282964632</v>
@@ -22611,7 +22635,7 @@
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759" s="34" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="B759" s="41">
         <v>79284686689</v>
@@ -22629,7 +22653,7 @@
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760" s="34" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="B760" s="41">
         <v>79881443000</v>
@@ -22645,7 +22669,7 @@
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" s="34" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="B761" s="41">
         <v>79284676296</v>
@@ -22665,7 +22689,7 @@
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762" s="34" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="B762" s="41">
         <v>79178319149</v>
@@ -22685,7 +22709,7 @@
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A763" s="34" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="B763" s="41">
         <v>79180111275</v>
@@ -22725,7 +22749,7 @@
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A765" s="34" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B765" s="41">
         <v>79185464331</v>
@@ -22741,7 +22765,7 @@
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A766" s="34" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="B766" s="41">
         <v>79508616872</v>
@@ -22763,7 +22787,7 @@
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A767" s="34" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="B767" s="41">
         <v>79250059441</v>
@@ -22785,7 +22809,7 @@
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A768" s="34" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="B768" s="41">
         <v>79183770735</v>
@@ -22801,7 +22825,7 @@
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A769" s="34" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B769" s="41">
         <v>79200786301</v>
@@ -22817,7 +22841,7 @@
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A770" s="34" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="B770" s="41">
         <v>79652492835</v>
@@ -22833,7 +22857,7 @@
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A771" s="34" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B771" s="41">
         <v>79162413260</v>
@@ -22851,7 +22875,7 @@
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A772" s="34" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="B772" s="41">
         <v>79281840365</v>
@@ -22885,7 +22909,7 @@
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A774" s="34" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B774" s="41">
         <v>79499830150</v>
@@ -22901,7 +22925,7 @@
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A775" s="34" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="B775" s="41">
         <v>79816830576</v>
@@ -22977,7 +23001,7 @@
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A779" s="34" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="B779" s="41">
         <v>79184473949</v>
@@ -22993,7 +23017,7 @@
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A780" s="34" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="B780" s="41">
         <v>79184360516</v>
@@ -23009,7 +23033,7 @@
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A781" s="34" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B781" s="41">
         <v>79615052548</v>
@@ -23043,7 +23067,7 @@
     </row>
     <row r="783" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A783" s="34" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="B783" s="41">
         <v>79169129452</v>
@@ -23065,7 +23089,7 @@
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A784" s="34" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="B784" s="41">
         <v>79381758949</v>
@@ -23087,7 +23111,7 @@
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" s="34" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="B785" s="41">
         <v>79286224084</v>
@@ -23103,7 +23127,7 @@
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" s="34" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="B786" s="41">
         <v>79189570316</v>
@@ -23125,7 +23149,7 @@
     </row>
     <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" s="34" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="B787" s="41">
         <v>79883476214</v>
@@ -23147,7 +23171,7 @@
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A788" s="34" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="B788" s="41">
         <v>79184373292</v>
@@ -23163,7 +23187,7 @@
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A789" s="34" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="B789" s="41">
         <v>79770611885</v>
@@ -23179,7 +23203,7 @@
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A790" s="34" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="B790" s="41">
         <v>79180818508</v>
@@ -23219,7 +23243,7 @@
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" s="34" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="B792" s="41">
         <v>79090535020</v>
@@ -23235,7 +23259,7 @@
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A793" s="34" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="B793" s="41">
         <v>79615006915</v>
@@ -23251,7 +23275,7 @@
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" s="34" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="B794" s="41">
         <v>79628530371</v>
@@ -23269,7 +23293,7 @@
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" s="34" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="B795" s="41">
         <v>79184279501</v>
@@ -23285,7 +23309,7 @@
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" s="34" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="B796" s="41">
         <v>79002614878</v>
@@ -23303,7 +23327,7 @@
     </row>
     <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" s="34" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="B797" s="41">
         <v>79154071725</v>
@@ -23321,7 +23345,7 @@
     </row>
     <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" s="34" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B798" s="41">
         <v>79183281110</v>
@@ -23343,7 +23367,7 @@
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" s="34" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B799" s="41">
         <v>79896303777</v>
@@ -23365,7 +23389,7 @@
     </row>
     <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" s="34" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B800" s="41">
         <v>79515542260</v>
@@ -23387,7 +23411,7 @@
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" s="34" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="B801" s="41">
         <v>79109409590</v>
@@ -23405,7 +23429,7 @@
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" s="34" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="B802" s="41">
         <v>79184692981</v>
@@ -23423,7 +23447,7 @@
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" s="34" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="B803" s="41">
         <v>79091661065</v>
@@ -23443,7 +23467,7 @@
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" s="19" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B804" s="42">
         <v>79161635439</v>
@@ -23461,7 +23485,7 @@
     </row>
     <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" s="19" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B805" s="42">
         <v>79085008025</v>
@@ -23477,7 +23501,7 @@
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" s="19" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="B806" s="42">
         <v>79252655620</v>
@@ -23493,7 +23517,7 @@
     </row>
     <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" s="19" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B807" s="42">
         <v>79892958854</v>
@@ -23573,7 +23597,7 @@
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" s="34" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B811" s="41">
         <v>79281983701</v>
@@ -23591,7 +23615,7 @@
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" s="34" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="B812" s="41">
         <v>79779823186</v>
@@ -23609,7 +23633,7 @@
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" s="34" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B813" s="41">
         <v>79262171635</v>
@@ -23627,7 +23651,7 @@
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" s="34" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="B814" s="41">
         <v>79268883600</v>
@@ -23645,7 +23669,7 @@
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" s="34" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="B815" s="41">
         <v>79171859656</v>
@@ -23663,7 +23687,7 @@
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" s="34" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="B816" s="41">
         <v>79185600417</v>
@@ -23681,7 +23705,7 @@
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" s="34" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="B817" s="41">
         <v>79602752962</v>
@@ -23697,7 +23721,7 @@
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" s="34" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="B818" s="41">
         <v>79184482714</v>
@@ -23713,7 +23737,7 @@
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" s="34" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="B819" s="41">
         <v>79284144391</v>
@@ -23729,7 +23753,7 @@
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" s="34" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="B820" s="41">
         <v>79189225377</v>
@@ -23745,7 +23769,7 @@
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" s="34" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="B821" s="41">
         <v>79281043723</v>
@@ -23763,7 +23787,7 @@
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" s="34" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="B822" s="41">
         <v>79282794857</v>
@@ -23781,7 +23805,7 @@
     </row>
     <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" s="34" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="B823" s="41">
         <v>79284072814</v>
@@ -23799,7 +23823,7 @@
     </row>
     <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" s="34" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="B824" s="41">
         <v>79493721137</v>
@@ -23817,7 +23841,7 @@
     </row>
     <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" s="34" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="B825" s="41">
         <v>79648832641</v>
@@ -23859,7 +23883,7 @@
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" s="34" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="B827" s="41">
         <v>79187552473</v>
@@ -23875,7 +23899,7 @@
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" s="34" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="B828" s="41">
         <v>79189222000</v>
@@ -23891,7 +23915,7 @@
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" s="34" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="B829" s="41">
         <v>79853876186</v>
@@ -23909,7 +23933,7 @@
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" s="34" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="B830" s="41">
         <v>79270624682</v>
@@ -23927,7 +23951,7 @@
     </row>
     <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" s="34" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="B831" s="41">
         <v>79522284007</v>
@@ -23945,7 +23969,7 @@
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" s="34" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="B832" s="41">
         <v>79884095007</v>
@@ -23963,7 +23987,7 @@
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" s="34" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="B833" s="41">
         <v>79891200614</v>
@@ -23979,7 +24003,7 @@
     </row>
     <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" s="34" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="B834" s="41">
         <v>79189377109</v>
@@ -23995,7 +24019,7 @@
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" s="34" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="B835" s="41">
         <v>79289606020</v>
@@ -24011,7 +24035,7 @@
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" s="34" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="B836" s="41">
         <v>79618431980</v>
@@ -24051,7 +24075,7 @@
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" s="34" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="B838" s="41">
         <v>79192492486</v>
@@ -24059,7 +24083,7 @@
       <c r="C838" s="33"/>
       <c r="D838" s="33"/>
       <c r="E838" s="33" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F838" s="33" t="s">
         <v>1341</v>
@@ -24069,14 +24093,14 @@
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" s="34" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="B839" s="41">
         <v>79182131150</v>
       </c>
       <c r="C839" s="33"/>
       <c r="D839" s="33" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="E839" s="33"/>
       <c r="F839" s="33"/>
@@ -24085,17 +24109,17 @@
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" s="34" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="B840" s="41">
         <v>79275956177</v>
       </c>
       <c r="C840" s="33" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="D840" s="33"/>
       <c r="E840" s="33" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="F840" s="33" t="s">
         <v>1342</v>
@@ -24105,17 +24129,17 @@
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" s="34" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="B841" s="41">
         <v>79789283600</v>
       </c>
       <c r="C841" s="33" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="D841" s="33"/>
       <c r="E841" s="33" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="F841" s="33" t="s">
         <v>1342</v>
@@ -24125,14 +24149,14 @@
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" s="34" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="B842" s="41">
         <v>79851997751</v>
       </c>
       <c r="C842" s="33"/>
       <c r="D842" s="33" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="E842" s="33"/>
       <c r="F842" s="33"/>
@@ -24141,14 +24165,14 @@
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" s="34" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="B843" s="41">
         <v>79282164434</v>
       </c>
       <c r="C843" s="33"/>
       <c r="D843" s="33" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="E843" s="33"/>
       <c r="F843" s="33"/>
@@ -24157,14 +24181,14 @@
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" s="34" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="B844" s="41">
         <v>79109617700</v>
       </c>
       <c r="C844" s="33"/>
       <c r="D844" s="33" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="E844" s="33"/>
       <c r="F844" s="33"/>
@@ -24203,11 +24227,11 @@
         <v>79898150360</v>
       </c>
       <c r="C846" s="33" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="D846" s="33"/>
       <c r="E846" s="33" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="F846" s="33" t="s">
         <v>1370</v>
@@ -24217,19 +24241,19 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" s="34" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="B847" s="41">
         <v>79185972895</v>
       </c>
       <c r="C847" s="33" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="D847" s="33" t="s">
         <v>1365</v>
       </c>
       <c r="E847" s="33" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="F847" s="33" t="s">
         <v>1368</v>
@@ -24239,7 +24263,7 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" s="34" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="B848" s="41">
         <v>79996262825</v>
@@ -24248,7 +24272,7 @@
         <v>1377</v>
       </c>
       <c r="D848" s="33" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="E848" s="33" t="s">
         <v>1371</v>
@@ -24261,7 +24285,7 @@
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" s="34" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="B849" s="41">
         <v>79851997751</v>
@@ -24270,7 +24294,7 @@
         <v>1377</v>
       </c>
       <c r="D849" s="33" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="E849" s="33" t="s">
         <v>1371</v>
@@ -24283,13 +24307,13 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" s="34" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="B850" s="41">
         <v>79604875670</v>
       </c>
       <c r="C850" s="33" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="D850" s="33" t="s">
         <v>1365</v>
@@ -24305,16 +24329,16 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" s="34" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="B851" s="41">
         <v>79184987541</v>
       </c>
       <c r="C851" s="33" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D851" s="33" t="s">
         <v>2203</v>
-      </c>
-      <c r="D851" s="33" t="s">
-        <v>2204</v>
       </c>
       <c r="E851" s="33"/>
       <c r="F851" s="33"/>
@@ -24323,14 +24347,14 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" s="34" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="B852" s="41">
         <v>79185058918</v>
       </c>
       <c r="C852" s="33"/>
       <c r="D852" s="33" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="E852" s="33"/>
       <c r="F852" s="33"/>
@@ -24339,17 +24363,17 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" s="34" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="B853" s="41">
         <v>79084845045</v>
       </c>
       <c r="C853" s="33"/>
       <c r="D853" s="33" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="E853" s="33" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="F853" s="33" t="s">
         <v>1372</v>
@@ -24359,13 +24383,13 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" s="34" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="B854" s="41">
         <v>79189841111</v>
       </c>
       <c r="C854" s="33" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D854" s="33"/>
       <c r="E854" s="33"/>
@@ -24375,19 +24399,19 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" s="34" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="B855" s="41">
         <v>79183593299</v>
       </c>
       <c r="C855" s="33" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D855" s="33" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="E855" s="33" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="F855" s="33" t="s">
         <v>1373</v>
@@ -24397,7 +24421,7 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" s="34" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="B856" s="41">
         <v>79286104433</v>
@@ -24406,7 +24430,7 @@
         <v>1378</v>
       </c>
       <c r="D856" s="33" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="E856" s="33"/>
       <c r="F856" s="33"/>
@@ -24415,13 +24439,13 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" s="34" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="B857" s="41">
         <v>79181204920</v>
       </c>
       <c r="C857" s="33" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D857" s="33" t="s">
         <v>1366</v>
@@ -24433,13 +24457,13 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" s="34" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="B858" s="41">
         <v>79180314664</v>
       </c>
       <c r="C858" s="33" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D858" s="33" t="s">
         <v>1367</v>
@@ -24451,7 +24475,7 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" s="34" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B859" s="41">
         <v>79255304182</v>
@@ -24460,7 +24484,7 @@
         <v>1378</v>
       </c>
       <c r="D859" s="33" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="E859" s="33"/>
       <c r="F859" s="33"/>
@@ -24469,13 +24493,13 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" s="34" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="B860" s="41">
         <v>79624321777</v>
       </c>
       <c r="C860" s="33" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D860" s="33" t="s">
         <v>1367</v>
@@ -24487,13 +24511,13 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" s="34" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="B861" s="41">
         <v>79034652185</v>
       </c>
       <c r="C861" s="33" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D861" s="33"/>
       <c r="E861" s="33"/>
@@ -24503,14 +24527,14 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" s="34" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="B862" s="41">
         <v>79654707870</v>
       </c>
       <c r="C862" s="33"/>
       <c r="D862" s="33" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="E862" s="33"/>
       <c r="F862" s="33"/>
@@ -24527,7 +24551,7 @@
       <c r="C863" s="33"/>
       <c r="D863" s="33"/>
       <c r="E863" s="33" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="F863" s="33" t="s">
         <v>1376</v>
@@ -24537,7 +24561,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" s="34" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="B864" s="41">
         <v>79284244414</v>
@@ -24547,7 +24571,7 @@
       </c>
       <c r="D864" s="33"/>
       <c r="E864" s="33" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="F864" s="33" t="s">
         <v>1374</v>
@@ -24557,17 +24581,17 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" s="34" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="B865" s="41">
         <v>79619719206</v>
       </c>
       <c r="C865" s="33" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="D865" s="33"/>
       <c r="E865" s="33" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="F865" s="33" t="s">
         <v>1375</v>
@@ -24577,7 +24601,7 @@
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" s="34" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="B866" s="41">
         <v>79530872704</v>
@@ -24586,10 +24610,10 @@
         <v>1379</v>
       </c>
       <c r="D866" s="33" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="E866" s="33" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="F866" s="33" t="s">
         <v>1375</v>
@@ -24605,10 +24629,10 @@
         <v>79187698925</v>
       </c>
       <c r="C867" s="33" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="D867" s="33" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="E867" s="33"/>
       <c r="F867" s="33"/>
@@ -24623,7 +24647,7 @@
         <v>79807420215</v>
       </c>
       <c r="C868" s="33" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="D868" s="33"/>
       <c r="E868" s="33"/>
@@ -24633,16 +24657,16 @@
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" s="34" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="B869" s="41">
         <v>79181112526</v>
       </c>
       <c r="C869" s="33" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D869" s="33" t="s">
         <v>1775</v>
-      </c>
-      <c r="D869" s="33" t="s">
-        <v>1776</v>
       </c>
       <c r="E869" s="33"/>
       <c r="F869" s="33"/>
@@ -24651,7 +24675,7 @@
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" s="19" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="B870" s="42">
         <v>79186726140</v>
@@ -24691,16 +24715,16 @@
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" s="34" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="B872" s="41">
         <v>79283003384</v>
       </c>
       <c r="C872" s="33" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D872" s="33" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="E872" s="33"/>
       <c r="F872" s="33"/>
@@ -24709,14 +24733,14 @@
     </row>
     <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" s="34" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="B873" s="41">
         <v>79682666663</v>
       </c>
       <c r="C873" s="33"/>
       <c r="D873" s="33" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="E873" s="33"/>
       <c r="F873" s="33"/>
@@ -24725,16 +24749,16 @@
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" s="34" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="B874" s="41">
         <v>79186726140</v>
       </c>
       <c r="C874" s="33" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="D874" s="33" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="E874" s="33"/>
       <c r="F874" s="33"/>
@@ -24743,16 +24767,16 @@
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" s="34" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="B875" s="41">
         <v>79898051733</v>
       </c>
       <c r="C875" s="33" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="D875" s="33" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="E875" s="33"/>
       <c r="F875" s="33"/>
@@ -24761,13 +24785,13 @@
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" s="34" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="B876" s="41">
         <v>79086789121</v>
       </c>
       <c r="C876" s="33" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="D876" s="33"/>
       <c r="E876" s="33"/>
@@ -24777,13 +24801,13 @@
     </row>
     <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" s="34" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="B877" s="41">
         <v>79528340083</v>
       </c>
       <c r="C877" s="33" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="D877" s="33"/>
       <c r="E877" s="33"/>
@@ -24793,16 +24817,16 @@
     </row>
     <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" s="34" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="B878" s="41">
         <v>79530930717</v>
       </c>
       <c r="C878" s="33" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="D878" s="33" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="E878" s="33"/>
       <c r="F878" s="33"/>
@@ -24811,14 +24835,14 @@
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" s="34" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="B879" s="41">
         <v>79275037361</v>
       </c>
       <c r="C879" s="33"/>
       <c r="D879" s="33" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="E879" s="33"/>
       <c r="F879" s="33"/>
@@ -24827,14 +24851,14 @@
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" s="34" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="B880" s="41">
         <v>79218083526</v>
       </c>
       <c r="C880" s="33"/>
       <c r="D880" s="33" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="E880" s="33"/>
       <c r="F880" s="33"/>
@@ -24843,17 +24867,17 @@
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" s="34" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="B881" s="41">
         <v>79185789000</v>
       </c>
       <c r="C881" s="33"/>
       <c r="D881" s="33" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="E881" s="33" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="F881" s="33" t="s">
         <v>1476</v>
@@ -24863,7 +24887,7 @@
     </row>
     <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" s="34" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="B882" s="41">
         <v>79877941509</v>
@@ -24871,7 +24895,7 @@
       <c r="C882" s="33"/>
       <c r="D882" s="33"/>
       <c r="E882" s="33" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="F882" s="33" t="s">
         <v>1477</v>
@@ -24881,14 +24905,14 @@
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" s="34" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="B883" s="41">
         <v>79618221503</v>
       </c>
       <c r="C883" s="33"/>
       <c r="D883" s="33" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="E883" s="33"/>
       <c r="F883" s="33"/>
@@ -24921,7 +24945,7 @@
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" s="34" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="B885" s="41">
         <v>79882548579</v>
@@ -24929,7 +24953,7 @@
       <c r="C885" s="33"/>
       <c r="D885" s="33"/>
       <c r="E885" s="33" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="F885" s="33" t="s">
         <v>1479</v>
@@ -24939,14 +24963,14 @@
     </row>
     <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" s="34" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B886" s="41">
         <v>79182900595</v>
       </c>
       <c r="C886" s="33"/>
       <c r="D886" s="33" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="E886" s="33"/>
       <c r="F886" s="33"/>
@@ -24955,13 +24979,13 @@
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" s="34" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B887" s="41">
         <v>79264823431</v>
       </c>
       <c r="C887" s="33" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="D887" s="33" t="s">
         <v>1480</v>
@@ -24973,13 +24997,13 @@
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" s="34" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B888" s="41">
         <v>79180246728</v>
       </c>
       <c r="C888" s="33" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="D888" s="33" t="s">
         <v>1480</v>
@@ -24991,13 +25015,13 @@
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" s="34" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="B889" s="41">
         <v>79263181485</v>
       </c>
       <c r="C889" s="33" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="D889" s="33"/>
       <c r="E889" s="33"/>
@@ -25007,13 +25031,13 @@
     </row>
     <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" s="34" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="B890" s="41">
         <v>79189573595</v>
       </c>
       <c r="C890" s="33" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="D890" s="33" t="s">
         <v>1481</v>
@@ -25025,7 +25049,7 @@
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" s="34" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B891" s="41">
         <v>79180129312</v>
@@ -25034,7 +25058,7 @@
         <v>1482</v>
       </c>
       <c r="D891" s="33" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="E891" s="33"/>
       <c r="F891" s="33"/>
@@ -25065,7 +25089,7 @@
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" s="34" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B893" s="41">
         <v>79207020082</v>
@@ -25077,7 +25101,7 @@
         <v>1491</v>
       </c>
       <c r="E893" s="33" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="F893" s="33" t="s">
         <v>1484</v>
@@ -25087,7 +25111,7 @@
     </row>
     <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" s="34" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="B894" s="41">
         <v>79185072237</v>
@@ -25096,7 +25120,7 @@
         <v>1492</v>
       </c>
       <c r="D894" s="33" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="E894" s="33"/>
       <c r="F894" s="33"/>
@@ -25105,13 +25129,13 @@
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" s="34" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="B895" s="41">
         <v>79182762440</v>
       </c>
       <c r="C895" s="33" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="D895" s="33"/>
       <c r="E895" s="33"/>
@@ -25121,13 +25145,13 @@
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" s="34" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="B896" s="41">
         <v>79518702052</v>
       </c>
       <c r="C896" s="33" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="D896" s="33"/>
       <c r="E896" s="33"/>
@@ -25137,13 +25161,13 @@
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" s="34" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="B897" s="41">
         <v>79885456732</v>
       </c>
       <c r="C897" s="33" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="D897" s="33"/>
       <c r="E897" s="33"/>
@@ -25153,7 +25177,7 @@
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" s="34" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="B898" s="41">
         <v>79186323631</v>
@@ -25162,7 +25186,7 @@
         <v>1490</v>
       </c>
       <c r="D898" s="33" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="E898" s="33"/>
       <c r="F898" s="33"/>
@@ -25177,11 +25201,11 @@
         <v>79608666999</v>
       </c>
       <c r="C899" s="33" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="D899" s="33"/>
       <c r="E899" s="33" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="F899" s="33" t="s">
         <v>1487</v>
@@ -25191,13 +25215,13 @@
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" s="34" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="B900" s="41">
         <v>79604946540</v>
       </c>
       <c r="C900" s="33" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="D900" s="33"/>
       <c r="E900" s="33" t="s">
@@ -25211,7 +25235,7 @@
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" s="34" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="B901" s="41">
         <v>79787713176</v>
@@ -25220,7 +25244,7 @@
         <v>1492</v>
       </c>
       <c r="D901" s="33" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E901" s="33" t="s">
         <v>1486</v>
@@ -25255,13 +25279,13 @@
     </row>
     <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" s="34" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="B903" s="41">
         <v>79881380533</v>
       </c>
       <c r="C903" s="33" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="D903" s="33"/>
       <c r="E903" s="33"/>
@@ -25271,19 +25295,19 @@
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" s="34" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="B904" s="41">
         <v>79876571770</v>
       </c>
       <c r="C904" s="33" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="D904" s="33" t="s">
         <v>1505</v>
       </c>
       <c r="E904" s="33" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="F904" s="33" t="s">
         <v>1496</v>
@@ -25293,7 +25317,7 @@
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" s="34" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="B905" s="41">
         <v>79185269969</v>
@@ -25305,7 +25329,7 @@
         <v>1505</v>
       </c>
       <c r="E905" s="33" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="F905" s="33" t="s">
         <v>1496</v>
@@ -25315,19 +25339,19 @@
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" s="34" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="B906" s="41">
         <v>79788069407</v>
       </c>
       <c r="C906" s="33" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="D906" s="33" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="E906" s="33" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="F906" s="33" t="s">
         <v>1496</v>
@@ -25337,19 +25361,19 @@
     </row>
     <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" s="34" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B907" s="41">
         <v>79809148895</v>
       </c>
       <c r="C907" s="33" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="D907" s="33" t="s">
         <v>1504</v>
       </c>
       <c r="E907" s="33" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="F907" s="33" t="s">
         <v>1494</v>
@@ -25359,7 +25383,7 @@
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" s="34" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="B908" s="41">
         <v>79374600054</v>
@@ -25368,7 +25392,7 @@
         <v>1503</v>
       </c>
       <c r="D908" s="33" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="E908" s="33"/>
       <c r="F908" s="33" t="s">
@@ -25385,7 +25409,7 @@
         <v>79852254751</v>
       </c>
       <c r="C909" s="33" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="D909" s="33" t="s">
         <v>1502</v>
@@ -25397,7 +25421,7 @@
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" s="34" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="B910" s="41">
         <v>79063480196</v>
@@ -25406,7 +25430,7 @@
         <v>1503</v>
       </c>
       <c r="D910" s="33" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="E910" s="33"/>
       <c r="F910" s="33"/>
@@ -25415,17 +25439,17 @@
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" s="34" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="B911" s="41">
         <v>79035002052</v>
       </c>
       <c r="C911" s="33"/>
       <c r="D911" s="33" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="E911" s="33" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="F911" s="33" t="s">
         <v>1497</v>
@@ -25435,14 +25459,14 @@
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" s="34" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="B912" s="41">
         <v>79883667602</v>
       </c>
       <c r="C912" s="33"/>
       <c r="D912" s="33" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="E912" s="33" t="s">
         <v>1499</v>
@@ -25455,7 +25479,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A913" s="34" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="B913" s="41">
         <v>79991733748</v>
@@ -25463,7 +25487,7 @@
       <c r="C913" s="33"/>
       <c r="D913" s="33"/>
       <c r="E913" s="33" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="F913" s="33"/>
       <c r="G913" s="33"/>
@@ -25471,17 +25495,17 @@
     </row>
     <row r="914" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A914" s="34" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="B914" s="41">
         <v>79168542102</v>
       </c>
       <c r="C914" s="33" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="D914" s="33"/>
       <c r="E914" s="33" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="F914" s="33" t="s">
         <v>1500</v>
@@ -25491,17 +25515,17 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A915" s="34" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B915" s="41">
         <v>79888928388</v>
       </c>
       <c r="C915" s="33" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="D915" s="33"/>
       <c r="E915" s="33" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="F915" s="33" t="s">
         <v>1500</v>
@@ -25511,17 +25535,17 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A916" s="34" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="B916" s="41">
         <v>79032374317</v>
       </c>
       <c r="C916" s="33" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="D916" s="33"/>
       <c r="E916" s="33" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="F916" s="33" t="s">
         <v>1501</v>
@@ -25553,7 +25577,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A918" s="34" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B918" s="41">
         <v>79207020082</v>
@@ -25562,7 +25586,7 @@
         <v>1508</v>
       </c>
       <c r="D918" s="33" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="E918" s="33"/>
       <c r="F918" s="33"/>
@@ -25576,13 +25600,13 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A919" s="34" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="B919" s="41">
         <v>79041183867</v>
       </c>
       <c r="C919" s="33" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="D919" s="33"/>
       <c r="E919" s="33"/>
@@ -25597,13 +25621,13 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A920" s="34" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="B920" s="41">
         <v>79032978483</v>
       </c>
       <c r="C920" s="33" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="D920" s="33"/>
       <c r="E920" s="33"/>
@@ -25618,7 +25642,7 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A921" s="34" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="B921" s="41">
         <v>79308038836</v>
@@ -25627,7 +25651,7 @@
         <v>1508</v>
       </c>
       <c r="D921" s="33" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="E921" s="33"/>
       <c r="F921" s="33"/>
@@ -25641,7 +25665,7 @@
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A922" s="34" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="B922" s="41">
         <v>79385488845</v>
@@ -25650,7 +25674,7 @@
         <v>1508</v>
       </c>
       <c r="D922" s="33" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="E922" s="33"/>
       <c r="F922" s="33"/>
@@ -25664,13 +25688,13 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A923" s="34" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="B923" s="41">
         <v>79046838139</v>
       </c>
       <c r="C923" s="33" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="D923" s="33"/>
       <c r="E923" s="33"/>
@@ -25685,16 +25709,16 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A924" s="34" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="B924" s="41">
         <v>79128268207</v>
       </c>
       <c r="C924" s="33" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="D924" s="33" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="E924" s="33"/>
       <c r="F924" s="33"/>
@@ -25708,7 +25732,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A925" s="34" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="B925" s="41">
         <v>79148261215</v>
@@ -25717,7 +25741,7 @@
         <v>1507</v>
       </c>
       <c r="D925" s="33" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="E925" s="33"/>
       <c r="F925" s="33"/>
@@ -25731,14 +25755,14 @@
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A926" s="34" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B926" s="41">
         <v>79267823227</v>
       </c>
       <c r="C926" s="33"/>
       <c r="D926" s="33" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="E926" s="33"/>
       <c r="F926" s="33"/>
@@ -25752,17 +25776,17 @@
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A927" s="34" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="B927" s="41">
         <v>79184915237</v>
       </c>
       <c r="C927" s="33"/>
       <c r="D927" s="33" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="E927" s="33" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="F927" s="33" t="s">
         <v>1509</v>
@@ -25777,17 +25801,17 @@
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A928" s="34" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B928" s="41">
         <v>79034390003</v>
       </c>
       <c r="C928" s="33"/>
       <c r="D928" s="33" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="E928" s="33" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F928" s="33" t="s">
         <v>1510</v>
@@ -25824,13 +25848,13 @@
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" s="34" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="B930" s="41">
         <v>79595062068</v>
       </c>
       <c r="C930" s="33" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="D930" s="33"/>
       <c r="E930" s="33"/>
@@ -25866,11 +25890,11 @@
         <v>79184277066</v>
       </c>
       <c r="C932" s="33" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D932" s="33"/>
       <c r="E932" s="33" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="F932" s="33" t="s">
         <v>1596</v>
@@ -25880,7 +25904,7 @@
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" s="34" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="B933" s="41">
         <v>79180664535</v>
@@ -25888,7 +25912,7 @@
       <c r="C933" s="33"/>
       <c r="D933" s="33"/>
       <c r="E933" s="33" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="F933" s="33" t="s">
         <v>1597</v>
@@ -25898,17 +25922,17 @@
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" s="34" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="B934" s="41">
         <v>79197382450</v>
       </c>
       <c r="C934" s="33"/>
       <c r="D934" s="33" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="E934" s="33" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="F934" s="33" t="s">
         <v>1598</v>
@@ -25918,19 +25942,19 @@
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" s="34" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="B935" s="41">
         <v>79885220528</v>
       </c>
       <c r="C935" s="33" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="D935" s="33" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="E935" s="33" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="F935" s="33" t="s">
         <v>1601</v>
@@ -25940,7 +25964,7 @@
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" s="34" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="B936" s="41">
         <v>79885093331</v>
@@ -25949,7 +25973,7 @@
         <v>1592</v>
       </c>
       <c r="D936" s="33" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="E936" s="33" t="s">
         <v>1602</v>
@@ -25962,7 +25986,7 @@
     </row>
     <row r="937" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A937" s="34" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B937" s="41">
         <v>79283483981</v>
@@ -25971,10 +25995,10 @@
         <v>1592</v>
       </c>
       <c r="D937" s="33" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="E937" s="33" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="F937" s="33" t="s">
         <v>1599</v>
@@ -25984,7 +26008,7 @@
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" s="34" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="B938" s="41">
         <v>79184400178</v>
@@ -25996,7 +26020,7 @@
         <v>1593</v>
       </c>
       <c r="E938" s="33" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="F938" s="33" t="s">
         <v>1599</v>
@@ -26006,16 +26030,16 @@
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" s="34" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="B939" s="41">
         <v>79183270587</v>
       </c>
       <c r="C939" s="33" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="D939" s="33" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="E939" s="33"/>
       <c r="F939" s="33"/>
@@ -26024,7 +26048,7 @@
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" s="34" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="B940" s="41">
         <v>79183889940</v>
@@ -26033,7 +26057,7 @@
         <v>1592</v>
       </c>
       <c r="D940" s="33" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="E940" s="33"/>
       <c r="F940" s="33"/>
@@ -26042,13 +26066,13 @@
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" s="34" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="B941" s="41">
         <v>79994722206</v>
       </c>
       <c r="C941" s="33" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="D941" s="33"/>
       <c r="E941" s="33"/>
@@ -26058,17 +26082,17 @@
     </row>
     <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" s="34" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="B942" s="41">
         <v>79184165266</v>
       </c>
       <c r="C942" s="33" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="D942" s="33"/>
       <c r="E942" s="33" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F942" s="33" t="s">
         <v>1604</v>
@@ -26084,11 +26108,11 @@
         <v>79184277066</v>
       </c>
       <c r="C943" s="33" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="D943" s="33"/>
       <c r="E943" s="33" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F943" s="33" t="s">
         <v>1603</v>
@@ -26098,7 +26122,7 @@
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" s="34" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="B944" s="41">
         <v>79160231803</v>
@@ -26107,7 +26131,7 @@
         <v>1595</v>
       </c>
       <c r="D944" s="33" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="E944" s="33"/>
       <c r="F944" s="33"/>
@@ -26116,13 +26140,13 @@
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" s="34" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="B945" s="41">
         <v>79251587458</v>
       </c>
       <c r="C945" s="33" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="D945" s="33" t="s">
         <v>1594</v>
@@ -26134,7 +26158,7 @@
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" s="34" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="B946" s="41">
         <v>79385519412</v>
@@ -26143,7 +26167,7 @@
         <v>1595</v>
       </c>
       <c r="D946" s="33" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="E946" s="33"/>
       <c r="F946" s="33"/>
@@ -26170,11 +26194,11 @@
         <v>79184277066</v>
       </c>
       <c r="C948" s="33" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D948" s="33"/>
       <c r="E948" s="33" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="F948" s="33" t="s">
         <v>1596</v>
@@ -26202,11 +26226,11 @@
         <v>79184277066</v>
       </c>
       <c r="C950" s="33" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="D950" s="33"/>
       <c r="E950" s="33" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F950" s="33" t="s">
         <v>1603</v>
@@ -26240,13 +26264,13 @@
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" s="34" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="B952" s="35">
         <v>79895106888</v>
       </c>
       <c r="C952" s="33" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="D952" s="33"/>
       <c r="E952" s="33"/>
@@ -26256,7 +26280,7 @@
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" s="34" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="B953" s="35">
         <v>79189487859</v>
@@ -26265,7 +26289,7 @@
         <v>1623</v>
       </c>
       <c r="D953" s="33" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="E953" s="33"/>
       <c r="F953" s="33"/>
@@ -26274,7 +26298,7 @@
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" s="34" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="B954" s="35">
         <v>79094690279</v>
@@ -26284,7 +26308,7 @@
       </c>
       <c r="D954" s="33"/>
       <c r="E954" s="33" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="F954" s="33" t="s">
         <v>1624</v>
@@ -26294,7 +26318,7 @@
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" s="34" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
       <c r="B955" s="35">
         <v>79270465755</v>
@@ -26304,7 +26328,7 @@
       </c>
       <c r="D955" s="33"/>
       <c r="E955" s="33" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="F955" s="33" t="s">
         <v>1624</v>
@@ -26314,17 +26338,17 @@
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" s="34" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="B956" s="35">
         <v>79181514761</v>
       </c>
       <c r="C956" s="33" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="D956" s="33"/>
       <c r="E956" s="33" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="F956" s="33" t="s">
         <v>1625</v>
@@ -26346,17 +26370,17 @@
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" s="34" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="B958" s="35">
         <v>79286120337</v>
       </c>
       <c r="C958" s="33" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="D958" s="33"/>
       <c r="E958" s="33" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="F958" s="33" t="s">
         <v>1626</v>
@@ -26366,13 +26390,13 @@
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" s="34" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="B959" s="35">
         <v>79181603172</v>
       </c>
       <c r="C959" s="33" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="D959" s="33" t="s">
         <v>1627</v>
@@ -26384,7 +26408,7 @@
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" s="34" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="B960" s="35">
         <v>79528474569</v>
@@ -26393,7 +26417,7 @@
         <v>1628</v>
       </c>
       <c r="D960" s="33" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E960" s="33"/>
       <c r="F960" s="33"/>
@@ -26402,14 +26426,14 @@
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" s="34" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="B961" s="35">
         <v>79891443888</v>
       </c>
       <c r="C961" s="33"/>
       <c r="D961" s="33" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="E961" s="33"/>
       <c r="F961" s="33"/>
@@ -26430,14 +26454,14 @@
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" s="34" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="B963" s="35">
         <v>79186956626</v>
       </c>
       <c r="C963" s="33"/>
       <c r="D963" s="33" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="E963" s="33"/>
       <c r="F963" s="33"/>
@@ -26446,7 +26470,7 @@
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" s="34" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="B964" s="35">
         <v>79183433464</v>
@@ -26454,7 +26478,7 @@
       <c r="C964" s="33"/>
       <c r="D964" s="33"/>
       <c r="E964" s="33" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="F964" s="33" t="s">
         <v>1629</v>
@@ -26464,13 +26488,13 @@
     </row>
     <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" s="34" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="B965" s="35">
         <v>79094646000</v>
       </c>
       <c r="C965" s="33" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D965" s="33"/>
       <c r="E965" s="33"/>
@@ -26480,13 +26504,13 @@
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" s="34" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="B966" s="35">
         <v>79854264076</v>
       </c>
       <c r="C966" s="33" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D966" s="33"/>
       <c r="E966" s="33"/>
@@ -26496,13 +26520,13 @@
     </row>
     <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" s="34" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="B967" s="35">
         <v>79186525585</v>
       </c>
       <c r="C967" s="33" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D967" s="33"/>
       <c r="E967" s="33"/>
@@ -26512,17 +26536,17 @@
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" s="34" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="B968" s="35">
         <v>79528581269</v>
       </c>
       <c r="C968" s="33" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D968" s="33"/>
       <c r="E968" s="33" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="F968" s="33" t="s">
         <v>1630</v>
@@ -26532,16 +26556,16 @@
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" s="34" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="B969" s="35">
         <v>79673053030</v>
       </c>
       <c r="C969" s="33" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D969" s="33" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="E969" s="33"/>
       <c r="F969" s="33"/>
@@ -26562,7 +26586,7 @@
     </row>
     <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" s="34" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="B971" s="35">
         <v>79886696618</v>
@@ -26570,7 +26594,7 @@
       <c r="C971" s="33"/>
       <c r="D971" s="33"/>
       <c r="E971" s="33" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="F971" s="33" t="s">
         <v>1631</v>
@@ -26614,7 +26638,7 @@
       </c>
       <c r="D973" s="20"/>
       <c r="E973" s="20" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="F973" s="20" t="s">
         <v>1104</v>
@@ -26648,7 +26672,7 @@
     </row>
     <row r="975" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A975" s="19" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B975" s="42">
         <v>79165690999</v>
@@ -26703,7 +26727,7 @@
         <v>1618</v>
       </c>
       <c r="D977" s="33" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="E977" s="33"/>
       <c r="F977" s="33"/>
@@ -26712,7 +26736,7 @@
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" s="34" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="B978" s="35">
         <v>79117974075</v>
@@ -26721,7 +26745,7 @@
         <v>1618</v>
       </c>
       <c r="D978" s="33" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="E978" s="33"/>
       <c r="F978" s="33"/>
@@ -26730,7 +26754,7 @@
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" s="34" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="B979" s="35">
         <v>79615951401</v>
@@ -26739,7 +26763,7 @@
         <v>1618</v>
       </c>
       <c r="D979" s="33" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="E979" s="33"/>
       <c r="F979" s="33"/>
@@ -26748,16 +26772,16 @@
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" s="34" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="B980" s="35">
         <v>79274773218</v>
       </c>
       <c r="C980" s="33" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="D980" s="33" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="E980" s="33"/>
       <c r="F980" s="33"/>
@@ -26766,7 +26790,7 @@
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" s="34" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="B981" s="35">
         <v>79673005052</v>
@@ -26775,7 +26799,7 @@
         <v>1618</v>
       </c>
       <c r="D981" s="33" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="E981" s="33"/>
       <c r="F981" s="33"/>
@@ -26784,13 +26808,13 @@
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" s="34" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="B982" s="35">
         <v>79625245851</v>
       </c>
       <c r="C982" s="33" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="D982" s="33" t="s">
         <v>1620</v>
@@ -26802,7 +26826,7 @@
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" s="34" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="B983" s="35">
         <v>79898052605</v>
@@ -26811,7 +26835,7 @@
         <v>1618</v>
       </c>
       <c r="D983" s="33" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="E983" s="33"/>
       <c r="F983" s="33"/>
@@ -26820,7 +26844,7 @@
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" s="34" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="B984" s="35">
         <v>79992365729</v>
@@ -26829,7 +26853,7 @@
         <v>1618</v>
       </c>
       <c r="D984" s="33" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="E984" s="33"/>
       <c r="F984" s="33"/>
@@ -26862,13 +26886,13 @@
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" s="34" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="B986" s="41">
         <v>79182119543</v>
       </c>
       <c r="C986" s="33" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="D986" s="33"/>
       <c r="E986" s="33"/>
@@ -26878,17 +26902,17 @@
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" s="34" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="B987" s="41">
         <v>79886039199</v>
       </c>
       <c r="C987" s="33" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D987" s="33"/>
       <c r="E987" s="33" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="F987" s="33" t="s">
         <v>1616</v>
@@ -26898,13 +26922,13 @@
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" s="34" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="B988" s="41">
         <v>79182846179</v>
       </c>
       <c r="C988" s="33" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D988" s="33" t="s">
         <v>1621</v>
@@ -26916,7 +26940,7 @@
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" s="34" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="B989" s="41">
         <v>79185545589</v>
@@ -26925,7 +26949,7 @@
         <v>1637</v>
       </c>
       <c r="D989" s="33" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="E989" s="33"/>
       <c r="F989" s="33"/>
@@ -26934,13 +26958,13 @@
     </row>
     <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" s="34" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="B990" s="41">
         <v>79637505138</v>
       </c>
       <c r="C990" s="33" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D990" s="33"/>
       <c r="E990" s="33"/>
@@ -26950,16 +26974,16 @@
     </row>
     <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" s="34" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="B991" s="41">
         <v>79604757152</v>
       </c>
       <c r="C991" s="33" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D991" s="33" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="E991" s="33"/>
       <c r="F991" s="33"/>
@@ -26968,13 +26992,13 @@
     </row>
     <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" s="34" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="B992" s="41">
         <v>79182762782</v>
       </c>
       <c r="C992" s="33" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D992" s="33" t="s">
         <v>1622</v>
@@ -27010,13 +27034,13 @@
     </row>
     <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" s="34" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="B994" s="41">
         <v>79892941007</v>
       </c>
       <c r="C994" s="33" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="D994" s="33"/>
       <c r="E994" s="33"/>
@@ -27026,7 +27050,7 @@
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" s="34" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="B995" s="41">
         <v>79060896267</v>
@@ -27036,7 +27060,7 @@
       </c>
       <c r="D995" s="33"/>
       <c r="E995" s="33" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="F995" s="33" t="s">
         <v>1617</v>
@@ -27046,13 +27070,13 @@
     </row>
     <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" s="34" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="B996" s="41">
         <v>79384227276</v>
       </c>
       <c r="C996" s="33" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="D996" s="33"/>
       <c r="E996" s="33"/>
@@ -27086,14 +27110,14 @@
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" s="34" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="B998" s="41">
         <v>79614238176</v>
       </c>
       <c r="C998" s="33"/>
       <c r="D998" s="33" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="E998" s="33"/>
       <c r="F998" s="33"/>
@@ -27114,13 +27138,13 @@
     </row>
     <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" s="34" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="B1000" s="41">
         <v>79280121007</v>
       </c>
       <c r="C1000" s="35" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="D1000" s="35"/>
       <c r="E1000" s="35"/>
@@ -27142,13 +27166,13 @@
     </row>
     <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" s="34" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="B1002" s="41">
         <v>79180985165</v>
       </c>
       <c r="C1002" s="35" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="D1002" s="35"/>
       <c r="E1002" s="35"/>
@@ -27158,13 +27182,13 @@
     </row>
     <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" s="34" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="B1003" s="41">
         <v>79186200028</v>
       </c>
       <c r="C1003" s="35" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="D1003" s="35"/>
       <c r="E1003" s="35"/>
@@ -27174,13 +27198,13 @@
     </row>
     <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" s="34" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="B1004" s="41">
         <v>79190278727</v>
       </c>
       <c r="C1004" s="35" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="D1004" s="35"/>
       <c r="E1004" s="35"/>
@@ -27202,13 +27226,13 @@
     </row>
     <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" s="34" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="B1006" s="41">
         <v>79615280373</v>
       </c>
       <c r="C1006" s="35" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="D1006" s="35"/>
       <c r="E1006" s="35"/>
@@ -27218,13 +27242,13 @@
     </row>
     <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1007" s="34" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="B1007" s="41">
         <v>79622028701</v>
       </c>
       <c r="C1007" s="35" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="D1007" s="35"/>
       <c r="E1007" s="35"/>
@@ -27234,13 +27258,13 @@
     </row>
     <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1008" s="34" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="B1008" s="41">
         <v>79185055723</v>
       </c>
       <c r="C1008" s="35" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="D1008" s="35"/>
       <c r="E1008" s="35"/>
@@ -27250,13 +27274,13 @@
     </row>
     <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" s="34" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="B1009" s="41">
         <v>79788139855</v>
       </c>
       <c r="C1009" s="35" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="D1009" s="35"/>
       <c r="E1009" s="35"/>
@@ -27278,7 +27302,7 @@
     </row>
     <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" s="34" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="B1011" s="41">
         <v>79189749194</v>
@@ -27286,7 +27310,7 @@
       <c r="C1011" s="35"/>
       <c r="D1011" s="35"/>
       <c r="E1011" s="35" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="F1011" s="35" t="s">
         <v>1636</v>
@@ -27296,16 +27320,16 @@
     </row>
     <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" s="34" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="B1012" s="41">
         <v>79184801108</v>
       </c>
       <c r="C1012" s="35" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="D1012" s="35" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="E1012" s="35"/>
       <c r="F1012" s="35"/>
@@ -27314,13 +27338,13 @@
     </row>
     <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" s="34" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
       <c r="B1013" s="41">
         <v>79646847710</v>
       </c>
       <c r="C1013" s="35" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="D1013" s="35"/>
       <c r="E1013" s="35"/>
@@ -27330,13 +27354,13 @@
     </row>
     <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" s="34" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="B1014" s="41">
         <v>79649041350</v>
       </c>
       <c r="C1014" s="35" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="D1014" s="35"/>
       <c r="E1014" s="35"/>
@@ -27358,14 +27382,14 @@
     </row>
     <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" s="34" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="B1016" s="33">
         <v>79181537666</v>
       </c>
       <c r="C1016" s="33"/>
       <c r="D1016" s="33" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="E1016" s="33"/>
       <c r="F1016" s="33"/>
@@ -27374,14 +27398,14 @@
     </row>
     <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" s="34" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="B1017" s="33">
         <v>79051511564</v>
       </c>
       <c r="C1017" s="33"/>
       <c r="D1017" s="33" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="E1017" s="33"/>
       <c r="F1017" s="33"/>
@@ -27390,14 +27414,14 @@
     </row>
     <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" s="34" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="B1018" s="33">
         <v>79254155954</v>
       </c>
       <c r="C1018" s="33"/>
       <c r="D1018" s="33" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="E1018" s="33"/>
       <c r="F1018" s="33"/>
@@ -27406,14 +27430,14 @@
     </row>
     <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" s="34" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="B1019" s="33">
         <v>79626803581</v>
       </c>
       <c r="C1019" s="33"/>
       <c r="D1019" s="33" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="E1019" s="33"/>
       <c r="F1019" s="33"/>
@@ -27434,13 +27458,13 @@
     </row>
     <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" s="34" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="B1021" s="33">
         <v>79281059268</v>
       </c>
       <c r="C1021" s="33" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="D1021" s="33"/>
       <c r="E1021" s="33"/>
@@ -27450,16 +27474,16 @@
     </row>
     <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" s="34" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
       <c r="B1022" s="33">
         <v>79183388668</v>
       </c>
       <c r="C1022" s="33" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="D1022" s="33" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="E1022" s="33"/>
       <c r="F1022" s="33"/>
@@ -27468,13 +27492,13 @@
     </row>
     <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" s="34" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
       <c r="B1023" s="33">
         <v>79067249922</v>
       </c>
       <c r="C1023" s="33" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="D1023" s="33"/>
       <c r="E1023" s="33"/>
@@ -27496,16 +27520,16 @@
     </row>
     <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1025" s="34" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="B1025" s="33">
         <v>79052993315</v>
       </c>
       <c r="C1025" s="33" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="D1025" s="33" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="E1025" s="33"/>
       <c r="F1025" s="33"/>
@@ -27514,7 +27538,7 @@
     </row>
     <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1026" s="34" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="B1026" s="33">
         <v>79043499977</v>
@@ -27522,7 +27546,7 @@
       <c r="C1026" s="33"/>
       <c r="D1026" s="33"/>
       <c r="E1026" s="33" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="F1026" s="33" t="s">
         <v>1751</v>
@@ -27544,13 +27568,13 @@
     </row>
     <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1028" s="34" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="B1028" s="33">
         <v>79052875113</v>
       </c>
       <c r="C1028" s="33" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="D1028" s="33"/>
       <c r="E1028" s="33"/>
@@ -27560,14 +27584,14 @@
     </row>
     <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1029" s="34" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
       <c r="B1029" s="33">
         <v>79061820166</v>
       </c>
       <c r="C1029" s="33"/>
       <c r="D1029" s="33" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="E1029" s="33"/>
       <c r="F1029" s="33"/>
@@ -27576,14 +27600,14 @@
     </row>
     <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1030" s="34" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="B1030" s="33">
         <v>79189333736</v>
       </c>
       <c r="C1030" s="33"/>
       <c r="D1030" s="33" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="E1030" s="33"/>
       <c r="F1030" s="33"/>
@@ -27592,14 +27616,14 @@
     </row>
     <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1031" s="34" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="B1031" s="33">
         <v>79064327871</v>
       </c>
       <c r="C1031" s="33"/>
       <c r="D1031" s="33" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="E1031" s="33"/>
       <c r="F1031" s="33"/>
@@ -27608,13 +27632,13 @@
     </row>
     <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1032" s="34" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="B1032" s="33">
         <v>79102891788</v>
       </c>
       <c r="C1032" s="33" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="D1032" s="33"/>
       <c r="E1032" s="33"/>
@@ -27636,16 +27660,16 @@
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1034" s="34" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="B1034" s="33">
         <v>79183561661</v>
       </c>
       <c r="C1034" s="33" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="D1034" s="33" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="E1034" s="33"/>
       <c r="F1034" s="33"/>
@@ -27654,19 +27678,19 @@
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1035" s="34" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="B1035" s="33">
         <v>79537206758</v>
       </c>
       <c r="C1035" s="33" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="D1035" s="33" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1035" s="33" t="s">
         <v>2196</v>
-      </c>
-      <c r="E1035" s="33" t="s">
-        <v>2197</v>
       </c>
       <c r="F1035" s="33" t="s">
         <v>1752</v>
@@ -27750,7 +27774,7 @@
     </row>
     <row r="1040" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1040" s="6" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B1040" s="3"/>
       <c r="C1040" s="3"/>
@@ -27762,14 +27786,14 @@
     </row>
     <row r="1041" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1041" s="6" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="B1041" s="3">
         <v>79788288099</v>
       </c>
       <c r="C1041" s="3"/>
       <c r="D1041" s="3" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="E1041" s="3"/>
       <c r="F1041" s="3"/>
@@ -27778,14 +27802,14 @@
     </row>
     <row r="1042" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1042" s="6" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="B1042" s="3">
         <v>79065859343</v>
       </c>
       <c r="C1042" s="3"/>
       <c r="D1042" s="3" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="E1042" s="3"/>
       <c r="F1042" s="3"/>
@@ -27794,7 +27818,7 @@
     </row>
     <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1043" s="6" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="B1043" s="3">
         <v>79184427932</v>
@@ -27802,24 +27826,24 @@
       <c r="C1043" s="3"/>
       <c r="D1043" s="3"/>
       <c r="E1043" s="3" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="F1043" s="3" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="G1043" s="18"/>
       <c r="H1043" s="30"/>
     </row>
     <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1044" s="6" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="B1044" s="3">
         <v>79780015912</v>
       </c>
       <c r="C1044" s="3"/>
       <c r="D1044" s="3" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="E1044" s="3"/>
       <c r="F1044" s="3"/>
@@ -27828,47 +27852,47 @@
     </row>
     <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1045" s="6" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="B1045" s="3">
         <v>79183756404</v>
       </c>
       <c r="C1045" s="3"/>
       <c r="D1045" s="3" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E1045" s="3" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="F1045" s="3" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="G1045" s="18"/>
       <c r="H1045" s="30"/>
     </row>
     <row r="1046" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1046" s="6" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B1046" s="3">
         <v>79031442806</v>
       </c>
       <c r="C1046" s="3"/>
       <c r="D1046" s="3" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E1046" s="3" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="F1046" s="3" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="G1046" s="18"/>
       <c r="H1046" s="30"/>
     </row>
     <row r="1047" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1047" s="6" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B1047" s="3"/>
       <c r="C1047" s="3"/>
@@ -27880,36 +27904,36 @@
     </row>
     <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1048" s="6" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="B1048" s="3">
         <v>79624430220</v>
       </c>
       <c r="C1048" s="3" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="D1048" s="3" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E1048" s="3" t="s">
         <v>2395</v>
       </c>
-      <c r="E1048" s="3" t="s">
-        <v>2396</v>
-      </c>
       <c r="F1048" s="3" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="G1048" s="18"/>
       <c r="H1048" s="30"/>
     </row>
     <row r="1049" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1049" s="6" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="B1049" s="3">
         <v>79602429824</v>
       </c>
       <c r="C1049" s="3"/>
       <c r="D1049" s="3" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="E1049" s="3"/>
       <c r="F1049" s="3"/>
@@ -27918,7 +27942,7 @@
     </row>
     <row r="1050" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1050" s="6" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B1050" s="3"/>
       <c r="C1050" s="3"/>
@@ -27930,14 +27954,14 @@
     </row>
     <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1051" s="6" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="B1051" s="3">
         <v>79789971387</v>
       </c>
       <c r="C1051" s="3"/>
       <c r="D1051" s="3" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="E1051" s="3"/>
       <c r="F1051" s="3"/>
@@ -27946,14 +27970,14 @@
     </row>
     <row r="1052" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1052" s="6" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B1052" s="3">
         <v>79661185577</v>
       </c>
       <c r="C1052" s="3"/>
       <c r="D1052" s="3" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="E1052" s="3"/>
       <c r="F1052" s="3"/>
@@ -27982,7 +28006,7 @@
     </row>
     <row r="1054" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1054" s="6" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="B1054" s="3"/>
       <c r="C1054" s="3"/>
@@ -27994,13 +28018,13 @@
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1055" s="6" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="B1055" s="18">
         <v>79186452525</v>
       </c>
       <c r="C1055" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D1055" s="3"/>
       <c r="E1055" s="3"/>
@@ -28010,13 +28034,13 @@
     </row>
     <row r="1056" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1056" s="6" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B1056" s="18">
         <v>79189484040</v>
       </c>
       <c r="C1056" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D1056" s="3"/>
       <c r="E1056" s="3"/>
@@ -28026,14 +28050,14 @@
     </row>
     <row r="1057" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1057" s="6" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="B1057" s="18">
         <v>79183860270</v>
       </c>
       <c r="C1057" s="3"/>
       <c r="D1057" s="3" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="E1057" s="3"/>
       <c r="F1057" s="3"/>
@@ -28042,16 +28066,16 @@
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1058" s="6" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="B1058" s="18">
         <v>79779455485</v>
       </c>
       <c r="C1058" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D1058" s="3" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="E1058" s="3"/>
       <c r="F1058" s="3"/>
@@ -28060,16 +28084,16 @@
     </row>
     <row r="1059" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1059" s="6" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="B1059" s="18">
         <v>79056507300</v>
       </c>
       <c r="C1059" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D1059" s="3" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="E1059" s="3"/>
       <c r="F1059" s="3"/>
@@ -28078,16 +28102,16 @@
     </row>
     <row r="1060" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1060" s="6" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="B1060" s="18">
         <v>79258091550</v>
       </c>
       <c r="C1060" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D1060" s="3" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="E1060" s="3"/>
       <c r="F1060" s="3"/>
@@ -28096,27 +28120,27 @@
     </row>
     <row r="1061" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1061" s="6" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="B1061" s="18">
         <v>79185091900</v>
       </c>
       <c r="C1061" s="3"/>
       <c r="D1061" s="3" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="E1061" s="3" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="F1061" s="3" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="G1061" s="3"/>
       <c r="H1061" s="3"/>
     </row>
     <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1062" s="6" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B1062" s="18"/>
       <c r="C1062" s="3"/>
@@ -28128,14 +28152,14 @@
     </row>
     <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1063" s="6" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="B1063" s="18">
         <v>79649334332</v>
       </c>
       <c r="C1063" s="3"/>
       <c r="D1063" s="3" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="E1063" s="3"/>
       <c r="F1063" s="3"/>
@@ -28144,14 +28168,14 @@
     </row>
     <row r="1064" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1064" s="6" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="B1064" s="18">
         <v>79783434760</v>
       </c>
       <c r="C1064" s="3"/>
       <c r="D1064" s="3" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="E1064" s="3"/>
       <c r="F1064" s="3"/>
@@ -28160,13 +28184,13 @@
     </row>
     <row r="1065" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1065" s="6" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B1065" s="18">
         <v>79493130260</v>
       </c>
       <c r="C1065" s="3" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="D1065" s="3"/>
       <c r="E1065" s="3"/>
@@ -28176,7 +28200,7 @@
     </row>
     <row r="1066" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1066" s="6" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="B1066" s="18">
         <v>79990156363</v>
@@ -28184,24 +28208,24 @@
       <c r="C1066" s="3"/>
       <c r="D1066" s="3"/>
       <c r="E1066" s="3" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="F1066" s="3" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="G1066" s="3"/>
       <c r="H1066" s="3"/>
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1067" s="6" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B1067" s="18">
         <v>79880146339</v>
       </c>
       <c r="C1067" s="3"/>
       <c r="D1067" s="3" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="E1067" s="3"/>
       <c r="F1067" s="3"/>
@@ -28210,16 +28234,16 @@
     </row>
     <row r="1068" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1068" s="6" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="B1068" s="18">
         <v>79604622005</v>
       </c>
       <c r="C1068" s="3" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="D1068" s="3" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="E1068" s="3"/>
       <c r="F1068" s="3"/>
@@ -28228,13 +28252,13 @@
     </row>
     <row r="1069" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1069" s="6" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B1069" s="18">
         <v>79192563907</v>
       </c>
       <c r="C1069" s="3" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="D1069" s="3"/>
       <c r="E1069" s="3"/>
@@ -28244,13 +28268,13 @@
     </row>
     <row r="1070" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1070" s="6" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="B1070" s="18">
         <v>79180335333</v>
       </c>
       <c r="C1070" s="3" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="D1070" s="3"/>
       <c r="E1070" s="3"/>
@@ -28280,7 +28304,7 @@
     </row>
     <row r="1072" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1072" s="6" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="B1072" s="18"/>
       <c r="C1072" s="3"/>
@@ -28292,16 +28316,16 @@
     </row>
     <row r="1073" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1073" s="6" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B1073" s="18">
         <v>79183073394</v>
       </c>
       <c r="C1073" s="3" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="D1073" s="3" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="E1073" s="3"/>
       <c r="F1073" s="3"/>
@@ -28310,7 +28334,7 @@
     </row>
     <row r="1074" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1074" s="6" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="B1074" s="18"/>
       <c r="C1074" s="3"/>
@@ -28322,36 +28346,36 @@
     </row>
     <row r="1075" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1075" s="6" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B1075" s="18">
         <v>79615215290</v>
       </c>
       <c r="C1075" s="3" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D1075" s="3" t="s">
         <v>2402</v>
       </c>
-      <c r="D1075" s="3" t="s">
+      <c r="E1075" s="3" t="s">
         <v>2403</v>
       </c>
-      <c r="E1075" s="3" t="s">
-        <v>2404</v>
-      </c>
       <c r="F1075" s="3" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="G1075" s="3"/>
       <c r="H1075" s="3"/>
     </row>
     <row r="1076" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1076" s="6" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B1076" s="18">
         <v>79094569745</v>
       </c>
       <c r="C1076" s="3"/>
       <c r="D1076" s="3" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E1076" s="3"/>
       <c r="F1076" s="3"/>
@@ -28360,13 +28384,13 @@
     </row>
     <row r="1077" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1077" s="6" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="B1077" s="18">
         <v>79180757000</v>
       </c>
       <c r="C1077" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1077" s="3"/>
       <c r="E1077" s="3"/>
@@ -28376,16 +28400,16 @@
     </row>
     <row r="1078" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1078" s="6" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="B1078" s="18">
         <v>79628609461</v>
       </c>
       <c r="C1078" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1078" s="3" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="E1078" s="3"/>
       <c r="F1078" s="3"/>
@@ -28394,16 +28418,16 @@
     </row>
     <row r="1079" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1079" s="6" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B1079" s="18">
         <v>79184101450</v>
       </c>
       <c r="C1079" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1079" s="3" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="E1079" s="3"/>
       <c r="F1079" s="3"/>
@@ -28412,29 +28436,29 @@
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1080" s="6" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B1080" s="18">
         <v>79183999079</v>
       </c>
       <c r="C1080" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1080" s="3" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="E1080" s="3" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="F1080" s="3" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="G1080" s="3"/>
       <c r="H1080" s="3"/>
     </row>
     <row r="1081" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1081" s="6" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="B1081" s="18">
         <v>79181433232</v>
@@ -28442,17 +28466,17 @@
       <c r="C1081" s="3"/>
       <c r="D1081" s="3"/>
       <c r="E1081" s="3" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="F1081" s="3" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="G1081" s="3"/>
       <c r="H1081" s="3"/>
     </row>
     <row r="1082" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1082" s="6" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="B1082" s="18">
         <v>79817025393</v>
@@ -28460,23 +28484,23 @@
       <c r="C1082" s="3"/>
       <c r="D1082" s="3"/>
       <c r="E1082" s="3" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="F1082" s="3" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="G1082" s="3"/>
       <c r="H1082" s="3"/>
     </row>
     <row r="1083" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1083" s="6" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="B1083" s="18">
         <v>79184302094</v>
       </c>
       <c r="C1083" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1083" s="3"/>
       <c r="E1083" s="3"/>
@@ -28486,7 +28510,7 @@
     </row>
     <row r="1084" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1084" s="6" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="B1084" s="18"/>
       <c r="C1084" s="3"/>
@@ -28498,35 +28522,35 @@
     </row>
     <row r="1085" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1085" s="6" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B1085" s="18">
         <v>79287677710</v>
       </c>
       <c r="C1085" s="3" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D1085" s="3" t="s">
         <v>2333</v>
       </c>
-      <c r="D1085" s="3" t="s">
+      <c r="E1085" s="3" t="s">
         <v>2334</v>
       </c>
-      <c r="E1085" s="3" t="s">
-        <v>2335</v>
-      </c>
       <c r="F1085" s="3" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="G1085" s="3"/>
       <c r="H1085" s="3"/>
     </row>
     <row r="1086" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1086" s="6" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="B1086" s="18">
         <v>79615198406</v>
       </c>
       <c r="C1086" s="3" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="D1086" s="3"/>
       <c r="E1086" s="3"/>
@@ -28536,7 +28560,7 @@
     </row>
     <row r="1087" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1087" s="6" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="B1087" s="18">
         <v>79620503561</v>
@@ -28544,65 +28568,65 @@
       <c r="C1087" s="3"/>
       <c r="D1087" s="3"/>
       <c r="E1087" s="3" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="F1087" s="3" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="G1087" s="3"/>
       <c r="H1087" s="3"/>
     </row>
     <row r="1088" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1088" s="6" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="B1088" s="18">
         <v>79093732088</v>
       </c>
       <c r="C1088" s="3" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="D1088" s="3" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="E1088" s="3" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="F1088" s="3" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="G1088" s="3"/>
       <c r="H1088" s="3"/>
     </row>
     <row r="1089" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1089" s="6" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="B1089" s="18">
         <v>79060683338</v>
       </c>
       <c r="C1089" s="3" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="D1089" s="3"/>
       <c r="E1089" s="3" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="F1089" s="3" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="G1089" s="3"/>
       <c r="H1089" s="3"/>
     </row>
     <row r="1090" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1090" s="6" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B1090" s="18">
         <v>79184137117</v>
       </c>
       <c r="C1090" s="3" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="D1090" s="3"/>
       <c r="E1090" s="3"/>
@@ -28612,13 +28636,13 @@
     </row>
     <row r="1091" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1091" s="6" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="B1091" s="18">
         <v>79180660587</v>
       </c>
       <c r="C1091" s="3" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="D1091" s="3"/>
       <c r="E1091" s="3"/>
@@ -28628,7 +28652,7 @@
     </row>
     <row r="1092" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1092" s="6" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B1092" s="18"/>
       <c r="C1092" s="3"/>
@@ -28640,38 +28664,38 @@
     </row>
     <row r="1093" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1093" s="6" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="B1093" s="18">
         <v>79002359970</v>
       </c>
       <c r="C1093" s="3" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="D1093" s="3" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="E1093" s="3" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="F1093" s="3" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="G1093" s="3"/>
       <c r="H1093" s="3"/>
     </row>
     <row r="1094" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1094" s="6" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="B1094" s="18">
         <v>79892306069</v>
       </c>
       <c r="C1094" s="3" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="D1094" s="3" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="E1094" s="3"/>
       <c r="F1094" s="3"/>
@@ -28680,7 +28704,7 @@
     </row>
     <row r="1095" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1095" s="6" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="B1095" s="18"/>
       <c r="C1095" s="3"/>
@@ -28692,13 +28716,13 @@
     </row>
     <row r="1096" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1096" s="6" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="B1096" s="18">
         <v>79615101239</v>
       </c>
       <c r="C1096" s="3" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="D1096" s="3"/>
       <c r="E1096" s="3"/>
@@ -28708,16 +28732,16 @@
     </row>
     <row r="1097" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1097" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B1097" s="18">
         <v>79287753737</v>
       </c>
       <c r="C1097" s="3" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="D1097" s="3" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="E1097" s="3"/>
       <c r="F1097" s="3"/>
@@ -28726,36 +28750,36 @@
     </row>
     <row r="1098" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1098" s="6" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="B1098" s="18">
         <v>79283348884</v>
       </c>
       <c r="C1098" s="3" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="D1098" s="3" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="E1098" s="3" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="F1098" s="3" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="G1098" s="3"/>
       <c r="H1098" s="3"/>
     </row>
     <row r="1099" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1099" s="6" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="B1099" s="18">
         <v>79381175888</v>
       </c>
       <c r="C1099" s="3"/>
       <c r="D1099" s="3" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="E1099" s="3"/>
       <c r="F1099" s="3"/>
@@ -28782,13 +28806,13 @@
         <v>79536931038</v>
       </c>
       <c r="C1101" s="29" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D1101" s="29" t="s">
         <v>1865</v>
       </c>
-      <c r="D1101" s="29" t="s">
+      <c r="E1101" s="29" t="s">
         <v>1866</v>
-      </c>
-      <c r="E1101" s="29" t="s">
-        <v>1867</v>
       </c>
       <c r="F1101" s="29" t="s">
         <v>1213</v>
@@ -28818,7 +28842,7 @@
     </row>
     <row r="1103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1103" s="6" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B1103" s="18"/>
       <c r="C1103" s="3"/>
@@ -28830,7 +28854,7 @@
     </row>
     <row r="1104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1104" s="6" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="B1104" s="18">
         <v>79900137808</v>
@@ -28838,26 +28862,26 @@
       <c r="C1104" s="3"/>
       <c r="D1104" s="3"/>
       <c r="E1104" s="3" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="F1104" s="3" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="G1104" s="3"/>
       <c r="H1104" s="3"/>
     </row>
     <row r="1105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1105" s="6" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B1105" s="18">
         <v>79649134155</v>
       </c>
       <c r="C1105" s="3" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="D1105" s="3" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="E1105" s="3"/>
       <c r="F1105" s="3"/>
@@ -28866,13 +28890,13 @@
     </row>
     <row r="1106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1106" s="6" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="B1106" s="18">
         <v>79186587857</v>
       </c>
       <c r="C1106" s="3" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="D1106" s="3"/>
       <c r="E1106" s="3"/>
@@ -28882,13 +28906,13 @@
     </row>
     <row r="1107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1107" s="6" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B1107" s="18">
         <v>79183710874</v>
       </c>
       <c r="C1107" s="3" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="D1107" s="3"/>
       <c r="E1107" s="3"/>
@@ -28898,34 +28922,34 @@
     </row>
     <row r="1108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1108" s="6" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="B1108" s="18">
         <v>79185758610</v>
       </c>
       <c r="C1108" s="3" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="D1108" s="3"/>
       <c r="E1108" s="3" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="F1108" s="3" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G1108" s="3"/>
       <c r="H1108" s="3"/>
     </row>
     <row r="1109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1109" s="6" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="B1109" s="18">
         <v>79528107175</v>
       </c>
       <c r="C1109" s="3"/>
       <c r="D1109" s="3" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="E1109" s="3"/>
       <c r="F1109" s="3"/>
@@ -28934,29 +28958,29 @@
     </row>
     <row r="1110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1110" s="6" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B1110" s="18">
         <v>79530981964</v>
       </c>
       <c r="C1110" s="3" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="D1110" s="3" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="E1110" s="3" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="F1110" s="3" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G1110" s="3"/>
       <c r="H1110" s="3"/>
     </row>
     <row r="1111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1111" s="6" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B1111" s="18"/>
       <c r="C1111" s="3"/>
@@ -28968,13 +28992,13 @@
     </row>
     <row r="1112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1112" s="6" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="B1112" s="18">
         <v>79884919692</v>
       </c>
       <c r="C1112" s="3" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="D1112" s="3"/>
       <c r="E1112" s="3"/>
@@ -28984,13 +29008,13 @@
     </row>
     <row r="1113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1113" s="6" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="B1113" s="18">
         <v>79164495884</v>
       </c>
       <c r="C1113" s="3" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="D1113" s="3"/>
       <c r="E1113" s="3"/>
@@ -29000,14 +29024,14 @@
     </row>
     <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1114" s="6" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="B1114" s="18">
         <v>79493057717</v>
       </c>
       <c r="C1114" s="3"/>
       <c r="D1114" s="3" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="E1114" s="3"/>
       <c r="F1114" s="3"/>
@@ -29016,7 +29040,7 @@
     </row>
     <row r="1115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1115" s="6" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="B1115" s="18"/>
       <c r="C1115" s="3"/>
@@ -29028,14 +29052,14 @@
     </row>
     <row r="1116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1116" s="6" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B1116" s="18">
         <v>79180769237</v>
       </c>
       <c r="C1116" s="3"/>
       <c r="D1116" s="3" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="E1116" s="3"/>
       <c r="F1116" s="3"/>
@@ -29044,7 +29068,7 @@
     </row>
     <row r="1117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1117" s="6" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="B1117" s="18">
         <v>79180119455</v>
@@ -29052,24 +29076,24 @@
       <c r="C1117" s="3"/>
       <c r="D1117" s="3"/>
       <c r="E1117" s="3" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="F1117" s="3" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="G1117" s="3"/>
       <c r="H1117" s="3"/>
     </row>
     <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1118" s="6" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="B1118" s="18">
         <v>79787625654</v>
       </c>
       <c r="C1118" s="3"/>
       <c r="D1118" s="3" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="E1118" s="3"/>
       <c r="F1118" s="3"/>
@@ -29078,14 +29102,14 @@
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1119" s="6" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B1119" s="18">
         <v>79884788948</v>
       </c>
       <c r="C1119" s="3"/>
       <c r="D1119" s="3" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="E1119" s="3"/>
       <c r="F1119" s="3"/>
@@ -29094,7 +29118,7 @@
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1120" s="6" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B1120" s="18"/>
       <c r="C1120" s="3"/>
@@ -29106,14 +29130,14 @@
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1121" s="6" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="B1121" s="18">
         <v>79205825242</v>
       </c>
       <c r="C1121" s="3"/>
       <c r="D1121" s="3" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="E1121" s="3"/>
       <c r="F1121" s="3"/>
@@ -29122,14 +29146,14 @@
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1122" s="6" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="B1122" s="18">
         <v>79181511141</v>
       </c>
       <c r="C1122" s="3"/>
       <c r="D1122" s="3" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="E1122" s="3"/>
       <c r="F1122" s="3"/>
@@ -29158,7 +29182,7 @@
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1124" s="6" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B1124" s="18"/>
       <c r="C1124" s="3"/>
@@ -29170,7 +29194,7 @@
     </row>
     <row r="1125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1125" s="6" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B1125" s="18">
         <v>79118596500</v>
@@ -29178,39 +29202,39 @@
       <c r="C1125" s="18"/>
       <c r="D1125" s="18"/>
       <c r="E1125" s="18" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="F1125" s="18" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="G1125" s="18"/>
       <c r="H1125" s="18"/>
     </row>
     <row r="1126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1126" s="6" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B1126" s="18">
         <v>79780187528</v>
       </c>
       <c r="C1126" s="18" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D1126" s="18" t="s">
         <v>2364</v>
       </c>
-      <c r="D1126" s="18" t="s">
-        <v>2365</v>
-      </c>
       <c r="E1126" s="18" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="F1126" s="18" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G1126" s="18"/>
       <c r="H1126" s="18"/>
     </row>
     <row r="1127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1127" s="6" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B1127" s="18">
         <v>79037376464</v>
@@ -29218,17 +29242,17 @@
       <c r="C1127" s="18"/>
       <c r="D1127" s="18"/>
       <c r="E1127" s="18" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="F1127" s="18" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G1127" s="18"/>
       <c r="H1127" s="18"/>
     </row>
     <row r="1128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1128" s="6" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B1128" s="18"/>
       <c r="C1128" s="18"/>
@@ -29240,7 +29264,7 @@
     </row>
     <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1129" s="6" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B1129" s="18">
         <v>79103223870</v>
@@ -29248,10 +29272,10 @@
       <c r="C1129" s="18"/>
       <c r="D1129" s="18"/>
       <c r="E1129" s="18" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="F1129" s="18" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="G1129" s="18"/>
       <c r="H1129" s="18"/>
@@ -29278,7 +29302,7 @@
     </row>
     <row r="1131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1131" s="6" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B1131" s="18"/>
       <c r="C1131" s="18"/>
@@ -29290,36 +29314,36 @@
     </row>
     <row r="1132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1132" s="6" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B1132" s="18">
         <v>79284697777</v>
       </c>
       <c r="C1132" s="18" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="D1132" s="18" t="s">
+        <v>2453</v>
+      </c>
+      <c r="E1132" s="18" t="s">
         <v>2454</v>
       </c>
-      <c r="E1132" s="18" t="s">
-        <v>2455</v>
-      </c>
       <c r="F1132" s="18" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="G1132" s="18"/>
       <c r="H1132" s="18"/>
     </row>
     <row r="1133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1133" s="6" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B1133" s="18">
         <v>79181601208</v>
       </c>
       <c r="C1133" s="18"/>
       <c r="D1133" s="18" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="E1133" s="18"/>
       <c r="F1133" s="18"/>
@@ -29328,7 +29352,7 @@
     </row>
     <row r="1134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1134" s="6" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B1134" s="30"/>
       <c r="C1134" s="18"/>
@@ -29340,16 +29364,16 @@
     </row>
     <row r="1135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1135" s="6" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="B1135" s="18">
         <v>79001236569</v>
       </c>
       <c r="C1135" s="18" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="D1135" s="18" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="E1135" s="18"/>
       <c r="F1135" s="18"/>
@@ -29358,38 +29382,38 @@
     </row>
     <row r="1136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1136" s="6" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B1136" s="18">
         <v>79991005104</v>
       </c>
       <c r="C1136" s="18" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="D1136" s="18" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="E1136" s="18" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="F1136" s="18" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G1136" s="18"/>
       <c r="H1136" s="18"/>
     </row>
     <row r="1137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1137" s="6" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B1137" s="18">
         <v>79371249966</v>
       </c>
       <c r="C1137" s="18" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="D1137" s="18" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="E1137" s="18"/>
       <c r="F1137" s="18"/>
@@ -29398,13 +29422,13 @@
     </row>
     <row r="1138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1138" s="6" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B1138" s="18">
         <v>79185805028</v>
       </c>
       <c r="C1138" s="18" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="D1138" s="18"/>
       <c r="E1138" s="18"/>
@@ -29414,7 +29438,7 @@
     </row>
     <row r="1139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1139" s="6" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B1139" s="18"/>
       <c r="C1139" s="18"/>
@@ -29426,16 +29450,16 @@
     </row>
     <row r="1140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1140" s="6" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B1140" s="18">
         <v>79687042488</v>
       </c>
       <c r="C1140" s="18" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="D1140" s="18" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="E1140" s="18"/>
       <c r="F1140" s="18"/>
@@ -29444,7 +29468,7 @@
     </row>
     <row r="1141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1141" s="16" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B1141" s="18"/>
       <c r="C1141" s="18"/>
@@ -29462,13 +29486,13 @@
         <v>79283483981</v>
       </c>
       <c r="C1142" s="3" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="D1142" s="3" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="E1142" s="3" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="F1142" s="3" t="s">
         <v>1599</v>
@@ -29498,7 +29522,7 @@
     </row>
     <row r="1144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1144" s="6" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B1144" s="30"/>
       <c r="C1144" s="18"/>
@@ -29516,7 +29540,7 @@
         <v>79110886608</v>
       </c>
       <c r="C1145" s="18" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="D1145" s="18"/>
       <c r="E1145" s="18"/>
@@ -29526,14 +29550,14 @@
     </row>
     <row r="1146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1146" s="6" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B1146" s="18">
         <v>79884718844</v>
       </c>
       <c r="C1146" s="18"/>
       <c r="D1146" s="18" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="E1146" s="18"/>
       <c r="F1146" s="18"/>
@@ -29542,16 +29566,16 @@
     </row>
     <row r="1147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1147" s="6" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B1147" s="18">
         <v>79185416500</v>
       </c>
       <c r="C1147" s="18" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="D1147" s="18" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="E1147" s="18"/>
       <c r="F1147" s="18"/>
@@ -29560,16 +29584,16 @@
     </row>
     <row r="1148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1148" s="6" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B1148" s="18">
         <v>79883514535</v>
       </c>
       <c r="C1148" s="18" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="D1148" s="18" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="E1148" s="18"/>
       <c r="F1148" s="18"/>
@@ -29578,16 +29602,16 @@
     </row>
     <row r="1149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1149" s="6" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B1149" s="18">
         <v>79181927858</v>
       </c>
       <c r="C1149" s="18" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="D1149" s="18" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="E1149" s="18"/>
       <c r="F1149" s="18"/>
@@ -29596,13 +29620,13 @@
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1150" s="6" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B1150" s="18">
         <v>79034731171</v>
       </c>
       <c r="C1150" s="18" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="D1150" s="18"/>
       <c r="E1150" s="18"/>
@@ -29612,7 +29636,7 @@
     </row>
     <row r="1151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1151" s="6" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B1151" s="18"/>
       <c r="C1151" s="18"/>
@@ -29624,13 +29648,13 @@
     </row>
     <row r="1152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1152" s="6" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B1152" s="18">
         <v>79518399099</v>
       </c>
       <c r="C1152" s="18" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="D1152" s="18"/>
       <c r="E1152" s="18"/>
@@ -29640,7 +29664,7 @@
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1153" s="6" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B1153" s="18">
         <v>79199932589</v>
@@ -29648,17 +29672,17 @@
       <c r="C1153" s="18"/>
       <c r="D1153" s="18"/>
       <c r="E1153" s="18" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="F1153" s="18" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G1153" s="18"/>
       <c r="H1153" s="18"/>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1154" s="6" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B1154" s="18">
         <v>79898068383</v>
@@ -29666,23 +29690,23 @@
       <c r="C1154" s="18"/>
       <c r="D1154" s="18"/>
       <c r="E1154" s="18" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="F1154" s="18" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G1154" s="18"/>
       <c r="H1154" s="18"/>
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1155" s="6" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B1155" s="18">
         <v>79493272312</v>
       </c>
       <c r="C1155" s="18" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="D1155" s="18"/>
       <c r="E1155" s="18"/>
@@ -29692,13 +29716,13 @@
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1156" s="6" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B1156" s="18">
         <v>79184455113</v>
       </c>
       <c r="C1156" s="18" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="D1156" s="18"/>
       <c r="E1156" s="18"/>
@@ -29708,13 +29732,13 @@
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1157" s="6" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B1157" s="18">
         <v>79494697622</v>
       </c>
       <c r="C1157" s="18" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="D1157" s="18"/>
       <c r="E1157" s="18"/>
@@ -29724,13 +29748,13 @@
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1158" s="6" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B1158" s="18">
         <v>79288803878</v>
       </c>
       <c r="C1158" s="18" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="D1158" s="18"/>
       <c r="E1158" s="18"/>
@@ -29740,16 +29764,16 @@
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1159" s="6" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B1159" s="18">
         <v>79284223859</v>
       </c>
       <c r="C1159" s="18" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="D1159" s="3" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="E1159" s="18"/>
       <c r="F1159" s="18"/>
@@ -29758,7 +29782,7 @@
     </row>
     <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1160" s="6" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B1160" s="18"/>
       <c r="C1160" s="18"/>
@@ -29770,22 +29794,22 @@
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1161" s="6" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B1161" s="18">
         <v>79189338233</v>
       </c>
       <c r="C1161" s="18" t="s">
+        <v>2442</v>
+      </c>
+      <c r="D1161" s="18" t="s">
         <v>2443</v>
       </c>
-      <c r="D1161" s="18" t="s">
-        <v>2444</v>
-      </c>
       <c r="E1161" s="18" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="F1161" s="18" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G1161" s="18"/>
       <c r="H1161" s="18"/>
@@ -29812,7 +29836,7 @@
     </row>
     <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1163" s="6" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B1163" s="3"/>
       <c r="C1163" s="3"/>
@@ -29824,14 +29848,14 @@
     </row>
     <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1164" s="6" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B1164" s="3">
         <v>79110886608</v>
       </c>
       <c r="C1164" s="3"/>
       <c r="D1164" s="3" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="E1164" s="3"/>
       <c r="F1164" s="3"/>
@@ -29840,14 +29864,14 @@
     </row>
     <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1165" s="6" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B1165" s="3">
         <v>79282750088</v>
       </c>
       <c r="C1165" s="3"/>
       <c r="D1165" s="3" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="E1165" s="3"/>
       <c r="F1165" s="3"/>
@@ -29856,14 +29880,14 @@
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1166" s="6" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B1166" s="3">
         <v>79384085482</v>
       </c>
       <c r="C1166" s="3"/>
       <c r="D1166" s="3" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="E1166" s="3"/>
       <c r="F1166" s="3"/>
@@ -29872,7 +29896,7 @@
     </row>
     <row r="1167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1167" s="6" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1167" s="3"/>
       <c r="C1167" s="3"/>
@@ -29884,13 +29908,13 @@
     </row>
     <row r="1168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1168" s="6" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B1168" s="3">
         <v>79622153493</v>
       </c>
       <c r="C1168" s="3" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="D1168" s="3"/>
       <c r="E1168" s="3"/>
@@ -29900,16 +29924,16 @@
     </row>
     <row r="1169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1169" s="6" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B1169" s="3">
         <v>79266122721</v>
       </c>
       <c r="C1169" s="3" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="D1169" s="3" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="E1169" s="3"/>
       <c r="F1169" s="3"/>
@@ -29918,14 +29942,14 @@
     </row>
     <row r="1170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1170" s="6" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B1170" s="3">
         <v>79997719518</v>
       </c>
       <c r="C1170" s="3"/>
       <c r="D1170" s="3" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="E1170" s="3"/>
       <c r="F1170" s="3"/>
@@ -29934,13 +29958,13 @@
     </row>
     <row r="1171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1171" s="6" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B1171" s="3">
         <v>79813022825</v>
       </c>
       <c r="C1171" s="3" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="D1171" s="3"/>
       <c r="E1171" s="3"/>
@@ -29950,7 +29974,7 @@
     </row>
     <row r="1172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1172" s="6" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B1172" s="3"/>
       <c r="C1172" s="3"/>
@@ -29962,51 +29986,51 @@
     </row>
     <row r="1173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1173" s="6" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B1173" s="3">
         <v>79892367996</v>
       </c>
       <c r="C1173" s="3" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="D1173" s="3" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="E1173" s="3" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="F1173" s="3" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="G1173" s="3"/>
       <c r="H1173" s="3"/>
     </row>
     <row r="1174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1174" s="6" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B1174" s="3">
         <v>79182617888</v>
       </c>
       <c r="C1174" s="3" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="D1174" s="3" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="E1174" s="3" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="F1174" s="3" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="G1174" s="3"/>
       <c r="H1174" s="3"/>
     </row>
     <row r="1175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1175" s="6" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B1175" s="3"/>
       <c r="C1175" s="3"/>
@@ -30018,14 +30042,14 @@
     </row>
     <row r="1176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1176" s="6" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B1176" s="3">
         <v>79932156329</v>
       </c>
       <c r="C1176" s="3"/>
       <c r="D1176" s="3" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="E1176" s="3"/>
       <c r="F1176" s="3"/>
@@ -30034,14 +30058,14 @@
     </row>
     <row r="1177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1177" s="6" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="B1177" s="3">
         <v>79171772386</v>
       </c>
       <c r="C1177" s="3"/>
       <c r="D1177" s="3" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="E1177" s="3"/>
       <c r="F1177" s="3"/>
@@ -30050,14 +30074,14 @@
     </row>
     <row r="1178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1178" s="6" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B1178" s="3">
         <v>79515365516</v>
       </c>
       <c r="C1178" s="3"/>
       <c r="D1178" s="3" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="E1178" s="3"/>
       <c r="F1178" s="3"/>
@@ -30066,14 +30090,14 @@
     </row>
     <row r="1179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1179" s="6" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B1179" s="3">
         <v>79186559582</v>
       </c>
       <c r="C1179" s="3"/>
       <c r="D1179" s="3" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="E1179" s="3"/>
       <c r="F1179" s="3"/>
@@ -30082,7 +30106,7 @@
     </row>
     <row r="1180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1180" s="6" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="B1180" s="3">
         <v>79180300643</v>
@@ -30090,17 +30114,17 @@
       <c r="C1180" s="3"/>
       <c r="D1180" s="3"/>
       <c r="E1180" s="3" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="F1180" s="3" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="G1180" s="3"/>
       <c r="H1180" s="3"/>
     </row>
     <row r="1181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1181" s="6" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="B1181" s="3"/>
       <c r="C1181" s="3"/>
@@ -30112,13 +30136,13 @@
     </row>
     <row r="1182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1182" s="6" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="B1182" s="3">
         <v>79081882253</v>
       </c>
       <c r="C1182" s="3" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="D1182" s="3"/>
       <c r="E1182" s="3"/>
@@ -30128,13 +30152,13 @@
     </row>
     <row r="1183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1183" s="6" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="B1183" s="3">
         <v>79184570319</v>
       </c>
       <c r="C1183" s="3" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="D1183" s="3"/>
       <c r="E1183" s="3"/>
@@ -30144,7 +30168,7 @@
     </row>
     <row r="1184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1184" s="6" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="B1184" s="3"/>
       <c r="C1184" s="3"/>
@@ -30156,13 +30180,13 @@
     </row>
     <row r="1185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1185" s="6" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="B1185" s="3">
         <v>79884600699</v>
       </c>
       <c r="C1185" s="3" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="D1185" s="3"/>
       <c r="E1185" s="3"/>
@@ -30172,13 +30196,13 @@
     </row>
     <row r="1186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1186" s="6" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="B1186" s="3">
         <v>79615933002</v>
       </c>
       <c r="C1186" s="3" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="D1186" s="3"/>
       <c r="E1186" s="3"/>
@@ -30188,13 +30212,13 @@
     </row>
     <row r="1187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1187" s="6" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="B1187" s="3">
         <v>79287615615</v>
       </c>
       <c r="C1187" s="3" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="D1187" s="3"/>
       <c r="E1187" s="3"/>
@@ -30204,7 +30228,7 @@
     </row>
     <row r="1188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1188" s="6" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="B1188" s="3"/>
       <c r="C1188" s="3"/>
@@ -30216,27 +30240,27 @@
     </row>
     <row r="1189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1189" s="6" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="B1189" s="3">
         <v>79282298724</v>
       </c>
       <c r="C1189" s="3"/>
       <c r="D1189" s="3" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="E1189" s="3" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="F1189" s="3" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="G1189" s="3"/>
       <c r="H1189" s="3"/>
     </row>
     <row r="1190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1190" s="6" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="B1190" s="3"/>
       <c r="C1190" s="3"/>
@@ -30248,7 +30272,7 @@
     </row>
     <row r="1191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1191" s="6" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="B1191" s="3">
         <v>79608204295</v>
@@ -30256,17 +30280,17 @@
       <c r="C1191" s="3"/>
       <c r="D1191" s="3"/>
       <c r="E1191" s="3" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="F1191" s="3" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="G1191" s="3"/>
       <c r="H1191" s="3"/>
     </row>
     <row r="1192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1192" s="6" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="B1192" s="3">
         <v>79064969201</v>
@@ -30274,10 +30298,10 @@
       <c r="C1192" s="3"/>
       <c r="D1192" s="3"/>
       <c r="E1192" s="3" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="F1192" s="3" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="G1192" s="3"/>
       <c r="H1192" s="3"/>
@@ -30304,7 +30328,7 @@
     </row>
     <row r="1194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1194" s="6" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="B1194" s="3"/>
       <c r="C1194" s="3"/>
@@ -30316,7 +30340,7 @@
     </row>
     <row r="1195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1195" s="6" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="B1195" s="3">
         <v>79883604002</v>
@@ -30324,7 +30348,7 @@
       <c r="C1195" s="3"/>
       <c r="D1195" s="3"/>
       <c r="E1195" s="3" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="F1195" s="3"/>
       <c r="G1195" s="3"/>
@@ -30332,7 +30356,7 @@
     </row>
     <row r="1196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1196" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="B1196" s="3">
         <v>79384102024</v>
@@ -30340,7 +30364,7 @@
       <c r="C1196" s="3"/>
       <c r="D1196" s="3"/>
       <c r="E1196" s="3" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="F1196" s="3"/>
       <c r="G1196" s="3"/>
@@ -30348,7 +30372,7 @@
     </row>
     <row r="1197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1197" s="6" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="B1197" s="3"/>
       <c r="C1197" s="3"/>
@@ -30360,14 +30384,14 @@
     </row>
     <row r="1198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1198" s="6" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="B1198" s="3">
         <v>79898514111</v>
       </c>
       <c r="C1198" s="3"/>
       <c r="D1198" s="3" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="E1198" s="3"/>
       <c r="F1198" s="3"/>
@@ -30376,27 +30400,27 @@
     </row>
     <row r="1199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1199" s="6" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="B1199" s="3">
         <v>79374645805</v>
       </c>
       <c r="C1199" s="3" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="D1199" s="3"/>
       <c r="E1199" s="3" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="F1199" s="3" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="G1199" s="3"/>
       <c r="H1199" s="3"/>
     </row>
     <row r="1200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1200" s="6" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="B1200" s="3">
         <v>79892931818</v>
@@ -30404,17 +30428,17 @@
       <c r="C1200" s="3"/>
       <c r="D1200" s="3"/>
       <c r="E1200" s="3" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="F1200" s="3" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="G1200" s="3"/>
       <c r="H1200" s="3"/>
     </row>
     <row r="1201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1201" s="6" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="B1201" s="3"/>
       <c r="C1201" s="3"/>
@@ -30426,7 +30450,7 @@
     </row>
     <row r="1202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1202" s="6" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="B1202" s="3">
         <v>79504617288</v>
@@ -30434,26 +30458,26 @@
       <c r="C1202" s="3"/>
       <c r="D1202" s="3"/>
       <c r="E1202" s="3" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="F1202" s="3" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="G1202" s="3"/>
       <c r="H1202" s="3"/>
     </row>
     <row r="1203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1203" s="6" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="B1203" s="3">
         <v>79085129986</v>
       </c>
       <c r="C1203" s="3" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="D1203" s="3" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="E1203" s="3"/>
       <c r="F1203" s="3"/>
@@ -30462,7 +30486,7 @@
     </row>
     <row r="1204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1204" s="6" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="B1204" s="3"/>
       <c r="C1204" s="3"/>
@@ -30474,14 +30498,14 @@
     </row>
     <row r="1205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1205" s="6" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B1205" s="3">
         <v>79913567286</v>
       </c>
       <c r="C1205" s="3"/>
       <c r="D1205" s="3" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="E1205" s="3"/>
       <c r="F1205" s="3"/>
@@ -30490,13 +30514,13 @@
     </row>
     <row r="1206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1206" s="6" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="B1206" s="3">
         <v>79185010806</v>
       </c>
       <c r="C1206" s="3" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="D1206" s="3"/>
       <c r="E1206" s="3"/>
@@ -30506,13 +30530,13 @@
     </row>
     <row r="1207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1207" s="6" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B1207" s="3">
         <v>79183185307</v>
       </c>
       <c r="C1207" s="3" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="D1207" s="3"/>
       <c r="E1207" s="3"/>
@@ -30522,7 +30546,7 @@
     </row>
     <row r="1208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1208" s="6" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="B1208" s="3"/>
       <c r="C1208" s="3"/>
@@ -30534,13 +30558,13 @@
     </row>
     <row r="1209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1209" s="6" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="B1209" s="3">
         <v>79266566385</v>
       </c>
       <c r="C1209" s="3" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="D1209" s="3"/>
       <c r="E1209" s="3"/>
@@ -30570,7 +30594,7 @@
     </row>
     <row r="1211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1211" s="6" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="B1211" s="3"/>
       <c r="C1211" s="3"/>
@@ -30582,7 +30606,7 @@
     </row>
     <row r="1212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1212" s="6" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="B1212" s="3">
         <v>79284341070</v>
@@ -30590,17 +30614,17 @@
       <c r="C1212" s="3"/>
       <c r="D1212" s="3"/>
       <c r="E1212" s="3" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="F1212" s="3" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="G1212" s="3"/>
       <c r="H1212" s="3"/>
     </row>
     <row r="1213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1213" s="6" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B1213" s="3">
         <v>79267958573</v>
@@ -30608,24 +30632,24 @@
       <c r="C1213" s="3"/>
       <c r="D1213" s="3"/>
       <c r="E1213" s="3" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="F1213" s="3" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="G1213" s="3"/>
       <c r="H1213" s="3"/>
     </row>
     <row r="1214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1214" s="6" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B1214" s="3">
         <v>79282480877</v>
       </c>
       <c r="C1214" s="3"/>
       <c r="D1214" s="3" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="E1214" s="3"/>
       <c r="F1214" s="3"/>
@@ -30654,7 +30678,7 @@
     </row>
     <row r="1216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1216" s="6" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B1216" s="3"/>
       <c r="C1216" s="3"/>
@@ -30666,7 +30690,7 @@
     </row>
     <row r="1217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1217" s="6" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="B1217" s="3">
         <v>79181763655</v>
@@ -30674,17 +30698,17 @@
       <c r="C1217" s="3"/>
       <c r="D1217" s="3"/>
       <c r="E1217" s="3" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="F1217" s="3" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="G1217" s="3"/>
       <c r="H1217" s="3"/>
     </row>
     <row r="1218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1218" s="6" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="B1218" s="3"/>
       <c r="C1218" s="3"/>
@@ -30696,7 +30720,7 @@
     </row>
     <row r="1219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1219" s="6" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="B1219" s="3">
         <v>79184256275</v>
@@ -30704,26 +30728,26 @@
       <c r="C1219" s="3"/>
       <c r="D1219" s="3"/>
       <c r="E1219" s="3" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="F1219" s="3" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="G1219" s="3"/>
       <c r="H1219" s="3"/>
     </row>
     <row r="1220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1220" s="6" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="B1220" s="3">
         <v>79883151515</v>
       </c>
       <c r="C1220" s="3" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D1220" s="3" t="s">
         <v>2640</v>
-      </c>
-      <c r="D1220" s="3" t="s">
-        <v>2641</v>
       </c>
       <c r="E1220" s="3"/>
       <c r="F1220" s="3"/>
@@ -30752,7 +30776,7 @@
     </row>
     <row r="1222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1222" s="40" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B1222" s="2"/>
       <c r="C1222" s="2"/>
@@ -30764,27 +30788,27 @@
     </row>
     <row r="1223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1223" s="7" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="B1223" s="2">
         <v>79281186882</v>
       </c>
       <c r="C1223" s="2"/>
       <c r="D1223" s="2" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E1223" s="2" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F1223" s="2" t="s">
         <v>2222</v>
-      </c>
-      <c r="E1223" s="2" t="s">
-        <v>2224</v>
-      </c>
-      <c r="F1223" s="2" t="s">
-        <v>2223</v>
       </c>
       <c r="G1223" s="2"/>
       <c r="H1223" s="2"/>
     </row>
     <row r="1224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1224" s="40" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="B1224" s="2"/>
       <c r="C1224" s="2"/>
@@ -30796,13 +30820,13 @@
     </row>
     <row r="1225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1225" s="7" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="B1225" s="2">
         <v>79034547400</v>
       </c>
       <c r="C1225" s="2" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="D1225" s="2"/>
       <c r="E1225" s="2"/>
@@ -30812,13 +30836,13 @@
     </row>
     <row r="1226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1226" s="7" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="B1226" s="2">
         <v>79287721255</v>
       </c>
       <c r="C1226" s="2" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="D1226" s="2"/>
       <c r="E1226" s="2"/>
@@ -30848,7 +30872,7 @@
     </row>
     <row r="1228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1228" s="40" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="B1228" s="2"/>
       <c r="C1228" s="2"/>
@@ -30860,16 +30884,16 @@
     </row>
     <row r="1229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1229" s="7" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="B1229" s="2">
         <v>79183615308</v>
       </c>
       <c r="C1229" s="2" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="D1229" s="2" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="E1229" s="2"/>
       <c r="F1229" s="2"/>
@@ -30878,36 +30902,36 @@
     </row>
     <row r="1230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1230" s="7" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="B1230" s="2">
         <v>79186212666</v>
       </c>
       <c r="C1230" s="2" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D1230" s="2" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E1230" s="2" t="s">
+        <v>2318</v>
+      </c>
+      <c r="F1230" s="2" t="s">
         <v>2316</v>
-      </c>
-      <c r="D1230" s="2" t="s">
-        <v>2331</v>
-      </c>
-      <c r="E1230" s="2" t="s">
-        <v>2319</v>
-      </c>
-      <c r="F1230" s="2" t="s">
-        <v>2317</v>
       </c>
       <c r="G1230" s="2"/>
       <c r="H1230" s="2"/>
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1231" s="7" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B1231" s="2">
         <v>79951882337</v>
       </c>
       <c r="C1231" s="2"/>
       <c r="D1231" s="2" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="E1231" s="2"/>
       <c r="F1231" s="2"/>
@@ -30916,7 +30940,7 @@
     </row>
     <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1232" s="7" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="B1232" s="2">
         <v>79002796431</v>
@@ -30924,23 +30948,23 @@
       <c r="C1232" s="2"/>
       <c r="D1232" s="2"/>
       <c r="E1232" s="2" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="F1232" s="2" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="G1232" s="2"/>
       <c r="H1232" s="2"/>
     </row>
     <row r="1233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1233" s="7" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="B1233" s="2">
         <v>79384126478</v>
       </c>
       <c r="C1233" s="2" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="D1233" s="2"/>
       <c r="E1233" s="2"/>
@@ -30950,7 +30974,7 @@
     </row>
     <row r="1234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1234" s="40" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="B1234" s="2"/>
       <c r="C1234" s="2"/>
@@ -30962,22 +30986,22 @@
     </row>
     <row r="1235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1235" s="7" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="B1235" s="2">
         <v>79184673083</v>
       </c>
       <c r="C1235" s="2" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="D1235" s="2" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="E1235" s="2" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="F1235" s="2" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="G1235" s="2"/>
       <c r="H1235" s="2"/>
@@ -30990,10 +31014,10 @@
         <v>79184987541</v>
       </c>
       <c r="C1236" s="2" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="D1236" s="2" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="E1236" s="2"/>
       <c r="F1236" s="2"/>
@@ -31002,33 +31026,33 @@
     </row>
     <row r="1237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1237" s="7" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="B1237" s="2">
         <v>79624504198</v>
       </c>
       <c r="C1237" s="2"/>
       <c r="D1237" s="2" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="E1237" s="2" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="F1237" s="2" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="G1237" s="2"/>
       <c r="H1237" s="2"/>
     </row>
     <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1238" s="7" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="B1238" s="2">
         <v>79180458777</v>
       </c>
       <c r="C1238" s="2" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="D1238" s="2"/>
       <c r="E1238" s="2"/>
@@ -31038,7 +31062,7 @@
     </row>
     <row r="1239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1239" s="40" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="B1239" s="2"/>
       <c r="C1239" s="2"/>
@@ -31050,16 +31074,16 @@
     </row>
     <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1240" s="7" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="B1240" s="2">
         <v>79183291413</v>
       </c>
       <c r="C1240" s="2" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="D1240" s="2" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="E1240" s="2"/>
       <c r="F1240" s="2"/>
@@ -31068,7 +31092,7 @@
     </row>
     <row r="1241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1241" s="7" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="B1241" s="2">
         <v>79882371168</v>
@@ -31076,24 +31100,24 @@
       <c r="C1241" s="2"/>
       <c r="D1241" s="2"/>
       <c r="E1241" s="2" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="F1241" s="2" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="G1241" s="2"/>
       <c r="H1241" s="2"/>
     </row>
     <row r="1242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1242" s="7" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="B1242" s="2">
         <v>79885577597</v>
       </c>
       <c r="C1242" s="2"/>
       <c r="D1242" s="2" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="E1242" s="2"/>
       <c r="F1242" s="2"/>
@@ -31102,12 +31126,12 @@
     </row>
     <row r="1243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1243" s="7" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="B1243" s="17"/>
       <c r="C1243" s="2"/>
       <c r="D1243" s="2" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="E1243" s="2"/>
       <c r="F1243" s="2"/>
@@ -31136,7 +31160,7 @@
     </row>
     <row r="1245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1245" s="40" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="B1245" s="17"/>
       <c r="C1245" s="2"/>
@@ -31148,16 +31172,16 @@
     </row>
     <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1246" s="7" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="B1246" s="17">
         <v>79802319741</v>
       </c>
       <c r="C1246" s="2" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="D1246" s="2" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="E1246" s="2"/>
       <c r="F1246" s="2"/>
@@ -31166,7 +31190,7 @@
     </row>
     <row r="1247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1247" s="7" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="B1247" s="17">
         <v>79298260798</v>
@@ -31174,24 +31198,24 @@
       <c r="C1247" s="2"/>
       <c r="D1247" s="2"/>
       <c r="E1247" s="2" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="F1247" s="2" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="G1247" s="2"/>
       <c r="H1247" s="2"/>
     </row>
     <row r="1248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1248" s="7" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="B1248" s="17">
         <v>79615901223</v>
       </c>
       <c r="C1248" s="2"/>
       <c r="D1248" s="2" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="E1248" s="2"/>
       <c r="F1248" s="2"/>
@@ -31200,7 +31224,7 @@
     </row>
     <row r="1249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1249" s="7" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="B1249" s="17">
         <v>79183331040</v>
@@ -31208,37 +31232,37 @@
       <c r="C1249" s="2"/>
       <c r="D1249" s="2"/>
       <c r="E1249" s="2" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="F1249" s="2" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="G1249" s="2"/>
       <c r="H1249" s="2"/>
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1250" s="7" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B1250" s="17">
         <v>79064077747</v>
       </c>
       <c r="C1250" s="2" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="D1250" s="2"/>
       <c r="E1250" s="2" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="F1250" s="2" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="G1250" s="2"/>
       <c r="H1250" s="2"/>
     </row>
     <row r="1251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1251" s="40" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="B1251" s="17"/>
       <c r="C1251" s="2"/>
@@ -31250,38 +31274,38 @@
     </row>
     <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1252" s="7" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="B1252" s="17">
         <v>79181978847</v>
       </c>
       <c r="C1252" s="2" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="D1252" s="2" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="E1252" s="2" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="F1252" s="2" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="G1252" s="2"/>
       <c r="H1252" s="2"/>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1253" s="7" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="B1253" s="17">
         <v>79183346962</v>
       </c>
       <c r="C1253" s="2" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="D1253" s="2" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="E1253" s="2"/>
       <c r="F1253" s="2"/>
@@ -31290,7 +31314,7 @@
     </row>
     <row r="1254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1254" s="40" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="B1254" s="17"/>
       <c r="C1254" s="2"/>
@@ -31302,14 +31326,14 @@
     </row>
     <row r="1255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1255" s="7" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="B1255" s="17">
         <v>79518493781</v>
       </c>
       <c r="C1255" s="2"/>
       <c r="D1255" s="2" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="E1255" s="2"/>
       <c r="F1255" s="2"/>
@@ -31318,14 +31342,14 @@
     </row>
     <row r="1256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1256" s="7" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="B1256" s="17">
         <v>79180651355</v>
       </c>
       <c r="C1256" s="2"/>
       <c r="D1256" s="2" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="E1256" s="2"/>
       <c r="F1256" s="2"/>
@@ -31334,13 +31358,13 @@
     </row>
     <row r="1257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1257" s="7" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="B1257" s="17">
         <v>79281140670</v>
       </c>
       <c r="C1257" s="2" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="D1257" s="2"/>
       <c r="E1257" s="2"/>
@@ -31350,7 +31374,7 @@
     </row>
     <row r="1258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1258" s="40" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="B1258" s="17"/>
       <c r="C1258" s="2"/>
@@ -31362,14 +31386,14 @@
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1259" s="7" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="B1259" s="17">
         <v>79200671177</v>
       </c>
       <c r="C1259" s="2"/>
       <c r="D1259" s="2" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="E1259" s="2"/>
       <c r="F1259" s="2"/>
@@ -31378,7 +31402,7 @@
     </row>
     <row r="1260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1260" s="7" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="B1260" s="17">
         <v>79186201442</v>
@@ -31386,17 +31410,17 @@
       <c r="C1260" s="2"/>
       <c r="D1260" s="2"/>
       <c r="E1260" s="2" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="F1260" s="2" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1260" s="2"/>
       <c r="H1260" s="2"/>
     </row>
     <row r="1261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1261" s="40" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="B1261" s="17"/>
       <c r="C1261" s="2"/>
@@ -31408,13 +31432,13 @@
     </row>
     <row r="1262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1262" s="7" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="B1262" s="17">
         <v>79183108008</v>
       </c>
       <c r="C1262" s="2" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="D1262" s="2"/>
       <c r="E1262" s="2"/>
@@ -31424,27 +31448,27 @@
     </row>
     <row r="1263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1263" s="7" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="B1263" s="17">
         <v>79097178862</v>
       </c>
       <c r="C1263" s="2" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="D1263" s="2"/>
       <c r="E1263" s="2" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="F1263" s="2" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="G1263" s="2"/>
       <c r="H1263" s="2"/>
     </row>
     <row r="1264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1264" s="40" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="B1264" s="17"/>
       <c r="C1264" s="2"/>
@@ -31456,13 +31480,13 @@
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1265" s="7" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="B1265" s="17">
         <v>79787819232</v>
       </c>
       <c r="C1265" s="2" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="D1265" s="2"/>
       <c r="E1265" s="2"/>
@@ -31490,7 +31514,7 @@
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1267" s="40" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="B1267" s="17"/>
       <c r="C1267" s="2"/>
@@ -31502,36 +31526,36 @@
     </row>
     <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1268" s="7" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="B1268" s="17">
         <v>79181206771</v>
       </c>
       <c r="C1268" s="2" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D1268" s="2" t="s">
         <v>2462</v>
       </c>
-      <c r="D1268" s="2" t="s">
-        <v>2463</v>
-      </c>
       <c r="E1268" s="2" t="s">
+        <v>2464</v>
+      </c>
+      <c r="F1268" s="2" t="s">
         <v>2465</v>
-      </c>
-      <c r="F1268" s="2" t="s">
-        <v>2466</v>
       </c>
       <c r="G1268" s="2"/>
       <c r="H1268" s="2"/>
     </row>
     <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1269" s="7" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="B1269" s="17">
         <v>79286136662</v>
       </c>
       <c r="C1269" s="2"/>
       <c r="D1269" s="2" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="E1269" s="2"/>
       <c r="F1269" s="2"/>
@@ -31540,7 +31564,7 @@
     </row>
     <row r="1270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1270" s="40" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="B1270" s="17"/>
       <c r="C1270" s="2"/>
@@ -31552,14 +31576,14 @@
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1271" s="7" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="B1271" s="17">
         <v>375297856891</v>
       </c>
       <c r="C1271" s="2"/>
       <c r="D1271" s="2" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="E1271" s="2"/>
       <c r="F1271" s="2"/>
@@ -31568,16 +31592,16 @@
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1272" s="7" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="B1272" s="17">
         <v>79787715371</v>
       </c>
       <c r="C1272" s="2" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="D1272" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="E1272" s="2"/>
       <c r="F1272" s="2"/>
@@ -31586,14 +31610,14 @@
     </row>
     <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1273" s="7" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="B1273" s="17">
         <v>79189218545</v>
       </c>
       <c r="C1273" s="2"/>
       <c r="D1273" s="2" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="E1273" s="2"/>
       <c r="F1273" s="2"/>
@@ -31602,7 +31626,7 @@
     </row>
     <row r="1274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1274" s="40" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="B1274" s="17"/>
       <c r="C1274" s="2"/>
@@ -31614,16 +31638,16 @@
     </row>
     <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1275" s="7" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="B1275" s="17">
         <v>79883302117</v>
       </c>
       <c r="C1275" s="2" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="D1275" s="2" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="E1275" s="2"/>
       <c r="F1275" s="2"/>
@@ -31632,13 +31656,13 @@
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1276" s="7" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="B1276" s="17">
         <v>79885414599</v>
       </c>
       <c r="C1276" s="2" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="D1276" s="2"/>
       <c r="E1276" s="2"/>
@@ -31648,7 +31672,7 @@
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1277" s="7" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="B1277" s="17">
         <v>79606987172</v>
@@ -31656,17 +31680,17 @@
       <c r="C1277" s="2"/>
       <c r="D1277" s="2"/>
       <c r="E1277" s="2" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="F1277" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="G1277" s="2"/>
       <c r="H1277" s="2"/>
     </row>
     <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1278" s="40" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B1278" s="17"/>
       <c r="C1278" s="2"/>
@@ -31678,13 +31702,13 @@
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1279" s="7" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="B1279" s="17">
         <v>79002702201</v>
       </c>
       <c r="C1279" s="2" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="D1279" s="2"/>
       <c r="E1279" s="2"/>
@@ -31712,7 +31736,7 @@
     </row>
     <row r="1281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1281" s="40" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="B1281" s="17"/>
       <c r="C1281" s="2"/>
@@ -31724,13 +31748,13 @@
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1282" s="7" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="B1282" s="17">
         <v>79036910787</v>
       </c>
       <c r="C1282" s="2" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="D1282" s="2"/>
       <c r="E1282" s="2"/>
@@ -31740,58 +31764,58 @@
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1283" s="7" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="B1283" s="17">
         <v>79085097827</v>
       </c>
       <c r="C1283" s="2" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="D1283" s="2" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="E1283" s="2" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="F1283" s="2" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="G1283" s="2"/>
       <c r="H1283" s="2"/>
     </row>
     <row r="1284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1284" s="7" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="B1284" s="17">
         <v>79786456031</v>
       </c>
       <c r="C1284" s="2" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="D1284" s="2" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="E1284" s="2" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="F1284" s="2" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="G1284" s="2"/>
       <c r="H1284" s="2"/>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1285" s="7" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="B1285" s="17">
         <v>79180492172</v>
       </c>
       <c r="C1285" s="2"/>
       <c r="D1285" s="2" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="E1285" s="2"/>
       <c r="F1285" s="2"/>
@@ -31800,7 +31824,7 @@
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1286" s="40" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="B1286" s="17"/>
       <c r="C1286" s="2"/>
@@ -31812,7 +31836,7 @@
     </row>
     <row r="1287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1287" s="7" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="B1287" s="17">
         <v>79530708343</v>
@@ -31820,26 +31844,26 @@
       <c r="C1287" s="2"/>
       <c r="D1287" s="2"/>
       <c r="E1287" s="2" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="F1287" s="2" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="G1287" s="2"/>
       <c r="H1287" s="2"/>
     </row>
     <row r="1288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1288" s="7" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="B1288" s="17">
         <v>79618588262</v>
       </c>
       <c r="C1288" s="2" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="D1288" s="2" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="E1288" s="2"/>
       <c r="F1288" s="2"/>
@@ -31848,7 +31872,7 @@
     </row>
     <row r="1289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1289" s="7" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="B1289" s="17">
         <v>79990580869</v>
@@ -31856,17 +31880,17 @@
       <c r="C1289" s="2"/>
       <c r="D1289" s="2"/>
       <c r="E1289" s="2" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="F1289" s="2" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="G1289" s="2"/>
       <c r="H1289" s="2"/>
     </row>
     <row r="1290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1290" s="7" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="B1290" s="17">
         <v>79283306686</v>
@@ -31874,23 +31898,23 @@
       <c r="C1290" s="2"/>
       <c r="D1290" s="2"/>
       <c r="E1290" s="2" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="F1290" s="2" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="G1290" s="2"/>
       <c r="H1290" s="2"/>
     </row>
     <row r="1291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1291" s="7" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="B1291" s="17">
         <v>79184803174</v>
       </c>
       <c r="C1291" s="2" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="D1291" s="2"/>
       <c r="E1291" s="2"/>
@@ -31900,13 +31924,13 @@
     </row>
     <row r="1292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1292" s="7" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="B1292" s="17">
         <v>79186825836</v>
       </c>
       <c r="C1292" s="2" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="D1292" s="2"/>
       <c r="E1292" s="2"/>
@@ -31916,13 +31940,13 @@
     </row>
     <row r="1293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1293" s="7" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="B1293" s="17">
         <v>79182466940</v>
       </c>
       <c r="C1293" s="2" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="D1293" s="2"/>
       <c r="E1293" s="2"/>
@@ -31932,7 +31956,7 @@
     </row>
     <row r="1294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1294" s="40" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="B1294" s="17"/>
       <c r="C1294" s="2"/>
@@ -31943,16 +31967,16 @@
     </row>
     <row r="1295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1295" s="7" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="B1295" s="17">
         <v>79149202703</v>
       </c>
       <c r="C1295" s="2" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D1295" s="2" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="E1295" s="2"/>
       <c r="F1295" s="2"/>
@@ -31960,26 +31984,26 @@
     </row>
     <row r="1296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1296" s="7" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="B1296" s="17">
         <v>79885468941</v>
       </c>
       <c r="C1296" s="2" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D1296" s="2"/>
       <c r="E1296" s="2" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="F1296" s="2" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="G1296" s="2"/>
     </row>
     <row r="1297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1297" s="40" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="B1297" s="17"/>
       <c r="C1297" s="2"/>
@@ -31990,16 +32014,16 @@
     </row>
     <row r="1298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1298" s="7" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="B1298" s="17">
         <v>79806633494</v>
       </c>
       <c r="C1298" s="2" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
       <c r="D1298" s="2" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="E1298" s="2"/>
       <c r="F1298" s="2"/>
@@ -32024,7 +32048,7 @@
     </row>
     <row r="1300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1300" s="40" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="B1300" s="17"/>
       <c r="C1300" s="2"/>
@@ -32035,13 +32059,13 @@
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1301" s="7" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="B1301" s="17">
         <v>79525837593</v>
       </c>
       <c r="C1301" s="2" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="D1301" s="2"/>
       <c r="E1301" s="2"/>
@@ -32050,16 +32074,16 @@
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1302" s="7" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="B1302" s="17">
         <v>79183870112</v>
       </c>
       <c r="C1302" s="2" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="D1302" s="2" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="E1302" s="2"/>
       <c r="F1302" s="2"/>
@@ -32067,14 +32091,14 @@
     </row>
     <row r="1303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1303" s="7" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="B1303" s="17">
         <v>79182842938</v>
       </c>
       <c r="C1303" s="2"/>
       <c r="D1303" s="2" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="E1303" s="2"/>
       <c r="F1303" s="2"/>
@@ -32082,7 +32106,7 @@
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1304" s="40" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="B1304" s="17"/>
       <c r="C1304" s="2"/>
@@ -32093,28 +32117,28 @@
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1305" s="7" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="B1305" s="17">
         <v>79183772137</v>
       </c>
       <c r="C1305" s="2" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="D1305" s="2" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="E1305" s="2" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="F1305" s="2" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="G1305" s="2"/>
     </row>
     <row r="1306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1306" s="7" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="B1306" s="17">
         <v>79897201133</v>
@@ -32122,23 +32146,23 @@
       <c r="C1306" s="2"/>
       <c r="D1306" s="2"/>
       <c r="E1306" s="2" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="F1306" s="2" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="G1306" s="2"/>
     </row>
     <row r="1307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1307" s="7" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="B1307" s="17">
         <v>79615332857</v>
       </c>
       <c r="C1307" s="2"/>
       <c r="D1307" s="2" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="E1307" s="2"/>
       <c r="F1307" s="2"/>
@@ -32146,14 +32170,14 @@
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1308" s="7" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="B1308" s="17">
         <v>79184188755</v>
       </c>
       <c r="C1308" s="2"/>
       <c r="D1308" s="2" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="E1308" s="2"/>
       <c r="F1308" s="2"/>
@@ -32161,7 +32185,7 @@
     </row>
     <row r="1309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1309" s="40" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="B1309" s="17"/>
       <c r="C1309" s="2"/>
@@ -32172,14 +32196,14 @@
     </row>
     <row r="1310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1310" s="7" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="B1310" s="17">
         <v>79034550320</v>
       </c>
       <c r="C1310" s="2"/>
       <c r="D1310" s="2" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="E1310" s="2"/>
       <c r="F1310" s="2"/>
@@ -32187,13 +32211,13 @@
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1311" s="7" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="B1311" s="17">
         <v>79497336125</v>
       </c>
       <c r="C1311" s="2" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="D1311" s="2"/>
       <c r="E1311" s="2"/>
@@ -32202,14 +32226,14 @@
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1312" s="7" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="B1312" s="17">
         <v>79676739173</v>
       </c>
       <c r="C1312" s="2"/>
       <c r="D1312" s="2" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="E1312" s="2"/>
       <c r="F1312" s="2"/>
@@ -32234,7 +32258,7 @@
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1314" s="40" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="B1314" s="17"/>
       <c r="C1314" s="2"/>
@@ -32245,26 +32269,26 @@
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1315" s="7" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="B1315" s="17">
         <v>79183767815</v>
       </c>
       <c r="C1315" s="2"/>
       <c r="D1315" s="2" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="E1315" s="2" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="F1315" s="2" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="G1315" s="2"/>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1316" s="40" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="C1316" s="2"/>
       <c r="D1316" s="2"/>
@@ -32274,13 +32298,13 @@
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1317" s="7" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="B1317" s="17">
         <v>79528700394</v>
       </c>
       <c r="C1317" s="2" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="D1317" s="2"/>
       <c r="E1317" s="2"/>
@@ -32289,13 +32313,13 @@
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1318" s="7" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="B1318" s="17">
         <v>79054305403</v>
       </c>
       <c r="C1318" s="2" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="D1318" s="2"/>
       <c r="E1318" s="2"/>
@@ -32304,14 +32328,14 @@
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1319" s="7" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="B1319" s="17">
         <v>79064046088</v>
       </c>
       <c r="C1319" s="2"/>
       <c r="D1319" s="2" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="E1319" s="2"/>
       <c r="F1319" s="2"/>
@@ -32319,16 +32343,16 @@
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1320" s="7" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="B1320" s="17">
         <v>79284483258</v>
       </c>
       <c r="C1320" s="2" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="D1320" s="2" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="E1320" s="2"/>
       <c r="F1320" s="2"/>
@@ -32336,7 +32360,7 @@
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1321" s="40" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="B1321" s="17"/>
       <c r="C1321" s="2"/>
@@ -32347,13 +32371,13 @@
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1322" s="7" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="B1322">
         <v>79081817570</v>
       </c>
       <c r="C1322" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="D1322" s="2"/>
       <c r="E1322" s="2"/>
@@ -32362,23 +32386,23 @@
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1323" s="7" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="B1323">
         <v>79045033313</v>
       </c>
       <c r="D1323" s="2"/>
       <c r="E1323" s="2" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="F1323" s="2" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="G1323" s="2"/>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1324" s="40" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="D1324" s="2"/>
       <c r="E1324" s="2"/>
@@ -32387,26 +32411,26 @@
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1325" s="7" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="B1325" s="17">
         <v>79186195666</v>
       </c>
       <c r="C1325" s="2" t="s">
-        <v>731</v>
+        <v>2723</v>
       </c>
       <c r="D1325" s="2"/>
       <c r="E1325" s="2" t="s">
-        <v>731</v>
+        <v>2731</v>
       </c>
       <c r="F1325" s="2" t="s">
-        <v>731</v>
+        <v>2729</v>
       </c>
       <c r="G1325" s="2"/>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1326" s="7" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="B1326" s="17">
         <v>79780648554</v>
@@ -32414,23 +32438,23 @@
       <c r="C1326" s="2"/>
       <c r="D1326" s="2"/>
       <c r="E1326" s="2" t="s">
-        <v>731</v>
+        <v>2731</v>
       </c>
       <c r="F1326" s="2" t="s">
-        <v>731</v>
+        <v>2730</v>
       </c>
       <c r="G1326" s="2"/>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1327" s="7" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="B1327" s="17">
         <v>79493022752</v>
       </c>
       <c r="C1327" s="2"/>
       <c r="D1327" s="2" t="s">
-        <v>731</v>
+        <v>2724</v>
       </c>
       <c r="E1327" s="2"/>
       <c r="F1327" s="2"/>
@@ -32438,7 +32462,7 @@
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1328" s="40" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="B1328" s="17"/>
       <c r="C1328" s="2"/>
@@ -32449,14 +32473,14 @@
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1329" s="7" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="B1329" s="17">
         <v>79085033991</v>
       </c>
       <c r="C1329" s="2"/>
       <c r="D1329" s="2" t="s">
-        <v>731</v>
+        <v>2725</v>
       </c>
       <c r="E1329" s="2"/>
       <c r="F1329" s="2"/>
@@ -32464,7 +32488,7 @@
     </row>
     <row r="1330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1330" s="7" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="B1330" s="17">
         <v>79282576368</v>
@@ -32477,7 +32501,7 @@
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1331" s="40" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="B1331" s="17"/>
       <c r="C1331" s="2"/>
@@ -32488,13 +32512,13 @@
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1332" s="7" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="B1332" s="17">
         <v>79054871997</v>
       </c>
       <c r="C1332" s="2" t="s">
-        <v>731</v>
+        <v>2728</v>
       </c>
       <c r="D1332" s="2"/>
       <c r="E1332" s="2"/>
@@ -32503,14 +32527,14 @@
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1333" s="7" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="B1333" s="17">
         <v>79193683714</v>
       </c>
       <c r="C1333" s="2"/>
       <c r="D1333" s="2" t="s">
-        <v>731</v>
+        <v>2727</v>
       </c>
       <c r="E1333" s="2"/>
       <c r="F1333" s="2"/>
@@ -32518,14 +32542,14 @@
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1334" s="7" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="B1334" s="17">
         <v>79586493944</v>
       </c>
       <c r="C1334" s="2"/>
       <c r="D1334" s="2" t="s">
-        <v>731</v>
+        <v>2726</v>
       </c>
       <c r="E1334" s="2"/>
       <c r="F1334" s="2"/>
@@ -32533,13 +32557,13 @@
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1335" s="7" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="B1335" s="17">
         <v>79780045546</v>
       </c>
       <c r="C1335" s="2" t="s">
-        <v>731</v>
+        <v>2728</v>
       </c>
       <c r="D1335" s="2"/>
       <c r="E1335" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656B46BD-EE31-4C15-862E-705F01F4862E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA438933-58D3-47CC-B0B0-822207699AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4214" uniqueCount="2732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4214" uniqueCount="2733">
   <si>
     <t>Пароль</t>
   </si>
@@ -7386,9 +7386,6 @@
     <t>!https://disk.yandex.ru/d/mANBZHgi1nFiog</t>
   </si>
   <si>
-    <t>!https://disk.yandex.ru/d/N2q_kuKYQoghKw</t>
-  </si>
-  <si>
     <t>!https://disk.yandex.ru/d/iBPZCOFaPqVCwA</t>
   </si>
   <si>
@@ -7401,9 +7398,6 @@
     <t>!https://disk.yandex.ru/d/f1RIE0m0BBEifw</t>
   </si>
   <si>
-    <t>!https://disk.yandex.ru/d/o0HaEp7UvXRC5w</t>
-  </si>
-  <si>
     <t>!https://disk.yandex.ru/d/xMKY80LtJxpW0g</t>
   </si>
   <si>
@@ -8230,6 +8224,15 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/P1cyniJFzuwCaw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/N2q_kuKYQoghKw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/o0HaEp7UvXRC5w</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/mBLEef6zsiWZiw</t>
   </si>
 </sst>
 </file>
@@ -24945,7 +24948,7 @@
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" s="34" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="B885" s="41">
         <v>79882548579</v>
@@ -24963,7 +24966,7 @@
     </row>
     <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" s="34" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B886" s="41">
         <v>79182900595</v>
@@ -24979,7 +24982,7 @@
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" s="34" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="B887" s="41">
         <v>79264823431</v>
@@ -24997,7 +25000,7 @@
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" s="34" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="B888" s="41">
         <v>79180246728</v>
@@ -25015,7 +25018,7 @@
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" s="34" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="B889" s="41">
         <v>79263181485</v>
@@ -25031,7 +25034,7 @@
     </row>
     <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" s="34" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="B890" s="41">
         <v>79189573595</v>
@@ -25049,7 +25052,7 @@
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" s="34" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B891" s="41">
         <v>79180129312</v>
@@ -25089,7 +25092,7 @@
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" s="34" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="B893" s="41">
         <v>79207020082</v>
@@ -25111,7 +25114,7 @@
     </row>
     <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" s="34" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B894" s="41">
         <v>79185072237</v>
@@ -25129,7 +25132,7 @@
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" s="34" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="B895" s="41">
         <v>79182762440</v>
@@ -25145,7 +25148,7 @@
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" s="34" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="B896" s="41">
         <v>79518702052</v>
@@ -25161,7 +25164,7 @@
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" s="34" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="B897" s="41">
         <v>79885456732</v>
@@ -25177,7 +25180,7 @@
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" s="34" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="B898" s="41">
         <v>79186323631</v>
@@ -25215,7 +25218,7 @@
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" s="34" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="B900" s="41">
         <v>79604946540</v>
@@ -25235,7 +25238,7 @@
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" s="34" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="B901" s="41">
         <v>79787713176</v>
@@ -25279,7 +25282,7 @@
     </row>
     <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" s="34" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="B903" s="41">
         <v>79881380533</v>
@@ -25295,7 +25298,7 @@
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" s="34" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="B904" s="41">
         <v>79876571770</v>
@@ -25317,7 +25320,7 @@
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" s="34" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="B905" s="41">
         <v>79185269969</v>
@@ -25339,7 +25342,7 @@
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" s="34" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="B906" s="41">
         <v>79788069407</v>
@@ -25361,7 +25364,7 @@
     </row>
     <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" s="34" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="B907" s="41">
         <v>79809148895</v>
@@ -25383,7 +25386,7 @@
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" s="34" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="B908" s="41">
         <v>79374600054</v>
@@ -25421,7 +25424,7 @@
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" s="34" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="B910" s="41">
         <v>79063480196</v>
@@ -25439,7 +25442,7 @@
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" s="34" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="B911" s="41">
         <v>79035002052</v>
@@ -25459,7 +25462,7 @@
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" s="34" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="B912" s="41">
         <v>79883667602</v>
@@ -25479,7 +25482,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A913" s="34" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="B913" s="41">
         <v>79991733748</v>
@@ -25495,7 +25498,7 @@
     </row>
     <row r="914" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A914" s="34" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="B914" s="41">
         <v>79168542102</v>
@@ -25515,7 +25518,7 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A915" s="34" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="B915" s="41">
         <v>79888928388</v>
@@ -25535,7 +25538,7 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A916" s="34" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="B916" s="41">
         <v>79032374317</v>
@@ -25577,7 +25580,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A918" s="34" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="B918" s="41">
         <v>79207020082</v>
@@ -25600,7 +25603,7 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A919" s="34" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="B919" s="41">
         <v>79041183867</v>
@@ -25621,7 +25624,7 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A920" s="34" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="B920" s="41">
         <v>79032978483</v>
@@ -25642,7 +25645,7 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A921" s="34" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="B921" s="41">
         <v>79308038836</v>
@@ -25665,7 +25668,7 @@
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A922" s="34" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="B922" s="41">
         <v>79385488845</v>
@@ -25688,7 +25691,7 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A923" s="34" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="B923" s="41">
         <v>79046838139</v>
@@ -25709,7 +25712,7 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A924" s="34" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="B924" s="41">
         <v>79128268207</v>
@@ -25732,7 +25735,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A925" s="34" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="B925" s="41">
         <v>79148261215</v>
@@ -25755,7 +25758,7 @@
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A926" s="34" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="B926" s="41">
         <v>79267823227</v>
@@ -25776,7 +25779,7 @@
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A927" s="34" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="B927" s="41">
         <v>79184915237</v>
@@ -25801,7 +25804,7 @@
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A928" s="34" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="B928" s="41">
         <v>79034390003</v>
@@ -25848,7 +25851,7 @@
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" s="34" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="B930" s="41">
         <v>79595062068</v>
@@ -25904,7 +25907,7 @@
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" s="34" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
       <c r="B933" s="41">
         <v>79180664535</v>
@@ -25922,7 +25925,7 @@
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" s="34" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="B934" s="41">
         <v>79197382450</v>
@@ -25942,7 +25945,7 @@
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" s="34" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="B935" s="41">
         <v>79885220528</v>
@@ -25964,7 +25967,7 @@
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" s="34" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="B936" s="41">
         <v>79885093331</v>
@@ -26008,7 +26011,7 @@
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" s="34" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="B938" s="41">
         <v>79184400178</v>
@@ -26030,7 +26033,7 @@
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" s="34" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
       <c r="B939" s="41">
         <v>79183270587</v>
@@ -26048,7 +26051,7 @@
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" s="34" t="s">
-        <v>2654</v>
+        <v>2652</v>
       </c>
       <c r="B940" s="41">
         <v>79183889940</v>
@@ -26066,7 +26069,7 @@
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" s="34" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="B941" s="41">
         <v>79994722206</v>
@@ -26082,7 +26085,7 @@
     </row>
     <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" s="34" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="B942" s="41">
         <v>79184165266</v>
@@ -26122,7 +26125,7 @@
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" s="34" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="B944" s="41">
         <v>79160231803</v>
@@ -26140,7 +26143,7 @@
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" s="34" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="B945" s="41">
         <v>79251587458</v>
@@ -26158,7 +26161,7 @@
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" s="34" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="B946" s="41">
         <v>79385519412</v>
@@ -26264,7 +26267,7 @@
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" s="34" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="B952" s="35">
         <v>79895106888</v>
@@ -26280,7 +26283,7 @@
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" s="34" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="B953" s="35">
         <v>79189487859</v>
@@ -26298,7 +26301,7 @@
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" s="34" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="B954" s="35">
         <v>79094690279</v>
@@ -26318,7 +26321,7 @@
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" s="34" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="B955" s="35">
         <v>79270465755</v>
@@ -26338,7 +26341,7 @@
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" s="34" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="B956" s="35">
         <v>79181514761</v>
@@ -26370,7 +26373,7 @@
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" s="34" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="B958" s="35">
         <v>79286120337</v>
@@ -26390,7 +26393,7 @@
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" s="34" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="B959" s="35">
         <v>79181603172</v>
@@ -26408,7 +26411,7 @@
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" s="34" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="B960" s="35">
         <v>79528474569</v>
@@ -26426,7 +26429,7 @@
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" s="34" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="B961" s="35">
         <v>79891443888</v>
@@ -26454,7 +26457,7 @@
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" s="34" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="B963" s="35">
         <v>79186956626</v>
@@ -26470,7 +26473,7 @@
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" s="34" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="B964" s="35">
         <v>79183433464</v>
@@ -26488,7 +26491,7 @@
     </row>
     <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" s="34" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="B965" s="35">
         <v>79094646000</v>
@@ -26504,7 +26507,7 @@
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" s="34" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="B966" s="35">
         <v>79854264076</v>
@@ -26520,7 +26523,7 @@
     </row>
     <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" s="34" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="B967" s="35">
         <v>79186525585</v>
@@ -26536,7 +26539,7 @@
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" s="34" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="B968" s="35">
         <v>79528581269</v>
@@ -26556,7 +26559,7 @@
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" s="34" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="B969" s="35">
         <v>79673053030</v>
@@ -26586,7 +26589,7 @@
     </row>
     <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" s="34" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="B971" s="35">
         <v>79886696618</v>
@@ -26736,7 +26739,7 @@
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" s="34" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="B978" s="35">
         <v>79117974075</v>
@@ -26754,7 +26757,7 @@
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" s="34" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="B979" s="35">
         <v>79615951401</v>
@@ -26772,7 +26775,7 @@
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" s="34" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="B980" s="35">
         <v>79274773218</v>
@@ -26790,7 +26793,7 @@
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" s="34" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
       <c r="B981" s="35">
         <v>79673005052</v>
@@ -26808,7 +26811,7 @@
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" s="34" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
       <c r="B982" s="35">
         <v>79625245851</v>
@@ -26826,7 +26829,7 @@
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" s="34" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="B983" s="35">
         <v>79898052605</v>
@@ -26844,7 +26847,7 @@
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" s="34" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="B984" s="35">
         <v>79992365729</v>
@@ -26886,7 +26889,7 @@
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" s="34" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="B986" s="41">
         <v>79182119543</v>
@@ -26902,7 +26905,7 @@
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" s="34" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="B987" s="41">
         <v>79886039199</v>
@@ -26922,7 +26925,7 @@
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" s="34" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="B988" s="41">
         <v>79182846179</v>
@@ -26940,7 +26943,7 @@
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" s="34" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B989" s="41">
         <v>79185545589</v>
@@ -26958,7 +26961,7 @@
     </row>
     <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" s="34" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="B990" s="41">
         <v>79637505138</v>
@@ -26974,7 +26977,7 @@
     </row>
     <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" s="34" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="B991" s="41">
         <v>79604757152</v>
@@ -26992,7 +26995,7 @@
     </row>
     <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" s="34" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="B992" s="41">
         <v>79182762782</v>
@@ -27034,7 +27037,7 @@
     </row>
     <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" s="34" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
       <c r="B994" s="41">
         <v>79892941007</v>
@@ -27050,7 +27053,7 @@
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" s="34" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="B995" s="41">
         <v>79060896267</v>
@@ -27070,7 +27073,7 @@
     </row>
     <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" s="34" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
       <c r="B996" s="41">
         <v>79384227276</v>
@@ -27110,7 +27113,7 @@
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" s="34" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
       <c r="B998" s="41">
         <v>79614238176</v>
@@ -27138,7 +27141,7 @@
     </row>
     <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" s="34" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
       <c r="B1000" s="41">
         <v>79280121007</v>
@@ -27166,7 +27169,7 @@
     </row>
     <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" s="34" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
       <c r="B1002" s="41">
         <v>79180985165</v>
@@ -27182,7 +27185,7 @@
     </row>
     <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" s="34" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
       <c r="B1003" s="41">
         <v>79186200028</v>
@@ -27198,7 +27201,7 @@
     </row>
     <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" s="34" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
       <c r="B1004" s="41">
         <v>79190278727</v>
@@ -27226,7 +27229,7 @@
     </row>
     <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" s="34" t="s">
-        <v>2699</v>
+        <v>2697</v>
       </c>
       <c r="B1006" s="41">
         <v>79615280373</v>
@@ -27242,7 +27245,7 @@
     </row>
     <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1007" s="34" t="s">
-        <v>2700</v>
+        <v>2698</v>
       </c>
       <c r="B1007" s="41">
         <v>79622028701</v>
@@ -27258,7 +27261,7 @@
     </row>
     <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1008" s="34" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
       <c r="B1008" s="41">
         <v>79185055723</v>
@@ -27274,7 +27277,7 @@
     </row>
     <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" s="34" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
       <c r="B1009" s="41">
         <v>79788139855</v>
@@ -27302,7 +27305,7 @@
     </row>
     <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" s="34" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="B1011" s="41">
         <v>79189749194</v>
@@ -27320,7 +27323,7 @@
     </row>
     <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" s="34" t="s">
-        <v>2704</v>
+        <v>2702</v>
       </c>
       <c r="B1012" s="41">
         <v>79184801108</v>
@@ -27338,7 +27341,7 @@
     </row>
     <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" s="34" t="s">
-        <v>2705</v>
+        <v>2703</v>
       </c>
       <c r="B1013" s="41">
         <v>79646847710</v>
@@ -27354,7 +27357,7 @@
     </row>
     <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" s="34" t="s">
-        <v>2706</v>
+        <v>2704</v>
       </c>
       <c r="B1014" s="41">
         <v>79649041350</v>
@@ -27382,7 +27385,7 @@
     </row>
     <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" s="34" t="s">
-        <v>2707</v>
+        <v>2705</v>
       </c>
       <c r="B1016" s="33">
         <v>79181537666</v>
@@ -27398,7 +27401,7 @@
     </row>
     <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" s="34" t="s">
-        <v>2708</v>
+        <v>2706</v>
       </c>
       <c r="B1017" s="33">
         <v>79051511564</v>
@@ -27414,7 +27417,7 @@
     </row>
     <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" s="34" t="s">
-        <v>2709</v>
+        <v>2707</v>
       </c>
       <c r="B1018" s="33">
         <v>79254155954</v>
@@ -27430,7 +27433,7 @@
     </row>
     <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" s="34" t="s">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="B1019" s="33">
         <v>79626803581</v>
@@ -27458,7 +27461,7 @@
     </row>
     <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" s="34" t="s">
-        <v>2711</v>
+        <v>2709</v>
       </c>
       <c r="B1021" s="33">
         <v>79281059268</v>
@@ -27474,7 +27477,7 @@
     </row>
     <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" s="34" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
       <c r="B1022" s="33">
         <v>79183388668</v>
@@ -27492,7 +27495,7 @@
     </row>
     <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" s="34" t="s">
-        <v>2713</v>
+        <v>2711</v>
       </c>
       <c r="B1023" s="33">
         <v>79067249922</v>
@@ -27520,7 +27523,7 @@
     </row>
     <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1025" s="34" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="B1025" s="33">
         <v>79052993315</v>
@@ -27538,7 +27541,7 @@
     </row>
     <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1026" s="34" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="B1026" s="33">
         <v>79043499977</v>
@@ -27568,7 +27571,7 @@
     </row>
     <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1028" s="34" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="B1028" s="33">
         <v>79052875113</v>
@@ -27584,7 +27587,7 @@
     </row>
     <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1029" s="34" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="B1029" s="33">
         <v>79061820166</v>
@@ -27600,7 +27603,7 @@
     </row>
     <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1030" s="34" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
       <c r="B1030" s="33">
         <v>79189333736</v>
@@ -27616,7 +27619,7 @@
     </row>
     <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1031" s="34" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="B1031" s="33">
         <v>79064327871</v>
@@ -27632,7 +27635,7 @@
     </row>
     <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1032" s="34" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="B1032" s="33">
         <v>79102891788</v>
@@ -27660,7 +27663,7 @@
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1034" s="34" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="B1034" s="33">
         <v>79183561661</v>
@@ -27678,7 +27681,7 @@
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1035" s="34" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="B1035" s="33">
         <v>79537206758</v>
@@ -29323,10 +29326,10 @@
         <v>2437</v>
       </c>
       <c r="D1132" s="18" t="s">
+        <v>2452</v>
+      </c>
+      <c r="E1132" s="18" t="s">
         <v>2453</v>
-      </c>
-      <c r="E1132" s="18" t="s">
-        <v>2454</v>
       </c>
       <c r="F1132" s="18" t="s">
         <v>1911</v>
@@ -29343,7 +29346,7 @@
       </c>
       <c r="C1133" s="18"/>
       <c r="D1133" s="18" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="E1133" s="18"/>
       <c r="F1133" s="18"/>
@@ -29373,7 +29376,7 @@
         <v>2438</v>
       </c>
       <c r="D1135" s="18" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="E1135" s="18"/>
       <c r="F1135" s="18"/>
@@ -29388,13 +29391,13 @@
         <v>79991005104</v>
       </c>
       <c r="C1136" s="18" t="s">
-        <v>2438</v>
+        <v>2732</v>
       </c>
       <c r="D1136" s="18" t="s">
-        <v>2450</v>
+        <v>2730</v>
       </c>
       <c r="E1136" s="18" t="s">
-        <v>2455</v>
+        <v>2731</v>
       </c>
       <c r="F1136" s="18" t="s">
         <v>1912</v>
@@ -29672,7 +29675,7 @@
       <c r="C1153" s="18"/>
       <c r="D1153" s="18"/>
       <c r="E1153" s="18" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="F1153" s="18" t="s">
         <v>2020</v>
@@ -29690,7 +29693,7 @@
       <c r="C1154" s="18"/>
       <c r="D1154" s="18"/>
       <c r="E1154" s="18" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="F1154" s="18" t="s">
         <v>2021</v>
@@ -29722,7 +29725,7 @@
         <v>79184455113</v>
       </c>
       <c r="C1156" s="18" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="D1156" s="18"/>
       <c r="E1156" s="18"/>
@@ -29806,7 +29809,7 @@
         <v>2443</v>
       </c>
       <c r="E1161" s="18" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="F1161" s="18" t="s">
         <v>2022</v>
@@ -29855,7 +29858,7 @@
       </c>
       <c r="C1164" s="3"/>
       <c r="D1164" s="3" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="E1164" s="3"/>
       <c r="F1164" s="3"/>
@@ -29871,7 +29874,7 @@
       </c>
       <c r="C1165" s="3"/>
       <c r="D1165" s="3" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
       <c r="E1165" s="3"/>
       <c r="F1165" s="3"/>
@@ -29887,7 +29890,7 @@
       </c>
       <c r="C1166" s="3"/>
       <c r="D1166" s="3" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="E1166" s="3"/>
       <c r="F1166" s="3"/>
@@ -29914,7 +29917,7 @@
         <v>79622153493</v>
       </c>
       <c r="C1168" s="3" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="D1168" s="3"/>
       <c r="E1168" s="3"/>
@@ -29930,10 +29933,10 @@
         <v>79266122721</v>
       </c>
       <c r="C1169" s="3" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="D1169" s="3" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="E1169" s="3"/>
       <c r="F1169" s="3"/>
@@ -29949,7 +29952,7 @@
       </c>
       <c r="C1170" s="3"/>
       <c r="D1170" s="3" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
       <c r="E1170" s="3"/>
       <c r="F1170" s="3"/>
@@ -29964,7 +29967,7 @@
         <v>79813022825</v>
       </c>
       <c r="C1171" s="3" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="D1171" s="3"/>
       <c r="E1171" s="3"/>
@@ -29992,13 +29995,13 @@
         <v>79892367996</v>
       </c>
       <c r="C1173" s="3" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="D1173" s="3" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="E1173" s="3" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="F1173" s="3" t="s">
         <v>2034</v>
@@ -30014,13 +30017,13 @@
         <v>79182617888</v>
       </c>
       <c r="C1174" s="3" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="D1174" s="3" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="E1174" s="3" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="F1174" s="3" t="s">
         <v>2034</v>
@@ -30049,7 +30052,7 @@
       </c>
       <c r="C1176" s="3"/>
       <c r="D1176" s="3" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="E1176" s="3"/>
       <c r="F1176" s="3"/>
@@ -30065,7 +30068,7 @@
       </c>
       <c r="C1177" s="3"/>
       <c r="D1177" s="3" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="E1177" s="3"/>
       <c r="F1177" s="3"/>
@@ -30081,7 +30084,7 @@
       </c>
       <c r="C1178" s="3"/>
       <c r="D1178" s="3" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="E1178" s="3"/>
       <c r="F1178" s="3"/>
@@ -30097,7 +30100,7 @@
       </c>
       <c r="C1179" s="3"/>
       <c r="D1179" s="3" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="E1179" s="3"/>
       <c r="F1179" s="3"/>
@@ -30114,7 +30117,7 @@
       <c r="C1180" s="3"/>
       <c r="D1180" s="3"/>
       <c r="E1180" s="3" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="F1180" s="3" t="s">
         <v>2060</v>
@@ -30142,7 +30145,7 @@
         <v>79081882253</v>
       </c>
       <c r="C1182" s="3" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="D1182" s="3"/>
       <c r="E1182" s="3"/>
@@ -30158,7 +30161,7 @@
         <v>79184570319</v>
       </c>
       <c r="C1183" s="3" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="D1183" s="3"/>
       <c r="E1183" s="3"/>
@@ -30186,7 +30189,7 @@
         <v>79884600699</v>
       </c>
       <c r="C1185" s="3" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="D1185" s="3"/>
       <c r="E1185" s="3"/>
@@ -30202,7 +30205,7 @@
         <v>79615933002</v>
       </c>
       <c r="C1186" s="3" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="D1186" s="3"/>
       <c r="E1186" s="3"/>
@@ -30218,7 +30221,7 @@
         <v>79287615615</v>
       </c>
       <c r="C1187" s="3" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="D1187" s="3"/>
       <c r="E1187" s="3"/>
@@ -30247,10 +30250,10 @@
       </c>
       <c r="C1189" s="3"/>
       <c r="D1189" s="3" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="E1189" s="3" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="F1189" s="3" t="s">
         <v>2070</v>
@@ -30280,7 +30283,7 @@
       <c r="C1191" s="3"/>
       <c r="D1191" s="3"/>
       <c r="E1191" s="3" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="F1191" s="3" t="s">
         <v>2071</v>
@@ -30298,7 +30301,7 @@
       <c r="C1192" s="3"/>
       <c r="D1192" s="3"/>
       <c r="E1192" s="3" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="F1192" s="3" t="s">
         <v>2072</v>
@@ -30348,7 +30351,7 @@
       <c r="C1195" s="3"/>
       <c r="D1195" s="3"/>
       <c r="E1195" s="3" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="F1195" s="3"/>
       <c r="G1195" s="3"/>
@@ -30364,7 +30367,7 @@
       <c r="C1196" s="3"/>
       <c r="D1196" s="3"/>
       <c r="E1196" s="3" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="F1196" s="3"/>
       <c r="G1196" s="3"/>
@@ -30391,7 +30394,7 @@
       </c>
       <c r="C1198" s="3"/>
       <c r="D1198" s="3" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="E1198" s="3"/>
       <c r="F1198" s="3"/>
@@ -30406,11 +30409,11 @@
         <v>79374645805</v>
       </c>
       <c r="C1199" s="3" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="D1199" s="3"/>
       <c r="E1199" s="3" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="F1199" s="3" t="s">
         <v>2080</v>
@@ -30428,7 +30431,7 @@
       <c r="C1200" s="3"/>
       <c r="D1200" s="3"/>
       <c r="E1200" s="3" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="F1200" s="3" t="s">
         <v>2080</v>
@@ -30458,7 +30461,7 @@
       <c r="C1202" s="3"/>
       <c r="D1202" s="3"/>
       <c r="E1202" s="3" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
       <c r="F1202" s="3" t="s">
         <v>2161</v>
@@ -30474,10 +30477,10 @@
         <v>79085129986</v>
       </c>
       <c r="C1203" s="3" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="D1203" s="3" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="E1203" s="3"/>
       <c r="F1203" s="3"/>
@@ -30505,7 +30508,7 @@
       </c>
       <c r="C1205" s="3"/>
       <c r="D1205" s="3" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="E1205" s="3"/>
       <c r="F1205" s="3"/>
@@ -30520,7 +30523,7 @@
         <v>79185010806</v>
       </c>
       <c r="C1206" s="3" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="D1206" s="3"/>
       <c r="E1206" s="3"/>
@@ -30536,7 +30539,7 @@
         <v>79183185307</v>
       </c>
       <c r="C1207" s="3" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="D1207" s="3"/>
       <c r="E1207" s="3"/>
@@ -30564,7 +30567,7 @@
         <v>79266566385</v>
       </c>
       <c r="C1209" s="3" t="s">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="D1209" s="3"/>
       <c r="E1209" s="3"/>
@@ -30614,7 +30617,7 @@
       <c r="C1212" s="3"/>
       <c r="D1212" s="3"/>
       <c r="E1212" s="3" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="F1212" s="3" t="s">
         <v>2204</v>
@@ -30632,7 +30635,7 @@
       <c r="C1213" s="3"/>
       <c r="D1213" s="3"/>
       <c r="E1213" s="3" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="F1213" s="3" t="s">
         <v>2205</v>
@@ -30649,7 +30652,7 @@
       </c>
       <c r="C1214" s="3"/>
       <c r="D1214" s="3" t="s">
-        <v>2641</v>
+        <v>2639</v>
       </c>
       <c r="E1214" s="3"/>
       <c r="F1214" s="3"/>
@@ -30698,7 +30701,7 @@
       <c r="C1217" s="3"/>
       <c r="D1217" s="3"/>
       <c r="E1217" s="3" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="F1217" s="3" t="s">
         <v>2214</v>
@@ -30728,7 +30731,7 @@
       <c r="C1219" s="3"/>
       <c r="D1219" s="3"/>
       <c r="E1219" s="3" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="F1219" s="3" t="s">
         <v>2215</v>
@@ -30744,10 +30747,10 @@
         <v>79883151515</v>
       </c>
       <c r="C1220" s="3" t="s">
-        <v>2639</v>
+        <v>2637</v>
       </c>
       <c r="D1220" s="3" t="s">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="E1220" s="3"/>
       <c r="F1220" s="3"/>
@@ -31514,7 +31517,7 @@
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1267" s="40" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="B1267" s="17"/>
       <c r="C1267" s="2"/>
@@ -31526,36 +31529,36 @@
     </row>
     <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1268" s="7" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="B1268" s="17">
         <v>79181206771</v>
       </c>
       <c r="C1268" s="2" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="D1268" s="2" t="s">
+        <v>2460</v>
+      </c>
+      <c r="E1268" s="2" t="s">
         <v>2462</v>
       </c>
-      <c r="E1268" s="2" t="s">
-        <v>2464</v>
-      </c>
       <c r="F1268" s="2" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="G1268" s="2"/>
       <c r="H1268" s="2"/>
     </row>
     <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1269" s="7" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="B1269" s="17">
         <v>79286136662</v>
       </c>
       <c r="C1269" s="2"/>
       <c r="D1269" s="2" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="E1269" s="2"/>
       <c r="F1269" s="2"/>
@@ -31564,7 +31567,7 @@
     </row>
     <row r="1270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1270" s="40" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="B1270" s="17"/>
       <c r="C1270" s="2"/>
@@ -31576,14 +31579,14 @@
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1271" s="7" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="B1271" s="17">
         <v>375297856891</v>
       </c>
       <c r="C1271" s="2"/>
       <c r="D1271" s="2" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="E1271" s="2"/>
       <c r="F1271" s="2"/>
@@ -31592,16 +31595,16 @@
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1272" s="7" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="B1272" s="17">
         <v>79787715371</v>
       </c>
       <c r="C1272" s="2" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="D1272" s="2" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="E1272" s="2"/>
       <c r="F1272" s="2"/>
@@ -31610,14 +31613,14 @@
     </row>
     <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1273" s="7" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="B1273" s="17">
         <v>79189218545</v>
       </c>
       <c r="C1273" s="2"/>
       <c r="D1273" s="2" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="E1273" s="2"/>
       <c r="F1273" s="2"/>
@@ -31626,7 +31629,7 @@
     </row>
     <row r="1274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1274" s="40" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="B1274" s="17"/>
       <c r="C1274" s="2"/>
@@ -31638,16 +31641,16 @@
     </row>
     <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1275" s="7" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="B1275" s="17">
         <v>79883302117</v>
       </c>
       <c r="C1275" s="2" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="D1275" s="2" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="E1275" s="2"/>
       <c r="F1275" s="2"/>
@@ -31656,13 +31659,13 @@
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1276" s="7" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="B1276" s="17">
         <v>79885414599</v>
       </c>
       <c r="C1276" s="2" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="D1276" s="2"/>
       <c r="E1276" s="2"/>
@@ -31672,7 +31675,7 @@
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1277" s="7" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="B1277" s="17">
         <v>79606987172</v>
@@ -31680,17 +31683,17 @@
       <c r="C1277" s="2"/>
       <c r="D1277" s="2"/>
       <c r="E1277" s="2" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="F1277" s="2" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="G1277" s="2"/>
       <c r="H1277" s="2"/>
     </row>
     <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1278" s="40" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="B1278" s="17"/>
       <c r="C1278" s="2"/>
@@ -31702,13 +31705,13 @@
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1279" s="7" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="B1279" s="17">
         <v>79002702201</v>
       </c>
       <c r="C1279" s="2" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="D1279" s="2"/>
       <c r="E1279" s="2"/>
@@ -31736,7 +31739,7 @@
     </row>
     <row r="1281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1281" s="40" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="B1281" s="17"/>
       <c r="C1281" s="2"/>
@@ -31748,13 +31751,13 @@
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1282" s="7" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="B1282" s="17">
         <v>79036910787</v>
       </c>
       <c r="C1282" s="2" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="D1282" s="2"/>
       <c r="E1282" s="2"/>
@@ -31764,58 +31767,58 @@
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1283" s="7" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
       <c r="B1283" s="17">
         <v>79085097827</v>
       </c>
       <c r="C1283" s="2" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="D1283" s="2" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="E1283" s="2" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="F1283" s="2" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="G1283" s="2"/>
       <c r="H1283" s="2"/>
     </row>
     <row r="1284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1284" s="7" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="B1284" s="17">
         <v>79786456031</v>
       </c>
       <c r="C1284" s="2" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="D1284" s="2" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="E1284" s="2" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="F1284" s="2" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="G1284" s="2"/>
       <c r="H1284" s="2"/>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1285" s="7" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="B1285" s="17">
         <v>79180492172</v>
       </c>
       <c r="C1285" s="2"/>
       <c r="D1285" s="2" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="E1285" s="2"/>
       <c r="F1285" s="2"/>
@@ -31824,7 +31827,7 @@
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1286" s="40" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="B1286" s="17"/>
       <c r="C1286" s="2"/>
@@ -31836,7 +31839,7 @@
     </row>
     <row r="1287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1287" s="7" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="B1287" s="17">
         <v>79530708343</v>
@@ -31844,26 +31847,26 @@
       <c r="C1287" s="2"/>
       <c r="D1287" s="2"/>
       <c r="E1287" s="2" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="F1287" s="2" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="G1287" s="2"/>
       <c r="H1287" s="2"/>
     </row>
     <row r="1288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1288" s="7" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
       <c r="B1288" s="17">
         <v>79618588262</v>
       </c>
       <c r="C1288" s="2" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="D1288" s="2" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="E1288" s="2"/>
       <c r="F1288" s="2"/>
@@ -31872,7 +31875,7 @@
     </row>
     <row r="1289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1289" s="7" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="B1289" s="17">
         <v>79990580869</v>
@@ -31880,17 +31883,17 @@
       <c r="C1289" s="2"/>
       <c r="D1289" s="2"/>
       <c r="E1289" s="2" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="F1289" s="2" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="G1289" s="2"/>
       <c r="H1289" s="2"/>
     </row>
     <row r="1290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1290" s="7" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="B1290" s="17">
         <v>79283306686</v>
@@ -31898,23 +31901,23 @@
       <c r="C1290" s="2"/>
       <c r="D1290" s="2"/>
       <c r="E1290" s="2" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="F1290" s="2" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="G1290" s="2"/>
       <c r="H1290" s="2"/>
     </row>
     <row r="1291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1291" s="7" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
       <c r="B1291" s="17">
         <v>79184803174</v>
       </c>
       <c r="C1291" s="2" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="D1291" s="2"/>
       <c r="E1291" s="2"/>
@@ -31924,13 +31927,13 @@
     </row>
     <row r="1292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1292" s="7" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
       <c r="B1292" s="17">
         <v>79186825836</v>
       </c>
       <c r="C1292" s="2" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="D1292" s="2"/>
       <c r="E1292" s="2"/>
@@ -31940,13 +31943,13 @@
     </row>
     <row r="1293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1293" s="7" t="s">
-        <v>2558</v>
+        <v>2556</v>
       </c>
       <c r="B1293" s="17">
         <v>79182466940</v>
       </c>
       <c r="C1293" s="2" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="D1293" s="2"/>
       <c r="E1293" s="2"/>
@@ -31956,7 +31959,7 @@
     </row>
     <row r="1294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1294" s="40" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="B1294" s="17"/>
       <c r="C1294" s="2"/>
@@ -31967,16 +31970,16 @@
     </row>
     <row r="1295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1295" s="7" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="B1295" s="17">
         <v>79149202703</v>
       </c>
       <c r="C1295" s="2" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="D1295" s="2" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="E1295" s="2"/>
       <c r="F1295" s="2"/>
@@ -31984,26 +31987,26 @@
     </row>
     <row r="1296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1296" s="7" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="B1296" s="17">
         <v>79885468941</v>
       </c>
       <c r="C1296" s="2" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="D1296" s="2"/>
       <c r="E1296" s="2" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="F1296" s="2" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="G1296" s="2"/>
     </row>
     <row r="1297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1297" s="40" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="B1297" s="17"/>
       <c r="C1297" s="2"/>
@@ -32014,16 +32017,16 @@
     </row>
     <row r="1298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1298" s="7" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="B1298" s="17">
         <v>79806633494</v>
       </c>
       <c r="C1298" s="2" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="D1298" s="2" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="E1298" s="2"/>
       <c r="F1298" s="2"/>
@@ -32048,7 +32051,7 @@
     </row>
     <row r="1300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1300" s="40" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
       <c r="B1300" s="17"/>
       <c r="C1300" s="2"/>
@@ -32059,13 +32062,13 @@
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1301" s="7" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="B1301" s="17">
         <v>79525837593</v>
       </c>
       <c r="C1301" s="2" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="D1301" s="2"/>
       <c r="E1301" s="2"/>
@@ -32074,16 +32077,16 @@
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1302" s="7" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="B1302" s="17">
         <v>79183870112</v>
       </c>
       <c r="C1302" s="2" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="D1302" s="2" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="E1302" s="2"/>
       <c r="F1302" s="2"/>
@@ -32091,14 +32094,14 @@
     </row>
     <row r="1303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1303" s="7" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="B1303" s="17">
         <v>79182842938</v>
       </c>
       <c r="C1303" s="2"/>
       <c r="D1303" s="2" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="E1303" s="2"/>
       <c r="F1303" s="2"/>
@@ -32106,7 +32109,7 @@
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1304" s="40" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="B1304" s="17"/>
       <c r="C1304" s="2"/>
@@ -32117,28 +32120,28 @@
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1305" s="7" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="B1305" s="17">
         <v>79183772137</v>
       </c>
       <c r="C1305" s="2" t="s">
-        <v>2602</v>
+        <v>2600</v>
       </c>
       <c r="D1305" s="2" t="s">
-        <v>2600</v>
+        <v>2598</v>
       </c>
       <c r="E1305" s="2" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="F1305" s="2" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="G1305" s="2"/>
     </row>
     <row r="1306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1306" s="7" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="B1306" s="17">
         <v>79897201133</v>
@@ -32146,23 +32149,23 @@
       <c r="C1306" s="2"/>
       <c r="D1306" s="2"/>
       <c r="E1306" s="2" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="F1306" s="2" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="G1306" s="2"/>
     </row>
     <row r="1307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1307" s="7" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="B1307" s="17">
         <v>79615332857</v>
       </c>
       <c r="C1307" s="2"/>
       <c r="D1307" s="2" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="E1307" s="2"/>
       <c r="F1307" s="2"/>
@@ -32170,14 +32173,14 @@
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1308" s="7" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="B1308" s="17">
         <v>79184188755</v>
       </c>
       <c r="C1308" s="2"/>
       <c r="D1308" s="2" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="E1308" s="2"/>
       <c r="F1308" s="2"/>
@@ -32185,7 +32188,7 @@
     </row>
     <row r="1309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1309" s="40" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="B1309" s="17"/>
       <c r="C1309" s="2"/>
@@ -32196,14 +32199,14 @@
     </row>
     <row r="1310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1310" s="7" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
       <c r="B1310" s="17">
         <v>79034550320</v>
       </c>
       <c r="C1310" s="2"/>
       <c r="D1310" s="2" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="E1310" s="2"/>
       <c r="F1310" s="2"/>
@@ -32211,13 +32214,13 @@
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1311" s="7" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="B1311" s="17">
         <v>79497336125</v>
       </c>
       <c r="C1311" s="2" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="D1311" s="2"/>
       <c r="E1311" s="2"/>
@@ -32226,14 +32229,14 @@
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1312" s="7" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="B1312" s="17">
         <v>79676739173</v>
       </c>
       <c r="C1312" s="2"/>
       <c r="D1312" s="2" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
       <c r="E1312" s="2"/>
       <c r="F1312" s="2"/>
@@ -32258,7 +32261,7 @@
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1314" s="40" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="B1314" s="17"/>
       <c r="C1314" s="2"/>
@@ -32269,26 +32272,26 @@
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1315" s="7" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="B1315" s="17">
         <v>79183767815</v>
       </c>
       <c r="C1315" s="2"/>
       <c r="D1315" s="2" t="s">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="E1315" s="2" t="s">
-        <v>2621</v>
+        <v>2619</v>
       </c>
       <c r="F1315" s="2" t="s">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="G1315" s="2"/>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1316" s="40" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="C1316" s="2"/>
       <c r="D1316" s="2"/>
@@ -32298,13 +32301,13 @@
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1317" s="7" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="B1317" s="17">
         <v>79528700394</v>
       </c>
       <c r="C1317" s="2" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="D1317" s="2"/>
       <c r="E1317" s="2"/>
@@ -32313,13 +32316,13 @@
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1318" s="7" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="B1318" s="17">
         <v>79054305403</v>
       </c>
       <c r="C1318" s="2" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="D1318" s="2"/>
       <c r="E1318" s="2"/>
@@ -32328,14 +32331,14 @@
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1319" s="7" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="B1319" s="17">
         <v>79064046088</v>
       </c>
       <c r="C1319" s="2"/>
       <c r="D1319" s="2" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="E1319" s="2"/>
       <c r="F1319" s="2"/>
@@ -32343,16 +32346,16 @@
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1320" s="7" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="B1320" s="17">
         <v>79284483258</v>
       </c>
       <c r="C1320" s="2" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="D1320" s="2" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="E1320" s="2"/>
       <c r="F1320" s="2"/>
@@ -32360,7 +32363,7 @@
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1321" s="40" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
       <c r="B1321" s="17"/>
       <c r="C1321" s="2"/>
@@ -32371,13 +32374,13 @@
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1322" s="7" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="B1322">
         <v>79081817570</v>
       </c>
       <c r="C1322" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="D1322" s="2"/>
       <c r="E1322" s="2"/>
@@ -32386,23 +32389,23 @@
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1323" s="7" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="B1323">
         <v>79045033313</v>
       </c>
       <c r="D1323" s="2"/>
       <c r="E1323" s="2" t="s">
-        <v>2623</v>
+        <v>2621</v>
       </c>
       <c r="F1323" s="2" t="s">
-        <v>2622</v>
+        <v>2620</v>
       </c>
       <c r="G1323" s="2"/>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1324" s="40" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
       <c r="D1324" s="2"/>
       <c r="E1324" s="2"/>
@@ -32411,26 +32414,26 @@
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1325" s="7" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="B1325" s="17">
         <v>79186195666</v>
       </c>
       <c r="C1325" s="2" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="D1325" s="2"/>
       <c r="E1325" s="2" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
       <c r="F1325" s="2" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
       <c r="G1325" s="2"/>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1326" s="7" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="B1326" s="17">
         <v>79780648554</v>
@@ -32438,23 +32441,23 @@
       <c r="C1326" s="2"/>
       <c r="D1326" s="2"/>
       <c r="E1326" s="2" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
       <c r="F1326" s="2" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="G1326" s="2"/>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1327" s="7" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="B1327" s="17">
         <v>79493022752</v>
       </c>
       <c r="C1327" s="2"/>
       <c r="D1327" s="2" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
       <c r="E1327" s="2"/>
       <c r="F1327" s="2"/>
@@ -32462,7 +32465,7 @@
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1328" s="40" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="B1328" s="17"/>
       <c r="C1328" s="2"/>
@@ -32473,14 +32476,14 @@
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1329" s="7" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="B1329" s="17">
         <v>79085033991</v>
       </c>
       <c r="C1329" s="2"/>
       <c r="D1329" s="2" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
       <c r="E1329" s="2"/>
       <c r="F1329" s="2"/>
@@ -32488,7 +32491,7 @@
     </row>
     <row r="1330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1330" s="7" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="B1330" s="17">
         <v>79282576368</v>
@@ -32501,7 +32504,7 @@
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1331" s="40" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
       <c r="B1331" s="17"/>
       <c r="C1331" s="2"/>
@@ -32512,13 +32515,13 @@
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1332" s="7" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="B1332" s="17">
         <v>79054871997</v>
       </c>
       <c r="C1332" s="2" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="D1332" s="2"/>
       <c r="E1332" s="2"/>
@@ -32527,14 +32530,14 @@
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1333" s="7" t="s">
-        <v>2633</v>
+        <v>2631</v>
       </c>
       <c r="B1333" s="17">
         <v>79193683714</v>
       </c>
       <c r="C1333" s="2"/>
       <c r="D1333" s="2" t="s">
-        <v>2727</v>
+        <v>2725</v>
       </c>
       <c r="E1333" s="2"/>
       <c r="F1333" s="2"/>
@@ -32542,14 +32545,14 @@
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1334" s="7" t="s">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="B1334" s="17">
         <v>79586493944</v>
       </c>
       <c r="C1334" s="2"/>
       <c r="D1334" s="2" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="E1334" s="2"/>
       <c r="F1334" s="2"/>
@@ -32557,13 +32560,13 @@
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1335" s="7" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="B1335" s="17">
         <v>79780045546</v>
       </c>
       <c r="C1335" s="2" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="D1335" s="2"/>
       <c r="E1335" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA438933-58D3-47CC-B0B0-822207699AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB13B41-2476-45C4-AFA7-3CD3825E68C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4214" uniqueCount="2733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="2740">
   <si>
     <t>Пароль</t>
   </si>
@@ -6708,9 +6708,6 @@
     <t>https://disk.yandex.ru/d/UxxkSdyrYVkKOw</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/Y_ydhxC3q4W2RQ</t>
-  </si>
-  <si>
     <t>/?35020</t>
   </si>
   <si>
@@ -6975,60 +6972,21 @@
     <t>71168</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/uTFRqewiEU2Dug</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/yYI0mYEzMQixBw</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/q2khSj3BqXgrbA</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/5StYQ1WU1Gwohw</t>
   </si>
   <si>
     <t>https://disk.yandex.ru/i/2AeWQW2ZgDgZdw</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/FO1XCqpn3sh1sQ</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/v4mLn_t--sSUmw</t>
   </si>
   <si>
     <t>https://disk.yandex.ru/i/kNhyAy6LNqeFbw</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/jFZy7Zhe593nvw</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/wOIZfLUiJGTY7A</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/4USrRjQ5rlxS0Q</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/JbidCuKpaQQrPA</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/OX5LRriEzJsimA</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/xTrgISfJwTSOzw</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/HHtCpkrFNJWrZA</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/04NqA5nstOOvdw</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/Wq77S0n_knU3kw</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/ik-H_UgpkunJwA</t>
-  </si>
-  <si>
     <t>32351</t>
   </si>
   <si>
@@ -7236,9 +7194,6 @@
     <t>19232</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/sHoLaZvUkEqXuQ</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/d/YWKLkH1mraRwcQ</t>
   </si>
   <si>
@@ -8233,6 +8188,72 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/mBLEef6zsiWZiw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/Y_ydhxC3q4W2RQ</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/q2khSj3BqXgrbA</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/yYI0mYEzMQixBw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/uTFRqewiEU2Dug</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/Wq77S0n_knU3kw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/04NqA5nstOOvdw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/xTrgISfJwTSOzw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/sHoLaZvUkEqXuQ</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/HHtCpkrFNJWrZA</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/OX5LRriEzJsimA</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/ik-H_UgpkunJwA</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/JbidCuKpaQQrPA</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/FO1XCqpn3sh1sQ</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/jFZy7Zhe593nvw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/4USrRjQ5rlxS0Q</t>
+  </si>
+  <si>
+    <t>18/09/26/10:00</t>
+  </si>
+  <si>
+    <t>40332</t>
+  </si>
+  <si>
+    <t>18/09/26/12:30</t>
+  </si>
+  <si>
+    <t>77713</t>
+  </si>
+  <si>
+    <t>79922</t>
+  </si>
+  <si>
+    <t>* Дима</t>
+  </si>
+  <si>
+    <t>* ДанНя</t>
   </si>
 </sst>
 </file>
@@ -23246,7 +23267,7 @@
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" s="34" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="B792" s="41">
         <v>79090535020</v>
@@ -23262,7 +23283,7 @@
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A793" s="34" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="B793" s="41">
         <v>79615006915</v>
@@ -23278,7 +23299,7 @@
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" s="34" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="B794" s="41">
         <v>79628530371</v>
@@ -23296,7 +23317,7 @@
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" s="34" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="B795" s="41">
         <v>79184279501</v>
@@ -23312,7 +23333,7 @@
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" s="34" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="B796" s="41">
         <v>79002614878</v>
@@ -23330,7 +23351,7 @@
     </row>
     <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" s="34" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="B797" s="41">
         <v>79154071725</v>
@@ -23348,7 +23369,7 @@
     </row>
     <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" s="34" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="B798" s="41">
         <v>79183281110</v>
@@ -23370,7 +23391,7 @@
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" s="34" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B799" s="41">
         <v>79896303777</v>
@@ -23392,7 +23413,7 @@
     </row>
     <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" s="34" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B800" s="41">
         <v>79515542260</v>
@@ -23414,7 +23435,7 @@
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" s="34" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B801" s="41">
         <v>79109409590</v>
@@ -23432,7 +23453,7 @@
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" s="34" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="B802" s="41">
         <v>79184692981</v>
@@ -23450,7 +23471,7 @@
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" s="34" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="B803" s="41">
         <v>79091661065</v>
@@ -23470,7 +23491,7 @@
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" s="19" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="B804" s="42">
         <v>79161635439</v>
@@ -23488,7 +23509,7 @@
     </row>
     <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" s="19" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B805" s="42">
         <v>79085008025</v>
@@ -23504,7 +23525,7 @@
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" s="19" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B806" s="42">
         <v>79252655620</v>
@@ -23520,7 +23541,7 @@
     </row>
     <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" s="19" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="B807" s="42">
         <v>79892958854</v>
@@ -23600,7 +23621,7 @@
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" s="34" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B811" s="41">
         <v>79281983701</v>
@@ -23618,7 +23639,7 @@
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" s="34" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B812" s="41">
         <v>79779823186</v>
@@ -23636,7 +23657,7 @@
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" s="34" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="B813" s="41">
         <v>79262171635</v>
@@ -23654,7 +23675,7 @@
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" s="34" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B814" s="41">
         <v>79268883600</v>
@@ -23672,7 +23693,7 @@
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" s="34" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="B815" s="41">
         <v>79171859656</v>
@@ -23690,7 +23711,7 @@
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" s="34" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="B816" s="41">
         <v>79185600417</v>
@@ -23708,7 +23729,7 @@
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" s="34" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="B817" s="41">
         <v>79602752962</v>
@@ -23724,7 +23745,7 @@
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" s="34" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="B818" s="41">
         <v>79184482714</v>
@@ -23740,7 +23761,7 @@
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" s="34" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="B819" s="41">
         <v>79284144391</v>
@@ -23756,7 +23777,7 @@
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" s="34" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="B820" s="41">
         <v>79189225377</v>
@@ -23772,7 +23793,7 @@
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" s="34" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="B821" s="41">
         <v>79281043723</v>
@@ -23790,7 +23811,7 @@
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" s="34" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="B822" s="41">
         <v>79282794857</v>
@@ -23808,7 +23829,7 @@
     </row>
     <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" s="34" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="B823" s="41">
         <v>79284072814</v>
@@ -23826,7 +23847,7 @@
     </row>
     <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" s="34" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="B824" s="41">
         <v>79493721137</v>
@@ -23844,7 +23865,7 @@
     </row>
     <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" s="34" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="B825" s="41">
         <v>79648832641</v>
@@ -23886,7 +23907,7 @@
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" s="34" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="B827" s="41">
         <v>79187552473</v>
@@ -23902,7 +23923,7 @@
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" s="34" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="B828" s="41">
         <v>79189222000</v>
@@ -23918,7 +23939,7 @@
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" s="34" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="B829" s="41">
         <v>79853876186</v>
@@ -23936,7 +23957,7 @@
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" s="34" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="B830" s="41">
         <v>79270624682</v>
@@ -23954,7 +23975,7 @@
     </row>
     <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" s="34" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="B831" s="41">
         <v>79522284007</v>
@@ -23972,7 +23993,7 @@
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" s="34" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="B832" s="41">
         <v>79884095007</v>
@@ -23990,7 +24011,7 @@
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" s="34" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="B833" s="41">
         <v>79891200614</v>
@@ -24006,7 +24027,7 @@
     </row>
     <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" s="34" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="B834" s="41">
         <v>79189377109</v>
@@ -24022,7 +24043,7 @@
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" s="34" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="B835" s="41">
         <v>79289606020</v>
@@ -24038,7 +24059,7 @@
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" s="34" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="B836" s="41">
         <v>79618431980</v>
@@ -24078,7 +24099,7 @@
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" s="34" t="s">
-        <v>2375</v>
+        <v>2361</v>
       </c>
       <c r="B838" s="41">
         <v>79192492486</v>
@@ -24096,7 +24117,7 @@
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" s="34" t="s">
-        <v>2376</v>
+        <v>2362</v>
       </c>
       <c r="B839" s="41">
         <v>79182131150</v>
@@ -24112,7 +24133,7 @@
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" s="34" t="s">
-        <v>2377</v>
+        <v>2363</v>
       </c>
       <c r="B840" s="41">
         <v>79275956177</v>
@@ -24132,7 +24153,7 @@
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" s="34" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B841" s="41">
         <v>79789283600</v>
@@ -24152,7 +24173,7 @@
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" s="34" t="s">
-        <v>2378</v>
+        <v>2364</v>
       </c>
       <c r="B842" s="41">
         <v>79851997751</v>
@@ -24168,7 +24189,7 @@
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" s="34" t="s">
-        <v>2379</v>
+        <v>2365</v>
       </c>
       <c r="B843" s="41">
         <v>79282164434</v>
@@ -24184,7 +24205,7 @@
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" s="34" t="s">
-        <v>2380</v>
+        <v>2366</v>
       </c>
       <c r="B844" s="41">
         <v>79109617700</v>
@@ -24244,7 +24265,7 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" s="34" t="s">
-        <v>2406</v>
+        <v>2391</v>
       </c>
       <c r="B847" s="41">
         <v>79185972895</v>
@@ -24266,7 +24287,7 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" s="34" t="s">
-        <v>2407</v>
+        <v>2392</v>
       </c>
       <c r="B848" s="41">
         <v>79996262825</v>
@@ -24288,7 +24309,7 @@
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" s="34" t="s">
-        <v>2378</v>
+        <v>2364</v>
       </c>
       <c r="B849" s="41">
         <v>79851997751</v>
@@ -24310,7 +24331,7 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" s="34" t="s">
-        <v>2408</v>
+        <v>2393</v>
       </c>
       <c r="B850" s="41">
         <v>79604875670</v>
@@ -24332,7 +24353,7 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" s="34" t="s">
-        <v>2409</v>
+        <v>2394</v>
       </c>
       <c r="B851" s="41">
         <v>79184987541</v>
@@ -24350,7 +24371,7 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" s="34" t="s">
-        <v>2410</v>
+        <v>2395</v>
       </c>
       <c r="B852" s="41">
         <v>79185058918</v>
@@ -24366,7 +24387,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" s="34" t="s">
-        <v>2411</v>
+        <v>2396</v>
       </c>
       <c r="B853" s="41">
         <v>79084845045</v>
@@ -24386,7 +24407,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" s="34" t="s">
-        <v>2412</v>
+        <v>2397</v>
       </c>
       <c r="B854" s="41">
         <v>79189841111</v>
@@ -24402,7 +24423,7 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" s="34" t="s">
-        <v>2413</v>
+        <v>2398</v>
       </c>
       <c r="B855" s="41">
         <v>79183593299</v>
@@ -24424,7 +24445,7 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" s="34" t="s">
-        <v>2414</v>
+        <v>2399</v>
       </c>
       <c r="B856" s="41">
         <v>79286104433</v>
@@ -24442,7 +24463,7 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" s="34" t="s">
-        <v>2415</v>
+        <v>2400</v>
       </c>
       <c r="B857" s="41">
         <v>79181204920</v>
@@ -24460,7 +24481,7 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" s="34" t="s">
-        <v>2416</v>
+        <v>2401</v>
       </c>
       <c r="B858" s="41">
         <v>79180314664</v>
@@ -24478,7 +24499,7 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" s="34" t="s">
-        <v>2417</v>
+        <v>2402</v>
       </c>
       <c r="B859" s="41">
         <v>79255304182</v>
@@ -24496,7 +24517,7 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" s="34" t="s">
-        <v>2418</v>
+        <v>2403</v>
       </c>
       <c r="B860" s="41">
         <v>79624321777</v>
@@ -24514,7 +24535,7 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" s="34" t="s">
-        <v>2419</v>
+        <v>2404</v>
       </c>
       <c r="B861" s="41">
         <v>79034652185</v>
@@ -24530,7 +24551,7 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" s="34" t="s">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="B862" s="41">
         <v>79654707870</v>
@@ -24564,7 +24585,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" s="34" t="s">
-        <v>2421</v>
+        <v>2406</v>
       </c>
       <c r="B864" s="41">
         <v>79284244414</v>
@@ -24584,7 +24605,7 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" s="34" t="s">
-        <v>2422</v>
+        <v>2407</v>
       </c>
       <c r="B865" s="41">
         <v>79619719206</v>
@@ -24604,7 +24625,7 @@
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" s="34" t="s">
-        <v>2423</v>
+        <v>2408</v>
       </c>
       <c r="B866" s="41">
         <v>79530872704</v>
@@ -24660,7 +24681,7 @@
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" s="34" t="s">
-        <v>2424</v>
+        <v>2409</v>
       </c>
       <c r="B869" s="41">
         <v>79181112526</v>
@@ -24678,7 +24699,7 @@
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" s="19" t="s">
-        <v>2425</v>
+        <v>2410</v>
       </c>
       <c r="B870" s="42">
         <v>79186726140</v>
@@ -24718,7 +24739,7 @@
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" s="34" t="s">
-        <v>2426</v>
+        <v>2411</v>
       </c>
       <c r="B872" s="41">
         <v>79283003384</v>
@@ -24736,7 +24757,7 @@
     </row>
     <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" s="34" t="s">
-        <v>2427</v>
+        <v>2412</v>
       </c>
       <c r="B873" s="41">
         <v>79682666663</v>
@@ -24752,7 +24773,7 @@
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" s="34" t="s">
-        <v>2425</v>
+        <v>2410</v>
       </c>
       <c r="B874" s="41">
         <v>79186726140</v>
@@ -24770,7 +24791,7 @@
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" s="34" t="s">
-        <v>2428</v>
+        <v>2413</v>
       </c>
       <c r="B875" s="41">
         <v>79898051733</v>
@@ -24788,7 +24809,7 @@
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" s="34" t="s">
-        <v>2429</v>
+        <v>2414</v>
       </c>
       <c r="B876" s="41">
         <v>79086789121</v>
@@ -24804,7 +24825,7 @@
     </row>
     <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" s="34" t="s">
-        <v>2430</v>
+        <v>2415</v>
       </c>
       <c r="B877" s="41">
         <v>79528340083</v>
@@ -24820,7 +24841,7 @@
     </row>
     <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" s="34" t="s">
-        <v>2431</v>
+        <v>2416</v>
       </c>
       <c r="B878" s="41">
         <v>79530930717</v>
@@ -24838,7 +24859,7 @@
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" s="34" t="s">
-        <v>2432</v>
+        <v>2417</v>
       </c>
       <c r="B879" s="41">
         <v>79275037361</v>
@@ -24854,7 +24875,7 @@
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" s="34" t="s">
-        <v>2433</v>
+        <v>2418</v>
       </c>
       <c r="B880" s="41">
         <v>79218083526</v>
@@ -24870,7 +24891,7 @@
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" s="34" t="s">
-        <v>2434</v>
+        <v>2419</v>
       </c>
       <c r="B881" s="41">
         <v>79185789000</v>
@@ -24890,7 +24911,7 @@
     </row>
     <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" s="34" t="s">
-        <v>2435</v>
+        <v>2420</v>
       </c>
       <c r="B882" s="41">
         <v>79877941509</v>
@@ -24908,7 +24929,7 @@
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" s="34" t="s">
-        <v>2436</v>
+        <v>2421</v>
       </c>
       <c r="B883" s="41">
         <v>79618221503</v>
@@ -24948,7 +24969,7 @@
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" s="34" t="s">
-        <v>2506</v>
+        <v>2491</v>
       </c>
       <c r="B885" s="41">
         <v>79882548579</v>
@@ -24966,7 +24987,7 @@
     </row>
     <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" s="34" t="s">
-        <v>2507</v>
+        <v>2492</v>
       </c>
       <c r="B886" s="41">
         <v>79182900595</v>
@@ -24982,7 +25003,7 @@
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" s="34" t="s">
-        <v>2508</v>
+        <v>2493</v>
       </c>
       <c r="B887" s="41">
         <v>79264823431</v>
@@ -25000,7 +25021,7 @@
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" s="34" t="s">
-        <v>2509</v>
+        <v>2494</v>
       </c>
       <c r="B888" s="41">
         <v>79180246728</v>
@@ -25018,7 +25039,7 @@
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" s="34" t="s">
-        <v>2510</v>
+        <v>2495</v>
       </c>
       <c r="B889" s="41">
         <v>79263181485</v>
@@ -25034,7 +25055,7 @@
     </row>
     <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" s="34" t="s">
-        <v>2511</v>
+        <v>2496</v>
       </c>
       <c r="B890" s="41">
         <v>79189573595</v>
@@ -25052,7 +25073,7 @@
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" s="34" t="s">
-        <v>2512</v>
+        <v>2497</v>
       </c>
       <c r="B891" s="41">
         <v>79180129312</v>
@@ -25092,7 +25113,7 @@
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" s="34" t="s">
-        <v>2513</v>
+        <v>2498</v>
       </c>
       <c r="B893" s="41">
         <v>79207020082</v>
@@ -25114,7 +25135,7 @@
     </row>
     <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" s="34" t="s">
-        <v>2514</v>
+        <v>2499</v>
       </c>
       <c r="B894" s="41">
         <v>79185072237</v>
@@ -25132,7 +25153,7 @@
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" s="34" t="s">
-        <v>2515</v>
+        <v>2500</v>
       </c>
       <c r="B895" s="41">
         <v>79182762440</v>
@@ -25148,7 +25169,7 @@
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" s="34" t="s">
-        <v>2516</v>
+        <v>2501</v>
       </c>
       <c r="B896" s="41">
         <v>79518702052</v>
@@ -25164,7 +25185,7 @@
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" s="34" t="s">
-        <v>2517</v>
+        <v>2502</v>
       </c>
       <c r="B897" s="41">
         <v>79885456732</v>
@@ -25180,7 +25201,7 @@
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" s="34" t="s">
-        <v>2518</v>
+        <v>2503</v>
       </c>
       <c r="B898" s="41">
         <v>79186323631</v>
@@ -25218,7 +25239,7 @@
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" s="34" t="s">
-        <v>2519</v>
+        <v>2504</v>
       </c>
       <c r="B900" s="41">
         <v>79604946540</v>
@@ -25238,7 +25259,7 @@
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" s="34" t="s">
-        <v>2520</v>
+        <v>2505</v>
       </c>
       <c r="B901" s="41">
         <v>79787713176</v>
@@ -25282,7 +25303,7 @@
     </row>
     <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" s="34" t="s">
-        <v>2521</v>
+        <v>2506</v>
       </c>
       <c r="B903" s="41">
         <v>79881380533</v>
@@ -25298,7 +25319,7 @@
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" s="34" t="s">
-        <v>2522</v>
+        <v>2507</v>
       </c>
       <c r="B904" s="41">
         <v>79876571770</v>
@@ -25320,7 +25341,7 @@
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" s="34" t="s">
-        <v>2523</v>
+        <v>2508</v>
       </c>
       <c r="B905" s="41">
         <v>79185269969</v>
@@ -25342,7 +25363,7 @@
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" s="34" t="s">
-        <v>2524</v>
+        <v>2509</v>
       </c>
       <c r="B906" s="41">
         <v>79788069407</v>
@@ -25364,7 +25385,7 @@
     </row>
     <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" s="34" t="s">
-        <v>2525</v>
+        <v>2510</v>
       </c>
       <c r="B907" s="41">
         <v>79809148895</v>
@@ -25386,7 +25407,7 @@
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" s="34" t="s">
-        <v>2526</v>
+        <v>2511</v>
       </c>
       <c r="B908" s="41">
         <v>79374600054</v>
@@ -25424,7 +25445,7 @@
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" s="34" t="s">
-        <v>2527</v>
+        <v>2512</v>
       </c>
       <c r="B910" s="41">
         <v>79063480196</v>
@@ -25442,7 +25463,7 @@
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" s="34" t="s">
-        <v>2516</v>
+        <v>2501</v>
       </c>
       <c r="B911" s="41">
         <v>79035002052</v>
@@ -25462,7 +25483,7 @@
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" s="34" t="s">
-        <v>2528</v>
+        <v>2513</v>
       </c>
       <c r="B912" s="41">
         <v>79883667602</v>
@@ -25482,7 +25503,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A913" s="34" t="s">
-        <v>2529</v>
+        <v>2514</v>
       </c>
       <c r="B913" s="41">
         <v>79991733748</v>
@@ -25498,7 +25519,7 @@
     </row>
     <row r="914" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A914" s="34" t="s">
-        <v>2530</v>
+        <v>2515</v>
       </c>
       <c r="B914" s="41">
         <v>79168542102</v>
@@ -25518,7 +25539,7 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A915" s="34" t="s">
-        <v>2531</v>
+        <v>2516</v>
       </c>
       <c r="B915" s="41">
         <v>79888928388</v>
@@ -25538,7 +25559,7 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A916" s="34" t="s">
-        <v>2532</v>
+        <v>2517</v>
       </c>
       <c r="B916" s="41">
         <v>79032374317</v>
@@ -25580,7 +25601,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A918" s="34" t="s">
-        <v>2513</v>
+        <v>2498</v>
       </c>
       <c r="B918" s="41">
         <v>79207020082</v>
@@ -25603,7 +25624,7 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A919" s="34" t="s">
-        <v>2533</v>
+        <v>2518</v>
       </c>
       <c r="B919" s="41">
         <v>79041183867</v>
@@ -25624,7 +25645,7 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A920" s="34" t="s">
-        <v>2534</v>
+        <v>2519</v>
       </c>
       <c r="B920" s="41">
         <v>79032978483</v>
@@ -25645,7 +25666,7 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A921" s="34" t="s">
-        <v>2535</v>
+        <v>2520</v>
       </c>
       <c r="B921" s="41">
         <v>79308038836</v>
@@ -25668,7 +25689,7 @@
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A922" s="34" t="s">
-        <v>2536</v>
+        <v>2521</v>
       </c>
       <c r="B922" s="41">
         <v>79385488845</v>
@@ -25691,7 +25712,7 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A923" s="34" t="s">
-        <v>2537</v>
+        <v>2522</v>
       </c>
       <c r="B923" s="41">
         <v>79046838139</v>
@@ -25712,7 +25733,7 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A924" s="34" t="s">
-        <v>2538</v>
+        <v>2523</v>
       </c>
       <c r="B924" s="41">
         <v>79128268207</v>
@@ -25735,7 +25756,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A925" s="34" t="s">
-        <v>2539</v>
+        <v>2524</v>
       </c>
       <c r="B925" s="41">
         <v>79148261215</v>
@@ -25758,7 +25779,7 @@
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A926" s="34" t="s">
-        <v>2540</v>
+        <v>2525</v>
       </c>
       <c r="B926" s="41">
         <v>79267823227</v>
@@ -25779,7 +25800,7 @@
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A927" s="34" t="s">
-        <v>2541</v>
+        <v>2526</v>
       </c>
       <c r="B927" s="41">
         <v>79184915237</v>
@@ -25804,7 +25825,7 @@
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A928" s="34" t="s">
-        <v>2542</v>
+        <v>2527</v>
       </c>
       <c r="B928" s="41">
         <v>79034390003</v>
@@ -25851,7 +25872,7 @@
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" s="34" t="s">
-        <v>2543</v>
+        <v>2528</v>
       </c>
       <c r="B930" s="41">
         <v>79595062068</v>
@@ -25907,7 +25928,7 @@
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" s="34" t="s">
-        <v>2646</v>
+        <v>2631</v>
       </c>
       <c r="B933" s="41">
         <v>79180664535</v>
@@ -25925,7 +25946,7 @@
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" s="34" t="s">
-        <v>2647</v>
+        <v>2632</v>
       </c>
       <c r="B934" s="41">
         <v>79197382450</v>
@@ -25945,7 +25966,7 @@
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" s="34" t="s">
-        <v>2648</v>
+        <v>2633</v>
       </c>
       <c r="B935" s="41">
         <v>79885220528</v>
@@ -25967,7 +25988,7 @@
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" s="34" t="s">
-        <v>2649</v>
+        <v>2634</v>
       </c>
       <c r="B936" s="41">
         <v>79885093331</v>
@@ -26011,7 +26032,7 @@
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" s="34" t="s">
-        <v>2650</v>
+        <v>2635</v>
       </c>
       <c r="B938" s="41">
         <v>79184400178</v>
@@ -26033,7 +26054,7 @@
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" s="34" t="s">
-        <v>2651</v>
+        <v>2636</v>
       </c>
       <c r="B939" s="41">
         <v>79183270587</v>
@@ -26051,7 +26072,7 @@
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" s="34" t="s">
-        <v>2652</v>
+        <v>2637</v>
       </c>
       <c r="B940" s="41">
         <v>79183889940</v>
@@ -26069,7 +26090,7 @@
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" s="34" t="s">
-        <v>2653</v>
+        <v>2638</v>
       </c>
       <c r="B941" s="41">
         <v>79994722206</v>
@@ -26085,7 +26106,7 @@
     </row>
     <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" s="34" t="s">
-        <v>2654</v>
+        <v>2639</v>
       </c>
       <c r="B942" s="41">
         <v>79184165266</v>
@@ -26125,7 +26146,7 @@
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" s="34" t="s">
-        <v>2655</v>
+        <v>2640</v>
       </c>
       <c r="B944" s="41">
         <v>79160231803</v>
@@ -26143,7 +26164,7 @@
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" s="34" t="s">
-        <v>2656</v>
+        <v>2641</v>
       </c>
       <c r="B945" s="41">
         <v>79251587458</v>
@@ -26161,7 +26182,7 @@
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" s="34" t="s">
-        <v>2657</v>
+        <v>2642</v>
       </c>
       <c r="B946" s="41">
         <v>79385519412</v>
@@ -26267,7 +26288,7 @@
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" s="34" t="s">
-        <v>2658</v>
+        <v>2643</v>
       </c>
       <c r="B952" s="35">
         <v>79895106888</v>
@@ -26283,7 +26304,7 @@
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" s="34" t="s">
-        <v>2659</v>
+        <v>2644</v>
       </c>
       <c r="B953" s="35">
         <v>79189487859</v>
@@ -26301,7 +26322,7 @@
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" s="34" t="s">
-        <v>2660</v>
+        <v>2645</v>
       </c>
       <c r="B954" s="35">
         <v>79094690279</v>
@@ -26321,7 +26342,7 @@
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" s="34" t="s">
-        <v>2661</v>
+        <v>2646</v>
       </c>
       <c r="B955" s="35">
         <v>79270465755</v>
@@ -26341,7 +26362,7 @@
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" s="34" t="s">
-        <v>2662</v>
+        <v>2647</v>
       </c>
       <c r="B956" s="35">
         <v>79181514761</v>
@@ -26373,7 +26394,7 @@
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" s="34" t="s">
-        <v>2663</v>
+        <v>2648</v>
       </c>
       <c r="B958" s="35">
         <v>79286120337</v>
@@ -26393,7 +26414,7 @@
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" s="34" t="s">
-        <v>2664</v>
+        <v>2649</v>
       </c>
       <c r="B959" s="35">
         <v>79181603172</v>
@@ -26411,7 +26432,7 @@
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" s="34" t="s">
-        <v>2665</v>
+        <v>2650</v>
       </c>
       <c r="B960" s="35">
         <v>79528474569</v>
@@ -26429,7 +26450,7 @@
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" s="34" t="s">
-        <v>2666</v>
+        <v>2651</v>
       </c>
       <c r="B961" s="35">
         <v>79891443888</v>
@@ -26457,7 +26478,7 @@
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" s="34" t="s">
-        <v>2667</v>
+        <v>2652</v>
       </c>
       <c r="B963" s="35">
         <v>79186956626</v>
@@ -26473,7 +26494,7 @@
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" s="34" t="s">
-        <v>2668</v>
+        <v>2653</v>
       </c>
       <c r="B964" s="35">
         <v>79183433464</v>
@@ -26491,7 +26512,7 @@
     </row>
     <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" s="34" t="s">
-        <v>2669</v>
+        <v>2654</v>
       </c>
       <c r="B965" s="35">
         <v>79094646000</v>
@@ -26507,7 +26528,7 @@
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" s="34" t="s">
-        <v>2670</v>
+        <v>2655</v>
       </c>
       <c r="B966" s="35">
         <v>79854264076</v>
@@ -26523,7 +26544,7 @@
     </row>
     <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" s="34" t="s">
-        <v>2671</v>
+        <v>2656</v>
       </c>
       <c r="B967" s="35">
         <v>79186525585</v>
@@ -26539,7 +26560,7 @@
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" s="34" t="s">
-        <v>2672</v>
+        <v>2657</v>
       </c>
       <c r="B968" s="35">
         <v>79528581269</v>
@@ -26559,7 +26580,7 @@
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" s="34" t="s">
-        <v>2673</v>
+        <v>2658</v>
       </c>
       <c r="B969" s="35">
         <v>79673053030</v>
@@ -26589,7 +26610,7 @@
     </row>
     <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" s="34" t="s">
-        <v>2674</v>
+        <v>2659</v>
       </c>
       <c r="B971" s="35">
         <v>79886696618</v>
@@ -26739,7 +26760,7 @@
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" s="34" t="s">
-        <v>2675</v>
+        <v>2660</v>
       </c>
       <c r="B978" s="35">
         <v>79117974075</v>
@@ -26757,7 +26778,7 @@
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" s="34" t="s">
-        <v>2676</v>
+        <v>2661</v>
       </c>
       <c r="B979" s="35">
         <v>79615951401</v>
@@ -26775,7 +26796,7 @@
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" s="34" t="s">
-        <v>2677</v>
+        <v>2662</v>
       </c>
       <c r="B980" s="35">
         <v>79274773218</v>
@@ -26793,7 +26814,7 @@
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" s="34" t="s">
-        <v>2678</v>
+        <v>2663</v>
       </c>
       <c r="B981" s="35">
         <v>79673005052</v>
@@ -26811,7 +26832,7 @@
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" s="34" t="s">
-        <v>2679</v>
+        <v>2664</v>
       </c>
       <c r="B982" s="35">
         <v>79625245851</v>
@@ -26829,7 +26850,7 @@
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" s="34" t="s">
-        <v>2680</v>
+        <v>2665</v>
       </c>
       <c r="B983" s="35">
         <v>79898052605</v>
@@ -26847,7 +26868,7 @@
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" s="34" t="s">
-        <v>2681</v>
+        <v>2666</v>
       </c>
       <c r="B984" s="35">
         <v>79992365729</v>
@@ -26889,7 +26910,7 @@
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" s="34" t="s">
-        <v>2682</v>
+        <v>2667</v>
       </c>
       <c r="B986" s="41">
         <v>79182119543</v>
@@ -26905,7 +26926,7 @@
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" s="34" t="s">
-        <v>2683</v>
+        <v>2668</v>
       </c>
       <c r="B987" s="41">
         <v>79886039199</v>
@@ -26925,7 +26946,7 @@
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" s="34" t="s">
-        <v>2684</v>
+        <v>2669</v>
       </c>
       <c r="B988" s="41">
         <v>79182846179</v>
@@ -26943,7 +26964,7 @@
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" s="34" t="s">
-        <v>2685</v>
+        <v>2670</v>
       </c>
       <c r="B989" s="41">
         <v>79185545589</v>
@@ -26961,7 +26982,7 @@
     </row>
     <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" s="34" t="s">
-        <v>2686</v>
+        <v>2671</v>
       </c>
       <c r="B990" s="41">
         <v>79637505138</v>
@@ -26977,7 +26998,7 @@
     </row>
     <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" s="34" t="s">
-        <v>2687</v>
+        <v>2672</v>
       </c>
       <c r="B991" s="41">
         <v>79604757152</v>
@@ -26995,7 +27016,7 @@
     </row>
     <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" s="34" t="s">
-        <v>2688</v>
+        <v>2673</v>
       </c>
       <c r="B992" s="41">
         <v>79182762782</v>
@@ -27037,7 +27058,7 @@
     </row>
     <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" s="34" t="s">
-        <v>2689</v>
+        <v>2674</v>
       </c>
       <c r="B994" s="41">
         <v>79892941007</v>
@@ -27053,7 +27074,7 @@
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" s="34" t="s">
-        <v>2690</v>
+        <v>2675</v>
       </c>
       <c r="B995" s="41">
         <v>79060896267</v>
@@ -27073,7 +27094,7 @@
     </row>
     <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" s="34" t="s">
-        <v>2691</v>
+        <v>2676</v>
       </c>
       <c r="B996" s="41">
         <v>79384227276</v>
@@ -27113,7 +27134,7 @@
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" s="34" t="s">
-        <v>2692</v>
+        <v>2677</v>
       </c>
       <c r="B998" s="41">
         <v>79614238176</v>
@@ -27141,7 +27162,7 @@
     </row>
     <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" s="34" t="s">
-        <v>2693</v>
+        <v>2678</v>
       </c>
       <c r="B1000" s="41">
         <v>79280121007</v>
@@ -27169,7 +27190,7 @@
     </row>
     <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" s="34" t="s">
-        <v>2694</v>
+        <v>2679</v>
       </c>
       <c r="B1002" s="41">
         <v>79180985165</v>
@@ -27185,7 +27206,7 @@
     </row>
     <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" s="34" t="s">
-        <v>2695</v>
+        <v>2680</v>
       </c>
       <c r="B1003" s="41">
         <v>79186200028</v>
@@ -27201,7 +27222,7 @@
     </row>
     <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" s="34" t="s">
-        <v>2696</v>
+        <v>2681</v>
       </c>
       <c r="B1004" s="41">
         <v>79190278727</v>
@@ -27229,7 +27250,7 @@
     </row>
     <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" s="34" t="s">
-        <v>2697</v>
+        <v>2682</v>
       </c>
       <c r="B1006" s="41">
         <v>79615280373</v>
@@ -27245,7 +27266,7 @@
     </row>
     <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1007" s="34" t="s">
-        <v>2698</v>
+        <v>2683</v>
       </c>
       <c r="B1007" s="41">
         <v>79622028701</v>
@@ -27261,7 +27282,7 @@
     </row>
     <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1008" s="34" t="s">
-        <v>2699</v>
+        <v>2684</v>
       </c>
       <c r="B1008" s="41">
         <v>79185055723</v>
@@ -27277,7 +27298,7 @@
     </row>
     <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" s="34" t="s">
-        <v>2700</v>
+        <v>2685</v>
       </c>
       <c r="B1009" s="41">
         <v>79788139855</v>
@@ -27305,7 +27326,7 @@
     </row>
     <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" s="34" t="s">
-        <v>2701</v>
+        <v>2686</v>
       </c>
       <c r="B1011" s="41">
         <v>79189749194</v>
@@ -27323,7 +27344,7 @@
     </row>
     <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" s="34" t="s">
-        <v>2702</v>
+        <v>2687</v>
       </c>
       <c r="B1012" s="41">
         <v>79184801108</v>
@@ -27341,7 +27362,7 @@
     </row>
     <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" s="34" t="s">
-        <v>2703</v>
+        <v>2688</v>
       </c>
       <c r="B1013" s="41">
         <v>79646847710</v>
@@ -27357,7 +27378,7 @@
     </row>
     <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" s="34" t="s">
-        <v>2704</v>
+        <v>2689</v>
       </c>
       <c r="B1014" s="41">
         <v>79649041350</v>
@@ -27385,7 +27406,7 @@
     </row>
     <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" s="34" t="s">
-        <v>2705</v>
+        <v>2690</v>
       </c>
       <c r="B1016" s="33">
         <v>79181537666</v>
@@ -27401,7 +27422,7 @@
     </row>
     <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" s="34" t="s">
-        <v>2706</v>
+        <v>2691</v>
       </c>
       <c r="B1017" s="33">
         <v>79051511564</v>
@@ -27417,7 +27438,7 @@
     </row>
     <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" s="34" t="s">
-        <v>2707</v>
+        <v>2692</v>
       </c>
       <c r="B1018" s="33">
         <v>79254155954</v>
@@ -27433,7 +27454,7 @@
     </row>
     <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" s="34" t="s">
-        <v>2708</v>
+        <v>2693</v>
       </c>
       <c r="B1019" s="33">
         <v>79626803581</v>
@@ -27461,7 +27482,7 @@
     </row>
     <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" s="34" t="s">
-        <v>2709</v>
+        <v>2694</v>
       </c>
       <c r="B1021" s="33">
         <v>79281059268</v>
@@ -27477,7 +27498,7 @@
     </row>
     <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" s="34" t="s">
-        <v>2710</v>
+        <v>2695</v>
       </c>
       <c r="B1022" s="33">
         <v>79183388668</v>
@@ -27495,7 +27516,7 @@
     </row>
     <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" s="34" t="s">
-        <v>2711</v>
+        <v>2696</v>
       </c>
       <c r="B1023" s="33">
         <v>79067249922</v>
@@ -27523,7 +27544,7 @@
     </row>
     <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1025" s="34" t="s">
-        <v>2712</v>
+        <v>2697</v>
       </c>
       <c r="B1025" s="33">
         <v>79052993315</v>
@@ -27541,7 +27562,7 @@
     </row>
     <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1026" s="34" t="s">
-        <v>2713</v>
+        <v>2698</v>
       </c>
       <c r="B1026" s="33">
         <v>79043499977</v>
@@ -27571,7 +27592,7 @@
     </row>
     <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1028" s="34" t="s">
-        <v>2714</v>
+        <v>2699</v>
       </c>
       <c r="B1028" s="33">
         <v>79052875113</v>
@@ -27587,7 +27608,7 @@
     </row>
     <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1029" s="34" t="s">
-        <v>2715</v>
+        <v>2700</v>
       </c>
       <c r="B1029" s="33">
         <v>79061820166</v>
@@ -27603,7 +27624,7 @@
     </row>
     <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1030" s="34" t="s">
-        <v>2716</v>
+        <v>2701</v>
       </c>
       <c r="B1030" s="33">
         <v>79189333736</v>
@@ -27619,7 +27640,7 @@
     </row>
     <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1031" s="34" t="s">
-        <v>2717</v>
+        <v>2702</v>
       </c>
       <c r="B1031" s="33">
         <v>79064327871</v>
@@ -27635,7 +27656,7 @@
     </row>
     <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1032" s="34" t="s">
-        <v>2718</v>
+        <v>2703</v>
       </c>
       <c r="B1032" s="33">
         <v>79102891788</v>
@@ -27663,13 +27684,13 @@
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1034" s="34" t="s">
-        <v>2719</v>
+        <v>2704</v>
       </c>
       <c r="B1034" s="33">
         <v>79183561661</v>
       </c>
       <c r="C1034" s="33" t="s">
-        <v>2404</v>
+        <v>2389</v>
       </c>
       <c r="D1034" s="33" t="s">
         <v>2207</v>
@@ -27681,7 +27702,7 @@
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1035" s="34" t="s">
-        <v>2720</v>
+        <v>2705</v>
       </c>
       <c r="B1035" s="33">
         <v>79537206758</v>
@@ -27796,7 +27817,7 @@
       </c>
       <c r="C1041" s="3"/>
       <c r="D1041" s="3" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="E1041" s="3"/>
       <c r="F1041" s="3"/>
@@ -27812,7 +27833,7 @@
       </c>
       <c r="C1042" s="3"/>
       <c r="D1042" s="3" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="E1042" s="3"/>
       <c r="F1042" s="3"/>
@@ -27829,7 +27850,7 @@
       <c r="C1043" s="3"/>
       <c r="D1043" s="3"/>
       <c r="E1043" s="3" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="F1043" s="3" t="s">
         <v>1767</v>
@@ -27846,7 +27867,7 @@
       </c>
       <c r="C1044" s="3"/>
       <c r="D1044" s="3" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="E1044" s="3"/>
       <c r="F1044" s="3"/>
@@ -27865,7 +27886,7 @@
         <v>1769</v>
       </c>
       <c r="E1045" s="3" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="F1045" s="3" t="s">
         <v>1766</v>
@@ -27885,7 +27906,7 @@
         <v>1769</v>
       </c>
       <c r="E1046" s="3" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="F1046" s="3" t="s">
         <v>1766</v>
@@ -27913,13 +27934,13 @@
         <v>79624430220</v>
       </c>
       <c r="C1048" s="3" t="s">
-        <v>2396</v>
+        <v>2382</v>
       </c>
       <c r="D1048" s="3" t="s">
-        <v>2394</v>
+        <v>2380</v>
       </c>
       <c r="E1048" s="3" t="s">
-        <v>2395</v>
+        <v>2381</v>
       </c>
       <c r="F1048" s="3" t="s">
         <v>1768</v>
@@ -27936,7 +27957,7 @@
       </c>
       <c r="C1049" s="3"/>
       <c r="D1049" s="3" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="E1049" s="3"/>
       <c r="F1049" s="3"/>
@@ -27964,7 +27985,7 @@
       </c>
       <c r="C1051" s="3"/>
       <c r="D1051" s="3" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="E1051" s="3"/>
       <c r="F1051" s="3"/>
@@ -27980,7 +28001,7 @@
       </c>
       <c r="C1052" s="3"/>
       <c r="D1052" s="3" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="E1052" s="3"/>
       <c r="F1052" s="3"/>
@@ -28027,7 +28048,7 @@
         <v>79186452525</v>
       </c>
       <c r="C1055" s="3" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="D1055" s="3"/>
       <c r="E1055" s="3"/>
@@ -28043,7 +28064,7 @@
         <v>79189484040</v>
       </c>
       <c r="C1056" s="3" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="D1056" s="3"/>
       <c r="E1056" s="3"/>
@@ -28060,7 +28081,7 @@
       </c>
       <c r="C1057" s="3"/>
       <c r="D1057" s="3" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="E1057" s="3"/>
       <c r="F1057" s="3"/>
@@ -28075,7 +28096,7 @@
         <v>79779455485</v>
       </c>
       <c r="C1058" s="3" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="D1058" s="3" t="s">
         <v>1828</v>
@@ -28093,7 +28114,7 @@
         <v>79056507300</v>
       </c>
       <c r="C1059" s="3" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="D1059" s="3" t="s">
         <v>1827</v>
@@ -28111,7 +28132,7 @@
         <v>79258091550</v>
       </c>
       <c r="C1060" s="3" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="D1060" s="3" t="s">
         <v>1827</v>
@@ -28130,10 +28151,10 @@
       </c>
       <c r="C1061" s="3"/>
       <c r="D1061" s="3" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="E1061" s="3" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="F1061" s="3" t="s">
         <v>1825</v>
@@ -28162,7 +28183,7 @@
       </c>
       <c r="C1063" s="3"/>
       <c r="D1063" s="3" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="E1063" s="3"/>
       <c r="F1063" s="3"/>
@@ -28178,7 +28199,7 @@
       </c>
       <c r="C1064" s="3"/>
       <c r="D1064" s="3" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="E1064" s="3"/>
       <c r="F1064" s="3"/>
@@ -28193,7 +28214,7 @@
         <v>79493130260</v>
       </c>
       <c r="C1065" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D1065" s="3"/>
       <c r="E1065" s="3"/>
@@ -28211,7 +28232,7 @@
       <c r="C1066" s="3"/>
       <c r="D1066" s="3"/>
       <c r="E1066" s="3" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="F1066" s="3" t="s">
         <v>1826</v>
@@ -28228,7 +28249,7 @@
       </c>
       <c r="C1067" s="3"/>
       <c r="D1067" s="3" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="E1067" s="3"/>
       <c r="F1067" s="3"/>
@@ -28243,10 +28264,10 @@
         <v>79604622005</v>
       </c>
       <c r="C1068" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D1068" s="3" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="E1068" s="3"/>
       <c r="F1068" s="3"/>
@@ -28261,7 +28282,7 @@
         <v>79192563907</v>
       </c>
       <c r="C1069" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D1069" s="3"/>
       <c r="E1069" s="3"/>
@@ -28277,7 +28298,7 @@
         <v>79180335333</v>
       </c>
       <c r="C1070" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D1070" s="3"/>
       <c r="E1070" s="3"/>
@@ -28325,10 +28346,10 @@
         <v>79183073394</v>
       </c>
       <c r="C1073" s="3" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="D1073" s="3" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E1073" s="3"/>
       <c r="F1073" s="3"/>
@@ -28355,13 +28376,13 @@
         <v>79615215290</v>
       </c>
       <c r="C1075" s="3" t="s">
-        <v>2401</v>
+        <v>2386</v>
       </c>
       <c r="D1075" s="3" t="s">
-        <v>2402</v>
+        <v>2387</v>
       </c>
       <c r="E1075" s="3" t="s">
-        <v>2403</v>
+        <v>2388</v>
       </c>
       <c r="F1075" s="3" t="s">
         <v>1857</v>
@@ -28378,7 +28399,7 @@
       </c>
       <c r="C1076" s="3"/>
       <c r="D1076" s="3" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="E1076" s="3"/>
       <c r="F1076" s="3"/>
@@ -28393,7 +28414,7 @@
         <v>79180757000</v>
       </c>
       <c r="C1077" s="3" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="D1077" s="3"/>
       <c r="E1077" s="3"/>
@@ -28409,10 +28430,10 @@
         <v>79628609461</v>
       </c>
       <c r="C1078" s="3" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="D1078" s="3" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="E1078" s="3"/>
       <c r="F1078" s="3"/>
@@ -28427,10 +28448,10 @@
         <v>79184101450</v>
       </c>
       <c r="C1079" s="3" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="D1079" s="3" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="E1079" s="3"/>
       <c r="F1079" s="3"/>
@@ -28445,13 +28466,13 @@
         <v>79183999079</v>
       </c>
       <c r="C1080" s="3" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="D1080" s="3" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="E1080" s="3" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="F1080" s="3" t="s">
         <v>1891</v>
@@ -28469,7 +28490,7 @@
       <c r="C1081" s="3"/>
       <c r="D1081" s="3"/>
       <c r="E1081" s="3" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="F1081" s="3" t="s">
         <v>1858</v>
@@ -28487,7 +28508,7 @@
       <c r="C1082" s="3"/>
       <c r="D1082" s="3"/>
       <c r="E1082" s="3" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="F1082" s="3" t="s">
         <v>1858</v>
@@ -28503,7 +28524,7 @@
         <v>79184302094</v>
       </c>
       <c r="C1083" s="3" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="D1083" s="3"/>
       <c r="E1083" s="3"/>
@@ -28531,13 +28552,13 @@
         <v>79287677710</v>
       </c>
       <c r="C1085" s="3" t="s">
-        <v>2332</v>
+        <v>2318</v>
       </c>
       <c r="D1085" s="3" t="s">
-        <v>2333</v>
+        <v>2319</v>
       </c>
       <c r="E1085" s="3" t="s">
-        <v>2334</v>
+        <v>2320</v>
       </c>
       <c r="F1085" s="3" t="s">
         <v>1860</v>
@@ -28553,7 +28574,7 @@
         <v>79615198406</v>
       </c>
       <c r="C1086" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1086" s="3"/>
       <c r="E1086" s="3"/>
@@ -28571,7 +28592,7 @@
       <c r="C1087" s="3"/>
       <c r="D1087" s="3"/>
       <c r="E1087" s="3" t="s">
-        <v>2334</v>
+        <v>2320</v>
       </c>
       <c r="F1087" s="3" t="s">
         <v>1859</v>
@@ -28587,13 +28608,13 @@
         <v>79093732088</v>
       </c>
       <c r="C1088" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1088" s="3" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="E1088" s="3" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="F1088" s="3" t="s">
         <v>1859</v>
@@ -28609,11 +28630,11 @@
         <v>79060683338</v>
       </c>
       <c r="C1089" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1089" s="3"/>
       <c r="E1089" s="3" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="F1089" s="3" t="s">
         <v>1859</v>
@@ -28629,7 +28650,7 @@
         <v>79184137117</v>
       </c>
       <c r="C1090" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1090" s="3"/>
       <c r="E1090" s="3"/>
@@ -28645,7 +28666,7 @@
         <v>79180660587</v>
       </c>
       <c r="C1091" s="3" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D1091" s="3"/>
       <c r="E1091" s="3"/>
@@ -28673,13 +28694,13 @@
         <v>79002359970</v>
       </c>
       <c r="C1093" s="3" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="D1093" s="3" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="E1093" s="3" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="F1093" s="3" t="s">
         <v>1861</v>
@@ -28695,10 +28716,10 @@
         <v>79892306069</v>
       </c>
       <c r="C1094" s="3" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="D1094" s="3" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="E1094" s="3"/>
       <c r="F1094" s="3"/>
@@ -28725,7 +28746,7 @@
         <v>79615101239</v>
       </c>
       <c r="C1096" s="3" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="D1096" s="3"/>
       <c r="E1096" s="3"/>
@@ -28741,10 +28762,10 @@
         <v>79287753737</v>
       </c>
       <c r="C1097" s="3" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="D1097" s="3" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="E1097" s="3"/>
       <c r="F1097" s="3"/>
@@ -28759,13 +28780,13 @@
         <v>79283348884</v>
       </c>
       <c r="C1098" s="3" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="D1098" s="3" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="E1098" s="3" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="F1098" s="3" t="s">
         <v>1862</v>
@@ -28782,7 +28803,7 @@
       </c>
       <c r="C1099" s="3"/>
       <c r="D1099" s="3" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="E1099" s="3"/>
       <c r="F1099" s="3"/>
@@ -28865,7 +28886,7 @@
       <c r="C1104" s="3"/>
       <c r="D1104" s="3"/>
       <c r="E1104" s="3" t="s">
-        <v>2371</v>
+        <v>2357</v>
       </c>
       <c r="F1104" s="3" t="s">
         <v>1888</v>
@@ -28881,10 +28902,10 @@
         <v>79649134155</v>
       </c>
       <c r="C1105" s="3" t="s">
-        <v>2361</v>
+        <v>2347</v>
       </c>
       <c r="D1105" s="3" t="s">
-        <v>2370</v>
+        <v>2356</v>
       </c>
       <c r="E1105" s="3"/>
       <c r="F1105" s="3"/>
@@ -28899,7 +28920,7 @@
         <v>79186587857</v>
       </c>
       <c r="C1106" s="3" t="s">
-        <v>2361</v>
+        <v>2347</v>
       </c>
       <c r="D1106" s="3"/>
       <c r="E1106" s="3"/>
@@ -28915,7 +28936,7 @@
         <v>79183710874</v>
       </c>
       <c r="C1107" s="3" t="s">
-        <v>2361</v>
+        <v>2347</v>
       </c>
       <c r="D1107" s="3"/>
       <c r="E1107" s="3"/>
@@ -28931,11 +28952,11 @@
         <v>79185758610</v>
       </c>
       <c r="C1108" s="3" t="s">
-        <v>2361</v>
+        <v>2347</v>
       </c>
       <c r="D1108" s="3"/>
       <c r="E1108" s="3" t="s">
-        <v>2371</v>
+        <v>2357</v>
       </c>
       <c r="F1108" s="3" t="s">
         <v>1889</v>
@@ -28952,7 +28973,7 @@
       </c>
       <c r="C1109" s="3"/>
       <c r="D1109" s="3" t="s">
-        <v>2369</v>
+        <v>2355</v>
       </c>
       <c r="E1109" s="3"/>
       <c r="F1109" s="3"/>
@@ -28967,13 +28988,13 @@
         <v>79530981964</v>
       </c>
       <c r="C1110" s="3" t="s">
-        <v>2361</v>
+        <v>2347</v>
       </c>
       <c r="D1110" s="3" t="s">
-        <v>2369</v>
+        <v>2355</v>
       </c>
       <c r="E1110" s="3" t="s">
-        <v>2371</v>
+        <v>2357</v>
       </c>
       <c r="F1110" s="3" t="s">
         <v>1889</v>
@@ -29001,7 +29022,7 @@
         <v>79884919692</v>
       </c>
       <c r="C1112" s="3" t="s">
-        <v>2362</v>
+        <v>2348</v>
       </c>
       <c r="D1112" s="3"/>
       <c r="E1112" s="3"/>
@@ -29017,7 +29038,7 @@
         <v>79164495884</v>
       </c>
       <c r="C1113" s="3" t="s">
-        <v>2362</v>
+        <v>2348</v>
       </c>
       <c r="D1113" s="3"/>
       <c r="E1113" s="3"/>
@@ -29034,7 +29055,7 @@
       </c>
       <c r="C1114" s="3"/>
       <c r="D1114" s="3" t="s">
-        <v>2368</v>
+        <v>2354</v>
       </c>
       <c r="E1114" s="3"/>
       <c r="F1114" s="3"/>
@@ -29062,7 +29083,7 @@
       </c>
       <c r="C1116" s="3"/>
       <c r="D1116" s="3" t="s">
-        <v>2367</v>
+        <v>2353</v>
       </c>
       <c r="E1116" s="3"/>
       <c r="F1116" s="3"/>
@@ -29079,7 +29100,7 @@
       <c r="C1117" s="3"/>
       <c r="D1117" s="3"/>
       <c r="E1117" s="3" t="s">
-        <v>2372</v>
+        <v>2358</v>
       </c>
       <c r="F1117" s="3" t="s">
         <v>1890</v>
@@ -29096,7 +29117,7 @@
       </c>
       <c r="C1118" s="3"/>
       <c r="D1118" s="3" t="s">
-        <v>2366</v>
+        <v>2352</v>
       </c>
       <c r="E1118" s="3"/>
       <c r="F1118" s="3"/>
@@ -29112,7 +29133,7 @@
       </c>
       <c r="C1119" s="3"/>
       <c r="D1119" s="3" t="s">
-        <v>2366</v>
+        <v>2352</v>
       </c>
       <c r="E1119" s="3"/>
       <c r="F1119" s="3"/>
@@ -29140,7 +29161,7 @@
       </c>
       <c r="C1121" s="3"/>
       <c r="D1121" s="3" t="s">
-        <v>2365</v>
+        <v>2351</v>
       </c>
       <c r="E1121" s="3"/>
       <c r="F1121" s="3"/>
@@ -29156,7 +29177,7 @@
       </c>
       <c r="C1122" s="3"/>
       <c r="D1122" s="3" t="s">
-        <v>2365</v>
+        <v>2351</v>
       </c>
       <c r="E1122" s="3"/>
       <c r="F1122" s="3"/>
@@ -29205,7 +29226,7 @@
       <c r="C1125" s="18"/>
       <c r="D1125" s="18"/>
       <c r="E1125" s="18" t="s">
-        <v>2373</v>
+        <v>2359</v>
       </c>
       <c r="F1125" s="18" t="s">
         <v>1899</v>
@@ -29221,13 +29242,13 @@
         <v>79780187528</v>
       </c>
       <c r="C1126" s="18" t="s">
-        <v>2363</v>
+        <v>2349</v>
       </c>
       <c r="D1126" s="18" t="s">
-        <v>2364</v>
+        <v>2350</v>
       </c>
       <c r="E1126" s="18" t="s">
-        <v>2373</v>
+        <v>2359</v>
       </c>
       <c r="F1126" s="18" t="s">
         <v>1898</v>
@@ -29245,7 +29266,7 @@
       <c r="C1127" s="18"/>
       <c r="D1127" s="18"/>
       <c r="E1127" s="18" t="s">
-        <v>2373</v>
+        <v>2359</v>
       </c>
       <c r="F1127" s="18" t="s">
         <v>1898</v>
@@ -29275,7 +29296,7 @@
       <c r="C1129" s="18"/>
       <c r="D1129" s="18"/>
       <c r="E1129" s="18" t="s">
-        <v>2374</v>
+        <v>2360</v>
       </c>
       <c r="F1129" s="18" t="s">
         <v>1900</v>
@@ -29323,13 +29344,13 @@
         <v>79284697777</v>
       </c>
       <c r="C1132" s="18" t="s">
+        <v>2422</v>
+      </c>
+      <c r="D1132" s="18" t="s">
         <v>2437</v>
       </c>
-      <c r="D1132" s="18" t="s">
-        <v>2452</v>
-      </c>
       <c r="E1132" s="18" t="s">
-        <v>2453</v>
+        <v>2438</v>
       </c>
       <c r="F1132" s="18" t="s">
         <v>1911</v>
@@ -29346,7 +29367,7 @@
       </c>
       <c r="C1133" s="18"/>
       <c r="D1133" s="18" t="s">
-        <v>2451</v>
+        <v>2436</v>
       </c>
       <c r="E1133" s="18"/>
       <c r="F1133" s="18"/>
@@ -29373,10 +29394,10 @@
         <v>79001236569</v>
       </c>
       <c r="C1135" s="18" t="s">
-        <v>2438</v>
+        <v>2423</v>
       </c>
       <c r="D1135" s="18" t="s">
-        <v>2450</v>
+        <v>2435</v>
       </c>
       <c r="E1135" s="18"/>
       <c r="F1135" s="18"/>
@@ -29391,13 +29412,13 @@
         <v>79991005104</v>
       </c>
       <c r="C1136" s="18" t="s">
-        <v>2732</v>
+        <v>2717</v>
       </c>
       <c r="D1136" s="18" t="s">
-        <v>2730</v>
+        <v>2715</v>
       </c>
       <c r="E1136" s="18" t="s">
-        <v>2731</v>
+        <v>2716</v>
       </c>
       <c r="F1136" s="18" t="s">
         <v>1912</v>
@@ -29413,10 +29434,10 @@
         <v>79371249966</v>
       </c>
       <c r="C1137" s="18" t="s">
-        <v>2438</v>
+        <v>2423</v>
       </c>
       <c r="D1137" s="18" t="s">
-        <v>2449</v>
+        <v>2434</v>
       </c>
       <c r="E1137" s="18"/>
       <c r="F1137" s="18"/>
@@ -29431,7 +29452,7 @@
         <v>79185805028</v>
       </c>
       <c r="C1138" s="18" t="s">
-        <v>2438</v>
+        <v>2423</v>
       </c>
       <c r="D1138" s="18"/>
       <c r="E1138" s="18"/>
@@ -29459,10 +29480,10 @@
         <v>79687042488</v>
       </c>
       <c r="C1140" s="18" t="s">
-        <v>2439</v>
+        <v>2424</v>
       </c>
       <c r="D1140" s="18" t="s">
-        <v>2448</v>
+        <v>2433</v>
       </c>
       <c r="E1140" s="18"/>
       <c r="F1140" s="18"/>
@@ -29543,7 +29564,7 @@
         <v>79110886608</v>
       </c>
       <c r="C1145" s="18" t="s">
-        <v>2440</v>
+        <v>2425</v>
       </c>
       <c r="D1145" s="18"/>
       <c r="E1145" s="18"/>
@@ -29560,7 +29581,7 @@
       </c>
       <c r="C1146" s="18"/>
       <c r="D1146" s="18" t="s">
-        <v>2447</v>
+        <v>2432</v>
       </c>
       <c r="E1146" s="18"/>
       <c r="F1146" s="18"/>
@@ -29575,10 +29596,10 @@
         <v>79185416500</v>
       </c>
       <c r="C1147" s="18" t="s">
-        <v>2440</v>
+        <v>2425</v>
       </c>
       <c r="D1147" s="18" t="s">
-        <v>2446</v>
+        <v>2431</v>
       </c>
       <c r="E1147" s="18"/>
       <c r="F1147" s="18"/>
@@ -29593,10 +29614,10 @@
         <v>79883514535</v>
       </c>
       <c r="C1148" s="18" t="s">
-        <v>2440</v>
+        <v>2425</v>
       </c>
       <c r="D1148" s="18" t="s">
-        <v>2446</v>
+        <v>2431</v>
       </c>
       <c r="E1148" s="18"/>
       <c r="F1148" s="18"/>
@@ -29611,10 +29632,10 @@
         <v>79181927858</v>
       </c>
       <c r="C1149" s="18" t="s">
-        <v>2440</v>
+        <v>2425</v>
       </c>
       <c r="D1149" s="18" t="s">
-        <v>2445</v>
+        <v>2430</v>
       </c>
       <c r="E1149" s="18"/>
       <c r="F1149" s="18"/>
@@ -29629,7 +29650,7 @@
         <v>79034731171</v>
       </c>
       <c r="C1150" s="18" t="s">
-        <v>2440</v>
+        <v>2425</v>
       </c>
       <c r="D1150" s="18"/>
       <c r="E1150" s="18"/>
@@ -29657,7 +29678,7 @@
         <v>79518399099</v>
       </c>
       <c r="C1152" s="18" t="s">
-        <v>2441</v>
+        <v>2426</v>
       </c>
       <c r="D1152" s="18"/>
       <c r="E1152" s="18"/>
@@ -29675,7 +29696,7 @@
       <c r="C1153" s="18"/>
       <c r="D1153" s="18"/>
       <c r="E1153" s="18" t="s">
-        <v>2454</v>
+        <v>2439</v>
       </c>
       <c r="F1153" s="18" t="s">
         <v>2020</v>
@@ -29693,7 +29714,7 @@
       <c r="C1154" s="18"/>
       <c r="D1154" s="18"/>
       <c r="E1154" s="18" t="s">
-        <v>2454</v>
+        <v>2439</v>
       </c>
       <c r="F1154" s="18" t="s">
         <v>2021</v>
@@ -29709,7 +29730,7 @@
         <v>79493272312</v>
       </c>
       <c r="C1155" s="18" t="s">
-        <v>2441</v>
+        <v>2426</v>
       </c>
       <c r="D1155" s="18"/>
       <c r="E1155" s="18"/>
@@ -29725,7 +29746,7 @@
         <v>79184455113</v>
       </c>
       <c r="C1156" s="18" t="s">
-        <v>2483</v>
+        <v>2468</v>
       </c>
       <c r="D1156" s="18"/>
       <c r="E1156" s="18"/>
@@ -29741,7 +29762,7 @@
         <v>79494697622</v>
       </c>
       <c r="C1157" s="18" t="s">
-        <v>2441</v>
+        <v>2426</v>
       </c>
       <c r="D1157" s="18"/>
       <c r="E1157" s="18"/>
@@ -29757,7 +29778,7 @@
         <v>79288803878</v>
       </c>
       <c r="C1158" s="18" t="s">
-        <v>2441</v>
+        <v>2426</v>
       </c>
       <c r="D1158" s="18"/>
       <c r="E1158" s="18"/>
@@ -29773,10 +29794,10 @@
         <v>79284223859</v>
       </c>
       <c r="C1159" s="18" t="s">
-        <v>2441</v>
+        <v>2426</v>
       </c>
       <c r="D1159" s="3" t="s">
-        <v>2444</v>
+        <v>2429</v>
       </c>
       <c r="E1159" s="18"/>
       <c r="F1159" s="18"/>
@@ -29803,13 +29824,13 @@
         <v>79189338233</v>
       </c>
       <c r="C1161" s="18" t="s">
-        <v>2442</v>
+        <v>2427</v>
       </c>
       <c r="D1161" s="18" t="s">
-        <v>2443</v>
+        <v>2428</v>
       </c>
       <c r="E1161" s="18" t="s">
-        <v>2455</v>
+        <v>2440</v>
       </c>
       <c r="F1161" s="18" t="s">
         <v>2022</v>
@@ -29858,7 +29879,7 @@
       </c>
       <c r="C1164" s="3"/>
       <c r="D1164" s="3" t="s">
-        <v>2499</v>
+        <v>2484</v>
       </c>
       <c r="E1164" s="3"/>
       <c r="F1164" s="3"/>
@@ -29874,7 +29895,7 @@
       </c>
       <c r="C1165" s="3"/>
       <c r="D1165" s="3" t="s">
-        <v>2498</v>
+        <v>2483</v>
       </c>
       <c r="E1165" s="3"/>
       <c r="F1165" s="3"/>
@@ -29890,7 +29911,7 @@
       </c>
       <c r="C1166" s="3"/>
       <c r="D1166" s="3" t="s">
-        <v>2497</v>
+        <v>2482</v>
       </c>
       <c r="E1166" s="3"/>
       <c r="F1166" s="3"/>
@@ -29917,7 +29938,7 @@
         <v>79622153493</v>
       </c>
       <c r="C1168" s="3" t="s">
-        <v>2484</v>
+        <v>2469</v>
       </c>
       <c r="D1168" s="3"/>
       <c r="E1168" s="3"/>
@@ -29933,10 +29954,10 @@
         <v>79266122721</v>
       </c>
       <c r="C1169" s="3" t="s">
-        <v>2484</v>
+        <v>2469</v>
       </c>
       <c r="D1169" s="3" t="s">
-        <v>2496</v>
+        <v>2481</v>
       </c>
       <c r="E1169" s="3"/>
       <c r="F1169" s="3"/>
@@ -29952,7 +29973,7 @@
       </c>
       <c r="C1170" s="3"/>
       <c r="D1170" s="3" t="s">
-        <v>2495</v>
+        <v>2480</v>
       </c>
       <c r="E1170" s="3"/>
       <c r="F1170" s="3"/>
@@ -29967,7 +29988,7 @@
         <v>79813022825</v>
       </c>
       <c r="C1171" s="3" t="s">
-        <v>2484</v>
+        <v>2469</v>
       </c>
       <c r="D1171" s="3"/>
       <c r="E1171" s="3"/>
@@ -29995,13 +30016,13 @@
         <v>79892367996</v>
       </c>
       <c r="C1173" s="3" t="s">
+        <v>2470</v>
+      </c>
+      <c r="D1173" s="3" t="s">
+        <v>2479</v>
+      </c>
+      <c r="E1173" s="3" t="s">
         <v>2485</v>
-      </c>
-      <c r="D1173" s="3" t="s">
-        <v>2494</v>
-      </c>
-      <c r="E1173" s="3" t="s">
-        <v>2500</v>
       </c>
       <c r="F1173" s="3" t="s">
         <v>2034</v>
@@ -30017,13 +30038,13 @@
         <v>79182617888</v>
       </c>
       <c r="C1174" s="3" t="s">
+        <v>2470</v>
+      </c>
+      <c r="D1174" s="3" t="s">
+        <v>2479</v>
+      </c>
+      <c r="E1174" s="3" t="s">
         <v>2485</v>
-      </c>
-      <c r="D1174" s="3" t="s">
-        <v>2494</v>
-      </c>
-      <c r="E1174" s="3" t="s">
-        <v>2500</v>
       </c>
       <c r="F1174" s="3" t="s">
         <v>2034</v>
@@ -30052,7 +30073,7 @@
       </c>
       <c r="C1176" s="3"/>
       <c r="D1176" s="3" t="s">
-        <v>2493</v>
+        <v>2478</v>
       </c>
       <c r="E1176" s="3"/>
       <c r="F1176" s="3"/>
@@ -30068,7 +30089,7 @@
       </c>
       <c r="C1177" s="3"/>
       <c r="D1177" s="3" t="s">
-        <v>2492</v>
+        <v>2477</v>
       </c>
       <c r="E1177" s="3"/>
       <c r="F1177" s="3"/>
@@ -30084,7 +30105,7 @@
       </c>
       <c r="C1178" s="3"/>
       <c r="D1178" s="3" t="s">
-        <v>2491</v>
+        <v>2476</v>
       </c>
       <c r="E1178" s="3"/>
       <c r="F1178" s="3"/>
@@ -30100,7 +30121,7 @@
       </c>
       <c r="C1179" s="3"/>
       <c r="D1179" s="3" t="s">
-        <v>2491</v>
+        <v>2476</v>
       </c>
       <c r="E1179" s="3"/>
       <c r="F1179" s="3"/>
@@ -30117,7 +30138,7 @@
       <c r="C1180" s="3"/>
       <c r="D1180" s="3"/>
       <c r="E1180" s="3" t="s">
-        <v>2501</v>
+        <v>2486</v>
       </c>
       <c r="F1180" s="3" t="s">
         <v>2060</v>
@@ -30145,7 +30166,7 @@
         <v>79081882253</v>
       </c>
       <c r="C1182" s="3" t="s">
-        <v>2486</v>
+        <v>2471</v>
       </c>
       <c r="D1182" s="3"/>
       <c r="E1182" s="3"/>
@@ -30161,7 +30182,7 @@
         <v>79184570319</v>
       </c>
       <c r="C1183" s="3" t="s">
-        <v>2486</v>
+        <v>2471</v>
       </c>
       <c r="D1183" s="3"/>
       <c r="E1183" s="3"/>
@@ -30189,7 +30210,7 @@
         <v>79884600699</v>
       </c>
       <c r="C1185" s="3" t="s">
-        <v>2487</v>
+        <v>2472</v>
       </c>
       <c r="D1185" s="3"/>
       <c r="E1185" s="3"/>
@@ -30205,7 +30226,7 @@
         <v>79615933002</v>
       </c>
       <c r="C1186" s="3" t="s">
-        <v>2487</v>
+        <v>2472</v>
       </c>
       <c r="D1186" s="3"/>
       <c r="E1186" s="3"/>
@@ -30221,7 +30242,7 @@
         <v>79287615615</v>
       </c>
       <c r="C1187" s="3" t="s">
-        <v>2487</v>
+        <v>2472</v>
       </c>
       <c r="D1187" s="3"/>
       <c r="E1187" s="3"/>
@@ -30250,10 +30271,10 @@
       </c>
       <c r="C1189" s="3"/>
       <c r="D1189" s="3" t="s">
-        <v>2490</v>
+        <v>2475</v>
       </c>
       <c r="E1189" s="3" t="s">
-        <v>2502</v>
+        <v>2487</v>
       </c>
       <c r="F1189" s="3" t="s">
         <v>2070</v>
@@ -30283,7 +30304,7 @@
       <c r="C1191" s="3"/>
       <c r="D1191" s="3"/>
       <c r="E1191" s="3" t="s">
-        <v>2503</v>
+        <v>2488</v>
       </c>
       <c r="F1191" s="3" t="s">
         <v>2071</v>
@@ -30301,7 +30322,7 @@
       <c r="C1192" s="3"/>
       <c r="D1192" s="3"/>
       <c r="E1192" s="3" t="s">
-        <v>2503</v>
+        <v>2488</v>
       </c>
       <c r="F1192" s="3" t="s">
         <v>2072</v>
@@ -30351,7 +30372,7 @@
       <c r="C1195" s="3"/>
       <c r="D1195" s="3"/>
       <c r="E1195" s="3" t="s">
-        <v>2504</v>
+        <v>2489</v>
       </c>
       <c r="F1195" s="3"/>
       <c r="G1195" s="3"/>
@@ -30367,7 +30388,7 @@
       <c r="C1196" s="3"/>
       <c r="D1196" s="3"/>
       <c r="E1196" s="3" t="s">
-        <v>2504</v>
+        <v>2489</v>
       </c>
       <c r="F1196" s="3"/>
       <c r="G1196" s="3"/>
@@ -30394,7 +30415,7 @@
       </c>
       <c r="C1198" s="3"/>
       <c r="D1198" s="3" t="s">
-        <v>2489</v>
+        <v>2474</v>
       </c>
       <c r="E1198" s="3"/>
       <c r="F1198" s="3"/>
@@ -30409,11 +30430,11 @@
         <v>79374645805</v>
       </c>
       <c r="C1199" s="3" t="s">
-        <v>2488</v>
+        <v>2473</v>
       </c>
       <c r="D1199" s="3"/>
       <c r="E1199" s="3" t="s">
-        <v>2505</v>
+        <v>2490</v>
       </c>
       <c r="F1199" s="3" t="s">
         <v>2080</v>
@@ -30431,7 +30452,7 @@
       <c r="C1200" s="3"/>
       <c r="D1200" s="3"/>
       <c r="E1200" s="3" t="s">
-        <v>2505</v>
+        <v>2490</v>
       </c>
       <c r="F1200" s="3" t="s">
         <v>2080</v>
@@ -30461,7 +30482,7 @@
       <c r="C1202" s="3"/>
       <c r="D1202" s="3"/>
       <c r="E1202" s="3" t="s">
-        <v>2642</v>
+        <v>2627</v>
       </c>
       <c r="F1202" s="3" t="s">
         <v>2161</v>
@@ -30477,10 +30498,10 @@
         <v>79085129986</v>
       </c>
       <c r="C1203" s="3" t="s">
-        <v>2634</v>
+        <v>2619</v>
       </c>
       <c r="D1203" s="3" t="s">
-        <v>2641</v>
+        <v>2626</v>
       </c>
       <c r="E1203" s="3"/>
       <c r="F1203" s="3"/>
@@ -30508,7 +30529,7 @@
       </c>
       <c r="C1205" s="3"/>
       <c r="D1205" s="3" t="s">
-        <v>2640</v>
+        <v>2625</v>
       </c>
       <c r="E1205" s="3"/>
       <c r="F1205" s="3"/>
@@ -30523,7 +30544,7 @@
         <v>79185010806</v>
       </c>
       <c r="C1206" s="3" t="s">
-        <v>2635</v>
+        <v>2620</v>
       </c>
       <c r="D1206" s="3"/>
       <c r="E1206" s="3"/>
@@ -30539,7 +30560,7 @@
         <v>79183185307</v>
       </c>
       <c r="C1207" s="3" t="s">
-        <v>2635</v>
+        <v>2620</v>
       </c>
       <c r="D1207" s="3"/>
       <c r="E1207" s="3"/>
@@ -30567,7 +30588,7 @@
         <v>79266566385</v>
       </c>
       <c r="C1209" s="3" t="s">
-        <v>2636</v>
+        <v>2621</v>
       </c>
       <c r="D1209" s="3"/>
       <c r="E1209" s="3"/>
@@ -30617,7 +30638,7 @@
       <c r="C1212" s="3"/>
       <c r="D1212" s="3"/>
       <c r="E1212" s="3" t="s">
-        <v>2643</v>
+        <v>2628</v>
       </c>
       <c r="F1212" s="3" t="s">
         <v>2204</v>
@@ -30635,7 +30656,7 @@
       <c r="C1213" s="3"/>
       <c r="D1213" s="3"/>
       <c r="E1213" s="3" t="s">
-        <v>2643</v>
+        <v>2628</v>
       </c>
       <c r="F1213" s="3" t="s">
         <v>2205</v>
@@ -30652,7 +30673,7 @@
       </c>
       <c r="C1214" s="3"/>
       <c r="D1214" s="3" t="s">
-        <v>2639</v>
+        <v>2624</v>
       </c>
       <c r="E1214" s="3"/>
       <c r="F1214" s="3"/>
@@ -30701,7 +30722,7 @@
       <c r="C1217" s="3"/>
       <c r="D1217" s="3"/>
       <c r="E1217" s="3" t="s">
-        <v>2644</v>
+        <v>2629</v>
       </c>
       <c r="F1217" s="3" t="s">
         <v>2214</v>
@@ -30731,7 +30752,7 @@
       <c r="C1219" s="3"/>
       <c r="D1219" s="3"/>
       <c r="E1219" s="3" t="s">
-        <v>2645</v>
+        <v>2630</v>
       </c>
       <c r="F1219" s="3" t="s">
         <v>2215</v>
@@ -30747,10 +30768,10 @@
         <v>79883151515</v>
       </c>
       <c r="C1220" s="3" t="s">
-        <v>2637</v>
+        <v>2622</v>
       </c>
       <c r="D1220" s="3" t="s">
-        <v>2638</v>
+        <v>2623</v>
       </c>
       <c r="E1220" s="3"/>
       <c r="F1220" s="3"/>
@@ -30778,368 +30799,368 @@
       <c r="H1221" s="3"/>
     </row>
     <row r="1222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1222" s="40" t="s">
+      <c r="A1222" s="6" t="s">
         <v>2216</v>
       </c>
-      <c r="B1222" s="2"/>
-      <c r="C1222" s="2"/>
-      <c r="D1222" s="2"/>
-      <c r="E1222" s="2"/>
-      <c r="F1222" s="2"/>
-      <c r="G1222" s="2"/>
-      <c r="H1222" s="2"/>
+      <c r="B1222" s="3"/>
+      <c r="C1222" s="3"/>
+      <c r="D1222" s="3"/>
+      <c r="E1222" s="3"/>
+      <c r="F1222" s="3"/>
+      <c r="G1222" s="3"/>
+      <c r="H1222" s="3"/>
     </row>
     <row r="1223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1223" s="7" t="s">
+      <c r="A1223" s="6" t="s">
         <v>2217</v>
       </c>
-      <c r="B1223" s="2">
+      <c r="B1223" s="3">
         <v>79281186882</v>
       </c>
-      <c r="C1223" s="2"/>
-      <c r="D1223" s="2" t="s">
+      <c r="C1223" s="3"/>
+      <c r="D1223" s="3" t="s">
         <v>2221</v>
       </c>
-      <c r="E1223" s="2" t="s">
+      <c r="E1223" s="3" t="s">
         <v>2223</v>
       </c>
-      <c r="F1223" s="2" t="s">
+      <c r="F1223" s="3" t="s">
         <v>2222</v>
       </c>
-      <c r="G1223" s="2"/>
-      <c r="H1223" s="2"/>
+      <c r="G1223" s="3"/>
+      <c r="H1223" s="3"/>
     </row>
     <row r="1224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1224" s="40" t="s">
+      <c r="A1224" s="6" t="s">
         <v>2218</v>
       </c>
-      <c r="B1224" s="2"/>
-      <c r="C1224" s="2"/>
-      <c r="D1224" s="2"/>
-      <c r="E1224" s="2"/>
-      <c r="F1224" s="2"/>
-      <c r="G1224" s="2"/>
-      <c r="H1224" s="2"/>
+      <c r="B1224" s="3"/>
+      <c r="C1224" s="3"/>
+      <c r="D1224" s="3"/>
+      <c r="E1224" s="3"/>
+      <c r="F1224" s="3"/>
+      <c r="G1224" s="3"/>
+      <c r="H1224" s="3"/>
     </row>
     <row r="1225" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1225" s="7" t="s">
+      <c r="A1225" s="6" t="s">
         <v>2219</v>
       </c>
-      <c r="B1225" s="2">
+      <c r="B1225" s="3">
         <v>79034547400</v>
       </c>
-      <c r="C1225" s="2" t="s">
-        <v>2224</v>
-      </c>
-      <c r="D1225" s="2"/>
-      <c r="E1225" s="2"/>
-      <c r="F1225" s="2"/>
-      <c r="G1225" s="2"/>
-      <c r="H1225" s="2"/>
+      <c r="C1225" s="3" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D1225" s="3"/>
+      <c r="E1225" s="3"/>
+      <c r="F1225" s="3"/>
+      <c r="G1225" s="3"/>
+      <c r="H1225" s="3"/>
     </row>
     <row r="1226" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1226" s="7" t="s">
+      <c r="A1226" s="6" t="s">
         <v>2220</v>
       </c>
-      <c r="B1226" s="2">
+      <c r="B1226" s="3">
         <v>79287721255</v>
       </c>
-      <c r="C1226" s="2" t="s">
-        <v>2224</v>
-      </c>
-      <c r="D1226" s="2"/>
-      <c r="E1226" s="2"/>
-      <c r="F1226" s="2"/>
-      <c r="G1226" s="2"/>
-      <c r="H1226" s="2"/>
+      <c r="C1226" s="3" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D1226" s="3"/>
+      <c r="E1226" s="3"/>
+      <c r="F1226" s="3"/>
+      <c r="G1226" s="3"/>
+      <c r="H1226" s="3"/>
     </row>
     <row r="1227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1227" s="7"/>
-      <c r="B1227" s="2"/>
-      <c r="C1227" s="2" t="s">
+      <c r="A1227" s="6"/>
+      <c r="B1227" s="3"/>
+      <c r="C1227" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1227" s="2" t="s">
+      <c r="D1227" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1227" s="2" t="s">
+      <c r="E1227" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1227" s="4" t="s">
+      <c r="F1227" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G1227" s="2" t="s">
+      <c r="G1227" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1227" s="2"/>
+      <c r="H1227" s="3"/>
     </row>
     <row r="1228" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1228" s="40" t="s">
+      <c r="A1228" s="6" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B1228" s="3"/>
+      <c r="C1228" s="3"/>
+      <c r="D1228" s="3"/>
+      <c r="E1228" s="3"/>
+      <c r="F1228" s="3"/>
+      <c r="G1228" s="3"/>
+      <c r="H1228" s="3"/>
+    </row>
+    <row r="1229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1229" s="6" t="s">
         <v>2300</v>
       </c>
-      <c r="B1228" s="2"/>
-      <c r="C1228" s="2"/>
-      <c r="D1228" s="2"/>
-      <c r="E1228" s="2"/>
-      <c r="F1228" s="2"/>
-      <c r="G1228" s="2"/>
-      <c r="H1228" s="2"/>
-    </row>
-    <row r="1229" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1229" s="7" t="s">
+      <c r="B1229" s="3">
+        <v>79183615308</v>
+      </c>
+      <c r="C1229" s="3" t="s">
+        <v>2719</v>
+      </c>
+      <c r="D1229" s="3" t="s">
+        <v>2729</v>
+      </c>
+      <c r="E1229" s="3"/>
+      <c r="F1229" s="3"/>
+      <c r="G1229" s="3"/>
+      <c r="H1229" s="3"/>
+    </row>
+    <row r="1230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1230" s="6" t="s">
         <v>2301</v>
       </c>
-      <c r="B1229" s="2">
-        <v>79183615308</v>
-      </c>
-      <c r="C1229" s="2" t="s">
+      <c r="B1230" s="3">
+        <v>79186212666</v>
+      </c>
+      <c r="C1230" s="3" t="s">
+        <v>2719</v>
+      </c>
+      <c r="D1230" s="3" t="s">
+        <v>2728</v>
+      </c>
+      <c r="E1230" s="3" t="s">
+        <v>2730</v>
+      </c>
+      <c r="F1230" s="3" t="s">
+        <v>2312</v>
+      </c>
+      <c r="G1230" s="3"/>
+      <c r="H1230" s="3"/>
+    </row>
+    <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1231" s="6" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B1231" s="3">
+        <v>79951882337</v>
+      </c>
+      <c r="C1231" s="3"/>
+      <c r="D1231" s="3" t="s">
+        <v>2727</v>
+      </c>
+      <c r="E1231" s="3"/>
+      <c r="F1231" s="3"/>
+      <c r="G1231" s="3"/>
+      <c r="H1231" s="3"/>
+    </row>
+    <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1232" s="6" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1232" s="3">
+        <v>79002796431</v>
+      </c>
+      <c r="C1232" s="3"/>
+      <c r="D1232" s="3"/>
+      <c r="E1232" s="3" t="s">
+        <v>2730</v>
+      </c>
+      <c r="F1232" s="3" t="s">
+        <v>2313</v>
+      </c>
+      <c r="G1232" s="3"/>
+      <c r="H1232" s="3"/>
+    </row>
+    <row r="1233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1233" s="6" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B1233" s="3">
+        <v>79384126478</v>
+      </c>
+      <c r="C1233" s="3" t="s">
+        <v>2719</v>
+      </c>
+      <c r="D1233" s="3"/>
+      <c r="E1233" s="3"/>
+      <c r="F1233" s="3"/>
+      <c r="G1233" s="3"/>
+      <c r="H1233" s="3"/>
+    </row>
+    <row r="1234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1234" s="6" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B1234" s="3"/>
+      <c r="C1234" s="3"/>
+      <c r="D1234" s="3"/>
+      <c r="E1234" s="3"/>
+      <c r="F1234" s="3"/>
+      <c r="G1234" s="3"/>
+      <c r="H1234" s="3"/>
+    </row>
+    <row r="1235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1235" s="6" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B1235" s="3">
+        <v>79184673083</v>
+      </c>
+      <c r="C1235" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D1235" s="3" t="s">
+        <v>2726</v>
+      </c>
+      <c r="E1235" s="3" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F1235" s="3" t="s">
         <v>2315</v>
       </c>
-      <c r="D1229" s="2" t="s">
-        <v>2324</v>
-      </c>
-      <c r="E1229" s="2"/>
-      <c r="F1229" s="2"/>
-      <c r="G1229" s="2"/>
-      <c r="H1229" s="2"/>
-    </row>
-    <row r="1230" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1230" s="7" t="s">
-        <v>2302</v>
-      </c>
-      <c r="B1230" s="2">
-        <v>79186212666</v>
-      </c>
-      <c r="C1230" s="2" t="s">
-        <v>2315</v>
-      </c>
-      <c r="D1230" s="2" t="s">
-        <v>2330</v>
-      </c>
-      <c r="E1230" s="2" t="s">
-        <v>2318</v>
-      </c>
-      <c r="F1230" s="2" t="s">
+      <c r="G1235" s="3"/>
+      <c r="H1235" s="3"/>
+    </row>
+    <row r="1236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1236" s="6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1236" s="3">
+        <v>79184987541</v>
+      </c>
+      <c r="C1236" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D1236" s="3" t="s">
+        <v>2725</v>
+      </c>
+      <c r="E1236" s="3"/>
+      <c r="F1236" s="3"/>
+      <c r="G1236" s="3"/>
+      <c r="H1236" s="3"/>
+    </row>
+    <row r="1237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1237" s="6" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B1237" s="3">
+        <v>79624504198</v>
+      </c>
+      <c r="C1237" s="3"/>
+      <c r="D1237" s="3" t="s">
+        <v>2724</v>
+      </c>
+      <c r="E1237" s="3" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F1237" s="3" t="s">
+        <v>2314</v>
+      </c>
+      <c r="G1237" s="3"/>
+      <c r="H1237" s="3"/>
+    </row>
+    <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1238" s="6" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B1238" s="3">
+        <v>79180458777</v>
+      </c>
+      <c r="C1238" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D1238" s="3"/>
+      <c r="E1238" s="3"/>
+      <c r="F1238" s="3"/>
+      <c r="G1238" s="3"/>
+      <c r="H1238" s="3"/>
+    </row>
+    <row r="1239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1239" s="6" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B1239" s="3"/>
+      <c r="C1239" s="3"/>
+      <c r="D1239" s="3"/>
+      <c r="E1239" s="3"/>
+      <c r="F1239" s="3"/>
+      <c r="G1239" s="3"/>
+      <c r="H1239" s="3"/>
+    </row>
+    <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1240" s="6" t="s">
+        <v>2310</v>
+      </c>
+      <c r="B1240" s="3">
+        <v>79183291413</v>
+      </c>
+      <c r="C1240" s="3" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D1240" s="3" t="s">
+        <v>2723</v>
+      </c>
+      <c r="E1240" s="3"/>
+      <c r="F1240" s="3"/>
+      <c r="G1240" s="3"/>
+      <c r="H1240" s="3"/>
+    </row>
+    <row r="1241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1241" s="6" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B1241" s="3">
+        <v>79882371168</v>
+      </c>
+      <c r="C1241" s="3"/>
+      <c r="D1241" s="3"/>
+      <c r="E1241" s="3" t="s">
+        <v>2732</v>
+      </c>
+      <c r="F1241" s="3" t="s">
         <v>2316</v>
       </c>
-      <c r="G1230" s="2"/>
-      <c r="H1230" s="2"/>
-    </row>
-    <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1231" s="7" t="s">
-        <v>2303</v>
-      </c>
-      <c r="B1231" s="2">
-        <v>79951882337</v>
-      </c>
-      <c r="C1231" s="2"/>
-      <c r="D1231" s="2" t="s">
-        <v>2325</v>
-      </c>
-      <c r="E1231" s="2"/>
-      <c r="F1231" s="2"/>
-      <c r="G1231" s="2"/>
-      <c r="H1231" s="2"/>
-    </row>
-    <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1232" s="7" t="s">
-        <v>2304</v>
-      </c>
-      <c r="B1232" s="2">
-        <v>79002796431</v>
-      </c>
-      <c r="C1232" s="2"/>
-      <c r="D1232" s="2"/>
-      <c r="E1232" s="2" t="s">
-        <v>2318</v>
-      </c>
-      <c r="F1232" s="2" t="s">
+      <c r="G1241" s="3"/>
+      <c r="H1241" s="3"/>
+    </row>
+    <row r="1242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1242" s="6" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B1242" s="3">
+        <v>79885577597</v>
+      </c>
+      <c r="C1242" s="3"/>
+      <c r="D1242" s="3" t="s">
+        <v>2722</v>
+      </c>
+      <c r="E1242" s="3"/>
+      <c r="F1242" s="3"/>
+      <c r="G1242" s="3"/>
+      <c r="H1242" s="3"/>
+    </row>
+    <row r="1243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1243" s="6" t="s">
         <v>2317</v>
       </c>
-      <c r="G1232" s="2"/>
-      <c r="H1232" s="2"/>
-    </row>
-    <row r="1233" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1233" s="7" t="s">
-        <v>2305</v>
-      </c>
-      <c r="B1233" s="2">
-        <v>79384126478</v>
-      </c>
-      <c r="C1233" s="2" t="s">
-        <v>2315</v>
-      </c>
-      <c r="D1233" s="2"/>
-      <c r="E1233" s="2"/>
-      <c r="F1233" s="2"/>
-      <c r="G1233" s="2"/>
-      <c r="H1233" s="2"/>
-    </row>
-    <row r="1234" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1234" s="40" t="s">
-        <v>2306</v>
-      </c>
-      <c r="B1234" s="2"/>
-      <c r="C1234" s="2"/>
-      <c r="D1234" s="2"/>
-      <c r="E1234" s="2"/>
-      <c r="F1234" s="2"/>
-      <c r="G1234" s="2"/>
-      <c r="H1234" s="2"/>
-    </row>
-    <row r="1235" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1235" s="7" t="s">
-        <v>2307</v>
-      </c>
-      <c r="B1235" s="2">
-        <v>79184673083</v>
-      </c>
-      <c r="C1235" s="2" t="s">
-        <v>2314</v>
-      </c>
-      <c r="D1235" s="2" t="s">
-        <v>2327</v>
-      </c>
-      <c r="E1235" s="2" t="s">
-        <v>2321</v>
-      </c>
-      <c r="F1235" s="2" t="s">
-        <v>2320</v>
-      </c>
-      <c r="G1235" s="2"/>
-      <c r="H1235" s="2"/>
-    </row>
-    <row r="1236" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1236" s="7" t="s">
-        <v>1364</v>
-      </c>
-      <c r="B1236" s="2">
-        <v>79184987541</v>
-      </c>
-      <c r="C1236" s="2" t="s">
-        <v>2314</v>
-      </c>
-      <c r="D1236" s="2" t="s">
-        <v>2400</v>
-      </c>
-      <c r="E1236" s="2"/>
-      <c r="F1236" s="2"/>
-      <c r="G1236" s="2"/>
-      <c r="H1236" s="2"/>
-    </row>
-    <row r="1237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1237" s="7" t="s">
-        <v>2308</v>
-      </c>
-      <c r="B1237" s="2">
-        <v>79624504198</v>
-      </c>
-      <c r="C1237" s="2"/>
-      <c r="D1237" s="2" t="s">
-        <v>2326</v>
-      </c>
-      <c r="E1237" s="2" t="s">
-        <v>2321</v>
-      </c>
-      <c r="F1237" s="2" t="s">
-        <v>2319</v>
-      </c>
-      <c r="G1237" s="2"/>
-      <c r="H1237" s="2"/>
-    </row>
-    <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1238" s="7" t="s">
-        <v>2309</v>
-      </c>
-      <c r="B1238" s="2">
-        <v>79180458777</v>
-      </c>
-      <c r="C1238" s="2" t="s">
-        <v>2314</v>
-      </c>
-      <c r="D1238" s="2"/>
-      <c r="E1238" s="2"/>
-      <c r="F1238" s="2"/>
-      <c r="G1238" s="2"/>
-      <c r="H1238" s="2"/>
-    </row>
-    <row r="1239" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1239" s="40" t="s">
-        <v>2310</v>
-      </c>
-      <c r="B1239" s="2"/>
-      <c r="C1239" s="2"/>
-      <c r="D1239" s="2"/>
-      <c r="E1239" s="2"/>
-      <c r="F1239" s="2"/>
-      <c r="G1239" s="2"/>
-      <c r="H1239" s="2"/>
-    </row>
-    <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1240" s="7" t="s">
-        <v>2311</v>
-      </c>
-      <c r="B1240" s="2">
-        <v>79183291413</v>
-      </c>
-      <c r="C1240" s="2" t="s">
-        <v>2313</v>
-      </c>
-      <c r="D1240" s="2" t="s">
-        <v>2328</v>
-      </c>
-      <c r="E1240" s="2"/>
-      <c r="F1240" s="2"/>
-      <c r="G1240" s="2"/>
-      <c r="H1240" s="2"/>
-    </row>
-    <row r="1241" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1241" s="7" t="s">
-        <v>2312</v>
-      </c>
-      <c r="B1241" s="2">
-        <v>79882371168</v>
-      </c>
-      <c r="C1241" s="2"/>
-      <c r="D1241" s="2"/>
-      <c r="E1241" s="2" t="s">
-        <v>2323</v>
-      </c>
-      <c r="F1241" s="2" t="s">
-        <v>2322</v>
-      </c>
-      <c r="G1241" s="2"/>
-      <c r="H1241" s="2"/>
-    </row>
-    <row r="1242" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1242" s="7" t="s">
-        <v>2381</v>
-      </c>
-      <c r="B1242" s="2">
-        <v>79885577597</v>
-      </c>
-      <c r="C1242" s="2"/>
-      <c r="D1242" s="2" t="s">
-        <v>2329</v>
-      </c>
-      <c r="E1242" s="2"/>
-      <c r="F1242" s="2"/>
-      <c r="G1242" s="2"/>
-      <c r="H1242" s="2"/>
-    </row>
-    <row r="1243" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1243" s="7" t="s">
-        <v>2331</v>
-      </c>
-      <c r="B1243" s="17"/>
-      <c r="C1243" s="2"/>
-      <c r="D1243" s="2" t="s">
-        <v>2329</v>
-      </c>
-      <c r="E1243" s="2"/>
-      <c r="F1243" s="2"/>
-      <c r="G1243" s="2"/>
-      <c r="H1243" s="2"/>
+      <c r="B1243" s="18"/>
+      <c r="C1243" s="3"/>
+      <c r="D1243" s="3" t="s">
+        <v>2722</v>
+      </c>
+      <c r="E1243" s="3"/>
+      <c r="F1243" s="3"/>
+      <c r="G1243" s="3"/>
+      <c r="H1243" s="3"/>
     </row>
     <row r="1244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1244" s="7"/>
@@ -31163,7 +31184,7 @@
     </row>
     <row r="1245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1245" s="40" t="s">
-        <v>2335</v>
+        <v>2321</v>
       </c>
       <c r="B1245" s="17"/>
       <c r="C1245" s="2"/>
@@ -31175,16 +31196,16 @@
     </row>
     <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1246" s="7" t="s">
-        <v>2336</v>
+        <v>2322</v>
       </c>
       <c r="B1246" s="17">
         <v>79802319741</v>
       </c>
       <c r="C1246" s="2" t="s">
-        <v>2348</v>
+        <v>2334</v>
       </c>
       <c r="D1246" s="2" t="s">
-        <v>2355</v>
+        <v>2341</v>
       </c>
       <c r="E1246" s="2"/>
       <c r="F1246" s="2"/>
@@ -31193,7 +31214,7 @@
     </row>
     <row r="1247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1247" s="7" t="s">
-        <v>2337</v>
+        <v>2323</v>
       </c>
       <c r="B1247" s="17">
         <v>79298260798</v>
@@ -31201,24 +31222,24 @@
       <c r="C1247" s="2"/>
       <c r="D1247" s="2"/>
       <c r="E1247" s="2" t="s">
-        <v>2352</v>
+        <v>2338</v>
       </c>
       <c r="F1247" s="2" t="s">
-        <v>2405</v>
+        <v>2390</v>
       </c>
       <c r="G1247" s="2"/>
       <c r="H1247" s="2"/>
     </row>
     <row r="1248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1248" s="7" t="s">
-        <v>2338</v>
+        <v>2324</v>
       </c>
       <c r="B1248" s="17">
         <v>79615901223</v>
       </c>
       <c r="C1248" s="2"/>
       <c r="D1248" s="2" t="s">
-        <v>2356</v>
+        <v>2342</v>
       </c>
       <c r="E1248" s="2"/>
       <c r="F1248" s="2"/>
@@ -31227,7 +31248,7 @@
     </row>
     <row r="1249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1249" s="7" t="s">
-        <v>2339</v>
+        <v>2325</v>
       </c>
       <c r="B1249" s="17">
         <v>79183331040</v>
@@ -31235,37 +31256,37 @@
       <c r="C1249" s="2"/>
       <c r="D1249" s="2"/>
       <c r="E1249" s="2" t="s">
-        <v>2352</v>
+        <v>2338</v>
       </c>
       <c r="F1249" s="2" t="s">
-        <v>2351</v>
+        <v>2337</v>
       </c>
       <c r="G1249" s="2"/>
       <c r="H1249" s="2"/>
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1250" s="7" t="s">
-        <v>2340</v>
+        <v>2326</v>
       </c>
       <c r="B1250" s="17">
         <v>79064077747</v>
       </c>
       <c r="C1250" s="2" t="s">
-        <v>2348</v>
+        <v>2334</v>
       </c>
       <c r="D1250" s="2"/>
       <c r="E1250" s="2" t="s">
-        <v>2352</v>
+        <v>2338</v>
       </c>
       <c r="F1250" s="2" t="s">
-        <v>2351</v>
+        <v>2337</v>
       </c>
       <c r="G1250" s="2"/>
       <c r="H1250" s="2"/>
     </row>
     <row r="1251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1251" s="40" t="s">
-        <v>2341</v>
+        <v>2327</v>
       </c>
       <c r="B1251" s="17"/>
       <c r="C1251" s="2"/>
@@ -31277,38 +31298,38 @@
     </row>
     <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1252" s="7" t="s">
-        <v>2342</v>
+        <v>2328</v>
       </c>
       <c r="B1252" s="17">
         <v>79181978847</v>
       </c>
       <c r="C1252" s="2" t="s">
-        <v>2349</v>
+        <v>2335</v>
       </c>
       <c r="D1252" s="2" t="s">
-        <v>2357</v>
+        <v>2343</v>
       </c>
       <c r="E1252" s="2" t="s">
-        <v>2354</v>
+        <v>2340</v>
       </c>
       <c r="F1252" s="2" t="s">
-        <v>2353</v>
+        <v>2339</v>
       </c>
       <c r="G1252" s="2"/>
       <c r="H1252" s="2"/>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1253" s="7" t="s">
-        <v>2343</v>
+        <v>2329</v>
       </c>
       <c r="B1253" s="17">
         <v>79183346962</v>
       </c>
       <c r="C1253" s="2" t="s">
-        <v>2349</v>
+        <v>2335</v>
       </c>
       <c r="D1253" s="2" t="s">
-        <v>2358</v>
+        <v>2344</v>
       </c>
       <c r="E1253" s="2"/>
       <c r="F1253" s="2"/>
@@ -31317,7 +31338,7 @@
     </row>
     <row r="1254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1254" s="40" t="s">
-        <v>2344</v>
+        <v>2330</v>
       </c>
       <c r="B1254" s="17"/>
       <c r="C1254" s="2"/>
@@ -31329,14 +31350,14 @@
     </row>
     <row r="1255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1255" s="7" t="s">
-        <v>2345</v>
+        <v>2331</v>
       </c>
       <c r="B1255" s="17">
         <v>79518493781</v>
       </c>
       <c r="C1255" s="2"/>
       <c r="D1255" s="2" t="s">
-        <v>2359</v>
+        <v>2345</v>
       </c>
       <c r="E1255" s="2"/>
       <c r="F1255" s="2"/>
@@ -31345,14 +31366,14 @@
     </row>
     <row r="1256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1256" s="7" t="s">
-        <v>2346</v>
+        <v>2332</v>
       </c>
       <c r="B1256" s="17">
         <v>79180651355</v>
       </c>
       <c r="C1256" s="2"/>
       <c r="D1256" s="2" t="s">
-        <v>2360</v>
+        <v>2346</v>
       </c>
       <c r="E1256" s="2"/>
       <c r="F1256" s="2"/>
@@ -31361,13 +31382,13 @@
     </row>
     <row r="1257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1257" s="7" t="s">
-        <v>2347</v>
+        <v>2333</v>
       </c>
       <c r="B1257" s="17">
         <v>79281140670</v>
       </c>
       <c r="C1257" s="2" t="s">
-        <v>2350</v>
+        <v>2336</v>
       </c>
       <c r="D1257" s="2"/>
       <c r="E1257" s="2"/>
@@ -31377,7 +31398,7 @@
     </row>
     <row r="1258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1258" s="40" t="s">
-        <v>2382</v>
+        <v>2368</v>
       </c>
       <c r="B1258" s="17"/>
       <c r="C1258" s="2"/>
@@ -31389,14 +31410,14 @@
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1259" s="7" t="s">
-        <v>2383</v>
+        <v>2369</v>
       </c>
       <c r="B1259" s="17">
         <v>79200671177</v>
       </c>
       <c r="C1259" s="2"/>
       <c r="D1259" s="2" t="s">
-        <v>2392</v>
+        <v>2378</v>
       </c>
       <c r="E1259" s="2"/>
       <c r="F1259" s="2"/>
@@ -31405,7 +31426,7 @@
     </row>
     <row r="1260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1260" s="7" t="s">
-        <v>2384</v>
+        <v>2370</v>
       </c>
       <c r="B1260" s="17">
         <v>79186201442</v>
@@ -31413,17 +31434,17 @@
       <c r="C1260" s="2"/>
       <c r="D1260" s="2"/>
       <c r="E1260" s="2" t="s">
-        <v>2389</v>
+        <v>2375</v>
       </c>
       <c r="F1260" s="2" t="s">
-        <v>2388</v>
+        <v>2374</v>
       </c>
       <c r="G1260" s="2"/>
       <c r="H1260" s="2"/>
     </row>
     <row r="1261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1261" s="40" t="s">
-        <v>2385</v>
+        <v>2371</v>
       </c>
       <c r="B1261" s="17"/>
       <c r="C1261" s="2"/>
@@ -31435,13 +31456,13 @@
     </row>
     <row r="1262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1262" s="7" t="s">
-        <v>2386</v>
+        <v>2372</v>
       </c>
       <c r="B1262" s="17">
         <v>79183108008</v>
       </c>
       <c r="C1262" s="2" t="s">
-        <v>2393</v>
+        <v>2379</v>
       </c>
       <c r="D1262" s="2"/>
       <c r="E1262" s="2"/>
@@ -31451,27 +31472,27 @@
     </row>
     <row r="1263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1263" s="7" t="s">
-        <v>2387</v>
+        <v>2373</v>
       </c>
       <c r="B1263" s="17">
         <v>79097178862</v>
       </c>
       <c r="C1263" s="2" t="s">
-        <v>2393</v>
+        <v>2379</v>
       </c>
       <c r="D1263" s="2"/>
       <c r="E1263" s="2" t="s">
-        <v>2391</v>
+        <v>2377</v>
       </c>
       <c r="F1263" s="2" t="s">
-        <v>2390</v>
+        <v>2376</v>
       </c>
       <c r="G1263" s="2"/>
       <c r="H1263" s="2"/>
     </row>
     <row r="1264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1264" s="40" t="s">
-        <v>2397</v>
+        <v>2383</v>
       </c>
       <c r="B1264" s="17"/>
       <c r="C1264" s="2"/>
@@ -31483,13 +31504,13 @@
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1265" s="7" t="s">
-        <v>2399</v>
+        <v>2385</v>
       </c>
       <c r="B1265" s="17">
         <v>79787819232</v>
       </c>
       <c r="C1265" s="2" t="s">
-        <v>2398</v>
+        <v>2384</v>
       </c>
       <c r="D1265" s="2"/>
       <c r="E1265" s="2"/>
@@ -31517,7 +31538,7 @@
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1267" s="40" t="s">
-        <v>2456</v>
+        <v>2441</v>
       </c>
       <c r="B1267" s="17"/>
       <c r="C1267" s="2"/>
@@ -31529,36 +31550,36 @@
     </row>
     <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1268" s="7" t="s">
-        <v>2457</v>
+        <v>2442</v>
       </c>
       <c r="B1268" s="17">
         <v>79181206771</v>
       </c>
       <c r="C1268" s="2" t="s">
-        <v>2459</v>
+        <v>2444</v>
       </c>
       <c r="D1268" s="2" t="s">
-        <v>2460</v>
+        <v>2445</v>
       </c>
       <c r="E1268" s="2" t="s">
-        <v>2462</v>
+        <v>2447</v>
       </c>
       <c r="F1268" s="2" t="s">
-        <v>2463</v>
+        <v>2448</v>
       </c>
       <c r="G1268" s="2"/>
       <c r="H1268" s="2"/>
     </row>
     <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1269" s="7" t="s">
-        <v>2458</v>
+        <v>2443</v>
       </c>
       <c r="B1269" s="17">
         <v>79286136662</v>
       </c>
       <c r="C1269" s="2"/>
       <c r="D1269" s="2" t="s">
-        <v>2461</v>
+        <v>2446</v>
       </c>
       <c r="E1269" s="2"/>
       <c r="F1269" s="2"/>
@@ -31567,7 +31588,7 @@
     </row>
     <row r="1270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1270" s="40" t="s">
-        <v>2467</v>
+        <v>2452</v>
       </c>
       <c r="B1270" s="17"/>
       <c r="C1270" s="2"/>
@@ -31579,14 +31600,14 @@
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1271" s="7" t="s">
-        <v>2464</v>
+        <v>2449</v>
       </c>
       <c r="B1271" s="17">
         <v>375297856891</v>
       </c>
       <c r="C1271" s="2"/>
       <c r="D1271" s="2" t="s">
-        <v>2478</v>
+        <v>2463</v>
       </c>
       <c r="E1271" s="2"/>
       <c r="F1271" s="2"/>
@@ -31595,16 +31616,16 @@
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1272" s="7" t="s">
-        <v>2465</v>
+        <v>2450</v>
       </c>
       <c r="B1272" s="17">
         <v>79787715371</v>
       </c>
       <c r="C1272" s="2" t="s">
-        <v>2479</v>
+        <v>2464</v>
       </c>
       <c r="D1272" s="2" t="s">
-        <v>2476</v>
+        <v>2461</v>
       </c>
       <c r="E1272" s="2"/>
       <c r="F1272" s="2"/>
@@ -31613,14 +31634,14 @@
     </row>
     <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1273" s="7" t="s">
-        <v>2466</v>
+        <v>2451</v>
       </c>
       <c r="B1273" s="17">
         <v>79189218545</v>
       </c>
       <c r="C1273" s="2"/>
       <c r="D1273" s="2" t="s">
-        <v>2477</v>
+        <v>2462</v>
       </c>
       <c r="E1273" s="2"/>
       <c r="F1273" s="2"/>
@@ -31629,7 +31650,7 @@
     </row>
     <row r="1274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1274" s="40" t="s">
-        <v>2468</v>
+        <v>2453</v>
       </c>
       <c r="B1274" s="17"/>
       <c r="C1274" s="2"/>
@@ -31641,16 +31662,16 @@
     </row>
     <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1275" s="7" t="s">
-        <v>2469</v>
+        <v>2454</v>
       </c>
       <c r="B1275" s="17">
         <v>79883302117</v>
       </c>
       <c r="C1275" s="2" t="s">
-        <v>2481</v>
+        <v>2466</v>
       </c>
       <c r="D1275" s="2" t="s">
-        <v>2480</v>
+        <v>2465</v>
       </c>
       <c r="E1275" s="2"/>
       <c r="F1275" s="2"/>
@@ -31659,13 +31680,13 @@
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1276" s="7" t="s">
-        <v>2470</v>
+        <v>2455</v>
       </c>
       <c r="B1276" s="17">
         <v>79885414599</v>
       </c>
       <c r="C1276" s="2" t="s">
-        <v>2481</v>
+        <v>2466</v>
       </c>
       <c r="D1276" s="2"/>
       <c r="E1276" s="2"/>
@@ -31675,7 +31696,7 @@
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1277" s="7" t="s">
-        <v>2471</v>
+        <v>2456</v>
       </c>
       <c r="B1277" s="17">
         <v>79606987172</v>
@@ -31683,17 +31704,17 @@
       <c r="C1277" s="2"/>
       <c r="D1277" s="2"/>
       <c r="E1277" s="2" t="s">
-        <v>2475</v>
+        <v>2460</v>
       </c>
       <c r="F1277" s="2" t="s">
-        <v>2474</v>
+        <v>2459</v>
       </c>
       <c r="G1277" s="2"/>
       <c r="H1277" s="2"/>
     </row>
     <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1278" s="40" t="s">
-        <v>2473</v>
+        <v>2458</v>
       </c>
       <c r="B1278" s="17"/>
       <c r="C1278" s="2"/>
@@ -31705,13 +31726,13 @@
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1279" s="7" t="s">
-        <v>2472</v>
+        <v>2457</v>
       </c>
       <c r="B1279" s="17">
         <v>79002702201</v>
       </c>
       <c r="C1279" s="2" t="s">
-        <v>2482</v>
+        <v>2467</v>
       </c>
       <c r="D1279" s="2"/>
       <c r="E1279" s="2"/>
@@ -31739,7 +31760,7 @@
     </row>
     <row r="1281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1281" s="40" t="s">
-        <v>2544</v>
+        <v>2529</v>
       </c>
       <c r="B1281" s="17"/>
       <c r="C1281" s="2"/>
@@ -31751,13 +31772,13 @@
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1282" s="7" t="s">
-        <v>2545</v>
+        <v>2530</v>
       </c>
       <c r="B1282" s="17">
         <v>79036910787</v>
       </c>
       <c r="C1282" s="2" t="s">
-        <v>2562</v>
+        <v>2547</v>
       </c>
       <c r="D1282" s="2"/>
       <c r="E1282" s="2"/>
@@ -31767,58 +31788,58 @@
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1283" s="7" t="s">
-        <v>2546</v>
+        <v>2531</v>
       </c>
       <c r="B1283" s="17">
         <v>79085097827</v>
       </c>
       <c r="C1283" s="2" t="s">
-        <v>2562</v>
+        <v>2547</v>
       </c>
       <c r="D1283" s="2" t="s">
-        <v>2574</v>
+        <v>2559</v>
       </c>
       <c r="E1283" s="2" t="s">
-        <v>2568</v>
+        <v>2553</v>
       </c>
       <c r="F1283" s="2" t="s">
-        <v>2566</v>
+        <v>2551</v>
       </c>
       <c r="G1283" s="2"/>
       <c r="H1283" s="2"/>
     </row>
     <row r="1284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1284" s="7" t="s">
-        <v>2547</v>
+        <v>2532</v>
       </c>
       <c r="B1284" s="17">
         <v>79786456031</v>
       </c>
       <c r="C1284" s="2" t="s">
-        <v>2562</v>
+        <v>2547</v>
       </c>
       <c r="D1284" s="2" t="s">
-        <v>2575</v>
+        <v>2560</v>
       </c>
       <c r="E1284" s="2" t="s">
-        <v>2568</v>
+        <v>2553</v>
       </c>
       <c r="F1284" s="2" t="s">
-        <v>2567</v>
+        <v>2552</v>
       </c>
       <c r="G1284" s="2"/>
       <c r="H1284" s="2"/>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1285" s="7" t="s">
-        <v>2548</v>
+        <v>2533</v>
       </c>
       <c r="B1285" s="17">
         <v>79180492172</v>
       </c>
       <c r="C1285" s="2"/>
       <c r="D1285" s="2" t="s">
-        <v>2575</v>
+        <v>2560</v>
       </c>
       <c r="E1285" s="2"/>
       <c r="F1285" s="2"/>
@@ -31827,7 +31848,7 @@
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1286" s="40" t="s">
-        <v>2549</v>
+        <v>2534</v>
       </c>
       <c r="B1286" s="17"/>
       <c r="C1286" s="2"/>
@@ -31839,7 +31860,7 @@
     </row>
     <row r="1287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1287" s="7" t="s">
-        <v>2550</v>
+        <v>2535</v>
       </c>
       <c r="B1287" s="17">
         <v>79530708343</v>
@@ -31847,26 +31868,26 @@
       <c r="C1287" s="2"/>
       <c r="D1287" s="2"/>
       <c r="E1287" s="2" t="s">
-        <v>2571</v>
+        <v>2556</v>
       </c>
       <c r="F1287" s="2" t="s">
-        <v>2569</v>
+        <v>2554</v>
       </c>
       <c r="G1287" s="2"/>
       <c r="H1287" s="2"/>
     </row>
     <row r="1288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1288" s="7" t="s">
-        <v>2551</v>
+        <v>2536</v>
       </c>
       <c r="B1288" s="17">
         <v>79618588262</v>
       </c>
       <c r="C1288" s="2" t="s">
-        <v>2563</v>
+        <v>2548</v>
       </c>
       <c r="D1288" s="2" t="s">
-        <v>2576</v>
+        <v>2561</v>
       </c>
       <c r="E1288" s="2"/>
       <c r="F1288" s="2"/>
@@ -31875,7 +31896,7 @@
     </row>
     <row r="1289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1289" s="7" t="s">
-        <v>2552</v>
+        <v>2537</v>
       </c>
       <c r="B1289" s="17">
         <v>79990580869</v>
@@ -31883,17 +31904,17 @@
       <c r="C1289" s="2"/>
       <c r="D1289" s="2"/>
       <c r="E1289" s="2" t="s">
-        <v>2571</v>
+        <v>2556</v>
       </c>
       <c r="F1289" s="2" t="s">
-        <v>2570</v>
+        <v>2555</v>
       </c>
       <c r="G1289" s="2"/>
       <c r="H1289" s="2"/>
     </row>
     <row r="1290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1290" s="7" t="s">
-        <v>2553</v>
+        <v>2538</v>
       </c>
       <c r="B1290" s="17">
         <v>79283306686</v>
@@ -31901,23 +31922,23 @@
       <c r="C1290" s="2"/>
       <c r="D1290" s="2"/>
       <c r="E1290" s="2" t="s">
-        <v>2571</v>
+        <v>2556</v>
       </c>
       <c r="F1290" s="2" t="s">
-        <v>2570</v>
+        <v>2555</v>
       </c>
       <c r="G1290" s="2"/>
       <c r="H1290" s="2"/>
     </row>
     <row r="1291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1291" s="7" t="s">
-        <v>2554</v>
+        <v>2539</v>
       </c>
       <c r="B1291" s="17">
         <v>79184803174</v>
       </c>
       <c r="C1291" s="2" t="s">
-        <v>2563</v>
+        <v>2548</v>
       </c>
       <c r="D1291" s="2"/>
       <c r="E1291" s="2"/>
@@ -31927,13 +31948,13 @@
     </row>
     <row r="1292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1292" s="7" t="s">
-        <v>2555</v>
+        <v>2540</v>
       </c>
       <c r="B1292" s="17">
         <v>79186825836</v>
       </c>
       <c r="C1292" s="2" t="s">
-        <v>2563</v>
+        <v>2548</v>
       </c>
       <c r="D1292" s="2"/>
       <c r="E1292" s="2"/>
@@ -31943,13 +31964,13 @@
     </row>
     <row r="1293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1293" s="7" t="s">
-        <v>2556</v>
+        <v>2541</v>
       </c>
       <c r="B1293" s="17">
         <v>79182466940</v>
       </c>
       <c r="C1293" s="2" t="s">
-        <v>2563</v>
+        <v>2548</v>
       </c>
       <c r="D1293" s="2"/>
       <c r="E1293" s="2"/>
@@ -31959,7 +31980,7 @@
     </row>
     <row r="1294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1294" s="40" t="s">
-        <v>2558</v>
+        <v>2543</v>
       </c>
       <c r="B1294" s="17"/>
       <c r="C1294" s="2"/>
@@ -31970,16 +31991,16 @@
     </row>
     <row r="1295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1295" s="7" t="s">
-        <v>2557</v>
+        <v>2542</v>
       </c>
       <c r="B1295" s="17">
         <v>79149202703</v>
       </c>
       <c r="C1295" s="2" t="s">
-        <v>2564</v>
+        <v>2549</v>
       </c>
       <c r="D1295" s="2" t="s">
-        <v>2577</v>
+        <v>2562</v>
       </c>
       <c r="E1295" s="2"/>
       <c r="F1295" s="2"/>
@@ -31987,26 +32008,26 @@
     </row>
     <row r="1296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1296" s="7" t="s">
-        <v>2559</v>
+        <v>2544</v>
       </c>
       <c r="B1296" s="17">
         <v>79885468941</v>
       </c>
       <c r="C1296" s="2" t="s">
-        <v>2564</v>
+        <v>2549</v>
       </c>
       <c r="D1296" s="2"/>
       <c r="E1296" s="2" t="s">
-        <v>2573</v>
+        <v>2558</v>
       </c>
       <c r="F1296" s="2" t="s">
-        <v>2572</v>
+        <v>2557</v>
       </c>
       <c r="G1296" s="2"/>
     </row>
     <row r="1297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1297" s="40" t="s">
-        <v>2560</v>
+        <v>2545</v>
       </c>
       <c r="B1297" s="17"/>
       <c r="C1297" s="2"/>
@@ -32017,16 +32038,16 @@
     </row>
     <row r="1298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1298" s="7" t="s">
-        <v>2561</v>
+        <v>2546</v>
       </c>
       <c r="B1298" s="17">
         <v>79806633494</v>
       </c>
       <c r="C1298" s="2" t="s">
-        <v>2565</v>
+        <v>2550</v>
       </c>
       <c r="D1298" s="2" t="s">
-        <v>2578</v>
+        <v>2563</v>
       </c>
       <c r="E1298" s="2"/>
       <c r="F1298" s="2"/>
@@ -32051,7 +32072,7 @@
     </row>
     <row r="1300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1300" s="40" t="s">
-        <v>2579</v>
+        <v>2564</v>
       </c>
       <c r="B1300" s="17"/>
       <c r="C1300" s="2"/>
@@ -32062,13 +32083,13 @@
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1301" s="7" t="s">
-        <v>2580</v>
+        <v>2565</v>
       </c>
       <c r="B1301" s="17">
         <v>79525837593</v>
       </c>
       <c r="C1301" s="2" t="s">
-        <v>2597</v>
+        <v>2582</v>
       </c>
       <c r="D1301" s="2"/>
       <c r="E1301" s="2"/>
@@ -32077,16 +32098,16 @@
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1302" s="7" t="s">
-        <v>2581</v>
+        <v>2566</v>
       </c>
       <c r="B1302" s="17">
         <v>79183870112</v>
       </c>
       <c r="C1302" s="2" t="s">
-        <v>2597</v>
+        <v>2582</v>
       </c>
       <c r="D1302" s="2" t="s">
-        <v>2595</v>
+        <v>2580</v>
       </c>
       <c r="E1302" s="2"/>
       <c r="F1302" s="2"/>
@@ -32094,14 +32115,14 @@
     </row>
     <row r="1303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1303" s="7" t="s">
-        <v>2582</v>
+        <v>2567</v>
       </c>
       <c r="B1303" s="17">
         <v>79182842938</v>
       </c>
       <c r="C1303" s="2"/>
       <c r="D1303" s="2" t="s">
-        <v>2596</v>
+        <v>2581</v>
       </c>
       <c r="E1303" s="2"/>
       <c r="F1303" s="2"/>
@@ -32109,7 +32130,7 @@
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1304" s="40" t="s">
-        <v>2583</v>
+        <v>2568</v>
       </c>
       <c r="B1304" s="17"/>
       <c r="C1304" s="2"/>
@@ -32120,28 +32141,28 @@
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1305" s="7" t="s">
-        <v>2584</v>
+        <v>2569</v>
       </c>
       <c r="B1305" s="17">
         <v>79183772137</v>
       </c>
       <c r="C1305" s="2" t="s">
-        <v>2600</v>
+        <v>2585</v>
       </c>
       <c r="D1305" s="2" t="s">
-        <v>2598</v>
+        <v>2583</v>
       </c>
       <c r="E1305" s="2" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="F1305" s="2" t="s">
-        <v>2592</v>
+        <v>2577</v>
       </c>
       <c r="G1305" s="2"/>
     </row>
     <row r="1306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1306" s="7" t="s">
-        <v>2585</v>
+        <v>2570</v>
       </c>
       <c r="B1306" s="17">
         <v>79897201133</v>
@@ -32149,23 +32170,23 @@
       <c r="C1306" s="2"/>
       <c r="D1306" s="2"/>
       <c r="E1306" s="2" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="F1306" s="2" t="s">
-        <v>2593</v>
+        <v>2578</v>
       </c>
       <c r="G1306" s="2"/>
     </row>
     <row r="1307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1307" s="7" t="s">
-        <v>2586</v>
+        <v>2571</v>
       </c>
       <c r="B1307" s="17">
         <v>79615332857</v>
       </c>
       <c r="C1307" s="2"/>
       <c r="D1307" s="2" t="s">
-        <v>2599</v>
+        <v>2584</v>
       </c>
       <c r="E1307" s="2"/>
       <c r="F1307" s="2"/>
@@ -32173,14 +32194,14 @@
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1308" s="7" t="s">
-        <v>2587</v>
+        <v>2572</v>
       </c>
       <c r="B1308" s="17">
         <v>79184188755</v>
       </c>
       <c r="C1308" s="2"/>
       <c r="D1308" s="2" t="s">
-        <v>2599</v>
+        <v>2584</v>
       </c>
       <c r="E1308" s="2"/>
       <c r="F1308" s="2"/>
@@ -32188,7 +32209,7 @@
     </row>
     <row r="1309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1309" s="40" t="s">
-        <v>2588</v>
+        <v>2573</v>
       </c>
       <c r="B1309" s="17"/>
       <c r="C1309" s="2"/>
@@ -32199,14 +32220,14 @@
     </row>
     <row r="1310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1310" s="7" t="s">
-        <v>2589</v>
+        <v>2574</v>
       </c>
       <c r="B1310" s="17">
         <v>79034550320</v>
       </c>
       <c r="C1310" s="2"/>
       <c r="D1310" s="2" t="s">
-        <v>2601</v>
+        <v>2586</v>
       </c>
       <c r="E1310" s="2"/>
       <c r="F1310" s="2"/>
@@ -32214,13 +32235,13 @@
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1311" s="7" t="s">
-        <v>2590</v>
+        <v>2575</v>
       </c>
       <c r="B1311" s="17">
         <v>79497336125</v>
       </c>
       <c r="C1311" s="2" t="s">
-        <v>2603</v>
+        <v>2588</v>
       </c>
       <c r="D1311" s="2"/>
       <c r="E1311" s="2"/>
@@ -32229,14 +32250,14 @@
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1312" s="7" t="s">
-        <v>2591</v>
+        <v>2576</v>
       </c>
       <c r="B1312" s="17">
         <v>79676739173</v>
       </c>
       <c r="C1312" s="2"/>
       <c r="D1312" s="2" t="s">
-        <v>2602</v>
+        <v>2587</v>
       </c>
       <c r="E1312" s="2"/>
       <c r="F1312" s="2"/>
@@ -32261,7 +32282,7 @@
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1314" s="40" t="s">
-        <v>2604</v>
+        <v>2589</v>
       </c>
       <c r="B1314" s="17"/>
       <c r="C1314" s="2"/>
@@ -32272,26 +32293,26 @@
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1315" s="7" t="s">
-        <v>2605</v>
+        <v>2590</v>
       </c>
       <c r="B1315" s="17">
         <v>79183767815</v>
       </c>
       <c r="C1315" s="2"/>
       <c r="D1315" s="2" t="s">
-        <v>2614</v>
+        <v>2599</v>
       </c>
       <c r="E1315" s="2" t="s">
-        <v>2619</v>
+        <v>2604</v>
       </c>
       <c r="F1315" s="2" t="s">
-        <v>2618</v>
+        <v>2603</v>
       </c>
       <c r="G1315" s="2"/>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1316" s="40" t="s">
-        <v>2609</v>
+        <v>2594</v>
       </c>
       <c r="C1316" s="2"/>
       <c r="D1316" s="2"/>
@@ -32301,13 +32322,13 @@
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1317" s="7" t="s">
-        <v>2606</v>
+        <v>2591</v>
       </c>
       <c r="B1317" s="17">
         <v>79528700394</v>
       </c>
       <c r="C1317" s="2" t="s">
-        <v>2616</v>
+        <v>2601</v>
       </c>
       <c r="D1317" s="2"/>
       <c r="E1317" s="2"/>
@@ -32316,13 +32337,13 @@
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1318" s="7" t="s">
-        <v>2607</v>
+        <v>2592</v>
       </c>
       <c r="B1318" s="17">
         <v>79054305403</v>
       </c>
       <c r="C1318" s="2" t="s">
-        <v>2616</v>
+        <v>2601</v>
       </c>
       <c r="D1318" s="2"/>
       <c r="E1318" s="2"/>
@@ -32331,14 +32352,14 @@
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1319" s="7" t="s">
-        <v>2608</v>
+        <v>2593</v>
       </c>
       <c r="B1319" s="17">
         <v>79064046088</v>
       </c>
       <c r="C1319" s="2"/>
       <c r="D1319" s="2" t="s">
-        <v>2615</v>
+        <v>2600</v>
       </c>
       <c r="E1319" s="2"/>
       <c r="F1319" s="2"/>
@@ -32346,16 +32367,16 @@
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1320" s="7" t="s">
-        <v>2610</v>
+        <v>2595</v>
       </c>
       <c r="B1320" s="17">
         <v>79284483258</v>
       </c>
       <c r="C1320" s="2" t="s">
-        <v>2616</v>
+        <v>2601</v>
       </c>
       <c r="D1320" s="2" t="s">
-        <v>2615</v>
+        <v>2600</v>
       </c>
       <c r="E1320" s="2"/>
       <c r="F1320" s="2"/>
@@ -32363,7 +32384,7 @@
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1321" s="40" t="s">
-        <v>2611</v>
+        <v>2596</v>
       </c>
       <c r="B1321" s="17"/>
       <c r="C1321" s="2"/>
@@ -32374,13 +32395,13 @@
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1322" s="7" t="s">
-        <v>2612</v>
+        <v>2597</v>
       </c>
       <c r="B1322">
         <v>79081817570</v>
       </c>
       <c r="C1322" t="s">
-        <v>2617</v>
+        <v>2602</v>
       </c>
       <c r="D1322" s="2"/>
       <c r="E1322" s="2"/>
@@ -32389,23 +32410,23 @@
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1323" s="7" t="s">
-        <v>2613</v>
+        <v>2598</v>
       </c>
       <c r="B1323">
         <v>79045033313</v>
       </c>
       <c r="D1323" s="2"/>
       <c r="E1323" s="2" t="s">
-        <v>2621</v>
+        <v>2606</v>
       </c>
       <c r="F1323" s="2" t="s">
-        <v>2620</v>
+        <v>2605</v>
       </c>
       <c r="G1323" s="2"/>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1324" s="40" t="s">
-        <v>2622</v>
+        <v>2607</v>
       </c>
       <c r="D1324" s="2"/>
       <c r="E1324" s="2"/>
@@ -32414,26 +32435,26 @@
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1325" s="7" t="s">
-        <v>2623</v>
+        <v>2608</v>
       </c>
       <c r="B1325" s="17">
         <v>79186195666</v>
       </c>
       <c r="C1325" s="2" t="s">
-        <v>2721</v>
+        <v>2706</v>
       </c>
       <c r="D1325" s="2"/>
       <c r="E1325" s="2" t="s">
-        <v>2729</v>
+        <v>2714</v>
       </c>
       <c r="F1325" s="2" t="s">
-        <v>2727</v>
+        <v>2712</v>
       </c>
       <c r="G1325" s="2"/>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1326" s="7" t="s">
-        <v>2624</v>
+        <v>2609</v>
       </c>
       <c r="B1326" s="17">
         <v>79780648554</v>
@@ -32441,23 +32462,23 @@
       <c r="C1326" s="2"/>
       <c r="D1326" s="2"/>
       <c r="E1326" s="2" t="s">
-        <v>2729</v>
+        <v>2714</v>
       </c>
       <c r="F1326" s="2" t="s">
-        <v>2728</v>
+        <v>2713</v>
       </c>
       <c r="G1326" s="2"/>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1327" s="7" t="s">
-        <v>2625</v>
+        <v>2610</v>
       </c>
       <c r="B1327" s="17">
         <v>79493022752</v>
       </c>
       <c r="C1327" s="2"/>
       <c r="D1327" s="2" t="s">
-        <v>2722</v>
+        <v>2707</v>
       </c>
       <c r="E1327" s="2"/>
       <c r="F1327" s="2"/>
@@ -32465,7 +32486,7 @@
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1328" s="40" t="s">
-        <v>2626</v>
+        <v>2611</v>
       </c>
       <c r="B1328" s="17"/>
       <c r="C1328" s="2"/>
@@ -32476,35 +32497,35 @@
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1329" s="7" t="s">
-        <v>2627</v>
+        <v>2612</v>
       </c>
       <c r="B1329" s="17">
         <v>79085033991</v>
       </c>
       <c r="C1329" s="2"/>
-      <c r="D1329" s="2" t="s">
-        <v>2723</v>
-      </c>
+      <c r="D1329" s="2"/>
       <c r="E1329" s="2"/>
       <c r="F1329" s="2"/>
       <c r="G1329" s="2"/>
     </row>
     <row r="1330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1330" s="7" t="s">
-        <v>2628</v>
+        <v>2613</v>
       </c>
       <c r="B1330" s="17">
         <v>79282576368</v>
       </c>
       <c r="C1330" s="2"/>
-      <c r="D1330" s="2"/>
+      <c r="D1330" s="2" t="s">
+        <v>2708</v>
+      </c>
       <c r="E1330" s="2"/>
       <c r="F1330" s="2"/>
       <c r="G1330" s="2"/>
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1331" s="40" t="s">
-        <v>2629</v>
+        <v>2614</v>
       </c>
       <c r="B1331" s="17"/>
       <c r="C1331" s="2"/>
@@ -32515,13 +32536,13 @@
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1332" s="7" t="s">
-        <v>2630</v>
+        <v>2615</v>
       </c>
       <c r="B1332" s="17">
         <v>79054871997</v>
       </c>
       <c r="C1332" s="2" t="s">
-        <v>2726</v>
+        <v>2711</v>
       </c>
       <c r="D1332" s="2"/>
       <c r="E1332" s="2"/>
@@ -32530,14 +32551,14 @@
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1333" s="7" t="s">
-        <v>2631</v>
+        <v>2616</v>
       </c>
       <c r="B1333" s="17">
         <v>79193683714</v>
       </c>
       <c r="C1333" s="2"/>
       <c r="D1333" s="2" t="s">
-        <v>2725</v>
+        <v>2710</v>
       </c>
       <c r="E1333" s="2"/>
       <c r="F1333" s="2"/>
@@ -32545,14 +32566,14 @@
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1334" s="7" t="s">
-        <v>2632</v>
+        <v>2617</v>
       </c>
       <c r="B1334" s="17">
         <v>79586493944</v>
       </c>
       <c r="C1334" s="2"/>
       <c r="D1334" s="2" t="s">
-        <v>2724</v>
+        <v>2709</v>
       </c>
       <c r="E1334" s="2"/>
       <c r="F1334" s="2"/>
@@ -32560,13 +32581,13 @@
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1335" s="7" t="s">
-        <v>2633</v>
+        <v>2618</v>
       </c>
       <c r="B1335" s="17">
         <v>79780045546</v>
       </c>
       <c r="C1335" s="2" t="s">
-        <v>2726</v>
+        <v>2711</v>
       </c>
       <c r="D1335" s="2"/>
       <c r="E1335" s="2"/>
@@ -32576,14 +32597,24 @@
     <row r="1336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1336" s="7"/>
       <c r="B1336" s="17"/>
-      <c r="C1336" s="2"/>
-      <c r="D1336" s="2"/>
-      <c r="E1336" s="2"/>
-      <c r="F1336" s="2"/>
+      <c r="C1336" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1336" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1336" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1336" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1336" s="2"/>
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1337" s="7"/>
+      <c r="A1337" s="40" t="s">
+        <v>2733</v>
+      </c>
       <c r="B1337" s="17"/>
       <c r="C1337" s="2"/>
       <c r="D1337" s="2"/>
@@ -32592,16 +32623,27 @@
       <c r="G1337" s="2"/>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1338" s="7"/>
-      <c r="B1338" s="17"/>
-      <c r="C1338" s="2"/>
-      <c r="D1338" s="2"/>
+      <c r="A1338" s="7" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B1338" s="17">
+        <v>79782640332</v>
+      </c>
+      <c r="C1338" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1338" s="2" t="s">
+        <v>2738</v>
+      </c>
       <c r="E1338" s="2"/>
       <c r="F1338" s="2"/>
       <c r="G1338" s="2"/>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1339" s="1"/>
+      <c r="A1339" s="40" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B1339" s="17"/>
       <c r="C1339" s="2"/>
       <c r="D1339" s="2"/>
       <c r="E1339" s="2"/>
@@ -32609,162 +32651,434 @@
       <c r="G1339" s="2"/>
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1340" s="1"/>
+      <c r="A1340" s="7" t="s">
+        <v>2736</v>
+      </c>
+      <c r="B1340" s="17">
+        <v>79530977713</v>
+      </c>
+      <c r="C1340" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1340" s="2" t="s">
+        <v>2738</v>
+      </c>
+      <c r="E1340" s="2"/>
+      <c r="F1340" s="2"/>
+      <c r="G1340" s="2"/>
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1341" s="1"/>
+      <c r="A1341" s="7" t="s">
+        <v>2737</v>
+      </c>
+      <c r="B1341" s="17">
+        <v>79896279922</v>
+      </c>
+      <c r="C1341" s="2"/>
+      <c r="D1341" s="2" t="s">
+        <v>2739</v>
+      </c>
+      <c r="E1341" s="2"/>
+      <c r="F1341" s="2"/>
+      <c r="G1341" s="2"/>
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1342" s="1"/>
+      <c r="A1342" s="7"/>
+      <c r="B1342" s="17"/>
+      <c r="C1342" s="2"/>
+      <c r="D1342" s="2"/>
+      <c r="E1342" s="2"/>
+      <c r="F1342" s="2"/>
+      <c r="G1342" s="2"/>
     </row>
     <row r="1343" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1343" s="1"/>
+      <c r="A1343" s="7"/>
+      <c r="B1343" s="17"/>
+      <c r="C1343" s="2"/>
+      <c r="D1343" s="2"/>
+      <c r="E1343" s="2"/>
+      <c r="F1343" s="2"/>
+      <c r="G1343" s="2"/>
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1344" s="1"/>
-    </row>
-    <row r="1345" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1345" s="1"/>
-    </row>
-    <row r="1346" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1346" s="1"/>
-    </row>
-    <row r="1347" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1347" s="1"/>
-    </row>
-    <row r="1348" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1348" s="1"/>
-    </row>
-    <row r="1349" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1349" s="1"/>
-    </row>
-    <row r="1350" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1350" s="1"/>
-    </row>
-    <row r="1351" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1351" s="1"/>
-    </row>
-    <row r="1352" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1352" s="1"/>
-    </row>
-    <row r="1353" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1353" s="1"/>
-    </row>
-    <row r="1354" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1354" s="1"/>
-    </row>
-    <row r="1355" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1355" s="1"/>
-    </row>
-    <row r="1356" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1356" s="1"/>
-    </row>
-    <row r="1357" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1357" s="1"/>
-    </row>
-    <row r="1358" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1358" s="1"/>
-    </row>
-    <row r="1359" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1359" s="1"/>
-    </row>
-    <row r="1360" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1360" s="1"/>
-    </row>
-    <row r="1361" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1361" s="1"/>
-    </row>
-    <row r="1362" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1362" s="1"/>
-    </row>
-    <row r="1363" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1363" s="1"/>
-    </row>
-    <row r="1364" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1364" s="1"/>
-    </row>
-    <row r="1365" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1365" s="1"/>
-    </row>
-    <row r="1366" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1366" s="1"/>
-    </row>
-    <row r="1367" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1367" s="1"/>
-    </row>
-    <row r="1368" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1368" s="1"/>
-    </row>
-    <row r="1369" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1369" s="1"/>
-    </row>
-    <row r="1370" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1370" s="1"/>
-    </row>
-    <row r="1371" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1371" s="1"/>
-    </row>
-    <row r="1372" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1372" s="1"/>
-    </row>
-    <row r="1373" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1373" s="1"/>
-    </row>
-    <row r="1374" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1374" s="1"/>
-    </row>
-    <row r="1375" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1375" s="1"/>
-    </row>
-    <row r="1376" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1376" s="1"/>
-    </row>
-    <row r="1377" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1377" s="1"/>
-    </row>
-    <row r="1378" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1378" s="1"/>
-    </row>
-    <row r="1379" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1379" s="1"/>
-    </row>
-    <row r="1380" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1380" s="1"/>
-    </row>
-    <row r="1381" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1381" s="1"/>
-    </row>
-    <row r="1382" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1382" s="1"/>
-    </row>
-    <row r="1383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1344" s="7"/>
+      <c r="B1344" s="17"/>
+      <c r="C1344" s="2"/>
+      <c r="D1344" s="2"/>
+      <c r="E1344" s="2"/>
+      <c r="F1344" s="2"/>
+      <c r="G1344" s="2"/>
+    </row>
+    <row r="1345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1345" s="7"/>
+      <c r="B1345" s="17"/>
+      <c r="C1345" s="2"/>
+      <c r="D1345" s="2"/>
+      <c r="E1345" s="2"/>
+      <c r="F1345" s="2"/>
+      <c r="G1345" s="2"/>
+    </row>
+    <row r="1346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1346" s="7"/>
+      <c r="B1346" s="17"/>
+      <c r="C1346" s="2"/>
+      <c r="D1346" s="2"/>
+      <c r="E1346" s="2"/>
+      <c r="F1346" s="2"/>
+      <c r="G1346" s="2"/>
+    </row>
+    <row r="1347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1347" s="7"/>
+      <c r="B1347" s="17"/>
+      <c r="C1347" s="2"/>
+      <c r="D1347" s="2"/>
+      <c r="E1347" s="2"/>
+      <c r="F1347" s="2"/>
+      <c r="G1347" s="2"/>
+    </row>
+    <row r="1348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1348" s="7"/>
+      <c r="B1348" s="17"/>
+      <c r="C1348" s="2"/>
+      <c r="D1348" s="2"/>
+      <c r="E1348" s="2"/>
+      <c r="F1348" s="2"/>
+      <c r="G1348" s="2"/>
+    </row>
+    <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1349" s="7"/>
+      <c r="B1349" s="17"/>
+      <c r="C1349" s="2"/>
+      <c r="D1349" s="2"/>
+      <c r="E1349" s="2"/>
+      <c r="F1349" s="2"/>
+      <c r="G1349" s="2"/>
+    </row>
+    <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1350" s="7"/>
+      <c r="B1350" s="17"/>
+      <c r="C1350" s="2"/>
+      <c r="D1350" s="2"/>
+      <c r="E1350" s="2"/>
+      <c r="F1350" s="2"/>
+      <c r="G1350" s="2"/>
+    </row>
+    <row r="1351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1351" s="7"/>
+      <c r="B1351" s="17"/>
+      <c r="C1351" s="2"/>
+      <c r="D1351" s="2"/>
+      <c r="E1351" s="2"/>
+      <c r="F1351" s="2"/>
+      <c r="G1351" s="2"/>
+    </row>
+    <row r="1352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1352" s="7"/>
+      <c r="B1352" s="17"/>
+      <c r="C1352" s="2"/>
+      <c r="D1352" s="2"/>
+      <c r="E1352" s="2"/>
+      <c r="F1352" s="2"/>
+      <c r="G1352" s="2"/>
+    </row>
+    <row r="1353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1353" s="7"/>
+      <c r="B1353" s="17"/>
+      <c r="C1353" s="2"/>
+      <c r="D1353" s="2"/>
+      <c r="E1353" s="2"/>
+      <c r="F1353" s="2"/>
+      <c r="G1353" s="2"/>
+    </row>
+    <row r="1354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1354" s="7"/>
+      <c r="B1354" s="17"/>
+      <c r="C1354" s="2"/>
+      <c r="D1354" s="2"/>
+      <c r="E1354" s="2"/>
+      <c r="F1354" s="2"/>
+      <c r="G1354" s="2"/>
+    </row>
+    <row r="1355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1355" s="7"/>
+      <c r="B1355" s="17"/>
+      <c r="C1355" s="2"/>
+      <c r="D1355" s="2"/>
+      <c r="E1355" s="2"/>
+      <c r="F1355" s="2"/>
+      <c r="G1355" s="2"/>
+    </row>
+    <row r="1356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1356" s="7"/>
+      <c r="B1356" s="17"/>
+      <c r="C1356" s="2"/>
+      <c r="D1356" s="2"/>
+      <c r="E1356" s="2"/>
+      <c r="F1356" s="2"/>
+      <c r="G1356" s="2"/>
+    </row>
+    <row r="1357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1357" s="7"/>
+      <c r="B1357" s="17"/>
+      <c r="C1357" s="2"/>
+      <c r="D1357" s="2"/>
+      <c r="E1357" s="2"/>
+      <c r="F1357" s="2"/>
+      <c r="G1357" s="2"/>
+    </row>
+    <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1358" s="7"/>
+      <c r="B1358" s="17"/>
+      <c r="C1358" s="2"/>
+      <c r="D1358" s="2"/>
+      <c r="E1358" s="2"/>
+      <c r="F1358" s="2"/>
+      <c r="G1358" s="2"/>
+    </row>
+    <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1359" s="7"/>
+      <c r="B1359" s="17"/>
+      <c r="C1359" s="2"/>
+      <c r="D1359" s="2"/>
+      <c r="E1359" s="2"/>
+      <c r="F1359" s="2"/>
+      <c r="G1359" s="2"/>
+    </row>
+    <row r="1360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1360" s="7"/>
+      <c r="B1360" s="17"/>
+      <c r="C1360" s="2"/>
+      <c r="D1360" s="2"/>
+      <c r="E1360" s="2"/>
+      <c r="F1360" s="2"/>
+      <c r="G1360" s="2"/>
+    </row>
+    <row r="1361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1361" s="7"/>
+      <c r="B1361" s="17"/>
+      <c r="C1361" s="2"/>
+      <c r="D1361" s="2"/>
+      <c r="E1361" s="2"/>
+      <c r="F1361" s="2"/>
+      <c r="G1361" s="2"/>
+    </row>
+    <row r="1362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1362" s="7"/>
+      <c r="B1362" s="17"/>
+      <c r="C1362" s="2"/>
+      <c r="D1362" s="2"/>
+      <c r="E1362" s="2"/>
+      <c r="F1362" s="2"/>
+      <c r="G1362" s="2"/>
+    </row>
+    <row r="1363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1363" s="7"/>
+      <c r="B1363" s="17"/>
+      <c r="C1363" s="2"/>
+      <c r="D1363" s="2"/>
+      <c r="E1363" s="2"/>
+      <c r="F1363" s="2"/>
+      <c r="G1363" s="2"/>
+    </row>
+    <row r="1364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1364" s="7"/>
+      <c r="B1364" s="17"/>
+      <c r="C1364" s="2"/>
+      <c r="D1364" s="2"/>
+      <c r="E1364" s="2"/>
+      <c r="F1364" s="2"/>
+      <c r="G1364" s="2"/>
+    </row>
+    <row r="1365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1365" s="7"/>
+      <c r="B1365" s="17"/>
+      <c r="C1365" s="2"/>
+      <c r="D1365" s="2"/>
+      <c r="E1365" s="2"/>
+      <c r="F1365" s="2"/>
+      <c r="G1365" s="2"/>
+    </row>
+    <row r="1366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1366" s="7"/>
+      <c r="B1366" s="17"/>
+      <c r="C1366" s="2"/>
+      <c r="D1366" s="2"/>
+      <c r="E1366" s="2"/>
+      <c r="F1366" s="2"/>
+      <c r="G1366" s="2"/>
+    </row>
+    <row r="1367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1367" s="7"/>
+      <c r="B1367" s="17"/>
+      <c r="C1367" s="2"/>
+      <c r="D1367" s="2"/>
+      <c r="E1367" s="2"/>
+      <c r="F1367" s="2"/>
+      <c r="G1367" s="2"/>
+    </row>
+    <row r="1368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1368" s="7"/>
+      <c r="B1368" s="17"/>
+      <c r="C1368" s="2"/>
+      <c r="D1368" s="2"/>
+      <c r="E1368" s="2"/>
+      <c r="F1368" s="2"/>
+      <c r="G1368" s="2"/>
+    </row>
+    <row r="1369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1369" s="7"/>
+      <c r="B1369" s="17"/>
+      <c r="C1369" s="2"/>
+      <c r="D1369" s="2"/>
+      <c r="E1369" s="2"/>
+      <c r="F1369" s="2"/>
+      <c r="G1369" s="2"/>
+    </row>
+    <row r="1370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1370" s="7"/>
+      <c r="B1370" s="17"/>
+      <c r="C1370" s="2"/>
+      <c r="D1370" s="2"/>
+      <c r="E1370" s="2"/>
+      <c r="F1370" s="2"/>
+      <c r="G1370" s="2"/>
+    </row>
+    <row r="1371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1371" s="7"/>
+      <c r="B1371" s="17"/>
+      <c r="C1371" s="2"/>
+      <c r="D1371" s="2"/>
+      <c r="E1371" s="2"/>
+      <c r="F1371" s="2"/>
+      <c r="G1371" s="2"/>
+    </row>
+    <row r="1372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1372" s="7"/>
+      <c r="B1372" s="17"/>
+      <c r="C1372" s="2"/>
+      <c r="D1372" s="2"/>
+      <c r="E1372" s="2"/>
+      <c r="F1372" s="2"/>
+      <c r="G1372" s="2"/>
+    </row>
+    <row r="1373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1373" s="7"/>
+      <c r="B1373" s="17"/>
+      <c r="C1373" s="2"/>
+      <c r="D1373" s="2"/>
+      <c r="E1373" s="2"/>
+      <c r="F1373" s="2"/>
+      <c r="G1373" s="2"/>
+    </row>
+    <row r="1374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1374" s="7"/>
+      <c r="B1374" s="17"/>
+      <c r="C1374" s="2"/>
+      <c r="D1374" s="2"/>
+      <c r="E1374" s="2"/>
+      <c r="F1374" s="2"/>
+      <c r="G1374" s="2"/>
+    </row>
+    <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1375" s="7"/>
+      <c r="B1375" s="17"/>
+      <c r="C1375" s="2"/>
+      <c r="D1375" s="2"/>
+      <c r="E1375" s="2"/>
+      <c r="F1375" s="2"/>
+      <c r="G1375" s="2"/>
+    </row>
+    <row r="1376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1376" s="7"/>
+      <c r="B1376" s="17"/>
+      <c r="C1376" s="2"/>
+      <c r="D1376" s="2"/>
+      <c r="E1376" s="2"/>
+      <c r="F1376" s="2"/>
+      <c r="G1376" s="2"/>
+    </row>
+    <row r="1377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1377" s="7"/>
+      <c r="B1377" s="17"/>
+      <c r="C1377" s="2"/>
+      <c r="D1377" s="2"/>
+      <c r="E1377" s="2"/>
+      <c r="F1377" s="2"/>
+      <c r="G1377" s="2"/>
+    </row>
+    <row r="1378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1378" s="7"/>
+      <c r="B1378" s="17"/>
+      <c r="C1378" s="2"/>
+      <c r="D1378" s="2"/>
+      <c r="E1378" s="2"/>
+      <c r="F1378" s="2"/>
+      <c r="G1378" s="2"/>
+    </row>
+    <row r="1379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1379" s="7"/>
+      <c r="B1379" s="17"/>
+      <c r="C1379" s="2"/>
+      <c r="D1379" s="2"/>
+      <c r="E1379" s="2"/>
+      <c r="F1379" s="2"/>
+      <c r="G1379" s="2"/>
+    </row>
+    <row r="1380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1380" s="7"/>
+      <c r="B1380" s="17"/>
+      <c r="C1380" s="2"/>
+      <c r="D1380" s="2"/>
+      <c r="E1380" s="2"/>
+      <c r="F1380" s="2"/>
+      <c r="G1380" s="2"/>
+    </row>
+    <row r="1381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1381" s="7"/>
+      <c r="B1381" s="17"/>
+      <c r="C1381" s="2"/>
+      <c r="D1381" s="2"/>
+      <c r="E1381" s="2"/>
+      <c r="F1381" s="2"/>
+      <c r="G1381" s="2"/>
+    </row>
+    <row r="1382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1382" s="7"/>
+      <c r="B1382" s="17"/>
+      <c r="C1382" s="2"/>
+      <c r="D1382" s="2"/>
+      <c r="E1382" s="2"/>
+      <c r="F1382" s="2"/>
+      <c r="G1382" s="2"/>
+    </row>
+    <row r="1383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1383" s="1"/>
     </row>
-    <row r="1384" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1384" s="1"/>
     </row>
-    <row r="1385" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1385" s="1"/>
     </row>
-    <row r="1386" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1386" s="1"/>
     </row>
-    <row r="1387" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1387" s="1"/>
     </row>
-    <row r="1388" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1388" s="1"/>
     </row>
-    <row r="1389" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1389" s="1"/>
     </row>
-    <row r="1390" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1390" s="1"/>
     </row>
-    <row r="1391" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1391" s="1"/>
     </row>
-    <row r="1392" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1392" s="1"/>
     </row>
     <row r="1393" spans="1:1" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB13B41-2476-45C4-AFA7-3CD3825E68C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A67207-B7A2-44B7-9260-101E9FE3CB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="2740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4229" uniqueCount="2744">
   <si>
     <t>Пароль</t>
   </si>
@@ -7194,6 +7194,9 @@
     <t>19232</t>
   </si>
   <si>
+    <t>https://disk.yandex.ru/d/sHoLaZvUkEqXuQ</t>
+  </si>
+  <si>
     <t>https://disk.yandex.ru/d/YWKLkH1mraRwcQ</t>
   </si>
   <si>
@@ -8250,10 +8253,19 @@
     <t>79922</t>
   </si>
   <si>
-    <t>* Дима</t>
-  </si>
-  <si>
-    <t>* ДанНя</t>
+    <t>https://disk.yandex.ru/d/AaMSeOmt8mwTig</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/gqAisbxvrduzRA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/jFTrKE3oT0UxBQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Im0cYk4gDt5Jxg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/yP04F8cfKjdgog</t>
   </si>
 </sst>
 </file>
@@ -24265,7 +24277,7 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" s="34" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="B847" s="41">
         <v>79185972895</v>
@@ -24287,7 +24299,7 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" s="34" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="B848" s="41">
         <v>79996262825</v>
@@ -24331,7 +24343,7 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" s="34" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="B850" s="41">
         <v>79604875670</v>
@@ -24353,7 +24365,7 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" s="34" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="B851" s="41">
         <v>79184987541</v>
@@ -24371,7 +24383,7 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" s="34" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="B852" s="41">
         <v>79185058918</v>
@@ -24387,7 +24399,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" s="34" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="B853" s="41">
         <v>79084845045</v>
@@ -24407,7 +24419,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" s="34" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="B854" s="41">
         <v>79189841111</v>
@@ -24423,7 +24435,7 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" s="34" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="B855" s="41">
         <v>79183593299</v>
@@ -24445,7 +24457,7 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" s="34" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="B856" s="41">
         <v>79286104433</v>
@@ -24463,7 +24475,7 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" s="34" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="B857" s="41">
         <v>79181204920</v>
@@ -24481,7 +24493,7 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" s="34" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="B858" s="41">
         <v>79180314664</v>
@@ -24499,7 +24511,7 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" s="34" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="B859" s="41">
         <v>79255304182</v>
@@ -24517,7 +24529,7 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" s="34" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="B860" s="41">
         <v>79624321777</v>
@@ -24535,7 +24547,7 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" s="34" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="B861" s="41">
         <v>79034652185</v>
@@ -24551,7 +24563,7 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" s="34" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="B862" s="41">
         <v>79654707870</v>
@@ -24585,7 +24597,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" s="34" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="B864" s="41">
         <v>79284244414</v>
@@ -24605,7 +24617,7 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" s="34" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="B865" s="41">
         <v>79619719206</v>
@@ -24625,7 +24637,7 @@
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" s="34" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="B866" s="41">
         <v>79530872704</v>
@@ -24681,7 +24693,7 @@
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" s="34" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="B869" s="41">
         <v>79181112526</v>
@@ -24699,7 +24711,7 @@
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" s="19" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="B870" s="42">
         <v>79186726140</v>
@@ -24739,7 +24751,7 @@
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" s="34" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="B872" s="41">
         <v>79283003384</v>
@@ -24757,7 +24769,7 @@
     </row>
     <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" s="34" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="B873" s="41">
         <v>79682666663</v>
@@ -24773,7 +24785,7 @@
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" s="34" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="B874" s="41">
         <v>79186726140</v>
@@ -24791,7 +24803,7 @@
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" s="34" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="B875" s="41">
         <v>79898051733</v>
@@ -24809,7 +24821,7 @@
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" s="34" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="B876" s="41">
         <v>79086789121</v>
@@ -24825,7 +24837,7 @@
     </row>
     <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" s="34" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="B877" s="41">
         <v>79528340083</v>
@@ -24841,7 +24853,7 @@
     </row>
     <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" s="34" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="B878" s="41">
         <v>79530930717</v>
@@ -24859,7 +24871,7 @@
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" s="34" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="B879" s="41">
         <v>79275037361</v>
@@ -24875,7 +24887,7 @@
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" s="34" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="B880" s="41">
         <v>79218083526</v>
@@ -24891,7 +24903,7 @@
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" s="34" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="B881" s="41">
         <v>79185789000</v>
@@ -24911,7 +24923,7 @@
     </row>
     <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" s="34" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="B882" s="41">
         <v>79877941509</v>
@@ -24929,7 +24941,7 @@
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" s="34" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="B883" s="41">
         <v>79618221503</v>
@@ -24969,7 +24981,7 @@
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" s="34" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="B885" s="41">
         <v>79882548579</v>
@@ -24987,7 +24999,7 @@
     </row>
     <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" s="34" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="B886" s="41">
         <v>79182900595</v>
@@ -25003,7 +25015,7 @@
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" s="34" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="B887" s="41">
         <v>79264823431</v>
@@ -25021,7 +25033,7 @@
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" s="34" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="B888" s="41">
         <v>79180246728</v>
@@ -25039,7 +25051,7 @@
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" s="34" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="B889" s="41">
         <v>79263181485</v>
@@ -25055,7 +25067,7 @@
     </row>
     <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" s="34" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="B890" s="41">
         <v>79189573595</v>
@@ -25073,7 +25085,7 @@
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" s="34" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="B891" s="41">
         <v>79180129312</v>
@@ -25113,7 +25125,7 @@
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" s="34" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="B893" s="41">
         <v>79207020082</v>
@@ -25135,7 +25147,7 @@
     </row>
     <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" s="34" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="B894" s="41">
         <v>79185072237</v>
@@ -25153,7 +25165,7 @@
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" s="34" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="B895" s="41">
         <v>79182762440</v>
@@ -25169,7 +25181,7 @@
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" s="34" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="B896" s="41">
         <v>79518702052</v>
@@ -25185,7 +25197,7 @@
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" s="34" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="B897" s="41">
         <v>79885456732</v>
@@ -25201,7 +25213,7 @@
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" s="34" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="B898" s="41">
         <v>79186323631</v>
@@ -25239,7 +25251,7 @@
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" s="34" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="B900" s="41">
         <v>79604946540</v>
@@ -25259,7 +25271,7 @@
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" s="34" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="B901" s="41">
         <v>79787713176</v>
@@ -25303,7 +25315,7 @@
     </row>
     <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" s="34" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="B903" s="41">
         <v>79881380533</v>
@@ -25319,7 +25331,7 @@
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" s="34" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="B904" s="41">
         <v>79876571770</v>
@@ -25341,7 +25353,7 @@
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" s="34" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="B905" s="41">
         <v>79185269969</v>
@@ -25363,7 +25375,7 @@
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" s="34" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="B906" s="41">
         <v>79788069407</v>
@@ -25385,7 +25397,7 @@
     </row>
     <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" s="34" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="B907" s="41">
         <v>79809148895</v>
@@ -25407,7 +25419,7 @@
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" s="34" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="B908" s="41">
         <v>79374600054</v>
@@ -25445,7 +25457,7 @@
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" s="34" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="B910" s="41">
         <v>79063480196</v>
@@ -25463,7 +25475,7 @@
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" s="34" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="B911" s="41">
         <v>79035002052</v>
@@ -25483,7 +25495,7 @@
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" s="34" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="B912" s="41">
         <v>79883667602</v>
@@ -25503,7 +25515,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A913" s="34" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="B913" s="41">
         <v>79991733748</v>
@@ -25519,7 +25531,7 @@
     </row>
     <row r="914" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A914" s="34" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="B914" s="41">
         <v>79168542102</v>
@@ -25539,7 +25551,7 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A915" s="34" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="B915" s="41">
         <v>79888928388</v>
@@ -25559,7 +25571,7 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A916" s="34" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="B916" s="41">
         <v>79032374317</v>
@@ -25601,7 +25613,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A918" s="34" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="B918" s="41">
         <v>79207020082</v>
@@ -25624,7 +25636,7 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A919" s="34" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="B919" s="41">
         <v>79041183867</v>
@@ -25645,7 +25657,7 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A920" s="34" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="B920" s="41">
         <v>79032978483</v>
@@ -25666,7 +25678,7 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A921" s="34" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="B921" s="41">
         <v>79308038836</v>
@@ -25689,7 +25701,7 @@
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A922" s="34" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="B922" s="41">
         <v>79385488845</v>
@@ -25712,7 +25724,7 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A923" s="34" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="B923" s="41">
         <v>79046838139</v>
@@ -25733,7 +25745,7 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A924" s="34" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="B924" s="41">
         <v>79128268207</v>
@@ -25756,7 +25768,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A925" s="34" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="B925" s="41">
         <v>79148261215</v>
@@ -25779,7 +25791,7 @@
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A926" s="34" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="B926" s="41">
         <v>79267823227</v>
@@ -25800,7 +25812,7 @@
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A927" s="34" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="B927" s="41">
         <v>79184915237</v>
@@ -25825,7 +25837,7 @@
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A928" s="34" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="B928" s="41">
         <v>79034390003</v>
@@ -25872,7 +25884,7 @@
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" s="34" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="B930" s="41">
         <v>79595062068</v>
@@ -25928,7 +25940,7 @@
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" s="34" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="B933" s="41">
         <v>79180664535</v>
@@ -25946,7 +25958,7 @@
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" s="34" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="B934" s="41">
         <v>79197382450</v>
@@ -25966,7 +25978,7 @@
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" s="34" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="B935" s="41">
         <v>79885220528</v>
@@ -25988,7 +26000,7 @@
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" s="34" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="B936" s="41">
         <v>79885093331</v>
@@ -26032,7 +26044,7 @@
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" s="34" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="B938" s="41">
         <v>79184400178</v>
@@ -26054,7 +26066,7 @@
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" s="34" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="B939" s="41">
         <v>79183270587</v>
@@ -26072,7 +26084,7 @@
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" s="34" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="B940" s="41">
         <v>79183889940</v>
@@ -26090,7 +26102,7 @@
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" s="34" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="B941" s="41">
         <v>79994722206</v>
@@ -26106,7 +26118,7 @@
     </row>
     <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" s="34" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="B942" s="41">
         <v>79184165266</v>
@@ -26146,7 +26158,7 @@
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" s="34" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="B944" s="41">
         <v>79160231803</v>
@@ -26164,7 +26176,7 @@
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" s="34" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="B945" s="41">
         <v>79251587458</v>
@@ -26182,7 +26194,7 @@
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" s="34" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="B946" s="41">
         <v>79385519412</v>
@@ -26288,7 +26300,7 @@
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" s="34" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="B952" s="35">
         <v>79895106888</v>
@@ -26304,7 +26316,7 @@
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" s="34" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="B953" s="35">
         <v>79189487859</v>
@@ -26322,7 +26334,7 @@
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" s="34" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="B954" s="35">
         <v>79094690279</v>
@@ -26342,7 +26354,7 @@
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" s="34" t="s">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="B955" s="35">
         <v>79270465755</v>
@@ -26362,7 +26374,7 @@
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" s="34" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="B956" s="35">
         <v>79181514761</v>
@@ -26394,7 +26406,7 @@
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" s="34" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="B958" s="35">
         <v>79286120337</v>
@@ -26414,7 +26426,7 @@
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" s="34" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="B959" s="35">
         <v>79181603172</v>
@@ -26432,7 +26444,7 @@
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" s="34" t="s">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="B960" s="35">
         <v>79528474569</v>
@@ -26450,7 +26462,7 @@
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" s="34" t="s">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="B961" s="35">
         <v>79891443888</v>
@@ -26478,7 +26490,7 @@
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" s="34" t="s">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="B963" s="35">
         <v>79186956626</v>
@@ -26494,7 +26506,7 @@
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" s="34" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="B964" s="35">
         <v>79183433464</v>
@@ -26512,7 +26524,7 @@
     </row>
     <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" s="34" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B965" s="35">
         <v>79094646000</v>
@@ -26528,7 +26540,7 @@
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" s="34" t="s">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="B966" s="35">
         <v>79854264076</v>
@@ -26544,7 +26556,7 @@
     </row>
     <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" s="34" t="s">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="B967" s="35">
         <v>79186525585</v>
@@ -26560,7 +26572,7 @@
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" s="34" t="s">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="B968" s="35">
         <v>79528581269</v>
@@ -26580,7 +26592,7 @@
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" s="34" t="s">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="B969" s="35">
         <v>79673053030</v>
@@ -26610,7 +26622,7 @@
     </row>
     <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" s="34" t="s">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="B971" s="35">
         <v>79886696618</v>
@@ -26760,7 +26772,7 @@
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" s="34" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="B978" s="35">
         <v>79117974075</v>
@@ -26778,7 +26790,7 @@
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" s="34" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="B979" s="35">
         <v>79615951401</v>
@@ -26796,7 +26808,7 @@
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" s="34" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="B980" s="35">
         <v>79274773218</v>
@@ -26814,7 +26826,7 @@
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" s="34" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="B981" s="35">
         <v>79673005052</v>
@@ -26832,7 +26844,7 @@
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" s="34" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="B982" s="35">
         <v>79625245851</v>
@@ -26850,7 +26862,7 @@
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" s="34" t="s">
-        <v>2665</v>
+        <v>2666</v>
       </c>
       <c r="B983" s="35">
         <v>79898052605</v>
@@ -26868,7 +26880,7 @@
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" s="34" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="B984" s="35">
         <v>79992365729</v>
@@ -26910,7 +26922,7 @@
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" s="34" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="B986" s="41">
         <v>79182119543</v>
@@ -26926,7 +26938,7 @@
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" s="34" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="B987" s="41">
         <v>79886039199</v>
@@ -26946,7 +26958,7 @@
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" s="34" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="B988" s="41">
         <v>79182846179</v>
@@ -26964,7 +26976,7 @@
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" s="34" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="B989" s="41">
         <v>79185545589</v>
@@ -26982,7 +26994,7 @@
     </row>
     <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" s="34" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="B990" s="41">
         <v>79637505138</v>
@@ -26998,7 +27010,7 @@
     </row>
     <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" s="34" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="B991" s="41">
         <v>79604757152</v>
@@ -27016,7 +27028,7 @@
     </row>
     <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" s="34" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="B992" s="41">
         <v>79182762782</v>
@@ -27058,7 +27070,7 @@
     </row>
     <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" s="34" t="s">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="B994" s="41">
         <v>79892941007</v>
@@ -27074,7 +27086,7 @@
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" s="34" t="s">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="B995" s="41">
         <v>79060896267</v>
@@ -27094,7 +27106,7 @@
     </row>
     <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" s="34" t="s">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="B996" s="41">
         <v>79384227276</v>
@@ -27134,7 +27146,7 @@
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" s="34" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="B998" s="41">
         <v>79614238176</v>
@@ -27162,7 +27174,7 @@
     </row>
     <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" s="34" t="s">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="B1000" s="41">
         <v>79280121007</v>
@@ -27190,7 +27202,7 @@
     </row>
     <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" s="34" t="s">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="B1002" s="41">
         <v>79180985165</v>
@@ -27206,7 +27218,7 @@
     </row>
     <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" s="34" t="s">
-        <v>2680</v>
+        <v>2681</v>
       </c>
       <c r="B1003" s="41">
         <v>79186200028</v>
@@ -27222,7 +27234,7 @@
     </row>
     <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" s="34" t="s">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="B1004" s="41">
         <v>79190278727</v>
@@ -27250,7 +27262,7 @@
     </row>
     <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" s="34" t="s">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="B1006" s="41">
         <v>79615280373</v>
@@ -27266,7 +27278,7 @@
     </row>
     <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1007" s="34" t="s">
-        <v>2683</v>
+        <v>2684</v>
       </c>
       <c r="B1007" s="41">
         <v>79622028701</v>
@@ -27282,7 +27294,7 @@
     </row>
     <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1008" s="34" t="s">
-        <v>2684</v>
+        <v>2685</v>
       </c>
       <c r="B1008" s="41">
         <v>79185055723</v>
@@ -27298,7 +27310,7 @@
     </row>
     <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" s="34" t="s">
-        <v>2685</v>
+        <v>2686</v>
       </c>
       <c r="B1009" s="41">
         <v>79788139855</v>
@@ -27326,7 +27338,7 @@
     </row>
     <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" s="34" t="s">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="B1011" s="41">
         <v>79189749194</v>
@@ -27344,7 +27356,7 @@
     </row>
     <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" s="34" t="s">
-        <v>2687</v>
+        <v>2688</v>
       </c>
       <c r="B1012" s="41">
         <v>79184801108</v>
@@ -27362,7 +27374,7 @@
     </row>
     <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" s="34" t="s">
-        <v>2688</v>
+        <v>2689</v>
       </c>
       <c r="B1013" s="41">
         <v>79646847710</v>
@@ -27378,7 +27390,7 @@
     </row>
     <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" s="34" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="B1014" s="41">
         <v>79649041350</v>
@@ -27406,7 +27418,7 @@
     </row>
     <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" s="34" t="s">
-        <v>2690</v>
+        <v>2691</v>
       </c>
       <c r="B1016" s="33">
         <v>79181537666</v>
@@ -27422,7 +27434,7 @@
     </row>
     <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" s="34" t="s">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="B1017" s="33">
         <v>79051511564</v>
@@ -27438,7 +27450,7 @@
     </row>
     <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" s="34" t="s">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="B1018" s="33">
         <v>79254155954</v>
@@ -27454,7 +27466,7 @@
     </row>
     <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" s="34" t="s">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="B1019" s="33">
         <v>79626803581</v>
@@ -27482,7 +27494,7 @@
     </row>
     <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" s="34" t="s">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="B1021" s="33">
         <v>79281059268</v>
@@ -27498,7 +27510,7 @@
     </row>
     <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" s="34" t="s">
-        <v>2695</v>
+        <v>2696</v>
       </c>
       <c r="B1022" s="33">
         <v>79183388668</v>
@@ -27516,7 +27528,7 @@
     </row>
     <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" s="34" t="s">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="B1023" s="33">
         <v>79067249922</v>
@@ -27544,7 +27556,7 @@
     </row>
     <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1025" s="34" t="s">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="B1025" s="33">
         <v>79052993315</v>
@@ -27562,7 +27574,7 @@
     </row>
     <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1026" s="34" t="s">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="B1026" s="33">
         <v>79043499977</v>
@@ -27592,7 +27604,7 @@
     </row>
     <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1028" s="34" t="s">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="B1028" s="33">
         <v>79052875113</v>
@@ -27608,7 +27620,7 @@
     </row>
     <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1029" s="34" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="B1029" s="33">
         <v>79061820166</v>
@@ -27624,7 +27636,7 @@
     </row>
     <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1030" s="34" t="s">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="B1030" s="33">
         <v>79189333736</v>
@@ -27640,7 +27652,7 @@
     </row>
     <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1031" s="34" t="s">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="B1031" s="33">
         <v>79064327871</v>
@@ -27656,7 +27668,7 @@
     </row>
     <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1032" s="34" t="s">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="B1032" s="33">
         <v>79102891788</v>
@@ -27684,13 +27696,13 @@
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1034" s="34" t="s">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="B1034" s="33">
         <v>79183561661</v>
       </c>
       <c r="C1034" s="33" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="D1034" s="33" t="s">
         <v>2207</v>
@@ -27702,7 +27714,7 @@
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1035" s="34" t="s">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="B1035" s="33">
         <v>79537206758</v>
@@ -28376,13 +28388,13 @@
         <v>79615215290</v>
       </c>
       <c r="C1075" s="3" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="D1075" s="3" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="E1075" s="3" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="F1075" s="3" t="s">
         <v>1857</v>
@@ -29344,13 +29356,13 @@
         <v>79284697777</v>
       </c>
       <c r="C1132" s="18" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="D1132" s="18" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="E1132" s="18" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="F1132" s="18" t="s">
         <v>1911</v>
@@ -29367,7 +29379,7 @@
       </c>
       <c r="C1133" s="18"/>
       <c r="D1133" s="18" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="E1133" s="18"/>
       <c r="F1133" s="18"/>
@@ -29394,10 +29406,10 @@
         <v>79001236569</v>
       </c>
       <c r="C1135" s="18" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D1135" s="18" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="E1135" s="18"/>
       <c r="F1135" s="18"/>
@@ -29412,13 +29424,13 @@
         <v>79991005104</v>
       </c>
       <c r="C1136" s="18" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D1136" s="18" t="s">
+        <v>2716</v>
+      </c>
+      <c r="E1136" s="18" t="s">
         <v>2717</v>
-      </c>
-      <c r="D1136" s="18" t="s">
-        <v>2715</v>
-      </c>
-      <c r="E1136" s="18" t="s">
-        <v>2716</v>
       </c>
       <c r="F1136" s="18" t="s">
         <v>1912</v>
@@ -29434,10 +29446,10 @@
         <v>79371249966</v>
       </c>
       <c r="C1137" s="18" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D1137" s="18" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="E1137" s="18"/>
       <c r="F1137" s="18"/>
@@ -29452,7 +29464,7 @@
         <v>79185805028</v>
       </c>
       <c r="C1138" s="18" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D1138" s="18"/>
       <c r="E1138" s="18"/>
@@ -29480,10 +29492,10 @@
         <v>79687042488</v>
       </c>
       <c r="C1140" s="18" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="D1140" s="18" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="E1140" s="18"/>
       <c r="F1140" s="18"/>
@@ -29564,7 +29576,7 @@
         <v>79110886608</v>
       </c>
       <c r="C1145" s="18" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="D1145" s="18"/>
       <c r="E1145" s="18"/>
@@ -29581,7 +29593,7 @@
       </c>
       <c r="C1146" s="18"/>
       <c r="D1146" s="18" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E1146" s="18"/>
       <c r="F1146" s="18"/>
@@ -29596,10 +29608,10 @@
         <v>79185416500</v>
       </c>
       <c r="C1147" s="18" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="D1147" s="18" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="E1147" s="18"/>
       <c r="F1147" s="18"/>
@@ -29614,10 +29626,10 @@
         <v>79883514535</v>
       </c>
       <c r="C1148" s="18" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="D1148" s="18" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="E1148" s="18"/>
       <c r="F1148" s="18"/>
@@ -29632,10 +29644,10 @@
         <v>79181927858</v>
       </c>
       <c r="C1149" s="18" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="D1149" s="18" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="E1149" s="18"/>
       <c r="F1149" s="18"/>
@@ -29650,7 +29662,7 @@
         <v>79034731171</v>
       </c>
       <c r="C1150" s="18" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="D1150" s="18"/>
       <c r="E1150" s="18"/>
@@ -29678,7 +29690,7 @@
         <v>79518399099</v>
       </c>
       <c r="C1152" s="18" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D1152" s="18"/>
       <c r="E1152" s="18"/>
@@ -29696,7 +29708,7 @@
       <c r="C1153" s="18"/>
       <c r="D1153" s="18"/>
       <c r="E1153" s="18" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="F1153" s="18" t="s">
         <v>2020</v>
@@ -29714,7 +29726,7 @@
       <c r="C1154" s="18"/>
       <c r="D1154" s="18"/>
       <c r="E1154" s="18" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="F1154" s="18" t="s">
         <v>2021</v>
@@ -29730,7 +29742,7 @@
         <v>79493272312</v>
       </c>
       <c r="C1155" s="18" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D1155" s="18"/>
       <c r="E1155" s="18"/>
@@ -29746,7 +29758,7 @@
         <v>79184455113</v>
       </c>
       <c r="C1156" s="18" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="D1156" s="18"/>
       <c r="E1156" s="18"/>
@@ -29762,7 +29774,7 @@
         <v>79494697622</v>
       </c>
       <c r="C1157" s="18" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D1157" s="18"/>
       <c r="E1157" s="18"/>
@@ -29778,7 +29790,7 @@
         <v>79288803878</v>
       </c>
       <c r="C1158" s="18" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D1158" s="18"/>
       <c r="E1158" s="18"/>
@@ -29794,10 +29806,10 @@
         <v>79284223859</v>
       </c>
       <c r="C1159" s="18" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D1159" s="3" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="E1159" s="18"/>
       <c r="F1159" s="18"/>
@@ -29824,13 +29836,13 @@
         <v>79189338233</v>
       </c>
       <c r="C1161" s="18" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="D1161" s="18" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="E1161" s="18" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="F1161" s="18" t="s">
         <v>2022</v>
@@ -29879,7 +29891,7 @@
       </c>
       <c r="C1164" s="3"/>
       <c r="D1164" s="3" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="E1164" s="3"/>
       <c r="F1164" s="3"/>
@@ -29895,7 +29907,7 @@
       </c>
       <c r="C1165" s="3"/>
       <c r="D1165" s="3" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="E1165" s="3"/>
       <c r="F1165" s="3"/>
@@ -29911,7 +29923,7 @@
       </c>
       <c r="C1166" s="3"/>
       <c r="D1166" s="3" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="E1166" s="3"/>
       <c r="F1166" s="3"/>
@@ -29938,7 +29950,7 @@
         <v>79622153493</v>
       </c>
       <c r="C1168" s="3" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="D1168" s="3"/>
       <c r="E1168" s="3"/>
@@ -29954,10 +29966,10 @@
         <v>79266122721</v>
       </c>
       <c r="C1169" s="3" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="D1169" s="3" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="E1169" s="3"/>
       <c r="F1169" s="3"/>
@@ -29973,7 +29985,7 @@
       </c>
       <c r="C1170" s="3"/>
       <c r="D1170" s="3" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="E1170" s="3"/>
       <c r="F1170" s="3"/>
@@ -29988,7 +30000,7 @@
         <v>79813022825</v>
       </c>
       <c r="C1171" s="3" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="D1171" s="3"/>
       <c r="E1171" s="3"/>
@@ -30016,13 +30028,13 @@
         <v>79892367996</v>
       </c>
       <c r="C1173" s="3" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="D1173" s="3" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="E1173" s="3" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="F1173" s="3" t="s">
         <v>2034</v>
@@ -30038,13 +30050,13 @@
         <v>79182617888</v>
       </c>
       <c r="C1174" s="3" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="D1174" s="3" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="E1174" s="3" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="F1174" s="3" t="s">
         <v>2034</v>
@@ -30073,7 +30085,7 @@
       </c>
       <c r="C1176" s="3"/>
       <c r="D1176" s="3" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="E1176" s="3"/>
       <c r="F1176" s="3"/>
@@ -30089,7 +30101,7 @@
       </c>
       <c r="C1177" s="3"/>
       <c r="D1177" s="3" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="E1177" s="3"/>
       <c r="F1177" s="3"/>
@@ -30105,7 +30117,7 @@
       </c>
       <c r="C1178" s="3"/>
       <c r="D1178" s="3" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="E1178" s="3"/>
       <c r="F1178" s="3"/>
@@ -30121,7 +30133,7 @@
       </c>
       <c r="C1179" s="3"/>
       <c r="D1179" s="3" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="E1179" s="3"/>
       <c r="F1179" s="3"/>
@@ -30138,7 +30150,7 @@
       <c r="C1180" s="3"/>
       <c r="D1180" s="3"/>
       <c r="E1180" s="3" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="F1180" s="3" t="s">
         <v>2060</v>
@@ -30166,7 +30178,7 @@
         <v>79081882253</v>
       </c>
       <c r="C1182" s="3" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="D1182" s="3"/>
       <c r="E1182" s="3"/>
@@ -30182,7 +30194,7 @@
         <v>79184570319</v>
       </c>
       <c r="C1183" s="3" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="D1183" s="3"/>
       <c r="E1183" s="3"/>
@@ -30210,7 +30222,7 @@
         <v>79884600699</v>
       </c>
       <c r="C1185" s="3" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="D1185" s="3"/>
       <c r="E1185" s="3"/>
@@ -30226,7 +30238,7 @@
         <v>79615933002</v>
       </c>
       <c r="C1186" s="3" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="D1186" s="3"/>
       <c r="E1186" s="3"/>
@@ -30242,7 +30254,7 @@
         <v>79287615615</v>
       </c>
       <c r="C1187" s="3" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="D1187" s="3"/>
       <c r="E1187" s="3"/>
@@ -30271,10 +30283,10 @@
       </c>
       <c r="C1189" s="3"/>
       <c r="D1189" s="3" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="E1189" s="3" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="F1189" s="3" t="s">
         <v>2070</v>
@@ -30304,7 +30316,7 @@
       <c r="C1191" s="3"/>
       <c r="D1191" s="3"/>
       <c r="E1191" s="3" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="F1191" s="3" t="s">
         <v>2071</v>
@@ -30322,7 +30334,7 @@
       <c r="C1192" s="3"/>
       <c r="D1192" s="3"/>
       <c r="E1192" s="3" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="F1192" s="3" t="s">
         <v>2072</v>
@@ -30372,7 +30384,7 @@
       <c r="C1195" s="3"/>
       <c r="D1195" s="3"/>
       <c r="E1195" s="3" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="F1195" s="3"/>
       <c r="G1195" s="3"/>
@@ -30388,7 +30400,7 @@
       <c r="C1196" s="3"/>
       <c r="D1196" s="3"/>
       <c r="E1196" s="3" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="F1196" s="3"/>
       <c r="G1196" s="3"/>
@@ -30415,7 +30427,7 @@
       </c>
       <c r="C1198" s="3"/>
       <c r="D1198" s="3" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="E1198" s="3"/>
       <c r="F1198" s="3"/>
@@ -30430,11 +30442,11 @@
         <v>79374645805</v>
       </c>
       <c r="C1199" s="3" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="D1199" s="3"/>
       <c r="E1199" s="3" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="F1199" s="3" t="s">
         <v>2080</v>
@@ -30452,7 +30464,7 @@
       <c r="C1200" s="3"/>
       <c r="D1200" s="3"/>
       <c r="E1200" s="3" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="F1200" s="3" t="s">
         <v>2080</v>
@@ -30482,7 +30494,7 @@
       <c r="C1202" s="3"/>
       <c r="D1202" s="3"/>
       <c r="E1202" s="3" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="F1202" s="3" t="s">
         <v>2161</v>
@@ -30498,10 +30510,10 @@
         <v>79085129986</v>
       </c>
       <c r="C1203" s="3" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="D1203" s="3" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="E1203" s="3"/>
       <c r="F1203" s="3"/>
@@ -30529,7 +30541,7 @@
       </c>
       <c r="C1205" s="3"/>
       <c r="D1205" s="3" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="E1205" s="3"/>
       <c r="F1205" s="3"/>
@@ -30544,7 +30556,7 @@
         <v>79185010806</v>
       </c>
       <c r="C1206" s="3" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="D1206" s="3"/>
       <c r="E1206" s="3"/>
@@ -30560,7 +30572,7 @@
         <v>79183185307</v>
       </c>
       <c r="C1207" s="3" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="D1207" s="3"/>
       <c r="E1207" s="3"/>
@@ -30588,7 +30600,7 @@
         <v>79266566385</v>
       </c>
       <c r="C1209" s="3" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="D1209" s="3"/>
       <c r="E1209" s="3"/>
@@ -30638,7 +30650,7 @@
       <c r="C1212" s="3"/>
       <c r="D1212" s="3"/>
       <c r="E1212" s="3" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="F1212" s="3" t="s">
         <v>2204</v>
@@ -30656,7 +30668,7 @@
       <c r="C1213" s="3"/>
       <c r="D1213" s="3"/>
       <c r="E1213" s="3" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="F1213" s="3" t="s">
         <v>2205</v>
@@ -30673,7 +30685,7 @@
       </c>
       <c r="C1214" s="3"/>
       <c r="D1214" s="3" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="E1214" s="3"/>
       <c r="F1214" s="3"/>
@@ -30722,7 +30734,7 @@
       <c r="C1217" s="3"/>
       <c r="D1217" s="3"/>
       <c r="E1217" s="3" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="F1217" s="3" t="s">
         <v>2214</v>
@@ -30752,7 +30764,7 @@
       <c r="C1219" s="3"/>
       <c r="D1219" s="3"/>
       <c r="E1219" s="3" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="F1219" s="3" t="s">
         <v>2215</v>
@@ -30768,10 +30780,10 @@
         <v>79883151515</v>
       </c>
       <c r="C1220" s="3" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
       <c r="D1220" s="3" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="E1220" s="3"/>
       <c r="F1220" s="3"/>
@@ -30850,7 +30862,7 @@
         <v>79034547400</v>
       </c>
       <c r="C1225" s="3" t="s">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="D1225" s="3"/>
       <c r="E1225" s="3"/>
@@ -30866,7 +30878,7 @@
         <v>79287721255</v>
       </c>
       <c r="C1226" s="3" t="s">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="D1226" s="3"/>
       <c r="E1226" s="3"/>
@@ -30914,10 +30926,10 @@
         <v>79183615308</v>
       </c>
       <c r="C1229" s="3" t="s">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="D1229" s="3" t="s">
-        <v>2729</v>
+        <v>2730</v>
       </c>
       <c r="E1229" s="3"/>
       <c r="F1229" s="3"/>
@@ -30932,13 +30944,13 @@
         <v>79186212666</v>
       </c>
       <c r="C1230" s="3" t="s">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="D1230" s="3" t="s">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="E1230" s="3" t="s">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="F1230" s="3" t="s">
         <v>2312</v>
@@ -30955,7 +30967,7 @@
       </c>
       <c r="C1231" s="3"/>
       <c r="D1231" s="3" t="s">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="E1231" s="3"/>
       <c r="F1231" s="3"/>
@@ -30972,7 +30984,7 @@
       <c r="C1232" s="3"/>
       <c r="D1232" s="3"/>
       <c r="E1232" s="3" t="s">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="F1232" s="3" t="s">
         <v>2313</v>
@@ -30988,7 +31000,7 @@
         <v>79384126478</v>
       </c>
       <c r="C1233" s="3" t="s">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="D1233" s="3"/>
       <c r="E1233" s="3"/>
@@ -31016,13 +31028,13 @@
         <v>79184673083</v>
       </c>
       <c r="C1235" s="3" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="D1235" s="3" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="E1235" s="3" t="s">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="F1235" s="3" t="s">
         <v>2315</v>
@@ -31038,12 +31050,14 @@
         <v>79184987541</v>
       </c>
       <c r="C1236" s="3" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="D1236" s="3" t="s">
-        <v>2725</v>
-      </c>
-      <c r="E1236" s="3"/>
+        <v>2726</v>
+      </c>
+      <c r="E1236" s="3" t="s">
+        <v>2386</v>
+      </c>
       <c r="F1236" s="3"/>
       <c r="G1236" s="3"/>
       <c r="H1236" s="3"/>
@@ -31057,10 +31071,10 @@
       </c>
       <c r="C1237" s="3"/>
       <c r="D1237" s="3" t="s">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="E1237" s="3" t="s">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="F1237" s="3" t="s">
         <v>2314</v>
@@ -31076,7 +31090,7 @@
         <v>79180458777</v>
       </c>
       <c r="C1238" s="3" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="D1238" s="3"/>
       <c r="E1238" s="3"/>
@@ -31104,10 +31118,10 @@
         <v>79183291413</v>
       </c>
       <c r="C1240" s="3" t="s">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="D1240" s="3" t="s">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="E1240" s="3"/>
       <c r="F1240" s="3"/>
@@ -31124,7 +31138,7 @@
       <c r="C1241" s="3"/>
       <c r="D1241" s="3"/>
       <c r="E1241" s="3" t="s">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="F1241" s="3" t="s">
         <v>2316</v>
@@ -31141,7 +31155,7 @@
       </c>
       <c r="C1242" s="3"/>
       <c r="D1242" s="3" t="s">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="E1242" s="3"/>
       <c r="F1242" s="3"/>
@@ -31155,7 +31169,7 @@
       <c r="B1243" s="18"/>
       <c r="C1243" s="3"/>
       <c r="D1243" s="3" t="s">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="E1243" s="3"/>
       <c r="F1243" s="3"/>
@@ -31225,7 +31239,7 @@
         <v>2338</v>
       </c>
       <c r="F1247" s="2" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="G1247" s="2"/>
       <c r="H1247" s="2"/>
@@ -31538,7 +31552,7 @@
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1267" s="40" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="B1267" s="17"/>
       <c r="C1267" s="2"/>
@@ -31550,36 +31564,36 @@
     </row>
     <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1268" s="7" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="B1268" s="17">
         <v>79181206771</v>
       </c>
       <c r="C1268" s="2" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="D1268" s="2" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="E1268" s="2" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="F1268" s="2" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G1268" s="2"/>
       <c r="H1268" s="2"/>
     </row>
     <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1269" s="7" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="B1269" s="17">
         <v>79286136662</v>
       </c>
       <c r="C1269" s="2"/>
       <c r="D1269" s="2" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="E1269" s="2"/>
       <c r="F1269" s="2"/>
@@ -31588,7 +31602,7 @@
     </row>
     <row r="1270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1270" s="40" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="B1270" s="17"/>
       <c r="C1270" s="2"/>
@@ -31600,14 +31614,14 @@
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1271" s="7" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="B1271" s="17">
         <v>375297856891</v>
       </c>
       <c r="C1271" s="2"/>
       <c r="D1271" s="2" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="E1271" s="2"/>
       <c r="F1271" s="2"/>
@@ -31616,16 +31630,16 @@
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1272" s="7" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="B1272" s="17">
         <v>79787715371</v>
       </c>
       <c r="C1272" s="2" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="D1272" s="2" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="E1272" s="2"/>
       <c r="F1272" s="2"/>
@@ -31634,14 +31648,14 @@
     </row>
     <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1273" s="7" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="B1273" s="17">
         <v>79189218545</v>
       </c>
       <c r="C1273" s="2"/>
       <c r="D1273" s="2" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="E1273" s="2"/>
       <c r="F1273" s="2"/>
@@ -31650,7 +31664,7 @@
     </row>
     <row r="1274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1274" s="40" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="B1274" s="17"/>
       <c r="C1274" s="2"/>
@@ -31662,16 +31676,16 @@
     </row>
     <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1275" s="7" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="B1275" s="17">
         <v>79883302117</v>
       </c>
       <c r="C1275" s="2" t="s">
+        <v>2467</v>
+      </c>
+      <c r="D1275" s="2" t="s">
         <v>2466</v>
-      </c>
-      <c r="D1275" s="2" t="s">
-        <v>2465</v>
       </c>
       <c r="E1275" s="2"/>
       <c r="F1275" s="2"/>
@@ -31680,13 +31694,13 @@
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1276" s="7" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="B1276" s="17">
         <v>79885414599</v>
       </c>
       <c r="C1276" s="2" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="D1276" s="2"/>
       <c r="E1276" s="2"/>
@@ -31696,7 +31710,7 @@
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1277" s="7" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="B1277" s="17">
         <v>79606987172</v>
@@ -31704,17 +31718,17 @@
       <c r="C1277" s="2"/>
       <c r="D1277" s="2"/>
       <c r="E1277" s="2" t="s">
+        <v>2461</v>
+      </c>
+      <c r="F1277" s="2" t="s">
         <v>2460</v>
-      </c>
-      <c r="F1277" s="2" t="s">
-        <v>2459</v>
       </c>
       <c r="G1277" s="2"/>
       <c r="H1277" s="2"/>
     </row>
     <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1278" s="40" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="B1278" s="17"/>
       <c r="C1278" s="2"/>
@@ -31726,13 +31740,13 @@
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1279" s="7" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="B1279" s="17">
         <v>79002702201</v>
       </c>
       <c r="C1279" s="2" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="D1279" s="2"/>
       <c r="E1279" s="2"/>
@@ -31760,7 +31774,7 @@
     </row>
     <row r="1281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1281" s="40" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="B1281" s="17"/>
       <c r="C1281" s="2"/>
@@ -31772,13 +31786,13 @@
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1282" s="7" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="B1282" s="17">
         <v>79036910787</v>
       </c>
       <c r="C1282" s="2" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="D1282" s="2"/>
       <c r="E1282" s="2"/>
@@ -31788,58 +31802,58 @@
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1283" s="7" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="B1283" s="17">
         <v>79085097827</v>
       </c>
       <c r="C1283" s="2" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="D1283" s="2" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="E1283" s="2" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="F1283" s="2" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="G1283" s="2"/>
       <c r="H1283" s="2"/>
     </row>
     <row r="1284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1284" s="7" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="B1284" s="17">
         <v>79786456031</v>
       </c>
       <c r="C1284" s="2" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="D1284" s="2" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="E1284" s="2" t="s">
+        <v>2554</v>
+      </c>
+      <c r="F1284" s="2" t="s">
         <v>2553</v>
-      </c>
-      <c r="F1284" s="2" t="s">
-        <v>2552</v>
       </c>
       <c r="G1284" s="2"/>
       <c r="H1284" s="2"/>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1285" s="7" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="B1285" s="17">
         <v>79180492172</v>
       </c>
       <c r="C1285" s="2"/>
       <c r="D1285" s="2" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="E1285" s="2"/>
       <c r="F1285" s="2"/>
@@ -31848,7 +31862,7 @@
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1286" s="40" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="B1286" s="17"/>
       <c r="C1286" s="2"/>
@@ -31860,7 +31874,7 @@
     </row>
     <row r="1287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1287" s="7" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="B1287" s="17">
         <v>79530708343</v>
@@ -31868,26 +31882,26 @@
       <c r="C1287" s="2"/>
       <c r="D1287" s="2"/>
       <c r="E1287" s="2" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="F1287" s="2" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="G1287" s="2"/>
       <c r="H1287" s="2"/>
     </row>
     <row r="1288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1288" s="7" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="B1288" s="17">
         <v>79618588262</v>
       </c>
       <c r="C1288" s="2" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D1288" s="2" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="E1288" s="2"/>
       <c r="F1288" s="2"/>
@@ -31896,7 +31910,7 @@
     </row>
     <row r="1289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1289" s="7" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="B1289" s="17">
         <v>79990580869</v>
@@ -31904,17 +31918,17 @@
       <c r="C1289" s="2"/>
       <c r="D1289" s="2"/>
       <c r="E1289" s="2" t="s">
+        <v>2557</v>
+      </c>
+      <c r="F1289" s="2" t="s">
         <v>2556</v>
-      </c>
-      <c r="F1289" s="2" t="s">
-        <v>2555</v>
       </c>
       <c r="G1289" s="2"/>
       <c r="H1289" s="2"/>
     </row>
     <row r="1290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1290" s="7" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="B1290" s="17">
         <v>79283306686</v>
@@ -31922,23 +31936,23 @@
       <c r="C1290" s="2"/>
       <c r="D1290" s="2"/>
       <c r="E1290" s="2" t="s">
+        <v>2557</v>
+      </c>
+      <c r="F1290" s="2" t="s">
         <v>2556</v>
-      </c>
-      <c r="F1290" s="2" t="s">
-        <v>2555</v>
       </c>
       <c r="G1290" s="2"/>
       <c r="H1290" s="2"/>
     </row>
     <row r="1291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1291" s="7" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="B1291" s="17">
         <v>79184803174</v>
       </c>
       <c r="C1291" s="2" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D1291" s="2"/>
       <c r="E1291" s="2"/>
@@ -31948,13 +31962,13 @@
     </row>
     <row r="1292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1292" s="7" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="B1292" s="17">
         <v>79186825836</v>
       </c>
       <c r="C1292" s="2" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D1292" s="2"/>
       <c r="E1292" s="2"/>
@@ -31964,13 +31978,13 @@
     </row>
     <row r="1293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1293" s="7" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="B1293" s="17">
         <v>79182466940</v>
       </c>
       <c r="C1293" s="2" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D1293" s="2"/>
       <c r="E1293" s="2"/>
@@ -31980,7 +31994,7 @@
     </row>
     <row r="1294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1294" s="40" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="B1294" s="17"/>
       <c r="C1294" s="2"/>
@@ -31991,16 +32005,16 @@
     </row>
     <row r="1295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1295" s="7" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="B1295" s="17">
         <v>79149202703</v>
       </c>
       <c r="C1295" s="2" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="D1295" s="2" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="E1295" s="2"/>
       <c r="F1295" s="2"/>
@@ -32008,26 +32022,26 @@
     </row>
     <row r="1296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1296" s="7" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="B1296" s="17">
         <v>79885468941</v>
       </c>
       <c r="C1296" s="2" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="D1296" s="2"/>
       <c r="E1296" s="2" t="s">
+        <v>2559</v>
+      </c>
+      <c r="F1296" s="2" t="s">
         <v>2558</v>
-      </c>
-      <c r="F1296" s="2" t="s">
-        <v>2557</v>
       </c>
       <c r="G1296" s="2"/>
     </row>
     <row r="1297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1297" s="40" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="B1297" s="17"/>
       <c r="C1297" s="2"/>
@@ -32038,16 +32052,16 @@
     </row>
     <row r="1298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1298" s="7" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="B1298" s="17">
         <v>79806633494</v>
       </c>
       <c r="C1298" s="2" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="D1298" s="2" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="E1298" s="2"/>
       <c r="F1298" s="2"/>
@@ -32072,7 +32086,7 @@
     </row>
     <row r="1300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1300" s="40" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="B1300" s="17"/>
       <c r="C1300" s="2"/>
@@ -32083,13 +32097,13 @@
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1301" s="7" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="B1301" s="17">
         <v>79525837593</v>
       </c>
       <c r="C1301" s="2" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="D1301" s="2"/>
       <c r="E1301" s="2"/>
@@ -32098,16 +32112,16 @@
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1302" s="7" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="B1302" s="17">
         <v>79183870112</v>
       </c>
       <c r="C1302" s="2" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="D1302" s="2" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="E1302" s="2"/>
       <c r="F1302" s="2"/>
@@ -32115,14 +32129,14 @@
     </row>
     <row r="1303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1303" s="7" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="B1303" s="17">
         <v>79182842938</v>
       </c>
       <c r="C1303" s="2"/>
       <c r="D1303" s="2" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="E1303" s="2"/>
       <c r="F1303" s="2"/>
@@ -32130,7 +32144,7 @@
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1304" s="40" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="B1304" s="17"/>
       <c r="C1304" s="2"/>
@@ -32141,28 +32155,28 @@
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1305" s="7" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="B1305" s="17">
         <v>79183772137</v>
       </c>
       <c r="C1305" s="2" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="D1305" s="2" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="E1305" s="2" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="F1305" s="2" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="G1305" s="2"/>
     </row>
     <row r="1306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1306" s="7" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="B1306" s="17">
         <v>79897201133</v>
@@ -32170,23 +32184,23 @@
       <c r="C1306" s="2"/>
       <c r="D1306" s="2"/>
       <c r="E1306" s="2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F1306" s="2" t="s">
         <v>2579</v>
-      </c>
-      <c r="F1306" s="2" t="s">
-        <v>2578</v>
       </c>
       <c r="G1306" s="2"/>
     </row>
     <row r="1307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1307" s="7" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="B1307" s="17">
         <v>79615332857</v>
       </c>
       <c r="C1307" s="2"/>
       <c r="D1307" s="2" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="E1307" s="2"/>
       <c r="F1307" s="2"/>
@@ -32194,14 +32208,14 @@
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1308" s="7" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="B1308" s="17">
         <v>79184188755</v>
       </c>
       <c r="C1308" s="2"/>
       <c r="D1308" s="2" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="E1308" s="2"/>
       <c r="F1308" s="2"/>
@@ -32209,7 +32223,7 @@
     </row>
     <row r="1309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1309" s="40" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="B1309" s="17"/>
       <c r="C1309" s="2"/>
@@ -32220,14 +32234,14 @@
     </row>
     <row r="1310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1310" s="7" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="B1310" s="17">
         <v>79034550320</v>
       </c>
       <c r="C1310" s="2"/>
       <c r="D1310" s="2" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="E1310" s="2"/>
       <c r="F1310" s="2"/>
@@ -32235,13 +32249,13 @@
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1311" s="7" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="B1311" s="17">
         <v>79497336125</v>
       </c>
       <c r="C1311" s="2" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="D1311" s="2"/>
       <c r="E1311" s="2"/>
@@ -32250,14 +32264,14 @@
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1312" s="7" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="B1312" s="17">
         <v>79676739173</v>
       </c>
       <c r="C1312" s="2"/>
       <c r="D1312" s="2" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="E1312" s="2"/>
       <c r="F1312" s="2"/>
@@ -32282,7 +32296,7 @@
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1314" s="40" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="B1314" s="17"/>
       <c r="C1314" s="2"/>
@@ -32293,26 +32307,26 @@
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1315" s="7" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="B1315" s="17">
         <v>79183767815</v>
       </c>
       <c r="C1315" s="2"/>
       <c r="D1315" s="2" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="E1315" s="2" t="s">
+        <v>2605</v>
+      </c>
+      <c r="F1315" s="2" t="s">
         <v>2604</v>
-      </c>
-      <c r="F1315" s="2" t="s">
-        <v>2603</v>
       </c>
       <c r="G1315" s="2"/>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1316" s="40" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="C1316" s="2"/>
       <c r="D1316" s="2"/>
@@ -32322,13 +32336,13 @@
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1317" s="7" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="B1317" s="17">
         <v>79528700394</v>
       </c>
       <c r="C1317" s="2" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="D1317" s="2"/>
       <c r="E1317" s="2"/>
@@ -32337,13 +32351,13 @@
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1318" s="7" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="B1318" s="17">
         <v>79054305403</v>
       </c>
       <c r="C1318" s="2" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="D1318" s="2"/>
       <c r="E1318" s="2"/>
@@ -32352,14 +32366,14 @@
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1319" s="7" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="B1319" s="17">
         <v>79064046088</v>
       </c>
       <c r="C1319" s="2"/>
       <c r="D1319" s="2" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="E1319" s="2"/>
       <c r="F1319" s="2"/>
@@ -32367,16 +32381,16 @@
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1320" s="7" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="B1320" s="17">
         <v>79284483258</v>
       </c>
       <c r="C1320" s="2" t="s">
+        <v>2602</v>
+      </c>
+      <c r="D1320" s="2" t="s">
         <v>2601</v>
-      </c>
-      <c r="D1320" s="2" t="s">
-        <v>2600</v>
       </c>
       <c r="E1320" s="2"/>
       <c r="F1320" s="2"/>
@@ -32384,7 +32398,7 @@
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1321" s="40" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="B1321" s="17"/>
       <c r="C1321" s="2"/>
@@ -32395,13 +32409,13 @@
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1322" s="7" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="B1322">
         <v>79081817570</v>
       </c>
       <c r="C1322" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="D1322" s="2"/>
       <c r="E1322" s="2"/>
@@ -32410,23 +32424,23 @@
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1323" s="7" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="B1323">
         <v>79045033313</v>
       </c>
       <c r="D1323" s="2"/>
       <c r="E1323" s="2" t="s">
+        <v>2607</v>
+      </c>
+      <c r="F1323" s="2" t="s">
         <v>2606</v>
-      </c>
-      <c r="F1323" s="2" t="s">
-        <v>2605</v>
       </c>
       <c r="G1323" s="2"/>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1324" s="40" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="D1324" s="2"/>
       <c r="E1324" s="2"/>
@@ -32435,26 +32449,26 @@
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1325" s="7" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="B1325" s="17">
         <v>79186195666</v>
       </c>
       <c r="C1325" s="2" t="s">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="D1325" s="2"/>
       <c r="E1325" s="2" t="s">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="F1325" s="2" t="s">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="G1325" s="2"/>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1326" s="7" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="B1326" s="17">
         <v>79780648554</v>
@@ -32462,23 +32476,23 @@
       <c r="C1326" s="2"/>
       <c r="D1326" s="2"/>
       <c r="E1326" s="2" t="s">
+        <v>2715</v>
+      </c>
+      <c r="F1326" s="2" t="s">
         <v>2714</v>
-      </c>
-      <c r="F1326" s="2" t="s">
-        <v>2713</v>
       </c>
       <c r="G1326" s="2"/>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1327" s="7" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="B1327" s="17">
         <v>79493022752</v>
       </c>
       <c r="C1327" s="2"/>
       <c r="D1327" s="2" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="E1327" s="2"/>
       <c r="F1327" s="2"/>
@@ -32486,7 +32500,7 @@
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1328" s="40" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="B1328" s="17"/>
       <c r="C1328" s="2"/>
@@ -32497,7 +32511,7 @@
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1329" s="7" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="B1329" s="17">
         <v>79085033991</v>
@@ -32510,14 +32524,14 @@
     </row>
     <row r="1330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1330" s="7" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="B1330" s="17">
         <v>79282576368</v>
       </c>
       <c r="C1330" s="2"/>
       <c r="D1330" s="2" t="s">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="E1330" s="2"/>
       <c r="F1330" s="2"/>
@@ -32525,7 +32539,7 @@
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1331" s="40" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="B1331" s="17"/>
       <c r="C1331" s="2"/>
@@ -32536,13 +32550,13 @@
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1332" s="7" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="B1332" s="17">
         <v>79054871997</v>
       </c>
       <c r="C1332" s="2" t="s">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="D1332" s="2"/>
       <c r="E1332" s="2"/>
@@ -32551,14 +32565,14 @@
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1333" s="7" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="B1333" s="17">
         <v>79193683714</v>
       </c>
       <c r="C1333" s="2"/>
       <c r="D1333" s="2" t="s">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="E1333" s="2"/>
       <c r="F1333" s="2"/>
@@ -32566,14 +32580,14 @@
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1334" s="7" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="B1334" s="17">
         <v>79586493944</v>
       </c>
       <c r="C1334" s="2"/>
       <c r="D1334" s="2" t="s">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="E1334" s="2"/>
       <c r="F1334" s="2"/>
@@ -32581,13 +32595,13 @@
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1335" s="7" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="B1335" s="17">
         <v>79780045546</v>
       </c>
       <c r="C1335" s="2" t="s">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="D1335" s="2"/>
       <c r="E1335" s="2"/>
@@ -32613,7 +32627,7 @@
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1337" s="40" t="s">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="B1337" s="17"/>
       <c r="C1337" s="2"/>
@@ -32624,16 +32638,16 @@
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1338" s="7" t="s">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="B1338" s="17">
         <v>79782640332</v>
       </c>
       <c r="C1338" s="2" t="s">
-        <v>731</v>
+        <v>2740</v>
       </c>
       <c r="D1338" s="2" t="s">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="E1338" s="2"/>
       <c r="F1338" s="2"/>
@@ -32641,7 +32655,7 @@
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1339" s="40" t="s">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="B1339" s="17"/>
       <c r="C1339" s="2"/>
@@ -32652,16 +32666,16 @@
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1340" s="7" t="s">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="B1340" s="17">
         <v>79530977713</v>
       </c>
       <c r="C1340" s="2" t="s">
-        <v>731</v>
+        <v>2743</v>
       </c>
       <c r="D1340" s="2" t="s">
-        <v>2738</v>
+        <v>2742</v>
       </c>
       <c r="E1340" s="2"/>
       <c r="F1340" s="2"/>
@@ -32669,14 +32683,14 @@
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1341" s="7" t="s">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="B1341" s="17">
         <v>79896279922</v>
       </c>
       <c r="C1341" s="2"/>
       <c r="D1341" s="2" t="s">
-        <v>2739</v>
+        <v>2741</v>
       </c>
       <c r="E1341" s="2"/>
       <c r="F1341" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A67207-B7A2-44B7-9260-101E9FE3CB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3348389C-BDCC-4859-8E5D-8C7266D810DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4229" uniqueCount="2744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4231" uniqueCount="2746">
   <si>
     <t>Пароль</t>
   </si>
@@ -8266,6 +8266,12 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/yP04F8cfKjdgog</t>
+  </si>
+  <si>
+    <t>27871</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/JZKtKj8YWmY9ew</t>
   </si>
 </sst>
 </file>
@@ -32697,12 +32703,18 @@
       <c r="G1341" s="2"/>
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1342" s="7"/>
-      <c r="B1342" s="17"/>
-      <c r="C1342" s="2"/>
-      <c r="D1342" s="2"/>
-      <c r="E1342" s="2"/>
-      <c r="F1342" s="2"/>
+      <c r="A1342" s="34" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B1342" s="33">
+        <v>79064327871</v>
+      </c>
+      <c r="C1342" s="33"/>
+      <c r="D1342" s="33" t="s">
+        <v>2745</v>
+      </c>
+      <c r="E1342" s="33"/>
+      <c r="F1342" s="33"/>
       <c r="G1342" s="2"/>
     </row>
     <row r="1343" spans="1:7" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3348389C-BDCC-4859-8E5D-8C7266D810DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00FEE3C-8E65-4846-9FB2-3C8FCE56B29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4231" uniqueCount="2746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4232" uniqueCount="2746">
   <si>
     <t>Пароль</t>
   </si>
@@ -32480,7 +32480,9 @@
         <v>79780648554</v>
       </c>
       <c r="C1326" s="2"/>
-      <c r="D1326" s="2"/>
+      <c r="D1326" s="2" t="s">
+        <v>2708</v>
+      </c>
       <c r="E1326" s="2" t="s">
         <v>2715</v>
       </c>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00FEE3C-8E65-4846-9FB2-3C8FCE56B29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B6C516-E0F0-4E90-9FE5-FDAB67D43A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4232" uniqueCount="2746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4232" uniqueCount="2748">
   <si>
     <t>Пароль</t>
   </si>
@@ -8217,9 +8217,6 @@
     <t>!https://disk.yandex.ru/d/sHoLaZvUkEqXuQ</t>
   </si>
   <si>
-    <t>!https://disk.yandex.ru/d/HHtCpkrFNJWrZA</t>
-  </si>
-  <si>
     <t>!https://disk.yandex.ru/d/OX5LRriEzJsimA</t>
   </si>
   <si>
@@ -8272,6 +8269,15 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/JZKtKj8YWmY9ew</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/yYI0mYEzMQixBw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/HHtCpkrFNJWrZA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/jFZy7Zhe593nvw</t>
   </si>
 </sst>
 </file>
@@ -30935,7 +30941,7 @@
         <v>2720</v>
       </c>
       <c r="D1229" s="3" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="E1229" s="3"/>
       <c r="F1229" s="3"/>
@@ -30953,10 +30959,10 @@
         <v>2720</v>
       </c>
       <c r="D1230" s="3" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="E1230" s="3" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="F1230" s="3" t="s">
         <v>2312</v>
@@ -30973,7 +30979,7 @@
       </c>
       <c r="C1231" s="3"/>
       <c r="D1231" s="3" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="E1231" s="3"/>
       <c r="F1231" s="3"/>
@@ -30990,7 +30996,7 @@
       <c r="C1232" s="3"/>
       <c r="D1232" s="3"/>
       <c r="E1232" s="3" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="F1232" s="3" t="s">
         <v>2313</v>
@@ -31027,25 +31033,25 @@
       <c r="H1234" s="3"/>
     </row>
     <row r="1235" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1235" s="6" t="s">
+      <c r="A1235" s="8" t="s">
         <v>2306</v>
       </c>
-      <c r="B1235" s="3">
+      <c r="B1235" s="5">
         <v>79184673083</v>
       </c>
-      <c r="C1235" s="3" t="s">
-        <v>2721</v>
-      </c>
-      <c r="D1235" s="3" t="s">
-        <v>2727</v>
-      </c>
-      <c r="E1235" s="3" t="s">
-        <v>2732</v>
-      </c>
-      <c r="F1235" s="3" t="s">
+      <c r="C1235" s="5" t="s">
+        <v>2745</v>
+      </c>
+      <c r="D1235" s="5" t="s">
+        <v>2746</v>
+      </c>
+      <c r="E1235" s="5" t="s">
+        <v>2747</v>
+      </c>
+      <c r="F1235" s="5" t="s">
         <v>2315</v>
       </c>
-      <c r="G1235" s="3"/>
+      <c r="G1235" s="5"/>
       <c r="H1235" s="3"/>
     </row>
     <row r="1236" spans="1:8" x14ac:dyDescent="0.25">
@@ -31080,7 +31086,7 @@
         <v>2725</v>
       </c>
       <c r="E1237" s="3" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="F1237" s="3" t="s">
         <v>2314</v>
@@ -31095,7 +31101,7 @@
       <c r="B1238" s="3">
         <v>79180458777</v>
       </c>
-      <c r="C1238" s="3" t="s">
+      <c r="C1238" s="18" t="s">
         <v>2721</v>
       </c>
       <c r="D1238" s="3"/>
@@ -31144,7 +31150,7 @@
       <c r="C1241" s="3"/>
       <c r="D1241" s="3"/>
       <c r="E1241" s="3" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="F1241" s="3" t="s">
         <v>2316</v>
@@ -32635,7 +32641,7 @@
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1337" s="40" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="B1337" s="17"/>
       <c r="C1337" s="2"/>
@@ -32646,16 +32652,16 @@
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1338" s="7" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="B1338" s="17">
         <v>79782640332</v>
       </c>
       <c r="C1338" s="2" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="D1338" s="2" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="E1338" s="2"/>
       <c r="F1338" s="2"/>
@@ -32663,7 +32669,7 @@
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1339" s="40" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="B1339" s="17"/>
       <c r="C1339" s="2"/>
@@ -32674,16 +32680,16 @@
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1340" s="7" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="B1340" s="17">
         <v>79530977713</v>
       </c>
       <c r="C1340" s="2" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="D1340" s="2" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="E1340" s="2"/>
       <c r="F1340" s="2"/>
@@ -32691,14 +32697,14 @@
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1341" s="7" t="s">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="B1341" s="17">
         <v>79896279922</v>
       </c>
       <c r="C1341" s="2"/>
       <c r="D1341" s="2" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="E1341" s="2"/>
       <c r="F1341" s="2"/>
@@ -32706,14 +32712,14 @@
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1342" s="34" t="s">
-        <v>2744</v>
-      </c>
-      <c r="B1342" s="33">
+        <v>2743</v>
+      </c>
+      <c r="B1342" s="35">
         <v>79064327871</v>
       </c>
       <c r="C1342" s="33"/>
       <c r="D1342" s="33" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="E1342" s="33"/>
       <c r="F1342" s="33"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B6C516-E0F0-4E90-9FE5-FDAB67D43A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C968E6F-5A95-4D7D-B8A0-A3A1AD665A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4232" uniqueCount="2748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="2762">
   <si>
     <t>Пароль</t>
   </si>
@@ -8278,6 +8278,48 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/jFZy7Zhe593nvw</t>
+  </si>
+  <si>
+    <t>43700</t>
+  </si>
+  <si>
+    <t>* Лев</t>
+  </si>
+  <si>
+    <t>53503</t>
+  </si>
+  <si>
+    <t>84446</t>
+  </si>
+  <si>
+    <t>* ДанНя</t>
+  </si>
+  <si>
+    <t>19/09/26/12:30</t>
+  </si>
+  <si>
+    <t>87841</t>
+  </si>
+  <si>
+    <t>80562</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>/ ДанНя</t>
+  </si>
+  <si>
+    <t>? ДанНя</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/c06jSZjfPtK0Vg</t>
+  </si>
+  <si>
+    <t>? https://disk.yandex.ru/d/c06jSZjfPtK0Vg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/IUieEBvU0HqqLg</t>
   </si>
 </sst>
 </file>
@@ -32728,14 +32770,24 @@
     <row r="1343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1343" s="7"/>
       <c r="B1343" s="17"/>
-      <c r="C1343" s="2"/>
-      <c r="D1343" s="2"/>
-      <c r="E1343" s="2"/>
-      <c r="F1343" s="2"/>
+      <c r="C1343" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1343" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1343" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1343" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1343" s="2"/>
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1344" s="7"/>
+      <c r="A1344" s="40" t="s">
+        <v>2753</v>
+      </c>
       <c r="B1344" s="17"/>
       <c r="C1344" s="2"/>
       <c r="D1344" s="2"/>
@@ -32744,48 +32796,98 @@
       <c r="G1344" s="2"/>
     </row>
     <row r="1345" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1345" s="7"/>
-      <c r="B1345" s="17"/>
+      <c r="A1345" s="7" t="s">
+        <v>2748</v>
+      </c>
+      <c r="B1345" s="17">
+        <v>79184743700</v>
+      </c>
       <c r="C1345" s="2"/>
       <c r="D1345" s="2"/>
-      <c r="E1345" s="2"/>
-      <c r="F1345" s="2"/>
+      <c r="E1345" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1345" s="2" t="s">
+        <v>2749</v>
+      </c>
       <c r="G1345" s="2"/>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1346" s="7"/>
-      <c r="B1346" s="17"/>
+      <c r="A1346" s="7" t="s">
+        <v>2750</v>
+      </c>
+      <c r="B1346" s="17">
+        <v>79186353503</v>
+      </c>
       <c r="C1346" s="2"/>
-      <c r="D1346" s="2"/>
+      <c r="D1346" s="2" t="s">
+        <v>2761</v>
+      </c>
       <c r="E1346" s="2"/>
       <c r="F1346" s="2"/>
       <c r="G1346" s="2"/>
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1347" s="7"/>
-      <c r="B1347" s="17"/>
-      <c r="C1347" s="2"/>
-      <c r="D1347" s="2"/>
-      <c r="E1347" s="2"/>
-      <c r="F1347" s="2"/>
+      <c r="A1347" s="7" t="s">
+        <v>2751</v>
+      </c>
+      <c r="B1347" s="17">
+        <v>79676684446</v>
+      </c>
+      <c r="C1347" s="2" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D1347" s="2" t="s">
+        <v>2752</v>
+      </c>
+      <c r="E1347" s="2" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F1347" s="2" t="s">
+        <v>2757</v>
+      </c>
       <c r="G1347" s="2"/>
     </row>
     <row r="1348" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1348" s="7"/>
-      <c r="B1348" s="17"/>
-      <c r="C1348" s="2"/>
-      <c r="D1348" s="2"/>
-      <c r="E1348" s="2"/>
-      <c r="F1348" s="2"/>
+      <c r="A1348" s="7" t="s">
+        <v>2754</v>
+      </c>
+      <c r="B1348" s="17">
+        <v>79183887841</v>
+      </c>
+      <c r="C1348" s="2" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D1348" s="2" t="s">
+        <v>2752</v>
+      </c>
+      <c r="E1348" s="2" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F1348" s="2" t="s">
+        <v>2757</v>
+      </c>
       <c r="G1348" s="2"/>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1349" s="7"/>
-      <c r="B1349" s="17"/>
-      <c r="C1349" s="2"/>
-      <c r="D1349" s="2"/>
-      <c r="E1349" s="2"/>
-      <c r="F1349" s="2"/>
+      <c r="A1349" s="7" t="s">
+        <v>2755</v>
+      </c>
+      <c r="B1349" s="17">
+        <v>79198880562</v>
+      </c>
+      <c r="C1349" s="2" t="s">
+        <v>2759</v>
+      </c>
+      <c r="D1349" s="2" t="s">
+        <v>2758</v>
+      </c>
+      <c r="E1349" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1349" s="2" t="s">
+        <v>2757</v>
+      </c>
       <c r="G1349" s="2"/>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C968E6F-5A95-4D7D-B8A0-A3A1AD665A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E4A090-5581-419D-AF22-378A7F1B4A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="2762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4264" uniqueCount="2767">
   <si>
     <t>Пароль</t>
   </si>
@@ -8310,9 +8310,6 @@
     <t>/ ДанНя</t>
   </si>
   <si>
-    <t>? ДанНя</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/d/c06jSZjfPtK0Vg</t>
   </si>
   <si>
@@ -8320,6 +8317,24 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/IUieEBvU0HqqLg</t>
+  </si>
+  <si>
+    <t>19/09/26/15:00</t>
+  </si>
+  <si>
+    <t>40037</t>
+  </si>
+  <si>
+    <t>* Дима</t>
+  </si>
+  <si>
+    <t>98925</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/DmR9JRLcME490g</t>
+  </si>
+  <si>
+    <t>? https://disk.yandex.ru/d/DmR9JRLcME490g</t>
   </si>
 </sst>
 </file>
@@ -32821,7 +32836,7 @@
       </c>
       <c r="C1346" s="2"/>
       <c r="D1346" s="2" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="E1346" s="2"/>
       <c r="F1346" s="2"/>
@@ -32835,10 +32850,10 @@
         <v>79676684446</v>
       </c>
       <c r="C1347" s="2" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="D1347" s="2" t="s">
-        <v>2752</v>
+        <v>2765</v>
       </c>
       <c r="E1347" s="2" t="s">
         <v>2756</v>
@@ -32856,10 +32871,10 @@
         <v>79183887841</v>
       </c>
       <c r="C1348" s="2" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="D1348" s="2" t="s">
-        <v>2752</v>
+        <v>2765</v>
       </c>
       <c r="E1348" s="2" t="s">
         <v>2756</v>
@@ -32877,10 +32892,10 @@
         <v>79198880562</v>
       </c>
       <c r="C1349" s="2" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="D1349" s="2" t="s">
-        <v>2758</v>
+        <v>2766</v>
       </c>
       <c r="E1349" s="2" t="s">
         <v>731</v>
@@ -32891,7 +32906,9 @@
       <c r="G1349" s="2"/>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1350" s="7"/>
+      <c r="A1350" s="40" t="s">
+        <v>2761</v>
+      </c>
       <c r="B1350" s="17"/>
       <c r="C1350" s="2"/>
       <c r="D1350" s="2"/>
@@ -32900,19 +32917,35 @@
       <c r="G1350" s="2"/>
     </row>
     <row r="1351" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1351" s="7"/>
-      <c r="B1351" s="17"/>
-      <c r="C1351" s="2"/>
-      <c r="D1351" s="2"/>
+      <c r="A1351" s="7" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B1351" s="17">
+        <v>79882440037</v>
+      </c>
+      <c r="C1351" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1351" s="2" t="s">
+        <v>2763</v>
+      </c>
       <c r="E1351" s="2"/>
       <c r="F1351" s="2"/>
       <c r="G1351" s="2"/>
     </row>
     <row r="1352" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1352" s="7"/>
-      <c r="B1352" s="17"/>
-      <c r="C1352" s="2"/>
-      <c r="D1352" s="2"/>
+      <c r="A1352" s="7" t="s">
+        <v>2764</v>
+      </c>
+      <c r="B1352" s="17">
+        <v>79187698925</v>
+      </c>
+      <c r="C1352" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1352" s="2" t="s">
+        <v>2752</v>
+      </c>
       <c r="E1352" s="2"/>
       <c r="F1352" s="2"/>
       <c r="G1352" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E4A090-5581-419D-AF22-378A7F1B4A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51C58BF-4E17-4C87-9F33-C6D44D4F2B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4264" uniqueCount="2767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4264" uniqueCount="2766">
   <si>
     <t>Пароль</t>
   </si>
@@ -8332,9 +8332,6 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/DmR9JRLcME490g</t>
-  </si>
-  <si>
-    <t>? https://disk.yandex.ru/d/DmR9JRLcME490g</t>
   </si>
 </sst>
 </file>
@@ -32895,7 +32892,7 @@
         <v>2758</v>
       </c>
       <c r="D1349" s="2" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="E1349" s="2" t="s">
         <v>731</v>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E2074B-27C7-448B-9138-CA06C9111DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790452FA-3B8A-469E-BE80-B5E2DE732630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4271" uniqueCount="2775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4271" uniqueCount="2776">
   <si>
     <t>Пароль</t>
   </si>
@@ -8355,10 +8355,13 @@
     <t>58378</t>
   </si>
   <si>
-    <t>*ДимМа</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/d/17OB49vvhEZY2A</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/gC0OeOdke7sMeA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/rFxcuyqhm3zS-g</t>
   </si>
 </sst>
 </file>
@@ -32993,7 +32996,7 @@
         <v>79189831000</v>
       </c>
       <c r="C1354" s="2" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="D1354" s="2"/>
       <c r="E1354" s="2"/>
@@ -33021,10 +33024,10 @@
       <c r="C1356" s="2"/>
       <c r="D1356" s="2"/>
       <c r="E1356" s="2" t="s">
-        <v>731</v>
+        <v>2775</v>
       </c>
       <c r="F1356" s="2" t="s">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="G1356" s="2"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790452FA-3B8A-469E-BE80-B5E2DE732630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCE35D2-B07A-4F54-AA53-32F8A517A276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4271" uniqueCount="2776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4296" uniqueCount="2792">
   <si>
     <t>Пароль</t>
   </si>
@@ -8362,6 +8362,54 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/rFxcuyqhm3zS-g</t>
+  </si>
+  <si>
+    <t>21/09/26/10:00</t>
+  </si>
+  <si>
+    <t>66868</t>
+  </si>
+  <si>
+    <t>24737</t>
+  </si>
+  <si>
+    <t>21/09/26/12:30</t>
+  </si>
+  <si>
+    <t>24303</t>
+  </si>
+  <si>
+    <t>21/09/26/15:00</t>
+  </si>
+  <si>
+    <t>47502</t>
+  </si>
+  <si>
+    <t>02828</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/FfxX-BgCK1I-fg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/VMeJYnMDZROPMA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/aReZWXacqw_3oQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/THJLArvhcUYk-A</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/8Kh1R_8Ce42WDg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/_GoZaNV-8thaXQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/IB5N39BpXGRUGQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/AnHHYgEmAWkwFA</t>
   </si>
 </sst>
 </file>
@@ -32898,7 +32946,7 @@
         <v>79183887841</v>
       </c>
       <c r="C1348" s="2" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="D1348" s="2" t="s">
         <v>2739</v>
@@ -33034,14 +33082,24 @@
     <row r="1357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1357" s="7"/>
       <c r="B1357" s="17"/>
-      <c r="C1357" s="2"/>
-      <c r="D1357" s="2"/>
-      <c r="E1357" s="2"/>
-      <c r="F1357" s="2"/>
+      <c r="C1357" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1357" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1357" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1357" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1357" s="2"/>
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1358" s="7"/>
+      <c r="A1358" s="40" t="s">
+        <v>2776</v>
+      </c>
       <c r="B1358" s="17"/>
       <c r="C1358" s="2"/>
       <c r="D1358" s="2"/>
@@ -33050,25 +33108,47 @@
       <c r="G1358" s="2"/>
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1359" s="7"/>
-      <c r="B1359" s="17"/>
-      <c r="C1359" s="2"/>
-      <c r="D1359" s="2"/>
+      <c r="A1359" s="7" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B1359" s="17">
+        <v>79381366868</v>
+      </c>
+      <c r="C1359" s="2" t="s">
+        <v>2785</v>
+      </c>
+      <c r="D1359" s="2" t="s">
+        <v>2784</v>
+      </c>
       <c r="E1359" s="2"/>
       <c r="F1359" s="2"/>
       <c r="G1359" s="2"/>
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1360" s="7"/>
-      <c r="B1360" s="17"/>
-      <c r="C1360" s="2"/>
-      <c r="D1360" s="2"/>
-      <c r="E1360" s="2"/>
-      <c r="F1360" s="2"/>
+      <c r="A1360" s="7" t="s">
+        <v>2778</v>
+      </c>
+      <c r="B1360" s="17">
+        <v>79636924737</v>
+      </c>
+      <c r="C1360" s="2" t="s">
+        <v>2785</v>
+      </c>
+      <c r="D1360" s="2" t="s">
+        <v>2784</v>
+      </c>
+      <c r="E1360" s="2" t="s">
+        <v>2789</v>
+      </c>
+      <c r="F1360" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="G1360" s="2"/>
     </row>
     <row r="1361" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1361" s="7"/>
+      <c r="A1361" s="40" t="s">
+        <v>2779</v>
+      </c>
       <c r="B1361" s="17"/>
       <c r="C1361" s="2"/>
       <c r="D1361" s="2"/>
@@ -33077,16 +33157,28 @@
       <c r="G1361" s="2"/>
     </row>
     <row r="1362" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1362" s="7"/>
-      <c r="B1362" s="17"/>
-      <c r="C1362" s="2"/>
+      <c r="A1362" s="7" t="s">
+        <v>2780</v>
+      </c>
+      <c r="B1362" s="17">
+        <v>79265224303</v>
+      </c>
+      <c r="C1362" s="2" t="s">
+        <v>2786</v>
+      </c>
       <c r="D1362" s="2"/>
-      <c r="E1362" s="2"/>
-      <c r="F1362" s="2"/>
+      <c r="E1362" s="2" t="s">
+        <v>2790</v>
+      </c>
+      <c r="F1362" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="G1362" s="2"/>
     </row>
     <row r="1363" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1363" s="7"/>
+      <c r="A1363" s="40" t="s">
+        <v>2781</v>
+      </c>
       <c r="B1363" s="17"/>
       <c r="C1363" s="2"/>
       <c r="D1363" s="2"/>
@@ -33095,21 +33187,37 @@
       <c r="G1363" s="2"/>
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1364" s="7"/>
-      <c r="B1364" s="17"/>
-      <c r="C1364" s="2"/>
-      <c r="D1364" s="2"/>
+      <c r="A1364" s="7" t="s">
+        <v>2782</v>
+      </c>
+      <c r="B1364" s="17">
+        <v>79064147502</v>
+      </c>
+      <c r="C1364" s="2" t="s">
+        <v>2788</v>
+      </c>
+      <c r="D1364" s="2" t="s">
+        <v>2787</v>
+      </c>
       <c r="E1364" s="2"/>
       <c r="F1364" s="2"/>
       <c r="G1364" s="2"/>
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1365" s="7"/>
-      <c r="B1365" s="17"/>
+      <c r="A1365" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B1365" s="17">
+        <v>79628802828</v>
+      </c>
       <c r="C1365" s="2"/>
       <c r="D1365" s="2"/>
-      <c r="E1365" s="2"/>
-      <c r="F1365" s="2"/>
+      <c r="E1365" s="2" t="s">
+        <v>2791</v>
+      </c>
+      <c r="F1365" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="G1365" s="2"/>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCE35D2-B07A-4F54-AA53-32F8A517A276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63885866-A2E0-4314-8387-011796012D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8367,9 +8367,6 @@
     <t>21/09/26/10:00</t>
   </si>
   <si>
-    <t>66868</t>
-  </si>
-  <si>
     <t>24737</t>
   </si>
   <si>
@@ -8410,6 +8407,9 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/AnHHYgEmAWkwFA</t>
+  </si>
+  <si>
+    <t>65868</t>
   </si>
 </sst>
 </file>
@@ -33109,16 +33109,16 @@
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1359" s="7" t="s">
-        <v>2777</v>
+        <v>2791</v>
       </c>
       <c r="B1359" s="17">
-        <v>79381366868</v>
+        <v>79381365868</v>
       </c>
       <c r="C1359" s="2" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="D1359" s="2" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="E1359" s="2"/>
       <c r="F1359" s="2"/>
@@ -33126,19 +33126,19 @@
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1360" s="7" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="B1360" s="17">
         <v>79636924737</v>
       </c>
       <c r="C1360" s="2" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="D1360" s="2" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="E1360" s="2" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="F1360" s="2" t="s">
         <v>731</v>
@@ -33147,7 +33147,7 @@
     </row>
     <row r="1361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1361" s="40" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="B1361" s="17"/>
       <c r="C1361" s="2"/>
@@ -33158,17 +33158,17 @@
     </row>
     <row r="1362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1362" s="7" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="B1362" s="17">
         <v>79265224303</v>
       </c>
       <c r="C1362" s="2" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="D1362" s="2"/>
       <c r="E1362" s="2" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="F1362" s="2" t="s">
         <v>731</v>
@@ -33177,7 +33177,7 @@
     </row>
     <row r="1363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1363" s="40" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="B1363" s="17"/>
       <c r="C1363" s="2"/>
@@ -33188,16 +33188,16 @@
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1364" s="7" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="B1364" s="17">
         <v>79064147502</v>
       </c>
       <c r="C1364" s="2" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="D1364" s="2" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="E1364" s="2"/>
       <c r="F1364" s="2"/>
@@ -33205,7 +33205,7 @@
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1365" s="7" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="B1365" s="17">
         <v>79628802828</v>
@@ -33213,7 +33213,7 @@
       <c r="C1365" s="2"/>
       <c r="D1365" s="2"/>
       <c r="E1365" s="2" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="F1365" s="2" t="s">
         <v>731</v>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6190B795-3A48-4C2F-845D-56071027C62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A32C11-2840-44C6-B91D-A59736835476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8265,15 +8265,6 @@
     <t>https://disk.yandex.ru/d/8Kh1R_8Ce42WDg</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/_GoZaNV-8thaXQ</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/IB5N39BpXGRUGQ</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/AnHHYgEmAWkwFA</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/PVavNJ0-e2GnJA</t>
   </si>
   <si>
@@ -8419,6 +8410,15 @@
   </si>
   <si>
     <t>/?25393</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/6f0rJLLU3cA0kg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/fHln89Mf2TbvPA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/yqOBCTioQYV0DQ</t>
   </si>
 </sst>
 </file>
@@ -28203,7 +28203,7 @@
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1055" s="33" t="s">
-        <v>2756</v>
+        <v>2753</v>
       </c>
       <c r="B1055" s="34">
         <v>79186452525</v>
@@ -28219,7 +28219,7 @@
     </row>
     <row r="1056" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1056" s="33" t="s">
-        <v>2757</v>
+        <v>2754</v>
       </c>
       <c r="B1056" s="34">
         <v>79189484040</v>
@@ -28235,7 +28235,7 @@
     </row>
     <row r="1057" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1057" s="33" t="s">
-        <v>2758</v>
+        <v>2755</v>
       </c>
       <c r="B1057" s="34">
         <v>79183860270</v>
@@ -28251,7 +28251,7 @@
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1058" s="33" t="s">
-        <v>2759</v>
+        <v>2756</v>
       </c>
       <c r="B1058" s="34">
         <v>79779455485</v>
@@ -28269,7 +28269,7 @@
     </row>
     <row r="1059" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1059" s="33" t="s">
-        <v>2760</v>
+        <v>2757</v>
       </c>
       <c r="B1059" s="34">
         <v>79056507300</v>
@@ -28287,7 +28287,7 @@
     </row>
     <row r="1060" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1060" s="33" t="s">
-        <v>2761</v>
+        <v>2758</v>
       </c>
       <c r="B1060" s="34">
         <v>79258091550</v>
@@ -28305,7 +28305,7 @@
     </row>
     <row r="1061" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1061" s="33" t="s">
-        <v>2762</v>
+        <v>2759</v>
       </c>
       <c r="B1061" s="34">
         <v>79185091900</v>
@@ -28337,7 +28337,7 @@
     </row>
     <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1063" s="33" t="s">
-        <v>2763</v>
+        <v>2760</v>
       </c>
       <c r="B1063" s="34">
         <v>79649334332</v>
@@ -28353,7 +28353,7 @@
     </row>
     <row r="1064" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1064" s="33" t="s">
-        <v>2764</v>
+        <v>2761</v>
       </c>
       <c r="B1064" s="34">
         <v>79783434760</v>
@@ -28369,7 +28369,7 @@
     </row>
     <row r="1065" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1065" s="33" t="s">
-        <v>2765</v>
+        <v>2762</v>
       </c>
       <c r="B1065" s="34">
         <v>79493130260</v>
@@ -28385,7 +28385,7 @@
     </row>
     <row r="1066" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1066" s="33" t="s">
-        <v>2766</v>
+        <v>2763</v>
       </c>
       <c r="B1066" s="34">
         <v>79990156363</v>
@@ -28403,7 +28403,7 @@
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1067" s="33" t="s">
-        <v>2767</v>
+        <v>2764</v>
       </c>
       <c r="B1067" s="34">
         <v>79880146339</v>
@@ -28419,7 +28419,7 @@
     </row>
     <row r="1068" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1068" s="33" t="s">
-        <v>2768</v>
+        <v>2765</v>
       </c>
       <c r="B1068" s="34">
         <v>79604622005</v>
@@ -28437,7 +28437,7 @@
     </row>
     <row r="1069" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1069" s="33" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="B1069" s="34">
         <v>79192563907</v>
@@ -28453,7 +28453,7 @@
     </row>
     <row r="1070" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1070" s="33" t="s">
-        <v>2770</v>
+        <v>2767</v>
       </c>
       <c r="B1070" s="34">
         <v>79180335333</v>
@@ -28501,7 +28501,7 @@
     </row>
     <row r="1073" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1073" s="33" t="s">
-        <v>2771</v>
+        <v>2768</v>
       </c>
       <c r="B1073" s="34">
         <v>79183073394</v>
@@ -28531,7 +28531,7 @@
     </row>
     <row r="1075" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1075" s="33" t="s">
-        <v>2772</v>
+        <v>2769</v>
       </c>
       <c r="B1075" s="34">
         <v>79615215290</v>
@@ -28553,7 +28553,7 @@
     </row>
     <row r="1076" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1076" s="33" t="s">
-        <v>2773</v>
+        <v>2770</v>
       </c>
       <c r="B1076" s="34">
         <v>79094569745</v>
@@ -28569,7 +28569,7 @@
     </row>
     <row r="1077" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1077" s="33" t="s">
-        <v>2774</v>
+        <v>2771</v>
       </c>
       <c r="B1077" s="34">
         <v>79180757000</v>
@@ -28585,7 +28585,7 @@
     </row>
     <row r="1078" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1078" s="33" t="s">
-        <v>2775</v>
+        <v>2772</v>
       </c>
       <c r="B1078" s="34">
         <v>79628609461</v>
@@ -28603,7 +28603,7 @@
     </row>
     <row r="1079" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1079" s="33" t="s">
-        <v>2776</v>
+        <v>2773</v>
       </c>
       <c r="B1079" s="34">
         <v>79184101450</v>
@@ -28621,7 +28621,7 @@
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1080" s="33" t="s">
-        <v>2777</v>
+        <v>2774</v>
       </c>
       <c r="B1080" s="34">
         <v>79183999079</v>
@@ -28643,7 +28643,7 @@
     </row>
     <row r="1081" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1081" s="33" t="s">
-        <v>2778</v>
+        <v>2775</v>
       </c>
       <c r="B1081" s="34">
         <v>79181433232</v>
@@ -28661,7 +28661,7 @@
     </row>
     <row r="1082" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1082" s="33" t="s">
-        <v>2794</v>
+        <v>2791</v>
       </c>
       <c r="B1082" s="34">
         <v>79817025393</v>
@@ -28679,7 +28679,7 @@
     </row>
     <row r="1083" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1083" s="33" t="s">
-        <v>2793</v>
+        <v>2790</v>
       </c>
       <c r="B1083" s="34">
         <v>79184302094</v>
@@ -28707,7 +28707,7 @@
     </row>
     <row r="1085" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1085" s="33" t="s">
-        <v>2792</v>
+        <v>2789</v>
       </c>
       <c r="B1085" s="34">
         <v>79287677710</v>
@@ -28729,7 +28729,7 @@
     </row>
     <row r="1086" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1086" s="33" t="s">
-        <v>2791</v>
+        <v>2788</v>
       </c>
       <c r="B1086" s="34">
         <v>79615198406</v>
@@ -28745,7 +28745,7 @@
     </row>
     <row r="1087" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1087" s="33" t="s">
-        <v>2790</v>
+        <v>2787</v>
       </c>
       <c r="B1087" s="34">
         <v>79620503561</v>
@@ -28763,7 +28763,7 @@
     </row>
     <row r="1088" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1088" s="33" t="s">
-        <v>2789</v>
+        <v>2786</v>
       </c>
       <c r="B1088" s="34">
         <v>79093732088</v>
@@ -28785,7 +28785,7 @@
     </row>
     <row r="1089" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1089" s="33" t="s">
-        <v>2788</v>
+        <v>2785</v>
       </c>
       <c r="B1089" s="34">
         <v>79060683338</v>
@@ -28805,7 +28805,7 @@
     </row>
     <row r="1090" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1090" s="33" t="s">
-        <v>2787</v>
+        <v>2784</v>
       </c>
       <c r="B1090" s="34">
         <v>79184137117</v>
@@ -28821,7 +28821,7 @@
     </row>
     <row r="1091" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1091" s="33" t="s">
-        <v>2786</v>
+        <v>2783</v>
       </c>
       <c r="B1091" s="34">
         <v>79180660587</v>
@@ -28849,7 +28849,7 @@
     </row>
     <row r="1093" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1093" s="33" t="s">
-        <v>2785</v>
+        <v>2782</v>
       </c>
       <c r="B1093" s="34">
         <v>79002359970</v>
@@ -28871,7 +28871,7 @@
     </row>
     <row r="1094" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1094" s="33" t="s">
-        <v>2784</v>
+        <v>2781</v>
       </c>
       <c r="B1094" s="34">
         <v>79892306069</v>
@@ -28901,7 +28901,7 @@
     </row>
     <row r="1096" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1096" s="33" t="s">
-        <v>2783</v>
+        <v>2780</v>
       </c>
       <c r="B1096" s="34">
         <v>79615101239</v>
@@ -28917,7 +28917,7 @@
     </row>
     <row r="1097" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1097" s="33" t="s">
-        <v>2782</v>
+        <v>2779</v>
       </c>
       <c r="B1097" s="34">
         <v>79287753737</v>
@@ -28935,7 +28935,7 @@
     </row>
     <row r="1098" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1098" s="33" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="B1098" s="34">
         <v>79283348884</v>
@@ -28957,7 +28957,7 @@
     </row>
     <row r="1099" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1099" s="33" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="B1099" s="34">
         <v>79381175888</v>
@@ -28985,7 +28985,7 @@
     </row>
     <row r="1101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1101" s="33" t="s">
-        <v>2779</v>
+        <v>2776</v>
       </c>
       <c r="B1101" s="39">
         <v>79536931038</v>
@@ -31580,7 +31580,7 @@
       </c>
       <c r="C1259" s="3"/>
       <c r="D1259" s="3" t="s">
-        <v>2751</v>
+        <v>2748</v>
       </c>
       <c r="E1259" s="3"/>
       <c r="F1259" s="3"/>
@@ -31597,10 +31597,10 @@
       <c r="C1260" s="3"/>
       <c r="D1260" s="3"/>
       <c r="E1260" s="3" t="s">
-        <v>2752</v>
+        <v>2749</v>
       </c>
       <c r="F1260" s="3" t="s">
-        <v>2754</v>
+        <v>2751</v>
       </c>
       <c r="G1260" s="3"/>
       <c r="H1260" s="3"/>
@@ -31625,7 +31625,7 @@
         <v>79183108008</v>
       </c>
       <c r="C1262" s="3" t="s">
-        <v>2749</v>
+        <v>2746</v>
       </c>
       <c r="D1262" s="3"/>
       <c r="E1262" s="3"/>
@@ -31641,14 +31641,14 @@
         <v>79097178862</v>
       </c>
       <c r="C1263" s="3" t="s">
-        <v>2749</v>
+        <v>2746</v>
       </c>
       <c r="D1263" s="3"/>
       <c r="E1263" s="3" t="s">
-        <v>2753</v>
+        <v>2750</v>
       </c>
       <c r="F1263" s="3" t="s">
-        <v>2755</v>
+        <v>2752</v>
       </c>
       <c r="G1263" s="3"/>
       <c r="H1263" s="3"/>
@@ -31673,7 +31673,7 @@
         <v>79787819232</v>
       </c>
       <c r="C1265" s="3" t="s">
-        <v>2750</v>
+        <v>2747</v>
       </c>
       <c r="D1265" s="3"/>
       <c r="E1265" s="3"/>
@@ -33143,10 +33143,10 @@
         <v>2738</v>
       </c>
       <c r="E1360" s="2" t="s">
+        <v>2792</v>
+      </c>
+      <c r="F1360" s="2" t="s">
         <v>2743</v>
-      </c>
-      <c r="F1360" s="2" t="s">
-        <v>2746</v>
       </c>
       <c r="G1360" s="2"/>
     </row>
@@ -33173,10 +33173,10 @@
       </c>
       <c r="D1362" s="2"/>
       <c r="E1362" s="2" t="s">
+        <v>2793</v>
+      </c>
+      <c r="F1362" s="2" t="s">
         <v>2744</v>
-      </c>
-      <c r="F1362" s="2" t="s">
-        <v>2747</v>
       </c>
       <c r="G1362" s="2"/>
     </row>
@@ -33218,10 +33218,10 @@
       <c r="C1365" s="2"/>
       <c r="D1365" s="2"/>
       <c r="E1365" s="2" t="s">
+        <v>2794</v>
+      </c>
+      <c r="F1365" s="2" t="s">
         <v>2745</v>
-      </c>
-      <c r="F1365" s="2" t="s">
-        <v>2748</v>
       </c>
       <c r="G1365" s="2"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A32C11-2840-44C6-B91D-A59736835476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8F63F7-AF25-4D10-989A-0E5FD6367AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4296" uniqueCount="2795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4303" uniqueCount="2798">
   <si>
     <t>Пароль</t>
   </si>
@@ -8419,6 +8419,15 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/yqOBCTioQYV0DQ</t>
+  </si>
+  <si>
+    <t>22/09/26/12:30</t>
+  </si>
+  <si>
+    <t>67398</t>
+  </si>
+  <si>
+    <t>81271</t>
   </si>
 </sst>
 </file>
@@ -33226,7 +33235,9 @@
       <c r="G1365" s="2"/>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1366" s="7"/>
+      <c r="A1366" s="7" t="s">
+        <v>2795</v>
+      </c>
       <c r="B1366" s="17"/>
       <c r="C1366" s="2"/>
       <c r="D1366" s="2"/>
@@ -33235,21 +33246,37 @@
       <c r="G1366" s="2"/>
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1367" s="7"/>
-      <c r="B1367" s="17"/>
-      <c r="C1367" s="2"/>
+      <c r="A1367" s="7" t="s">
+        <v>2796</v>
+      </c>
+      <c r="B1367" s="17">
+        <v>79324167398</v>
+      </c>
+      <c r="C1367" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="D1367" s="2"/>
       <c r="E1367" s="2"/>
       <c r="F1367" s="2"/>
       <c r="G1367" s="2"/>
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1368" s="7"/>
-      <c r="B1368" s="17"/>
-      <c r="C1368" s="2"/>
+      <c r="A1368" s="7" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B1368" s="17">
+        <v>79056181271</v>
+      </c>
+      <c r="C1368" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="D1368" s="2"/>
-      <c r="E1368" s="2"/>
-      <c r="F1368" s="2"/>
+      <c r="E1368" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1368" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="G1368" s="2"/>
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8F63F7-AF25-4D10-989A-0E5FD6367AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43A02D2-9C20-4A00-8A7D-2E9B3CD214BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4303" uniqueCount="2798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4303" uniqueCount="2801">
   <si>
     <t>Пароль</t>
   </si>
@@ -8428,6 +8428,15 @@
   </si>
   <si>
     <t>81271</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/0PMH4lWlGrXCUw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/jTqEyb82h0dXxw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/va9x8P7PHGTpzA</t>
   </si>
 </sst>
 </file>
@@ -33253,7 +33262,7 @@
         <v>79324167398</v>
       </c>
       <c r="C1367" s="2" t="s">
-        <v>731</v>
+        <v>2798</v>
       </c>
       <c r="D1367" s="2"/>
       <c r="E1367" s="2"/>
@@ -33268,14 +33277,14 @@
         <v>79056181271</v>
       </c>
       <c r="C1368" s="2" t="s">
-        <v>731</v>
+        <v>2798</v>
       </c>
       <c r="D1368" s="2"/>
       <c r="E1368" s="2" t="s">
-        <v>731</v>
+        <v>2800</v>
       </c>
       <c r="F1368" s="2" t="s">
-        <v>731</v>
+        <v>2799</v>
       </c>
       <c r="G1368" s="2"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43A02D2-9C20-4A00-8A7D-2E9B3CD214BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5622A6CD-FF5E-4B85-BC6B-1A6D4A695576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4303" uniqueCount="2801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4307" uniqueCount="2805">
   <si>
     <t>Пароль</t>
   </si>
@@ -8437,6 +8437,18 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/va9x8P7PHGTpzA</t>
+  </si>
+  <si>
+    <t>23/09/26/12:30</t>
+  </si>
+  <si>
+    <t>29955</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/nu0QXsQ3TslLnw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/4rrHTUSdnjFDdQ</t>
   </si>
 </sst>
 </file>
@@ -33289,7 +33301,9 @@
       <c r="G1368" s="2"/>
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1369" s="7"/>
+      <c r="A1369" s="7" t="s">
+        <v>2801</v>
+      </c>
       <c r="B1369" s="17"/>
       <c r="C1369" s="2"/>
       <c r="D1369" s="2"/>
@@ -33298,10 +33312,18 @@
       <c r="G1369" s="2"/>
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1370" s="7"/>
-      <c r="B1370" s="17"/>
-      <c r="C1370" s="2"/>
-      <c r="D1370" s="2"/>
+      <c r="A1370" s="7" t="s">
+        <v>2802</v>
+      </c>
+      <c r="B1370" s="17">
+        <v>79276629955</v>
+      </c>
+      <c r="C1370" s="2" t="s">
+        <v>2803</v>
+      </c>
+      <c r="D1370" s="2" t="s">
+        <v>2804</v>
+      </c>
       <c r="E1370" s="2"/>
       <c r="F1370" s="2"/>
       <c r="G1370" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0B1397-6D2B-499E-AF3C-9B86E3CA545D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1070615-2C1A-42C9-9543-64E8D77BF62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4314" uniqueCount="2808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4315" uniqueCount="2809">
   <si>
     <t>Пароль</t>
   </si>
@@ -8458,6 +8458,9 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/VbtuRt_mGwhaFg</t>
+  </si>
+  <si>
+    <t>06569</t>
   </si>
 </sst>
 </file>
@@ -33363,8 +33366,12 @@
       <c r="G1372" s="2"/>
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1373" s="7"/>
-      <c r="B1373" s="16"/>
+      <c r="A1373" s="7" t="s">
+        <v>2808</v>
+      </c>
+      <c r="B1373" s="16">
+        <v>79496106569</v>
+      </c>
       <c r="C1373" s="2" t="s">
         <v>2806</v>
       </c>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1070615-2C1A-42C9-9543-64E8D77BF62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C50547-E0C7-4532-9E85-B9B1BCB28A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4315" uniqueCount="2809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4326" uniqueCount="2819">
   <si>
     <t>Пароль</t>
   </si>
@@ -8461,6 +8461,36 @@
   </si>
   <si>
     <t>06569</t>
+  </si>
+  <si>
+    <t>25/09/26/10:00</t>
+  </si>
+  <si>
+    <t>90768</t>
+  </si>
+  <si>
+    <t>16412</t>
+  </si>
+  <si>
+    <t>25/09/26/15:00</t>
+  </si>
+  <si>
+    <t>18503</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/7yOPZjleeyUa5w</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Xlj5JdmGvFsPIA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/-H5lAKsT8SR4eg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/PWhZ4OVR8bWifg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/w8_g3g1dKVk9Bg</t>
   </si>
 </sst>
 </file>
@@ -33383,7 +33413,9 @@
       <c r="G1373" s="2"/>
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1374" s="7"/>
+      <c r="A1374" s="37" t="s">
+        <v>2809</v>
+      </c>
       <c r="B1374" s="16"/>
       <c r="C1374" s="2"/>
       <c r="D1374" s="2"/>
@@ -33392,25 +33424,41 @@
       <c r="G1374" s="2"/>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1375" s="7"/>
-      <c r="B1375" s="16"/>
-      <c r="C1375" s="2"/>
-      <c r="D1375" s="2"/>
+      <c r="A1375" s="7" t="s">
+        <v>2810</v>
+      </c>
+      <c r="B1375" s="16">
+        <v>79287390768</v>
+      </c>
+      <c r="C1375" s="2" t="s">
+        <v>2818</v>
+      </c>
+      <c r="D1375" s="2" t="s">
+        <v>2814</v>
+      </c>
       <c r="E1375" s="2"/>
       <c r="F1375" s="2"/>
       <c r="G1375" s="2"/>
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1376" s="7"/>
-      <c r="B1376" s="16"/>
-      <c r="C1376" s="2"/>
+      <c r="A1376" s="7" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1376" s="16">
+        <v>79085216412</v>
+      </c>
+      <c r="C1376" s="2" t="s">
+        <v>2818</v>
+      </c>
       <c r="D1376" s="2"/>
       <c r="E1376" s="2"/>
       <c r="F1376" s="2"/>
       <c r="G1376" s="2"/>
     </row>
     <row r="1377" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1377" s="7"/>
+      <c r="A1377" s="37" t="s">
+        <v>2812</v>
+      </c>
       <c r="B1377" s="16"/>
       <c r="C1377" s="2"/>
       <c r="D1377" s="2"/>
@@ -33419,12 +33467,22 @@
       <c r="G1377" s="2"/>
     </row>
     <row r="1378" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1378" s="7"/>
-      <c r="B1378" s="16"/>
-      <c r="C1378" s="2"/>
+      <c r="A1378" s="7" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B1378" s="16">
+        <v>79803218503</v>
+      </c>
+      <c r="C1378" s="2" t="s">
+        <v>2815</v>
+      </c>
       <c r="D1378" s="2"/>
-      <c r="E1378" s="2"/>
-      <c r="F1378" s="2"/>
+      <c r="E1378" s="2" t="s">
+        <v>2816</v>
+      </c>
+      <c r="F1378" s="2" t="s">
+        <v>2817</v>
+      </c>
       <c r="G1378" s="2"/>
     </row>
     <row r="1379" spans="1:7" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2132C9F4-8C73-4B9D-85C8-8F4C04FFF028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB22B9C-663E-4FBD-9DF1-D50AD293C44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4363" uniqueCount="2839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="2840">
   <si>
     <t>Пароль</t>
   </si>
@@ -8551,6 +8551,9 @@
   </si>
   <si>
     <t>* общ</t>
+  </si>
+  <si>
+    <t>88829</t>
   </si>
 </sst>
 </file>
@@ -33808,10 +33811,16 @@
       <c r="H1393" s="2"/>
     </row>
     <row r="1394" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1394" s="7"/>
-      <c r="B1394" s="16"/>
+      <c r="A1394" s="7" t="s">
+        <v>2839</v>
+      </c>
+      <c r="B1394" s="16">
+        <v>79032888829</v>
+      </c>
       <c r="C1394" s="2"/>
-      <c r="D1394" s="2"/>
+      <c r="D1394" s="2" t="s">
+        <v>2836</v>
+      </c>
       <c r="E1394" s="2"/>
       <c r="F1394" s="2"/>
       <c r="G1394" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB22B9C-663E-4FBD-9DF1-D50AD293C44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B93F0D-5E36-406A-9DEC-F206CC30CC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="2840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="2843">
   <si>
     <t>Пароль</t>
   </si>
@@ -8535,9 +8535,6 @@
     <t>27391</t>
   </si>
   <si>
-    <t>* ДимМа</t>
-  </si>
-  <si>
     <t>* Go</t>
   </si>
   <si>
@@ -8554,6 +8551,18 @@
   </si>
   <si>
     <t>88829</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/tC9K-oTdrp79lw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/lmbiau6IYHF5iA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/57CLTjS72PT-_w</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/nz9Ad_9tE6aofg</t>
   </si>
 </sst>
 </file>
@@ -33607,7 +33616,7 @@
       </c>
       <c r="C1381" s="2"/>
       <c r="D1381" s="2" t="s">
-        <v>2833</v>
+        <v>2842</v>
       </c>
       <c r="E1381" s="2"/>
       <c r="F1381" s="2"/>
@@ -33621,10 +33630,10 @@
         <v>79381241749</v>
       </c>
       <c r="C1382" s="2" t="s">
-        <v>731</v>
+        <v>2839</v>
       </c>
       <c r="D1382" s="2" t="s">
-        <v>2834</v>
+        <v>2841</v>
       </c>
       <c r="E1382" s="2"/>
       <c r="F1382" s="2"/>
@@ -33638,7 +33647,7 @@
         <v>79183931723</v>
       </c>
       <c r="C1383" s="2" t="s">
-        <v>731</v>
+        <v>2839</v>
       </c>
       <c r="D1383" s="2"/>
       <c r="E1383" s="2"/>
@@ -33666,13 +33675,13 @@
         <v>79895207444</v>
       </c>
       <c r="C1385" s="2" t="s">
-        <v>731</v>
+        <v>2839</v>
       </c>
       <c r="D1385" s="2" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="E1385" s="2" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="F1385" s="2" t="s">
         <v>731</v>
@@ -33688,7 +33697,7 @@
         <v>79054396611</v>
       </c>
       <c r="C1386" s="2" t="s">
-        <v>731</v>
+        <v>2840</v>
       </c>
       <c r="D1386" s="2"/>
       <c r="E1386" s="2"/>
@@ -33704,7 +33713,7 @@
         <v>79189914636</v>
       </c>
       <c r="C1387" s="2" t="s">
-        <v>731</v>
+        <v>2840</v>
       </c>
       <c r="D1387" s="2"/>
       <c r="E1387" s="2"/>
@@ -33720,10 +33729,10 @@
         <v>79281644488</v>
       </c>
       <c r="C1388" s="2" t="s">
-        <v>731</v>
+        <v>2840</v>
       </c>
       <c r="D1388" s="2" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="E1388" s="2"/>
       <c r="F1388" s="2"/>
@@ -33751,7 +33760,7 @@
       </c>
       <c r="C1390" s="2"/>
       <c r="D1390" s="2" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="E1390" s="2"/>
       <c r="F1390" s="2"/>
@@ -33769,7 +33778,7 @@
         <v>731</v>
       </c>
       <c r="D1391" s="2" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="E1391" s="2"/>
       <c r="F1391" s="2"/>
@@ -33803,7 +33812,7 @@
         <v>731</v>
       </c>
       <c r="D1393" s="2" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="E1393" s="2"/>
       <c r="F1393" s="2"/>
@@ -33812,14 +33821,14 @@
     </row>
     <row r="1394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1394" s="7" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B1394" s="16">
         <v>79032888829</v>
       </c>
       <c r="C1394" s="2"/>
       <c r="D1394" s="2" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="E1394" s="2"/>
       <c r="F1394" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B93F0D-5E36-406A-9DEC-F206CC30CC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9592F42B-8DCC-4D5E-9A2C-BCAB0925872D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="2843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="2845">
   <si>
     <t>Пароль</t>
   </si>
@@ -8535,21 +8535,6 @@
     <t>27391</t>
   </si>
   <si>
-    <t>* Go</t>
-  </si>
-  <si>
-    <t>* Олег</t>
-  </si>
-  <si>
-    <t>* Дима</t>
-  </si>
-  <si>
-    <t>* Рамиль</t>
-  </si>
-  <si>
-    <t>* общ</t>
-  </si>
-  <si>
     <t>88829</t>
   </si>
   <si>
@@ -8563,6 +8548,27 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/nz9Ad_9tE6aofg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/b0jhXL1ANsG_OA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/hJn8MHrzIlHlQg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/X7GUvGXphPjaMw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/ngWLwTxLxDD55g</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Y14p6cQHw4C5Ww</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/oaSt3Co4L92WRQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/40c0_uD_UOdTCg</t>
   </si>
 </sst>
 </file>
@@ -33616,7 +33622,7 @@
       </c>
       <c r="C1381" s="2"/>
       <c r="D1381" s="2" t="s">
-        <v>2842</v>
+        <v>2837</v>
       </c>
       <c r="E1381" s="2"/>
       <c r="F1381" s="2"/>
@@ -33630,10 +33636,10 @@
         <v>79381241749</v>
       </c>
       <c r="C1382" s="2" t="s">
-        <v>2839</v>
+        <v>2834</v>
       </c>
       <c r="D1382" s="2" t="s">
-        <v>2841</v>
+        <v>2836</v>
       </c>
       <c r="E1382" s="2"/>
       <c r="F1382" s="2"/>
@@ -33647,7 +33653,7 @@
         <v>79183931723</v>
       </c>
       <c r="C1383" s="2" t="s">
-        <v>2839</v>
+        <v>2834</v>
       </c>
       <c r="D1383" s="2"/>
       <c r="E1383" s="2"/>
@@ -33675,16 +33681,16 @@
         <v>79895207444</v>
       </c>
       <c r="C1385" s="2" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1385" s="2" t="s">
         <v>2839</v>
       </c>
-      <c r="D1385" s="2" t="s">
-        <v>2833</v>
-      </c>
       <c r="E1385" s="2" t="s">
-        <v>2837</v>
+        <v>2843</v>
       </c>
       <c r="F1385" s="2" t="s">
-        <v>731</v>
+        <v>2844</v>
       </c>
       <c r="G1385" s="2"/>
       <c r="H1385" s="2"/>
@@ -33697,7 +33703,7 @@
         <v>79054396611</v>
       </c>
       <c r="C1386" s="2" t="s">
-        <v>2840</v>
+        <v>2835</v>
       </c>
       <c r="D1386" s="2"/>
       <c r="E1386" s="2"/>
@@ -33713,7 +33719,7 @@
         <v>79189914636</v>
       </c>
       <c r="C1387" s="2" t="s">
-        <v>2840</v>
+        <v>2835</v>
       </c>
       <c r="D1387" s="2"/>
       <c r="E1387" s="2"/>
@@ -33729,10 +33735,10 @@
         <v>79281644488</v>
       </c>
       <c r="C1388" s="2" t="s">
+        <v>2835</v>
+      </c>
+      <c r="D1388" s="2" t="s">
         <v>2840</v>
-      </c>
-      <c r="D1388" s="2" t="s">
-        <v>2834</v>
       </c>
       <c r="E1388" s="2"/>
       <c r="F1388" s="2"/>
@@ -33760,7 +33766,7 @@
       </c>
       <c r="C1390" s="2"/>
       <c r="D1390" s="2" t="s">
-        <v>2835</v>
+        <v>2841</v>
       </c>
       <c r="E1390" s="2"/>
       <c r="F1390" s="2"/>
@@ -33775,10 +33781,10 @@
         <v>79034655195</v>
       </c>
       <c r="C1391" s="2" t="s">
-        <v>731</v>
+        <v>2838</v>
       </c>
       <c r="D1391" s="2" t="s">
-        <v>2835</v>
+        <v>2841</v>
       </c>
       <c r="E1391" s="2"/>
       <c r="F1391" s="2"/>
@@ -33793,7 +33799,7 @@
         <v>79181891524</v>
       </c>
       <c r="C1392" s="2" t="s">
-        <v>731</v>
+        <v>2838</v>
       </c>
       <c r="D1392" s="2"/>
       <c r="E1392" s="2"/>
@@ -33809,10 +33815,10 @@
         <v>79197527391</v>
       </c>
       <c r="C1393" s="2" t="s">
-        <v>731</v>
+        <v>2838</v>
       </c>
       <c r="D1393" s="2" t="s">
-        <v>2836</v>
+        <v>2842</v>
       </c>
       <c r="E1393" s="2"/>
       <c r="F1393" s="2"/>
@@ -33821,14 +33827,14 @@
     </row>
     <row r="1394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1394" s="7" t="s">
-        <v>2838</v>
+        <v>2833</v>
       </c>
       <c r="B1394" s="16">
         <v>79032888829</v>
       </c>
       <c r="C1394" s="2"/>
       <c r="D1394" s="2" t="s">
-        <v>2835</v>
+        <v>2841</v>
       </c>
       <c r="E1394" s="2"/>
       <c r="F1394" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9592F42B-8DCC-4D5E-9A2C-BCAB0925872D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C918277B-9456-490B-867B-39411F447CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="2845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="2846">
   <si>
     <t>Пароль</t>
   </si>
@@ -8569,6 +8569,9 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/i/40c0_uD_UOdTCg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/5Lp9GtGVEs8CYg</t>
   </si>
 </sst>
 </file>
@@ -31617,7 +31620,7 @@
         <v>79181978847</v>
       </c>
       <c r="C1252" s="3" t="s">
-        <v>2622</v>
+        <v>2845</v>
       </c>
       <c r="D1252" s="3" t="s">
         <v>2627</v>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C918277B-9456-490B-867B-39411F447CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368EDCCB-D0E9-4736-803D-1C0E09A7AEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="2846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4384" uniqueCount="2859">
   <si>
     <t>Пароль</t>
   </si>
@@ -8572,6 +8572,45 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/5Lp9GtGVEs8CYg</t>
+  </si>
+  <si>
+    <t>27/09/26/10:00</t>
+  </si>
+  <si>
+    <t>92956</t>
+  </si>
+  <si>
+    <t>27/09/26/12:30</t>
+  </si>
+  <si>
+    <t>15277</t>
+  </si>
+  <si>
+    <t>23366</t>
+  </si>
+  <si>
+    <t>27/09/26/15:00</t>
+  </si>
+  <si>
+    <t>26026</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/IXMoREWwLYuL2w</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/umAHFZyeLJvsJQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/kJVTRFiGHEsEYw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/vhRDvpXrq6a-bw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/7fquLgxRsrYjqQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/DrJEp8zIXx2S-Q</t>
   </si>
 </sst>
 </file>
@@ -33847,15 +33886,25 @@
     <row r="1395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1395" s="7"/>
       <c r="B1395" s="16"/>
-      <c r="C1395" s="2"/>
-      <c r="D1395" s="2"/>
-      <c r="E1395" s="2"/>
-      <c r="F1395" s="2"/>
+      <c r="C1395" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1395" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1395" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1395" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1395" s="2"/>
       <c r="H1395" s="2"/>
     </row>
     <row r="1396" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1396" s="7"/>
+      <c r="A1396" s="37" t="s">
+        <v>2846</v>
+      </c>
       <c r="B1396" s="16"/>
       <c r="C1396" s="2"/>
       <c r="D1396" s="2"/>
@@ -33865,17 +33914,27 @@
       <c r="H1396" s="2"/>
     </row>
     <row r="1397" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1397" s="7"/>
-      <c r="B1397" s="16"/>
+      <c r="A1397" s="7" t="s">
+        <v>2847</v>
+      </c>
+      <c r="B1397" s="16">
+        <v>79282292956</v>
+      </c>
       <c r="C1397" s="2"/>
       <c r="D1397" s="2"/>
-      <c r="E1397" s="2"/>
-      <c r="F1397" s="2"/>
+      <c r="E1397" s="2" t="s">
+        <v>2856</v>
+      </c>
+      <c r="F1397" s="2" t="s">
+        <v>2855</v>
+      </c>
       <c r="G1397" s="2"/>
       <c r="H1397" s="2"/>
     </row>
     <row r="1398" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1398" s="7"/>
+      <c r="A1398" s="37" t="s">
+        <v>2848</v>
+      </c>
       <c r="B1398" s="16"/>
       <c r="C1398" s="2"/>
       <c r="D1398" s="2"/>
@@ -33885,27 +33944,47 @@
       <c r="H1398" s="2"/>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1399" s="7"/>
-      <c r="B1399" s="16"/>
-      <c r="C1399" s="2"/>
-      <c r="D1399" s="2"/>
+      <c r="A1399" s="7" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B1399" s="16">
+        <v>79892315277</v>
+      </c>
+      <c r="C1399" s="2" t="s">
+        <v>2853</v>
+      </c>
+      <c r="D1399" s="2" t="s">
+        <v>2854</v>
+      </c>
       <c r="E1399" s="2"/>
       <c r="F1399" s="2"/>
       <c r="G1399" s="2"/>
       <c r="H1399" s="2"/>
     </row>
     <row r="1400" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1400" s="7"/>
-      <c r="B1400" s="16"/>
-      <c r="C1400" s="2"/>
+      <c r="A1400" s="7" t="s">
+        <v>2850</v>
+      </c>
+      <c r="B1400" s="16">
+        <v>79182323366</v>
+      </c>
+      <c r="C1400" s="2" t="s">
+        <v>2853</v>
+      </c>
       <c r="D1400" s="2"/>
-      <c r="E1400" s="2"/>
-      <c r="F1400" s="2"/>
+      <c r="E1400" s="2" t="s">
+        <v>2858</v>
+      </c>
+      <c r="F1400" s="2" t="s">
+        <v>2857</v>
+      </c>
       <c r="G1400" s="2"/>
       <c r="H1400" s="2"/>
     </row>
     <row r="1401" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1401" s="7"/>
+      <c r="A1401" s="37" t="s">
+        <v>2851</v>
+      </c>
       <c r="B1401" s="16"/>
       <c r="C1401" s="2"/>
       <c r="D1401" s="2"/>
@@ -33915,9 +33994,15 @@
       <c r="H1401" s="2"/>
     </row>
     <row r="1402" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1402" s="7"/>
-      <c r="B1402" s="16"/>
-      <c r="C1402" s="2"/>
+      <c r="A1402" s="7" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B1402" s="16">
+        <v>79937726026</v>
+      </c>
+      <c r="C1402" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="D1402" s="2"/>
       <c r="E1402" s="2"/>
       <c r="F1402" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368EDCCB-D0E9-4736-803D-1C0E09A7AEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C2D857-3859-41E9-9AD7-0A0D0DDB0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22095" yWindow="225" windowWidth="29505" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4384" uniqueCount="2859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4384" uniqueCount="2860">
   <si>
     <t>Пароль</t>
   </si>
@@ -8611,6 +8611,9 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/DrJEp8zIXx2S-Q</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/ZQLvNM8nbGg7Cw</t>
   </si>
 </sst>
 </file>
@@ -34001,7 +34004,7 @@
         <v>79937726026</v>
       </c>
       <c r="C1402" s="2" t="s">
-        <v>731</v>
+        <v>2859</v>
       </c>
       <c r="D1402" s="2"/>
       <c r="E1402" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C2D857-3859-41E9-9AD7-0A0D0DDB0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD058B5-53E8-44EE-9989-6D3BD0B9742A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4384" uniqueCount="2860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4388" uniqueCount="2864">
   <si>
     <t>Пароль</t>
   </si>
@@ -8614,6 +8614,18 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/ZQLvNM8nbGg7Cw</t>
+  </si>
+  <si>
+    <t>30/09/26/12:30</t>
+  </si>
+  <si>
+    <t>96243</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/m-8Q0mALwJHc2g</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/tBZmdnrxMFPOAQ</t>
   </si>
 </sst>
 </file>
@@ -34013,7 +34025,9 @@
       <c r="H1402" s="2"/>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1403" s="7"/>
+      <c r="A1403" s="7" t="s">
+        <v>2860</v>
+      </c>
       <c r="B1403" s="16"/>
       <c r="C1403" s="2"/>
       <c r="D1403" s="2"/>
@@ -34023,10 +34037,18 @@
       <c r="H1403" s="2"/>
     </row>
     <row r="1404" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1404" s="7"/>
-      <c r="B1404" s="16"/>
-      <c r="C1404" s="2"/>
-      <c r="D1404" s="2"/>
+      <c r="A1404" s="7" t="s">
+        <v>2861</v>
+      </c>
+      <c r="B1404" s="16">
+        <v>79508496243</v>
+      </c>
+      <c r="C1404" s="2" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D1404" s="2" t="s">
+        <v>2862</v>
+      </c>
       <c r="E1404" s="2"/>
       <c r="F1404" s="2"/>
       <c r="G1404" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EADF2DE-88F4-4A60-81A5-9A212E53AD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6809D8A9-90F7-41B0-BD28-0B0C254C0057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27390" yWindow="0" windowWidth="24315" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4398" uniqueCount="2869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="2870">
   <si>
     <t>Пароль</t>
   </si>
@@ -8637,10 +8637,13 @@
     <t>77077</t>
   </si>
   <si>
-    <t>* Дима</t>
-  </si>
-  <si>
-    <t>* ДимМа</t>
+    <t>https://disk.yandex.ru/d/xOiBO_HLjQ4MmQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/yQNlUVuVyVnyVQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/wuErqVheVPpjhw</t>
   </si>
 </sst>
 </file>
@@ -34104,7 +34107,9 @@
       <c r="F1406" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="G1406" s="2"/>
+      <c r="G1406" s="2" t="s">
+        <v>2869</v>
+      </c>
       <c r="H1406" s="2"/>
     </row>
     <row r="1407" spans="1:8" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6809D8A9-90F7-41B0-BD28-0B0C254C0057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27491AF3-5A55-4A08-8343-F654687D8388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27390" yWindow="0" windowWidth="24315" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="2870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="2871">
   <si>
     <t>Пароль</t>
   </si>
@@ -8644,6 +8644,9 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/i/wuErqVheVPpjhw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/ibUZqU_nhxIpCQ</t>
   </si>
 </sst>
 </file>
@@ -34096,7 +34099,7 @@
         <v>79045010358</v>
       </c>
       <c r="C1406" s="2" t="s">
-        <v>731</v>
+        <v>2870</v>
       </c>
       <c r="D1406" s="2" t="s">
         <v>2867</v>
@@ -34136,7 +34139,7 @@
         <v>79281777077</v>
       </c>
       <c r="C1408" s="2" t="s">
-        <v>731</v>
+        <v>2870</v>
       </c>
       <c r="D1408" s="2"/>
       <c r="E1408" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27491AF3-5A55-4A08-8343-F654687D8388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352A2539-8A1E-47B2-90AE-38E8A4E0629E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27390" yWindow="0" windowWidth="24315" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="2871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="2873">
   <si>
     <t>Пароль</t>
   </si>
@@ -8647,6 +8647,12 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/ibUZqU_nhxIpCQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/N4tL1ZWCVGXOOw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/IalGJPwtzHP-MA</t>
   </si>
 </sst>
 </file>
@@ -34105,10 +34111,10 @@
         <v>2867</v>
       </c>
       <c r="E1406" s="2" t="s">
-        <v>731</v>
+        <v>2872</v>
       </c>
       <c r="F1406" s="2" t="s">
-        <v>731</v>
+        <v>2871</v>
       </c>
       <c r="G1406" s="2" t="s">
         <v>2869</v>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352A2539-8A1E-47B2-90AE-38E8A4E0629E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7681235C-F223-4F82-A14F-4DCACFA9DE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="0" windowWidth="24315" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23250" yWindow="0" windowWidth="28455" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="2873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4427" uniqueCount="2888">
   <si>
     <t>Пароль</t>
   </si>
@@ -8653,6 +8653,51 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/IalGJPwtzHP-MA</t>
+  </si>
+  <si>
+    <t>03/10/26/10:00</t>
+  </si>
+  <si>
+    <t>31643</t>
+  </si>
+  <si>
+    <t>03988</t>
+  </si>
+  <si>
+    <t>03/10/26/12:30</t>
+  </si>
+  <si>
+    <t>75008</t>
+  </si>
+  <si>
+    <t>10505</t>
+  </si>
+  <si>
+    <t>03/10/26/15:00</t>
+  </si>
+  <si>
+    <t>74373</t>
+  </si>
+  <si>
+    <t>55444</t>
+  </si>
+  <si>
+    <t>15068</t>
+  </si>
+  <si>
+    <t>* Раммиль</t>
+  </si>
+  <si>
+    <t>* ДимМа</t>
+  </si>
+  <si>
+    <t>* GoPro</t>
+  </si>
+  <si>
+    <t>* Рамиль</t>
+  </si>
+  <si>
+    <t>* все</t>
   </si>
 </sst>
 </file>
@@ -34156,15 +34201,25 @@
     <row r="1409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1409" s="7"/>
       <c r="B1409" s="16"/>
-      <c r="C1409" s="2"/>
-      <c r="D1409" s="2"/>
-      <c r="E1409" s="2"/>
-      <c r="F1409" s="2"/>
+      <c r="C1409" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1409" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1409" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1409" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1409" s="2"/>
       <c r="H1409" s="2"/>
     </row>
     <row r="1410" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1410" s="7"/>
+      <c r="A1410" s="37" t="s">
+        <v>2873</v>
+      </c>
       <c r="B1410" s="16"/>
       <c r="C1410" s="2"/>
       <c r="D1410" s="2"/>
@@ -34174,27 +34229,49 @@
       <c r="H1410" s="2"/>
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1411" s="7"/>
-      <c r="B1411" s="16"/>
-      <c r="C1411" s="2"/>
-      <c r="D1411" s="2"/>
-      <c r="E1411" s="2"/>
-      <c r="F1411" s="2"/>
+      <c r="A1411" s="7" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B1411" s="16">
+        <v>79034731643</v>
+      </c>
+      <c r="C1411" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1411" s="2" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E1411" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1411" s="2" t="s">
+        <v>2887</v>
+      </c>
       <c r="G1411" s="2"/>
       <c r="H1411" s="2"/>
     </row>
     <row r="1412" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1412" s="7"/>
-      <c r="B1412" s="16"/>
-      <c r="C1412" s="2"/>
-      <c r="D1412" s="2"/>
+      <c r="A1412" s="7" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B1412" s="16">
+        <v>79288803988</v>
+      </c>
+      <c r="C1412" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1412" s="2" t="s">
+        <v>2886</v>
+      </c>
       <c r="E1412" s="2"/>
       <c r="F1412" s="2"/>
       <c r="G1412" s="2"/>
       <c r="H1412" s="2"/>
     </row>
     <row r="1413" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1413" s="7"/>
+      <c r="A1413" s="37" t="s">
+        <v>2876</v>
+      </c>
       <c r="B1413" s="16"/>
       <c r="C1413" s="2"/>
       <c r="D1413" s="2"/>
@@ -34204,27 +34281,45 @@
       <c r="H1413" s="2"/>
     </row>
     <row r="1414" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1414" s="7"/>
-      <c r="B1414" s="16"/>
-      <c r="C1414" s="2"/>
-      <c r="D1414" s="2"/>
+      <c r="A1414" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="B1414" s="16">
+        <v>79184775008</v>
+      </c>
+      <c r="C1414" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1414" s="2" t="s">
+        <v>2885</v>
+      </c>
       <c r="E1414" s="2"/>
       <c r="F1414" s="2"/>
       <c r="G1414" s="2"/>
       <c r="H1414" s="2"/>
     </row>
     <row r="1415" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1415" s="7"/>
-      <c r="B1415" s="16"/>
-      <c r="C1415" s="2"/>
-      <c r="D1415" s="2"/>
+      <c r="A1415" s="7" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B1415" s="16">
+        <v>79185810505</v>
+      </c>
+      <c r="C1415" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1415" s="2" t="s">
+        <v>2884</v>
+      </c>
       <c r="E1415" s="2"/>
       <c r="F1415" s="2"/>
       <c r="G1415" s="2"/>
       <c r="H1415" s="2"/>
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1416" s="7"/>
+      <c r="A1416" s="37" t="s">
+        <v>2879</v>
+      </c>
       <c r="B1416" s="16"/>
       <c r="C1416" s="2"/>
       <c r="D1416" s="2"/>
@@ -34234,30 +34329,50 @@
       <c r="H1416" s="2"/>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1417" s="7"/>
-      <c r="B1417" s="16"/>
+      <c r="A1417" s="7" t="s">
+        <v>2880</v>
+      </c>
+      <c r="B1417" s="16">
+        <v>79876274373</v>
+      </c>
       <c r="C1417" s="2"/>
       <c r="D1417" s="2"/>
-      <c r="E1417" s="2"/>
-      <c r="F1417" s="2"/>
+      <c r="E1417" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1417" s="2" t="s">
+        <v>2884</v>
+      </c>
       <c r="G1417" s="2"/>
       <c r="H1417" s="2"/>
     </row>
     <row r="1418" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1418" s="7"/>
-      <c r="B1418" s="16"/>
+      <c r="A1418" s="7" t="s">
+        <v>2881</v>
+      </c>
+      <c r="B1418" s="16">
+        <v>79186355444</v>
+      </c>
       <c r="C1418" s="2"/>
-      <c r="D1418" s="2"/>
+      <c r="D1418" s="2" t="s">
+        <v>2883</v>
+      </c>
       <c r="E1418" s="2"/>
       <c r="F1418" s="2"/>
       <c r="G1418" s="2"/>
       <c r="H1418" s="2"/>
     </row>
     <row r="1419" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1419" s="7"/>
-      <c r="B1419" s="16"/>
+      <c r="A1419" s="7" t="s">
+        <v>2882</v>
+      </c>
+      <c r="B1419" s="16">
+        <v>79184115068</v>
+      </c>
       <c r="C1419" s="2"/>
-      <c r="D1419" s="2"/>
+      <c r="D1419" s="2" t="s">
+        <v>2883</v>
+      </c>
       <c r="E1419" s="2"/>
       <c r="F1419" s="2"/>
       <c r="G1419" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7681235C-F223-4F82-A14F-4DCACFA9DE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02555D0-6C87-40B8-9D56-A06FB87FAB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23250" yWindow="0" windowWidth="28455" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4427" uniqueCount="2888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4427" uniqueCount="2890">
   <si>
     <t>Пароль</t>
   </si>
@@ -8685,19 +8685,25 @@
     <t>15068</t>
   </si>
   <si>
-    <t>* Раммиль</t>
-  </si>
-  <si>
-    <t>* ДимМа</t>
-  </si>
-  <si>
-    <t>* GoPro</t>
-  </si>
-  <si>
-    <t>* Рамиль</t>
-  </si>
-  <si>
-    <t>* все</t>
+    <t>https://disk.yandex.ru/d/H16cXNgZqBsriQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/LStQOJB0hI90JA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/bFa575EnFoXuKQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/TliTFvn42_Ka_Q</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/P3RfTZQ35wqg1Q</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/s-YGfrgY2TEOKw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/k1lcHqoVYLYQBg</t>
   </si>
 </sst>
 </file>
@@ -34236,16 +34242,16 @@
         <v>79034731643</v>
       </c>
       <c r="C1411" s="2" t="s">
-        <v>731</v>
+        <v>2883</v>
       </c>
       <c r="D1411" s="2" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="E1411" s="2" t="s">
         <v>731</v>
       </c>
       <c r="F1411" s="2" t="s">
-        <v>2887</v>
+        <v>731</v>
       </c>
       <c r="G1411" s="2"/>
       <c r="H1411" s="2"/>
@@ -34258,10 +34264,10 @@
         <v>79288803988</v>
       </c>
       <c r="C1412" s="2" t="s">
-        <v>731</v>
+        <v>2883</v>
       </c>
       <c r="D1412" s="2" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="E1412" s="2"/>
       <c r="F1412" s="2"/>
@@ -34288,10 +34294,10 @@
         <v>79184775008</v>
       </c>
       <c r="C1414" s="2" t="s">
-        <v>731</v>
+        <v>2886</v>
       </c>
       <c r="D1414" s="2" t="s">
-        <v>2885</v>
+        <v>2887</v>
       </c>
       <c r="E1414" s="2"/>
       <c r="F1414" s="2"/>
@@ -34306,10 +34312,10 @@
         <v>79185810505</v>
       </c>
       <c r="C1415" s="2" t="s">
-        <v>731</v>
+        <v>2886</v>
       </c>
       <c r="D1415" s="2" t="s">
-        <v>2884</v>
+        <v>2889</v>
       </c>
       <c r="E1415" s="2"/>
       <c r="F1415" s="2"/>
@@ -34341,7 +34347,7 @@
         <v>731</v>
       </c>
       <c r="F1417" s="2" t="s">
-        <v>2884</v>
+        <v>731</v>
       </c>
       <c r="G1417" s="2"/>
       <c r="H1417" s="2"/>
@@ -34355,7 +34361,7 @@
       </c>
       <c r="C1418" s="2"/>
       <c r="D1418" s="2" t="s">
-        <v>2883</v>
+        <v>2888</v>
       </c>
       <c r="E1418" s="2"/>
       <c r="F1418" s="2"/>
@@ -34371,7 +34377,7 @@
       </c>
       <c r="C1419" s="2"/>
       <c r="D1419" s="2" t="s">
-        <v>2883</v>
+        <v>2888</v>
       </c>
       <c r="E1419" s="2"/>
       <c r="F1419" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02555D0-6C87-40B8-9D56-A06FB87FAB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8400D01-AF4E-41CF-9953-B691FC8FE14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23250" yWindow="0" windowWidth="28455" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4427" uniqueCount="2890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4427" uniqueCount="2894">
   <si>
     <t>Пароль</t>
   </si>
@@ -8704,6 +8704,18 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/k1lcHqoVYLYQBg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/MYOliQdh0iUpKw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/fyF1AoTo-PmSRA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/ef_dgOXXpFR7Tw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/QAXPhurJGmXlyw</t>
   </si>
 </sst>
 </file>
@@ -34248,10 +34260,10 @@
         <v>2884</v>
       </c>
       <c r="E1411" s="2" t="s">
-        <v>731</v>
+        <v>2892</v>
       </c>
       <c r="F1411" s="2" t="s">
-        <v>731</v>
+        <v>2890</v>
       </c>
       <c r="G1411" s="2"/>
       <c r="H1411" s="2"/>
@@ -34344,10 +34356,10 @@
       <c r="C1417" s="2"/>
       <c r="D1417" s="2"/>
       <c r="E1417" s="2" t="s">
-        <v>731</v>
+        <v>2893</v>
       </c>
       <c r="F1417" s="2" t="s">
-        <v>731</v>
+        <v>2891</v>
       </c>
       <c r="G1417" s="2"/>
       <c r="H1417" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8400D01-AF4E-41CF-9953-B691FC8FE14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C993A0-0136-42EE-A1F3-329D88EE3720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23250" yWindow="0" windowWidth="28455" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23415" yWindow="0" windowWidth="28290" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4427" uniqueCount="2894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4440" uniqueCount="2901">
   <si>
     <t>Пароль</t>
   </si>
@@ -8716,6 +8716,27 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/QAXPhurJGmXlyw</t>
+  </si>
+  <si>
+    <t>41001</t>
+  </si>
+  <si>
+    <t>46645</t>
+  </si>
+  <si>
+    <t>62953</t>
+  </si>
+  <si>
+    <t>04/10/26/10:00</t>
+  </si>
+  <si>
+    <t>04/10/26/12:30</t>
+  </si>
+  <si>
+    <t>45838</t>
+  </si>
+  <si>
+    <t>80763</t>
   </si>
 </sst>
 </file>
@@ -34397,7 +34418,9 @@
       <c r="H1419" s="2"/>
     </row>
     <row r="1420" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1420" s="7"/>
+      <c r="A1420" s="37" t="s">
+        <v>2897</v>
+      </c>
       <c r="B1420" s="16"/>
       <c r="C1420" s="2"/>
       <c r="D1420" s="2"/>
@@ -34407,9 +34430,15 @@
       <c r="H1420" s="2"/>
     </row>
     <row r="1421" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1421" s="7"/>
-      <c r="B1421" s="16"/>
-      <c r="C1421" s="2"/>
+      <c r="A1421" s="7" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B1421" s="16">
+        <v>79287641001</v>
+      </c>
+      <c r="C1421" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="D1421" s="2"/>
       <c r="E1421" s="2"/>
       <c r="F1421" s="2"/>
@@ -34417,19 +34446,33 @@
       <c r="H1421" s="2"/>
     </row>
     <row r="1422" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1422" s="7"/>
-      <c r="B1422" s="16"/>
-      <c r="C1422" s="2"/>
-      <c r="D1422" s="2"/>
+      <c r="A1422" s="7" t="s">
+        <v>2895</v>
+      </c>
+      <c r="B1422" s="16">
+        <v>79384046645</v>
+      </c>
+      <c r="C1422" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1422" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="E1422" s="2"/>
       <c r="F1422" s="2"/>
       <c r="G1422" s="2"/>
       <c r="H1422" s="2"/>
     </row>
     <row r="1423" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1423" s="7"/>
-      <c r="B1423" s="16"/>
-      <c r="C1423" s="2"/>
+      <c r="A1423" s="7" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B1423" s="16">
+        <v>79525762953</v>
+      </c>
+      <c r="C1423" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="D1423" s="2"/>
       <c r="E1423" s="2"/>
       <c r="F1423" s="2"/>
@@ -34437,7 +34480,9 @@
       <c r="H1423" s="2"/>
     </row>
     <row r="1424" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1424" s="7"/>
+      <c r="A1424" s="37" t="s">
+        <v>2898</v>
+      </c>
       <c r="B1424" s="16"/>
       <c r="C1424" s="2"/>
       <c r="D1424" s="2"/>
@@ -34447,20 +34492,32 @@
       <c r="H1424" s="2"/>
     </row>
     <row r="1425" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1425" s="7"/>
-      <c r="B1425" s="16"/>
+      <c r="A1425" s="7" t="s">
+        <v>2899</v>
+      </c>
+      <c r="B1425" s="16">
+        <v>79873945838</v>
+      </c>
       <c r="C1425" s="2"/>
-      <c r="D1425" s="2"/>
+      <c r="D1425" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="E1425" s="2"/>
       <c r="F1425" s="2"/>
       <c r="G1425" s="2"/>
       <c r="H1425" s="2"/>
     </row>
     <row r="1426" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1426" s="7"/>
-      <c r="B1426" s="16"/>
+      <c r="A1426" s="7" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B1426" s="16">
+        <v>79515080763</v>
+      </c>
       <c r="C1426" s="2"/>
-      <c r="D1426" s="2"/>
+      <c r="D1426" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="E1426" s="2"/>
       <c r="F1426" s="2"/>
       <c r="G1426" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C993A0-0136-42EE-A1F3-329D88EE3720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E7395F-C206-4B2D-B546-CB28B8560B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23415" yWindow="0" windowWidth="28290" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4440" uniqueCount="2901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4440" uniqueCount="2905">
   <si>
     <t>Пароль</t>
   </si>
@@ -8737,6 +8737,18 @@
   </si>
   <si>
     <t>80763</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/LM1xkfA1zVRStQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/-AUsdYdpCqiMZw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/0HqNtWNdxci9nQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/-LUiogjILPZcVA</t>
   </si>
 </sst>
 </file>
@@ -34437,7 +34449,7 @@
         <v>79287641001</v>
       </c>
       <c r="C1421" s="2" t="s">
-        <v>731</v>
+        <v>2901</v>
       </c>
       <c r="D1421" s="2"/>
       <c r="E1421" s="2"/>
@@ -34453,10 +34465,10 @@
         <v>79384046645</v>
       </c>
       <c r="C1422" s="2" t="s">
-        <v>731</v>
+        <v>2901</v>
       </c>
       <c r="D1422" s="2" t="s">
-        <v>731</v>
+        <v>2902</v>
       </c>
       <c r="E1422" s="2"/>
       <c r="F1422" s="2"/>
@@ -34471,7 +34483,7 @@
         <v>79525762953</v>
       </c>
       <c r="C1423" s="2" t="s">
-        <v>731</v>
+        <v>2901</v>
       </c>
       <c r="D1423" s="2"/>
       <c r="E1423" s="2"/>
@@ -34500,7 +34512,7 @@
       </c>
       <c r="C1425" s="2"/>
       <c r="D1425" s="2" t="s">
-        <v>731</v>
+        <v>2903</v>
       </c>
       <c r="E1425" s="2"/>
       <c r="F1425" s="2"/>
@@ -34516,7 +34528,7 @@
       </c>
       <c r="C1426" s="2"/>
       <c r="D1426" s="2" t="s">
-        <v>731</v>
+        <v>2904</v>
       </c>
       <c r="E1426" s="2"/>
       <c r="F1426" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD149042-2052-4A9C-BC64-EB103321D212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1748153F-50F9-4BBE-83DB-C3E7FE4A05CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26835" yWindow="0" windowWidth="24870" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4440" uniqueCount="2904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4443" uniqueCount="2907">
   <si>
     <t>Пароль</t>
   </si>
@@ -8746,6 +8746,15 @@
   </si>
   <si>
     <t>/?32351</t>
+  </si>
+  <si>
+    <t>05/10/26/12:30</t>
+  </si>
+  <si>
+    <t>60254</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/I8kM1RYj9TpuMQ</t>
   </si>
 </sst>
 </file>
@@ -34533,7 +34542,9 @@
       <c r="H1426" s="2"/>
     </row>
     <row r="1427" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1427" s="7"/>
+      <c r="A1427" s="37" t="s">
+        <v>2904</v>
+      </c>
       <c r="B1427" s="16"/>
       <c r="C1427" s="2"/>
       <c r="D1427" s="2"/>
@@ -34543,10 +34554,16 @@
       <c r="H1427" s="2"/>
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1428" s="7"/>
-      <c r="B1428" s="16"/>
+      <c r="A1428" s="7" t="s">
+        <v>2905</v>
+      </c>
+      <c r="B1428" s="16">
+        <v>79588660254</v>
+      </c>
       <c r="C1428" s="2"/>
-      <c r="D1428" s="2"/>
+      <c r="D1428" s="2" t="s">
+        <v>2906</v>
+      </c>
       <c r="E1428" s="2"/>
       <c r="F1428" s="2"/>
       <c r="G1428" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1748153F-50F9-4BBE-83DB-C3E7FE4A05CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F90F1E-C1BB-4B0B-A0BF-0CFABAE7DAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4443" uniqueCount="2907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4452" uniqueCount="2912">
   <si>
     <t>Пароль</t>
   </si>
@@ -6567,42 +6567,12 @@
     <t>06/09/26/10:00</t>
   </si>
   <si>
-    <t>19741</t>
-  </si>
-  <si>
-    <t>60798</t>
-  </si>
-  <si>
-    <t>01223</t>
-  </si>
-  <si>
-    <t>31040</t>
-  </si>
-  <si>
-    <t>77747</t>
-  </si>
-  <si>
     <t>06/09/26/12:30</t>
   </si>
   <si>
-    <t>78847</t>
-  </si>
-  <si>
-    <t>46962</t>
-  </si>
-  <si>
     <t>06/09/26/15:00</t>
   </si>
   <si>
-    <t>93781</t>
-  </si>
-  <si>
-    <t>51355</t>
-  </si>
-  <si>
-    <t>40670</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/fwV95TPRAXiGVA</t>
   </si>
   <si>
@@ -6672,21 +6642,9 @@
     <t>07/09/26/10:00</t>
   </si>
   <si>
-    <t>71177</t>
-  </si>
-  <si>
-    <t>01442</t>
-  </si>
-  <si>
     <t>07/09/26/12:30</t>
   </si>
   <si>
-    <t>08008</t>
-  </si>
-  <si>
-    <t>78862</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/d/cBxI9oVWs89QnA</t>
   </si>
   <si>
@@ -8755,6 +8713,63 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/I8kM1RYj9TpuMQ</t>
+  </si>
+  <si>
+    <t>06/10/26/12:30</t>
+  </si>
+  <si>
+    <t>91506</t>
+  </si>
+  <si>
+    <t>77062</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/WBEzhF4rXmDyrg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/CFgtRJGq7HAwrw</t>
+  </si>
+  <si>
+    <t>/?19741</t>
+  </si>
+  <si>
+    <t>/?60798</t>
+  </si>
+  <si>
+    <t>/?01223</t>
+  </si>
+  <si>
+    <t>/?31040</t>
+  </si>
+  <si>
+    <t>/?77747</t>
+  </si>
+  <si>
+    <t>/?78847</t>
+  </si>
+  <si>
+    <t>/?46962</t>
+  </si>
+  <si>
+    <t>/?93781</t>
+  </si>
+  <si>
+    <t>/?51355</t>
+  </si>
+  <si>
+    <t>/?40670</t>
+  </si>
+  <si>
+    <t>/?71177</t>
+  </si>
+  <si>
+    <t>/?01442</t>
+  </si>
+  <si>
+    <t>/?08008</t>
+  </si>
+  <si>
+    <t>/?78862</t>
   </si>
 </sst>
 </file>
@@ -24596,7 +24611,7 @@
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" s="32" t="s">
-        <v>2205</v>
+        <v>2195</v>
       </c>
       <c r="B838" s="38">
         <v>79192492486</v>
@@ -24614,7 +24629,7 @@
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" s="32" t="s">
-        <v>2206</v>
+        <v>2196</v>
       </c>
       <c r="B839" s="38">
         <v>79182131150</v>
@@ -24630,7 +24645,7 @@
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" s="32" t="s">
-        <v>2207</v>
+        <v>2197</v>
       </c>
       <c r="B840" s="38">
         <v>79275956177</v>
@@ -24670,7 +24685,7 @@
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" s="32" t="s">
-        <v>2208</v>
+        <v>2198</v>
       </c>
       <c r="B842" s="38">
         <v>79851997751</v>
@@ -24686,7 +24701,7 @@
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" s="32" t="s">
-        <v>2209</v>
+        <v>2199</v>
       </c>
       <c r="B843" s="38">
         <v>79282164434</v>
@@ -24702,7 +24717,7 @@
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" s="32" t="s">
-        <v>2210</v>
+        <v>2200</v>
       </c>
       <c r="B844" s="38">
         <v>79109617700</v>
@@ -24762,7 +24777,7 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" s="32" t="s">
-        <v>2228</v>
+        <v>2214</v>
       </c>
       <c r="B847" s="38">
         <v>79185972895</v>
@@ -24784,7 +24799,7 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" s="32" t="s">
-        <v>2229</v>
+        <v>2215</v>
       </c>
       <c r="B848" s="38">
         <v>79996262825</v>
@@ -24806,7 +24821,7 @@
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" s="32" t="s">
-        <v>2208</v>
+        <v>2198</v>
       </c>
       <c r="B849" s="38">
         <v>79851997751</v>
@@ -24828,7 +24843,7 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" s="32" t="s">
-        <v>2230</v>
+        <v>2216</v>
       </c>
       <c r="B850" s="38">
         <v>79604875670</v>
@@ -24850,7 +24865,7 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" s="32" t="s">
-        <v>2231</v>
+        <v>2217</v>
       </c>
       <c r="B851" s="38">
         <v>79184987541</v>
@@ -24868,7 +24883,7 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" s="32" t="s">
-        <v>2232</v>
+        <v>2218</v>
       </c>
       <c r="B852" s="38">
         <v>79185058918</v>
@@ -24884,7 +24899,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" s="32" t="s">
-        <v>2233</v>
+        <v>2219</v>
       </c>
       <c r="B853" s="38">
         <v>79084845045</v>
@@ -24904,7 +24919,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" s="32" t="s">
-        <v>2234</v>
+        <v>2220</v>
       </c>
       <c r="B854" s="38">
         <v>79189841111</v>
@@ -24920,7 +24935,7 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" s="32" t="s">
-        <v>2235</v>
+        <v>2221</v>
       </c>
       <c r="B855" s="38">
         <v>79183593299</v>
@@ -24942,7 +24957,7 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" s="32" t="s">
-        <v>2236</v>
+        <v>2222</v>
       </c>
       <c r="B856" s="38">
         <v>79286104433</v>
@@ -24960,7 +24975,7 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" s="32" t="s">
-        <v>2237</v>
+        <v>2223</v>
       </c>
       <c r="B857" s="38">
         <v>79181204920</v>
@@ -24978,7 +24993,7 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" s="32" t="s">
-        <v>2238</v>
+        <v>2224</v>
       </c>
       <c r="B858" s="38">
         <v>79180314664</v>
@@ -24996,7 +25011,7 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" s="32" t="s">
-        <v>2239</v>
+        <v>2225</v>
       </c>
       <c r="B859" s="38">
         <v>79255304182</v>
@@ -25014,7 +25029,7 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" s="32" t="s">
-        <v>2240</v>
+        <v>2226</v>
       </c>
       <c r="B860" s="38">
         <v>79624321777</v>
@@ -25032,7 +25047,7 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" s="32" t="s">
-        <v>2241</v>
+        <v>2227</v>
       </c>
       <c r="B861" s="38">
         <v>79034652185</v>
@@ -25048,7 +25063,7 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" s="32" t="s">
-        <v>2242</v>
+        <v>2228</v>
       </c>
       <c r="B862" s="38">
         <v>79654707870</v>
@@ -25082,7 +25097,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" s="32" t="s">
-        <v>2243</v>
+        <v>2229</v>
       </c>
       <c r="B864" s="38">
         <v>79284244414</v>
@@ -25102,7 +25117,7 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" s="32" t="s">
-        <v>2244</v>
+        <v>2230</v>
       </c>
       <c r="B865" s="38">
         <v>79619719206</v>
@@ -25122,7 +25137,7 @@
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" s="32" t="s">
-        <v>2245</v>
+        <v>2231</v>
       </c>
       <c r="B866" s="38">
         <v>79530872704</v>
@@ -25178,7 +25193,7 @@
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" s="32" t="s">
-        <v>2246</v>
+        <v>2232</v>
       </c>
       <c r="B869" s="38">
         <v>79181112526</v>
@@ -25196,7 +25211,7 @@
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" s="18" t="s">
-        <v>2247</v>
+        <v>2233</v>
       </c>
       <c r="B870" s="39">
         <v>79186726140</v>
@@ -25236,7 +25251,7 @@
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" s="32" t="s">
-        <v>2248</v>
+        <v>2234</v>
       </c>
       <c r="B872" s="38">
         <v>79283003384</v>
@@ -25254,7 +25269,7 @@
     </row>
     <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" s="32" t="s">
-        <v>2249</v>
+        <v>2235</v>
       </c>
       <c r="B873" s="38">
         <v>79682666663</v>
@@ -25270,7 +25285,7 @@
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" s="32" t="s">
-        <v>2247</v>
+        <v>2233</v>
       </c>
       <c r="B874" s="38">
         <v>79186726140</v>
@@ -25288,7 +25303,7 @@
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" s="32" t="s">
-        <v>2250</v>
+        <v>2236</v>
       </c>
       <c r="B875" s="38">
         <v>79898051733</v>
@@ -25306,7 +25321,7 @@
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" s="32" t="s">
-        <v>2251</v>
+        <v>2237</v>
       </c>
       <c r="B876" s="38">
         <v>79086789121</v>
@@ -25322,7 +25337,7 @@
     </row>
     <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" s="32" t="s">
-        <v>2252</v>
+        <v>2238</v>
       </c>
       <c r="B877" s="38">
         <v>79528340083</v>
@@ -25338,7 +25353,7 @@
     </row>
     <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" s="32" t="s">
-        <v>2253</v>
+        <v>2239</v>
       </c>
       <c r="B878" s="38">
         <v>79530930717</v>
@@ -25356,7 +25371,7 @@
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" s="32" t="s">
-        <v>2254</v>
+        <v>2240</v>
       </c>
       <c r="B879" s="38">
         <v>79275037361</v>
@@ -25372,7 +25387,7 @@
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" s="32" t="s">
-        <v>2255</v>
+        <v>2241</v>
       </c>
       <c r="B880" s="38">
         <v>79218083526</v>
@@ -25388,7 +25403,7 @@
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" s="32" t="s">
-        <v>2256</v>
+        <v>2242</v>
       </c>
       <c r="B881" s="38">
         <v>79185789000</v>
@@ -25408,7 +25423,7 @@
     </row>
     <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" s="32" t="s">
-        <v>2257</v>
+        <v>2243</v>
       </c>
       <c r="B882" s="38">
         <v>79877941509</v>
@@ -25426,7 +25441,7 @@
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" s="32" t="s">
-        <v>2258</v>
+        <v>2244</v>
       </c>
       <c r="B883" s="38">
         <v>79618221503</v>
@@ -25466,7 +25481,7 @@
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" s="32" t="s">
-        <v>2316</v>
+        <v>2302</v>
       </c>
       <c r="B885" s="38">
         <v>79882548579</v>
@@ -25484,7 +25499,7 @@
     </row>
     <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" s="32" t="s">
-        <v>2317</v>
+        <v>2303</v>
       </c>
       <c r="B886" s="38">
         <v>79182900595</v>
@@ -25500,7 +25515,7 @@
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" s="32" t="s">
-        <v>2318</v>
+        <v>2304</v>
       </c>
       <c r="B887" s="38">
         <v>79264823431</v>
@@ -25518,7 +25533,7 @@
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" s="32" t="s">
-        <v>2319</v>
+        <v>2305</v>
       </c>
       <c r="B888" s="38">
         <v>79180246728</v>
@@ -25536,7 +25551,7 @@
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" s="32" t="s">
-        <v>2320</v>
+        <v>2306</v>
       </c>
       <c r="B889" s="38">
         <v>79263181485</v>
@@ -25552,7 +25567,7 @@
     </row>
     <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" s="32" t="s">
-        <v>2321</v>
+        <v>2307</v>
       </c>
       <c r="B890" s="38">
         <v>79189573595</v>
@@ -25570,7 +25585,7 @@
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" s="32" t="s">
-        <v>2322</v>
+        <v>2308</v>
       </c>
       <c r="B891" s="38">
         <v>79180129312</v>
@@ -25610,7 +25625,7 @@
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" s="32" t="s">
-        <v>2323</v>
+        <v>2309</v>
       </c>
       <c r="B893" s="38">
         <v>79207020082</v>
@@ -25632,7 +25647,7 @@
     </row>
     <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" s="32" t="s">
-        <v>2324</v>
+        <v>2310</v>
       </c>
       <c r="B894" s="38">
         <v>79185072237</v>
@@ -25650,7 +25665,7 @@
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" s="32" t="s">
-        <v>2325</v>
+        <v>2311</v>
       </c>
       <c r="B895" s="38">
         <v>79182762440</v>
@@ -25666,7 +25681,7 @@
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" s="32" t="s">
-        <v>2326</v>
+        <v>2312</v>
       </c>
       <c r="B896" s="38">
         <v>79518702052</v>
@@ -25682,7 +25697,7 @@
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" s="32" t="s">
-        <v>2327</v>
+        <v>2313</v>
       </c>
       <c r="B897" s="38">
         <v>79885456732</v>
@@ -25698,7 +25713,7 @@
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" s="32" t="s">
-        <v>2328</v>
+        <v>2314</v>
       </c>
       <c r="B898" s="38">
         <v>79186323631</v>
@@ -25736,7 +25751,7 @@
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" s="32" t="s">
-        <v>2329</v>
+        <v>2315</v>
       </c>
       <c r="B900" s="38">
         <v>79604946540</v>
@@ -25756,7 +25771,7 @@
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" s="32" t="s">
-        <v>2330</v>
+        <v>2316</v>
       </c>
       <c r="B901" s="38">
         <v>79787713176</v>
@@ -25800,7 +25815,7 @@
     </row>
     <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" s="32" t="s">
-        <v>2331</v>
+        <v>2317</v>
       </c>
       <c r="B903" s="38">
         <v>79881380533</v>
@@ -25816,7 +25831,7 @@
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" s="32" t="s">
-        <v>2332</v>
+        <v>2318</v>
       </c>
       <c r="B904" s="38">
         <v>79876571770</v>
@@ -25838,7 +25853,7 @@
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" s="32" t="s">
-        <v>2333</v>
+        <v>2319</v>
       </c>
       <c r="B905" s="38">
         <v>79185269969</v>
@@ -25860,7 +25875,7 @@
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" s="32" t="s">
-        <v>2334</v>
+        <v>2320</v>
       </c>
       <c r="B906" s="38">
         <v>79788069407</v>
@@ -25882,7 +25897,7 @@
     </row>
     <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" s="32" t="s">
-        <v>2335</v>
+        <v>2321</v>
       </c>
       <c r="B907" s="38">
         <v>79809148895</v>
@@ -25904,7 +25919,7 @@
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" s="32" t="s">
-        <v>2336</v>
+        <v>2322</v>
       </c>
       <c r="B908" s="38">
         <v>79374600054</v>
@@ -25942,7 +25957,7 @@
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" s="32" t="s">
-        <v>2337</v>
+        <v>2323</v>
       </c>
       <c r="B910" s="38">
         <v>79063480196</v>
@@ -25960,7 +25975,7 @@
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" s="32" t="s">
-        <v>2326</v>
+        <v>2312</v>
       </c>
       <c r="B911" s="38">
         <v>79035002052</v>
@@ -25980,7 +25995,7 @@
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" s="32" t="s">
-        <v>2338</v>
+        <v>2324</v>
       </c>
       <c r="B912" s="38">
         <v>79883667602</v>
@@ -26000,7 +26015,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A913" s="32" t="s">
-        <v>2339</v>
+        <v>2325</v>
       </c>
       <c r="B913" s="38">
         <v>79991733748</v>
@@ -26016,7 +26031,7 @@
     </row>
     <row r="914" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A914" s="32" t="s">
-        <v>2340</v>
+        <v>2326</v>
       </c>
       <c r="B914" s="38">
         <v>79168542102</v>
@@ -26036,7 +26051,7 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A915" s="32" t="s">
-        <v>2341</v>
+        <v>2327</v>
       </c>
       <c r="B915" s="38">
         <v>79888928388</v>
@@ -26056,7 +26071,7 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A916" s="32" t="s">
-        <v>2342</v>
+        <v>2328</v>
       </c>
       <c r="B916" s="38">
         <v>79032374317</v>
@@ -26098,7 +26113,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A918" s="32" t="s">
-        <v>2323</v>
+        <v>2309</v>
       </c>
       <c r="B918" s="38">
         <v>79207020082</v>
@@ -26121,7 +26136,7 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A919" s="32" t="s">
-        <v>2343</v>
+        <v>2329</v>
       </c>
       <c r="B919" s="38">
         <v>79041183867</v>
@@ -26142,7 +26157,7 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A920" s="32" t="s">
-        <v>2344</v>
+        <v>2330</v>
       </c>
       <c r="B920" s="38">
         <v>79032978483</v>
@@ -26163,7 +26178,7 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A921" s="32" t="s">
-        <v>2345</v>
+        <v>2331</v>
       </c>
       <c r="B921" s="38">
         <v>79308038836</v>
@@ -26186,7 +26201,7 @@
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A922" s="32" t="s">
-        <v>2346</v>
+        <v>2332</v>
       </c>
       <c r="B922" s="38">
         <v>79385488845</v>
@@ -26209,7 +26224,7 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A923" s="32" t="s">
-        <v>2347</v>
+        <v>2333</v>
       </c>
       <c r="B923" s="38">
         <v>79046838139</v>
@@ -26230,7 +26245,7 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A924" s="32" t="s">
-        <v>2348</v>
+        <v>2334</v>
       </c>
       <c r="B924" s="38">
         <v>79128268207</v>
@@ -26253,7 +26268,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A925" s="32" t="s">
-        <v>2349</v>
+        <v>2335</v>
       </c>
       <c r="B925" s="38">
         <v>79148261215</v>
@@ -26276,7 +26291,7 @@
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A926" s="32" t="s">
-        <v>2350</v>
+        <v>2336</v>
       </c>
       <c r="B926" s="38">
         <v>79267823227</v>
@@ -26297,7 +26312,7 @@
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A927" s="32" t="s">
-        <v>2351</v>
+        <v>2337</v>
       </c>
       <c r="B927" s="38">
         <v>79184915237</v>
@@ -26322,7 +26337,7 @@
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A928" s="32" t="s">
-        <v>2352</v>
+        <v>2338</v>
       </c>
       <c r="B928" s="38">
         <v>79034390003</v>
@@ -26369,7 +26384,7 @@
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" s="32" t="s">
-        <v>2353</v>
+        <v>2339</v>
       </c>
       <c r="B930" s="38">
         <v>79595062068</v>
@@ -26425,7 +26440,7 @@
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" s="32" t="s">
-        <v>2428</v>
+        <v>2414</v>
       </c>
       <c r="B933" s="38">
         <v>79180664535</v>
@@ -26443,7 +26458,7 @@
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" s="32" t="s">
-        <v>2429</v>
+        <v>2415</v>
       </c>
       <c r="B934" s="38">
         <v>79197382450</v>
@@ -26463,7 +26478,7 @@
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" s="32" t="s">
-        <v>2430</v>
+        <v>2416</v>
       </c>
       <c r="B935" s="38">
         <v>79885220528</v>
@@ -26485,7 +26500,7 @@
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" s="32" t="s">
-        <v>2431</v>
+        <v>2417</v>
       </c>
       <c r="B936" s="38">
         <v>79885093331</v>
@@ -26529,7 +26544,7 @@
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" s="32" t="s">
-        <v>2432</v>
+        <v>2418</v>
       </c>
       <c r="B938" s="38">
         <v>79184400178</v>
@@ -26551,7 +26566,7 @@
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" s="32" t="s">
-        <v>2433</v>
+        <v>2419</v>
       </c>
       <c r="B939" s="38">
         <v>79183270587</v>
@@ -26569,7 +26584,7 @@
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" s="32" t="s">
-        <v>2434</v>
+        <v>2420</v>
       </c>
       <c r="B940" s="38">
         <v>79183889940</v>
@@ -26587,7 +26602,7 @@
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" s="32" t="s">
-        <v>2435</v>
+        <v>2421</v>
       </c>
       <c r="B941" s="38">
         <v>79994722206</v>
@@ -26603,7 +26618,7 @@
     </row>
     <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" s="32" t="s">
-        <v>2436</v>
+        <v>2422</v>
       </c>
       <c r="B942" s="38">
         <v>79184165266</v>
@@ -26643,7 +26658,7 @@
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" s="32" t="s">
-        <v>2437</v>
+        <v>2423</v>
       </c>
       <c r="B944" s="38">
         <v>79160231803</v>
@@ -26661,7 +26676,7 @@
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" s="32" t="s">
-        <v>2438</v>
+        <v>2424</v>
       </c>
       <c r="B945" s="38">
         <v>79251587458</v>
@@ -26679,7 +26694,7 @@
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" s="32" t="s">
-        <v>2439</v>
+        <v>2425</v>
       </c>
       <c r="B946" s="38">
         <v>79385519412</v>
@@ -26785,7 +26800,7 @@
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" s="32" t="s">
-        <v>2440</v>
+        <v>2426</v>
       </c>
       <c r="B952" s="33">
         <v>79895106888</v>
@@ -26801,7 +26816,7 @@
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" s="32" t="s">
-        <v>2441</v>
+        <v>2427</v>
       </c>
       <c r="B953" s="33">
         <v>79189487859</v>
@@ -26819,7 +26834,7 @@
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" s="32" t="s">
-        <v>2442</v>
+        <v>2428</v>
       </c>
       <c r="B954" s="33">
         <v>79094690279</v>
@@ -26839,7 +26854,7 @@
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" s="32" t="s">
-        <v>2443</v>
+        <v>2429</v>
       </c>
       <c r="B955" s="33">
         <v>79270465755</v>
@@ -26859,7 +26874,7 @@
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" s="32" t="s">
-        <v>2444</v>
+        <v>2430</v>
       </c>
       <c r="B956" s="33">
         <v>79181514761</v>
@@ -26891,7 +26906,7 @@
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" s="32" t="s">
-        <v>2445</v>
+        <v>2431</v>
       </c>
       <c r="B958" s="33">
         <v>79286120337</v>
@@ -26911,7 +26926,7 @@
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" s="32" t="s">
-        <v>2446</v>
+        <v>2432</v>
       </c>
       <c r="B959" s="33">
         <v>79181603172</v>
@@ -26929,7 +26944,7 @@
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" s="32" t="s">
-        <v>2447</v>
+        <v>2433</v>
       </c>
       <c r="B960" s="33">
         <v>79528474569</v>
@@ -26947,7 +26962,7 @@
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" s="32" t="s">
-        <v>2448</v>
+        <v>2434</v>
       </c>
       <c r="B961" s="33">
         <v>79891443888</v>
@@ -26975,7 +26990,7 @@
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" s="32" t="s">
-        <v>2449</v>
+        <v>2435</v>
       </c>
       <c r="B963" s="33">
         <v>79186956626</v>
@@ -26991,7 +27006,7 @@
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" s="32" t="s">
-        <v>2450</v>
+        <v>2436</v>
       </c>
       <c r="B964" s="33">
         <v>79183433464</v>
@@ -27009,7 +27024,7 @@
     </row>
     <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" s="32" t="s">
-        <v>2451</v>
+        <v>2437</v>
       </c>
       <c r="B965" s="33">
         <v>79094646000</v>
@@ -27025,7 +27040,7 @@
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" s="32" t="s">
-        <v>2452</v>
+        <v>2438</v>
       </c>
       <c r="B966" s="33">
         <v>79854264076</v>
@@ -27041,7 +27056,7 @@
     </row>
     <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" s="32" t="s">
-        <v>2453</v>
+        <v>2439</v>
       </c>
       <c r="B967" s="33">
         <v>79186525585</v>
@@ -27057,7 +27072,7 @@
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" s="32" t="s">
-        <v>2454</v>
+        <v>2440</v>
       </c>
       <c r="B968" s="33">
         <v>79528581269</v>
@@ -27077,7 +27092,7 @@
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" s="32" t="s">
-        <v>2455</v>
+        <v>2441</v>
       </c>
       <c r="B969" s="33">
         <v>79673053030</v>
@@ -27107,7 +27122,7 @@
     </row>
     <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" s="32" t="s">
-        <v>2456</v>
+        <v>2442</v>
       </c>
       <c r="B971" s="33">
         <v>79886696618</v>
@@ -27257,7 +27272,7 @@
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" s="32" t="s">
-        <v>2457</v>
+        <v>2443</v>
       </c>
       <c r="B978" s="33">
         <v>79117974075</v>
@@ -27275,7 +27290,7 @@
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" s="32" t="s">
-        <v>2458</v>
+        <v>2444</v>
       </c>
       <c r="B979" s="33">
         <v>79615951401</v>
@@ -27293,7 +27308,7 @@
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" s="32" t="s">
-        <v>2459</v>
+        <v>2445</v>
       </c>
       <c r="B980" s="33">
         <v>79274773218</v>
@@ -27311,7 +27326,7 @@
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" s="32" t="s">
-        <v>2460</v>
+        <v>2446</v>
       </c>
       <c r="B981" s="33">
         <v>79673005052</v>
@@ -27329,7 +27344,7 @@
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" s="32" t="s">
-        <v>2461</v>
+        <v>2447</v>
       </c>
       <c r="B982" s="33">
         <v>79625245851</v>
@@ -27347,7 +27362,7 @@
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" s="32" t="s">
-        <v>2462</v>
+        <v>2448</v>
       </c>
       <c r="B983" s="33">
         <v>79898052605</v>
@@ -27365,7 +27380,7 @@
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" s="32" t="s">
-        <v>2463</v>
+        <v>2449</v>
       </c>
       <c r="B984" s="33">
         <v>79992365729</v>
@@ -27407,7 +27422,7 @@
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" s="32" t="s">
-        <v>2464</v>
+        <v>2450</v>
       </c>
       <c r="B986" s="38">
         <v>79182119543</v>
@@ -27423,7 +27438,7 @@
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" s="32" t="s">
-        <v>2465</v>
+        <v>2451</v>
       </c>
       <c r="B987" s="38">
         <v>79886039199</v>
@@ -27443,7 +27458,7 @@
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" s="32" t="s">
-        <v>2466</v>
+        <v>2452</v>
       </c>
       <c r="B988" s="38">
         <v>79182846179</v>
@@ -27461,7 +27476,7 @@
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" s="32" t="s">
-        <v>2467</v>
+        <v>2453</v>
       </c>
       <c r="B989" s="38">
         <v>79185545589</v>
@@ -27479,7 +27494,7 @@
     </row>
     <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" s="32" t="s">
-        <v>2468</v>
+        <v>2454</v>
       </c>
       <c r="B990" s="38">
         <v>79637505138</v>
@@ -27495,7 +27510,7 @@
     </row>
     <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" s="32" t="s">
-        <v>2469</v>
+        <v>2455</v>
       </c>
       <c r="B991" s="38">
         <v>79604757152</v>
@@ -27513,7 +27528,7 @@
     </row>
     <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" s="32" t="s">
-        <v>2470</v>
+        <v>2456</v>
       </c>
       <c r="B992" s="38">
         <v>79182762782</v>
@@ -27555,7 +27570,7 @@
     </row>
     <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" s="32" t="s">
-        <v>2471</v>
+        <v>2457</v>
       </c>
       <c r="B994" s="38">
         <v>79892941007</v>
@@ -27571,7 +27586,7 @@
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" s="32" t="s">
-        <v>2472</v>
+        <v>2458</v>
       </c>
       <c r="B995" s="38">
         <v>79060896267</v>
@@ -27591,7 +27606,7 @@
     </row>
     <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" s="32" t="s">
-        <v>2473</v>
+        <v>2459</v>
       </c>
       <c r="B996" s="38">
         <v>79384227276</v>
@@ -27631,7 +27646,7 @@
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" s="32" t="s">
-        <v>2474</v>
+        <v>2460</v>
       </c>
       <c r="B998" s="38">
         <v>79614238176</v>
@@ -27659,7 +27674,7 @@
     </row>
     <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" s="32" t="s">
-        <v>2475</v>
+        <v>2461</v>
       </c>
       <c r="B1000" s="38">
         <v>79280121007</v>
@@ -27687,7 +27702,7 @@
     </row>
     <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" s="32" t="s">
-        <v>2476</v>
+        <v>2462</v>
       </c>
       <c r="B1002" s="38">
         <v>79180985165</v>
@@ -27703,7 +27718,7 @@
     </row>
     <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" s="32" t="s">
-        <v>2477</v>
+        <v>2463</v>
       </c>
       <c r="B1003" s="38">
         <v>79186200028</v>
@@ -27719,7 +27734,7 @@
     </row>
     <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" s="32" t="s">
-        <v>2478</v>
+        <v>2464</v>
       </c>
       <c r="B1004" s="38">
         <v>79190278727</v>
@@ -27747,7 +27762,7 @@
     </row>
     <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" s="32" t="s">
-        <v>2479</v>
+        <v>2465</v>
       </c>
       <c r="B1006" s="38">
         <v>79615280373</v>
@@ -27763,7 +27778,7 @@
     </row>
     <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1007" s="32" t="s">
-        <v>2480</v>
+        <v>2466</v>
       </c>
       <c r="B1007" s="38">
         <v>79622028701</v>
@@ -27779,7 +27794,7 @@
     </row>
     <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1008" s="32" t="s">
-        <v>2481</v>
+        <v>2467</v>
       </c>
       <c r="B1008" s="38">
         <v>79185055723</v>
@@ -27795,7 +27810,7 @@
     </row>
     <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" s="32" t="s">
-        <v>2482</v>
+        <v>2468</v>
       </c>
       <c r="B1009" s="38">
         <v>79788139855</v>
@@ -27823,7 +27838,7 @@
     </row>
     <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" s="32" t="s">
-        <v>2483</v>
+        <v>2469</v>
       </c>
       <c r="B1011" s="38">
         <v>79189749194</v>
@@ -27841,7 +27856,7 @@
     </row>
     <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" s="32" t="s">
-        <v>2484</v>
+        <v>2470</v>
       </c>
       <c r="B1012" s="38">
         <v>79184801108</v>
@@ -27859,7 +27874,7 @@
     </row>
     <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" s="32" t="s">
-        <v>2485</v>
+        <v>2471</v>
       </c>
       <c r="B1013" s="38">
         <v>79646847710</v>
@@ -27875,7 +27890,7 @@
     </row>
     <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" s="32" t="s">
-        <v>2486</v>
+        <v>2472</v>
       </c>
       <c r="B1014" s="38">
         <v>79649041350</v>
@@ -27903,7 +27918,7 @@
     </row>
     <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" s="32" t="s">
-        <v>2487</v>
+        <v>2473</v>
       </c>
       <c r="B1016" s="31">
         <v>79181537666</v>
@@ -27919,7 +27934,7 @@
     </row>
     <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" s="32" t="s">
-        <v>2488</v>
+        <v>2474</v>
       </c>
       <c r="B1017" s="31">
         <v>79051511564</v>
@@ -27935,7 +27950,7 @@
     </row>
     <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" s="32" t="s">
-        <v>2489</v>
+        <v>2475</v>
       </c>
       <c r="B1018" s="31">
         <v>79254155954</v>
@@ -27951,7 +27966,7 @@
     </row>
     <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" s="32" t="s">
-        <v>2490</v>
+        <v>2476</v>
       </c>
       <c r="B1019" s="31">
         <v>79626803581</v>
@@ -27979,7 +27994,7 @@
     </row>
     <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" s="32" t="s">
-        <v>2491</v>
+        <v>2477</v>
       </c>
       <c r="B1021" s="31">
         <v>79281059268</v>
@@ -27995,7 +28010,7 @@
     </row>
     <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" s="32" t="s">
-        <v>2492</v>
+        <v>2478</v>
       </c>
       <c r="B1022" s="31">
         <v>79183388668</v>
@@ -28013,7 +28028,7 @@
     </row>
     <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" s="32" t="s">
-        <v>2493</v>
+        <v>2479</v>
       </c>
       <c r="B1023" s="31">
         <v>79067249922</v>
@@ -28041,7 +28056,7 @@
     </row>
     <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1025" s="32" t="s">
-        <v>2494</v>
+        <v>2480</v>
       </c>
       <c r="B1025" s="31">
         <v>79052993315</v>
@@ -28059,7 +28074,7 @@
     </row>
     <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1026" s="32" t="s">
-        <v>2495</v>
+        <v>2481</v>
       </c>
       <c r="B1026" s="31">
         <v>79043499977</v>
@@ -28089,7 +28104,7 @@
     </row>
     <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1028" s="32" t="s">
-        <v>2496</v>
+        <v>2482</v>
       </c>
       <c r="B1028" s="31">
         <v>79052875113</v>
@@ -28105,7 +28120,7 @@
     </row>
     <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1029" s="32" t="s">
-        <v>2497</v>
+        <v>2483</v>
       </c>
       <c r="B1029" s="31">
         <v>79061820166</v>
@@ -28121,7 +28136,7 @@
     </row>
     <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1030" s="32" t="s">
-        <v>2498</v>
+        <v>2484</v>
       </c>
       <c r="B1030" s="31">
         <v>79189333736</v>
@@ -28137,7 +28152,7 @@
     </row>
     <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1031" s="32" t="s">
-        <v>2499</v>
+        <v>2485</v>
       </c>
       <c r="B1031" s="31">
         <v>79064327871</v>
@@ -28153,7 +28168,7 @@
     </row>
     <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1032" s="32" t="s">
-        <v>2500</v>
+        <v>2486</v>
       </c>
       <c r="B1032" s="31">
         <v>79102891788</v>
@@ -28181,13 +28196,13 @@
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1034" s="32" t="s">
-        <v>2501</v>
+        <v>2487</v>
       </c>
       <c r="B1034" s="31">
         <v>79183561661</v>
       </c>
       <c r="C1034" s="31" t="s">
-        <v>2226</v>
+        <v>2212</v>
       </c>
       <c r="D1034" s="31" t="s">
         <v>2080</v>
@@ -28199,7 +28214,7 @@
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1035" s="32" t="s">
-        <v>2502</v>
+        <v>2488</v>
       </c>
       <c r="B1035" s="31">
         <v>79537206758</v>
@@ -28307,7 +28322,7 @@
     </row>
     <row r="1041" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1041" s="32" t="s">
-        <v>2541</v>
+        <v>2527</v>
       </c>
       <c r="B1041" s="31">
         <v>79788288099</v>
@@ -28323,7 +28338,7 @@
     </row>
     <row r="1042" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1042" s="32" t="s">
-        <v>2542</v>
+        <v>2528</v>
       </c>
       <c r="B1042" s="31">
         <v>79065859343</v>
@@ -28339,7 +28354,7 @@
     </row>
     <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1043" s="32" t="s">
-        <v>2543</v>
+        <v>2529</v>
       </c>
       <c r="B1043" s="31">
         <v>79184427932</v>
@@ -28357,7 +28372,7 @@
     </row>
     <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1044" s="32" t="s">
-        <v>2544</v>
+        <v>2530</v>
       </c>
       <c r="B1044" s="31">
         <v>79780015912</v>
@@ -28373,7 +28388,7 @@
     </row>
     <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1045" s="32" t="s">
-        <v>2545</v>
+        <v>2531</v>
       </c>
       <c r="B1045" s="31">
         <v>79183756404</v>
@@ -28393,7 +28408,7 @@
     </row>
     <row r="1046" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1046" s="32" t="s">
-        <v>2546</v>
+        <v>2532</v>
       </c>
       <c r="B1046" s="31">
         <v>79031442806</v>
@@ -28425,19 +28440,19 @@
     </row>
     <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1048" s="32" t="s">
-        <v>2547</v>
+        <v>2533</v>
       </c>
       <c r="B1048" s="31">
         <v>79624430220</v>
       </c>
       <c r="C1048" s="31" t="s">
-        <v>2219</v>
+        <v>2205</v>
       </c>
       <c r="D1048" s="31" t="s">
-        <v>2217</v>
+        <v>2203</v>
       </c>
       <c r="E1048" s="31" t="s">
-        <v>2218</v>
+        <v>2204</v>
       </c>
       <c r="F1048" s="31" t="s">
         <v>1755</v>
@@ -28447,7 +28462,7 @@
     </row>
     <row r="1049" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1049" s="32" t="s">
-        <v>2548</v>
+        <v>2534</v>
       </c>
       <c r="B1049" s="31">
         <v>79602429824</v>
@@ -28475,7 +28490,7 @@
     </row>
     <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1051" s="32" t="s">
-        <v>2549</v>
+        <v>2535</v>
       </c>
       <c r="B1051" s="31">
         <v>79789971387</v>
@@ -28491,7 +28506,7 @@
     </row>
     <row r="1052" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1052" s="32" t="s">
-        <v>2550</v>
+        <v>2536</v>
       </c>
       <c r="B1052" s="31">
         <v>79661185577</v>
@@ -28539,7 +28554,7 @@
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1055" s="32" t="s">
-        <v>2589</v>
+        <v>2575</v>
       </c>
       <c r="B1055" s="33">
         <v>79186452525</v>
@@ -28555,7 +28570,7 @@
     </row>
     <row r="1056" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1056" s="32" t="s">
-        <v>2590</v>
+        <v>2576</v>
       </c>
       <c r="B1056" s="33">
         <v>79189484040</v>
@@ -28571,7 +28586,7 @@
     </row>
     <row r="1057" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1057" s="32" t="s">
-        <v>2591</v>
+        <v>2577</v>
       </c>
       <c r="B1057" s="33">
         <v>79183860270</v>
@@ -28587,7 +28602,7 @@
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1058" s="32" t="s">
-        <v>2592</v>
+        <v>2578</v>
       </c>
       <c r="B1058" s="33">
         <v>79779455485</v>
@@ -28605,7 +28620,7 @@
     </row>
     <row r="1059" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1059" s="32" t="s">
-        <v>2593</v>
+        <v>2579</v>
       </c>
       <c r="B1059" s="33">
         <v>79056507300</v>
@@ -28623,7 +28638,7 @@
     </row>
     <row r="1060" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1060" s="32" t="s">
-        <v>2594</v>
+        <v>2580</v>
       </c>
       <c r="B1060" s="33">
         <v>79258091550</v>
@@ -28641,7 +28656,7 @@
     </row>
     <row r="1061" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1061" s="32" t="s">
-        <v>2595</v>
+        <v>2581</v>
       </c>
       <c r="B1061" s="33">
         <v>79185091900</v>
@@ -28673,7 +28688,7 @@
     </row>
     <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1063" s="32" t="s">
-        <v>2596</v>
+        <v>2582</v>
       </c>
       <c r="B1063" s="33">
         <v>79649334332</v>
@@ -28689,7 +28704,7 @@
     </row>
     <row r="1064" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1064" s="32" t="s">
-        <v>2597</v>
+        <v>2583</v>
       </c>
       <c r="B1064" s="33">
         <v>79783434760</v>
@@ -28705,7 +28720,7 @@
     </row>
     <row r="1065" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1065" s="32" t="s">
-        <v>2598</v>
+        <v>2584</v>
       </c>
       <c r="B1065" s="33">
         <v>79493130260</v>
@@ -28721,7 +28736,7 @@
     </row>
     <row r="1066" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1066" s="32" t="s">
-        <v>2599</v>
+        <v>2585</v>
       </c>
       <c r="B1066" s="33">
         <v>79990156363</v>
@@ -28739,7 +28754,7 @@
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1067" s="32" t="s">
-        <v>2600</v>
+        <v>2586</v>
       </c>
       <c r="B1067" s="33">
         <v>79880146339</v>
@@ -28755,7 +28770,7 @@
     </row>
     <row r="1068" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1068" s="32" t="s">
-        <v>2601</v>
+        <v>2587</v>
       </c>
       <c r="B1068" s="33">
         <v>79604622005</v>
@@ -28773,7 +28788,7 @@
     </row>
     <row r="1069" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1069" s="32" t="s">
-        <v>2602</v>
+        <v>2588</v>
       </c>
       <c r="B1069" s="33">
         <v>79192563907</v>
@@ -28789,7 +28804,7 @@
     </row>
     <row r="1070" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1070" s="32" t="s">
-        <v>2603</v>
+        <v>2589</v>
       </c>
       <c r="B1070" s="33">
         <v>79180335333</v>
@@ -28837,7 +28852,7 @@
     </row>
     <row r="1073" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1073" s="32" t="s">
-        <v>2604</v>
+        <v>2590</v>
       </c>
       <c r="B1073" s="33">
         <v>79183073394</v>
@@ -28867,19 +28882,19 @@
     </row>
     <row r="1075" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1075" s="32" t="s">
-        <v>2605</v>
+        <v>2591</v>
       </c>
       <c r="B1075" s="33">
         <v>79615215290</v>
       </c>
       <c r="C1075" s="31" t="s">
-        <v>2223</v>
+        <v>2209</v>
       </c>
       <c r="D1075" s="31" t="s">
-        <v>2224</v>
+        <v>2210</v>
       </c>
       <c r="E1075" s="31" t="s">
-        <v>2225</v>
+        <v>2211</v>
       </c>
       <c r="F1075" s="31" t="s">
         <v>1806</v>
@@ -28889,7 +28904,7 @@
     </row>
     <row r="1076" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1076" s="32" t="s">
-        <v>2606</v>
+        <v>2592</v>
       </c>
       <c r="B1076" s="33">
         <v>79094569745</v>
@@ -28905,7 +28920,7 @@
     </row>
     <row r="1077" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1077" s="32" t="s">
-        <v>2607</v>
+        <v>2593</v>
       </c>
       <c r="B1077" s="33">
         <v>79180757000</v>
@@ -28921,7 +28936,7 @@
     </row>
     <row r="1078" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1078" s="32" t="s">
-        <v>2608</v>
+        <v>2594</v>
       </c>
       <c r="B1078" s="33">
         <v>79628609461</v>
@@ -28939,7 +28954,7 @@
     </row>
     <row r="1079" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1079" s="32" t="s">
-        <v>2609</v>
+        <v>2595</v>
       </c>
       <c r="B1079" s="33">
         <v>79184101450</v>
@@ -28957,7 +28972,7 @@
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1080" s="32" t="s">
-        <v>2610</v>
+        <v>2596</v>
       </c>
       <c r="B1080" s="33">
         <v>79183999079</v>
@@ -28979,7 +28994,7 @@
     </row>
     <row r="1081" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1081" s="32" t="s">
-        <v>2611</v>
+        <v>2597</v>
       </c>
       <c r="B1081" s="33">
         <v>79181433232</v>
@@ -28997,7 +29012,7 @@
     </row>
     <row r="1082" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1082" s="32" t="s">
-        <v>2627</v>
+        <v>2613</v>
       </c>
       <c r="B1082" s="33">
         <v>79817025393</v>
@@ -29015,7 +29030,7 @@
     </row>
     <row r="1083" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1083" s="32" t="s">
-        <v>2626</v>
+        <v>2612</v>
       </c>
       <c r="B1083" s="33">
         <v>79184302094</v>
@@ -29043,7 +29058,7 @@
     </row>
     <row r="1085" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1085" s="32" t="s">
-        <v>2625</v>
+        <v>2611</v>
       </c>
       <c r="B1085" s="33">
         <v>79287677710</v>
@@ -29065,7 +29080,7 @@
     </row>
     <row r="1086" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1086" s="32" t="s">
-        <v>2624</v>
+        <v>2610</v>
       </c>
       <c r="B1086" s="33">
         <v>79615198406</v>
@@ -29081,7 +29096,7 @@
     </row>
     <row r="1087" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1087" s="32" t="s">
-        <v>2623</v>
+        <v>2609</v>
       </c>
       <c r="B1087" s="33">
         <v>79620503561</v>
@@ -29099,7 +29114,7 @@
     </row>
     <row r="1088" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1088" s="32" t="s">
-        <v>2622</v>
+        <v>2608</v>
       </c>
       <c r="B1088" s="33">
         <v>79093732088</v>
@@ -29121,7 +29136,7 @@
     </row>
     <row r="1089" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1089" s="32" t="s">
-        <v>2621</v>
+        <v>2607</v>
       </c>
       <c r="B1089" s="33">
         <v>79060683338</v>
@@ -29141,7 +29156,7 @@
     </row>
     <row r="1090" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1090" s="32" t="s">
-        <v>2620</v>
+        <v>2606</v>
       </c>
       <c r="B1090" s="33">
         <v>79184137117</v>
@@ -29157,7 +29172,7 @@
     </row>
     <row r="1091" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1091" s="32" t="s">
-        <v>2619</v>
+        <v>2605</v>
       </c>
       <c r="B1091" s="33">
         <v>79180660587</v>
@@ -29185,7 +29200,7 @@
     </row>
     <row r="1093" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1093" s="32" t="s">
-        <v>2618</v>
+        <v>2604</v>
       </c>
       <c r="B1093" s="33">
         <v>79002359970</v>
@@ -29207,7 +29222,7 @@
     </row>
     <row r="1094" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1094" s="32" t="s">
-        <v>2617</v>
+        <v>2603</v>
       </c>
       <c r="B1094" s="33">
         <v>79892306069</v>
@@ -29237,7 +29252,7 @@
     </row>
     <row r="1096" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1096" s="32" t="s">
-        <v>2616</v>
+        <v>2602</v>
       </c>
       <c r="B1096" s="33">
         <v>79615101239</v>
@@ -29253,7 +29268,7 @@
     </row>
     <row r="1097" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1097" s="32" t="s">
-        <v>2615</v>
+        <v>2601</v>
       </c>
       <c r="B1097" s="33">
         <v>79287753737</v>
@@ -29271,7 +29286,7 @@
     </row>
     <row r="1098" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1098" s="32" t="s">
-        <v>2614</v>
+        <v>2600</v>
       </c>
       <c r="B1098" s="33">
         <v>79283348884</v>
@@ -29293,7 +29308,7 @@
     </row>
     <row r="1099" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1099" s="32" t="s">
-        <v>2613</v>
+        <v>2599</v>
       </c>
       <c r="B1099" s="33">
         <v>79381175888</v>
@@ -29321,7 +29336,7 @@
     </row>
     <row r="1101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1101" s="32" t="s">
-        <v>2612</v>
+        <v>2598</v>
       </c>
       <c r="B1101" s="38">
         <v>79536931038</v>
@@ -29375,7 +29390,7 @@
     </row>
     <row r="1104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1104" s="32" t="s">
-        <v>2644</v>
+        <v>2630</v>
       </c>
       <c r="B1104" s="33">
         <v>79900137808</v>
@@ -29383,7 +29398,7 @@
       <c r="C1104" s="31"/>
       <c r="D1104" s="31"/>
       <c r="E1104" s="31" t="s">
-        <v>2201</v>
+        <v>2191</v>
       </c>
       <c r="F1104" s="31" t="s">
         <v>1821</v>
@@ -29393,16 +29408,16 @@
     </row>
     <row r="1105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1105" s="32" t="s">
-        <v>2645</v>
+        <v>2631</v>
       </c>
       <c r="B1105" s="33">
         <v>79649134155</v>
       </c>
       <c r="C1105" s="31" t="s">
-        <v>2191</v>
+        <v>2181</v>
       </c>
       <c r="D1105" s="31" t="s">
-        <v>2200</v>
+        <v>2190</v>
       </c>
       <c r="E1105" s="31"/>
       <c r="F1105" s="31"/>
@@ -29411,13 +29426,13 @@
     </row>
     <row r="1106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1106" s="32" t="s">
-        <v>2646</v>
+        <v>2632</v>
       </c>
       <c r="B1106" s="33">
         <v>79186587857</v>
       </c>
       <c r="C1106" s="31" t="s">
-        <v>2191</v>
+        <v>2181</v>
       </c>
       <c r="D1106" s="31"/>
       <c r="E1106" s="31"/>
@@ -29427,13 +29442,13 @@
     </row>
     <row r="1107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1107" s="32" t="s">
-        <v>2647</v>
+        <v>2633</v>
       </c>
       <c r="B1107" s="33">
         <v>79183710874</v>
       </c>
       <c r="C1107" s="31" t="s">
-        <v>2191</v>
+        <v>2181</v>
       </c>
       <c r="D1107" s="31"/>
       <c r="E1107" s="31"/>
@@ -29443,17 +29458,17 @@
     </row>
     <row r="1108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1108" s="32" t="s">
-        <v>2648</v>
+        <v>2634</v>
       </c>
       <c r="B1108" s="33">
         <v>79185758610</v>
       </c>
       <c r="C1108" s="31" t="s">
-        <v>2191</v>
+        <v>2181</v>
       </c>
       <c r="D1108" s="31"/>
       <c r="E1108" s="31" t="s">
-        <v>2201</v>
+        <v>2191</v>
       </c>
       <c r="F1108" s="31" t="s">
         <v>1822</v>
@@ -29463,14 +29478,14 @@
     </row>
     <row r="1109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1109" s="32" t="s">
-        <v>2649</v>
+        <v>2635</v>
       </c>
       <c r="B1109" s="33">
         <v>79528107175</v>
       </c>
       <c r="C1109" s="31"/>
       <c r="D1109" s="31" t="s">
-        <v>2199</v>
+        <v>2189</v>
       </c>
       <c r="E1109" s="31"/>
       <c r="F1109" s="31"/>
@@ -29479,19 +29494,19 @@
     </row>
     <row r="1110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1110" s="32" t="s">
-        <v>2650</v>
+        <v>2636</v>
       </c>
       <c r="B1110" s="33">
         <v>79530981964</v>
       </c>
       <c r="C1110" s="31" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D1110" s="31" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E1110" s="31" t="s">
         <v>2191</v>
-      </c>
-      <c r="D1110" s="31" t="s">
-        <v>2199</v>
-      </c>
-      <c r="E1110" s="31" t="s">
-        <v>2201</v>
       </c>
       <c r="F1110" s="31" t="s">
         <v>1822</v>
@@ -29513,13 +29528,13 @@
     </row>
     <row r="1112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1112" s="32" t="s">
-        <v>2651</v>
+        <v>2637</v>
       </c>
       <c r="B1112" s="33">
         <v>79884919692</v>
       </c>
       <c r="C1112" s="31" t="s">
-        <v>2192</v>
+        <v>2182</v>
       </c>
       <c r="D1112" s="31"/>
       <c r="E1112" s="31"/>
@@ -29529,13 +29544,13 @@
     </row>
     <row r="1113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1113" s="32" t="s">
-        <v>2652</v>
+        <v>2638</v>
       </c>
       <c r="B1113" s="33">
         <v>79164495884</v>
       </c>
       <c r="C1113" s="31" t="s">
-        <v>2192</v>
+        <v>2182</v>
       </c>
       <c r="D1113" s="31"/>
       <c r="E1113" s="31"/>
@@ -29545,14 +29560,14 @@
     </row>
     <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1114" s="32" t="s">
-        <v>2653</v>
+        <v>2639</v>
       </c>
       <c r="B1114" s="33">
         <v>79493057717</v>
       </c>
       <c r="C1114" s="31"/>
       <c r="D1114" s="31" t="s">
-        <v>2198</v>
+        <v>2188</v>
       </c>
       <c r="E1114" s="31"/>
       <c r="F1114" s="31"/>
@@ -29573,14 +29588,14 @@
     </row>
     <row r="1116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1116" s="32" t="s">
-        <v>2654</v>
+        <v>2640</v>
       </c>
       <c r="B1116" s="33">
         <v>79180769237</v>
       </c>
       <c r="C1116" s="31"/>
       <c r="D1116" s="31" t="s">
-        <v>2197</v>
+        <v>2187</v>
       </c>
       <c r="E1116" s="31"/>
       <c r="F1116" s="31"/>
@@ -29589,7 +29604,7 @@
     </row>
     <row r="1117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1117" s="32" t="s">
-        <v>2655</v>
+        <v>2641</v>
       </c>
       <c r="B1117" s="33">
         <v>79180119455</v>
@@ -29597,7 +29612,7 @@
       <c r="C1117" s="31"/>
       <c r="D1117" s="31"/>
       <c r="E1117" s="31" t="s">
-        <v>2202</v>
+        <v>2192</v>
       </c>
       <c r="F1117" s="31" t="s">
         <v>1823</v>
@@ -29607,14 +29622,14 @@
     </row>
     <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1118" s="32" t="s">
-        <v>2656</v>
+        <v>2642</v>
       </c>
       <c r="B1118" s="33">
         <v>79787625654</v>
       </c>
       <c r="C1118" s="31"/>
       <c r="D1118" s="31" t="s">
-        <v>2196</v>
+        <v>2186</v>
       </c>
       <c r="E1118" s="31"/>
       <c r="F1118" s="31"/>
@@ -29623,14 +29638,14 @@
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1119" s="32" t="s">
-        <v>2657</v>
+        <v>2643</v>
       </c>
       <c r="B1119" s="33">
         <v>79884788948</v>
       </c>
       <c r="C1119" s="31"/>
       <c r="D1119" s="31" t="s">
-        <v>2196</v>
+        <v>2186</v>
       </c>
       <c r="E1119" s="31"/>
       <c r="F1119" s="31"/>
@@ -29651,14 +29666,14 @@
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1121" s="32" t="s">
-        <v>2658</v>
+        <v>2644</v>
       </c>
       <c r="B1121" s="33">
         <v>79205825242</v>
       </c>
       <c r="C1121" s="31"/>
       <c r="D1121" s="31" t="s">
-        <v>2195</v>
+        <v>2185</v>
       </c>
       <c r="E1121" s="31"/>
       <c r="F1121" s="31"/>
@@ -29667,14 +29682,14 @@
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1122" s="32" t="s">
-        <v>2659</v>
+        <v>2645</v>
       </c>
       <c r="B1122" s="33">
         <v>79181511141</v>
       </c>
       <c r="C1122" s="31"/>
       <c r="D1122" s="31" t="s">
-        <v>2195</v>
+        <v>2185</v>
       </c>
       <c r="E1122" s="31"/>
       <c r="F1122" s="31"/>
@@ -29715,7 +29730,7 @@
     </row>
     <row r="1125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1125" s="32" t="s">
-        <v>2660</v>
+        <v>2646</v>
       </c>
       <c r="B1125" s="33">
         <v>79118596500</v>
@@ -29723,7 +29738,7 @@
       <c r="C1125" s="33"/>
       <c r="D1125" s="33"/>
       <c r="E1125" s="33" t="s">
-        <v>2203</v>
+        <v>2193</v>
       </c>
       <c r="F1125" s="33" t="s">
         <v>1828</v>
@@ -29733,19 +29748,19 @@
     </row>
     <row r="1126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1126" s="32" t="s">
-        <v>2661</v>
+        <v>2647</v>
       </c>
       <c r="B1126" s="33">
         <v>79780187528</v>
       </c>
       <c r="C1126" s="33" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D1126" s="33" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1126" s="33" t="s">
         <v>2193</v>
-      </c>
-      <c r="D1126" s="33" t="s">
-        <v>2194</v>
-      </c>
-      <c r="E1126" s="33" t="s">
-        <v>2203</v>
       </c>
       <c r="F1126" s="33" t="s">
         <v>1827</v>
@@ -29755,7 +29770,7 @@
     </row>
     <row r="1127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1127" s="32" t="s">
-        <v>2662</v>
+        <v>2648</v>
       </c>
       <c r="B1127" s="33">
         <v>79037376464</v>
@@ -29763,7 +29778,7 @@
       <c r="C1127" s="33"/>
       <c r="D1127" s="33"/>
       <c r="E1127" s="33" t="s">
-        <v>2203</v>
+        <v>2193</v>
       </c>
       <c r="F1127" s="33" t="s">
         <v>1827</v>
@@ -29785,7 +29800,7 @@
     </row>
     <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1129" s="32" t="s">
-        <v>2663</v>
+        <v>2649</v>
       </c>
       <c r="B1129" s="33">
         <v>79103223870</v>
@@ -29793,7 +29808,7 @@
       <c r="C1129" s="33"/>
       <c r="D1129" s="33"/>
       <c r="E1129" s="33" t="s">
-        <v>2204</v>
+        <v>2194</v>
       </c>
       <c r="F1129" s="33" t="s">
         <v>1829</v>
@@ -29835,19 +29850,19 @@
     </row>
     <row r="1132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1132" s="32" t="s">
-        <v>2664</v>
+        <v>2650</v>
       </c>
       <c r="B1132" s="33">
         <v>79284697777</v>
       </c>
       <c r="C1132" s="33" t="s">
-        <v>2259</v>
+        <v>2245</v>
       </c>
       <c r="D1132" s="33" t="s">
-        <v>2274</v>
+        <v>2260</v>
       </c>
       <c r="E1132" s="33" t="s">
-        <v>2275</v>
+        <v>2261</v>
       </c>
       <c r="F1132" s="33" t="s">
         <v>1833</v>
@@ -29857,14 +29872,14 @@
     </row>
     <row r="1133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1133" s="32" t="s">
-        <v>2665</v>
+        <v>2651</v>
       </c>
       <c r="B1133" s="33">
         <v>79181601208</v>
       </c>
       <c r="C1133" s="33"/>
       <c r="D1133" s="33" t="s">
-        <v>2273</v>
+        <v>2259</v>
       </c>
       <c r="E1133" s="33"/>
       <c r="F1133" s="33"/>
@@ -29885,16 +29900,16 @@
     </row>
     <row r="1135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1135" s="32" t="s">
-        <v>2666</v>
+        <v>2652</v>
       </c>
       <c r="B1135" s="33">
         <v>79001236569</v>
       </c>
       <c r="C1135" s="33" t="s">
-        <v>2260</v>
+        <v>2246</v>
       </c>
       <c r="D1135" s="33" t="s">
-        <v>2272</v>
+        <v>2258</v>
       </c>
       <c r="E1135" s="33"/>
       <c r="F1135" s="33"/>
@@ -29903,19 +29918,19 @@
     </row>
     <row r="1136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1136" s="32" t="s">
-        <v>2667</v>
+        <v>2653</v>
       </c>
       <c r="B1136" s="33">
         <v>79991005104</v>
       </c>
       <c r="C1136" s="33" t="s">
-        <v>2507</v>
+        <v>2493</v>
       </c>
       <c r="D1136" s="33" t="s">
-        <v>2505</v>
+        <v>2491</v>
       </c>
       <c r="E1136" s="33" t="s">
-        <v>2506</v>
+        <v>2492</v>
       </c>
       <c r="F1136" s="33" t="s">
         <v>1834</v>
@@ -29925,16 +29940,16 @@
     </row>
     <row r="1137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1137" s="32" t="s">
-        <v>2668</v>
+        <v>2654</v>
       </c>
       <c r="B1137" s="33">
         <v>79371249966</v>
       </c>
       <c r="C1137" s="33" t="s">
-        <v>2260</v>
+        <v>2246</v>
       </c>
       <c r="D1137" s="33" t="s">
-        <v>2271</v>
+        <v>2257</v>
       </c>
       <c r="E1137" s="33"/>
       <c r="F1137" s="33"/>
@@ -29943,13 +29958,13 @@
     </row>
     <row r="1138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1138" s="32" t="s">
-        <v>2669</v>
+        <v>2655</v>
       </c>
       <c r="B1138" s="33">
         <v>79185805028</v>
       </c>
       <c r="C1138" s="33" t="s">
-        <v>2260</v>
+        <v>2246</v>
       </c>
       <c r="D1138" s="33"/>
       <c r="E1138" s="33"/>
@@ -29971,16 +29986,16 @@
     </row>
     <row r="1140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1140" s="32" t="s">
-        <v>2670</v>
+        <v>2656</v>
       </c>
       <c r="B1140" s="33">
         <v>79687042488</v>
       </c>
       <c r="C1140" s="33" t="s">
-        <v>2261</v>
+        <v>2247</v>
       </c>
       <c r="D1140" s="33" t="s">
-        <v>2270</v>
+        <v>2256</v>
       </c>
       <c r="E1140" s="33"/>
       <c r="F1140" s="33"/>
@@ -30001,7 +30016,7 @@
     </row>
     <row r="1142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1142" s="18" t="s">
-        <v>2671</v>
+        <v>2657</v>
       </c>
       <c r="B1142" s="40">
         <v>79283483981</v>
@@ -30055,13 +30070,13 @@
     </row>
     <row r="1145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1145" s="38" t="s">
-        <v>2684</v>
+        <v>2670</v>
       </c>
       <c r="B1145" s="38">
         <v>79110886608</v>
       </c>
       <c r="C1145" s="33" t="s">
-        <v>2262</v>
+        <v>2248</v>
       </c>
       <c r="D1145" s="33"/>
       <c r="E1145" s="33"/>
@@ -30071,14 +30086,14 @@
     </row>
     <row r="1146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1146" s="32" t="s">
-        <v>2685</v>
+        <v>2671</v>
       </c>
       <c r="B1146" s="33">
         <v>79884718844</v>
       </c>
       <c r="C1146" s="33"/>
       <c r="D1146" s="33" t="s">
-        <v>2269</v>
+        <v>2255</v>
       </c>
       <c r="E1146" s="33"/>
       <c r="F1146" s="33"/>
@@ -30087,16 +30102,16 @@
     </row>
     <row r="1147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1147" s="32" t="s">
-        <v>2686</v>
+        <v>2672</v>
       </c>
       <c r="B1147" s="33">
         <v>79185416500</v>
       </c>
       <c r="C1147" s="33" t="s">
-        <v>2262</v>
+        <v>2248</v>
       </c>
       <c r="D1147" s="33" t="s">
-        <v>2268</v>
+        <v>2254</v>
       </c>
       <c r="E1147" s="33"/>
       <c r="F1147" s="33"/>
@@ -30105,16 +30120,16 @@
     </row>
     <row r="1148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1148" s="32" t="s">
-        <v>2687</v>
+        <v>2673</v>
       </c>
       <c r="B1148" s="33">
         <v>79883514535</v>
       </c>
       <c r="C1148" s="33" t="s">
-        <v>2262</v>
+        <v>2248</v>
       </c>
       <c r="D1148" s="33" t="s">
-        <v>2268</v>
+        <v>2254</v>
       </c>
       <c r="E1148" s="33"/>
       <c r="F1148" s="33"/>
@@ -30123,16 +30138,16 @@
     </row>
     <row r="1149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1149" s="32" t="s">
-        <v>2688</v>
+        <v>2674</v>
       </c>
       <c r="B1149" s="33">
         <v>79181927858</v>
       </c>
       <c r="C1149" s="33" t="s">
-        <v>2262</v>
+        <v>2248</v>
       </c>
       <c r="D1149" s="33" t="s">
-        <v>2267</v>
+        <v>2253</v>
       </c>
       <c r="E1149" s="33"/>
       <c r="F1149" s="33"/>
@@ -30141,13 +30156,13 @@
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1150" s="32" t="s">
-        <v>2689</v>
+        <v>2675</v>
       </c>
       <c r="B1150" s="33">
         <v>79034731171</v>
       </c>
       <c r="C1150" s="33" t="s">
-        <v>2262</v>
+        <v>2248</v>
       </c>
       <c r="D1150" s="33"/>
       <c r="E1150" s="33"/>
@@ -30169,13 +30184,13 @@
     </row>
     <row r="1152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1152" s="32" t="s">
-        <v>2690</v>
+        <v>2676</v>
       </c>
       <c r="B1152" s="33">
         <v>79518399099</v>
       </c>
       <c r="C1152" s="33" t="s">
-        <v>2263</v>
+        <v>2249</v>
       </c>
       <c r="D1152" s="33"/>
       <c r="E1152" s="33"/>
@@ -30185,7 +30200,7 @@
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1153" s="32" t="s">
-        <v>2691</v>
+        <v>2677</v>
       </c>
       <c r="B1153" s="33">
         <v>79199932589</v>
@@ -30193,7 +30208,7 @@
       <c r="C1153" s="33"/>
       <c r="D1153" s="33"/>
       <c r="E1153" s="33" t="s">
-        <v>2276</v>
+        <v>2262</v>
       </c>
       <c r="F1153" s="33" t="s">
         <v>1928</v>
@@ -30203,7 +30218,7 @@
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1154" s="32" t="s">
-        <v>2692</v>
+        <v>2678</v>
       </c>
       <c r="B1154" s="33">
         <v>79898068383</v>
@@ -30211,7 +30226,7 @@
       <c r="C1154" s="33"/>
       <c r="D1154" s="33"/>
       <c r="E1154" s="33" t="s">
-        <v>2276</v>
+        <v>2262</v>
       </c>
       <c r="F1154" s="33" t="s">
         <v>1929</v>
@@ -30221,13 +30236,13 @@
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1155" s="32" t="s">
-        <v>2693</v>
+        <v>2679</v>
       </c>
       <c r="B1155" s="33">
         <v>79493272312</v>
       </c>
       <c r="C1155" s="33" t="s">
-        <v>2263</v>
+        <v>2249</v>
       </c>
       <c r="D1155" s="33"/>
       <c r="E1155" s="33"/>
@@ -30237,13 +30252,13 @@
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1156" s="32" t="s">
-        <v>2694</v>
+        <v>2680</v>
       </c>
       <c r="B1156" s="33">
         <v>79184455113</v>
       </c>
       <c r="C1156" s="33" t="s">
-        <v>2293</v>
+        <v>2279</v>
       </c>
       <c r="D1156" s="33"/>
       <c r="E1156" s="33"/>
@@ -30253,13 +30268,13 @@
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1157" s="32" t="s">
-        <v>2695</v>
+        <v>2681</v>
       </c>
       <c r="B1157" s="33">
         <v>79494697622</v>
       </c>
       <c r="C1157" s="33" t="s">
-        <v>2263</v>
+        <v>2249</v>
       </c>
       <c r="D1157" s="33"/>
       <c r="E1157" s="33"/>
@@ -30269,13 +30284,13 @@
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1158" s="32" t="s">
-        <v>2696</v>
+        <v>2682</v>
       </c>
       <c r="B1158" s="33">
         <v>79288803878</v>
       </c>
       <c r="C1158" s="33" t="s">
-        <v>2263</v>
+        <v>2249</v>
       </c>
       <c r="D1158" s="33"/>
       <c r="E1158" s="33"/>
@@ -30285,16 +30300,16 @@
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1159" s="32" t="s">
-        <v>2697</v>
+        <v>2683</v>
       </c>
       <c r="B1159" s="33">
         <v>79284223859</v>
       </c>
       <c r="C1159" s="33" t="s">
-        <v>2263</v>
+        <v>2249</v>
       </c>
       <c r="D1159" s="31" t="s">
-        <v>2266</v>
+        <v>2252</v>
       </c>
       <c r="E1159" s="33"/>
       <c r="F1159" s="33"/>
@@ -30315,19 +30330,19 @@
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1161" s="32" t="s">
-        <v>2698</v>
+        <v>2684</v>
       </c>
       <c r="B1161" s="33">
         <v>79189338233</v>
       </c>
       <c r="C1161" s="33" t="s">
-        <v>2264</v>
+        <v>2250</v>
       </c>
       <c r="D1161" s="33" t="s">
-        <v>2265</v>
+        <v>2251</v>
       </c>
       <c r="E1161" s="33" t="s">
-        <v>2277</v>
+        <v>2263</v>
       </c>
       <c r="F1161" s="33" t="s">
         <v>1930</v>
@@ -30369,14 +30384,14 @@
     </row>
     <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1164" s="32" t="s">
-        <v>2684</v>
+        <v>2670</v>
       </c>
       <c r="B1164" s="31">
         <v>79110886608</v>
       </c>
       <c r="C1164" s="31"/>
       <c r="D1164" s="31" t="s">
-        <v>2309</v>
+        <v>2295</v>
       </c>
       <c r="E1164" s="31"/>
       <c r="F1164" s="31"/>
@@ -30385,14 +30400,14 @@
     </row>
     <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1165" s="32" t="s">
-        <v>2699</v>
+        <v>2685</v>
       </c>
       <c r="B1165" s="31">
         <v>79282750088</v>
       </c>
       <c r="C1165" s="31"/>
       <c r="D1165" s="31" t="s">
-        <v>2308</v>
+        <v>2294</v>
       </c>
       <c r="E1165" s="31"/>
       <c r="F1165" s="31"/>
@@ -30401,14 +30416,14 @@
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1166" s="32" t="s">
-        <v>2700</v>
+        <v>2686</v>
       </c>
       <c r="B1166" s="31">
         <v>79384085482</v>
       </c>
       <c r="C1166" s="31"/>
       <c r="D1166" s="31" t="s">
-        <v>2307</v>
+        <v>2293</v>
       </c>
       <c r="E1166" s="31"/>
       <c r="F1166" s="31"/>
@@ -30429,13 +30444,13 @@
     </row>
     <row r="1168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1168" s="32" t="s">
-        <v>2706</v>
+        <v>2692</v>
       </c>
       <c r="B1168" s="31">
         <v>79622153493</v>
       </c>
       <c r="C1168" s="31" t="s">
-        <v>2294</v>
+        <v>2280</v>
       </c>
       <c r="D1168" s="31"/>
       <c r="E1168" s="31"/>
@@ -30445,16 +30460,16 @@
     </row>
     <row r="1169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1169" s="32" t="s">
-        <v>2705</v>
+        <v>2691</v>
       </c>
       <c r="B1169" s="31">
         <v>79266122721</v>
       </c>
       <c r="C1169" s="31" t="s">
-        <v>2294</v>
+        <v>2280</v>
       </c>
       <c r="D1169" s="31" t="s">
-        <v>2306</v>
+        <v>2292</v>
       </c>
       <c r="E1169" s="31"/>
       <c r="F1169" s="31"/>
@@ -30463,14 +30478,14 @@
     </row>
     <row r="1170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1170" s="32" t="s">
-        <v>2704</v>
+        <v>2690</v>
       </c>
       <c r="B1170" s="31">
         <v>79997719518</v>
       </c>
       <c r="C1170" s="31"/>
       <c r="D1170" s="31" t="s">
-        <v>2305</v>
+        <v>2291</v>
       </c>
       <c r="E1170" s="31"/>
       <c r="F1170" s="31"/>
@@ -30479,13 +30494,13 @@
     </row>
     <row r="1171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1171" s="32" t="s">
-        <v>2703</v>
+        <v>2689</v>
       </c>
       <c r="B1171" s="31">
         <v>79813022825</v>
       </c>
       <c r="C1171" s="31" t="s">
-        <v>2294</v>
+        <v>2280</v>
       </c>
       <c r="D1171" s="31"/>
       <c r="E1171" s="31"/>
@@ -30507,19 +30522,19 @@
     </row>
     <row r="1173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1173" s="32" t="s">
-        <v>2702</v>
+        <v>2688</v>
       </c>
       <c r="B1173" s="31">
         <v>79892367996</v>
       </c>
       <c r="C1173" s="31" t="s">
-        <v>2295</v>
+        <v>2281</v>
       </c>
       <c r="D1173" s="31" t="s">
-        <v>2304</v>
+        <v>2290</v>
       </c>
       <c r="E1173" s="31" t="s">
-        <v>2310</v>
+        <v>2296</v>
       </c>
       <c r="F1173" s="31" t="s">
         <v>1934</v>
@@ -30529,19 +30544,19 @@
     </row>
     <row r="1174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1174" s="32" t="s">
-        <v>2701</v>
+        <v>2687</v>
       </c>
       <c r="B1174" s="31">
         <v>79182617888</v>
       </c>
       <c r="C1174" s="31" t="s">
-        <v>2295</v>
+        <v>2281</v>
       </c>
       <c r="D1174" s="31" t="s">
-        <v>2304</v>
+        <v>2290</v>
       </c>
       <c r="E1174" s="31" t="s">
-        <v>2310</v>
+        <v>2296</v>
       </c>
       <c r="F1174" s="31" t="s">
         <v>1934</v>
@@ -30563,14 +30578,14 @@
     </row>
     <row r="1176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1176" s="32" t="s">
-        <v>2775</v>
+        <v>2761</v>
       </c>
       <c r="B1176" s="31">
         <v>79932156329</v>
       </c>
       <c r="C1176" s="31"/>
       <c r="D1176" s="31" t="s">
-        <v>2303</v>
+        <v>2289</v>
       </c>
       <c r="E1176" s="31"/>
       <c r="F1176" s="31"/>
@@ -30579,14 +30594,14 @@
     </row>
     <row r="1177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1177" s="32" t="s">
-        <v>2776</v>
+        <v>2762</v>
       </c>
       <c r="B1177" s="31">
         <v>79171772386</v>
       </c>
       <c r="C1177" s="31"/>
       <c r="D1177" s="31" t="s">
-        <v>2302</v>
+        <v>2288</v>
       </c>
       <c r="E1177" s="31"/>
       <c r="F1177" s="31"/>
@@ -30595,14 +30610,14 @@
     </row>
     <row r="1178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1178" s="32" t="s">
-        <v>2777</v>
+        <v>2763</v>
       </c>
       <c r="B1178" s="31">
         <v>79515365516</v>
       </c>
       <c r="C1178" s="31"/>
       <c r="D1178" s="31" t="s">
-        <v>2301</v>
+        <v>2287</v>
       </c>
       <c r="E1178" s="31"/>
       <c r="F1178" s="31"/>
@@ -30611,14 +30626,14 @@
     </row>
     <row r="1179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1179" s="32" t="s">
-        <v>2778</v>
+        <v>2764</v>
       </c>
       <c r="B1179" s="31">
         <v>79186559582</v>
       </c>
       <c r="C1179" s="31"/>
       <c r="D1179" s="31" t="s">
-        <v>2301</v>
+        <v>2287</v>
       </c>
       <c r="E1179" s="31"/>
       <c r="F1179" s="31"/>
@@ -30627,7 +30642,7 @@
     </row>
     <row r="1180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1180" s="32" t="s">
-        <v>2779</v>
+        <v>2765</v>
       </c>
       <c r="B1180" s="31">
         <v>79180300643</v>
@@ -30635,7 +30650,7 @@
       <c r="C1180" s="31"/>
       <c r="D1180" s="31"/>
       <c r="E1180" s="31" t="s">
-        <v>2311</v>
+        <v>2297</v>
       </c>
       <c r="F1180" s="31" t="s">
         <v>1953</v>
@@ -30657,13 +30672,13 @@
     </row>
     <row r="1182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1182" s="32" t="s">
-        <v>2780</v>
+        <v>2766</v>
       </c>
       <c r="B1182" s="31">
         <v>79081882253</v>
       </c>
       <c r="C1182" s="31" t="s">
-        <v>2296</v>
+        <v>2282</v>
       </c>
       <c r="D1182" s="31"/>
       <c r="E1182" s="31"/>
@@ -30673,13 +30688,13 @@
     </row>
     <row r="1183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1183" s="32" t="s">
-        <v>2781</v>
+        <v>2767</v>
       </c>
       <c r="B1183" s="31">
         <v>79184570319</v>
       </c>
       <c r="C1183" s="31" t="s">
-        <v>2296</v>
+        <v>2282</v>
       </c>
       <c r="D1183" s="31"/>
       <c r="E1183" s="31"/>
@@ -30701,13 +30716,13 @@
     </row>
     <row r="1185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1185" s="32" t="s">
-        <v>2782</v>
+        <v>2768</v>
       </c>
       <c r="B1185" s="31">
         <v>79884600699</v>
       </c>
       <c r="C1185" s="31" t="s">
-        <v>2297</v>
+        <v>2283</v>
       </c>
       <c r="D1185" s="31"/>
       <c r="E1185" s="31"/>
@@ -30717,13 +30732,13 @@
     </row>
     <row r="1186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1186" s="32" t="s">
-        <v>2783</v>
+        <v>2769</v>
       </c>
       <c r="B1186" s="31">
         <v>79615933002</v>
       </c>
       <c r="C1186" s="31" t="s">
-        <v>2297</v>
+        <v>2283</v>
       </c>
       <c r="D1186" s="31"/>
       <c r="E1186" s="31"/>
@@ -30733,13 +30748,13 @@
     </row>
     <row r="1187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1187" s="32" t="s">
-        <v>2784</v>
+        <v>2770</v>
       </c>
       <c r="B1187" s="31">
         <v>79287615615</v>
       </c>
       <c r="C1187" s="31" t="s">
-        <v>2297</v>
+        <v>2283</v>
       </c>
       <c r="D1187" s="31"/>
       <c r="E1187" s="31"/>
@@ -30761,17 +30776,17 @@
     </row>
     <row r="1189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1189" s="32" t="s">
-        <v>2785</v>
+        <v>2771</v>
       </c>
       <c r="B1189" s="31">
         <v>79282298724</v>
       </c>
       <c r="C1189" s="31"/>
       <c r="D1189" s="31" t="s">
-        <v>2300</v>
+        <v>2286</v>
       </c>
       <c r="E1189" s="31" t="s">
-        <v>2312</v>
+        <v>2298</v>
       </c>
       <c r="F1189" s="31" t="s">
         <v>1957</v>
@@ -30793,7 +30808,7 @@
     </row>
     <row r="1191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1191" s="32" t="s">
-        <v>2786</v>
+        <v>2772</v>
       </c>
       <c r="B1191" s="31">
         <v>79608204295</v>
@@ -30801,7 +30816,7 @@
       <c r="C1191" s="31"/>
       <c r="D1191" s="31"/>
       <c r="E1191" s="31" t="s">
-        <v>2313</v>
+        <v>2299</v>
       </c>
       <c r="F1191" s="31" t="s">
         <v>1958</v>
@@ -30811,7 +30826,7 @@
     </row>
     <row r="1192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1192" s="32" t="s">
-        <v>2787</v>
+        <v>2773</v>
       </c>
       <c r="B1192" s="31">
         <v>79064969201</v>
@@ -30819,7 +30834,7 @@
       <c r="C1192" s="31"/>
       <c r="D1192" s="31"/>
       <c r="E1192" s="31" t="s">
-        <v>2313</v>
+        <v>2299</v>
       </c>
       <c r="F1192" s="31" t="s">
         <v>1959</v>
@@ -30861,7 +30876,7 @@
     </row>
     <row r="1195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1195" s="32" t="s">
-        <v>2788</v>
+        <v>2774</v>
       </c>
       <c r="B1195" s="31">
         <v>79883604002</v>
@@ -30869,7 +30884,7 @@
       <c r="C1195" s="31"/>
       <c r="D1195" s="31"/>
       <c r="E1195" s="31" t="s">
-        <v>2314</v>
+        <v>2300</v>
       </c>
       <c r="F1195" s="31"/>
       <c r="G1195" s="31"/>
@@ -30877,7 +30892,7 @@
     </row>
     <row r="1196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1196" s="32" t="s">
-        <v>2789</v>
+        <v>2775</v>
       </c>
       <c r="B1196" s="31">
         <v>79384102024</v>
@@ -30885,7 +30900,7 @@
       <c r="C1196" s="31"/>
       <c r="D1196" s="31"/>
       <c r="E1196" s="31" t="s">
-        <v>2314</v>
+        <v>2300</v>
       </c>
       <c r="F1196" s="31"/>
       <c r="G1196" s="31"/>
@@ -30905,14 +30920,14 @@
     </row>
     <row r="1198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1198" s="32" t="s">
-        <v>2790</v>
+        <v>2776</v>
       </c>
       <c r="B1198" s="31">
         <v>79898514111</v>
       </c>
       <c r="C1198" s="31"/>
       <c r="D1198" s="31" t="s">
-        <v>2299</v>
+        <v>2285</v>
       </c>
       <c r="E1198" s="31"/>
       <c r="F1198" s="31"/>
@@ -30921,17 +30936,17 @@
     </row>
     <row r="1199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1199" s="32" t="s">
-        <v>2791</v>
+        <v>2777</v>
       </c>
       <c r="B1199" s="31">
         <v>79374645805</v>
       </c>
       <c r="C1199" s="31" t="s">
-        <v>2298</v>
+        <v>2284</v>
       </c>
       <c r="D1199" s="31"/>
       <c r="E1199" s="31" t="s">
-        <v>2315</v>
+        <v>2301</v>
       </c>
       <c r="F1199" s="31" t="s">
         <v>1962</v>
@@ -30941,7 +30956,7 @@
     </row>
     <row r="1200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1200" s="32" t="s">
-        <v>2792</v>
+        <v>2778</v>
       </c>
       <c r="B1200" s="31">
         <v>79892931818</v>
@@ -30949,7 +30964,7 @@
       <c r="C1200" s="31"/>
       <c r="D1200" s="31"/>
       <c r="E1200" s="31" t="s">
-        <v>2315</v>
+        <v>2301</v>
       </c>
       <c r="F1200" s="31" t="s">
         <v>1962</v>
@@ -30971,7 +30986,7 @@
     </row>
     <row r="1202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1202" s="32" t="s">
-        <v>2793</v>
+        <v>2779</v>
       </c>
       <c r="B1202" s="31">
         <v>79504617288</v>
@@ -30979,7 +30994,7 @@
       <c r="C1202" s="31"/>
       <c r="D1202" s="31"/>
       <c r="E1202" s="31" t="s">
-        <v>2424</v>
+        <v>2410</v>
       </c>
       <c r="F1202" s="31" t="s">
         <v>2038</v>
@@ -30989,16 +31004,16 @@
     </row>
     <row r="1203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1203" s="32" t="s">
-        <v>2794</v>
+        <v>2780</v>
       </c>
       <c r="B1203" s="31">
         <v>79085129986</v>
       </c>
       <c r="C1203" s="31" t="s">
-        <v>2416</v>
+        <v>2402</v>
       </c>
       <c r="D1203" s="31" t="s">
-        <v>2423</v>
+        <v>2409</v>
       </c>
       <c r="E1203" s="31"/>
       <c r="F1203" s="31"/>
@@ -31019,14 +31034,14 @@
     </row>
     <row r="1205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1205" s="32" t="s">
-        <v>2795</v>
+        <v>2781</v>
       </c>
       <c r="B1205" s="31">
         <v>79913567286</v>
       </c>
       <c r="C1205" s="31"/>
       <c r="D1205" s="31" t="s">
-        <v>2422</v>
+        <v>2408</v>
       </c>
       <c r="E1205" s="31"/>
       <c r="F1205" s="31"/>
@@ -31035,13 +31050,13 @@
     </row>
     <row r="1206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1206" s="32" t="s">
-        <v>2796</v>
+        <v>2782</v>
       </c>
       <c r="B1206" s="31">
         <v>79185010806</v>
       </c>
       <c r="C1206" s="31" t="s">
-        <v>2417</v>
+        <v>2403</v>
       </c>
       <c r="D1206" s="31"/>
       <c r="E1206" s="31"/>
@@ -31051,13 +31066,13 @@
     </row>
     <row r="1207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1207" s="32" t="s">
-        <v>2797</v>
+        <v>2783</v>
       </c>
       <c r="B1207" s="31">
         <v>79183185307</v>
       </c>
       <c r="C1207" s="31" t="s">
-        <v>2417</v>
+        <v>2403</v>
       </c>
       <c r="D1207" s="31"/>
       <c r="E1207" s="31"/>
@@ -31079,13 +31094,13 @@
     </row>
     <row r="1209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1209" s="32" t="s">
-        <v>2798</v>
+        <v>2784</v>
       </c>
       <c r="B1209" s="31">
         <v>79266566385</v>
       </c>
       <c r="C1209" s="31" t="s">
-        <v>2418</v>
+        <v>2404</v>
       </c>
       <c r="D1209" s="31"/>
       <c r="E1209" s="31"/>
@@ -31127,7 +31142,7 @@
     </row>
     <row r="1212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1212" s="32" t="s">
-        <v>2799</v>
+        <v>2785</v>
       </c>
       <c r="B1212" s="31">
         <v>79284341070</v>
@@ -31135,7 +31150,7 @@
       <c r="C1212" s="31"/>
       <c r="D1212" s="31"/>
       <c r="E1212" s="31" t="s">
-        <v>2425</v>
+        <v>2411</v>
       </c>
       <c r="F1212" s="31" t="s">
         <v>2077</v>
@@ -31145,7 +31160,7 @@
     </row>
     <row r="1213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1213" s="32" t="s">
-        <v>2800</v>
+        <v>2786</v>
       </c>
       <c r="B1213" s="31">
         <v>79267958573</v>
@@ -31153,7 +31168,7 @@
       <c r="C1213" s="31"/>
       <c r="D1213" s="31"/>
       <c r="E1213" s="31" t="s">
-        <v>2425</v>
+        <v>2411</v>
       </c>
       <c r="F1213" s="31" t="s">
         <v>2078</v>
@@ -31163,14 +31178,14 @@
     </row>
     <row r="1214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1214" s="32" t="s">
-        <v>2801</v>
+        <v>2787</v>
       </c>
       <c r="B1214" s="31">
         <v>79282480877</v>
       </c>
       <c r="C1214" s="31"/>
       <c r="D1214" s="31" t="s">
-        <v>2421</v>
+        <v>2407</v>
       </c>
       <c r="E1214" s="31"/>
       <c r="F1214" s="31"/>
@@ -31211,7 +31226,7 @@
     </row>
     <row r="1217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1217" s="32" t="s">
-        <v>2802</v>
+        <v>2788</v>
       </c>
       <c r="B1217" s="31">
         <v>79181763655</v>
@@ -31219,7 +31234,7 @@
       <c r="C1217" s="31"/>
       <c r="D1217" s="31"/>
       <c r="E1217" s="31" t="s">
-        <v>2426</v>
+        <v>2412</v>
       </c>
       <c r="F1217" s="31" t="s">
         <v>2083</v>
@@ -31241,7 +31256,7 @@
     </row>
     <row r="1219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1219" s="32" t="s">
-        <v>2803</v>
+        <v>2789</v>
       </c>
       <c r="B1219" s="31">
         <v>79184256275</v>
@@ -31249,7 +31264,7 @@
       <c r="C1219" s="31"/>
       <c r="D1219" s="31"/>
       <c r="E1219" s="31" t="s">
-        <v>2427</v>
+        <v>2413</v>
       </c>
       <c r="F1219" s="31" t="s">
         <v>2084</v>
@@ -31259,16 +31274,16 @@
     </row>
     <row r="1220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1220" s="32" t="s">
-        <v>2804</v>
+        <v>2790</v>
       </c>
       <c r="B1220" s="31">
         <v>79883151515</v>
       </c>
       <c r="C1220" s="31" t="s">
-        <v>2419</v>
+        <v>2405</v>
       </c>
       <c r="D1220" s="31" t="s">
-        <v>2420</v>
+        <v>2406</v>
       </c>
       <c r="E1220" s="31"/>
       <c r="F1220" s="31"/>
@@ -31309,7 +31324,7 @@
     </row>
     <row r="1223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1223" s="32" t="s">
-        <v>2890</v>
+        <v>2876</v>
       </c>
       <c r="B1223" s="31">
         <v>79281186882</v>
@@ -31341,13 +31356,13 @@
     </row>
     <row r="1225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1225" s="32" t="s">
-        <v>2891</v>
+        <v>2877</v>
       </c>
       <c r="B1225" s="31">
         <v>79034547400</v>
       </c>
       <c r="C1225" s="31" t="s">
-        <v>2508</v>
+        <v>2494</v>
       </c>
       <c r="D1225" s="31"/>
       <c r="E1225" s="31"/>
@@ -31357,13 +31372,13 @@
     </row>
     <row r="1226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1226" s="32" t="s">
-        <v>2892</v>
+        <v>2878</v>
       </c>
       <c r="B1226" s="31">
         <v>79287721255</v>
       </c>
       <c r="C1226" s="31" t="s">
-        <v>2508</v>
+        <v>2494</v>
       </c>
       <c r="D1226" s="31"/>
       <c r="E1226" s="31"/>
@@ -31405,16 +31420,16 @@
     </row>
     <row r="1229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1229" s="32" t="s">
-        <v>2893</v>
+        <v>2879</v>
       </c>
       <c r="B1229" s="31">
         <v>79183615308</v>
       </c>
       <c r="C1229" s="31" t="s">
-        <v>2509</v>
+        <v>2495</v>
       </c>
       <c r="D1229" s="31" t="s">
-        <v>2518</v>
+        <v>2504</v>
       </c>
       <c r="E1229" s="31"/>
       <c r="F1229" s="31"/>
@@ -31423,19 +31438,19 @@
     </row>
     <row r="1230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1230" s="32" t="s">
-        <v>2894</v>
+        <v>2880</v>
       </c>
       <c r="B1230" s="31">
         <v>79186212666</v>
       </c>
       <c r="C1230" s="31" t="s">
-        <v>2509</v>
+        <v>2495</v>
       </c>
       <c r="D1230" s="31" t="s">
-        <v>2517</v>
+        <v>2503</v>
       </c>
       <c r="E1230" s="31" t="s">
-        <v>2519</v>
+        <v>2505</v>
       </c>
       <c r="F1230" s="31" t="s">
         <v>2168</v>
@@ -31445,14 +31460,14 @@
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1231" s="32" t="s">
-        <v>2895</v>
+        <v>2881</v>
       </c>
       <c r="B1231" s="31">
         <v>79951882337</v>
       </c>
       <c r="C1231" s="31"/>
       <c r="D1231" s="31" t="s">
-        <v>2516</v>
+        <v>2502</v>
       </c>
       <c r="E1231" s="31"/>
       <c r="F1231" s="31"/>
@@ -31461,7 +31476,7 @@
     </row>
     <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1232" s="32" t="s">
-        <v>2896</v>
+        <v>2882</v>
       </c>
       <c r="B1232" s="31">
         <v>79002796431</v>
@@ -31469,7 +31484,7 @@
       <c r="C1232" s="31"/>
       <c r="D1232" s="31"/>
       <c r="E1232" s="31" t="s">
-        <v>2519</v>
+        <v>2505</v>
       </c>
       <c r="F1232" s="31" t="s">
         <v>2169</v>
@@ -31479,13 +31494,13 @@
     </row>
     <row r="1233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1233" s="32" t="s">
-        <v>2897</v>
+        <v>2883</v>
       </c>
       <c r="B1233" s="31">
         <v>79384126478</v>
       </c>
       <c r="C1233" s="31" t="s">
-        <v>2509</v>
+        <v>2495</v>
       </c>
       <c r="D1233" s="31"/>
       <c r="E1233" s="31"/>
@@ -31507,19 +31522,19 @@
     </row>
     <row r="1235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1235" s="18" t="s">
-        <v>2898</v>
+        <v>2884</v>
       </c>
       <c r="B1235" s="19">
         <v>79184673083</v>
       </c>
       <c r="C1235" s="19" t="s">
-        <v>2528</v>
+        <v>2514</v>
       </c>
       <c r="D1235" s="19" t="s">
-        <v>2529</v>
+        <v>2515</v>
       </c>
       <c r="E1235" s="19" t="s">
-        <v>2530</v>
+        <v>2516</v>
       </c>
       <c r="F1235" s="19" t="s">
         <v>2171</v>
@@ -31529,19 +31544,19 @@
     </row>
     <row r="1236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1236" s="32" t="s">
-        <v>2231</v>
+        <v>2217</v>
       </c>
       <c r="B1236" s="31">
         <v>79184987541</v>
       </c>
       <c r="C1236" s="31" t="s">
-        <v>2510</v>
+        <v>2496</v>
       </c>
       <c r="D1236" s="31" t="s">
-        <v>2515</v>
+        <v>2501</v>
       </c>
       <c r="E1236" s="31" t="s">
-        <v>2222</v>
+        <v>2208</v>
       </c>
       <c r="F1236" s="31"/>
       <c r="G1236" s="31"/>
@@ -31556,10 +31571,10 @@
       </c>
       <c r="C1237" s="31"/>
       <c r="D1237" s="31" t="s">
-        <v>2514</v>
+        <v>2500</v>
       </c>
       <c r="E1237" s="31" t="s">
-        <v>2520</v>
+        <v>2506</v>
       </c>
       <c r="F1237" s="31" t="s">
         <v>2170</v>
@@ -31569,13 +31584,13 @@
     </row>
     <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1238" s="32" t="s">
-        <v>2899</v>
+        <v>2885</v>
       </c>
       <c r="B1238" s="31">
         <v>79180458777</v>
       </c>
       <c r="C1238" s="33" t="s">
-        <v>2510</v>
+        <v>2496</v>
       </c>
       <c r="D1238" s="31"/>
       <c r="E1238" s="31"/>
@@ -31597,16 +31612,16 @@
     </row>
     <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1240" s="32" t="s">
-        <v>2900</v>
+        <v>2886</v>
       </c>
       <c r="B1240" s="31">
         <v>79183291413</v>
       </c>
       <c r="C1240" s="31" t="s">
-        <v>2511</v>
+        <v>2497</v>
       </c>
       <c r="D1240" s="31" t="s">
-        <v>2513</v>
+        <v>2499</v>
       </c>
       <c r="E1240" s="31"/>
       <c r="F1240" s="31"/>
@@ -31615,7 +31630,7 @@
     </row>
     <row r="1241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1241" s="32" t="s">
-        <v>2901</v>
+        <v>2887</v>
       </c>
       <c r="B1241" s="31">
         <v>79882371168</v>
@@ -31623,7 +31638,7 @@
       <c r="C1241" s="31"/>
       <c r="D1241" s="31"/>
       <c r="E1241" s="31" t="s">
-        <v>2521</v>
+        <v>2507</v>
       </c>
       <c r="F1241" s="31" t="s">
         <v>2172</v>
@@ -31633,14 +31648,14 @@
     </row>
     <row r="1242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1242" s="32" t="s">
-        <v>2902</v>
+        <v>2888</v>
       </c>
       <c r="B1242" s="31">
         <v>79885577597</v>
       </c>
       <c r="C1242" s="31"/>
       <c r="D1242" s="31" t="s">
-        <v>2512</v>
+        <v>2498</v>
       </c>
       <c r="E1242" s="31"/>
       <c r="F1242" s="31"/>
@@ -31649,12 +31664,12 @@
     </row>
     <row r="1243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1243" s="32" t="s">
-        <v>2903</v>
+        <v>2889</v>
       </c>
       <c r="B1243" s="33"/>
       <c r="C1243" s="31"/>
       <c r="D1243" s="31" t="s">
-        <v>2512</v>
+        <v>2498</v>
       </c>
       <c r="E1243" s="31"/>
       <c r="F1243" s="31"/>
@@ -31682,316 +31697,316 @@
       <c r="H1244" s="3"/>
     </row>
     <row r="1245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1245" s="6" t="s">
+      <c r="A1245" s="32" t="s">
         <v>2176</v>
       </c>
-      <c r="B1245" s="17"/>
-      <c r="C1245" s="3"/>
-      <c r="D1245" s="3"/>
-      <c r="E1245" s="3"/>
-      <c r="F1245" s="3"/>
-      <c r="G1245" s="3"/>
+      <c r="B1245" s="33"/>
+      <c r="C1245" s="31"/>
+      <c r="D1245" s="31"/>
+      <c r="E1245" s="31"/>
+      <c r="F1245" s="31"/>
+      <c r="G1245" s="31"/>
       <c r="H1245" s="3"/>
     </row>
     <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1246" s="6" t="s">
+      <c r="A1246" s="32" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B1246" s="33">
+        <v>79802319741</v>
+      </c>
+      <c r="C1246" s="31" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D1246" s="31" t="s">
+        <v>2545</v>
+      </c>
+      <c r="E1246" s="31"/>
+      <c r="F1246" s="31"/>
+      <c r="G1246" s="31"/>
+      <c r="H1246" s="3"/>
+    </row>
+    <row r="1247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1247" s="32" t="s">
+        <v>2899</v>
+      </c>
+      <c r="B1247" s="33">
+        <v>79298260798</v>
+      </c>
+      <c r="C1247" s="31"/>
+      <c r="D1247" s="31"/>
+      <c r="E1247" s="31" t="s">
+        <v>2546</v>
+      </c>
+      <c r="F1247" s="31" t="s">
+        <v>2213</v>
+      </c>
+      <c r="G1247" s="31"/>
+      <c r="H1247" s="3"/>
+    </row>
+    <row r="1248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1248" s="32" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B1248" s="33">
+        <v>79615901223</v>
+      </c>
+      <c r="C1248" s="31"/>
+      <c r="D1248" s="31" t="s">
+        <v>2544</v>
+      </c>
+      <c r="E1248" s="31"/>
+      <c r="F1248" s="31"/>
+      <c r="G1248" s="31"/>
+      <c r="H1248" s="3"/>
+    </row>
+    <row r="1249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1249" s="32" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B1249" s="33">
+        <v>79183331040</v>
+      </c>
+      <c r="C1249" s="31"/>
+      <c r="D1249" s="31"/>
+      <c r="E1249" s="31" t="s">
+        <v>2546</v>
+      </c>
+      <c r="F1249" s="31" t="s">
+        <v>2179</v>
+      </c>
+      <c r="G1249" s="31"/>
+      <c r="H1249" s="3"/>
+    </row>
+    <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1250" s="32" t="s">
+        <v>2902</v>
+      </c>
+      <c r="B1250" s="33">
+        <v>79064077747</v>
+      </c>
+      <c r="C1250" s="31" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D1250" s="31"/>
+      <c r="E1250" s="31" t="s">
+        <v>2546</v>
+      </c>
+      <c r="F1250" s="31" t="s">
+        <v>2179</v>
+      </c>
+      <c r="G1250" s="31"/>
+      <c r="H1250" s="3"/>
+    </row>
+    <row r="1251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1251" s="32" t="s">
         <v>2177</v>
       </c>
-      <c r="B1246" s="17">
-        <v>79802319741</v>
-      </c>
-      <c r="C1246" s="3" t="s">
-        <v>2551</v>
-      </c>
-      <c r="D1246" s="3" t="s">
-        <v>2559</v>
-      </c>
-      <c r="E1246" s="3"/>
-      <c r="F1246" s="3"/>
-      <c r="G1246" s="3"/>
-      <c r="H1246" s="3"/>
-    </row>
-    <row r="1247" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1247" s="6" t="s">
+      <c r="B1251" s="33"/>
+      <c r="C1251" s="31"/>
+      <c r="D1251" s="31"/>
+      <c r="E1251" s="31"/>
+      <c r="F1251" s="31"/>
+      <c r="G1251" s="31"/>
+      <c r="H1251" s="3"/>
+    </row>
+    <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1252" s="32" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B1252" s="33">
+        <v>79181978847</v>
+      </c>
+      <c r="C1252" s="31" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D1252" s="31" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E1252" s="31" t="s">
+        <v>2547</v>
+      </c>
+      <c r="F1252" s="31" t="s">
+        <v>2180</v>
+      </c>
+      <c r="G1252" s="31"/>
+      <c r="H1252" s="3"/>
+    </row>
+    <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1253" s="32" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B1253" s="33">
+        <v>79183346962</v>
+      </c>
+      <c r="C1253" s="31" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D1253" s="31" t="s">
+        <v>2542</v>
+      </c>
+      <c r="E1253" s="31"/>
+      <c r="F1253" s="31"/>
+      <c r="G1253" s="31"/>
+      <c r="H1253" s="3"/>
+    </row>
+    <row r="1254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1254" s="32" t="s">
         <v>2178</v>
       </c>
-      <c r="B1247" s="17">
-        <v>79298260798</v>
-      </c>
-      <c r="C1247" s="3"/>
-      <c r="D1247" s="3"/>
-      <c r="E1247" s="3" t="s">
-        <v>2560</v>
-      </c>
-      <c r="F1247" s="3" t="s">
-        <v>2227</v>
-      </c>
-      <c r="G1247" s="3"/>
-      <c r="H1247" s="3"/>
-    </row>
-    <row r="1248" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1248" s="6" t="s">
-        <v>2179</v>
-      </c>
-      <c r="B1248" s="17">
-        <v>79615901223</v>
-      </c>
-      <c r="C1248" s="3"/>
-      <c r="D1248" s="3" t="s">
-        <v>2558</v>
-      </c>
-      <c r="E1248" s="3"/>
-      <c r="F1248" s="3"/>
-      <c r="G1248" s="3"/>
-      <c r="H1248" s="3"/>
-    </row>
-    <row r="1249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1249" s="6" t="s">
-        <v>2180</v>
-      </c>
-      <c r="B1249" s="17">
-        <v>79183331040</v>
-      </c>
-      <c r="C1249" s="3"/>
-      <c r="D1249" s="3"/>
-      <c r="E1249" s="3" t="s">
-        <v>2560</v>
-      </c>
-      <c r="F1249" s="3" t="s">
-        <v>2189</v>
-      </c>
-      <c r="G1249" s="3"/>
-      <c r="H1249" s="3"/>
-    </row>
-    <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1250" s="6" t="s">
-        <v>2181</v>
-      </c>
-      <c r="B1250" s="17">
-        <v>79064077747</v>
-      </c>
-      <c r="C1250" s="3" t="s">
-        <v>2551</v>
-      </c>
-      <c r="D1250" s="3"/>
-      <c r="E1250" s="3" t="s">
-        <v>2560</v>
-      </c>
-      <c r="F1250" s="3" t="s">
-        <v>2189</v>
-      </c>
-      <c r="G1250" s="3"/>
-      <c r="H1250" s="3"/>
-    </row>
-    <row r="1251" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1251" s="6" t="s">
-        <v>2182</v>
-      </c>
-      <c r="B1251" s="17"/>
-      <c r="C1251" s="3"/>
-      <c r="D1251" s="3"/>
-      <c r="E1251" s="3"/>
-      <c r="F1251" s="3"/>
-      <c r="G1251" s="3"/>
-      <c r="H1251" s="3"/>
-    </row>
-    <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1252" s="6" t="s">
-        <v>2183</v>
-      </c>
-      <c r="B1252" s="17">
-        <v>79181978847</v>
-      </c>
-      <c r="C1252" s="3" t="s">
-        <v>2756</v>
-      </c>
-      <c r="D1252" s="3" t="s">
-        <v>2557</v>
-      </c>
-      <c r="E1252" s="3" t="s">
-        <v>2561</v>
-      </c>
-      <c r="F1252" s="3" t="s">
-        <v>2190</v>
-      </c>
-      <c r="G1252" s="3"/>
-      <c r="H1252" s="3"/>
-    </row>
-    <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1253" s="6" t="s">
-        <v>2184</v>
-      </c>
-      <c r="B1253" s="17">
-        <v>79183346962</v>
-      </c>
-      <c r="C1253" s="3" t="s">
-        <v>2552</v>
-      </c>
-      <c r="D1253" s="3" t="s">
-        <v>2556</v>
-      </c>
-      <c r="E1253" s="3"/>
-      <c r="F1253" s="3"/>
-      <c r="G1253" s="3"/>
-      <c r="H1253" s="3"/>
-    </row>
-    <row r="1254" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1254" s="6" t="s">
-        <v>2185</v>
-      </c>
-      <c r="B1254" s="17"/>
-      <c r="C1254" s="3"/>
-      <c r="D1254" s="3"/>
-      <c r="E1254" s="3"/>
-      <c r="F1254" s="3"/>
-      <c r="G1254" s="3"/>
+      <c r="B1254" s="33"/>
+      <c r="C1254" s="31"/>
+      <c r="D1254" s="31"/>
+      <c r="E1254" s="31"/>
+      <c r="F1254" s="31"/>
+      <c r="G1254" s="31"/>
       <c r="H1254" s="3"/>
     </row>
     <row r="1255" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1255" s="6" t="s">
-        <v>2186</v>
-      </c>
-      <c r="B1255" s="17">
+      <c r="A1255" s="32" t="s">
+        <v>2905</v>
+      </c>
+      <c r="B1255" s="33">
         <v>79518493781</v>
       </c>
-      <c r="C1255" s="3"/>
-      <c r="D1255" s="3" t="s">
-        <v>2555</v>
-      </c>
-      <c r="E1255" s="3"/>
-      <c r="F1255" s="3"/>
-      <c r="G1255" s="3"/>
+      <c r="C1255" s="31"/>
+      <c r="D1255" s="31" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E1255" s="31"/>
+      <c r="F1255" s="31"/>
+      <c r="G1255" s="31"/>
       <c r="H1255" s="3"/>
     </row>
     <row r="1256" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1256" s="6" t="s">
-        <v>2187</v>
-      </c>
-      <c r="B1256" s="17">
+      <c r="A1256" s="32" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B1256" s="33">
         <v>79180651355</v>
       </c>
-      <c r="C1256" s="3"/>
-      <c r="D1256" s="3" t="s">
-        <v>2554</v>
-      </c>
-      <c r="E1256" s="3"/>
-      <c r="F1256" s="3"/>
-      <c r="G1256" s="3"/>
+      <c r="C1256" s="31"/>
+      <c r="D1256" s="31" t="s">
+        <v>2540</v>
+      </c>
+      <c r="E1256" s="31"/>
+      <c r="F1256" s="31"/>
+      <c r="G1256" s="31"/>
       <c r="H1256" s="3"/>
     </row>
     <row r="1257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1257" s="6" t="s">
-        <v>2188</v>
-      </c>
-      <c r="B1257" s="17">
+      <c r="A1257" s="32" t="s">
+        <v>2907</v>
+      </c>
+      <c r="B1257" s="33">
         <v>79281140670</v>
       </c>
-      <c r="C1257" s="3" t="s">
-        <v>2553</v>
-      </c>
-      <c r="D1257" s="3"/>
-      <c r="E1257" s="3"/>
-      <c r="F1257" s="3"/>
-      <c r="G1257" s="3"/>
+      <c r="C1257" s="31" t="s">
+        <v>2539</v>
+      </c>
+      <c r="D1257" s="31"/>
+      <c r="E1257" s="31"/>
+      <c r="F1257" s="31"/>
+      <c r="G1257" s="31"/>
       <c r="H1257" s="3"/>
     </row>
     <row r="1258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1258" s="6" t="s">
-        <v>2211</v>
-      </c>
-      <c r="B1258" s="17"/>
-      <c r="C1258" s="3"/>
-      <c r="D1258" s="3"/>
-      <c r="E1258" s="3"/>
-      <c r="F1258" s="3"/>
-      <c r="G1258" s="3"/>
+      <c r="A1258" s="32" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1258" s="33"/>
+      <c r="C1258" s="31"/>
+      <c r="D1258" s="31"/>
+      <c r="E1258" s="31"/>
+      <c r="F1258" s="31"/>
+      <c r="G1258" s="31"/>
       <c r="H1258" s="3"/>
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1259" s="6" t="s">
-        <v>2212</v>
-      </c>
-      <c r="B1259" s="17">
+      <c r="A1259" s="32" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B1259" s="33">
         <v>79200671177</v>
       </c>
-      <c r="C1259" s="3"/>
-      <c r="D1259" s="3" t="s">
-        <v>2584</v>
-      </c>
-      <c r="E1259" s="3"/>
-      <c r="F1259" s="3"/>
-      <c r="G1259" s="3"/>
+      <c r="C1259" s="31"/>
+      <c r="D1259" s="31" t="s">
+        <v>2570</v>
+      </c>
+      <c r="E1259" s="31"/>
+      <c r="F1259" s="31"/>
+      <c r="G1259" s="31"/>
       <c r="H1259" s="3"/>
     </row>
     <row r="1260" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1260" s="6" t="s">
-        <v>2213</v>
-      </c>
-      <c r="B1260" s="17">
+      <c r="A1260" s="32" t="s">
+        <v>2909</v>
+      </c>
+      <c r="B1260" s="33">
         <v>79186201442</v>
       </c>
-      <c r="C1260" s="3"/>
-      <c r="D1260" s="3"/>
-      <c r="E1260" s="3" t="s">
-        <v>2585</v>
-      </c>
-      <c r="F1260" s="3" t="s">
-        <v>2587</v>
-      </c>
-      <c r="G1260" s="3"/>
+      <c r="C1260" s="31"/>
+      <c r="D1260" s="31"/>
+      <c r="E1260" s="31" t="s">
+        <v>2571</v>
+      </c>
+      <c r="F1260" s="31" t="s">
+        <v>2573</v>
+      </c>
+      <c r="G1260" s="31"/>
       <c r="H1260" s="3"/>
     </row>
     <row r="1261" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1261" s="6" t="s">
-        <v>2214</v>
-      </c>
-      <c r="B1261" s="17"/>
-      <c r="C1261" s="3"/>
-      <c r="D1261" s="3"/>
-      <c r="E1261" s="3"/>
-      <c r="F1261" s="3"/>
-      <c r="G1261" s="3"/>
+      <c r="A1261" s="32" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B1261" s="33"/>
+      <c r="C1261" s="31"/>
+      <c r="D1261" s="31"/>
+      <c r="E1261" s="31"/>
+      <c r="F1261" s="31"/>
+      <c r="G1261" s="31"/>
       <c r="H1261" s="3"/>
     </row>
     <row r="1262" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1262" s="6" t="s">
-        <v>2215</v>
-      </c>
-      <c r="B1262" s="17">
+      <c r="A1262" s="32" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B1262" s="33">
         <v>79183108008</v>
       </c>
-      <c r="C1262" s="3" t="s">
-        <v>2582</v>
-      </c>
-      <c r="D1262" s="3"/>
-      <c r="E1262" s="3"/>
-      <c r="F1262" s="3"/>
-      <c r="G1262" s="3"/>
+      <c r="C1262" s="31" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D1262" s="31"/>
+      <c r="E1262" s="31"/>
+      <c r="F1262" s="31"/>
+      <c r="G1262" s="31"/>
       <c r="H1262" s="3"/>
     </row>
     <row r="1263" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1263" s="6" t="s">
-        <v>2216</v>
-      </c>
-      <c r="B1263" s="17">
+      <c r="A1263" s="32" t="s">
+        <v>2911</v>
+      </c>
+      <c r="B1263" s="33">
         <v>79097178862</v>
       </c>
-      <c r="C1263" s="3" t="s">
-        <v>2582</v>
-      </c>
-      <c r="D1263" s="3"/>
-      <c r="E1263" s="3" t="s">
-        <v>2586</v>
-      </c>
-      <c r="F1263" s="3" t="s">
-        <v>2588</v>
-      </c>
-      <c r="G1263" s="3"/>
+      <c r="C1263" s="31" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D1263" s="31"/>
+      <c r="E1263" s="31" t="s">
+        <v>2572</v>
+      </c>
+      <c r="F1263" s="31" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G1263" s="31"/>
       <c r="H1263" s="3"/>
     </row>
     <row r="1264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1264" s="6" t="s">
-        <v>2220</v>
+        <v>2206</v>
       </c>
       <c r="B1264" s="17"/>
       <c r="C1264" s="3"/>
@@ -32003,13 +32018,13 @@
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1265" s="6" t="s">
-        <v>2221</v>
+        <v>2207</v>
       </c>
       <c r="B1265" s="17">
         <v>79787819232</v>
       </c>
       <c r="C1265" s="3" t="s">
-        <v>2583</v>
+        <v>2569</v>
       </c>
       <c r="D1265" s="3"/>
       <c r="E1265" s="3"/>
@@ -32037,7 +32052,7 @@
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1267" s="6" t="s">
-        <v>2278</v>
+        <v>2264</v>
       </c>
       <c r="B1267" s="17"/>
       <c r="C1267" s="3"/>
@@ -32049,36 +32064,36 @@
     </row>
     <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1268" s="6" t="s">
-        <v>2279</v>
+        <v>2265</v>
       </c>
       <c r="B1268" s="17">
         <v>79181206771</v>
       </c>
       <c r="C1268" s="3" t="s">
-        <v>2634</v>
+        <v>2620</v>
       </c>
       <c r="D1268" s="3" t="s">
-        <v>2641</v>
+        <v>2627</v>
       </c>
       <c r="E1268" s="3" t="s">
-        <v>2642</v>
+        <v>2628</v>
       </c>
       <c r="F1268" s="3" t="s">
-        <v>2281</v>
+        <v>2267</v>
       </c>
       <c r="G1268" s="3"/>
       <c r="H1268" s="3"/>
     </row>
     <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1269" s="6" t="s">
-        <v>2280</v>
+        <v>2266</v>
       </c>
       <c r="B1269" s="17">
         <v>79286136662</v>
       </c>
       <c r="C1269" s="3"/>
       <c r="D1269" s="3" t="s">
-        <v>2640</v>
+        <v>2626</v>
       </c>
       <c r="E1269" s="3"/>
       <c r="F1269" s="3"/>
@@ -32087,7 +32102,7 @@
     </row>
     <row r="1270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1270" s="6" t="s">
-        <v>2285</v>
+        <v>2271</v>
       </c>
       <c r="B1270" s="17"/>
       <c r="C1270" s="3"/>
@@ -32099,14 +32114,14 @@
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1271" s="8" t="s">
-        <v>2282</v>
+        <v>2268</v>
       </c>
       <c r="B1271" s="42">
         <v>375297856891</v>
       </c>
       <c r="C1271" s="5"/>
       <c r="D1271" s="5" t="s">
-        <v>2729</v>
+        <v>2715</v>
       </c>
       <c r="E1271" s="5"/>
       <c r="F1271" s="5"/>
@@ -32115,16 +32130,16 @@
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1272" s="6" t="s">
-        <v>2283</v>
+        <v>2269</v>
       </c>
       <c r="B1272" s="17">
         <v>79787715371</v>
       </c>
       <c r="C1272" s="3" t="s">
-        <v>2635</v>
+        <v>2621</v>
       </c>
       <c r="D1272" s="3" t="s">
-        <v>2639</v>
+        <v>2625</v>
       </c>
       <c r="E1272" s="3"/>
       <c r="F1272" s="3"/>
@@ -32133,14 +32148,14 @@
     </row>
     <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1273" s="6" t="s">
-        <v>2284</v>
+        <v>2270</v>
       </c>
       <c r="B1273" s="17">
         <v>79189218545</v>
       </c>
       <c r="C1273" s="3"/>
       <c r="D1273" s="3" t="s">
-        <v>2638</v>
+        <v>2624</v>
       </c>
       <c r="E1273" s="3"/>
       <c r="F1273" s="3"/>
@@ -32149,7 +32164,7 @@
     </row>
     <row r="1274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1274" s="6" t="s">
-        <v>2286</v>
+        <v>2272</v>
       </c>
       <c r="B1274" s="17"/>
       <c r="C1274" s="3"/>
@@ -32161,16 +32176,16 @@
     </row>
     <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1275" s="8" t="s">
-        <v>2287</v>
+        <v>2273</v>
       </c>
       <c r="B1275" s="42">
         <v>79883302117</v>
       </c>
       <c r="C1275" s="5" t="s">
-        <v>2872</v>
+        <v>2858</v>
       </c>
       <c r="D1275" s="5" t="s">
-        <v>2873</v>
+        <v>2859</v>
       </c>
       <c r="E1275" s="5"/>
       <c r="F1275" s="5"/>
@@ -32179,13 +32194,13 @@
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1276" s="6" t="s">
-        <v>2288</v>
+        <v>2274</v>
       </c>
       <c r="B1276" s="17">
         <v>79885414599</v>
       </c>
       <c r="C1276" s="3" t="s">
-        <v>2636</v>
+        <v>2622</v>
       </c>
       <c r="D1276" s="3"/>
       <c r="E1276" s="3"/>
@@ -32195,7 +32210,7 @@
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1277" s="6" t="s">
-        <v>2289</v>
+        <v>2275</v>
       </c>
       <c r="B1277" s="17">
         <v>79606987172</v>
@@ -32203,17 +32218,17 @@
       <c r="C1277" s="3"/>
       <c r="D1277" s="3"/>
       <c r="E1277" s="3" t="s">
-        <v>2643</v>
+        <v>2629</v>
       </c>
       <c r="F1277" s="3" t="s">
-        <v>2292</v>
+        <v>2278</v>
       </c>
       <c r="G1277" s="3"/>
       <c r="H1277" s="3"/>
     </row>
     <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1278" s="6" t="s">
-        <v>2291</v>
+        <v>2277</v>
       </c>
       <c r="B1278" s="17"/>
       <c r="C1278" s="3"/>
@@ -32225,13 +32240,13 @@
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1279" s="6" t="s">
-        <v>2290</v>
+        <v>2276</v>
       </c>
       <c r="B1279" s="17">
         <v>79002702201</v>
       </c>
       <c r="C1279" s="3" t="s">
-        <v>2637</v>
+        <v>2623</v>
       </c>
       <c r="D1279" s="3"/>
       <c r="E1279" s="3"/>
@@ -32259,7 +32274,7 @@
     </row>
     <row r="1281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1281" s="6" t="s">
-        <v>2354</v>
+        <v>2340</v>
       </c>
       <c r="B1281" s="17"/>
       <c r="C1281" s="3"/>
@@ -32271,13 +32286,13 @@
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1282" s="6" t="s">
-        <v>2355</v>
+        <v>2341</v>
       </c>
       <c r="B1282" s="17">
         <v>79036910787</v>
       </c>
       <c r="C1282" s="3" t="s">
-        <v>2707</v>
+        <v>2693</v>
       </c>
       <c r="D1282" s="3"/>
       <c r="E1282" s="3"/>
@@ -32287,58 +32302,58 @@
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1283" s="6" t="s">
-        <v>2356</v>
+        <v>2342</v>
       </c>
       <c r="B1283" s="17">
         <v>79085097827</v>
       </c>
       <c r="C1283" s="3" t="s">
-        <v>2707</v>
+        <v>2693</v>
       </c>
       <c r="D1283" s="3" t="s">
-        <v>2724</v>
+        <v>2710</v>
       </c>
       <c r="E1283" s="3" t="s">
-        <v>2725</v>
+        <v>2711</v>
       </c>
       <c r="F1283" s="3" t="s">
-        <v>2372</v>
+        <v>2358</v>
       </c>
       <c r="G1283" s="3"/>
       <c r="H1283" s="3"/>
     </row>
     <row r="1284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1284" s="6" t="s">
-        <v>2357</v>
+        <v>2343</v>
       </c>
       <c r="B1284" s="17">
         <v>79786456031</v>
       </c>
       <c r="C1284" s="3" t="s">
-        <v>2707</v>
+        <v>2693</v>
       </c>
       <c r="D1284" s="3" t="s">
-        <v>2723</v>
+        <v>2709</v>
       </c>
       <c r="E1284" s="3" t="s">
-        <v>2725</v>
+        <v>2711</v>
       </c>
       <c r="F1284" s="3" t="s">
-        <v>2373</v>
+        <v>2359</v>
       </c>
       <c r="G1284" s="3"/>
       <c r="H1284" s="3"/>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1285" s="6" t="s">
-        <v>2358</v>
+        <v>2344</v>
       </c>
       <c r="B1285" s="17">
         <v>79180492172</v>
       </c>
       <c r="C1285" s="3"/>
       <c r="D1285" s="3" t="s">
-        <v>2723</v>
+        <v>2709</v>
       </c>
       <c r="E1285" s="3"/>
       <c r="F1285" s="3"/>
@@ -32347,7 +32362,7 @@
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1286" s="6" t="s">
-        <v>2359</v>
+        <v>2345</v>
       </c>
       <c r="B1286" s="17"/>
       <c r="C1286" s="3"/>
@@ -32359,7 +32374,7 @@
     </row>
     <row r="1287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1287" s="6" t="s">
-        <v>2360</v>
+        <v>2346</v>
       </c>
       <c r="B1287" s="17">
         <v>79530708343</v>
@@ -32367,26 +32382,26 @@
       <c r="C1287" s="3"/>
       <c r="D1287" s="3"/>
       <c r="E1287" s="3" t="s">
-        <v>2726</v>
+        <v>2712</v>
       </c>
       <c r="F1287" s="3" t="s">
-        <v>2374</v>
+        <v>2360</v>
       </c>
       <c r="G1287" s="3"/>
       <c r="H1287" s="3"/>
     </row>
     <row r="1288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1288" s="6" t="s">
-        <v>2361</v>
+        <v>2347</v>
       </c>
       <c r="B1288" s="17">
         <v>79618588262</v>
       </c>
       <c r="C1288" s="3" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D1288" s="3" t="s">
         <v>2708</v>
-      </c>
-      <c r="D1288" s="3" t="s">
-        <v>2722</v>
       </c>
       <c r="E1288" s="3"/>
       <c r="F1288" s="3"/>
@@ -32395,7 +32410,7 @@
     </row>
     <row r="1289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1289" s="6" t="s">
-        <v>2362</v>
+        <v>2348</v>
       </c>
       <c r="B1289" s="17">
         <v>79990580869</v>
@@ -32403,17 +32418,17 @@
       <c r="C1289" s="3"/>
       <c r="D1289" s="3"/>
       <c r="E1289" s="3" t="s">
-        <v>2726</v>
+        <v>2712</v>
       </c>
       <c r="F1289" s="3" t="s">
-        <v>2375</v>
+        <v>2361</v>
       </c>
       <c r="G1289" s="3"/>
       <c r="H1289" s="3"/>
     </row>
     <row r="1290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1290" s="6" t="s">
-        <v>2363</v>
+        <v>2349</v>
       </c>
       <c r="B1290" s="17">
         <v>79283306686</v>
@@ -32421,23 +32436,23 @@
       <c r="C1290" s="3"/>
       <c r="D1290" s="3"/>
       <c r="E1290" s="3" t="s">
-        <v>2726</v>
+        <v>2712</v>
       </c>
       <c r="F1290" s="3" t="s">
-        <v>2375</v>
+        <v>2361</v>
       </c>
       <c r="G1290" s="3"/>
       <c r="H1290" s="3"/>
     </row>
     <row r="1291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1291" s="6" t="s">
-        <v>2364</v>
+        <v>2350</v>
       </c>
       <c r="B1291" s="17">
         <v>79184803174</v>
       </c>
       <c r="C1291" s="3" t="s">
-        <v>2708</v>
+        <v>2694</v>
       </c>
       <c r="D1291" s="3"/>
       <c r="E1291" s="3"/>
@@ -32447,13 +32462,13 @@
     </row>
     <row r="1292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1292" s="6" t="s">
-        <v>2365</v>
+        <v>2351</v>
       </c>
       <c r="B1292" s="17">
         <v>79186825836</v>
       </c>
       <c r="C1292" s="3" t="s">
-        <v>2708</v>
+        <v>2694</v>
       </c>
       <c r="D1292" s="3"/>
       <c r="E1292" s="3"/>
@@ -32463,13 +32478,13 @@
     </row>
     <row r="1293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1293" s="6" t="s">
-        <v>2366</v>
+        <v>2352</v>
       </c>
       <c r="B1293" s="17">
         <v>79182466940</v>
       </c>
       <c r="C1293" s="3" t="s">
-        <v>2708</v>
+        <v>2694</v>
       </c>
       <c r="D1293" s="3"/>
       <c r="E1293" s="3"/>
@@ -32479,7 +32494,7 @@
     </row>
     <row r="1294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1294" s="6" t="s">
-        <v>2368</v>
+        <v>2354</v>
       </c>
       <c r="B1294" s="17"/>
       <c r="C1294" s="3"/>
@@ -32491,16 +32506,16 @@
     </row>
     <row r="1295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1295" s="6" t="s">
-        <v>2367</v>
+        <v>2353</v>
       </c>
       <c r="B1295" s="17">
         <v>79149202703</v>
       </c>
       <c r="C1295" s="3" t="s">
-        <v>2709</v>
+        <v>2695</v>
       </c>
       <c r="D1295" s="3" t="s">
-        <v>2721</v>
+        <v>2707</v>
       </c>
       <c r="E1295" s="3"/>
       <c r="F1295" s="3"/>
@@ -32509,27 +32524,27 @@
     </row>
     <row r="1296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1296" s="6" t="s">
-        <v>2369</v>
+        <v>2355</v>
       </c>
       <c r="B1296" s="17">
         <v>79885468941</v>
       </c>
       <c r="C1296" s="3" t="s">
-        <v>2709</v>
+        <v>2695</v>
       </c>
       <c r="D1296" s="3"/>
       <c r="E1296" s="3" t="s">
-        <v>2727</v>
+        <v>2713</v>
       </c>
       <c r="F1296" s="3" t="s">
-        <v>2376</v>
+        <v>2362</v>
       </c>
       <c r="G1296" s="3"/>
       <c r="H1296" s="28"/>
     </row>
     <row r="1297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1297" s="6" t="s">
-        <v>2370</v>
+        <v>2356</v>
       </c>
       <c r="B1297" s="17"/>
       <c r="C1297" s="3"/>
@@ -32541,16 +32556,16 @@
     </row>
     <row r="1298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1298" s="6" t="s">
-        <v>2371</v>
+        <v>2357</v>
       </c>
       <c r="B1298" s="17">
         <v>79806633494</v>
       </c>
       <c r="C1298" s="3" t="s">
-        <v>2710</v>
+        <v>2696</v>
       </c>
       <c r="D1298" s="3" t="s">
-        <v>2720</v>
+        <v>2706</v>
       </c>
       <c r="E1298" s="3"/>
       <c r="F1298" s="3"/>
@@ -32577,7 +32592,7 @@
     </row>
     <row r="1300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1300" s="6" t="s">
-        <v>2377</v>
+        <v>2363</v>
       </c>
       <c r="B1300" s="17"/>
       <c r="C1300" s="3"/>
@@ -32589,13 +32604,13 @@
     </row>
     <row r="1301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1301" s="6" t="s">
-        <v>2378</v>
+        <v>2364</v>
       </c>
       <c r="B1301" s="17">
         <v>79525837593</v>
       </c>
       <c r="C1301" s="3" t="s">
-        <v>2711</v>
+        <v>2697</v>
       </c>
       <c r="D1301" s="3"/>
       <c r="E1301" s="3"/>
@@ -32605,16 +32620,16 @@
     </row>
     <row r="1302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1302" s="6" t="s">
-        <v>2379</v>
+        <v>2365</v>
       </c>
       <c r="B1302" s="17">
         <v>79183870112</v>
       </c>
       <c r="C1302" s="3" t="s">
-        <v>2711</v>
+        <v>2697</v>
       </c>
       <c r="D1302" s="3" t="s">
-        <v>2719</v>
+        <v>2705</v>
       </c>
       <c r="E1302" s="3"/>
       <c r="F1302" s="3"/>
@@ -32623,14 +32638,14 @@
     </row>
     <row r="1303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1303" s="6" t="s">
-        <v>2380</v>
+        <v>2366</v>
       </c>
       <c r="B1303" s="17">
         <v>79182842938</v>
       </c>
       <c r="C1303" s="3"/>
       <c r="D1303" s="3" t="s">
-        <v>2718</v>
+        <v>2704</v>
       </c>
       <c r="E1303" s="3"/>
       <c r="F1303" s="3"/>
@@ -32639,7 +32654,7 @@
     </row>
     <row r="1304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1304" s="6" t="s">
-        <v>2381</v>
+        <v>2367</v>
       </c>
       <c r="B1304" s="17"/>
       <c r="C1304" s="3"/>
@@ -32651,29 +32666,29 @@
     </row>
     <row r="1305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1305" s="6" t="s">
-        <v>2382</v>
+        <v>2368</v>
       </c>
       <c r="B1305" s="17">
         <v>79183772137</v>
       </c>
       <c r="C1305" s="3" t="s">
-        <v>2712</v>
+        <v>2698</v>
       </c>
       <c r="D1305" s="3" t="s">
-        <v>2717</v>
+        <v>2703</v>
       </c>
       <c r="E1305" s="3" t="s">
-        <v>2728</v>
+        <v>2714</v>
       </c>
       <c r="F1305" s="3" t="s">
-        <v>2390</v>
+        <v>2376</v>
       </c>
       <c r="G1305" s="3"/>
       <c r="H1305" s="28"/>
     </row>
     <row r="1306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1306" s="6" t="s">
-        <v>2383</v>
+        <v>2369</v>
       </c>
       <c r="B1306" s="17">
         <v>79897201133</v>
@@ -32681,24 +32696,24 @@
       <c r="C1306" s="3"/>
       <c r="D1306" s="3"/>
       <c r="E1306" s="3" t="s">
-        <v>2728</v>
+        <v>2714</v>
       </c>
       <c r="F1306" s="3" t="s">
-        <v>2391</v>
+        <v>2377</v>
       </c>
       <c r="G1306" s="3"/>
       <c r="H1306" s="28"/>
     </row>
     <row r="1307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1307" s="6" t="s">
-        <v>2384</v>
+        <v>2370</v>
       </c>
       <c r="B1307" s="17">
         <v>79615332857</v>
       </c>
       <c r="C1307" s="3"/>
       <c r="D1307" s="3" t="s">
-        <v>2716</v>
+        <v>2702</v>
       </c>
       <c r="E1307" s="3"/>
       <c r="F1307" s="3"/>
@@ -32707,14 +32722,14 @@
     </row>
     <row r="1308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1308" s="6" t="s">
-        <v>2385</v>
+        <v>2371</v>
       </c>
       <c r="B1308" s="17">
         <v>79184188755</v>
       </c>
       <c r="C1308" s="3"/>
       <c r="D1308" s="3" t="s">
-        <v>2716</v>
+        <v>2702</v>
       </c>
       <c r="E1308" s="3"/>
       <c r="F1308" s="3"/>
@@ -32723,7 +32738,7 @@
     </row>
     <row r="1309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1309" s="6" t="s">
-        <v>2386</v>
+        <v>2372</v>
       </c>
       <c r="B1309" s="17"/>
       <c r="C1309" s="3"/>
@@ -32735,14 +32750,14 @@
     </row>
     <row r="1310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1310" s="6" t="s">
-        <v>2387</v>
+        <v>2373</v>
       </c>
       <c r="B1310" s="17">
         <v>79034550320</v>
       </c>
       <c r="C1310" s="3"/>
       <c r="D1310" s="3" t="s">
-        <v>2715</v>
+        <v>2701</v>
       </c>
       <c r="E1310" s="3"/>
       <c r="F1310" s="3"/>
@@ -32751,13 +32766,13 @@
     </row>
     <row r="1311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1311" s="6" t="s">
-        <v>2388</v>
+        <v>2374</v>
       </c>
       <c r="B1311" s="17">
         <v>79497336125</v>
       </c>
       <c r="C1311" s="3" t="s">
-        <v>2713</v>
+        <v>2699</v>
       </c>
       <c r="D1311" s="3"/>
       <c r="E1311" s="3"/>
@@ -32767,14 +32782,14 @@
     </row>
     <row r="1312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1312" s="6" t="s">
-        <v>2389</v>
+        <v>2375</v>
       </c>
       <c r="B1312" s="17">
         <v>79676739173</v>
       </c>
       <c r="C1312" s="3"/>
       <c r="D1312" s="3" t="s">
-        <v>2714</v>
+        <v>2700</v>
       </c>
       <c r="E1312" s="3"/>
       <c r="F1312" s="3"/>
@@ -32800,7 +32815,7 @@
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1314" s="6" t="s">
-        <v>2392</v>
+        <v>2378</v>
       </c>
       <c r="B1314" s="17"/>
       <c r="C1314" s="3"/>
@@ -32811,26 +32826,26 @@
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1315" s="6" t="s">
-        <v>2393</v>
+        <v>2379</v>
       </c>
       <c r="B1315" s="17">
         <v>79183767815</v>
       </c>
       <c r="C1315" s="3"/>
       <c r="D1315" s="3" t="s">
-        <v>2823</v>
+        <v>2809</v>
       </c>
       <c r="E1315" s="3" t="s">
-        <v>2824</v>
+        <v>2810</v>
       </c>
       <c r="F1315" s="3" t="s">
-        <v>2402</v>
+        <v>2388</v>
       </c>
       <c r="G1315" s="2"/>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1316" s="6" t="s">
-        <v>2397</v>
+        <v>2383</v>
       </c>
       <c r="B1316" s="28"/>
       <c r="C1316" s="3"/>
@@ -32841,13 +32856,13 @@
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1317" s="6" t="s">
-        <v>2394</v>
+        <v>2380</v>
       </c>
       <c r="B1317" s="17">
         <v>79528700394</v>
       </c>
       <c r="C1317" s="3" t="s">
-        <v>2805</v>
+        <v>2791</v>
       </c>
       <c r="D1317" s="3"/>
       <c r="E1317" s="3"/>
@@ -32856,13 +32871,13 @@
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1318" s="6" t="s">
-        <v>2395</v>
+        <v>2381</v>
       </c>
       <c r="B1318" s="17">
         <v>79054305403</v>
       </c>
       <c r="C1318" s="3" t="s">
-        <v>2805</v>
+        <v>2791</v>
       </c>
       <c r="D1318" s="3"/>
       <c r="E1318" s="3"/>
@@ -32871,14 +32886,14 @@
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1319" s="6" t="s">
-        <v>2396</v>
+        <v>2382</v>
       </c>
       <c r="B1319" s="17">
         <v>79064046088</v>
       </c>
       <c r="C1319" s="3"/>
       <c r="D1319" s="3" t="s">
-        <v>2822</v>
+        <v>2808</v>
       </c>
       <c r="E1319" s="3"/>
       <c r="F1319" s="3"/>
@@ -32886,16 +32901,16 @@
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1320" s="6" t="s">
-        <v>2398</v>
+        <v>2384</v>
       </c>
       <c r="B1320" s="17">
         <v>79284483258</v>
       </c>
       <c r="C1320" s="3" t="s">
-        <v>2805</v>
+        <v>2791</v>
       </c>
       <c r="D1320" s="3" t="s">
-        <v>2822</v>
+        <v>2808</v>
       </c>
       <c r="E1320" s="3"/>
       <c r="F1320" s="3"/>
@@ -32903,7 +32918,7 @@
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1321" s="6" t="s">
-        <v>2399</v>
+        <v>2385</v>
       </c>
       <c r="B1321" s="17"/>
       <c r="C1321" s="3"/>
@@ -32914,13 +32929,13 @@
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1322" s="6" t="s">
-        <v>2400</v>
+        <v>2386</v>
       </c>
       <c r="B1322" s="28">
         <v>79081817570</v>
       </c>
       <c r="C1322" s="17" t="s">
-        <v>2806</v>
+        <v>2792</v>
       </c>
       <c r="D1322" s="3"/>
       <c r="E1322" s="3"/>
@@ -32929,7 +32944,7 @@
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1323" s="6" t="s">
-        <v>2401</v>
+        <v>2387</v>
       </c>
       <c r="B1323" s="28">
         <v>79045033313</v>
@@ -32937,16 +32952,16 @@
       <c r="C1323" s="28"/>
       <c r="D1323" s="3"/>
       <c r="E1323" s="3" t="s">
-        <v>2825</v>
+        <v>2811</v>
       </c>
       <c r="F1323" s="3" t="s">
-        <v>2403</v>
+        <v>2389</v>
       </c>
       <c r="G1323" s="2"/>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1324" s="6" t="s">
-        <v>2404</v>
+        <v>2390</v>
       </c>
       <c r="B1324" s="28"/>
       <c r="C1324" s="28"/>
@@ -32957,52 +32972,52 @@
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1325" s="6" t="s">
-        <v>2405</v>
+        <v>2391</v>
       </c>
       <c r="B1325" s="17">
         <v>79186195666</v>
       </c>
       <c r="C1325" s="3" t="s">
-        <v>2807</v>
+        <v>2793</v>
       </c>
       <c r="D1325" s="3"/>
       <c r="E1325" s="3" t="s">
-        <v>2826</v>
+        <v>2812</v>
       </c>
       <c r="F1325" s="3" t="s">
-        <v>2503</v>
+        <v>2489</v>
       </c>
       <c r="G1325" s="2"/>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1326" s="6" t="s">
-        <v>2406</v>
+        <v>2392</v>
       </c>
       <c r="B1326" s="17">
         <v>79780648554</v>
       </c>
       <c r="C1326" s="3"/>
       <c r="D1326" s="3" t="s">
-        <v>2821</v>
+        <v>2807</v>
       </c>
       <c r="E1326" s="3" t="s">
-        <v>2826</v>
+        <v>2812</v>
       </c>
       <c r="F1326" s="3" t="s">
-        <v>2504</v>
+        <v>2490</v>
       </c>
       <c r="G1326" s="2"/>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1327" s="6" t="s">
-        <v>2407</v>
+        <v>2393</v>
       </c>
       <c r="B1327" s="17">
         <v>79493022752</v>
       </c>
       <c r="C1327" s="3"/>
       <c r="D1327" s="3" t="s">
-        <v>2821</v>
+        <v>2807</v>
       </c>
       <c r="E1327" s="3"/>
       <c r="F1327" s="3"/>
@@ -33010,7 +33025,7 @@
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1328" s="6" t="s">
-        <v>2408</v>
+        <v>2394</v>
       </c>
       <c r="B1328" s="17"/>
       <c r="C1328" s="3"/>
@@ -33021,7 +33036,7 @@
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1329" s="6" t="s">
-        <v>2409</v>
+        <v>2395</v>
       </c>
       <c r="B1329" s="17">
         <v>79085033991</v>
@@ -33034,14 +33049,14 @@
     </row>
     <row r="1330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1330" s="6" t="s">
-        <v>2410</v>
+        <v>2396</v>
       </c>
       <c r="B1330" s="17">
         <v>79282576368</v>
       </c>
       <c r="C1330" s="3"/>
       <c r="D1330" s="3" t="s">
-        <v>2820</v>
+        <v>2806</v>
       </c>
       <c r="E1330" s="3"/>
       <c r="F1330" s="3"/>
@@ -33049,7 +33064,7 @@
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1331" s="6" t="s">
-        <v>2411</v>
+        <v>2397</v>
       </c>
       <c r="B1331" s="17"/>
       <c r="C1331" s="3"/>
@@ -33060,13 +33075,13 @@
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1332" s="6" t="s">
-        <v>2412</v>
+        <v>2398</v>
       </c>
       <c r="B1332" s="17">
         <v>79054871997</v>
       </c>
       <c r="C1332" s="3" t="s">
-        <v>2808</v>
+        <v>2794</v>
       </c>
       <c r="D1332" s="3"/>
       <c r="E1332" s="3"/>
@@ -33075,14 +33090,14 @@
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1333" s="6" t="s">
-        <v>2413</v>
+        <v>2399</v>
       </c>
       <c r="B1333" s="17">
         <v>79193683714</v>
       </c>
       <c r="C1333" s="3"/>
       <c r="D1333" s="3" t="s">
-        <v>2819</v>
+        <v>2805</v>
       </c>
       <c r="E1333" s="3"/>
       <c r="F1333" s="3"/>
@@ -33090,14 +33105,14 @@
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1334" s="6" t="s">
-        <v>2414</v>
+        <v>2400</v>
       </c>
       <c r="B1334" s="17">
         <v>79586493944</v>
       </c>
       <c r="C1334" s="3"/>
       <c r="D1334" s="3" t="s">
-        <v>2818</v>
+        <v>2804</v>
       </c>
       <c r="E1334" s="3"/>
       <c r="F1334" s="3"/>
@@ -33105,13 +33120,13 @@
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1335" s="6" t="s">
-        <v>2415</v>
+        <v>2401</v>
       </c>
       <c r="B1335" s="17">
         <v>79780045546</v>
       </c>
       <c r="C1335" s="3" t="s">
-        <v>2808</v>
+        <v>2794</v>
       </c>
       <c r="D1335" s="3"/>
       <c r="E1335" s="3"/>
@@ -33137,7 +33152,7 @@
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1337" s="6" t="s">
-        <v>2522</v>
+        <v>2508</v>
       </c>
       <c r="B1337" s="17"/>
       <c r="C1337" s="3"/>
@@ -33148,16 +33163,16 @@
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1338" s="8" t="s">
-        <v>2523</v>
+        <v>2509</v>
       </c>
       <c r="B1338" s="42">
         <v>79782640332</v>
       </c>
       <c r="C1338" s="5" t="s">
-        <v>2870</v>
+        <v>2856</v>
       </c>
       <c r="D1338" s="5" t="s">
-        <v>2871</v>
+        <v>2857</v>
       </c>
       <c r="E1338" s="5"/>
       <c r="F1338" s="5"/>
@@ -33165,7 +33180,7 @@
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1339" s="6" t="s">
-        <v>2524</v>
+        <v>2510</v>
       </c>
       <c r="B1339" s="17"/>
       <c r="C1339" s="3"/>
@@ -33176,16 +33191,16 @@
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1340" s="6" t="s">
-        <v>2525</v>
+        <v>2511</v>
       </c>
       <c r="B1340" s="17">
         <v>79530977713</v>
       </c>
       <c r="C1340" s="3" t="s">
-        <v>2809</v>
+        <v>2795</v>
       </c>
       <c r="D1340" s="3" t="s">
-        <v>2817</v>
+        <v>2803</v>
       </c>
       <c r="E1340" s="3"/>
       <c r="F1340" s="3"/>
@@ -33193,14 +33208,14 @@
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1341" s="6" t="s">
-        <v>2526</v>
+        <v>2512</v>
       </c>
       <c r="B1341" s="17">
         <v>79896279922</v>
       </c>
       <c r="C1341" s="3"/>
       <c r="D1341" s="3" t="s">
-        <v>2816</v>
+        <v>2802</v>
       </c>
       <c r="E1341" s="3"/>
       <c r="F1341" s="3"/>
@@ -33208,7 +33223,7 @@
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1342" s="8" t="s">
-        <v>2527</v>
+        <v>2513</v>
       </c>
       <c r="B1342" s="42">
         <v>79064327871</v>
@@ -33240,7 +33255,7 @@
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1344" s="6" t="s">
-        <v>2534</v>
+        <v>2520</v>
       </c>
       <c r="B1344" s="17"/>
       <c r="C1344" s="3"/>
@@ -33251,7 +33266,7 @@
     </row>
     <row r="1345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1345" s="6" t="s">
-        <v>2531</v>
+        <v>2517</v>
       </c>
       <c r="B1345" s="17">
         <v>79184743700</v>
@@ -33259,23 +33274,23 @@
       <c r="C1345" s="3"/>
       <c r="D1345" s="3"/>
       <c r="E1345" s="3" t="s">
-        <v>2827</v>
+        <v>2813</v>
       </c>
       <c r="F1345" s="3" t="s">
-        <v>2564</v>
+        <v>2550</v>
       </c>
       <c r="G1345" s="2"/>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1346" s="6" t="s">
-        <v>2532</v>
+        <v>2518</v>
       </c>
       <c r="B1346" s="17">
         <v>79186353503</v>
       </c>
       <c r="C1346" s="3"/>
       <c r="D1346" s="3" t="s">
-        <v>2815</v>
+        <v>2801</v>
       </c>
       <c r="E1346" s="3"/>
       <c r="F1346" s="3"/>
@@ -33283,70 +33298,70 @@
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1347" s="6" t="s">
-        <v>2533</v>
+        <v>2519</v>
       </c>
       <c r="B1347" s="17">
         <v>79676684446</v>
       </c>
       <c r="C1347" s="3" t="s">
-        <v>2537</v>
+        <v>2523</v>
       </c>
       <c r="D1347" s="3" t="s">
-        <v>2814</v>
+        <v>2800</v>
       </c>
       <c r="E1347" s="3" t="s">
-        <v>2565</v>
+        <v>2551</v>
       </c>
       <c r="F1347" s="3" t="s">
-        <v>2562</v>
+        <v>2548</v>
       </c>
       <c r="G1347" s="2"/>
     </row>
     <row r="1348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1348" s="6" t="s">
-        <v>2535</v>
+        <v>2521</v>
       </c>
       <c r="B1348" s="17">
         <v>79183887841</v>
       </c>
       <c r="C1348" s="3" t="s">
-        <v>2810</v>
+        <v>2796</v>
       </c>
       <c r="D1348" s="3" t="s">
-        <v>2814</v>
+        <v>2800</v>
       </c>
       <c r="E1348" s="3" t="s">
-        <v>2565</v>
+        <v>2551</v>
       </c>
       <c r="F1348" s="3" t="s">
-        <v>2562</v>
+        <v>2548</v>
       </c>
       <c r="G1348" s="2"/>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1349" s="6" t="s">
-        <v>2536</v>
+        <v>2522</v>
       </c>
       <c r="B1349" s="17">
         <v>79198880562</v>
       </c>
       <c r="C1349" s="3" t="s">
-        <v>2810</v>
+        <v>2796</v>
       </c>
       <c r="D1349" s="3" t="s">
-        <v>2814</v>
+        <v>2800</v>
       </c>
       <c r="E1349" s="3" t="s">
-        <v>2827</v>
+        <v>2813</v>
       </c>
       <c r="F1349" s="3" t="s">
-        <v>2563</v>
+        <v>2549</v>
       </c>
       <c r="G1349" s="2"/>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1350" s="6" t="s">
-        <v>2538</v>
+        <v>2524</v>
       </c>
       <c r="B1350" s="17"/>
       <c r="C1350" s="3"/>
@@ -33357,16 +33372,16 @@
     </row>
     <row r="1351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1351" s="6" t="s">
-        <v>2539</v>
+        <v>2525</v>
       </c>
       <c r="B1351" s="17">
         <v>79882440037</v>
       </c>
       <c r="C1351" s="3" t="s">
-        <v>2811</v>
+        <v>2797</v>
       </c>
       <c r="D1351" s="3" t="s">
-        <v>2813</v>
+        <v>2799</v>
       </c>
       <c r="E1351" s="3"/>
       <c r="F1351" s="3"/>
@@ -33374,16 +33389,16 @@
     </row>
     <row r="1352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1352" s="6" t="s">
-        <v>2540</v>
+        <v>2526</v>
       </c>
       <c r="B1352" s="17">
         <v>79187698925</v>
       </c>
       <c r="C1352" s="3" t="s">
-        <v>2811</v>
+        <v>2797</v>
       </c>
       <c r="D1352" s="3" t="s">
-        <v>2812</v>
+        <v>2798</v>
       </c>
       <c r="E1352" s="3"/>
       <c r="F1352" s="3"/>
@@ -33391,7 +33406,7 @@
     </row>
     <row r="1353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1353" s="6" t="s">
-        <v>2566</v>
+        <v>2552</v>
       </c>
       <c r="B1353" s="17"/>
       <c r="C1353" s="3"/>
@@ -33402,13 +33417,13 @@
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1354" s="6" t="s">
-        <v>2567</v>
+        <v>2553</v>
       </c>
       <c r="B1354" s="17">
         <v>79189831000</v>
       </c>
       <c r="C1354" s="3" t="s">
-        <v>2874</v>
+        <v>2860</v>
       </c>
       <c r="D1354" s="3"/>
       <c r="E1354" s="3"/>
@@ -33417,7 +33432,7 @@
     </row>
     <row r="1355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1355" s="6" t="s">
-        <v>2568</v>
+        <v>2554</v>
       </c>
       <c r="B1355" s="17"/>
       <c r="C1355" s="3"/>
@@ -33428,7 +33443,7 @@
     </row>
     <row r="1356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1356" s="6" t="s">
-        <v>2569</v>
+        <v>2555</v>
       </c>
       <c r="B1356" s="17">
         <v>79787158378</v>
@@ -33436,10 +33451,10 @@
       <c r="C1356" s="3"/>
       <c r="D1356" s="3"/>
       <c r="E1356" s="3" t="s">
-        <v>2885</v>
+        <v>2871</v>
       </c>
       <c r="F1356" s="3" t="s">
-        <v>2570</v>
+        <v>2556</v>
       </c>
       <c r="G1356" s="2"/>
     </row>
@@ -33462,7 +33477,7 @@
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1358" s="6" t="s">
-        <v>2571</v>
+        <v>2557</v>
       </c>
       <c r="B1358" s="17"/>
       <c r="C1358" s="3"/>
@@ -33473,16 +33488,16 @@
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1359" s="6" t="s">
-        <v>2572</v>
+        <v>2558</v>
       </c>
       <c r="B1359" s="17">
         <v>79381366868</v>
       </c>
       <c r="C1359" s="3" t="s">
-        <v>2875</v>
+        <v>2861</v>
       </c>
       <c r="D1359" s="3" t="s">
-        <v>2884</v>
+        <v>2870</v>
       </c>
       <c r="E1359" s="3"/>
       <c r="F1359" s="3"/>
@@ -33490,28 +33505,28 @@
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1360" s="6" t="s">
-        <v>2573</v>
+        <v>2559</v>
       </c>
       <c r="B1360" s="17">
         <v>79636924737</v>
       </c>
       <c r="C1360" s="3" t="s">
-        <v>2875</v>
+        <v>2861</v>
       </c>
       <c r="D1360" s="3" t="s">
-        <v>2884</v>
+        <v>2870</v>
       </c>
       <c r="E1360" s="3" t="s">
-        <v>2886</v>
+        <v>2872</v>
       </c>
       <c r="F1360" s="3" t="s">
-        <v>2579</v>
+        <v>2565</v>
       </c>
       <c r="G1360" s="2"/>
     </row>
     <row r="1361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1361" s="6" t="s">
-        <v>2574</v>
+        <v>2560</v>
       </c>
       <c r="B1361" s="17"/>
       <c r="C1361" s="3"/>
@@ -33522,26 +33537,26 @@
     </row>
     <row r="1362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1362" s="6" t="s">
-        <v>2575</v>
+        <v>2561</v>
       </c>
       <c r="B1362" s="17">
         <v>79265224303</v>
       </c>
       <c r="C1362" s="3" t="s">
-        <v>2876</v>
+        <v>2862</v>
       </c>
       <c r="D1362" s="3"/>
       <c r="E1362" s="3" t="s">
-        <v>2887</v>
+        <v>2873</v>
       </c>
       <c r="F1362" s="3" t="s">
-        <v>2580</v>
+        <v>2566</v>
       </c>
       <c r="G1362" s="2"/>
     </row>
     <row r="1363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1363" s="6" t="s">
-        <v>2576</v>
+        <v>2562</v>
       </c>
       <c r="B1363" s="17"/>
       <c r="C1363" s="3"/>
@@ -33552,16 +33567,16 @@
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1364" s="6" t="s">
-        <v>2577</v>
+        <v>2563</v>
       </c>
       <c r="B1364" s="17">
         <v>79064147502</v>
       </c>
       <c r="C1364" s="3" t="s">
-        <v>2877</v>
+        <v>2863</v>
       </c>
       <c r="D1364" s="3" t="s">
-        <v>2883</v>
+        <v>2869</v>
       </c>
       <c r="E1364" s="3"/>
       <c r="F1364" s="3"/>
@@ -33569,7 +33584,7 @@
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1365" s="6" t="s">
-        <v>2578</v>
+        <v>2564</v>
       </c>
       <c r="B1365" s="17">
         <v>79628802828</v>
@@ -33577,16 +33592,16 @@
       <c r="C1365" s="3"/>
       <c r="D1365" s="3"/>
       <c r="E1365" s="3" t="s">
-        <v>2888</v>
+        <v>2874</v>
       </c>
       <c r="F1365" s="3" t="s">
-        <v>2581</v>
+        <v>2567</v>
       </c>
       <c r="G1365" s="2"/>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1366" s="6" t="s">
-        <v>2628</v>
+        <v>2614</v>
       </c>
       <c r="B1366" s="17"/>
       <c r="C1366" s="3"/>
@@ -33597,13 +33612,13 @@
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1367" s="6" t="s">
-        <v>2629</v>
+        <v>2615</v>
       </c>
       <c r="B1367" s="17">
         <v>79324167398</v>
       </c>
       <c r="C1367" s="3" t="s">
-        <v>2878</v>
+        <v>2864</v>
       </c>
       <c r="D1367" s="3"/>
       <c r="E1367" s="3"/>
@@ -33612,26 +33627,26 @@
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1368" s="6" t="s">
-        <v>2630</v>
+        <v>2616</v>
       </c>
       <c r="B1368" s="17">
         <v>79056181271</v>
       </c>
       <c r="C1368" s="3" t="s">
-        <v>2878</v>
+        <v>2864</v>
       </c>
       <c r="D1368" s="3"/>
       <c r="E1368" s="3" t="s">
-        <v>2889</v>
+        <v>2875</v>
       </c>
       <c r="F1368" s="3" t="s">
-        <v>2631</v>
+        <v>2617</v>
       </c>
       <c r="G1368" s="2"/>
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1369" s="6" t="s">
-        <v>2632</v>
+        <v>2618</v>
       </c>
       <c r="B1369" s="17"/>
       <c r="C1369" s="3"/>
@@ -33642,16 +33657,16 @@
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1370" s="6" t="s">
-        <v>2633</v>
+        <v>2619</v>
       </c>
       <c r="B1370" s="17">
         <v>79276629955</v>
       </c>
       <c r="C1370" s="3" t="s">
-        <v>2879</v>
+        <v>2865</v>
       </c>
       <c r="D1370" s="3" t="s">
-        <v>2882</v>
+        <v>2868</v>
       </c>
       <c r="E1370" s="3"/>
       <c r="F1370" s="3"/>
@@ -33676,7 +33691,7 @@
     </row>
     <row r="1372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1372" s="6" t="s">
-        <v>2672</v>
+        <v>2658</v>
       </c>
       <c r="B1372" s="17"/>
       <c r="C1372" s="3"/>
@@ -33687,16 +33702,16 @@
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1373" s="6" t="s">
-        <v>2673</v>
+        <v>2659</v>
       </c>
       <c r="B1373" s="17">
         <v>79496106569</v>
       </c>
       <c r="C1373" s="3" t="s">
-        <v>2880</v>
+        <v>2866</v>
       </c>
       <c r="D1373" s="3" t="s">
-        <v>2881</v>
+        <v>2867</v>
       </c>
       <c r="E1373" s="3"/>
       <c r="F1373" s="3"/>
@@ -33704,7 +33719,7 @@
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1374" s="37" t="s">
-        <v>2674</v>
+        <v>2660</v>
       </c>
       <c r="B1374" s="16"/>
       <c r="C1374" s="2"/>
@@ -33715,16 +33730,16 @@
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1375" s="7" t="s">
-        <v>2675</v>
+        <v>2661</v>
       </c>
       <c r="B1375" s="16">
         <v>79287390768</v>
       </c>
       <c r="C1375" s="2" t="s">
-        <v>2683</v>
+        <v>2669</v>
       </c>
       <c r="D1375" s="2" t="s">
-        <v>2679</v>
+        <v>2665</v>
       </c>
       <c r="E1375" s="2"/>
       <c r="F1375" s="2"/>
@@ -33732,13 +33747,13 @@
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1376" s="7" t="s">
-        <v>2676</v>
+        <v>2662</v>
       </c>
       <c r="B1376" s="16">
         <v>79085216412</v>
       </c>
       <c r="C1376" s="2" t="s">
-        <v>2683</v>
+        <v>2669</v>
       </c>
       <c r="D1376" s="2"/>
       <c r="E1376" s="2"/>
@@ -33747,7 +33762,7 @@
     </row>
     <row r="1377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1377" s="37" t="s">
-        <v>2677</v>
+        <v>2663</v>
       </c>
       <c r="B1377" s="16"/>
       <c r="C1377" s="2"/>
@@ -33758,20 +33773,20 @@
     </row>
     <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1378" s="7" t="s">
-        <v>2678</v>
+        <v>2664</v>
       </c>
       <c r="B1378" s="16">
         <v>79803218503</v>
       </c>
       <c r="C1378" s="2" t="s">
-        <v>2680</v>
+        <v>2666</v>
       </c>
       <c r="D1378" s="2"/>
       <c r="E1378" s="2" t="s">
-        <v>2681</v>
+        <v>2667</v>
       </c>
       <c r="F1378" s="2" t="s">
-        <v>2682</v>
+        <v>2668</v>
       </c>
       <c r="G1378" s="2"/>
     </row>
@@ -33794,7 +33809,7 @@
     </row>
     <row r="1380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1380" s="37" t="s">
-        <v>2730</v>
+        <v>2716</v>
       </c>
       <c r="B1380" s="16"/>
       <c r="C1380" s="2"/>
@@ -33805,14 +33820,14 @@
     </row>
     <row r="1381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1381" s="7" t="s">
-        <v>2731</v>
+        <v>2717</v>
       </c>
       <c r="B1381" s="16">
         <v>79000072332</v>
       </c>
       <c r="C1381" s="2"/>
       <c r="D1381" s="2" t="s">
-        <v>2748</v>
+        <v>2734</v>
       </c>
       <c r="E1381" s="2"/>
       <c r="F1381" s="2"/>
@@ -33820,16 +33835,16 @@
     </row>
     <row r="1382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1382" s="7" t="s">
-        <v>2732</v>
+        <v>2718</v>
       </c>
       <c r="B1382" s="16">
         <v>79381241749</v>
       </c>
       <c r="C1382" s="2" t="s">
-        <v>2745</v>
+        <v>2731</v>
       </c>
       <c r="D1382" s="2" t="s">
-        <v>2747</v>
+        <v>2733</v>
       </c>
       <c r="E1382" s="2"/>
       <c r="F1382" s="2"/>
@@ -33837,13 +33852,13 @@
     </row>
     <row r="1383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1383" s="7" t="s">
-        <v>2733</v>
+        <v>2719</v>
       </c>
       <c r="B1383" s="16">
         <v>79183931723</v>
       </c>
       <c r="C1383" s="2" t="s">
-        <v>2745</v>
+        <v>2731</v>
       </c>
       <c r="D1383" s="2"/>
       <c r="E1383" s="2"/>
@@ -33853,7 +33868,7 @@
     </row>
     <row r="1384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1384" s="37" t="s">
-        <v>2734</v>
+        <v>2720</v>
       </c>
       <c r="B1384" s="16"/>
       <c r="C1384" s="2"/>
@@ -33865,35 +33880,35 @@
     </row>
     <row r="1385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1385" s="7" t="s">
-        <v>2735</v>
+        <v>2721</v>
       </c>
       <c r="B1385" s="16">
         <v>79895207444</v>
       </c>
       <c r="C1385" s="2" t="s">
-        <v>2745</v>
+        <v>2731</v>
       </c>
       <c r="D1385" s="2" t="s">
-        <v>2750</v>
+        <v>2736</v>
       </c>
       <c r="E1385" s="2" t="s">
-        <v>2754</v>
+        <v>2740</v>
       </c>
       <c r="F1385" s="2" t="s">
-        <v>2755</v>
+        <v>2741</v>
       </c>
       <c r="G1385" s="2"/>
       <c r="H1385" s="2"/>
     </row>
     <row r="1386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1386" s="7" t="s">
-        <v>2736</v>
+        <v>2722</v>
       </c>
       <c r="B1386" s="16">
         <v>79054396611</v>
       </c>
       <c r="C1386" s="2" t="s">
-        <v>2746</v>
+        <v>2732</v>
       </c>
       <c r="D1386" s="2"/>
       <c r="E1386" s="2"/>
@@ -33903,13 +33918,13 @@
     </row>
     <row r="1387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1387" s="7" t="s">
-        <v>2737</v>
+        <v>2723</v>
       </c>
       <c r="B1387" s="16">
         <v>79189914636</v>
       </c>
       <c r="C1387" s="2" t="s">
-        <v>2746</v>
+        <v>2732</v>
       </c>
       <c r="D1387" s="2"/>
       <c r="E1387" s="2"/>
@@ -33919,16 +33934,16 @@
     </row>
     <row r="1388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1388" s="7" t="s">
-        <v>2738</v>
+        <v>2724</v>
       </c>
       <c r="B1388" s="16">
         <v>79281644488</v>
       </c>
       <c r="C1388" s="2" t="s">
-        <v>2746</v>
+        <v>2732</v>
       </c>
       <c r="D1388" s="2" t="s">
-        <v>2751</v>
+        <v>2737</v>
       </c>
       <c r="E1388" s="2"/>
       <c r="F1388" s="2"/>
@@ -33937,7 +33952,7 @@
     </row>
     <row r="1389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1389" s="37" t="s">
-        <v>2739</v>
+        <v>2725</v>
       </c>
       <c r="B1389" s="16"/>
       <c r="C1389" s="2"/>
@@ -33949,14 +33964,14 @@
     </row>
     <row r="1390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1390" s="7" t="s">
-        <v>2740</v>
+        <v>2726</v>
       </c>
       <c r="B1390" s="16">
         <v>79969140482</v>
       </c>
       <c r="C1390" s="2"/>
       <c r="D1390" s="2" t="s">
-        <v>2752</v>
+        <v>2738</v>
       </c>
       <c r="E1390" s="2"/>
       <c r="F1390" s="2"/>
@@ -33965,16 +33980,16 @@
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1391" s="7" t="s">
-        <v>2741</v>
+        <v>2727</v>
       </c>
       <c r="B1391" s="16">
         <v>79034655195</v>
       </c>
       <c r="C1391" s="2" t="s">
-        <v>2749</v>
+        <v>2735</v>
       </c>
       <c r="D1391" s="2" t="s">
-        <v>2752</v>
+        <v>2738</v>
       </c>
       <c r="E1391" s="2"/>
       <c r="F1391" s="2"/>
@@ -33983,13 +33998,13 @@
     </row>
     <row r="1392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1392" s="7" t="s">
-        <v>2742</v>
+        <v>2728</v>
       </c>
       <c r="B1392" s="16">
         <v>79181891524</v>
       </c>
       <c r="C1392" s="2" t="s">
-        <v>2749</v>
+        <v>2735</v>
       </c>
       <c r="D1392" s="2"/>
       <c r="E1392" s="2"/>
@@ -33999,16 +34014,16 @@
     </row>
     <row r="1393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1393" s="7" t="s">
-        <v>2743</v>
+        <v>2729</v>
       </c>
       <c r="B1393" s="16">
         <v>79197527391</v>
       </c>
       <c r="C1393" s="2" t="s">
-        <v>2749</v>
+        <v>2735</v>
       </c>
       <c r="D1393" s="2" t="s">
-        <v>2753</v>
+        <v>2739</v>
       </c>
       <c r="E1393" s="2"/>
       <c r="F1393" s="2"/>
@@ -34017,14 +34032,14 @@
     </row>
     <row r="1394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1394" s="7" t="s">
-        <v>2744</v>
+        <v>2730</v>
       </c>
       <c r="B1394" s="16">
         <v>79032888829</v>
       </c>
       <c r="C1394" s="2"/>
       <c r="D1394" s="2" t="s">
-        <v>2752</v>
+        <v>2738</v>
       </c>
       <c r="E1394" s="2"/>
       <c r="F1394" s="2"/>
@@ -34051,7 +34066,7 @@
     </row>
     <row r="1396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1396" s="37" t="s">
-        <v>2757</v>
+        <v>2743</v>
       </c>
       <c r="B1396" s="16"/>
       <c r="C1396" s="2"/>
@@ -34063,7 +34078,7 @@
     </row>
     <row r="1397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1397" s="7" t="s">
-        <v>2758</v>
+        <v>2744</v>
       </c>
       <c r="B1397" s="16">
         <v>79282292956</v>
@@ -34071,17 +34086,17 @@
       <c r="C1397" s="2"/>
       <c r="D1397" s="2"/>
       <c r="E1397" s="2" t="s">
-        <v>2767</v>
+        <v>2753</v>
       </c>
       <c r="F1397" s="2" t="s">
-        <v>2766</v>
+        <v>2752</v>
       </c>
       <c r="G1397" s="2"/>
       <c r="H1397" s="2"/>
     </row>
     <row r="1398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1398" s="37" t="s">
-        <v>2759</v>
+        <v>2745</v>
       </c>
       <c r="B1398" s="16"/>
       <c r="C1398" s="2"/>
@@ -34093,16 +34108,16 @@
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1399" s="7" t="s">
-        <v>2760</v>
+        <v>2746</v>
       </c>
       <c r="B1399" s="16">
         <v>79892315277</v>
       </c>
       <c r="C1399" s="2" t="s">
-        <v>2764</v>
+        <v>2750</v>
       </c>
       <c r="D1399" s="2" t="s">
-        <v>2765</v>
+        <v>2751</v>
       </c>
       <c r="E1399" s="2"/>
       <c r="F1399" s="2"/>
@@ -34111,27 +34126,27 @@
     </row>
     <row r="1400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1400" s="7" t="s">
-        <v>2761</v>
+        <v>2747</v>
       </c>
       <c r="B1400" s="16">
         <v>79182323366</v>
       </c>
       <c r="C1400" s="2" t="s">
-        <v>2764</v>
+        <v>2750</v>
       </c>
       <c r="D1400" s="2"/>
       <c r="E1400" s="2" t="s">
-        <v>2769</v>
+        <v>2755</v>
       </c>
       <c r="F1400" s="2" t="s">
-        <v>2768</v>
+        <v>2754</v>
       </c>
       <c r="G1400" s="2"/>
       <c r="H1400" s="2"/>
     </row>
     <row r="1401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1401" s="37" t="s">
-        <v>2762</v>
+        <v>2748</v>
       </c>
       <c r="B1401" s="16"/>
       <c r="C1401" s="2"/>
@@ -34143,13 +34158,13 @@
     </row>
     <row r="1402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1402" s="7" t="s">
-        <v>2763</v>
+        <v>2749</v>
       </c>
       <c r="B1402" s="16">
         <v>79937726026</v>
       </c>
       <c r="C1402" s="2" t="s">
-        <v>2770</v>
+        <v>2756</v>
       </c>
       <c r="D1402" s="2"/>
       <c r="E1402" s="2"/>
@@ -34159,7 +34174,7 @@
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1403" s="7" t="s">
-        <v>2771</v>
+        <v>2757</v>
       </c>
       <c r="B1403" s="16"/>
       <c r="C1403" s="2"/>
@@ -34171,16 +34186,16 @@
     </row>
     <row r="1404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1404" s="7" t="s">
-        <v>2772</v>
+        <v>2758</v>
       </c>
       <c r="B1404" s="16">
         <v>79508496243</v>
       </c>
       <c r="C1404" s="2" t="s">
-        <v>2774</v>
+        <v>2760</v>
       </c>
       <c r="D1404" s="2" t="s">
-        <v>2773</v>
+        <v>2759</v>
       </c>
       <c r="E1404" s="2"/>
       <c r="F1404" s="2"/>
@@ -34189,7 +34204,7 @@
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1405" s="37" t="s">
-        <v>2828</v>
+        <v>2814</v>
       </c>
       <c r="B1405" s="16"/>
       <c r="C1405" s="2"/>
@@ -34201,38 +34216,38 @@
     </row>
     <row r="1406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1406" s="7" t="s">
-        <v>2829</v>
+        <v>2815</v>
       </c>
       <c r="B1406" s="16">
         <v>79045010358</v>
       </c>
       <c r="C1406" s="2" t="s">
-        <v>2835</v>
+        <v>2821</v>
       </c>
       <c r="D1406" s="2" t="s">
-        <v>2832</v>
+        <v>2818</v>
       </c>
       <c r="E1406" s="2" t="s">
-        <v>2837</v>
+        <v>2823</v>
       </c>
       <c r="F1406" s="2" t="s">
-        <v>2836</v>
+        <v>2822</v>
       </c>
       <c r="G1406" s="2" t="s">
-        <v>2834</v>
+        <v>2820</v>
       </c>
       <c r="H1406" s="2"/>
     </row>
     <row r="1407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1407" s="7" t="s">
-        <v>2830</v>
+        <v>2816</v>
       </c>
       <c r="B1407" s="16">
         <v>79155232799</v>
       </c>
       <c r="C1407" s="2"/>
       <c r="D1407" s="2" t="s">
-        <v>2833</v>
+        <v>2819</v>
       </c>
       <c r="E1407" s="2"/>
       <c r="F1407" s="2"/>
@@ -34241,13 +34256,13 @@
     </row>
     <row r="1408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1408" s="7" t="s">
-        <v>2831</v>
+        <v>2817</v>
       </c>
       <c r="B1408" s="16">
         <v>79281777077</v>
       </c>
       <c r="C1408" s="2" t="s">
-        <v>2835</v>
+        <v>2821</v>
       </c>
       <c r="D1408" s="2"/>
       <c r="E1408" s="2"/>
@@ -34275,7 +34290,7 @@
     </row>
     <row r="1410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1410" s="37" t="s">
-        <v>2838</v>
+        <v>2824</v>
       </c>
       <c r="B1410" s="16"/>
       <c r="C1410" s="2"/>
@@ -34287,38 +34302,38 @@
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1411" s="7" t="s">
-        <v>2839</v>
+        <v>2825</v>
       </c>
       <c r="B1411" s="16">
         <v>79034731643</v>
       </c>
       <c r="C1411" s="2" t="s">
-        <v>2848</v>
+        <v>2834</v>
       </c>
       <c r="D1411" s="2" t="s">
-        <v>2849</v>
+        <v>2835</v>
       </c>
       <c r="E1411" s="2" t="s">
-        <v>2857</v>
+        <v>2843</v>
       </c>
       <c r="F1411" s="2" t="s">
-        <v>2855</v>
+        <v>2841</v>
       </c>
       <c r="G1411" s="2"/>
       <c r="H1411" s="2"/>
     </row>
     <row r="1412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1412" s="7" t="s">
-        <v>2840</v>
+        <v>2826</v>
       </c>
       <c r="B1412" s="16">
         <v>79288803988</v>
       </c>
       <c r="C1412" s="2" t="s">
-        <v>2848</v>
+        <v>2834</v>
       </c>
       <c r="D1412" s="2" t="s">
-        <v>2850</v>
+        <v>2836</v>
       </c>
       <c r="E1412" s="2"/>
       <c r="F1412" s="2"/>
@@ -34327,7 +34342,7 @@
     </row>
     <row r="1413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1413" s="37" t="s">
-        <v>2841</v>
+        <v>2827</v>
       </c>
       <c r="B1413" s="16"/>
       <c r="C1413" s="2"/>
@@ -34339,16 +34354,16 @@
     </row>
     <row r="1414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1414" s="7" t="s">
-        <v>2842</v>
+        <v>2828</v>
       </c>
       <c r="B1414" s="16">
         <v>79184775008</v>
       </c>
       <c r="C1414" s="2" t="s">
-        <v>2851</v>
+        <v>2837</v>
       </c>
       <c r="D1414" s="2" t="s">
-        <v>2852</v>
+        <v>2838</v>
       </c>
       <c r="E1414" s="2"/>
       <c r="F1414" s="2"/>
@@ -34357,16 +34372,16 @@
     </row>
     <row r="1415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1415" s="7" t="s">
-        <v>2843</v>
+        <v>2829</v>
       </c>
       <c r="B1415" s="16">
         <v>79185810505</v>
       </c>
       <c r="C1415" s="2" t="s">
-        <v>2851</v>
+        <v>2837</v>
       </c>
       <c r="D1415" s="2" t="s">
-        <v>2854</v>
+        <v>2840</v>
       </c>
       <c r="E1415" s="2"/>
       <c r="F1415" s="2"/>
@@ -34375,7 +34390,7 @@
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1416" s="37" t="s">
-        <v>2844</v>
+        <v>2830</v>
       </c>
       <c r="B1416" s="16"/>
       <c r="C1416" s="2"/>
@@ -34387,7 +34402,7 @@
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1417" s="7" t="s">
-        <v>2845</v>
+        <v>2831</v>
       </c>
       <c r="B1417" s="16">
         <v>79876274373</v>
@@ -34395,24 +34410,24 @@
       <c r="C1417" s="2"/>
       <c r="D1417" s="2"/>
       <c r="E1417" s="2" t="s">
-        <v>2858</v>
+        <v>2844</v>
       </c>
       <c r="F1417" s="2" t="s">
-        <v>2856</v>
+        <v>2842</v>
       </c>
       <c r="G1417" s="2"/>
       <c r="H1417" s="2"/>
     </row>
     <row r="1418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1418" s="7" t="s">
-        <v>2846</v>
+        <v>2832</v>
       </c>
       <c r="B1418" s="16">
         <v>79186355444</v>
       </c>
       <c r="C1418" s="2"/>
       <c r="D1418" s="2" t="s">
-        <v>2853</v>
+        <v>2839</v>
       </c>
       <c r="E1418" s="2"/>
       <c r="F1418" s="2"/>
@@ -34421,14 +34436,14 @@
     </row>
     <row r="1419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1419" s="7" t="s">
-        <v>2847</v>
+        <v>2833</v>
       </c>
       <c r="B1419" s="16">
         <v>79184115068</v>
       </c>
       <c r="C1419" s="2"/>
       <c r="D1419" s="2" t="s">
-        <v>2853</v>
+        <v>2839</v>
       </c>
       <c r="E1419" s="2"/>
       <c r="F1419" s="2"/>
@@ -34437,7 +34452,7 @@
     </row>
     <row r="1420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1420" s="37" t="s">
-        <v>2862</v>
+        <v>2848</v>
       </c>
       <c r="B1420" s="16"/>
       <c r="C1420" s="2"/>
@@ -34449,13 +34464,13 @@
     </row>
     <row r="1421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1421" s="7" t="s">
-        <v>2859</v>
+        <v>2845</v>
       </c>
       <c r="B1421" s="16">
         <v>79287641001</v>
       </c>
       <c r="C1421" s="2" t="s">
-        <v>2866</v>
+        <v>2852</v>
       </c>
       <c r="D1421" s="2"/>
       <c r="E1421" s="2"/>
@@ -34465,16 +34480,16 @@
     </row>
     <row r="1422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1422" s="7" t="s">
-        <v>2860</v>
+        <v>2846</v>
       </c>
       <c r="B1422" s="16">
         <v>79384046645</v>
       </c>
       <c r="C1422" s="2" t="s">
-        <v>2866</v>
+        <v>2852</v>
       </c>
       <c r="D1422" s="2" t="s">
-        <v>2867</v>
+        <v>2853</v>
       </c>
       <c r="E1422" s="2"/>
       <c r="F1422" s="2"/>
@@ -34483,13 +34498,13 @@
     </row>
     <row r="1423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1423" s="7" t="s">
-        <v>2861</v>
+        <v>2847</v>
       </c>
       <c r="B1423" s="16">
         <v>79525762953</v>
       </c>
       <c r="C1423" s="2" t="s">
-        <v>2866</v>
+        <v>2852</v>
       </c>
       <c r="D1423" s="2"/>
       <c r="E1423" s="2"/>
@@ -34499,7 +34514,7 @@
     </row>
     <row r="1424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1424" s="37" t="s">
-        <v>2863</v>
+        <v>2849</v>
       </c>
       <c r="B1424" s="16"/>
       <c r="C1424" s="2"/>
@@ -34511,14 +34526,14 @@
     </row>
     <row r="1425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1425" s="7" t="s">
-        <v>2864</v>
+        <v>2850</v>
       </c>
       <c r="B1425" s="16">
         <v>79873945838</v>
       </c>
       <c r="C1425" s="2"/>
       <c r="D1425" s="2" t="s">
-        <v>2868</v>
+        <v>2854</v>
       </c>
       <c r="E1425" s="2"/>
       <c r="F1425" s="2"/>
@@ -34527,14 +34542,14 @@
     </row>
     <row r="1426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1426" s="7" t="s">
-        <v>2865</v>
+        <v>2851</v>
       </c>
       <c r="B1426" s="16">
         <v>79515080763</v>
       </c>
       <c r="C1426" s="2"/>
       <c r="D1426" s="2" t="s">
-        <v>2869</v>
+        <v>2855</v>
       </c>
       <c r="E1426" s="2"/>
       <c r="F1426" s="2"/>
@@ -34543,7 +34558,7 @@
     </row>
     <row r="1427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1427" s="37" t="s">
-        <v>2904</v>
+        <v>2890</v>
       </c>
       <c r="B1427" s="16"/>
       <c r="C1427" s="2"/>
@@ -34555,14 +34570,14 @@
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1428" s="7" t="s">
-        <v>2905</v>
+        <v>2891</v>
       </c>
       <c r="B1428" s="16">
         <v>79588660254</v>
       </c>
       <c r="C1428" s="2"/>
       <c r="D1428" s="2" t="s">
-        <v>2906</v>
+        <v>2892</v>
       </c>
       <c r="E1428" s="2"/>
       <c r="F1428" s="2"/>
@@ -34572,15 +34587,25 @@
     <row r="1429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1429" s="7"/>
       <c r="B1429" s="16"/>
-      <c r="C1429" s="2"/>
-      <c r="D1429" s="2"/>
-      <c r="E1429" s="2"/>
-      <c r="F1429" s="2"/>
+      <c r="C1429" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1429" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1429" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1429" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1429" s="2"/>
       <c r="H1429" s="2"/>
     </row>
     <row r="1430" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1430" s="7"/>
+      <c r="A1430" s="37" t="s">
+        <v>2893</v>
+      </c>
       <c r="B1430" s="16"/>
       <c r="C1430" s="2"/>
       <c r="D1430" s="2"/>
@@ -34590,177 +34615,446 @@
       <c r="H1430" s="2"/>
     </row>
     <row r="1431" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1431" s="1"/>
+      <c r="A1431" s="7" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B1431" s="16">
+        <v>79023891506</v>
+      </c>
+      <c r="C1431" s="2"/>
+      <c r="D1431" s="2" t="s">
+        <v>2897</v>
+      </c>
+      <c r="E1431" s="2"/>
+      <c r="F1431" s="2"/>
     </row>
     <row r="1432" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1432" s="1"/>
+      <c r="A1432" s="7" t="s">
+        <v>2895</v>
+      </c>
+      <c r="B1432" s="16">
+        <v>79184377062</v>
+      </c>
+      <c r="C1432" s="2" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D1432" s="2"/>
+      <c r="E1432" s="2"/>
+      <c r="F1432" s="2"/>
     </row>
     <row r="1433" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1433" s="1"/>
+      <c r="A1433" s="7"/>
+      <c r="B1433" s="16"/>
+      <c r="C1433" s="2"/>
+      <c r="D1433" s="2"/>
+      <c r="E1433" s="2"/>
+      <c r="F1433" s="2"/>
     </row>
     <row r="1434" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1434" s="1"/>
+      <c r="A1434" s="7"/>
+      <c r="B1434" s="16"/>
+      <c r="C1434" s="2"/>
+      <c r="D1434" s="2"/>
+      <c r="E1434" s="2"/>
+      <c r="F1434" s="2"/>
     </row>
     <row r="1435" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1435" s="1"/>
+      <c r="A1435" s="7"/>
+      <c r="B1435" s="16"/>
+      <c r="C1435" s="2"/>
+      <c r="D1435" s="2"/>
+      <c r="E1435" s="2"/>
+      <c r="F1435" s="2"/>
     </row>
     <row r="1436" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1436" s="1"/>
+      <c r="A1436" s="7"/>
+      <c r="B1436" s="16"/>
+      <c r="C1436" s="2"/>
+      <c r="D1436" s="2"/>
+      <c r="E1436" s="2"/>
+      <c r="F1436" s="2"/>
     </row>
     <row r="1437" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1437" s="1"/>
+      <c r="A1437" s="7"/>
+      <c r="B1437" s="16"/>
+      <c r="C1437" s="2"/>
+      <c r="D1437" s="2"/>
+      <c r="E1437" s="2"/>
+      <c r="F1437" s="2"/>
     </row>
     <row r="1438" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1438" s="1"/>
+      <c r="A1438" s="7"/>
+      <c r="B1438" s="16"/>
+      <c r="C1438" s="2"/>
+      <c r="D1438" s="2"/>
+      <c r="E1438" s="2"/>
+      <c r="F1438" s="2"/>
     </row>
     <row r="1439" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1439" s="1"/>
+      <c r="A1439" s="7"/>
+      <c r="B1439" s="16"/>
+      <c r="C1439" s="2"/>
+      <c r="D1439" s="2"/>
+      <c r="E1439" s="2"/>
+      <c r="F1439" s="2"/>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1440" s="1"/>
-    </row>
-    <row r="1441" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1441" s="1"/>
-    </row>
-    <row r="1442" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1442" s="1"/>
-    </row>
-    <row r="1443" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1443" s="1"/>
-    </row>
-    <row r="1444" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1444" s="1"/>
-    </row>
-    <row r="1445" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1445" s="1"/>
-    </row>
-    <row r="1446" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1446" s="1"/>
-    </row>
-    <row r="1447" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1447" s="1"/>
-    </row>
-    <row r="1448" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1448" s="1"/>
-    </row>
-    <row r="1449" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1449" s="1"/>
-    </row>
-    <row r="1450" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1450" s="1"/>
-    </row>
-    <row r="1451" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1451" s="1"/>
-    </row>
-    <row r="1452" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1452" s="1"/>
-    </row>
-    <row r="1453" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1453" s="1"/>
-    </row>
-    <row r="1454" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1454" s="1"/>
-    </row>
-    <row r="1455" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1455" s="1"/>
-    </row>
-    <row r="1456" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1456" s="1"/>
-    </row>
-    <row r="1457" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1457" s="1"/>
-    </row>
-    <row r="1458" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1458" s="1"/>
-    </row>
-    <row r="1459" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1459" s="1"/>
-    </row>
-    <row r="1460" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1460" s="1"/>
-    </row>
-    <row r="1461" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1461" s="1"/>
-    </row>
-    <row r="1462" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1462" s="1"/>
-    </row>
-    <row r="1463" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1463" s="1"/>
-    </row>
-    <row r="1464" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1464" s="1"/>
-    </row>
-    <row r="1465" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1465" s="1"/>
-    </row>
-    <row r="1466" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1466" s="1"/>
-    </row>
-    <row r="1467" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1467" s="1"/>
-    </row>
-    <row r="1468" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1468" s="1"/>
-    </row>
-    <row r="1469" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1469" s="1"/>
-    </row>
-    <row r="1470" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1470" s="1"/>
-    </row>
-    <row r="1471" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1471" s="1"/>
-    </row>
-    <row r="1472" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1472" s="1"/>
-    </row>
-    <row r="1473" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1473" s="1"/>
-    </row>
-    <row r="1474" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1474" s="1"/>
-    </row>
-    <row r="1475" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1475" s="1"/>
-    </row>
-    <row r="1476" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1476" s="1"/>
-    </row>
-    <row r="1477" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1477" s="1"/>
-    </row>
-    <row r="1478" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1478" s="1"/>
-    </row>
-    <row r="1479" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1479" s="1"/>
-    </row>
-    <row r="1480" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1480" s="1"/>
-    </row>
-    <row r="1481" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1481" s="1"/>
-    </row>
-    <row r="1482" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1482" s="1"/>
-    </row>
-    <row r="1483" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1483" s="1"/>
-    </row>
-    <row r="1484" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1440" s="7"/>
+      <c r="B1440" s="16"/>
+      <c r="C1440" s="2"/>
+      <c r="D1440" s="2"/>
+      <c r="E1440" s="2"/>
+      <c r="F1440" s="2"/>
+    </row>
+    <row r="1441" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1441" s="7"/>
+      <c r="B1441" s="16"/>
+      <c r="C1441" s="2"/>
+      <c r="D1441" s="2"/>
+      <c r="E1441" s="2"/>
+      <c r="F1441" s="2"/>
+    </row>
+    <row r="1442" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1442" s="7"/>
+      <c r="B1442" s="16"/>
+      <c r="C1442" s="2"/>
+      <c r="D1442" s="2"/>
+      <c r="E1442" s="2"/>
+      <c r="F1442" s="2"/>
+    </row>
+    <row r="1443" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1443" s="7"/>
+      <c r="B1443" s="16"/>
+      <c r="C1443" s="2"/>
+      <c r="D1443" s="2"/>
+      <c r="E1443" s="2"/>
+      <c r="F1443" s="2"/>
+    </row>
+    <row r="1444" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1444" s="7"/>
+      <c r="B1444" s="16"/>
+      <c r="C1444" s="2"/>
+      <c r="D1444" s="2"/>
+      <c r="E1444" s="2"/>
+      <c r="F1444" s="2"/>
+    </row>
+    <row r="1445" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1445" s="7"/>
+      <c r="B1445" s="16"/>
+      <c r="C1445" s="2"/>
+      <c r="D1445" s="2"/>
+      <c r="E1445" s="2"/>
+      <c r="F1445" s="2"/>
+    </row>
+    <row r="1446" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1446" s="7"/>
+      <c r="B1446" s="16"/>
+      <c r="C1446" s="2"/>
+      <c r="D1446" s="2"/>
+      <c r="E1446" s="2"/>
+      <c r="F1446" s="2"/>
+    </row>
+    <row r="1447" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1447" s="7"/>
+      <c r="B1447" s="16"/>
+      <c r="C1447" s="2"/>
+      <c r="D1447" s="2"/>
+      <c r="E1447" s="2"/>
+      <c r="F1447" s="2"/>
+    </row>
+    <row r="1448" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1448" s="7"/>
+      <c r="B1448" s="16"/>
+      <c r="C1448" s="2"/>
+      <c r="D1448" s="2"/>
+      <c r="E1448" s="2"/>
+      <c r="F1448" s="2"/>
+    </row>
+    <row r="1449" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1449" s="7"/>
+      <c r="B1449" s="16"/>
+      <c r="C1449" s="2"/>
+      <c r="D1449" s="2"/>
+      <c r="E1449" s="2"/>
+      <c r="F1449" s="2"/>
+    </row>
+    <row r="1450" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1450" s="7"/>
+      <c r="B1450" s="16"/>
+      <c r="C1450" s="2"/>
+      <c r="D1450" s="2"/>
+      <c r="E1450" s="2"/>
+      <c r="F1450" s="2"/>
+    </row>
+    <row r="1451" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1451" s="7"/>
+      <c r="B1451" s="16"/>
+      <c r="C1451" s="2"/>
+      <c r="D1451" s="2"/>
+      <c r="E1451" s="2"/>
+      <c r="F1451" s="2"/>
+    </row>
+    <row r="1452" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1452" s="7"/>
+      <c r="B1452" s="16"/>
+      <c r="C1452" s="2"/>
+      <c r="D1452" s="2"/>
+      <c r="E1452" s="2"/>
+      <c r="F1452" s="2"/>
+    </row>
+    <row r="1453" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1453" s="7"/>
+      <c r="B1453" s="16"/>
+      <c r="C1453" s="2"/>
+      <c r="D1453" s="2"/>
+      <c r="E1453" s="2"/>
+      <c r="F1453" s="2"/>
+    </row>
+    <row r="1454" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1454" s="7"/>
+      <c r="B1454" s="16"/>
+      <c r="C1454" s="2"/>
+      <c r="D1454" s="2"/>
+      <c r="E1454" s="2"/>
+      <c r="F1454" s="2"/>
+    </row>
+    <row r="1455" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1455" s="7"/>
+      <c r="B1455" s="16"/>
+      <c r="C1455" s="2"/>
+      <c r="D1455" s="2"/>
+      <c r="E1455" s="2"/>
+      <c r="F1455" s="2"/>
+    </row>
+    <row r="1456" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1456" s="7"/>
+      <c r="B1456" s="16"/>
+      <c r="C1456" s="2"/>
+      <c r="D1456" s="2"/>
+      <c r="E1456" s="2"/>
+      <c r="F1456" s="2"/>
+    </row>
+    <row r="1457" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1457" s="7"/>
+      <c r="B1457" s="16"/>
+      <c r="C1457" s="2"/>
+      <c r="D1457" s="2"/>
+      <c r="E1457" s="2"/>
+      <c r="F1457" s="2"/>
+    </row>
+    <row r="1458" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1458" s="7"/>
+      <c r="B1458" s="16"/>
+      <c r="C1458" s="2"/>
+      <c r="D1458" s="2"/>
+      <c r="E1458" s="2"/>
+      <c r="F1458" s="2"/>
+    </row>
+    <row r="1459" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1459" s="7"/>
+      <c r="B1459" s="16"/>
+      <c r="C1459" s="2"/>
+      <c r="D1459" s="2"/>
+      <c r="E1459" s="2"/>
+      <c r="F1459" s="2"/>
+    </row>
+    <row r="1460" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1460" s="7"/>
+      <c r="B1460" s="16"/>
+      <c r="C1460" s="2"/>
+      <c r="D1460" s="2"/>
+      <c r="E1460" s="2"/>
+      <c r="F1460" s="2"/>
+    </row>
+    <row r="1461" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1461" s="7"/>
+      <c r="B1461" s="16"/>
+      <c r="C1461" s="2"/>
+      <c r="D1461" s="2"/>
+      <c r="E1461" s="2"/>
+      <c r="F1461" s="2"/>
+    </row>
+    <row r="1462" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1462" s="7"/>
+      <c r="B1462" s="16"/>
+      <c r="C1462" s="2"/>
+      <c r="D1462" s="2"/>
+      <c r="E1462" s="2"/>
+      <c r="F1462" s="2"/>
+    </row>
+    <row r="1463" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1463" s="7"/>
+      <c r="B1463" s="16"/>
+      <c r="C1463" s="2"/>
+      <c r="D1463" s="2"/>
+      <c r="E1463" s="2"/>
+      <c r="F1463" s="2"/>
+    </row>
+    <row r="1464" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1464" s="7"/>
+      <c r="B1464" s="16"/>
+      <c r="C1464" s="2"/>
+      <c r="D1464" s="2"/>
+      <c r="E1464" s="2"/>
+      <c r="F1464" s="2"/>
+    </row>
+    <row r="1465" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1465" s="7"/>
+      <c r="B1465" s="16"/>
+      <c r="C1465" s="2"/>
+      <c r="D1465" s="2"/>
+      <c r="E1465" s="2"/>
+      <c r="F1465" s="2"/>
+    </row>
+    <row r="1466" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1466" s="7"/>
+      <c r="B1466" s="16"/>
+      <c r="C1466" s="2"/>
+      <c r="D1466" s="2"/>
+      <c r="E1466" s="2"/>
+      <c r="F1466" s="2"/>
+    </row>
+    <row r="1467" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1467" s="7"/>
+      <c r="B1467" s="16"/>
+      <c r="C1467" s="2"/>
+      <c r="D1467" s="2"/>
+      <c r="E1467" s="2"/>
+      <c r="F1467" s="2"/>
+    </row>
+    <row r="1468" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1468" s="7"/>
+      <c r="B1468" s="16"/>
+      <c r="C1468" s="2"/>
+      <c r="D1468" s="2"/>
+      <c r="E1468" s="2"/>
+      <c r="F1468" s="2"/>
+    </row>
+    <row r="1469" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1469" s="7"/>
+      <c r="B1469" s="16"/>
+      <c r="C1469" s="2"/>
+      <c r="D1469" s="2"/>
+      <c r="E1469" s="2"/>
+      <c r="F1469" s="2"/>
+    </row>
+    <row r="1470" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1470" s="7"/>
+      <c r="B1470" s="16"/>
+      <c r="C1470" s="2"/>
+      <c r="D1470" s="2"/>
+      <c r="E1470" s="2"/>
+      <c r="F1470" s="2"/>
+    </row>
+    <row r="1471" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1471" s="7"/>
+      <c r="B1471" s="16"/>
+      <c r="C1471" s="2"/>
+      <c r="D1471" s="2"/>
+      <c r="E1471" s="2"/>
+      <c r="F1471" s="2"/>
+    </row>
+    <row r="1472" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1472" s="7"/>
+      <c r="B1472" s="16"/>
+      <c r="C1472" s="2"/>
+      <c r="D1472" s="2"/>
+      <c r="E1472" s="2"/>
+      <c r="F1472" s="2"/>
+    </row>
+    <row r="1473" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1473" s="7"/>
+      <c r="B1473" s="16"/>
+      <c r="C1473" s="2"/>
+      <c r="D1473" s="2"/>
+      <c r="E1473" s="2"/>
+      <c r="F1473" s="2"/>
+    </row>
+    <row r="1474" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1474" s="7"/>
+      <c r="B1474" s="16"/>
+      <c r="C1474" s="2"/>
+      <c r="D1474" s="2"/>
+      <c r="E1474" s="2"/>
+      <c r="F1474" s="2"/>
+    </row>
+    <row r="1475" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1475" s="7"/>
+      <c r="B1475" s="16"/>
+      <c r="C1475" s="2"/>
+      <c r="D1475" s="2"/>
+      <c r="E1475" s="2"/>
+      <c r="F1475" s="2"/>
+    </row>
+    <row r="1476" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1476" s="7"/>
+      <c r="B1476" s="16"/>
+      <c r="C1476" s="2"/>
+      <c r="D1476" s="2"/>
+      <c r="E1476" s="2"/>
+      <c r="F1476" s="2"/>
+    </row>
+    <row r="1477" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1477" s="7"/>
+      <c r="B1477" s="16"/>
+      <c r="C1477" s="2"/>
+      <c r="D1477" s="2"/>
+      <c r="E1477" s="2"/>
+      <c r="F1477" s="2"/>
+    </row>
+    <row r="1478" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1478" s="7"/>
+      <c r="B1478" s="16"/>
+      <c r="C1478" s="2"/>
+      <c r="D1478" s="2"/>
+      <c r="E1478" s="2"/>
+      <c r="F1478" s="2"/>
+    </row>
+    <row r="1479" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1479" s="7"/>
+      <c r="B1479" s="16"/>
+      <c r="C1479" s="2"/>
+      <c r="D1479" s="2"/>
+      <c r="E1479" s="2"/>
+      <c r="F1479" s="2"/>
+    </row>
+    <row r="1480" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1480" s="7"/>
+      <c r="B1480" s="16"/>
+      <c r="C1480" s="2"/>
+      <c r="D1480" s="2"/>
+      <c r="E1480" s="2"/>
+      <c r="F1480" s="2"/>
+    </row>
+    <row r="1481" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1481" s="7"/>
+      <c r="B1481" s="16"/>
+      <c r="C1481" s="2"/>
+      <c r="D1481" s="2"/>
+      <c r="E1481" s="2"/>
+      <c r="F1481" s="2"/>
+    </row>
+    <row r="1482" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1482" s="7"/>
+      <c r="B1482" s="16"/>
+    </row>
+    <row r="1483" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1483" s="7"/>
+      <c r="B1483" s="16"/>
+    </row>
+    <row r="1484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1484" s="1"/>
     </row>
-    <row r="1485" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1485" s="1"/>
     </row>
-    <row r="1486" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1486" s="1"/>
     </row>
-    <row r="1487" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1487" s="1"/>
     </row>
-    <row r="1488" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1488" s="1"/>
     </row>
     <row r="1489" spans="1:1" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F90F1E-C1BB-4B0B-A0BF-0CFABAE7DAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE1DB02-6F6B-4794-971B-78311FD0E88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4452" uniqueCount="2912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4460" uniqueCount="2916">
   <si>
     <t>Пароль</t>
   </si>
@@ -8770,6 +8770,18 @@
   </si>
   <si>
     <t>/?78862</t>
+  </si>
+  <si>
+    <t>22888</t>
+  </si>
+  <si>
+    <t>16136</t>
+  </si>
+  <si>
+    <t>79270</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/EUqYrLvKhEQnVA</t>
   </si>
 </sst>
 </file>
@@ -34643,7 +34655,9 @@
       <c r="F1432" s="2"/>
     </row>
     <row r="1433" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1433" s="7"/>
+      <c r="A1433" s="37" t="s">
+        <v>2893</v>
+      </c>
       <c r="B1433" s="16"/>
       <c r="C1433" s="2"/>
       <c r="D1433" s="2"/>
@@ -34651,28 +34665,48 @@
       <c r="F1433" s="2"/>
     </row>
     <row r="1434" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1434" s="7"/>
-      <c r="B1434" s="16"/>
+      <c r="A1434" s="7" t="s">
+        <v>2912</v>
+      </c>
+      <c r="B1434" s="16">
+        <v>79066122888</v>
+      </c>
       <c r="C1434" s="2"/>
-      <c r="D1434" s="2"/>
+      <c r="D1434" s="2" t="s">
+        <v>2915</v>
+      </c>
       <c r="E1434" s="2"/>
       <c r="F1434" s="2"/>
     </row>
     <row r="1435" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1435" s="7"/>
-      <c r="B1435" s="16"/>
+      <c r="A1435" s="7" t="s">
+        <v>2913</v>
+      </c>
+      <c r="B1435" s="16">
+        <v>79959416136</v>
+      </c>
       <c r="C1435" s="2"/>
-      <c r="D1435" s="2"/>
+      <c r="D1435" s="2" t="s">
+        <v>2915</v>
+      </c>
       <c r="E1435" s="2"/>
       <c r="F1435" s="2"/>
     </row>
     <row r="1436" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1436" s="7"/>
-      <c r="B1436" s="16"/>
+      <c r="A1436" s="7" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B1436" s="16">
+        <v>79628779270</v>
+      </c>
       <c r="C1436" s="2"/>
       <c r="D1436" s="2"/>
-      <c r="E1436" s="2"/>
-      <c r="F1436" s="2"/>
+      <c r="E1436" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1436" s="2" t="s">
+        <v>731</v>
+      </c>
     </row>
     <row r="1437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1437" s="7"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE1DB02-6F6B-4794-971B-78311FD0E88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B7329D-415F-428E-9EB2-53BEFDD52E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4460" uniqueCount="2916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4460" uniqueCount="2918">
   <si>
     <t>Пароль</t>
   </si>
@@ -8782,6 +8782,12 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/EUqYrLvKhEQnVA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/aE6s0Lyid5h96A</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/L1tokmEblVCxpw</t>
   </si>
 </sst>
 </file>
@@ -34702,10 +34708,10 @@
       <c r="C1436" s="2"/>
       <c r="D1436" s="2"/>
       <c r="E1436" s="2" t="s">
-        <v>731</v>
+        <v>2917</v>
       </c>
       <c r="F1436" s="2" t="s">
-        <v>731</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="1437" spans="1:8" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B7329D-415F-428E-9EB2-53BEFDD52E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECBA0A4-E249-4DD9-97D1-FE3980D101CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4460" uniqueCount="2918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4470" uniqueCount="2925">
   <si>
     <t>Пароль</t>
   </si>
@@ -8031,21 +8031,9 @@
     <t>18503</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/7yOPZjleeyUa5w</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/Xlj5JdmGvFsPIA</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/-H5lAKsT8SR4eg</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/PWhZ4OVR8bWifg</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/w8_g3g1dKVk9Bg</t>
-  </si>
-  <si>
     <t>/?86608</t>
   </si>
   <si>
@@ -8229,36 +8217,6 @@
     <t>88829</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/tC9K-oTdrp79lw</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/lmbiau6IYHF5iA</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/57CLTjS72PT-_w</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/nz9Ad_9tE6aofg</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/b0jhXL1ANsG_OA</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/hJn8MHrzIlHlQg</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/X7GUvGXphPjaMw</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/ngWLwTxLxDD55g</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/Y14p6cQHw4C5Ww</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/oaSt3Co4L92WRQ</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/40c0_uD_UOdTCg</t>
   </si>
   <si>
@@ -8286,27 +8244,12 @@
     <t>26026</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/IXMoREWwLYuL2w</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/umAHFZyeLJvsJQ</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/kJVTRFiGHEsEYw</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/vhRDvpXrq6a-bw</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/7fquLgxRsrYjqQ</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/DrJEp8zIXx2S-Q</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/ZQLvNM8nbGg7Cw</t>
-  </si>
-  <si>
     <t>30/09/26/12:30</t>
   </si>
   <si>
@@ -8415,9 +8358,6 @@
     <t>!https://disk.yandex.ru/d/39jlmYAXMUCNvw</t>
   </si>
   <si>
-    <t>!https://disk.yandex.ru/d/fax7jYYqvSppAA</t>
-  </si>
-  <si>
     <t>!https://disk.yandex.ru/d/5Fh_cRghsUflaA</t>
   </si>
   <si>
@@ -8788,6 +8728,87 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/L1tokmEblVCxpw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/w8_g3g1dKVk9Bg</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/Xlj5JdmGvFsPIA</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/tC9K-oTdrp79lw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/lmbiau6IYHF5iA</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/b0jhXL1ANsG_OA</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/IXMoREWwLYuL2w</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/ZQLvNM8nbGg7Cw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/umAHFZyeLJvsJQ</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/ngWLwTxLxDD55g</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/Y14p6cQHw4C5Ww</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/X7GUvGXphPjaMw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/hJn8MHrzIlHlQg</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/57CLTjS72PT-_w</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/nz9Ad_9tE6aofg</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/7yOPZjleeyUa5w</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/-H5lAKsT8SR4eg</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/oaSt3Co4L92WRQ</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/vhRDvpXrq6a-bw</t>
+  </si>
+  <si>
+    <t>!https://disk.yandex.ru/d/DrJEp8zIXx2S-Q</t>
+  </si>
+  <si>
+    <t>08/10/26/11:30</t>
+  </si>
+  <si>
+    <t>97172</t>
+  </si>
+  <si>
+    <t>30457</t>
+  </si>
+  <si>
+    <t>08/10/26/15:00</t>
+  </si>
+  <si>
+    <t>09/10/26/11:30</t>
+  </si>
+  <si>
+    <t>00959</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/fax7jYYqvSppAA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/P1cyniJFzuwCaw</t>
   </si>
 </sst>
 </file>
@@ -30088,7 +30109,7 @@
     </row>
     <row r="1145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1145" s="38" t="s">
-        <v>2670</v>
+        <v>2666</v>
       </c>
       <c r="B1145" s="38">
         <v>79110886608</v>
@@ -30104,7 +30125,7 @@
     </row>
     <row r="1146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1146" s="32" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="B1146" s="33">
         <v>79884718844</v>
@@ -30120,7 +30141,7 @@
     </row>
     <row r="1147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1147" s="32" t="s">
-        <v>2672</v>
+        <v>2668</v>
       </c>
       <c r="B1147" s="33">
         <v>79185416500</v>
@@ -30138,7 +30159,7 @@
     </row>
     <row r="1148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1148" s="32" t="s">
-        <v>2673</v>
+        <v>2669</v>
       </c>
       <c r="B1148" s="33">
         <v>79883514535</v>
@@ -30156,7 +30177,7 @@
     </row>
     <row r="1149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1149" s="32" t="s">
-        <v>2674</v>
+        <v>2670</v>
       </c>
       <c r="B1149" s="33">
         <v>79181927858</v>
@@ -30174,7 +30195,7 @@
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1150" s="32" t="s">
-        <v>2675</v>
+        <v>2671</v>
       </c>
       <c r="B1150" s="33">
         <v>79034731171</v>
@@ -30202,7 +30223,7 @@
     </row>
     <row r="1152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1152" s="32" t="s">
-        <v>2676</v>
+        <v>2672</v>
       </c>
       <c r="B1152" s="33">
         <v>79518399099</v>
@@ -30218,7 +30239,7 @@
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1153" s="32" t="s">
-        <v>2677</v>
+        <v>2673</v>
       </c>
       <c r="B1153" s="33">
         <v>79199932589</v>
@@ -30236,7 +30257,7 @@
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1154" s="32" t="s">
-        <v>2678</v>
+        <v>2674</v>
       </c>
       <c r="B1154" s="33">
         <v>79898068383</v>
@@ -30254,7 +30275,7 @@
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1155" s="32" t="s">
-        <v>2679</v>
+        <v>2675</v>
       </c>
       <c r="B1155" s="33">
         <v>79493272312</v>
@@ -30270,7 +30291,7 @@
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1156" s="32" t="s">
-        <v>2680</v>
+        <v>2676</v>
       </c>
       <c r="B1156" s="33">
         <v>79184455113</v>
@@ -30286,7 +30307,7 @@
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1157" s="32" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="B1157" s="33">
         <v>79494697622</v>
@@ -30302,7 +30323,7 @@
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1158" s="32" t="s">
-        <v>2682</v>
+        <v>2678</v>
       </c>
       <c r="B1158" s="33">
         <v>79288803878</v>
@@ -30318,7 +30339,7 @@
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1159" s="32" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="B1159" s="33">
         <v>79284223859</v>
@@ -30348,7 +30369,7 @@
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1161" s="32" t="s">
-        <v>2684</v>
+        <v>2680</v>
       </c>
       <c r="B1161" s="33">
         <v>79189338233</v>
@@ -30402,7 +30423,7 @@
     </row>
     <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1164" s="32" t="s">
-        <v>2670</v>
+        <v>2666</v>
       </c>
       <c r="B1164" s="31">
         <v>79110886608</v>
@@ -30418,7 +30439,7 @@
     </row>
     <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1165" s="32" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="B1165" s="31">
         <v>79282750088</v>
@@ -30434,7 +30455,7 @@
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1166" s="32" t="s">
-        <v>2686</v>
+        <v>2682</v>
       </c>
       <c r="B1166" s="31">
         <v>79384085482</v>
@@ -30462,7 +30483,7 @@
     </row>
     <row r="1168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1168" s="32" t="s">
-        <v>2692</v>
+        <v>2688</v>
       </c>
       <c r="B1168" s="31">
         <v>79622153493</v>
@@ -30478,7 +30499,7 @@
     </row>
     <row r="1169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1169" s="32" t="s">
-        <v>2691</v>
+        <v>2687</v>
       </c>
       <c r="B1169" s="31">
         <v>79266122721</v>
@@ -30496,7 +30517,7 @@
     </row>
     <row r="1170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1170" s="32" t="s">
-        <v>2690</v>
+        <v>2686</v>
       </c>
       <c r="B1170" s="31">
         <v>79997719518</v>
@@ -30512,7 +30533,7 @@
     </row>
     <row r="1171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1171" s="32" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="B1171" s="31">
         <v>79813022825</v>
@@ -30540,7 +30561,7 @@
     </row>
     <row r="1173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1173" s="32" t="s">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="B1173" s="31">
         <v>79892367996</v>
@@ -30562,7 +30583,7 @@
     </row>
     <row r="1174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1174" s="32" t="s">
-        <v>2687</v>
+        <v>2683</v>
       </c>
       <c r="B1174" s="31">
         <v>79182617888</v>
@@ -30596,7 +30617,7 @@
     </row>
     <row r="1176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1176" s="32" t="s">
-        <v>2761</v>
+        <v>2742</v>
       </c>
       <c r="B1176" s="31">
         <v>79932156329</v>
@@ -30612,7 +30633,7 @@
     </row>
     <row r="1177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1177" s="32" t="s">
-        <v>2762</v>
+        <v>2743</v>
       </c>
       <c r="B1177" s="31">
         <v>79171772386</v>
@@ -30628,7 +30649,7 @@
     </row>
     <row r="1178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1178" s="32" t="s">
-        <v>2763</v>
+        <v>2744</v>
       </c>
       <c r="B1178" s="31">
         <v>79515365516</v>
@@ -30644,7 +30665,7 @@
     </row>
     <row r="1179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1179" s="32" t="s">
-        <v>2764</v>
+        <v>2745</v>
       </c>
       <c r="B1179" s="31">
         <v>79186559582</v>
@@ -30660,7 +30681,7 @@
     </row>
     <row r="1180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1180" s="32" t="s">
-        <v>2765</v>
+        <v>2746</v>
       </c>
       <c r="B1180" s="31">
         <v>79180300643</v>
@@ -30690,7 +30711,7 @@
     </row>
     <row r="1182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1182" s="32" t="s">
-        <v>2766</v>
+        <v>2747</v>
       </c>
       <c r="B1182" s="31">
         <v>79081882253</v>
@@ -30706,7 +30727,7 @@
     </row>
     <row r="1183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1183" s="32" t="s">
-        <v>2767</v>
+        <v>2748</v>
       </c>
       <c r="B1183" s="31">
         <v>79184570319</v>
@@ -30734,7 +30755,7 @@
     </row>
     <row r="1185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1185" s="32" t="s">
-        <v>2768</v>
+        <v>2749</v>
       </c>
       <c r="B1185" s="31">
         <v>79884600699</v>
@@ -30750,7 +30771,7 @@
     </row>
     <row r="1186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1186" s="32" t="s">
-        <v>2769</v>
+        <v>2750</v>
       </c>
       <c r="B1186" s="31">
         <v>79615933002</v>
@@ -30766,7 +30787,7 @@
     </row>
     <row r="1187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1187" s="32" t="s">
-        <v>2770</v>
+        <v>2751</v>
       </c>
       <c r="B1187" s="31">
         <v>79287615615</v>
@@ -30794,7 +30815,7 @@
     </row>
     <row r="1189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1189" s="32" t="s">
-        <v>2771</v>
+        <v>2752</v>
       </c>
       <c r="B1189" s="31">
         <v>79282298724</v>
@@ -30826,7 +30847,7 @@
     </row>
     <row r="1191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1191" s="32" t="s">
-        <v>2772</v>
+        <v>2753</v>
       </c>
       <c r="B1191" s="31">
         <v>79608204295</v>
@@ -30844,7 +30865,7 @@
     </row>
     <row r="1192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1192" s="32" t="s">
-        <v>2773</v>
+        <v>2754</v>
       </c>
       <c r="B1192" s="31">
         <v>79064969201</v>
@@ -30894,7 +30915,7 @@
     </row>
     <row r="1195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1195" s="32" t="s">
-        <v>2774</v>
+        <v>2755</v>
       </c>
       <c r="B1195" s="31">
         <v>79883604002</v>
@@ -30910,7 +30931,7 @@
     </row>
     <row r="1196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1196" s="32" t="s">
-        <v>2775</v>
+        <v>2756</v>
       </c>
       <c r="B1196" s="31">
         <v>79384102024</v>
@@ -30938,7 +30959,7 @@
     </row>
     <row r="1198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1198" s="32" t="s">
-        <v>2776</v>
+        <v>2757</v>
       </c>
       <c r="B1198" s="31">
         <v>79898514111</v>
@@ -30954,7 +30975,7 @@
     </row>
     <row r="1199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1199" s="32" t="s">
-        <v>2777</v>
+        <v>2758</v>
       </c>
       <c r="B1199" s="31">
         <v>79374645805</v>
@@ -30974,7 +30995,7 @@
     </row>
     <row r="1200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1200" s="32" t="s">
-        <v>2778</v>
+        <v>2759</v>
       </c>
       <c r="B1200" s="31">
         <v>79892931818</v>
@@ -31004,7 +31025,7 @@
     </row>
     <row r="1202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1202" s="32" t="s">
-        <v>2779</v>
+        <v>2760</v>
       </c>
       <c r="B1202" s="31">
         <v>79504617288</v>
@@ -31022,7 +31043,7 @@
     </row>
     <row r="1203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1203" s="32" t="s">
-        <v>2780</v>
+        <v>2761</v>
       </c>
       <c r="B1203" s="31">
         <v>79085129986</v>
@@ -31052,7 +31073,7 @@
     </row>
     <row r="1205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1205" s="32" t="s">
-        <v>2781</v>
+        <v>2762</v>
       </c>
       <c r="B1205" s="31">
         <v>79913567286</v>
@@ -31068,7 +31089,7 @@
     </row>
     <row r="1206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1206" s="32" t="s">
-        <v>2782</v>
+        <v>2763</v>
       </c>
       <c r="B1206" s="31">
         <v>79185010806</v>
@@ -31084,7 +31105,7 @@
     </row>
     <row r="1207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1207" s="32" t="s">
-        <v>2783</v>
+        <v>2764</v>
       </c>
       <c r="B1207" s="31">
         <v>79183185307</v>
@@ -31112,7 +31133,7 @@
     </row>
     <row r="1209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1209" s="32" t="s">
-        <v>2784</v>
+        <v>2765</v>
       </c>
       <c r="B1209" s="31">
         <v>79266566385</v>
@@ -31160,7 +31181,7 @@
     </row>
     <row r="1212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1212" s="32" t="s">
-        <v>2785</v>
+        <v>2766</v>
       </c>
       <c r="B1212" s="31">
         <v>79284341070</v>
@@ -31178,7 +31199,7 @@
     </row>
     <row r="1213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1213" s="32" t="s">
-        <v>2786</v>
+        <v>2767</v>
       </c>
       <c r="B1213" s="31">
         <v>79267958573</v>
@@ -31196,7 +31217,7 @@
     </row>
     <row r="1214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1214" s="32" t="s">
-        <v>2787</v>
+        <v>2768</v>
       </c>
       <c r="B1214" s="31">
         <v>79282480877</v>
@@ -31244,7 +31265,7 @@
     </row>
     <row r="1217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1217" s="32" t="s">
-        <v>2788</v>
+        <v>2769</v>
       </c>
       <c r="B1217" s="31">
         <v>79181763655</v>
@@ -31274,7 +31295,7 @@
     </row>
     <row r="1219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1219" s="32" t="s">
-        <v>2789</v>
+        <v>2770</v>
       </c>
       <c r="B1219" s="31">
         <v>79184256275</v>
@@ -31292,7 +31313,7 @@
     </row>
     <row r="1220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1220" s="32" t="s">
-        <v>2790</v>
+        <v>2771</v>
       </c>
       <c r="B1220" s="31">
         <v>79883151515</v>
@@ -31342,7 +31363,7 @@
     </row>
     <row r="1223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1223" s="32" t="s">
-        <v>2876</v>
+        <v>2856</v>
       </c>
       <c r="B1223" s="31">
         <v>79281186882</v>
@@ -31374,7 +31395,7 @@
     </row>
     <row r="1225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1225" s="32" t="s">
-        <v>2877</v>
+        <v>2857</v>
       </c>
       <c r="B1225" s="31">
         <v>79034547400</v>
@@ -31390,7 +31411,7 @@
     </row>
     <row r="1226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1226" s="32" t="s">
-        <v>2878</v>
+        <v>2858</v>
       </c>
       <c r="B1226" s="31">
         <v>79287721255</v>
@@ -31438,7 +31459,7 @@
     </row>
     <row r="1229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1229" s="32" t="s">
-        <v>2879</v>
+        <v>2859</v>
       </c>
       <c r="B1229" s="31">
         <v>79183615308</v>
@@ -31456,7 +31477,7 @@
     </row>
     <row r="1230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1230" s="32" t="s">
-        <v>2880</v>
+        <v>2860</v>
       </c>
       <c r="B1230" s="31">
         <v>79186212666</v>
@@ -31478,7 +31499,7 @@
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1231" s="32" t="s">
-        <v>2881</v>
+        <v>2861</v>
       </c>
       <c r="B1231" s="31">
         <v>79951882337</v>
@@ -31494,7 +31515,7 @@
     </row>
     <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1232" s="32" t="s">
-        <v>2882</v>
+        <v>2862</v>
       </c>
       <c r="B1232" s="31">
         <v>79002796431</v>
@@ -31512,7 +31533,7 @@
     </row>
     <row r="1233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1233" s="32" t="s">
-        <v>2883</v>
+        <v>2863</v>
       </c>
       <c r="B1233" s="31">
         <v>79384126478</v>
@@ -31540,7 +31561,7 @@
     </row>
     <row r="1235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1235" s="18" t="s">
-        <v>2884</v>
+        <v>2864</v>
       </c>
       <c r="B1235" s="19">
         <v>79184673083</v>
@@ -31602,7 +31623,7 @@
     </row>
     <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1238" s="32" t="s">
-        <v>2885</v>
+        <v>2865</v>
       </c>
       <c r="B1238" s="31">
         <v>79180458777</v>
@@ -31630,7 +31651,7 @@
     </row>
     <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1240" s="32" t="s">
-        <v>2886</v>
+        <v>2866</v>
       </c>
       <c r="B1240" s="31">
         <v>79183291413</v>
@@ -31648,7 +31669,7 @@
     </row>
     <row r="1241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1241" s="32" t="s">
-        <v>2887</v>
+        <v>2867</v>
       </c>
       <c r="B1241" s="31">
         <v>79882371168</v>
@@ -31666,7 +31687,7 @@
     </row>
     <row r="1242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1242" s="32" t="s">
-        <v>2888</v>
+        <v>2868</v>
       </c>
       <c r="B1242" s="31">
         <v>79885577597</v>
@@ -31682,7 +31703,7 @@
     </row>
     <row r="1243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1243" s="32" t="s">
-        <v>2889</v>
+        <v>2869</v>
       </c>
       <c r="B1243" s="33"/>
       <c r="C1243" s="31"/>
@@ -31728,7 +31749,7 @@
     </row>
     <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1246" s="32" t="s">
-        <v>2898</v>
+        <v>2878</v>
       </c>
       <c r="B1246" s="33">
         <v>79802319741</v>
@@ -31746,7 +31767,7 @@
     </row>
     <row r="1247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1247" s="32" t="s">
-        <v>2899</v>
+        <v>2879</v>
       </c>
       <c r="B1247" s="33">
         <v>79298260798</v>
@@ -31764,7 +31785,7 @@
     </row>
     <row r="1248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1248" s="32" t="s">
-        <v>2900</v>
+        <v>2880</v>
       </c>
       <c r="B1248" s="33">
         <v>79615901223</v>
@@ -31780,7 +31801,7 @@
     </row>
     <row r="1249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1249" s="32" t="s">
-        <v>2901</v>
+        <v>2881</v>
       </c>
       <c r="B1249" s="33">
         <v>79183331040</v>
@@ -31798,7 +31819,7 @@
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1250" s="32" t="s">
-        <v>2902</v>
+        <v>2882</v>
       </c>
       <c r="B1250" s="33">
         <v>79064077747</v>
@@ -31830,13 +31851,13 @@
     </row>
     <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1252" s="32" t="s">
-        <v>2903</v>
+        <v>2883</v>
       </c>
       <c r="B1252" s="33">
         <v>79181978847</v>
       </c>
       <c r="C1252" s="31" t="s">
-        <v>2742</v>
+        <v>2728</v>
       </c>
       <c r="D1252" s="31" t="s">
         <v>2543</v>
@@ -31852,7 +31873,7 @@
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1253" s="32" t="s">
-        <v>2904</v>
+        <v>2884</v>
       </c>
       <c r="B1253" s="33">
         <v>79183346962</v>
@@ -31882,7 +31903,7 @@
     </row>
     <row r="1255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1255" s="32" t="s">
-        <v>2905</v>
+        <v>2885</v>
       </c>
       <c r="B1255" s="33">
         <v>79518493781</v>
@@ -31898,7 +31919,7 @@
     </row>
     <row r="1256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1256" s="32" t="s">
-        <v>2906</v>
+        <v>2886</v>
       </c>
       <c r="B1256" s="33">
         <v>79180651355</v>
@@ -31914,7 +31935,7 @@
     </row>
     <row r="1257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1257" s="32" t="s">
-        <v>2907</v>
+        <v>2887</v>
       </c>
       <c r="B1257" s="33">
         <v>79281140670</v>
@@ -31942,7 +31963,7 @@
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1259" s="32" t="s">
-        <v>2908</v>
+        <v>2888</v>
       </c>
       <c r="B1259" s="33">
         <v>79200671177</v>
@@ -31958,7 +31979,7 @@
     </row>
     <row r="1260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1260" s="32" t="s">
-        <v>2909</v>
+        <v>2889</v>
       </c>
       <c r="B1260" s="33">
         <v>79186201442</v>
@@ -31988,7 +32009,7 @@
     </row>
     <row r="1262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1262" s="32" t="s">
-        <v>2910</v>
+        <v>2890</v>
       </c>
       <c r="B1262" s="33">
         <v>79183108008</v>
@@ -32004,7 +32025,7 @@
     </row>
     <row r="1263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1263" s="32" t="s">
-        <v>2911</v>
+        <v>2891</v>
       </c>
       <c r="B1263" s="33">
         <v>79097178862</v>
@@ -32139,7 +32160,7 @@
       </c>
       <c r="C1271" s="5"/>
       <c r="D1271" s="5" t="s">
-        <v>2715</v>
+        <v>2711</v>
       </c>
       <c r="E1271" s="5"/>
       <c r="F1271" s="5"/>
@@ -32200,10 +32221,10 @@
         <v>79883302117</v>
       </c>
       <c r="C1275" s="5" t="s">
-        <v>2858</v>
+        <v>2838</v>
       </c>
       <c r="D1275" s="5" t="s">
-        <v>2859</v>
+        <v>2839</v>
       </c>
       <c r="E1275" s="5"/>
       <c r="F1275" s="5"/>
@@ -32310,7 +32331,7 @@
         <v>79036910787</v>
       </c>
       <c r="C1282" s="3" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
       <c r="D1282" s="3"/>
       <c r="E1282" s="3"/>
@@ -32326,13 +32347,13 @@
         <v>79085097827</v>
       </c>
       <c r="C1283" s="3" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
       <c r="D1283" s="3" t="s">
-        <v>2710</v>
+        <v>2706</v>
       </c>
       <c r="E1283" s="3" t="s">
-        <v>2711</v>
+        <v>2707</v>
       </c>
       <c r="F1283" s="3" t="s">
         <v>2358</v>
@@ -32348,13 +32369,13 @@
         <v>79786456031</v>
       </c>
       <c r="C1284" s="3" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
       <c r="D1284" s="3" t="s">
-        <v>2709</v>
+        <v>2705</v>
       </c>
       <c r="E1284" s="3" t="s">
-        <v>2711</v>
+        <v>2707</v>
       </c>
       <c r="F1284" s="3" t="s">
         <v>2359</v>
@@ -32371,7 +32392,7 @@
       </c>
       <c r="C1285" s="3"/>
       <c r="D1285" s="3" t="s">
-        <v>2709</v>
+        <v>2705</v>
       </c>
       <c r="E1285" s="3"/>
       <c r="F1285" s="3"/>
@@ -32400,7 +32421,7 @@
       <c r="C1287" s="3"/>
       <c r="D1287" s="3"/>
       <c r="E1287" s="3" t="s">
-        <v>2712</v>
+        <v>2708</v>
       </c>
       <c r="F1287" s="3" t="s">
         <v>2360</v>
@@ -32416,10 +32437,10 @@
         <v>79618588262</v>
       </c>
       <c r="C1288" s="3" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="D1288" s="3" t="s">
-        <v>2708</v>
+        <v>2704</v>
       </c>
       <c r="E1288" s="3"/>
       <c r="F1288" s="3"/>
@@ -32436,7 +32457,7 @@
       <c r="C1289" s="3"/>
       <c r="D1289" s="3"/>
       <c r="E1289" s="3" t="s">
-        <v>2712</v>
+        <v>2708</v>
       </c>
       <c r="F1289" s="3" t="s">
         <v>2361</v>
@@ -32454,7 +32475,7 @@
       <c r="C1290" s="3"/>
       <c r="D1290" s="3"/>
       <c r="E1290" s="3" t="s">
-        <v>2712</v>
+        <v>2708</v>
       </c>
       <c r="F1290" s="3" t="s">
         <v>2361</v>
@@ -32470,7 +32491,7 @@
         <v>79184803174</v>
       </c>
       <c r="C1291" s="3" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="D1291" s="3"/>
       <c r="E1291" s="3"/>
@@ -32486,7 +32507,7 @@
         <v>79186825836</v>
       </c>
       <c r="C1292" s="3" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="D1292" s="3"/>
       <c r="E1292" s="3"/>
@@ -32502,7 +32523,7 @@
         <v>79182466940</v>
       </c>
       <c r="C1293" s="3" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="D1293" s="3"/>
       <c r="E1293" s="3"/>
@@ -32530,10 +32551,10 @@
         <v>79149202703</v>
       </c>
       <c r="C1295" s="3" t="s">
-        <v>2695</v>
+        <v>2691</v>
       </c>
       <c r="D1295" s="3" t="s">
-        <v>2707</v>
+        <v>2703</v>
       </c>
       <c r="E1295" s="3"/>
       <c r="F1295" s="3"/>
@@ -32548,11 +32569,11 @@
         <v>79885468941</v>
       </c>
       <c r="C1296" s="3" t="s">
-        <v>2695</v>
+        <v>2691</v>
       </c>
       <c r="D1296" s="3"/>
       <c r="E1296" s="3" t="s">
-        <v>2713</v>
+        <v>2709</v>
       </c>
       <c r="F1296" s="3" t="s">
         <v>2362</v>
@@ -32580,10 +32601,10 @@
         <v>79806633494</v>
       </c>
       <c r="C1298" s="3" t="s">
-        <v>2696</v>
+        <v>2692</v>
       </c>
       <c r="D1298" s="3" t="s">
-        <v>2706</v>
+        <v>2702</v>
       </c>
       <c r="E1298" s="3"/>
       <c r="F1298" s="3"/>
@@ -32628,7 +32649,7 @@
         <v>79525837593</v>
       </c>
       <c r="C1301" s="3" t="s">
-        <v>2697</v>
+        <v>2693</v>
       </c>
       <c r="D1301" s="3"/>
       <c r="E1301" s="3"/>
@@ -32644,10 +32665,10 @@
         <v>79183870112</v>
       </c>
       <c r="C1302" s="3" t="s">
-        <v>2697</v>
+        <v>2693</v>
       </c>
       <c r="D1302" s="3" t="s">
-        <v>2705</v>
+        <v>2701</v>
       </c>
       <c r="E1302" s="3"/>
       <c r="F1302" s="3"/>
@@ -32663,7 +32684,7 @@
       </c>
       <c r="C1303" s="3"/>
       <c r="D1303" s="3" t="s">
-        <v>2704</v>
+        <v>2700</v>
       </c>
       <c r="E1303" s="3"/>
       <c r="F1303" s="3"/>
@@ -32690,13 +32711,13 @@
         <v>79183772137</v>
       </c>
       <c r="C1305" s="3" t="s">
-        <v>2698</v>
+        <v>2694</v>
       </c>
       <c r="D1305" s="3" t="s">
-        <v>2703</v>
+        <v>2699</v>
       </c>
       <c r="E1305" s="3" t="s">
-        <v>2714</v>
+        <v>2710</v>
       </c>
       <c r="F1305" s="3" t="s">
         <v>2376</v>
@@ -32714,7 +32735,7 @@
       <c r="C1306" s="3"/>
       <c r="D1306" s="3"/>
       <c r="E1306" s="3" t="s">
-        <v>2714</v>
+        <v>2710</v>
       </c>
       <c r="F1306" s="3" t="s">
         <v>2377</v>
@@ -32731,7 +32752,7 @@
       </c>
       <c r="C1307" s="3"/>
       <c r="D1307" s="3" t="s">
-        <v>2702</v>
+        <v>2698</v>
       </c>
       <c r="E1307" s="3"/>
       <c r="F1307" s="3"/>
@@ -32747,7 +32768,7 @@
       </c>
       <c r="C1308" s="3"/>
       <c r="D1308" s="3" t="s">
-        <v>2702</v>
+        <v>2698</v>
       </c>
       <c r="E1308" s="3"/>
       <c r="F1308" s="3"/>
@@ -32775,7 +32796,7 @@
       </c>
       <c r="C1310" s="3"/>
       <c r="D1310" s="3" t="s">
-        <v>2701</v>
+        <v>2697</v>
       </c>
       <c r="E1310" s="3"/>
       <c r="F1310" s="3"/>
@@ -32790,7 +32811,7 @@
         <v>79497336125</v>
       </c>
       <c r="C1311" s="3" t="s">
-        <v>2699</v>
+        <v>2695</v>
       </c>
       <c r="D1311" s="3"/>
       <c r="E1311" s="3"/>
@@ -32807,7 +32828,7 @@
       </c>
       <c r="C1312" s="3"/>
       <c r="D1312" s="3" t="s">
-        <v>2700</v>
+        <v>2696</v>
       </c>
       <c r="E1312" s="3"/>
       <c r="F1312" s="3"/>
@@ -32851,10 +32872,10 @@
       </c>
       <c r="C1315" s="3"/>
       <c r="D1315" s="3" t="s">
-        <v>2809</v>
+        <v>2789</v>
       </c>
       <c r="E1315" s="3" t="s">
-        <v>2810</v>
+        <v>2790</v>
       </c>
       <c r="F1315" s="3" t="s">
         <v>2388</v>
@@ -32880,7 +32901,7 @@
         <v>79528700394</v>
       </c>
       <c r="C1317" s="3" t="s">
-        <v>2791</v>
+        <v>2772</v>
       </c>
       <c r="D1317" s="3"/>
       <c r="E1317" s="3"/>
@@ -32895,7 +32916,7 @@
         <v>79054305403</v>
       </c>
       <c r="C1318" s="3" t="s">
-        <v>2791</v>
+        <v>2772</v>
       </c>
       <c r="D1318" s="3"/>
       <c r="E1318" s="3"/>
@@ -32911,7 +32932,7 @@
       </c>
       <c r="C1319" s="3"/>
       <c r="D1319" s="3" t="s">
-        <v>2808</v>
+        <v>2788</v>
       </c>
       <c r="E1319" s="3"/>
       <c r="F1319" s="3"/>
@@ -32925,10 +32946,10 @@
         <v>79284483258</v>
       </c>
       <c r="C1320" s="3" t="s">
-        <v>2791</v>
+        <v>2772</v>
       </c>
       <c r="D1320" s="3" t="s">
-        <v>2808</v>
+        <v>2788</v>
       </c>
       <c r="E1320" s="3"/>
       <c r="F1320" s="3"/>
@@ -32953,7 +32974,7 @@
         <v>79081817570</v>
       </c>
       <c r="C1322" s="17" t="s">
-        <v>2792</v>
+        <v>2773</v>
       </c>
       <c r="D1322" s="3"/>
       <c r="E1322" s="3"/>
@@ -32970,7 +32991,7 @@
       <c r="C1323" s="28"/>
       <c r="D1323" s="3"/>
       <c r="E1323" s="3" t="s">
-        <v>2811</v>
+        <v>2791</v>
       </c>
       <c r="F1323" s="3" t="s">
         <v>2389</v>
@@ -32996,11 +33017,11 @@
         <v>79186195666</v>
       </c>
       <c r="C1325" s="3" t="s">
-        <v>2793</v>
+        <v>2923</v>
       </c>
       <c r="D1325" s="3"/>
       <c r="E1325" s="3" t="s">
-        <v>2812</v>
+        <v>2924</v>
       </c>
       <c r="F1325" s="3" t="s">
         <v>2489</v>
@@ -33016,10 +33037,10 @@
       </c>
       <c r="C1326" s="3"/>
       <c r="D1326" s="3" t="s">
-        <v>2807</v>
+        <v>2787</v>
       </c>
       <c r="E1326" s="3" t="s">
-        <v>2812</v>
+        <v>2792</v>
       </c>
       <c r="F1326" s="3" t="s">
         <v>2490</v>
@@ -33035,7 +33056,7 @@
       </c>
       <c r="C1327" s="3"/>
       <c r="D1327" s="3" t="s">
-        <v>2807</v>
+        <v>2787</v>
       </c>
       <c r="E1327" s="3"/>
       <c r="F1327" s="3"/>
@@ -33074,7 +33095,7 @@
       </c>
       <c r="C1330" s="3"/>
       <c r="D1330" s="3" t="s">
-        <v>2806</v>
+        <v>2786</v>
       </c>
       <c r="E1330" s="3"/>
       <c r="F1330" s="3"/>
@@ -33099,7 +33120,7 @@
         <v>79054871997</v>
       </c>
       <c r="C1332" s="3" t="s">
-        <v>2794</v>
+        <v>2774</v>
       </c>
       <c r="D1332" s="3"/>
       <c r="E1332" s="3"/>
@@ -33115,7 +33136,7 @@
       </c>
       <c r="C1333" s="3"/>
       <c r="D1333" s="3" t="s">
-        <v>2805</v>
+        <v>2785</v>
       </c>
       <c r="E1333" s="3"/>
       <c r="F1333" s="3"/>
@@ -33130,7 +33151,7 @@
       </c>
       <c r="C1334" s="3"/>
       <c r="D1334" s="3" t="s">
-        <v>2804</v>
+        <v>2784</v>
       </c>
       <c r="E1334" s="3"/>
       <c r="F1334" s="3"/>
@@ -33144,7 +33165,7 @@
         <v>79780045546</v>
       </c>
       <c r="C1335" s="3" t="s">
-        <v>2794</v>
+        <v>2774</v>
       </c>
       <c r="D1335" s="3"/>
       <c r="E1335" s="3"/>
@@ -33187,10 +33208,10 @@
         <v>79782640332</v>
       </c>
       <c r="C1338" s="5" t="s">
-        <v>2856</v>
+        <v>2836</v>
       </c>
       <c r="D1338" s="5" t="s">
-        <v>2857</v>
+        <v>2837</v>
       </c>
       <c r="E1338" s="5"/>
       <c r="F1338" s="5"/>
@@ -33215,10 +33236,10 @@
         <v>79530977713</v>
       </c>
       <c r="C1340" s="3" t="s">
-        <v>2795</v>
+        <v>2775</v>
       </c>
       <c r="D1340" s="3" t="s">
-        <v>2803</v>
+        <v>2783</v>
       </c>
       <c r="E1340" s="3"/>
       <c r="F1340" s="3"/>
@@ -33233,7 +33254,7 @@
       </c>
       <c r="C1341" s="3"/>
       <c r="D1341" s="3" t="s">
-        <v>2802</v>
+        <v>2782</v>
       </c>
       <c r="E1341" s="3"/>
       <c r="F1341" s="3"/>
@@ -33292,7 +33313,7 @@
       <c r="C1345" s="3"/>
       <c r="D1345" s="3"/>
       <c r="E1345" s="3" t="s">
-        <v>2813</v>
+        <v>2793</v>
       </c>
       <c r="F1345" s="3" t="s">
         <v>2550</v>
@@ -33308,7 +33329,7 @@
       </c>
       <c r="C1346" s="3"/>
       <c r="D1346" s="3" t="s">
-        <v>2801</v>
+        <v>2781</v>
       </c>
       <c r="E1346" s="3"/>
       <c r="F1346" s="3"/>
@@ -33325,7 +33346,7 @@
         <v>2523</v>
       </c>
       <c r="D1347" s="3" t="s">
-        <v>2800</v>
+        <v>2780</v>
       </c>
       <c r="E1347" s="3" t="s">
         <v>2551</v>
@@ -33343,10 +33364,10 @@
         <v>79183887841</v>
       </c>
       <c r="C1348" s="3" t="s">
-        <v>2796</v>
+        <v>2776</v>
       </c>
       <c r="D1348" s="3" t="s">
-        <v>2800</v>
+        <v>2780</v>
       </c>
       <c r="E1348" s="3" t="s">
         <v>2551</v>
@@ -33364,13 +33385,13 @@
         <v>79198880562</v>
       </c>
       <c r="C1349" s="3" t="s">
-        <v>2796</v>
+        <v>2776</v>
       </c>
       <c r="D1349" s="3" t="s">
-        <v>2800</v>
+        <v>2780</v>
       </c>
       <c r="E1349" s="3" t="s">
-        <v>2813</v>
+        <v>2793</v>
       </c>
       <c r="F1349" s="3" t="s">
         <v>2549</v>
@@ -33396,10 +33417,10 @@
         <v>79882440037</v>
       </c>
       <c r="C1351" s="3" t="s">
-        <v>2797</v>
+        <v>2777</v>
       </c>
       <c r="D1351" s="3" t="s">
-        <v>2799</v>
+        <v>2779</v>
       </c>
       <c r="E1351" s="3"/>
       <c r="F1351" s="3"/>
@@ -33413,10 +33434,10 @@
         <v>79187698925</v>
       </c>
       <c r="C1352" s="3" t="s">
-        <v>2797</v>
+        <v>2777</v>
       </c>
       <c r="D1352" s="3" t="s">
-        <v>2798</v>
+        <v>2778</v>
       </c>
       <c r="E1352" s="3"/>
       <c r="F1352" s="3"/>
@@ -33441,7 +33462,7 @@
         <v>79189831000</v>
       </c>
       <c r="C1354" s="3" t="s">
-        <v>2860</v>
+        <v>2840</v>
       </c>
       <c r="D1354" s="3"/>
       <c r="E1354" s="3"/>
@@ -33469,7 +33490,7 @@
       <c r="C1356" s="3"/>
       <c r="D1356" s="3"/>
       <c r="E1356" s="3" t="s">
-        <v>2871</v>
+        <v>2851</v>
       </c>
       <c r="F1356" s="3" t="s">
         <v>2556</v>
@@ -33512,10 +33533,10 @@
         <v>79381366868</v>
       </c>
       <c r="C1359" s="3" t="s">
-        <v>2861</v>
+        <v>2841</v>
       </c>
       <c r="D1359" s="3" t="s">
-        <v>2870</v>
+        <v>2850</v>
       </c>
       <c r="E1359" s="3"/>
       <c r="F1359" s="3"/>
@@ -33529,13 +33550,13 @@
         <v>79636924737</v>
       </c>
       <c r="C1360" s="3" t="s">
-        <v>2861</v>
+        <v>2841</v>
       </c>
       <c r="D1360" s="3" t="s">
-        <v>2870</v>
+        <v>2850</v>
       </c>
       <c r="E1360" s="3" t="s">
-        <v>2872</v>
+        <v>2852</v>
       </c>
       <c r="F1360" s="3" t="s">
         <v>2565</v>
@@ -33561,11 +33582,11 @@
         <v>79265224303</v>
       </c>
       <c r="C1362" s="3" t="s">
-        <v>2862</v>
+        <v>2842</v>
       </c>
       <c r="D1362" s="3"/>
       <c r="E1362" s="3" t="s">
-        <v>2873</v>
+        <v>2853</v>
       </c>
       <c r="F1362" s="3" t="s">
         <v>2566</v>
@@ -33591,10 +33612,10 @@
         <v>79064147502</v>
       </c>
       <c r="C1364" s="3" t="s">
-        <v>2863</v>
+        <v>2843</v>
       </c>
       <c r="D1364" s="3" t="s">
-        <v>2869</v>
+        <v>2849</v>
       </c>
       <c r="E1364" s="3"/>
       <c r="F1364" s="3"/>
@@ -33610,7 +33631,7 @@
       <c r="C1365" s="3"/>
       <c r="D1365" s="3"/>
       <c r="E1365" s="3" t="s">
-        <v>2874</v>
+        <v>2854</v>
       </c>
       <c r="F1365" s="3" t="s">
         <v>2567</v>
@@ -33636,7 +33657,7 @@
         <v>79324167398</v>
       </c>
       <c r="C1367" s="3" t="s">
-        <v>2864</v>
+        <v>2844</v>
       </c>
       <c r="D1367" s="3"/>
       <c r="E1367" s="3"/>
@@ -33651,11 +33672,11 @@
         <v>79056181271</v>
       </c>
       <c r="C1368" s="3" t="s">
-        <v>2864</v>
+        <v>2844</v>
       </c>
       <c r="D1368" s="3"/>
       <c r="E1368" s="3" t="s">
-        <v>2875</v>
+        <v>2855</v>
       </c>
       <c r="F1368" s="3" t="s">
         <v>2617</v>
@@ -33681,10 +33702,10 @@
         <v>79276629955</v>
       </c>
       <c r="C1370" s="3" t="s">
-        <v>2865</v>
+        <v>2845</v>
       </c>
       <c r="D1370" s="3" t="s">
-        <v>2868</v>
+        <v>2848</v>
       </c>
       <c r="E1370" s="3"/>
       <c r="F1370" s="3"/>
@@ -33726,473 +33747,473 @@
         <v>79496106569</v>
       </c>
       <c r="C1373" s="3" t="s">
-        <v>2866</v>
+        <v>2846</v>
       </c>
       <c r="D1373" s="3" t="s">
-        <v>2867</v>
+        <v>2847</v>
       </c>
       <c r="E1373" s="3"/>
       <c r="F1373" s="3"/>
       <c r="G1373" s="2"/>
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1374" s="37" t="s">
+      <c r="A1374" s="6" t="s">
         <v>2660</v>
       </c>
-      <c r="B1374" s="16"/>
-      <c r="C1374" s="2"/>
-      <c r="D1374" s="2"/>
-      <c r="E1374" s="2"/>
-      <c r="F1374" s="2"/>
+      <c r="B1374" s="17"/>
+      <c r="C1374" s="3"/>
+      <c r="D1374" s="3"/>
+      <c r="E1374" s="3"/>
+      <c r="F1374" s="3"/>
       <c r="G1374" s="2"/>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1375" s="7" t="s">
+      <c r="A1375" s="6" t="s">
         <v>2661</v>
       </c>
-      <c r="B1375" s="16">
+      <c r="B1375" s="17">
         <v>79287390768</v>
       </c>
-      <c r="C1375" s="2" t="s">
-        <v>2669</v>
-      </c>
-      <c r="D1375" s="2" t="s">
+      <c r="C1375" s="3" t="s">
+        <v>2898</v>
+      </c>
+      <c r="D1375" s="3" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E1375" s="3"/>
+      <c r="F1375" s="3"/>
+      <c r="G1375" s="2"/>
+    </row>
+    <row r="1376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1376" s="6" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B1376" s="17">
+        <v>79085216412</v>
+      </c>
+      <c r="C1376" s="3" t="s">
+        <v>2898</v>
+      </c>
+      <c r="D1376" s="3"/>
+      <c r="E1376" s="3"/>
+      <c r="F1376" s="3"/>
+      <c r="G1376" s="2"/>
+    </row>
+    <row r="1377" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1377" s="6" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B1377" s="17"/>
+      <c r="C1377" s="3"/>
+      <c r="D1377" s="3"/>
+      <c r="E1377" s="3"/>
+      <c r="F1377" s="3"/>
+      <c r="G1377" s="2"/>
+    </row>
+    <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1378" s="6" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B1378" s="17">
+        <v>79803218503</v>
+      </c>
+      <c r="C1378" s="3" t="s">
+        <v>2899</v>
+      </c>
+      <c r="D1378" s="3"/>
+      <c r="E1378" s="3" t="s">
+        <v>2913</v>
+      </c>
+      <c r="F1378" s="3" t="s">
         <v>2665</v>
       </c>
-      <c r="E1375" s="2"/>
-      <c r="F1375" s="2"/>
-      <c r="G1375" s="2"/>
-    </row>
-    <row r="1376" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1376" s="7" t="s">
-        <v>2662</v>
-      </c>
-      <c r="B1376" s="16">
-        <v>79085216412</v>
-      </c>
-      <c r="C1376" s="2" t="s">
-        <v>2669</v>
-      </c>
-      <c r="D1376" s="2"/>
-      <c r="E1376" s="2"/>
-      <c r="F1376" s="2"/>
-      <c r="G1376" s="2"/>
-    </row>
-    <row r="1377" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1377" s="37" t="s">
-        <v>2663</v>
-      </c>
-      <c r="B1377" s="16"/>
-      <c r="C1377" s="2"/>
-      <c r="D1377" s="2"/>
-      <c r="E1377" s="2"/>
-      <c r="F1377" s="2"/>
-      <c r="G1377" s="2"/>
-    </row>
-    <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1378" s="7" t="s">
-        <v>2664</v>
-      </c>
-      <c r="B1378" s="16">
-        <v>79803218503</v>
-      </c>
-      <c r="C1378" s="2" t="s">
-        <v>2666</v>
-      </c>
-      <c r="D1378" s="2"/>
-      <c r="E1378" s="2" t="s">
-        <v>2667</v>
-      </c>
-      <c r="F1378" s="2" t="s">
-        <v>2668</v>
-      </c>
       <c r="G1378" s="2"/>
     </row>
     <row r="1379" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1379" s="7"/>
-      <c r="B1379" s="16"/>
-      <c r="C1379" s="2" t="s">
+      <c r="A1379" s="6"/>
+      <c r="B1379" s="17"/>
+      <c r="C1379" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1379" s="2" t="s">
+      <c r="D1379" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1379" s="2" t="s">
+      <c r="E1379" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1379" s="4" t="s">
+      <c r="F1379" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G1379" s="2"/>
     </row>
     <row r="1380" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1380" s="37" t="s">
-        <v>2716</v>
-      </c>
-      <c r="B1380" s="16"/>
-      <c r="C1380" s="2"/>
-      <c r="D1380" s="2"/>
-      <c r="E1380" s="2"/>
-      <c r="F1380" s="2"/>
+      <c r="A1380" s="6" t="s">
+        <v>2712</v>
+      </c>
+      <c r="B1380" s="17"/>
+      <c r="C1380" s="3"/>
+      <c r="D1380" s="3"/>
+      <c r="E1380" s="3"/>
+      <c r="F1380" s="3"/>
       <c r="G1380" s="2"/>
     </row>
     <row r="1381" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1381" s="7" t="s">
-        <v>2717</v>
-      </c>
-      <c r="B1381" s="16">
+      <c r="A1381" s="6" t="s">
+        <v>2713</v>
+      </c>
+      <c r="B1381" s="17">
         <v>79000072332</v>
       </c>
-      <c r="C1381" s="2"/>
-      <c r="D1381" s="2" t="s">
-        <v>2734</v>
-      </c>
-      <c r="E1381" s="2"/>
-      <c r="F1381" s="2"/>
+      <c r="C1381" s="3"/>
+      <c r="D1381" s="3" t="s">
+        <v>2911</v>
+      </c>
+      <c r="E1381" s="3"/>
+      <c r="F1381" s="3"/>
       <c r="G1381" s="2"/>
     </row>
     <row r="1382" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1382" s="7" t="s">
-        <v>2718</v>
-      </c>
-      <c r="B1382" s="16">
+      <c r="A1382" s="6" t="s">
+        <v>2714</v>
+      </c>
+      <c r="B1382" s="17">
         <v>79381241749</v>
       </c>
-      <c r="C1382" s="2" t="s">
-        <v>2731</v>
-      </c>
-      <c r="D1382" s="2" t="s">
-        <v>2733</v>
-      </c>
-      <c r="E1382" s="2"/>
-      <c r="F1382" s="2"/>
+      <c r="C1382" s="3" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D1382" s="3" t="s">
+        <v>2910</v>
+      </c>
+      <c r="E1382" s="3"/>
+      <c r="F1382" s="3"/>
       <c r="G1382" s="2"/>
     </row>
     <row r="1383" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1383" s="7" t="s">
-        <v>2719</v>
-      </c>
-      <c r="B1383" s="16">
+      <c r="A1383" s="6" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B1383" s="17">
         <v>79183931723</v>
       </c>
-      <c r="C1383" s="2" t="s">
-        <v>2731</v>
-      </c>
-      <c r="D1383" s="2"/>
-      <c r="E1383" s="2"/>
-      <c r="F1383" s="2"/>
+      <c r="C1383" s="3" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D1383" s="3"/>
+      <c r="E1383" s="3"/>
+      <c r="F1383" s="3"/>
       <c r="G1383" s="2"/>
       <c r="H1383" s="2"/>
     </row>
     <row r="1384" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1384" s="37" t="s">
-        <v>2720</v>
-      </c>
-      <c r="B1384" s="16"/>
-      <c r="C1384" s="2"/>
-      <c r="D1384" s="2"/>
-      <c r="E1384" s="2"/>
-      <c r="F1384" s="2"/>
+      <c r="A1384" s="6" t="s">
+        <v>2716</v>
+      </c>
+      <c r="B1384" s="17"/>
+      <c r="C1384" s="3"/>
+      <c r="D1384" s="3"/>
+      <c r="E1384" s="3"/>
+      <c r="F1384" s="3"/>
       <c r="G1384" s="2"/>
       <c r="H1384" s="2"/>
     </row>
     <row r="1385" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1385" s="7" t="s">
-        <v>2721</v>
-      </c>
-      <c r="B1385" s="16">
+      <c r="A1385" s="6" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B1385" s="17">
         <v>79895207444</v>
       </c>
-      <c r="C1385" s="2" t="s">
-        <v>2731</v>
-      </c>
-      <c r="D1385" s="2" t="s">
-        <v>2736</v>
-      </c>
-      <c r="E1385" s="2" t="s">
-        <v>2740</v>
-      </c>
-      <c r="F1385" s="2" t="s">
-        <v>2741</v>
+      <c r="C1385" s="3" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D1385" s="3" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E1385" s="3" t="s">
+        <v>2914</v>
+      </c>
+      <c r="F1385" s="3" t="s">
+        <v>2727</v>
       </c>
       <c r="G1385" s="2"/>
       <c r="H1385" s="2"/>
     </row>
     <row r="1386" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1386" s="7" t="s">
-        <v>2722</v>
-      </c>
-      <c r="B1386" s="16">
+      <c r="A1386" s="6" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B1386" s="17">
         <v>79054396611</v>
       </c>
-      <c r="C1386" s="2" t="s">
-        <v>2732</v>
-      </c>
-      <c r="D1386" s="2"/>
-      <c r="E1386" s="2"/>
-      <c r="F1386" s="2"/>
+      <c r="C1386" s="3" t="s">
+        <v>2901</v>
+      </c>
+      <c r="D1386" s="3"/>
+      <c r="E1386" s="3"/>
+      <c r="F1386" s="3"/>
       <c r="G1386" s="2"/>
       <c r="H1386" s="2"/>
     </row>
     <row r="1387" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1387" s="7" t="s">
-        <v>2723</v>
-      </c>
-      <c r="B1387" s="16">
+      <c r="A1387" s="6" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B1387" s="17">
         <v>79189914636</v>
       </c>
-      <c r="C1387" s="2" t="s">
-        <v>2732</v>
-      </c>
-      <c r="D1387" s="2"/>
-      <c r="E1387" s="2"/>
-      <c r="F1387" s="2"/>
+      <c r="C1387" s="3" t="s">
+        <v>2901</v>
+      </c>
+      <c r="D1387" s="3"/>
+      <c r="E1387" s="3"/>
+      <c r="F1387" s="3"/>
       <c r="G1387" s="2"/>
       <c r="H1387" s="2"/>
     </row>
     <row r="1388" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1388" s="7" t="s">
-        <v>2724</v>
-      </c>
-      <c r="B1388" s="16">
+      <c r="A1388" s="6" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B1388" s="17">
         <v>79281644488</v>
       </c>
-      <c r="C1388" s="2" t="s">
-        <v>2732</v>
-      </c>
-      <c r="D1388" s="2" t="s">
-        <v>2737</v>
-      </c>
-      <c r="E1388" s="2"/>
-      <c r="F1388" s="2"/>
+      <c r="C1388" s="3" t="s">
+        <v>2901</v>
+      </c>
+      <c r="D1388" s="3" t="s">
+        <v>2908</v>
+      </c>
+      <c r="E1388" s="3"/>
+      <c r="F1388" s="3"/>
       <c r="G1388" s="2"/>
       <c r="H1388" s="2"/>
     </row>
     <row r="1389" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1389" s="37" t="s">
-        <v>2725</v>
-      </c>
-      <c r="B1389" s="16"/>
-      <c r="C1389" s="2"/>
-      <c r="D1389" s="2"/>
-      <c r="E1389" s="2"/>
-      <c r="F1389" s="2"/>
+      <c r="A1389" s="6" t="s">
+        <v>2721</v>
+      </c>
+      <c r="B1389" s="17"/>
+      <c r="C1389" s="3"/>
+      <c r="D1389" s="3"/>
+      <c r="E1389" s="3"/>
+      <c r="F1389" s="3"/>
       <c r="G1389" s="2"/>
       <c r="H1389" s="2"/>
     </row>
     <row r="1390" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1390" s="7" t="s">
-        <v>2726</v>
-      </c>
-      <c r="B1390" s="16">
+      <c r="A1390" s="6" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B1390" s="17">
         <v>79969140482</v>
       </c>
-      <c r="C1390" s="2"/>
-      <c r="D1390" s="2" t="s">
-        <v>2738</v>
-      </c>
-      <c r="E1390" s="2"/>
-      <c r="F1390" s="2"/>
+      <c r="C1390" s="3"/>
+      <c r="D1390" s="3" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E1390" s="3"/>
+      <c r="F1390" s="3"/>
       <c r="G1390" s="2"/>
       <c r="H1390" s="2"/>
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1391" s="7" t="s">
-        <v>2727</v>
-      </c>
-      <c r="B1391" s="16">
+      <c r="A1391" s="6" t="s">
+        <v>2723</v>
+      </c>
+      <c r="B1391" s="17">
         <v>79034655195</v>
       </c>
-      <c r="C1391" s="2" t="s">
-        <v>2735</v>
-      </c>
-      <c r="D1391" s="2" t="s">
-        <v>2738</v>
-      </c>
-      <c r="E1391" s="2"/>
-      <c r="F1391" s="2"/>
+      <c r="C1391" s="3" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D1391" s="3" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E1391" s="3"/>
+      <c r="F1391" s="3"/>
       <c r="G1391" s="2"/>
       <c r="H1391" s="2"/>
     </row>
     <row r="1392" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1392" s="7" t="s">
-        <v>2728</v>
-      </c>
-      <c r="B1392" s="16">
+      <c r="A1392" s="6" t="s">
+        <v>2724</v>
+      </c>
+      <c r="B1392" s="17">
         <v>79181891524</v>
       </c>
-      <c r="C1392" s="2" t="s">
-        <v>2735</v>
-      </c>
-      <c r="D1392" s="2"/>
-      <c r="E1392" s="2"/>
-      <c r="F1392" s="2"/>
+      <c r="C1392" s="3" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D1392" s="3"/>
+      <c r="E1392" s="3"/>
+      <c r="F1392" s="3"/>
       <c r="G1392" s="2"/>
       <c r="H1392" s="2"/>
     </row>
     <row r="1393" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1393" s="7" t="s">
-        <v>2729</v>
-      </c>
-      <c r="B1393" s="16">
+      <c r="A1393" s="6" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B1393" s="17">
         <v>79197527391</v>
       </c>
-      <c r="C1393" s="2" t="s">
-        <v>2735</v>
-      </c>
-      <c r="D1393" s="2" t="s">
-        <v>2739</v>
-      </c>
-      <c r="E1393" s="2"/>
-      <c r="F1393" s="2"/>
+      <c r="C1393" s="3" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D1393" s="3" t="s">
+        <v>2907</v>
+      </c>
+      <c r="E1393" s="3"/>
+      <c r="F1393" s="3"/>
       <c r="G1393" s="2"/>
       <c r="H1393" s="2"/>
     </row>
     <row r="1394" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1394" s="7" t="s">
-        <v>2730</v>
-      </c>
-      <c r="B1394" s="16">
+      <c r="A1394" s="6" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B1394" s="17">
         <v>79032888829</v>
       </c>
-      <c r="C1394" s="2"/>
-      <c r="D1394" s="2" t="s">
-        <v>2738</v>
-      </c>
-      <c r="E1394" s="2"/>
-      <c r="F1394" s="2"/>
+      <c r="C1394" s="3"/>
+      <c r="D1394" s="3" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E1394" s="3"/>
+      <c r="F1394" s="3"/>
       <c r="G1394" s="2"/>
       <c r="H1394" s="2"/>
     </row>
     <row r="1395" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1395" s="7"/>
-      <c r="B1395" s="16"/>
-      <c r="C1395" s="2" t="s">
+      <c r="A1395" s="6"/>
+      <c r="B1395" s="17"/>
+      <c r="C1395" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1395" s="2" t="s">
+      <c r="D1395" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1395" s="2" t="s">
+      <c r="E1395" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1395" s="4" t="s">
+      <c r="F1395" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G1395" s="2"/>
       <c r="H1395" s="2"/>
     </row>
     <row r="1396" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1396" s="37" t="s">
-        <v>2743</v>
-      </c>
-      <c r="B1396" s="16"/>
-      <c r="C1396" s="2"/>
-      <c r="D1396" s="2"/>
-      <c r="E1396" s="2"/>
-      <c r="F1396" s="2"/>
+      <c r="A1396" s="6" t="s">
+        <v>2729</v>
+      </c>
+      <c r="B1396" s="17"/>
+      <c r="C1396" s="3"/>
+      <c r="D1396" s="3"/>
+      <c r="E1396" s="3"/>
+      <c r="F1396" s="3"/>
       <c r="G1396" s="2"/>
       <c r="H1396" s="2"/>
     </row>
     <row r="1397" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1397" s="7" t="s">
-        <v>2744</v>
-      </c>
-      <c r="B1397" s="16">
+      <c r="A1397" s="6" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B1397" s="17">
         <v>79282292956</v>
       </c>
-      <c r="C1397" s="2"/>
-      <c r="D1397" s="2"/>
-      <c r="E1397" s="2" t="s">
-        <v>2753</v>
-      </c>
-      <c r="F1397" s="2" t="s">
-        <v>2752</v>
+      <c r="C1397" s="3"/>
+      <c r="D1397" s="3"/>
+      <c r="E1397" s="3" t="s">
+        <v>2915</v>
+      </c>
+      <c r="F1397" s="3" t="s">
+        <v>2736</v>
       </c>
       <c r="G1397" s="2"/>
       <c r="H1397" s="2"/>
     </row>
     <row r="1398" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1398" s="37" t="s">
-        <v>2745</v>
-      </c>
-      <c r="B1398" s="16"/>
-      <c r="C1398" s="2"/>
-      <c r="D1398" s="2"/>
-      <c r="E1398" s="2"/>
-      <c r="F1398" s="2"/>
+      <c r="A1398" s="6" t="s">
+        <v>2731</v>
+      </c>
+      <c r="B1398" s="17"/>
+      <c r="C1398" s="3"/>
+      <c r="D1398" s="3"/>
+      <c r="E1398" s="3"/>
+      <c r="F1398" s="3"/>
       <c r="G1398" s="2"/>
       <c r="H1398" s="2"/>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1399" s="7" t="s">
-        <v>2746</v>
-      </c>
-      <c r="B1399" s="16">
+      <c r="A1399" s="6" t="s">
+        <v>2732</v>
+      </c>
+      <c r="B1399" s="17">
         <v>79892315277</v>
       </c>
-      <c r="C1399" s="2" t="s">
-        <v>2750</v>
-      </c>
-      <c r="D1399" s="2" t="s">
-        <v>2751</v>
-      </c>
-      <c r="E1399" s="2"/>
-      <c r="F1399" s="2"/>
+      <c r="C1399" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="D1399" s="3" t="s">
+        <v>2905</v>
+      </c>
+      <c r="E1399" s="3"/>
+      <c r="F1399" s="3"/>
       <c r="G1399" s="2"/>
       <c r="H1399" s="2"/>
     </row>
     <row r="1400" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1400" s="7" t="s">
-        <v>2747</v>
-      </c>
-      <c r="B1400" s="16">
+      <c r="A1400" s="6" t="s">
+        <v>2733</v>
+      </c>
+      <c r="B1400" s="17">
         <v>79182323366</v>
       </c>
-      <c r="C1400" s="2" t="s">
-        <v>2750</v>
-      </c>
-      <c r="D1400" s="2"/>
-      <c r="E1400" s="2" t="s">
-        <v>2755</v>
-      </c>
-      <c r="F1400" s="2" t="s">
-        <v>2754</v>
+      <c r="C1400" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="D1400" s="3"/>
+      <c r="E1400" s="3" t="s">
+        <v>2916</v>
+      </c>
+      <c r="F1400" s="3" t="s">
+        <v>2737</v>
       </c>
       <c r="G1400" s="2"/>
       <c r="H1400" s="2"/>
     </row>
     <row r="1401" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1401" s="37" t="s">
-        <v>2748</v>
-      </c>
-      <c r="B1401" s="16"/>
-      <c r="C1401" s="2"/>
-      <c r="D1401" s="2"/>
-      <c r="E1401" s="2"/>
-      <c r="F1401" s="2"/>
+      <c r="A1401" s="6" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B1401" s="17"/>
+      <c r="C1401" s="3"/>
+      <c r="D1401" s="3"/>
+      <c r="E1401" s="3"/>
+      <c r="F1401" s="3"/>
       <c r="G1401" s="2"/>
       <c r="H1401" s="2"/>
     </row>
     <row r="1402" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1402" s="7" t="s">
-        <v>2749</v>
-      </c>
-      <c r="B1402" s="16">
+      <c r="A1402" s="6" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B1402" s="17">
         <v>79937726026</v>
       </c>
-      <c r="C1402" s="2" t="s">
-        <v>2756</v>
-      </c>
-      <c r="D1402" s="2"/>
-      <c r="E1402" s="2"/>
-      <c r="F1402" s="2"/>
+      <c r="C1402" s="3" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D1402" s="3"/>
+      <c r="E1402" s="3"/>
+      <c r="F1402" s="3"/>
       <c r="G1402" s="2"/>
       <c r="H1402" s="2"/>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1403" s="7" t="s">
-        <v>2757</v>
+        <v>2738</v>
       </c>
       <c r="B1403" s="16"/>
       <c r="C1403" s="2"/>
@@ -34204,16 +34225,16 @@
     </row>
     <row r="1404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1404" s="7" t="s">
-        <v>2758</v>
+        <v>2739</v>
       </c>
       <c r="B1404" s="16">
         <v>79508496243</v>
       </c>
       <c r="C1404" s="2" t="s">
-        <v>2760</v>
+        <v>2741</v>
       </c>
       <c r="D1404" s="2" t="s">
-        <v>2759</v>
+        <v>2740</v>
       </c>
       <c r="E1404" s="2"/>
       <c r="F1404" s="2"/>
@@ -34222,7 +34243,7 @@
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1405" s="37" t="s">
-        <v>2814</v>
+        <v>2794</v>
       </c>
       <c r="B1405" s="16"/>
       <c r="C1405" s="2"/>
@@ -34234,38 +34255,38 @@
     </row>
     <row r="1406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1406" s="7" t="s">
-        <v>2815</v>
+        <v>2795</v>
       </c>
       <c r="B1406" s="16">
         <v>79045010358</v>
       </c>
       <c r="C1406" s="2" t="s">
-        <v>2821</v>
+        <v>2801</v>
       </c>
       <c r="D1406" s="2" t="s">
-        <v>2818</v>
+        <v>2798</v>
       </c>
       <c r="E1406" s="2" t="s">
-        <v>2823</v>
+        <v>2803</v>
       </c>
       <c r="F1406" s="2" t="s">
-        <v>2822</v>
+        <v>2802</v>
       </c>
       <c r="G1406" s="2" t="s">
-        <v>2820</v>
+        <v>2800</v>
       </c>
       <c r="H1406" s="2"/>
     </row>
     <row r="1407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1407" s="7" t="s">
-        <v>2816</v>
+        <v>2796</v>
       </c>
       <c r="B1407" s="16">
         <v>79155232799</v>
       </c>
       <c r="C1407" s="2"/>
       <c r="D1407" s="2" t="s">
-        <v>2819</v>
+        <v>2799</v>
       </c>
       <c r="E1407" s="2"/>
       <c r="F1407" s="2"/>
@@ -34274,13 +34295,13 @@
     </row>
     <row r="1408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1408" s="7" t="s">
-        <v>2817</v>
+        <v>2797</v>
       </c>
       <c r="B1408" s="16">
         <v>79281777077</v>
       </c>
       <c r="C1408" s="2" t="s">
-        <v>2821</v>
+        <v>2801</v>
       </c>
       <c r="D1408" s="2"/>
       <c r="E1408" s="2"/>
@@ -34308,7 +34329,7 @@
     </row>
     <row r="1410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1410" s="37" t="s">
-        <v>2824</v>
+        <v>2804</v>
       </c>
       <c r="B1410" s="16"/>
       <c r="C1410" s="2"/>
@@ -34320,38 +34341,38 @@
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1411" s="7" t="s">
-        <v>2825</v>
+        <v>2805</v>
       </c>
       <c r="B1411" s="16">
         <v>79034731643</v>
       </c>
       <c r="C1411" s="2" t="s">
-        <v>2834</v>
+        <v>2814</v>
       </c>
       <c r="D1411" s="2" t="s">
-        <v>2835</v>
+        <v>2815</v>
       </c>
       <c r="E1411" s="2" t="s">
-        <v>2843</v>
+        <v>2823</v>
       </c>
       <c r="F1411" s="2" t="s">
-        <v>2841</v>
+        <v>2821</v>
       </c>
       <c r="G1411" s="2"/>
       <c r="H1411" s="2"/>
     </row>
     <row r="1412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1412" s="7" t="s">
-        <v>2826</v>
+        <v>2806</v>
       </c>
       <c r="B1412" s="16">
         <v>79288803988</v>
       </c>
       <c r="C1412" s="2" t="s">
-        <v>2834</v>
+        <v>2814</v>
       </c>
       <c r="D1412" s="2" t="s">
-        <v>2836</v>
+        <v>2816</v>
       </c>
       <c r="E1412" s="2"/>
       <c r="F1412" s="2"/>
@@ -34360,7 +34381,7 @@
     </row>
     <row r="1413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1413" s="37" t="s">
-        <v>2827</v>
+        <v>2807</v>
       </c>
       <c r="B1413" s="16"/>
       <c r="C1413" s="2"/>
@@ -34372,16 +34393,16 @@
     </row>
     <row r="1414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1414" s="7" t="s">
-        <v>2828</v>
+        <v>2808</v>
       </c>
       <c r="B1414" s="16">
         <v>79184775008</v>
       </c>
       <c r="C1414" s="2" t="s">
-        <v>2837</v>
+        <v>2817</v>
       </c>
       <c r="D1414" s="2" t="s">
-        <v>2838</v>
+        <v>2818</v>
       </c>
       <c r="E1414" s="2"/>
       <c r="F1414" s="2"/>
@@ -34390,16 +34411,16 @@
     </row>
     <row r="1415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1415" s="7" t="s">
-        <v>2829</v>
+        <v>2809</v>
       </c>
       <c r="B1415" s="16">
         <v>79185810505</v>
       </c>
       <c r="C1415" s="2" t="s">
-        <v>2837</v>
+        <v>2817</v>
       </c>
       <c r="D1415" s="2" t="s">
-        <v>2840</v>
+        <v>2820</v>
       </c>
       <c r="E1415" s="2"/>
       <c r="F1415" s="2"/>
@@ -34408,7 +34429,7 @@
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1416" s="37" t="s">
-        <v>2830</v>
+        <v>2810</v>
       </c>
       <c r="B1416" s="16"/>
       <c r="C1416" s="2"/>
@@ -34420,7 +34441,7 @@
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1417" s="7" t="s">
-        <v>2831</v>
+        <v>2811</v>
       </c>
       <c r="B1417" s="16">
         <v>79876274373</v>
@@ -34428,24 +34449,24 @@
       <c r="C1417" s="2"/>
       <c r="D1417" s="2"/>
       <c r="E1417" s="2" t="s">
-        <v>2844</v>
+        <v>2824</v>
       </c>
       <c r="F1417" s="2" t="s">
-        <v>2842</v>
+        <v>2822</v>
       </c>
       <c r="G1417" s="2"/>
       <c r="H1417" s="2"/>
     </row>
     <row r="1418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1418" s="7" t="s">
-        <v>2832</v>
+        <v>2812</v>
       </c>
       <c r="B1418" s="16">
         <v>79186355444</v>
       </c>
       <c r="C1418" s="2"/>
       <c r="D1418" s="2" t="s">
-        <v>2839</v>
+        <v>2819</v>
       </c>
       <c r="E1418" s="2"/>
       <c r="F1418" s="2"/>
@@ -34454,14 +34475,14 @@
     </row>
     <row r="1419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1419" s="7" t="s">
-        <v>2833</v>
+        <v>2813</v>
       </c>
       <c r="B1419" s="16">
         <v>79184115068</v>
       </c>
       <c r="C1419" s="2"/>
       <c r="D1419" s="2" t="s">
-        <v>2839</v>
+        <v>2819</v>
       </c>
       <c r="E1419" s="2"/>
       <c r="F1419" s="2"/>
@@ -34470,7 +34491,7 @@
     </row>
     <row r="1420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1420" s="37" t="s">
-        <v>2848</v>
+        <v>2828</v>
       </c>
       <c r="B1420" s="16"/>
       <c r="C1420" s="2"/>
@@ -34482,13 +34503,13 @@
     </row>
     <row r="1421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1421" s="7" t="s">
-        <v>2845</v>
+        <v>2825</v>
       </c>
       <c r="B1421" s="16">
         <v>79287641001</v>
       </c>
       <c r="C1421" s="2" t="s">
-        <v>2852</v>
+        <v>2832</v>
       </c>
       <c r="D1421" s="2"/>
       <c r="E1421" s="2"/>
@@ -34498,16 +34519,16 @@
     </row>
     <row r="1422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1422" s="7" t="s">
-        <v>2846</v>
+        <v>2826</v>
       </c>
       <c r="B1422" s="16">
         <v>79384046645</v>
       </c>
       <c r="C1422" s="2" t="s">
-        <v>2852</v>
+        <v>2832</v>
       </c>
       <c r="D1422" s="2" t="s">
-        <v>2853</v>
+        <v>2833</v>
       </c>
       <c r="E1422" s="2"/>
       <c r="F1422" s="2"/>
@@ -34516,13 +34537,13 @@
     </row>
     <row r="1423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1423" s="7" t="s">
-        <v>2847</v>
+        <v>2827</v>
       </c>
       <c r="B1423" s="16">
         <v>79525762953</v>
       </c>
       <c r="C1423" s="2" t="s">
-        <v>2852</v>
+        <v>2832</v>
       </c>
       <c r="D1423" s="2"/>
       <c r="E1423" s="2"/>
@@ -34532,7 +34553,7 @@
     </row>
     <row r="1424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1424" s="37" t="s">
-        <v>2849</v>
+        <v>2829</v>
       </c>
       <c r="B1424" s="16"/>
       <c r="C1424" s="2"/>
@@ -34544,14 +34565,14 @@
     </row>
     <row r="1425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1425" s="7" t="s">
-        <v>2850</v>
+        <v>2830</v>
       </c>
       <c r="B1425" s="16">
         <v>79873945838</v>
       </c>
       <c r="C1425" s="2"/>
       <c r="D1425" s="2" t="s">
-        <v>2854</v>
+        <v>2834</v>
       </c>
       <c r="E1425" s="2"/>
       <c r="F1425" s="2"/>
@@ -34560,14 +34581,14 @@
     </row>
     <row r="1426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1426" s="7" t="s">
-        <v>2851</v>
+        <v>2831</v>
       </c>
       <c r="B1426" s="16">
         <v>79515080763</v>
       </c>
       <c r="C1426" s="2"/>
       <c r="D1426" s="2" t="s">
-        <v>2855</v>
+        <v>2835</v>
       </c>
       <c r="E1426" s="2"/>
       <c r="F1426" s="2"/>
@@ -34576,7 +34597,7 @@
     </row>
     <row r="1427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1427" s="37" t="s">
-        <v>2890</v>
+        <v>2870</v>
       </c>
       <c r="B1427" s="16"/>
       <c r="C1427" s="2"/>
@@ -34588,14 +34609,14 @@
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1428" s="7" t="s">
-        <v>2891</v>
+        <v>2871</v>
       </c>
       <c r="B1428" s="16">
         <v>79588660254</v>
       </c>
       <c r="C1428" s="2"/>
       <c r="D1428" s="2" t="s">
-        <v>2892</v>
+        <v>2872</v>
       </c>
       <c r="E1428" s="2"/>
       <c r="F1428" s="2"/>
@@ -34622,7 +34643,7 @@
     </row>
     <row r="1430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1430" s="37" t="s">
-        <v>2893</v>
+        <v>2873</v>
       </c>
       <c r="B1430" s="16"/>
       <c r="C1430" s="2"/>
@@ -34634,27 +34655,27 @@
     </row>
     <row r="1431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1431" s="7" t="s">
-        <v>2894</v>
+        <v>2874</v>
       </c>
       <c r="B1431" s="16">
         <v>79023891506</v>
       </c>
       <c r="C1431" s="2"/>
       <c r="D1431" s="2" t="s">
-        <v>2897</v>
+        <v>2877</v>
       </c>
       <c r="E1431" s="2"/>
       <c r="F1431" s="2"/>
     </row>
     <row r="1432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1432" s="7" t="s">
-        <v>2895</v>
+        <v>2875</v>
       </c>
       <c r="B1432" s="16">
         <v>79184377062</v>
       </c>
       <c r="C1432" s="2" t="s">
-        <v>2896</v>
+        <v>2876</v>
       </c>
       <c r="D1432" s="2"/>
       <c r="E1432" s="2"/>
@@ -34662,7 +34683,7 @@
     </row>
     <row r="1433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1433" s="37" t="s">
-        <v>2893</v>
+        <v>2873</v>
       </c>
       <c r="B1433" s="16"/>
       <c r="C1433" s="2"/>
@@ -34672,35 +34693,35 @@
     </row>
     <row r="1434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1434" s="7" t="s">
-        <v>2912</v>
+        <v>2892</v>
       </c>
       <c r="B1434" s="16">
         <v>79066122888</v>
       </c>
       <c r="C1434" s="2"/>
       <c r="D1434" s="2" t="s">
-        <v>2915</v>
+        <v>2895</v>
       </c>
       <c r="E1434" s="2"/>
       <c r="F1434" s="2"/>
     </row>
     <row r="1435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1435" s="7" t="s">
-        <v>2913</v>
+        <v>2893</v>
       </c>
       <c r="B1435" s="16">
         <v>79959416136</v>
       </c>
       <c r="C1435" s="2"/>
       <c r="D1435" s="2" t="s">
-        <v>2915</v>
+        <v>2895</v>
       </c>
       <c r="E1435" s="2"/>
       <c r="F1435" s="2"/>
     </row>
     <row r="1436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1436" s="7" t="s">
-        <v>2914</v>
+        <v>2894</v>
       </c>
       <c r="B1436" s="16">
         <v>79628779270</v>
@@ -34708,14 +34729,16 @@
       <c r="C1436" s="2"/>
       <c r="D1436" s="2"/>
       <c r="E1436" s="2" t="s">
+        <v>2897</v>
+      </c>
+      <c r="F1436" s="2" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1437" s="37" t="s">
         <v>2917</v>
       </c>
-      <c r="F1436" s="2" t="s">
-        <v>2916</v>
-      </c>
-    </row>
-    <row r="1437" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1437" s="7"/>
       <c r="B1437" s="16"/>
       <c r="C1437" s="2"/>
       <c r="D1437" s="2"/>
@@ -34723,31 +34746,48 @@
       <c r="F1437" s="2"/>
     </row>
     <row r="1438" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1438" s="7"/>
-      <c r="B1438" s="16"/>
+      <c r="A1438" s="7" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B1438" s="16">
+        <v>79034397172</v>
+      </c>
       <c r="C1438" s="2"/>
       <c r="D1438" s="2"/>
-      <c r="E1438" s="2"/>
-      <c r="F1438" s="2"/>
+      <c r="E1438" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1438" s="2" t="s">
+        <v>731</v>
+      </c>
     </row>
     <row r="1439" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1439" s="7"/>
-      <c r="B1439" s="16"/>
+      <c r="A1439" s="37" t="s">
+        <v>2920</v>
+      </c>
       <c r="C1439" s="2"/>
       <c r="D1439" s="2"/>
       <c r="E1439" s="2"/>
       <c r="F1439" s="2"/>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1440" s="7"/>
-      <c r="B1440" s="16"/>
+      <c r="A1440" s="7" t="s">
+        <v>2919</v>
+      </c>
+      <c r="B1440" s="16">
+        <v>79493830457</v>
+      </c>
       <c r="C1440" s="2"/>
-      <c r="D1440" s="2"/>
+      <c r="D1440" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="E1440" s="2"/>
       <c r="F1440" s="2"/>
     </row>
     <row r="1441" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1441" s="7"/>
+      <c r="A1441" s="37" t="s">
+        <v>2921</v>
+      </c>
       <c r="B1441" s="16"/>
       <c r="C1441" s="2"/>
       <c r="D1441" s="2"/>
@@ -34755,10 +34795,16 @@
       <c r="F1441" s="2"/>
     </row>
     <row r="1442" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1442" s="7"/>
-      <c r="B1442" s="16"/>
+      <c r="A1442" s="7" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B1442" s="16">
+        <v>79030000959</v>
+      </c>
       <c r="C1442" s="2"/>
-      <c r="D1442" s="2"/>
+      <c r="D1442" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="E1442" s="2"/>
       <c r="F1442" s="2"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECBA0A4-E249-4DD9-97D1-FE3980D101CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6CA12A-7C4E-4657-8DF6-D4C5FB78007A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4470" uniqueCount="2925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4470" uniqueCount="2926">
   <si>
     <t>Пароль</t>
   </si>
@@ -8809,6 +8809,9 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/P1cyniJFzuwCaw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/HbzqNJoL4__IiQ</t>
   </si>
 </sst>
 </file>
@@ -34758,7 +34761,7 @@
         <v>731</v>
       </c>
       <c r="F1438" s="2" t="s">
-        <v>731</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="1439" spans="1:8" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6CA12A-7C4E-4657-8DF6-D4C5FB78007A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC06036C-87EC-450E-BAE4-3AD5D9C09B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4470" uniqueCount="2926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4470" uniqueCount="2927">
   <si>
     <t>Пароль</t>
   </si>
@@ -8812,6 +8812,9 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/i/HbzqNJoL4__IiQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/y2qD-Kda1uJ6lw</t>
   </si>
 </sst>
 </file>
@@ -34758,7 +34761,7 @@
       <c r="C1438" s="2"/>
       <c r="D1438" s="2"/>
       <c r="E1438" s="2" t="s">
-        <v>731</v>
+        <v>2926</v>
       </c>
       <c r="F1438" s="2" t="s">
         <v>2925</v>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC06036C-87EC-450E-BAE4-3AD5D9C09B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5202D4DC-F891-497C-89E5-22689E7EAD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4470" uniqueCount="2927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4504" uniqueCount="2948">
   <si>
     <t>Пароль</t>
   </si>
@@ -8815,6 +8815,69 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/y2qD-Kda1uJ6lw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/mHql6eHviB61ZQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/BuGd8wKiW9jycw</t>
+  </si>
+  <si>
+    <t>10/10/26/10:00</t>
+  </si>
+  <si>
+    <t>11990</t>
+  </si>
+  <si>
+    <t>92567</t>
+  </si>
+  <si>
+    <t>19714</t>
+  </si>
+  <si>
+    <t>10/10/26/12:30</t>
+  </si>
+  <si>
+    <t>82391</t>
+  </si>
+  <si>
+    <t>40206</t>
+  </si>
+  <si>
+    <t>58985</t>
+  </si>
+  <si>
+    <t>10/10/26/15:30</t>
+  </si>
+  <si>
+    <t>30806</t>
+  </si>
+  <si>
+    <t>69812</t>
+  </si>
+  <si>
+    <t>76326</t>
+  </si>
+  <si>
+    <t>32854</t>
+  </si>
+  <si>
+    <t>92843</t>
+  </si>
+  <si>
+    <t>* ДанНя/Рамиль</t>
+  </si>
+  <si>
+    <t>* Лев</t>
+  </si>
+  <si>
+    <t>* ДанНя/Дима</t>
+  </si>
+  <si>
+    <t>* ДанНЯ</t>
+  </si>
+  <si>
+    <t>* Дима</t>
   </si>
 </sst>
 </file>
@@ -34785,7 +34848,7 @@
       </c>
       <c r="C1440" s="2"/>
       <c r="D1440" s="2" t="s">
-        <v>731</v>
+        <v>2927</v>
       </c>
       <c r="E1440" s="2"/>
       <c r="F1440" s="2"/>
@@ -34809,7 +34872,7 @@
       </c>
       <c r="C1442" s="2"/>
       <c r="D1442" s="2" t="s">
-        <v>731</v>
+        <v>2928</v>
       </c>
       <c r="E1442" s="2"/>
       <c r="F1442" s="2"/>
@@ -34817,13 +34880,23 @@
     <row r="1443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1443" s="7"/>
       <c r="B1443" s="16"/>
-      <c r="C1443" s="2"/>
-      <c r="D1443" s="2"/>
-      <c r="E1443" s="2"/>
-      <c r="F1443" s="2"/>
+      <c r="C1443" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1443" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1443" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1443" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="1444" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1444" s="7"/>
+      <c r="A1444" s="37" t="s">
+        <v>2929</v>
+      </c>
       <c r="B1444" s="16"/>
       <c r="C1444" s="2"/>
       <c r="D1444" s="2"/>
@@ -34831,31 +34904,53 @@
       <c r="F1444" s="2"/>
     </row>
     <row r="1445" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1445" s="7"/>
-      <c r="B1445" s="16"/>
-      <c r="C1445" s="2"/>
-      <c r="D1445" s="2"/>
+      <c r="A1445" s="7" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1445" s="16">
+        <v>79181311990</v>
+      </c>
+      <c r="C1445" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1445" s="2" t="s">
+        <v>2943</v>
+      </c>
       <c r="E1445" s="2"/>
       <c r="F1445" s="2"/>
     </row>
     <row r="1446" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1446" s="7"/>
-      <c r="B1446" s="16"/>
-      <c r="C1446" s="2"/>
+      <c r="A1446" s="7" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B1446" s="16">
+        <v>79221892567</v>
+      </c>
+      <c r="C1446" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="D1446" s="2"/>
       <c r="E1446" s="2"/>
       <c r="F1446" s="2"/>
     </row>
     <row r="1447" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1447" s="7"/>
-      <c r="B1447" s="16"/>
-      <c r="C1447" s="2"/>
+      <c r="A1447" s="7" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B1447" s="16">
+        <v>79189219714</v>
+      </c>
+      <c r="C1447" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="D1447" s="2"/>
       <c r="E1447" s="2"/>
       <c r="F1447" s="2"/>
     </row>
     <row r="1448" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1448" s="7"/>
+      <c r="A1448" s="37" t="s">
+        <v>2933</v>
+      </c>
       <c r="B1448" s="16"/>
       <c r="C1448" s="2"/>
       <c r="D1448" s="2"/>
@@ -34863,39 +34958,69 @@
       <c r="F1448" s="2"/>
     </row>
     <row r="1449" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1449" s="7"/>
-      <c r="B1449" s="16"/>
-      <c r="C1449" s="2"/>
+      <c r="A1449" s="7" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B1449" s="16">
+        <v>79898382391</v>
+      </c>
+      <c r="C1449" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="D1449" s="2"/>
       <c r="E1449" s="2"/>
       <c r="F1449" s="2"/>
     </row>
     <row r="1450" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1450" s="7"/>
-      <c r="B1450" s="16"/>
+      <c r="A1450" s="7" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B1450" s="16">
+        <v>79867392843</v>
+      </c>
       <c r="C1450" s="2"/>
-      <c r="D1450" s="2"/>
+      <c r="D1450" s="2" t="s">
+        <v>2944</v>
+      </c>
       <c r="E1450" s="2"/>
       <c r="F1450" s="2"/>
     </row>
     <row r="1451" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1451" s="7"/>
-      <c r="B1451" s="16"/>
+      <c r="A1451" s="7" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B1451" s="16">
+        <v>79515340206</v>
+      </c>
       <c r="C1451" s="2"/>
-      <c r="D1451" s="2"/>
+      <c r="D1451" s="2" t="s">
+        <v>2946</v>
+      </c>
       <c r="E1451" s="2"/>
       <c r="F1451" s="2"/>
     </row>
     <row r="1452" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1452" s="7"/>
-      <c r="B1452" s="16"/>
-      <c r="C1452" s="2"/>
-      <c r="D1452" s="2"/>
-      <c r="E1452" s="2"/>
+      <c r="A1452" s="7" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B1452" s="16">
+        <v>79181058985</v>
+      </c>
+      <c r="C1452" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1452" s="2" t="s">
+        <v>2945</v>
+      </c>
+      <c r="E1452" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="F1452" s="2"/>
     </row>
     <row r="1453" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1453" s="7"/>
+      <c r="A1453" s="37" t="s">
+        <v>2937</v>
+      </c>
       <c r="B1453" s="16"/>
       <c r="C1453" s="2"/>
       <c r="D1453" s="2"/>
@@ -34903,34 +35028,62 @@
       <c r="F1453" s="2"/>
     </row>
     <row r="1454" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1454" s="7"/>
-      <c r="B1454" s="16"/>
+      <c r="A1454" s="7" t="s">
+        <v>2938</v>
+      </c>
+      <c r="B1454" s="16">
+        <v>79094330806</v>
+      </c>
       <c r="C1454" s="2"/>
       <c r="D1454" s="2"/>
-      <c r="E1454" s="2"/>
-      <c r="F1454" s="2"/>
+      <c r="E1454" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1454" s="2" t="s">
+        <v>731</v>
+      </c>
     </row>
     <row r="1455" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1455" s="7"/>
-      <c r="B1455" s="16"/>
+      <c r="A1455" s="7" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B1455" s="16">
+        <v>79892969812</v>
+      </c>
       <c r="C1455" s="2"/>
-      <c r="D1455" s="2"/>
+      <c r="D1455" s="2" t="s">
+        <v>2947</v>
+      </c>
       <c r="E1455" s="2"/>
       <c r="F1455" s="2"/>
     </row>
     <row r="1456" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1456" s="7"/>
-      <c r="B1456" s="16"/>
-      <c r="C1456" s="2"/>
-      <c r="D1456" s="2"/>
+      <c r="A1456" s="7" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B1456" s="16">
+        <v>79038276326</v>
+      </c>
+      <c r="C1456" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1456" s="2" t="s">
+        <v>2944</v>
+      </c>
       <c r="E1456" s="2"/>
       <c r="F1456" s="2"/>
     </row>
     <row r="1457" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1457" s="7"/>
-      <c r="B1457" s="16"/>
+      <c r="A1457" s="7" t="s">
+        <v>2941</v>
+      </c>
+      <c r="B1457" s="16">
+        <v>79612832854</v>
+      </c>
       <c r="C1457" s="2"/>
-      <c r="D1457" s="2"/>
+      <c r="D1457" s="2" t="s">
+        <v>2946</v>
+      </c>
       <c r="E1457" s="2"/>
       <c r="F1457" s="2"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5202D4DC-F891-497C-89E5-22689E7EAD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7213CBC4-BEF0-4487-9460-C13B0CC0CB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4504" uniqueCount="2948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4504" uniqueCount="2951">
   <si>
     <t>Пароль</t>
   </si>
@@ -8878,6 +8878,15 @@
   </si>
   <si>
     <t>* Дима</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/3OGg5RUkUpblwQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/s2FBrD2s34O1UA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/DtJn06qP4UjDXw</t>
   </si>
 </sst>
 </file>
@@ -34911,7 +34920,7 @@
         <v>79181311990</v>
       </c>
       <c r="C1445" s="2" t="s">
-        <v>731</v>
+        <v>2950</v>
       </c>
       <c r="D1445" s="2" t="s">
         <v>2943</v>
@@ -34927,7 +34936,7 @@
         <v>79221892567</v>
       </c>
       <c r="C1446" s="2" t="s">
-        <v>731</v>
+        <v>2950</v>
       </c>
       <c r="D1446" s="2"/>
       <c r="E1446" s="2"/>
@@ -34941,7 +34950,7 @@
         <v>79189219714</v>
       </c>
       <c r="C1447" s="2" t="s">
-        <v>731</v>
+        <v>2950</v>
       </c>
       <c r="D1447" s="2"/>
       <c r="E1447" s="2"/>
@@ -34965,7 +34974,7 @@
         <v>79898382391</v>
       </c>
       <c r="C1449" s="2" t="s">
-        <v>731</v>
+        <v>2948</v>
       </c>
       <c r="D1449" s="2"/>
       <c r="E1449" s="2"/>
@@ -35007,7 +35016,7 @@
         <v>79181058985</v>
       </c>
       <c r="C1452" s="2" t="s">
-        <v>731</v>
+        <v>2948</v>
       </c>
       <c r="D1452" s="2" t="s">
         <v>2945</v>
@@ -35065,7 +35074,7 @@
         <v>79038276326</v>
       </c>
       <c r="C1456" s="2" t="s">
-        <v>731</v>
+        <v>2949</v>
       </c>
       <c r="D1456" s="2" t="s">
         <v>2944</v>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7213CBC4-BEF0-4487-9460-C13B0CC0CB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C6AC4B-5F5A-4F46-AFF3-AF3BBE954A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4504" uniqueCount="2951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4504" uniqueCount="2956">
   <si>
     <t>Пароль</t>
   </si>
@@ -8865,21 +8865,6 @@
     <t>92843</t>
   </si>
   <si>
-    <t>* ДанНя/Рамиль</t>
-  </si>
-  <si>
-    <t>* Лев</t>
-  </si>
-  <si>
-    <t>* ДанНя/Дима</t>
-  </si>
-  <si>
-    <t>* ДанНЯ</t>
-  </si>
-  <si>
-    <t>* Дима</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/d/3OGg5RUkUpblwQ</t>
   </si>
   <si>
@@ -8887,6 +8872,36 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/DtJn06qP4UjDXw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/p_n0pO5838g1xQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/bftZ74j-co0Nnw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/l81JKKuhby283A</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/O4yx853huAUqrg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/drTcuV4JDIaMdA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/0XfEjbwenDo2yQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/I7wV_F7YZqqPew</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/nYAKUwCIKtj4Cw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/bs4FWaarmIzFNg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/FMvMA3pOR1wZAA</t>
   </si>
 </sst>
 </file>
@@ -34920,10 +34935,10 @@
         <v>79181311990</v>
       </c>
       <c r="C1445" s="2" t="s">
-        <v>2950</v>
+        <v>2945</v>
       </c>
       <c r="D1445" s="2" t="s">
-        <v>2943</v>
+        <v>2946</v>
       </c>
       <c r="E1445" s="2"/>
       <c r="F1445" s="2"/>
@@ -34936,7 +34951,7 @@
         <v>79221892567</v>
       </c>
       <c r="C1446" s="2" t="s">
-        <v>2950</v>
+        <v>2945</v>
       </c>
       <c r="D1446" s="2"/>
       <c r="E1446" s="2"/>
@@ -34950,7 +34965,7 @@
         <v>79189219714</v>
       </c>
       <c r="C1447" s="2" t="s">
-        <v>2950</v>
+        <v>2945</v>
       </c>
       <c r="D1447" s="2"/>
       <c r="E1447" s="2"/>
@@ -34974,7 +34989,7 @@
         <v>79898382391</v>
       </c>
       <c r="C1449" s="2" t="s">
-        <v>2948</v>
+        <v>2943</v>
       </c>
       <c r="D1449" s="2"/>
       <c r="E1449" s="2"/>
@@ -34989,7 +35004,7 @@
       </c>
       <c r="C1450" s="2"/>
       <c r="D1450" s="2" t="s">
-        <v>2944</v>
+        <v>2948</v>
       </c>
       <c r="E1450" s="2"/>
       <c r="F1450" s="2"/>
@@ -35003,7 +35018,7 @@
       </c>
       <c r="C1451" s="2"/>
       <c r="D1451" s="2" t="s">
-        <v>2946</v>
+        <v>2949</v>
       </c>
       <c r="E1451" s="2"/>
       <c r="F1451" s="2"/>
@@ -35016,13 +35031,13 @@
         <v>79181058985</v>
       </c>
       <c r="C1452" s="2" t="s">
-        <v>2948</v>
+        <v>2943</v>
       </c>
       <c r="D1452" s="2" t="s">
-        <v>2945</v>
+        <v>2947</v>
       </c>
       <c r="E1452" s="2" t="s">
-        <v>731</v>
+        <v>2953</v>
       </c>
       <c r="F1452" s="2"/>
     </row>
@@ -35046,10 +35061,10 @@
       <c r="C1454" s="2"/>
       <c r="D1454" s="2"/>
       <c r="E1454" s="2" t="s">
-        <v>731</v>
+        <v>2955</v>
       </c>
       <c r="F1454" s="2" t="s">
-        <v>731</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="1455" spans="1:6" x14ac:dyDescent="0.25">
@@ -35061,7 +35076,7 @@
       </c>
       <c r="C1455" s="2"/>
       <c r="D1455" s="2" t="s">
-        <v>2947</v>
+        <v>2951</v>
       </c>
       <c r="E1455" s="2"/>
       <c r="F1455" s="2"/>
@@ -35074,10 +35089,10 @@
         <v>79038276326</v>
       </c>
       <c r="C1456" s="2" t="s">
-        <v>2949</v>
+        <v>2944</v>
       </c>
       <c r="D1456" s="2" t="s">
-        <v>2944</v>
+        <v>2952</v>
       </c>
       <c r="E1456" s="2"/>
       <c r="F1456" s="2"/>
@@ -35091,7 +35106,7 @@
       </c>
       <c r="C1457" s="2"/>
       <c r="D1457" s="2" t="s">
-        <v>2946</v>
+        <v>2950</v>
       </c>
       <c r="E1457" s="2"/>
       <c r="F1457" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C6AC4B-5F5A-4F46-AFF3-AF3BBE954A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817CFFCF-6ED3-44FC-B6B3-00710819BCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4504" uniqueCount="2956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4526" uniqueCount="2965">
   <si>
     <t>Пароль</t>
   </si>
@@ -6657,9 +6657,6 @@
     <t>08/09/26/15:00</t>
   </si>
   <si>
-    <t>19232</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/d/sHoLaZvUkEqXuQ</t>
   </si>
   <si>
@@ -6831,42 +6828,15 @@
     <t>10/09/26/10:00</t>
   </si>
   <si>
-    <t>06771</t>
-  </si>
-  <si>
-    <t>36662</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/gmaOq_I5T85r-Q</t>
   </si>
   <si>
-    <t>56891</t>
-  </si>
-  <si>
-    <t>15371</t>
-  </si>
-  <si>
-    <t>18545</t>
-  </si>
-  <si>
     <t>11/09/26/10:00</t>
   </si>
   <si>
     <t>11/09/26/12:30</t>
   </si>
   <si>
-    <t>02117</t>
-  </si>
-  <si>
-    <t>14599</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>02201</t>
-  </si>
-  <si>
     <t>11/09/26/15:00</t>
   </si>
   <si>
@@ -8865,6 +8835,9 @@
     <t>92843</t>
   </si>
   <si>
+    <t>* Дима</t>
+  </si>
+  <si>
     <t>https://disk.yandex.ru/d/3OGg5RUkUpblwQ</t>
   </si>
   <si>
@@ -8902,6 +8875,60 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/FMvMA3pOR1wZAA</t>
+  </si>
+  <si>
+    <t>/?19232</t>
+  </si>
+  <si>
+    <t>/?06771</t>
+  </si>
+  <si>
+    <t>/?36662</t>
+  </si>
+  <si>
+    <t>/?56891</t>
+  </si>
+  <si>
+    <t>/?18545</t>
+  </si>
+  <si>
+    <t>/?02117</t>
+  </si>
+  <si>
+    <t>/?14599</t>
+  </si>
+  <si>
+    <t>/?87172</t>
+  </si>
+  <si>
+    <t>/?02201</t>
+  </si>
+  <si>
+    <t>11/10/26/10:00</t>
+  </si>
+  <si>
+    <t>54783</t>
+  </si>
+  <si>
+    <t>08128</t>
+  </si>
+  <si>
+    <t>69407</t>
+  </si>
+  <si>
+    <t>79005</t>
+  </si>
+  <si>
+    <t>11/10/26/12:30</t>
+  </si>
+  <si>
+    <t>11/10/26/14:00</t>
+  </si>
+  <si>
+    <t>98771</t>
+  </si>
+  <si>
+    <t>* ДимМа</t>
   </si>
 </sst>
 </file>
@@ -24909,7 +24936,7 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" s="32" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="B847" s="38">
         <v>79185972895</v>
@@ -24931,7 +24958,7 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" s="32" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="B848" s="38">
         <v>79996262825</v>
@@ -24975,7 +25002,7 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" s="32" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="B850" s="38">
         <v>79604875670</v>
@@ -24997,7 +25024,7 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" s="32" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B851" s="38">
         <v>79184987541</v>
@@ -25015,7 +25042,7 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" s="32" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="B852" s="38">
         <v>79185058918</v>
@@ -25031,7 +25058,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" s="32" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="B853" s="38">
         <v>79084845045</v>
@@ -25051,7 +25078,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" s="32" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="B854" s="38">
         <v>79189841111</v>
@@ -25067,7 +25094,7 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" s="32" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="B855" s="38">
         <v>79183593299</v>
@@ -25089,7 +25116,7 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" s="32" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="B856" s="38">
         <v>79286104433</v>
@@ -25107,7 +25134,7 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" s="32" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="B857" s="38">
         <v>79181204920</v>
@@ -25125,7 +25152,7 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" s="32" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="B858" s="38">
         <v>79180314664</v>
@@ -25143,7 +25170,7 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" s="32" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="B859" s="38">
         <v>79255304182</v>
@@ -25161,7 +25188,7 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" s="32" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="B860" s="38">
         <v>79624321777</v>
@@ -25179,7 +25206,7 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" s="32" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="B861" s="38">
         <v>79034652185</v>
@@ -25195,7 +25222,7 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" s="32" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="B862" s="38">
         <v>79654707870</v>
@@ -25229,7 +25256,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" s="32" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="B864" s="38">
         <v>79284244414</v>
@@ -25249,7 +25276,7 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" s="32" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="B865" s="38">
         <v>79619719206</v>
@@ -25269,7 +25296,7 @@
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" s="32" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="B866" s="38">
         <v>79530872704</v>
@@ -25325,7 +25352,7 @@
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" s="32" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B869" s="38">
         <v>79181112526</v>
@@ -25343,7 +25370,7 @@
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" s="18" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B870" s="39">
         <v>79186726140</v>
@@ -25383,7 +25410,7 @@
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" s="32" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B872" s="38">
         <v>79283003384</v>
@@ -25401,7 +25428,7 @@
     </row>
     <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" s="32" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="B873" s="38">
         <v>79682666663</v>
@@ -25417,7 +25444,7 @@
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" s="32" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B874" s="38">
         <v>79186726140</v>
@@ -25435,7 +25462,7 @@
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" s="32" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="B875" s="38">
         <v>79898051733</v>
@@ -25453,7 +25480,7 @@
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" s="32" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="B876" s="38">
         <v>79086789121</v>
@@ -25469,7 +25496,7 @@
     </row>
     <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" s="32" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B877" s="38">
         <v>79528340083</v>
@@ -25485,7 +25512,7 @@
     </row>
     <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" s="32" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B878" s="38">
         <v>79530930717</v>
@@ -25503,7 +25530,7 @@
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" s="32" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="B879" s="38">
         <v>79275037361</v>
@@ -25519,7 +25546,7 @@
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" s="32" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B880" s="38">
         <v>79218083526</v>
@@ -25535,7 +25562,7 @@
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" s="32" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B881" s="38">
         <v>79185789000</v>
@@ -25555,7 +25582,7 @@
     </row>
     <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" s="32" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="B882" s="38">
         <v>79877941509</v>
@@ -25573,7 +25600,7 @@
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" s="32" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B883" s="38">
         <v>79618221503</v>
@@ -25613,7 +25640,7 @@
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" s="32" t="s">
-        <v>2302</v>
+        <v>2292</v>
       </c>
       <c r="B885" s="38">
         <v>79882548579</v>
@@ -25631,7 +25658,7 @@
     </row>
     <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" s="32" t="s">
-        <v>2303</v>
+        <v>2293</v>
       </c>
       <c r="B886" s="38">
         <v>79182900595</v>
@@ -25647,7 +25674,7 @@
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" s="32" t="s">
-        <v>2304</v>
+        <v>2294</v>
       </c>
       <c r="B887" s="38">
         <v>79264823431</v>
@@ -25665,7 +25692,7 @@
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" s="32" t="s">
-        <v>2305</v>
+        <v>2295</v>
       </c>
       <c r="B888" s="38">
         <v>79180246728</v>
@@ -25683,7 +25710,7 @@
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" s="32" t="s">
-        <v>2306</v>
+        <v>2296</v>
       </c>
       <c r="B889" s="38">
         <v>79263181485</v>
@@ -25699,7 +25726,7 @@
     </row>
     <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" s="32" t="s">
-        <v>2307</v>
+        <v>2297</v>
       </c>
       <c r="B890" s="38">
         <v>79189573595</v>
@@ -25717,7 +25744,7 @@
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" s="32" t="s">
-        <v>2308</v>
+        <v>2298</v>
       </c>
       <c r="B891" s="38">
         <v>79180129312</v>
@@ -25757,7 +25784,7 @@
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" s="32" t="s">
-        <v>2309</v>
+        <v>2299</v>
       </c>
       <c r="B893" s="38">
         <v>79207020082</v>
@@ -25779,7 +25806,7 @@
     </row>
     <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" s="32" t="s">
-        <v>2310</v>
+        <v>2300</v>
       </c>
       <c r="B894" s="38">
         <v>79185072237</v>
@@ -25797,7 +25824,7 @@
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" s="32" t="s">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="B895" s="38">
         <v>79182762440</v>
@@ -25813,7 +25840,7 @@
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" s="32" t="s">
-        <v>2312</v>
+        <v>2302</v>
       </c>
       <c r="B896" s="38">
         <v>79518702052</v>
@@ -25829,7 +25856,7 @@
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" s="32" t="s">
-        <v>2313</v>
+        <v>2303</v>
       </c>
       <c r="B897" s="38">
         <v>79885456732</v>
@@ -25845,7 +25872,7 @@
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" s="32" t="s">
-        <v>2314</v>
+        <v>2304</v>
       </c>
       <c r="B898" s="38">
         <v>79186323631</v>
@@ -25883,7 +25910,7 @@
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" s="32" t="s">
-        <v>2315</v>
+        <v>2305</v>
       </c>
       <c r="B900" s="38">
         <v>79604946540</v>
@@ -25903,7 +25930,7 @@
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" s="32" t="s">
-        <v>2316</v>
+        <v>2306</v>
       </c>
       <c r="B901" s="38">
         <v>79787713176</v>
@@ -25947,7 +25974,7 @@
     </row>
     <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" s="32" t="s">
-        <v>2317</v>
+        <v>2307</v>
       </c>
       <c r="B903" s="38">
         <v>79881380533</v>
@@ -25963,7 +25990,7 @@
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" s="32" t="s">
-        <v>2318</v>
+        <v>2308</v>
       </c>
       <c r="B904" s="38">
         <v>79876571770</v>
@@ -25985,7 +26012,7 @@
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" s="32" t="s">
-        <v>2319</v>
+        <v>2309</v>
       </c>
       <c r="B905" s="38">
         <v>79185269969</v>
@@ -26007,7 +26034,7 @@
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" s="32" t="s">
-        <v>2320</v>
+        <v>2310</v>
       </c>
       <c r="B906" s="38">
         <v>79788069407</v>
@@ -26029,7 +26056,7 @@
     </row>
     <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" s="32" t="s">
-        <v>2321</v>
+        <v>2311</v>
       </c>
       <c r="B907" s="38">
         <v>79809148895</v>
@@ -26051,7 +26078,7 @@
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" s="32" t="s">
-        <v>2322</v>
+        <v>2312</v>
       </c>
       <c r="B908" s="38">
         <v>79374600054</v>
@@ -26089,7 +26116,7 @@
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" s="32" t="s">
-        <v>2323</v>
+        <v>2313</v>
       </c>
       <c r="B910" s="38">
         <v>79063480196</v>
@@ -26107,7 +26134,7 @@
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" s="32" t="s">
-        <v>2312</v>
+        <v>2302</v>
       </c>
       <c r="B911" s="38">
         <v>79035002052</v>
@@ -26127,7 +26154,7 @@
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" s="32" t="s">
-        <v>2324</v>
+        <v>2314</v>
       </c>
       <c r="B912" s="38">
         <v>79883667602</v>
@@ -26147,7 +26174,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A913" s="32" t="s">
-        <v>2325</v>
+        <v>2315</v>
       </c>
       <c r="B913" s="38">
         <v>79991733748</v>
@@ -26163,7 +26190,7 @@
     </row>
     <row r="914" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A914" s="32" t="s">
-        <v>2326</v>
+        <v>2316</v>
       </c>
       <c r="B914" s="38">
         <v>79168542102</v>
@@ -26183,7 +26210,7 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A915" s="32" t="s">
-        <v>2327</v>
+        <v>2317</v>
       </c>
       <c r="B915" s="38">
         <v>79888928388</v>
@@ -26203,7 +26230,7 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A916" s="32" t="s">
-        <v>2328</v>
+        <v>2318</v>
       </c>
       <c r="B916" s="38">
         <v>79032374317</v>
@@ -26245,7 +26272,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A918" s="32" t="s">
-        <v>2309</v>
+        <v>2299</v>
       </c>
       <c r="B918" s="38">
         <v>79207020082</v>
@@ -26268,7 +26295,7 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A919" s="32" t="s">
-        <v>2329</v>
+        <v>2319</v>
       </c>
       <c r="B919" s="38">
         <v>79041183867</v>
@@ -26289,7 +26316,7 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A920" s="32" t="s">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B920" s="38">
         <v>79032978483</v>
@@ -26310,7 +26337,7 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A921" s="32" t="s">
-        <v>2331</v>
+        <v>2321</v>
       </c>
       <c r="B921" s="38">
         <v>79308038836</v>
@@ -26333,7 +26360,7 @@
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A922" s="32" t="s">
-        <v>2332</v>
+        <v>2322</v>
       </c>
       <c r="B922" s="38">
         <v>79385488845</v>
@@ -26356,7 +26383,7 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A923" s="32" t="s">
-        <v>2333</v>
+        <v>2323</v>
       </c>
       <c r="B923" s="38">
         <v>79046838139</v>
@@ -26377,7 +26404,7 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A924" s="32" t="s">
-        <v>2334</v>
+        <v>2324</v>
       </c>
       <c r="B924" s="38">
         <v>79128268207</v>
@@ -26400,7 +26427,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A925" s="32" t="s">
-        <v>2335</v>
+        <v>2325</v>
       </c>
       <c r="B925" s="38">
         <v>79148261215</v>
@@ -26423,7 +26450,7 @@
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A926" s="32" t="s">
-        <v>2336</v>
+        <v>2326</v>
       </c>
       <c r="B926" s="38">
         <v>79267823227</v>
@@ -26444,7 +26471,7 @@
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A927" s="32" t="s">
-        <v>2337</v>
+        <v>2327</v>
       </c>
       <c r="B927" s="38">
         <v>79184915237</v>
@@ -26469,7 +26496,7 @@
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A928" s="32" t="s">
-        <v>2338</v>
+        <v>2328</v>
       </c>
       <c r="B928" s="38">
         <v>79034390003</v>
@@ -26516,7 +26543,7 @@
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" s="32" t="s">
-        <v>2339</v>
+        <v>2329</v>
       </c>
       <c r="B930" s="38">
         <v>79595062068</v>
@@ -26572,7 +26599,7 @@
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" s="32" t="s">
-        <v>2414</v>
+        <v>2404</v>
       </c>
       <c r="B933" s="38">
         <v>79180664535</v>
@@ -26590,7 +26617,7 @@
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" s="32" t="s">
-        <v>2415</v>
+        <v>2405</v>
       </c>
       <c r="B934" s="38">
         <v>79197382450</v>
@@ -26610,7 +26637,7 @@
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" s="32" t="s">
-        <v>2416</v>
+        <v>2406</v>
       </c>
       <c r="B935" s="38">
         <v>79885220528</v>
@@ -26632,7 +26659,7 @@
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" s="32" t="s">
-        <v>2417</v>
+        <v>2407</v>
       </c>
       <c r="B936" s="38">
         <v>79885093331</v>
@@ -26676,7 +26703,7 @@
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" s="32" t="s">
-        <v>2418</v>
+        <v>2408</v>
       </c>
       <c r="B938" s="38">
         <v>79184400178</v>
@@ -26698,7 +26725,7 @@
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" s="32" t="s">
-        <v>2419</v>
+        <v>2409</v>
       </c>
       <c r="B939" s="38">
         <v>79183270587</v>
@@ -26716,7 +26743,7 @@
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" s="32" t="s">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B940" s="38">
         <v>79183889940</v>
@@ -26734,7 +26761,7 @@
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" s="32" t="s">
-        <v>2421</v>
+        <v>2411</v>
       </c>
       <c r="B941" s="38">
         <v>79994722206</v>
@@ -26750,7 +26777,7 @@
     </row>
     <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" s="32" t="s">
-        <v>2422</v>
+        <v>2412</v>
       </c>
       <c r="B942" s="38">
         <v>79184165266</v>
@@ -26790,7 +26817,7 @@
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" s="32" t="s">
-        <v>2423</v>
+        <v>2413</v>
       </c>
       <c r="B944" s="38">
         <v>79160231803</v>
@@ -26808,7 +26835,7 @@
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" s="32" t="s">
-        <v>2424</v>
+        <v>2414</v>
       </c>
       <c r="B945" s="38">
         <v>79251587458</v>
@@ -26826,7 +26853,7 @@
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" s="32" t="s">
-        <v>2425</v>
+        <v>2415</v>
       </c>
       <c r="B946" s="38">
         <v>79385519412</v>
@@ -26932,7 +26959,7 @@
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" s="32" t="s">
-        <v>2426</v>
+        <v>2416</v>
       </c>
       <c r="B952" s="33">
         <v>79895106888</v>
@@ -26948,7 +26975,7 @@
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" s="32" t="s">
-        <v>2427</v>
+        <v>2417</v>
       </c>
       <c r="B953" s="33">
         <v>79189487859</v>
@@ -26966,7 +26993,7 @@
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" s="32" t="s">
-        <v>2428</v>
+        <v>2418</v>
       </c>
       <c r="B954" s="33">
         <v>79094690279</v>
@@ -26986,7 +27013,7 @@
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" s="32" t="s">
-        <v>2429</v>
+        <v>2419</v>
       </c>
       <c r="B955" s="33">
         <v>79270465755</v>
@@ -27006,7 +27033,7 @@
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" s="32" t="s">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B956" s="33">
         <v>79181514761</v>
@@ -27038,7 +27065,7 @@
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" s="32" t="s">
-        <v>2431</v>
+        <v>2421</v>
       </c>
       <c r="B958" s="33">
         <v>79286120337</v>
@@ -27058,7 +27085,7 @@
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" s="32" t="s">
-        <v>2432</v>
+        <v>2422</v>
       </c>
       <c r="B959" s="33">
         <v>79181603172</v>
@@ -27076,7 +27103,7 @@
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" s="32" t="s">
-        <v>2433</v>
+        <v>2423</v>
       </c>
       <c r="B960" s="33">
         <v>79528474569</v>
@@ -27094,7 +27121,7 @@
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" s="32" t="s">
-        <v>2434</v>
+        <v>2424</v>
       </c>
       <c r="B961" s="33">
         <v>79891443888</v>
@@ -27122,7 +27149,7 @@
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" s="32" t="s">
-        <v>2435</v>
+        <v>2425</v>
       </c>
       <c r="B963" s="33">
         <v>79186956626</v>
@@ -27138,7 +27165,7 @@
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" s="32" t="s">
-        <v>2436</v>
+        <v>2426</v>
       </c>
       <c r="B964" s="33">
         <v>79183433464</v>
@@ -27156,7 +27183,7 @@
     </row>
     <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" s="32" t="s">
-        <v>2437</v>
+        <v>2427</v>
       </c>
       <c r="B965" s="33">
         <v>79094646000</v>
@@ -27172,7 +27199,7 @@
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" s="32" t="s">
-        <v>2438</v>
+        <v>2428</v>
       </c>
       <c r="B966" s="33">
         <v>79854264076</v>
@@ -27188,7 +27215,7 @@
     </row>
     <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" s="32" t="s">
-        <v>2439</v>
+        <v>2429</v>
       </c>
       <c r="B967" s="33">
         <v>79186525585</v>
@@ -27204,7 +27231,7 @@
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" s="32" t="s">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B968" s="33">
         <v>79528581269</v>
@@ -27224,7 +27251,7 @@
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" s="32" t="s">
-        <v>2441</v>
+        <v>2431</v>
       </c>
       <c r="B969" s="33">
         <v>79673053030</v>
@@ -27254,7 +27281,7 @@
     </row>
     <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" s="32" t="s">
-        <v>2442</v>
+        <v>2432</v>
       </c>
       <c r="B971" s="33">
         <v>79886696618</v>
@@ -27404,7 +27431,7 @@
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" s="32" t="s">
-        <v>2443</v>
+        <v>2433</v>
       </c>
       <c r="B978" s="33">
         <v>79117974075</v>
@@ -27422,7 +27449,7 @@
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" s="32" t="s">
-        <v>2444</v>
+        <v>2434</v>
       </c>
       <c r="B979" s="33">
         <v>79615951401</v>
@@ -27440,7 +27467,7 @@
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" s="32" t="s">
-        <v>2445</v>
+        <v>2435</v>
       </c>
       <c r="B980" s="33">
         <v>79274773218</v>
@@ -27458,7 +27485,7 @@
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" s="32" t="s">
-        <v>2446</v>
+        <v>2436</v>
       </c>
       <c r="B981" s="33">
         <v>79673005052</v>
@@ -27476,7 +27503,7 @@
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" s="32" t="s">
-        <v>2447</v>
+        <v>2437</v>
       </c>
       <c r="B982" s="33">
         <v>79625245851</v>
@@ -27494,7 +27521,7 @@
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" s="32" t="s">
-        <v>2448</v>
+        <v>2438</v>
       </c>
       <c r="B983" s="33">
         <v>79898052605</v>
@@ -27512,7 +27539,7 @@
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" s="32" t="s">
-        <v>2449</v>
+        <v>2439</v>
       </c>
       <c r="B984" s="33">
         <v>79992365729</v>
@@ -27554,7 +27581,7 @@
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" s="32" t="s">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B986" s="38">
         <v>79182119543</v>
@@ -27570,7 +27597,7 @@
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" s="32" t="s">
-        <v>2451</v>
+        <v>2441</v>
       </c>
       <c r="B987" s="38">
         <v>79886039199</v>
@@ -27590,7 +27617,7 @@
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" s="32" t="s">
-        <v>2452</v>
+        <v>2442</v>
       </c>
       <c r="B988" s="38">
         <v>79182846179</v>
@@ -27608,7 +27635,7 @@
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" s="32" t="s">
-        <v>2453</v>
+        <v>2443</v>
       </c>
       <c r="B989" s="38">
         <v>79185545589</v>
@@ -27626,7 +27653,7 @@
     </row>
     <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" s="32" t="s">
-        <v>2454</v>
+        <v>2444</v>
       </c>
       <c r="B990" s="38">
         <v>79637505138</v>
@@ -27642,7 +27669,7 @@
     </row>
     <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" s="32" t="s">
-        <v>2455</v>
+        <v>2445</v>
       </c>
       <c r="B991" s="38">
         <v>79604757152</v>
@@ -27660,7 +27687,7 @@
     </row>
     <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" s="32" t="s">
-        <v>2456</v>
+        <v>2446</v>
       </c>
       <c r="B992" s="38">
         <v>79182762782</v>
@@ -27702,7 +27729,7 @@
     </row>
     <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" s="32" t="s">
-        <v>2457</v>
+        <v>2447</v>
       </c>
       <c r="B994" s="38">
         <v>79892941007</v>
@@ -27718,7 +27745,7 @@
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" s="32" t="s">
-        <v>2458</v>
+        <v>2448</v>
       </c>
       <c r="B995" s="38">
         <v>79060896267</v>
@@ -27738,7 +27765,7 @@
     </row>
     <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" s="32" t="s">
-        <v>2459</v>
+        <v>2449</v>
       </c>
       <c r="B996" s="38">
         <v>79384227276</v>
@@ -27778,7 +27805,7 @@
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" s="32" t="s">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B998" s="38">
         <v>79614238176</v>
@@ -27806,7 +27833,7 @@
     </row>
     <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" s="32" t="s">
-        <v>2461</v>
+        <v>2451</v>
       </c>
       <c r="B1000" s="38">
         <v>79280121007</v>
@@ -27834,7 +27861,7 @@
     </row>
     <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" s="32" t="s">
-        <v>2462</v>
+        <v>2452</v>
       </c>
       <c r="B1002" s="38">
         <v>79180985165</v>
@@ -27850,7 +27877,7 @@
     </row>
     <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" s="32" t="s">
-        <v>2463</v>
+        <v>2453</v>
       </c>
       <c r="B1003" s="38">
         <v>79186200028</v>
@@ -27866,7 +27893,7 @@
     </row>
     <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" s="32" t="s">
-        <v>2464</v>
+        <v>2454</v>
       </c>
       <c r="B1004" s="38">
         <v>79190278727</v>
@@ -27894,7 +27921,7 @@
     </row>
     <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" s="32" t="s">
-        <v>2465</v>
+        <v>2455</v>
       </c>
       <c r="B1006" s="38">
         <v>79615280373</v>
@@ -27910,7 +27937,7 @@
     </row>
     <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1007" s="32" t="s">
-        <v>2466</v>
+        <v>2456</v>
       </c>
       <c r="B1007" s="38">
         <v>79622028701</v>
@@ -27926,7 +27953,7 @@
     </row>
     <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1008" s="32" t="s">
-        <v>2467</v>
+        <v>2457</v>
       </c>
       <c r="B1008" s="38">
         <v>79185055723</v>
@@ -27942,7 +27969,7 @@
     </row>
     <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" s="32" t="s">
-        <v>2468</v>
+        <v>2458</v>
       </c>
       <c r="B1009" s="38">
         <v>79788139855</v>
@@ -27970,7 +27997,7 @@
     </row>
     <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" s="32" t="s">
-        <v>2469</v>
+        <v>2459</v>
       </c>
       <c r="B1011" s="38">
         <v>79189749194</v>
@@ -27988,7 +28015,7 @@
     </row>
     <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" s="32" t="s">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B1012" s="38">
         <v>79184801108</v>
@@ -28006,7 +28033,7 @@
     </row>
     <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" s="32" t="s">
-        <v>2471</v>
+        <v>2461</v>
       </c>
       <c r="B1013" s="38">
         <v>79646847710</v>
@@ -28022,7 +28049,7 @@
     </row>
     <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" s="32" t="s">
-        <v>2472</v>
+        <v>2462</v>
       </c>
       <c r="B1014" s="38">
         <v>79649041350</v>
@@ -28050,7 +28077,7 @@
     </row>
     <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" s="32" t="s">
-        <v>2473</v>
+        <v>2463</v>
       </c>
       <c r="B1016" s="31">
         <v>79181537666</v>
@@ -28066,7 +28093,7 @@
     </row>
     <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" s="32" t="s">
-        <v>2474</v>
+        <v>2464</v>
       </c>
       <c r="B1017" s="31">
         <v>79051511564</v>
@@ -28082,7 +28109,7 @@
     </row>
     <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" s="32" t="s">
-        <v>2475</v>
+        <v>2465</v>
       </c>
       <c r="B1018" s="31">
         <v>79254155954</v>
@@ -28098,7 +28125,7 @@
     </row>
     <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" s="32" t="s">
-        <v>2476</v>
+        <v>2466</v>
       </c>
       <c r="B1019" s="31">
         <v>79626803581</v>
@@ -28126,7 +28153,7 @@
     </row>
     <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" s="32" t="s">
-        <v>2477</v>
+        <v>2467</v>
       </c>
       <c r="B1021" s="31">
         <v>79281059268</v>
@@ -28142,7 +28169,7 @@
     </row>
     <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" s="32" t="s">
-        <v>2478</v>
+        <v>2468</v>
       </c>
       <c r="B1022" s="31">
         <v>79183388668</v>
@@ -28160,7 +28187,7 @@
     </row>
     <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" s="32" t="s">
-        <v>2479</v>
+        <v>2469</v>
       </c>
       <c r="B1023" s="31">
         <v>79067249922</v>
@@ -28188,7 +28215,7 @@
     </row>
     <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1025" s="32" t="s">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="B1025" s="31">
         <v>79052993315</v>
@@ -28206,7 +28233,7 @@
     </row>
     <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1026" s="32" t="s">
-        <v>2481</v>
+        <v>2471</v>
       </c>
       <c r="B1026" s="31">
         <v>79043499977</v>
@@ -28236,7 +28263,7 @@
     </row>
     <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1028" s="32" t="s">
-        <v>2482</v>
+        <v>2472</v>
       </c>
       <c r="B1028" s="31">
         <v>79052875113</v>
@@ -28252,7 +28279,7 @@
     </row>
     <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1029" s="32" t="s">
-        <v>2483</v>
+        <v>2473</v>
       </c>
       <c r="B1029" s="31">
         <v>79061820166</v>
@@ -28268,7 +28295,7 @@
     </row>
     <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1030" s="32" t="s">
-        <v>2484</v>
+        <v>2474</v>
       </c>
       <c r="B1030" s="31">
         <v>79189333736</v>
@@ -28284,7 +28311,7 @@
     </row>
     <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1031" s="32" t="s">
-        <v>2485</v>
+        <v>2475</v>
       </c>
       <c r="B1031" s="31">
         <v>79064327871</v>
@@ -28300,7 +28327,7 @@
     </row>
     <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1032" s="32" t="s">
-        <v>2486</v>
+        <v>2476</v>
       </c>
       <c r="B1032" s="31">
         <v>79102891788</v>
@@ -28328,13 +28355,13 @@
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1034" s="32" t="s">
-        <v>2487</v>
+        <v>2477</v>
       </c>
       <c r="B1034" s="31">
         <v>79183561661</v>
       </c>
       <c r="C1034" s="31" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="D1034" s="31" t="s">
         <v>2080</v>
@@ -28346,7 +28373,7 @@
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1035" s="32" t="s">
-        <v>2488</v>
+        <v>2478</v>
       </c>
       <c r="B1035" s="31">
         <v>79537206758</v>
@@ -28454,7 +28481,7 @@
     </row>
     <row r="1041" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1041" s="32" t="s">
-        <v>2527</v>
+        <v>2517</v>
       </c>
       <c r="B1041" s="31">
         <v>79788288099</v>
@@ -28470,7 +28497,7 @@
     </row>
     <row r="1042" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1042" s="32" t="s">
-        <v>2528</v>
+        <v>2518</v>
       </c>
       <c r="B1042" s="31">
         <v>79065859343</v>
@@ -28486,7 +28513,7 @@
     </row>
     <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1043" s="32" t="s">
-        <v>2529</v>
+        <v>2519</v>
       </c>
       <c r="B1043" s="31">
         <v>79184427932</v>
@@ -28504,7 +28531,7 @@
     </row>
     <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1044" s="32" t="s">
-        <v>2530</v>
+        <v>2520</v>
       </c>
       <c r="B1044" s="31">
         <v>79780015912</v>
@@ -28520,7 +28547,7 @@
     </row>
     <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1045" s="32" t="s">
-        <v>2531</v>
+        <v>2521</v>
       </c>
       <c r="B1045" s="31">
         <v>79183756404</v>
@@ -28540,7 +28567,7 @@
     </row>
     <row r="1046" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1046" s="32" t="s">
-        <v>2532</v>
+        <v>2522</v>
       </c>
       <c r="B1046" s="31">
         <v>79031442806</v>
@@ -28572,7 +28599,7 @@
     </row>
     <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1048" s="32" t="s">
-        <v>2533</v>
+        <v>2523</v>
       </c>
       <c r="B1048" s="31">
         <v>79624430220</v>
@@ -28594,7 +28621,7 @@
     </row>
     <row r="1049" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1049" s="32" t="s">
-        <v>2534</v>
+        <v>2524</v>
       </c>
       <c r="B1049" s="31">
         <v>79602429824</v>
@@ -28622,7 +28649,7 @@
     </row>
     <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1051" s="32" t="s">
-        <v>2535</v>
+        <v>2525</v>
       </c>
       <c r="B1051" s="31">
         <v>79789971387</v>
@@ -28638,7 +28665,7 @@
     </row>
     <row r="1052" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1052" s="32" t="s">
-        <v>2536</v>
+        <v>2526</v>
       </c>
       <c r="B1052" s="31">
         <v>79661185577</v>
@@ -28686,7 +28713,7 @@
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1055" s="32" t="s">
-        <v>2575</v>
+        <v>2565</v>
       </c>
       <c r="B1055" s="33">
         <v>79186452525</v>
@@ -28702,7 +28729,7 @@
     </row>
     <row r="1056" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1056" s="32" t="s">
-        <v>2576</v>
+        <v>2566</v>
       </c>
       <c r="B1056" s="33">
         <v>79189484040</v>
@@ -28718,7 +28745,7 @@
     </row>
     <row r="1057" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1057" s="32" t="s">
-        <v>2577</v>
+        <v>2567</v>
       </c>
       <c r="B1057" s="33">
         <v>79183860270</v>
@@ -28734,7 +28761,7 @@
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1058" s="32" t="s">
-        <v>2578</v>
+        <v>2568</v>
       </c>
       <c r="B1058" s="33">
         <v>79779455485</v>
@@ -28752,7 +28779,7 @@
     </row>
     <row r="1059" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1059" s="32" t="s">
-        <v>2579</v>
+        <v>2569</v>
       </c>
       <c r="B1059" s="33">
         <v>79056507300</v>
@@ -28770,7 +28797,7 @@
     </row>
     <row r="1060" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1060" s="32" t="s">
-        <v>2580</v>
+        <v>2570</v>
       </c>
       <c r="B1060" s="33">
         <v>79258091550</v>
@@ -28788,7 +28815,7 @@
     </row>
     <row r="1061" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1061" s="32" t="s">
-        <v>2581</v>
+        <v>2571</v>
       </c>
       <c r="B1061" s="33">
         <v>79185091900</v>
@@ -28820,7 +28847,7 @@
     </row>
     <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1063" s="32" t="s">
-        <v>2582</v>
+        <v>2572</v>
       </c>
       <c r="B1063" s="33">
         <v>79649334332</v>
@@ -28836,7 +28863,7 @@
     </row>
     <row r="1064" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1064" s="32" t="s">
-        <v>2583</v>
+        <v>2573</v>
       </c>
       <c r="B1064" s="33">
         <v>79783434760</v>
@@ -28852,7 +28879,7 @@
     </row>
     <row r="1065" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1065" s="32" t="s">
-        <v>2584</v>
+        <v>2574</v>
       </c>
       <c r="B1065" s="33">
         <v>79493130260</v>
@@ -28868,7 +28895,7 @@
     </row>
     <row r="1066" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1066" s="32" t="s">
-        <v>2585</v>
+        <v>2575</v>
       </c>
       <c r="B1066" s="33">
         <v>79990156363</v>
@@ -28886,7 +28913,7 @@
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1067" s="32" t="s">
-        <v>2586</v>
+        <v>2576</v>
       </c>
       <c r="B1067" s="33">
         <v>79880146339</v>
@@ -28902,7 +28929,7 @@
     </row>
     <row r="1068" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1068" s="32" t="s">
-        <v>2587</v>
+        <v>2577</v>
       </c>
       <c r="B1068" s="33">
         <v>79604622005</v>
@@ -28920,7 +28947,7 @@
     </row>
     <row r="1069" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1069" s="32" t="s">
-        <v>2588</v>
+        <v>2578</v>
       </c>
       <c r="B1069" s="33">
         <v>79192563907</v>
@@ -28936,7 +28963,7 @@
     </row>
     <row r="1070" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1070" s="32" t="s">
-        <v>2589</v>
+        <v>2579</v>
       </c>
       <c r="B1070" s="33">
         <v>79180335333</v>
@@ -28984,7 +29011,7 @@
     </row>
     <row r="1073" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1073" s="32" t="s">
-        <v>2590</v>
+        <v>2580</v>
       </c>
       <c r="B1073" s="33">
         <v>79183073394</v>
@@ -29014,19 +29041,19 @@
     </row>
     <row r="1075" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1075" s="32" t="s">
-        <v>2591</v>
+        <v>2581</v>
       </c>
       <c r="B1075" s="33">
         <v>79615215290</v>
       </c>
       <c r="C1075" s="31" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D1075" s="31" t="s">
         <v>2209</v>
       </c>
-      <c r="D1075" s="31" t="s">
+      <c r="E1075" s="31" t="s">
         <v>2210</v>
-      </c>
-      <c r="E1075" s="31" t="s">
-        <v>2211</v>
       </c>
       <c r="F1075" s="31" t="s">
         <v>1806</v>
@@ -29036,7 +29063,7 @@
     </row>
     <row r="1076" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1076" s="32" t="s">
-        <v>2592</v>
+        <v>2582</v>
       </c>
       <c r="B1076" s="33">
         <v>79094569745</v>
@@ -29052,7 +29079,7 @@
     </row>
     <row r="1077" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1077" s="32" t="s">
-        <v>2593</v>
+        <v>2583</v>
       </c>
       <c r="B1077" s="33">
         <v>79180757000</v>
@@ -29068,7 +29095,7 @@
     </row>
     <row r="1078" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1078" s="32" t="s">
-        <v>2594</v>
+        <v>2584</v>
       </c>
       <c r="B1078" s="33">
         <v>79628609461</v>
@@ -29086,7 +29113,7 @@
     </row>
     <row r="1079" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1079" s="32" t="s">
-        <v>2595</v>
+        <v>2585</v>
       </c>
       <c r="B1079" s="33">
         <v>79184101450</v>
@@ -29104,7 +29131,7 @@
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1080" s="32" t="s">
-        <v>2596</v>
+        <v>2586</v>
       </c>
       <c r="B1080" s="33">
         <v>79183999079</v>
@@ -29126,7 +29153,7 @@
     </row>
     <row r="1081" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1081" s="32" t="s">
-        <v>2597</v>
+        <v>2587</v>
       </c>
       <c r="B1081" s="33">
         <v>79181433232</v>
@@ -29144,7 +29171,7 @@
     </row>
     <row r="1082" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1082" s="32" t="s">
-        <v>2613</v>
+        <v>2603</v>
       </c>
       <c r="B1082" s="33">
         <v>79817025393</v>
@@ -29162,7 +29189,7 @@
     </row>
     <row r="1083" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1083" s="32" t="s">
-        <v>2612</v>
+        <v>2602</v>
       </c>
       <c r="B1083" s="33">
         <v>79184302094</v>
@@ -29190,7 +29217,7 @@
     </row>
     <row r="1085" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1085" s="32" t="s">
-        <v>2611</v>
+        <v>2601</v>
       </c>
       <c r="B1085" s="33">
         <v>79287677710</v>
@@ -29212,7 +29239,7 @@
     </row>
     <row r="1086" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1086" s="32" t="s">
-        <v>2610</v>
+        <v>2600</v>
       </c>
       <c r="B1086" s="33">
         <v>79615198406</v>
@@ -29228,7 +29255,7 @@
     </row>
     <row r="1087" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1087" s="32" t="s">
-        <v>2609</v>
+        <v>2599</v>
       </c>
       <c r="B1087" s="33">
         <v>79620503561</v>
@@ -29246,7 +29273,7 @@
     </row>
     <row r="1088" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1088" s="32" t="s">
-        <v>2608</v>
+        <v>2598</v>
       </c>
       <c r="B1088" s="33">
         <v>79093732088</v>
@@ -29268,7 +29295,7 @@
     </row>
     <row r="1089" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1089" s="32" t="s">
-        <v>2607</v>
+        <v>2597</v>
       </c>
       <c r="B1089" s="33">
         <v>79060683338</v>
@@ -29288,7 +29315,7 @@
     </row>
     <row r="1090" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1090" s="32" t="s">
-        <v>2606</v>
+        <v>2596</v>
       </c>
       <c r="B1090" s="33">
         <v>79184137117</v>
@@ -29304,7 +29331,7 @@
     </row>
     <row r="1091" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1091" s="32" t="s">
-        <v>2605</v>
+        <v>2595</v>
       </c>
       <c r="B1091" s="33">
         <v>79180660587</v>
@@ -29332,7 +29359,7 @@
     </row>
     <row r="1093" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1093" s="32" t="s">
-        <v>2604</v>
+        <v>2594</v>
       </c>
       <c r="B1093" s="33">
         <v>79002359970</v>
@@ -29354,7 +29381,7 @@
     </row>
     <row r="1094" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1094" s="32" t="s">
-        <v>2603</v>
+        <v>2593</v>
       </c>
       <c r="B1094" s="33">
         <v>79892306069</v>
@@ -29384,7 +29411,7 @@
     </row>
     <row r="1096" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1096" s="32" t="s">
-        <v>2602</v>
+        <v>2592</v>
       </c>
       <c r="B1096" s="33">
         <v>79615101239</v>
@@ -29400,7 +29427,7 @@
     </row>
     <row r="1097" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1097" s="32" t="s">
-        <v>2601</v>
+        <v>2591</v>
       </c>
       <c r="B1097" s="33">
         <v>79287753737</v>
@@ -29418,7 +29445,7 @@
     </row>
     <row r="1098" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1098" s="32" t="s">
-        <v>2600</v>
+        <v>2590</v>
       </c>
       <c r="B1098" s="33">
         <v>79283348884</v>
@@ -29440,7 +29467,7 @@
     </row>
     <row r="1099" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1099" s="32" t="s">
-        <v>2599</v>
+        <v>2589</v>
       </c>
       <c r="B1099" s="33">
         <v>79381175888</v>
@@ -29468,7 +29495,7 @@
     </row>
     <row r="1101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1101" s="32" t="s">
-        <v>2598</v>
+        <v>2588</v>
       </c>
       <c r="B1101" s="38">
         <v>79536931038</v>
@@ -29522,7 +29549,7 @@
     </row>
     <row r="1104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1104" s="32" t="s">
-        <v>2630</v>
+        <v>2620</v>
       </c>
       <c r="B1104" s="33">
         <v>79900137808</v>
@@ -29540,7 +29567,7 @@
     </row>
     <row r="1105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1105" s="32" t="s">
-        <v>2631</v>
+        <v>2621</v>
       </c>
       <c r="B1105" s="33">
         <v>79649134155</v>
@@ -29558,7 +29585,7 @@
     </row>
     <row r="1106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1106" s="32" t="s">
-        <v>2632</v>
+        <v>2622</v>
       </c>
       <c r="B1106" s="33">
         <v>79186587857</v>
@@ -29574,7 +29601,7 @@
     </row>
     <row r="1107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1107" s="32" t="s">
-        <v>2633</v>
+        <v>2623</v>
       </c>
       <c r="B1107" s="33">
         <v>79183710874</v>
@@ -29590,7 +29617,7 @@
     </row>
     <row r="1108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1108" s="32" t="s">
-        <v>2634</v>
+        <v>2624</v>
       </c>
       <c r="B1108" s="33">
         <v>79185758610</v>
@@ -29610,7 +29637,7 @@
     </row>
     <row r="1109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1109" s="32" t="s">
-        <v>2635</v>
+        <v>2625</v>
       </c>
       <c r="B1109" s="33">
         <v>79528107175</v>
@@ -29626,7 +29653,7 @@
     </row>
     <row r="1110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1110" s="32" t="s">
-        <v>2636</v>
+        <v>2626</v>
       </c>
       <c r="B1110" s="33">
         <v>79530981964</v>
@@ -29660,7 +29687,7 @@
     </row>
     <row r="1112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1112" s="32" t="s">
-        <v>2637</v>
+        <v>2627</v>
       </c>
       <c r="B1112" s="33">
         <v>79884919692</v>
@@ -29676,7 +29703,7 @@
     </row>
     <row r="1113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1113" s="32" t="s">
-        <v>2638</v>
+        <v>2628</v>
       </c>
       <c r="B1113" s="33">
         <v>79164495884</v>
@@ -29692,7 +29719,7 @@
     </row>
     <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1114" s="32" t="s">
-        <v>2639</v>
+        <v>2629</v>
       </c>
       <c r="B1114" s="33">
         <v>79493057717</v>
@@ -29720,7 +29747,7 @@
     </row>
     <row r="1116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1116" s="32" t="s">
-        <v>2640</v>
+        <v>2630</v>
       </c>
       <c r="B1116" s="33">
         <v>79180769237</v>
@@ -29736,7 +29763,7 @@
     </row>
     <row r="1117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1117" s="32" t="s">
-        <v>2641</v>
+        <v>2631</v>
       </c>
       <c r="B1117" s="33">
         <v>79180119455</v>
@@ -29754,7 +29781,7 @@
     </row>
     <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1118" s="32" t="s">
-        <v>2642</v>
+        <v>2632</v>
       </c>
       <c r="B1118" s="33">
         <v>79787625654</v>
@@ -29770,7 +29797,7 @@
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1119" s="32" t="s">
-        <v>2643</v>
+        <v>2633</v>
       </c>
       <c r="B1119" s="33">
         <v>79884788948</v>
@@ -29798,7 +29825,7 @@
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1121" s="32" t="s">
-        <v>2644</v>
+        <v>2634</v>
       </c>
       <c r="B1121" s="33">
         <v>79205825242</v>
@@ -29814,7 +29841,7 @@
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1122" s="32" t="s">
-        <v>2645</v>
+        <v>2635</v>
       </c>
       <c r="B1122" s="33">
         <v>79181511141</v>
@@ -29862,7 +29889,7 @@
     </row>
     <row r="1125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1125" s="32" t="s">
-        <v>2646</v>
+        <v>2636</v>
       </c>
       <c r="B1125" s="33">
         <v>79118596500</v>
@@ -29880,7 +29907,7 @@
     </row>
     <row r="1126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1126" s="32" t="s">
-        <v>2647</v>
+        <v>2637</v>
       </c>
       <c r="B1126" s="33">
         <v>79780187528</v>
@@ -29902,7 +29929,7 @@
     </row>
     <row r="1127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1127" s="32" t="s">
-        <v>2648</v>
+        <v>2638</v>
       </c>
       <c r="B1127" s="33">
         <v>79037376464</v>
@@ -29932,7 +29959,7 @@
     </row>
     <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1129" s="32" t="s">
-        <v>2649</v>
+        <v>2639</v>
       </c>
       <c r="B1129" s="33">
         <v>79103223870</v>
@@ -29982,19 +30009,19 @@
     </row>
     <row r="1132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1132" s="32" t="s">
-        <v>2650</v>
+        <v>2640</v>
       </c>
       <c r="B1132" s="33">
         <v>79284697777</v>
       </c>
       <c r="C1132" s="33" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="D1132" s="33" t="s">
+        <v>2259</v>
+      </c>
+      <c r="E1132" s="33" t="s">
         <v>2260</v>
-      </c>
-      <c r="E1132" s="33" t="s">
-        <v>2261</v>
       </c>
       <c r="F1132" s="33" t="s">
         <v>1833</v>
@@ -30004,14 +30031,14 @@
     </row>
     <row r="1133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1133" s="32" t="s">
-        <v>2651</v>
+        <v>2641</v>
       </c>
       <c r="B1133" s="33">
         <v>79181601208</v>
       </c>
       <c r="C1133" s="33"/>
       <c r="D1133" s="33" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="E1133" s="33"/>
       <c r="F1133" s="33"/>
@@ -30032,16 +30059,16 @@
     </row>
     <row r="1135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1135" s="32" t="s">
-        <v>2652</v>
+        <v>2642</v>
       </c>
       <c r="B1135" s="33">
         <v>79001236569</v>
       </c>
       <c r="C1135" s="33" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="D1135" s="33" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="E1135" s="33"/>
       <c r="F1135" s="33"/>
@@ -30050,19 +30077,19 @@
     </row>
     <row r="1136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1136" s="32" t="s">
-        <v>2653</v>
+        <v>2643</v>
       </c>
       <c r="B1136" s="33">
         <v>79991005104</v>
       </c>
       <c r="C1136" s="33" t="s">
-        <v>2493</v>
+        <v>2483</v>
       </c>
       <c r="D1136" s="33" t="s">
-        <v>2491</v>
+        <v>2481</v>
       </c>
       <c r="E1136" s="33" t="s">
-        <v>2492</v>
+        <v>2482</v>
       </c>
       <c r="F1136" s="33" t="s">
         <v>1834</v>
@@ -30072,16 +30099,16 @@
     </row>
     <row r="1137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1137" s="32" t="s">
-        <v>2654</v>
+        <v>2644</v>
       </c>
       <c r="B1137" s="33">
         <v>79371249966</v>
       </c>
       <c r="C1137" s="33" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="D1137" s="33" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="E1137" s="33"/>
       <c r="F1137" s="33"/>
@@ -30090,13 +30117,13 @@
     </row>
     <row r="1138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1138" s="32" t="s">
-        <v>2655</v>
+        <v>2645</v>
       </c>
       <c r="B1138" s="33">
         <v>79185805028</v>
       </c>
       <c r="C1138" s="33" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="D1138" s="33"/>
       <c r="E1138" s="33"/>
@@ -30118,16 +30145,16 @@
     </row>
     <row r="1140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1140" s="32" t="s">
-        <v>2656</v>
+        <v>2646</v>
       </c>
       <c r="B1140" s="33">
         <v>79687042488</v>
       </c>
       <c r="C1140" s="33" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="D1140" s="33" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="E1140" s="33"/>
       <c r="F1140" s="33"/>
@@ -30148,7 +30175,7 @@
     </row>
     <row r="1142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1142" s="18" t="s">
-        <v>2657</v>
+        <v>2647</v>
       </c>
       <c r="B1142" s="40">
         <v>79283483981</v>
@@ -30202,13 +30229,13 @@
     </row>
     <row r="1145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1145" s="38" t="s">
-        <v>2666</v>
+        <v>2656</v>
       </c>
       <c r="B1145" s="38">
         <v>79110886608</v>
       </c>
       <c r="C1145" s="33" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="D1145" s="33"/>
       <c r="E1145" s="33"/>
@@ -30218,14 +30245,14 @@
     </row>
     <row r="1146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1146" s="32" t="s">
-        <v>2667</v>
+        <v>2657</v>
       </c>
       <c r="B1146" s="33">
         <v>79884718844</v>
       </c>
       <c r="C1146" s="33"/>
       <c r="D1146" s="33" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="E1146" s="33"/>
       <c r="F1146" s="33"/>
@@ -30234,16 +30261,16 @@
     </row>
     <row r="1147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1147" s="32" t="s">
-        <v>2668</v>
+        <v>2658</v>
       </c>
       <c r="B1147" s="33">
         <v>79185416500</v>
       </c>
       <c r="C1147" s="33" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="D1147" s="33" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="E1147" s="33"/>
       <c r="F1147" s="33"/>
@@ -30252,16 +30279,16 @@
     </row>
     <row r="1148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1148" s="32" t="s">
-        <v>2669</v>
+        <v>2659</v>
       </c>
       <c r="B1148" s="33">
         <v>79883514535</v>
       </c>
       <c r="C1148" s="33" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="D1148" s="33" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="E1148" s="33"/>
       <c r="F1148" s="33"/>
@@ -30270,16 +30297,16 @@
     </row>
     <row r="1149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1149" s="32" t="s">
-        <v>2670</v>
+        <v>2660</v>
       </c>
       <c r="B1149" s="33">
         <v>79181927858</v>
       </c>
       <c r="C1149" s="33" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="D1149" s="33" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="E1149" s="33"/>
       <c r="F1149" s="33"/>
@@ -30288,13 +30315,13 @@
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1150" s="32" t="s">
-        <v>2671</v>
+        <v>2661</v>
       </c>
       <c r="B1150" s="33">
         <v>79034731171</v>
       </c>
       <c r="C1150" s="33" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="D1150" s="33"/>
       <c r="E1150" s="33"/>
@@ -30316,13 +30343,13 @@
     </row>
     <row r="1152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1152" s="32" t="s">
-        <v>2672</v>
+        <v>2662</v>
       </c>
       <c r="B1152" s="33">
         <v>79518399099</v>
       </c>
       <c r="C1152" s="33" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="D1152" s="33"/>
       <c r="E1152" s="33"/>
@@ -30332,7 +30359,7 @@
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1153" s="32" t="s">
-        <v>2673</v>
+        <v>2663</v>
       </c>
       <c r="B1153" s="33">
         <v>79199932589</v>
@@ -30340,7 +30367,7 @@
       <c r="C1153" s="33"/>
       <c r="D1153" s="33"/>
       <c r="E1153" s="33" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="F1153" s="33" t="s">
         <v>1928</v>
@@ -30350,7 +30377,7 @@
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1154" s="32" t="s">
-        <v>2674</v>
+        <v>2664</v>
       </c>
       <c r="B1154" s="33">
         <v>79898068383</v>
@@ -30358,7 +30385,7 @@
       <c r="C1154" s="33"/>
       <c r="D1154" s="33"/>
       <c r="E1154" s="33" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="F1154" s="33" t="s">
         <v>1929</v>
@@ -30368,13 +30395,13 @@
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1155" s="32" t="s">
-        <v>2675</v>
+        <v>2665</v>
       </c>
       <c r="B1155" s="33">
         <v>79493272312</v>
       </c>
       <c r="C1155" s="33" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="D1155" s="33"/>
       <c r="E1155" s="33"/>
@@ -30384,13 +30411,13 @@
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1156" s="32" t="s">
-        <v>2676</v>
+        <v>2666</v>
       </c>
       <c r="B1156" s="33">
         <v>79184455113</v>
       </c>
       <c r="C1156" s="33" t="s">
-        <v>2279</v>
+        <v>2269</v>
       </c>
       <c r="D1156" s="33"/>
       <c r="E1156" s="33"/>
@@ -30400,13 +30427,13 @@
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1157" s="32" t="s">
-        <v>2677</v>
+        <v>2667</v>
       </c>
       <c r="B1157" s="33">
         <v>79494697622</v>
       </c>
       <c r="C1157" s="33" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="D1157" s="33"/>
       <c r="E1157" s="33"/>
@@ -30416,13 +30443,13 @@
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1158" s="32" t="s">
-        <v>2678</v>
+        <v>2668</v>
       </c>
       <c r="B1158" s="33">
         <v>79288803878</v>
       </c>
       <c r="C1158" s="33" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="D1158" s="33"/>
       <c r="E1158" s="33"/>
@@ -30432,16 +30459,16 @@
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1159" s="32" t="s">
-        <v>2679</v>
+        <v>2669</v>
       </c>
       <c r="B1159" s="33">
         <v>79284223859</v>
       </c>
       <c r="C1159" s="33" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="D1159" s="31" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="E1159" s="33"/>
       <c r="F1159" s="33"/>
@@ -30462,19 +30489,19 @@
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1161" s="32" t="s">
-        <v>2680</v>
+        <v>2670</v>
       </c>
       <c r="B1161" s="33">
         <v>79189338233</v>
       </c>
       <c r="C1161" s="33" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D1161" s="33" t="s">
         <v>2250</v>
       </c>
-      <c r="D1161" s="33" t="s">
-        <v>2251</v>
-      </c>
       <c r="E1161" s="33" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="F1161" s="33" t="s">
         <v>1930</v>
@@ -30516,14 +30543,14 @@
     </row>
     <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1164" s="32" t="s">
-        <v>2666</v>
+        <v>2656</v>
       </c>
       <c r="B1164" s="31">
         <v>79110886608</v>
       </c>
       <c r="C1164" s="31"/>
       <c r="D1164" s="31" t="s">
-        <v>2295</v>
+        <v>2285</v>
       </c>
       <c r="E1164" s="31"/>
       <c r="F1164" s="31"/>
@@ -30532,14 +30559,14 @@
     </row>
     <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1165" s="32" t="s">
-        <v>2681</v>
+        <v>2671</v>
       </c>
       <c r="B1165" s="31">
         <v>79282750088</v>
       </c>
       <c r="C1165" s="31"/>
       <c r="D1165" s="31" t="s">
-        <v>2294</v>
+        <v>2284</v>
       </c>
       <c r="E1165" s="31"/>
       <c r="F1165" s="31"/>
@@ -30548,14 +30575,14 @@
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1166" s="32" t="s">
-        <v>2682</v>
+        <v>2672</v>
       </c>
       <c r="B1166" s="31">
         <v>79384085482</v>
       </c>
       <c r="C1166" s="31"/>
       <c r="D1166" s="31" t="s">
-        <v>2293</v>
+        <v>2283</v>
       </c>
       <c r="E1166" s="31"/>
       <c r="F1166" s="31"/>
@@ -30576,13 +30603,13 @@
     </row>
     <row r="1168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1168" s="32" t="s">
-        <v>2688</v>
+        <v>2678</v>
       </c>
       <c r="B1168" s="31">
         <v>79622153493</v>
       </c>
       <c r="C1168" s="31" t="s">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="D1168" s="31"/>
       <c r="E1168" s="31"/>
@@ -30592,16 +30619,16 @@
     </row>
     <row r="1169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1169" s="32" t="s">
-        <v>2687</v>
+        <v>2677</v>
       </c>
       <c r="B1169" s="31">
         <v>79266122721</v>
       </c>
       <c r="C1169" s="31" t="s">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="D1169" s="31" t="s">
-        <v>2292</v>
+        <v>2282</v>
       </c>
       <c r="E1169" s="31"/>
       <c r="F1169" s="31"/>
@@ -30610,14 +30637,14 @@
     </row>
     <row r="1170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1170" s="32" t="s">
-        <v>2686</v>
+        <v>2676</v>
       </c>
       <c r="B1170" s="31">
         <v>79997719518</v>
       </c>
       <c r="C1170" s="31"/>
       <c r="D1170" s="31" t="s">
-        <v>2291</v>
+        <v>2281</v>
       </c>
       <c r="E1170" s="31"/>
       <c r="F1170" s="31"/>
@@ -30626,13 +30653,13 @@
     </row>
     <row r="1171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1171" s="32" t="s">
-        <v>2685</v>
+        <v>2675</v>
       </c>
       <c r="B1171" s="31">
         <v>79813022825</v>
       </c>
       <c r="C1171" s="31" t="s">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="D1171" s="31"/>
       <c r="E1171" s="31"/>
@@ -30654,19 +30681,19 @@
     </row>
     <row r="1173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1173" s="32" t="s">
-        <v>2684</v>
+        <v>2674</v>
       </c>
       <c r="B1173" s="31">
         <v>79892367996</v>
       </c>
       <c r="C1173" s="31" t="s">
-        <v>2281</v>
+        <v>2271</v>
       </c>
       <c r="D1173" s="31" t="s">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="E1173" s="31" t="s">
-        <v>2296</v>
+        <v>2286</v>
       </c>
       <c r="F1173" s="31" t="s">
         <v>1934</v>
@@ -30676,19 +30703,19 @@
     </row>
     <row r="1174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1174" s="32" t="s">
-        <v>2683</v>
+        <v>2673</v>
       </c>
       <c r="B1174" s="31">
         <v>79182617888</v>
       </c>
       <c r="C1174" s="31" t="s">
-        <v>2281</v>
+        <v>2271</v>
       </c>
       <c r="D1174" s="31" t="s">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="E1174" s="31" t="s">
-        <v>2296</v>
+        <v>2286</v>
       </c>
       <c r="F1174" s="31" t="s">
         <v>1934</v>
@@ -30710,14 +30737,14 @@
     </row>
     <row r="1176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1176" s="32" t="s">
-        <v>2742</v>
+        <v>2732</v>
       </c>
       <c r="B1176" s="31">
         <v>79932156329</v>
       </c>
       <c r="C1176" s="31"/>
       <c r="D1176" s="31" t="s">
-        <v>2289</v>
+        <v>2279</v>
       </c>
       <c r="E1176" s="31"/>
       <c r="F1176" s="31"/>
@@ -30726,14 +30753,14 @@
     </row>
     <row r="1177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1177" s="32" t="s">
-        <v>2743</v>
+        <v>2733</v>
       </c>
       <c r="B1177" s="31">
         <v>79171772386</v>
       </c>
       <c r="C1177" s="31"/>
       <c r="D1177" s="31" t="s">
-        <v>2288</v>
+        <v>2278</v>
       </c>
       <c r="E1177" s="31"/>
       <c r="F1177" s="31"/>
@@ -30742,14 +30769,14 @@
     </row>
     <row r="1178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1178" s="32" t="s">
-        <v>2744</v>
+        <v>2734</v>
       </c>
       <c r="B1178" s="31">
         <v>79515365516</v>
       </c>
       <c r="C1178" s="31"/>
       <c r="D1178" s="31" t="s">
-        <v>2287</v>
+        <v>2277</v>
       </c>
       <c r="E1178" s="31"/>
       <c r="F1178" s="31"/>
@@ -30758,14 +30785,14 @@
     </row>
     <row r="1179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1179" s="32" t="s">
-        <v>2745</v>
+        <v>2735</v>
       </c>
       <c r="B1179" s="31">
         <v>79186559582</v>
       </c>
       <c r="C1179" s="31"/>
       <c r="D1179" s="31" t="s">
-        <v>2287</v>
+        <v>2277</v>
       </c>
       <c r="E1179" s="31"/>
       <c r="F1179" s="31"/>
@@ -30774,7 +30801,7 @@
     </row>
     <row r="1180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1180" s="32" t="s">
-        <v>2746</v>
+        <v>2736</v>
       </c>
       <c r="B1180" s="31">
         <v>79180300643</v>
@@ -30782,7 +30809,7 @@
       <c r="C1180" s="31"/>
       <c r="D1180" s="31"/>
       <c r="E1180" s="31" t="s">
-        <v>2297</v>
+        <v>2287</v>
       </c>
       <c r="F1180" s="31" t="s">
         <v>1953</v>
@@ -30804,13 +30831,13 @@
     </row>
     <row r="1182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1182" s="32" t="s">
-        <v>2747</v>
+        <v>2737</v>
       </c>
       <c r="B1182" s="31">
         <v>79081882253</v>
       </c>
       <c r="C1182" s="31" t="s">
-        <v>2282</v>
+        <v>2272</v>
       </c>
       <c r="D1182" s="31"/>
       <c r="E1182" s="31"/>
@@ -30820,13 +30847,13 @@
     </row>
     <row r="1183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1183" s="32" t="s">
-        <v>2748</v>
+        <v>2738</v>
       </c>
       <c r="B1183" s="31">
         <v>79184570319</v>
       </c>
       <c r="C1183" s="31" t="s">
-        <v>2282</v>
+        <v>2272</v>
       </c>
       <c r="D1183" s="31"/>
       <c r="E1183" s="31"/>
@@ -30848,13 +30875,13 @@
     </row>
     <row r="1185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1185" s="32" t="s">
-        <v>2749</v>
+        <v>2739</v>
       </c>
       <c r="B1185" s="31">
         <v>79884600699</v>
       </c>
       <c r="C1185" s="31" t="s">
-        <v>2283</v>
+        <v>2273</v>
       </c>
       <c r="D1185" s="31"/>
       <c r="E1185" s="31"/>
@@ -30864,13 +30891,13 @@
     </row>
     <row r="1186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1186" s="32" t="s">
-        <v>2750</v>
+        <v>2740</v>
       </c>
       <c r="B1186" s="31">
         <v>79615933002</v>
       </c>
       <c r="C1186" s="31" t="s">
-        <v>2283</v>
+        <v>2273</v>
       </c>
       <c r="D1186" s="31"/>
       <c r="E1186" s="31"/>
@@ -30880,13 +30907,13 @@
     </row>
     <row r="1187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1187" s="32" t="s">
-        <v>2751</v>
+        <v>2741</v>
       </c>
       <c r="B1187" s="31">
         <v>79287615615</v>
       </c>
       <c r="C1187" s="31" t="s">
-        <v>2283</v>
+        <v>2273</v>
       </c>
       <c r="D1187" s="31"/>
       <c r="E1187" s="31"/>
@@ -30908,17 +30935,17 @@
     </row>
     <row r="1189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1189" s="32" t="s">
-        <v>2752</v>
+        <v>2742</v>
       </c>
       <c r="B1189" s="31">
         <v>79282298724</v>
       </c>
       <c r="C1189" s="31"/>
       <c r="D1189" s="31" t="s">
-        <v>2286</v>
+        <v>2276</v>
       </c>
       <c r="E1189" s="31" t="s">
-        <v>2298</v>
+        <v>2288</v>
       </c>
       <c r="F1189" s="31" t="s">
         <v>1957</v>
@@ -30940,7 +30967,7 @@
     </row>
     <row r="1191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1191" s="32" t="s">
-        <v>2753</v>
+        <v>2743</v>
       </c>
       <c r="B1191" s="31">
         <v>79608204295</v>
@@ -30948,7 +30975,7 @@
       <c r="C1191" s="31"/>
       <c r="D1191" s="31"/>
       <c r="E1191" s="31" t="s">
-        <v>2299</v>
+        <v>2289</v>
       </c>
       <c r="F1191" s="31" t="s">
         <v>1958</v>
@@ -30958,7 +30985,7 @@
     </row>
     <row r="1192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1192" s="32" t="s">
-        <v>2754</v>
+        <v>2744</v>
       </c>
       <c r="B1192" s="31">
         <v>79064969201</v>
@@ -30966,7 +30993,7 @@
       <c r="C1192" s="31"/>
       <c r="D1192" s="31"/>
       <c r="E1192" s="31" t="s">
-        <v>2299</v>
+        <v>2289</v>
       </c>
       <c r="F1192" s="31" t="s">
         <v>1959</v>
@@ -31008,7 +31035,7 @@
     </row>
     <row r="1195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1195" s="32" t="s">
-        <v>2755</v>
+        <v>2745</v>
       </c>
       <c r="B1195" s="31">
         <v>79883604002</v>
@@ -31016,7 +31043,7 @@
       <c r="C1195" s="31"/>
       <c r="D1195" s="31"/>
       <c r="E1195" s="31" t="s">
-        <v>2300</v>
+        <v>2290</v>
       </c>
       <c r="F1195" s="31"/>
       <c r="G1195" s="31"/>
@@ -31024,7 +31051,7 @@
     </row>
     <row r="1196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1196" s="32" t="s">
-        <v>2756</v>
+        <v>2746</v>
       </c>
       <c r="B1196" s="31">
         <v>79384102024</v>
@@ -31032,7 +31059,7 @@
       <c r="C1196" s="31"/>
       <c r="D1196" s="31"/>
       <c r="E1196" s="31" t="s">
-        <v>2300</v>
+        <v>2290</v>
       </c>
       <c r="F1196" s="31"/>
       <c r="G1196" s="31"/>
@@ -31052,14 +31079,14 @@
     </row>
     <row r="1198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1198" s="32" t="s">
-        <v>2757</v>
+        <v>2747</v>
       </c>
       <c r="B1198" s="31">
         <v>79898514111</v>
       </c>
       <c r="C1198" s="31"/>
       <c r="D1198" s="31" t="s">
-        <v>2285</v>
+        <v>2275</v>
       </c>
       <c r="E1198" s="31"/>
       <c r="F1198" s="31"/>
@@ -31068,17 +31095,17 @@
     </row>
     <row r="1199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1199" s="32" t="s">
-        <v>2758</v>
+        <v>2748</v>
       </c>
       <c r="B1199" s="31">
         <v>79374645805</v>
       </c>
       <c r="C1199" s="31" t="s">
-        <v>2284</v>
+        <v>2274</v>
       </c>
       <c r="D1199" s="31"/>
       <c r="E1199" s="31" t="s">
-        <v>2301</v>
+        <v>2291</v>
       </c>
       <c r="F1199" s="31" t="s">
         <v>1962</v>
@@ -31088,7 +31115,7 @@
     </row>
     <row r="1200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1200" s="32" t="s">
-        <v>2759</v>
+        <v>2749</v>
       </c>
       <c r="B1200" s="31">
         <v>79892931818</v>
@@ -31096,7 +31123,7 @@
       <c r="C1200" s="31"/>
       <c r="D1200" s="31"/>
       <c r="E1200" s="31" t="s">
-        <v>2301</v>
+        <v>2291</v>
       </c>
       <c r="F1200" s="31" t="s">
         <v>1962</v>
@@ -31118,7 +31145,7 @@
     </row>
     <row r="1202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1202" s="32" t="s">
-        <v>2760</v>
+        <v>2750</v>
       </c>
       <c r="B1202" s="31">
         <v>79504617288</v>
@@ -31126,7 +31153,7 @@
       <c r="C1202" s="31"/>
       <c r="D1202" s="31"/>
       <c r="E1202" s="31" t="s">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="F1202" s="31" t="s">
         <v>2038</v>
@@ -31136,16 +31163,16 @@
     </row>
     <row r="1203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1203" s="32" t="s">
-        <v>2761</v>
+        <v>2751</v>
       </c>
       <c r="B1203" s="31">
         <v>79085129986</v>
       </c>
       <c r="C1203" s="31" t="s">
-        <v>2402</v>
+        <v>2392</v>
       </c>
       <c r="D1203" s="31" t="s">
-        <v>2409</v>
+        <v>2399</v>
       </c>
       <c r="E1203" s="31"/>
       <c r="F1203" s="31"/>
@@ -31166,14 +31193,14 @@
     </row>
     <row r="1205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1205" s="32" t="s">
-        <v>2762</v>
+        <v>2752</v>
       </c>
       <c r="B1205" s="31">
         <v>79913567286</v>
       </c>
       <c r="C1205" s="31"/>
       <c r="D1205" s="31" t="s">
-        <v>2408</v>
+        <v>2398</v>
       </c>
       <c r="E1205" s="31"/>
       <c r="F1205" s="31"/>
@@ -31182,13 +31209,13 @@
     </row>
     <row r="1206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1206" s="32" t="s">
-        <v>2763</v>
+        <v>2753</v>
       </c>
       <c r="B1206" s="31">
         <v>79185010806</v>
       </c>
       <c r="C1206" s="31" t="s">
-        <v>2403</v>
+        <v>2393</v>
       </c>
       <c r="D1206" s="31"/>
       <c r="E1206" s="31"/>
@@ -31198,13 +31225,13 @@
     </row>
     <row r="1207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1207" s="32" t="s">
-        <v>2764</v>
+        <v>2754</v>
       </c>
       <c r="B1207" s="31">
         <v>79183185307</v>
       </c>
       <c r="C1207" s="31" t="s">
-        <v>2403</v>
+        <v>2393</v>
       </c>
       <c r="D1207" s="31"/>
       <c r="E1207" s="31"/>
@@ -31226,13 +31253,13 @@
     </row>
     <row r="1209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1209" s="32" t="s">
-        <v>2765</v>
+        <v>2755</v>
       </c>
       <c r="B1209" s="31">
         <v>79266566385</v>
       </c>
       <c r="C1209" s="31" t="s">
-        <v>2404</v>
+        <v>2394</v>
       </c>
       <c r="D1209" s="31"/>
       <c r="E1209" s="31"/>
@@ -31274,7 +31301,7 @@
     </row>
     <row r="1212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1212" s="32" t="s">
-        <v>2766</v>
+        <v>2756</v>
       </c>
       <c r="B1212" s="31">
         <v>79284341070</v>
@@ -31282,7 +31309,7 @@
       <c r="C1212" s="31"/>
       <c r="D1212" s="31"/>
       <c r="E1212" s="31" t="s">
-        <v>2411</v>
+        <v>2401</v>
       </c>
       <c r="F1212" s="31" t="s">
         <v>2077</v>
@@ -31292,7 +31319,7 @@
     </row>
     <row r="1213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1213" s="32" t="s">
-        <v>2767</v>
+        <v>2757</v>
       </c>
       <c r="B1213" s="31">
         <v>79267958573</v>
@@ -31300,7 +31327,7 @@
       <c r="C1213" s="31"/>
       <c r="D1213" s="31"/>
       <c r="E1213" s="31" t="s">
-        <v>2411</v>
+        <v>2401</v>
       </c>
       <c r="F1213" s="31" t="s">
         <v>2078</v>
@@ -31310,14 +31337,14 @@
     </row>
     <row r="1214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1214" s="32" t="s">
-        <v>2768</v>
+        <v>2758</v>
       </c>
       <c r="B1214" s="31">
         <v>79282480877</v>
       </c>
       <c r="C1214" s="31"/>
       <c r="D1214" s="31" t="s">
-        <v>2407</v>
+        <v>2397</v>
       </c>
       <c r="E1214" s="31"/>
       <c r="F1214" s="31"/>
@@ -31358,7 +31385,7 @@
     </row>
     <row r="1217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1217" s="32" t="s">
-        <v>2769</v>
+        <v>2759</v>
       </c>
       <c r="B1217" s="31">
         <v>79181763655</v>
@@ -31366,7 +31393,7 @@
       <c r="C1217" s="31"/>
       <c r="D1217" s="31"/>
       <c r="E1217" s="31" t="s">
-        <v>2412</v>
+        <v>2402</v>
       </c>
       <c r="F1217" s="31" t="s">
         <v>2083</v>
@@ -31388,7 +31415,7 @@
     </row>
     <row r="1219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1219" s="32" t="s">
-        <v>2770</v>
+        <v>2760</v>
       </c>
       <c r="B1219" s="31">
         <v>79184256275</v>
@@ -31396,7 +31423,7 @@
       <c r="C1219" s="31"/>
       <c r="D1219" s="31"/>
       <c r="E1219" s="31" t="s">
-        <v>2413</v>
+        <v>2403</v>
       </c>
       <c r="F1219" s="31" t="s">
         <v>2084</v>
@@ -31406,16 +31433,16 @@
     </row>
     <row r="1220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1220" s="32" t="s">
-        <v>2771</v>
+        <v>2761</v>
       </c>
       <c r="B1220" s="31">
         <v>79883151515</v>
       </c>
       <c r="C1220" s="31" t="s">
-        <v>2405</v>
+        <v>2395</v>
       </c>
       <c r="D1220" s="31" t="s">
-        <v>2406</v>
+        <v>2396</v>
       </c>
       <c r="E1220" s="31"/>
       <c r="F1220" s="31"/>
@@ -31456,7 +31483,7 @@
     </row>
     <row r="1223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1223" s="32" t="s">
-        <v>2856</v>
+        <v>2846</v>
       </c>
       <c r="B1223" s="31">
         <v>79281186882</v>
@@ -31488,13 +31515,13 @@
     </row>
     <row r="1225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1225" s="32" t="s">
-        <v>2857</v>
+        <v>2847</v>
       </c>
       <c r="B1225" s="31">
         <v>79034547400</v>
       </c>
       <c r="C1225" s="31" t="s">
-        <v>2494</v>
+        <v>2484</v>
       </c>
       <c r="D1225" s="31"/>
       <c r="E1225" s="31"/>
@@ -31504,13 +31531,13 @@
     </row>
     <row r="1226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1226" s="32" t="s">
-        <v>2858</v>
+        <v>2848</v>
       </c>
       <c r="B1226" s="31">
         <v>79287721255</v>
       </c>
       <c r="C1226" s="31" t="s">
-        <v>2494</v>
+        <v>2484</v>
       </c>
       <c r="D1226" s="31"/>
       <c r="E1226" s="31"/>
@@ -31552,16 +31579,16 @@
     </row>
     <row r="1229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1229" s="32" t="s">
-        <v>2859</v>
+        <v>2849</v>
       </c>
       <c r="B1229" s="31">
         <v>79183615308</v>
       </c>
       <c r="C1229" s="31" t="s">
-        <v>2495</v>
+        <v>2485</v>
       </c>
       <c r="D1229" s="31" t="s">
-        <v>2504</v>
+        <v>2494</v>
       </c>
       <c r="E1229" s="31"/>
       <c r="F1229" s="31"/>
@@ -31570,19 +31597,19 @@
     </row>
     <row r="1230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1230" s="32" t="s">
-        <v>2860</v>
+        <v>2850</v>
       </c>
       <c r="B1230" s="31">
         <v>79186212666</v>
       </c>
       <c r="C1230" s="31" t="s">
+        <v>2485</v>
+      </c>
+      <c r="D1230" s="31" t="s">
+        <v>2493</v>
+      </c>
+      <c r="E1230" s="31" t="s">
         <v>2495</v>
-      </c>
-      <c r="D1230" s="31" t="s">
-        <v>2503</v>
-      </c>
-      <c r="E1230" s="31" t="s">
-        <v>2505</v>
       </c>
       <c r="F1230" s="31" t="s">
         <v>2168</v>
@@ -31592,14 +31619,14 @@
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1231" s="32" t="s">
-        <v>2861</v>
+        <v>2851</v>
       </c>
       <c r="B1231" s="31">
         <v>79951882337</v>
       </c>
       <c r="C1231" s="31"/>
       <c r="D1231" s="31" t="s">
-        <v>2502</v>
+        <v>2492</v>
       </c>
       <c r="E1231" s="31"/>
       <c r="F1231" s="31"/>
@@ -31608,7 +31635,7 @@
     </row>
     <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1232" s="32" t="s">
-        <v>2862</v>
+        <v>2852</v>
       </c>
       <c r="B1232" s="31">
         <v>79002796431</v>
@@ -31616,7 +31643,7 @@
       <c r="C1232" s="31"/>
       <c r="D1232" s="31"/>
       <c r="E1232" s="31" t="s">
-        <v>2505</v>
+        <v>2495</v>
       </c>
       <c r="F1232" s="31" t="s">
         <v>2169</v>
@@ -31626,13 +31653,13 @@
     </row>
     <row r="1233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1233" s="32" t="s">
-        <v>2863</v>
+        <v>2853</v>
       </c>
       <c r="B1233" s="31">
         <v>79384126478</v>
       </c>
       <c r="C1233" s="31" t="s">
-        <v>2495</v>
+        <v>2485</v>
       </c>
       <c r="D1233" s="31"/>
       <c r="E1233" s="31"/>
@@ -31654,19 +31681,19 @@
     </row>
     <row r="1235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1235" s="18" t="s">
-        <v>2864</v>
+        <v>2854</v>
       </c>
       <c r="B1235" s="19">
         <v>79184673083</v>
       </c>
       <c r="C1235" s="19" t="s">
-        <v>2514</v>
+        <v>2504</v>
       </c>
       <c r="D1235" s="19" t="s">
-        <v>2515</v>
+        <v>2505</v>
       </c>
       <c r="E1235" s="19" t="s">
-        <v>2516</v>
+        <v>2506</v>
       </c>
       <c r="F1235" s="19" t="s">
         <v>2171</v>
@@ -31676,19 +31703,19 @@
     </row>
     <row r="1236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1236" s="32" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B1236" s="31">
         <v>79184987541</v>
       </c>
       <c r="C1236" s="31" t="s">
-        <v>2496</v>
+        <v>2486</v>
       </c>
       <c r="D1236" s="31" t="s">
-        <v>2501</v>
+        <v>2491</v>
       </c>
       <c r="E1236" s="31" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="F1236" s="31"/>
       <c r="G1236" s="31"/>
@@ -31703,10 +31730,10 @@
       </c>
       <c r="C1237" s="31"/>
       <c r="D1237" s="31" t="s">
-        <v>2500</v>
+        <v>2490</v>
       </c>
       <c r="E1237" s="31" t="s">
-        <v>2506</v>
+        <v>2496</v>
       </c>
       <c r="F1237" s="31" t="s">
         <v>2170</v>
@@ -31716,13 +31743,13 @@
     </row>
     <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1238" s="32" t="s">
-        <v>2865</v>
+        <v>2855</v>
       </c>
       <c r="B1238" s="31">
         <v>79180458777</v>
       </c>
       <c r="C1238" s="33" t="s">
-        <v>2496</v>
+        <v>2486</v>
       </c>
       <c r="D1238" s="31"/>
       <c r="E1238" s="31"/>
@@ -31744,16 +31771,16 @@
     </row>
     <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1240" s="32" t="s">
-        <v>2866</v>
+        <v>2856</v>
       </c>
       <c r="B1240" s="31">
         <v>79183291413</v>
       </c>
       <c r="C1240" s="31" t="s">
-        <v>2497</v>
+        <v>2487</v>
       </c>
       <c r="D1240" s="31" t="s">
-        <v>2499</v>
+        <v>2489</v>
       </c>
       <c r="E1240" s="31"/>
       <c r="F1240" s="31"/>
@@ -31762,7 +31789,7 @@
     </row>
     <row r="1241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1241" s="32" t="s">
-        <v>2867</v>
+        <v>2857</v>
       </c>
       <c r="B1241" s="31">
         <v>79882371168</v>
@@ -31770,7 +31797,7 @@
       <c r="C1241" s="31"/>
       <c r="D1241" s="31"/>
       <c r="E1241" s="31" t="s">
-        <v>2507</v>
+        <v>2497</v>
       </c>
       <c r="F1241" s="31" t="s">
         <v>2172</v>
@@ -31780,14 +31807,14 @@
     </row>
     <row r="1242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1242" s="32" t="s">
-        <v>2868</v>
+        <v>2858</v>
       </c>
       <c r="B1242" s="31">
         <v>79885577597</v>
       </c>
       <c r="C1242" s="31"/>
       <c r="D1242" s="31" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
       <c r="E1242" s="31"/>
       <c r="F1242" s="31"/>
@@ -31796,12 +31823,12 @@
     </row>
     <row r="1243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1243" s="32" t="s">
-        <v>2869</v>
+        <v>2859</v>
       </c>
       <c r="B1243" s="33"/>
       <c r="C1243" s="31"/>
       <c r="D1243" s="31" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
       <c r="E1243" s="31"/>
       <c r="F1243" s="31"/>
@@ -31842,16 +31869,16 @@
     </row>
     <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1246" s="32" t="s">
-        <v>2878</v>
+        <v>2868</v>
       </c>
       <c r="B1246" s="33">
         <v>79802319741</v>
       </c>
       <c r="C1246" s="31" t="s">
-        <v>2537</v>
+        <v>2527</v>
       </c>
       <c r="D1246" s="31" t="s">
-        <v>2545</v>
+        <v>2535</v>
       </c>
       <c r="E1246" s="31"/>
       <c r="F1246" s="31"/>
@@ -31860,7 +31887,7 @@
     </row>
     <row r="1247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1247" s="32" t="s">
-        <v>2879</v>
+        <v>2869</v>
       </c>
       <c r="B1247" s="33">
         <v>79298260798</v>
@@ -31868,24 +31895,24 @@
       <c r="C1247" s="31"/>
       <c r="D1247" s="31"/>
       <c r="E1247" s="31" t="s">
-        <v>2546</v>
+        <v>2536</v>
       </c>
       <c r="F1247" s="31" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="G1247" s="31"/>
       <c r="H1247" s="3"/>
     </row>
     <row r="1248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1248" s="32" t="s">
-        <v>2880</v>
+        <v>2870</v>
       </c>
       <c r="B1248" s="33">
         <v>79615901223</v>
       </c>
       <c r="C1248" s="31"/>
       <c r="D1248" s="31" t="s">
-        <v>2544</v>
+        <v>2534</v>
       </c>
       <c r="E1248" s="31"/>
       <c r="F1248" s="31"/>
@@ -31894,7 +31921,7 @@
     </row>
     <row r="1249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1249" s="32" t="s">
-        <v>2881</v>
+        <v>2871</v>
       </c>
       <c r="B1249" s="33">
         <v>79183331040</v>
@@ -31902,7 +31929,7 @@
       <c r="C1249" s="31"/>
       <c r="D1249" s="31"/>
       <c r="E1249" s="31" t="s">
-        <v>2546</v>
+        <v>2536</v>
       </c>
       <c r="F1249" s="31" t="s">
         <v>2179</v>
@@ -31912,17 +31939,17 @@
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1250" s="32" t="s">
-        <v>2882</v>
+        <v>2872</v>
       </c>
       <c r="B1250" s="33">
         <v>79064077747</v>
       </c>
       <c r="C1250" s="31" t="s">
-        <v>2537</v>
+        <v>2527</v>
       </c>
       <c r="D1250" s="31"/>
       <c r="E1250" s="31" t="s">
-        <v>2546</v>
+        <v>2536</v>
       </c>
       <c r="F1250" s="31" t="s">
         <v>2179</v>
@@ -31944,19 +31971,19 @@
     </row>
     <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1252" s="32" t="s">
-        <v>2883</v>
+        <v>2873</v>
       </c>
       <c r="B1252" s="33">
         <v>79181978847</v>
       </c>
       <c r="C1252" s="31" t="s">
-        <v>2728</v>
+        <v>2718</v>
       </c>
       <c r="D1252" s="31" t="s">
-        <v>2543</v>
+        <v>2533</v>
       </c>
       <c r="E1252" s="31" t="s">
-        <v>2547</v>
+        <v>2537</v>
       </c>
       <c r="F1252" s="31" t="s">
         <v>2180</v>
@@ -31966,16 +31993,16 @@
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1253" s="32" t="s">
-        <v>2884</v>
+        <v>2874</v>
       </c>
       <c r="B1253" s="33">
         <v>79183346962</v>
       </c>
       <c r="C1253" s="31" t="s">
-        <v>2538</v>
+        <v>2528</v>
       </c>
       <c r="D1253" s="31" t="s">
-        <v>2542</v>
+        <v>2532</v>
       </c>
       <c r="E1253" s="31"/>
       <c r="F1253" s="31"/>
@@ -31996,14 +32023,14 @@
     </row>
     <row r="1255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1255" s="32" t="s">
-        <v>2885</v>
+        <v>2875</v>
       </c>
       <c r="B1255" s="33">
         <v>79518493781</v>
       </c>
       <c r="C1255" s="31"/>
       <c r="D1255" s="31" t="s">
-        <v>2541</v>
+        <v>2531</v>
       </c>
       <c r="E1255" s="31"/>
       <c r="F1255" s="31"/>
@@ -32012,14 +32039,14 @@
     </row>
     <row r="1256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1256" s="32" t="s">
-        <v>2886</v>
+        <v>2876</v>
       </c>
       <c r="B1256" s="33">
         <v>79180651355</v>
       </c>
       <c r="C1256" s="31"/>
       <c r="D1256" s="31" t="s">
-        <v>2540</v>
+        <v>2530</v>
       </c>
       <c r="E1256" s="31"/>
       <c r="F1256" s="31"/>
@@ -32028,13 +32055,13 @@
     </row>
     <row r="1257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1257" s="32" t="s">
-        <v>2887</v>
+        <v>2877</v>
       </c>
       <c r="B1257" s="33">
         <v>79281140670</v>
       </c>
       <c r="C1257" s="31" t="s">
-        <v>2539</v>
+        <v>2529</v>
       </c>
       <c r="D1257" s="31"/>
       <c r="E1257" s="31"/>
@@ -32056,14 +32083,14 @@
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1259" s="32" t="s">
-        <v>2888</v>
+        <v>2878</v>
       </c>
       <c r="B1259" s="33">
         <v>79200671177</v>
       </c>
       <c r="C1259" s="31"/>
       <c r="D1259" s="31" t="s">
-        <v>2570</v>
+        <v>2560</v>
       </c>
       <c r="E1259" s="31"/>
       <c r="F1259" s="31"/>
@@ -32072,7 +32099,7 @@
     </row>
     <row r="1260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1260" s="32" t="s">
-        <v>2889</v>
+        <v>2879</v>
       </c>
       <c r="B1260" s="33">
         <v>79186201442</v>
@@ -32080,10 +32107,10 @@
       <c r="C1260" s="31"/>
       <c r="D1260" s="31"/>
       <c r="E1260" s="31" t="s">
-        <v>2571</v>
+        <v>2561</v>
       </c>
       <c r="F1260" s="31" t="s">
-        <v>2573</v>
+        <v>2563</v>
       </c>
       <c r="G1260" s="31"/>
       <c r="H1260" s="3"/>
@@ -32102,13 +32129,13 @@
     </row>
     <row r="1262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1262" s="32" t="s">
-        <v>2890</v>
+        <v>2880</v>
       </c>
       <c r="B1262" s="33">
         <v>79183108008</v>
       </c>
       <c r="C1262" s="31" t="s">
-        <v>2568</v>
+        <v>2558</v>
       </c>
       <c r="D1262" s="31"/>
       <c r="E1262" s="31"/>
@@ -32118,295 +32145,295 @@
     </row>
     <row r="1263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1263" s="32" t="s">
-        <v>2891</v>
+        <v>2881</v>
       </c>
       <c r="B1263" s="33">
         <v>79097178862</v>
       </c>
       <c r="C1263" s="31" t="s">
-        <v>2568</v>
+        <v>2558</v>
       </c>
       <c r="D1263" s="31"/>
       <c r="E1263" s="31" t="s">
-        <v>2572</v>
+        <v>2562</v>
       </c>
       <c r="F1263" s="31" t="s">
-        <v>2574</v>
+        <v>2564</v>
       </c>
       <c r="G1263" s="31"/>
       <c r="H1263" s="3"/>
     </row>
     <row r="1264" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1264" s="6" t="s">
+      <c r="A1264" s="32" t="s">
         <v>2206</v>
       </c>
-      <c r="B1264" s="17"/>
-      <c r="C1264" s="3"/>
-      <c r="D1264" s="3"/>
-      <c r="E1264" s="3"/>
-      <c r="F1264" s="3"/>
-      <c r="G1264" s="3"/>
+      <c r="B1264" s="33"/>
+      <c r="C1264" s="31"/>
+      <c r="D1264" s="31"/>
+      <c r="E1264" s="31"/>
+      <c r="F1264" s="31"/>
+      <c r="G1264" s="31"/>
       <c r="H1264" s="3"/>
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1265" s="6" t="s">
-        <v>2207</v>
-      </c>
-      <c r="B1265" s="17">
+      <c r="A1265" s="32" t="s">
+        <v>2947</v>
+      </c>
+      <c r="B1265" s="33">
         <v>79787819232</v>
       </c>
-      <c r="C1265" s="3" t="s">
-        <v>2569</v>
-      </c>
-      <c r="D1265" s="3"/>
-      <c r="E1265" s="3"/>
-      <c r="F1265" s="3"/>
-      <c r="G1265" s="3"/>
+      <c r="C1265" s="31" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D1265" s="31"/>
+      <c r="E1265" s="31"/>
+      <c r="F1265" s="31"/>
+      <c r="G1265" s="31"/>
       <c r="H1265" s="3"/>
     </row>
     <row r="1266" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1266" s="6"/>
-      <c r="B1266" s="17"/>
-      <c r="C1266" s="3" t="s">
+      <c r="A1266" s="32"/>
+      <c r="B1266" s="33"/>
+      <c r="C1266" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D1266" s="3" t="s">
+      <c r="D1266" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E1266" s="3" t="s">
+      <c r="E1266" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F1266" s="3" t="s">
+      <c r="F1266" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="G1266" s="3"/>
+      <c r="G1266" s="31"/>
       <c r="H1266" s="3"/>
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1267" s="6" t="s">
+      <c r="A1267" s="32" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B1267" s="33"/>
+      <c r="C1267" s="31"/>
+      <c r="D1267" s="31"/>
+      <c r="E1267" s="31"/>
+      <c r="F1267" s="31"/>
+      <c r="G1267" s="31"/>
+      <c r="H1267" s="3"/>
+    </row>
+    <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1268" s="32" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B1268" s="33">
+        <v>79181206771</v>
+      </c>
+      <c r="C1268" s="31" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D1268" s="31" t="s">
+        <v>2617</v>
+      </c>
+      <c r="E1268" s="31" t="s">
+        <v>2618</v>
+      </c>
+      <c r="F1268" s="31" t="s">
         <v>2264</v>
       </c>
-      <c r="B1267" s="17"/>
-      <c r="C1267" s="3"/>
-      <c r="D1267" s="3"/>
-      <c r="E1267" s="3"/>
-      <c r="F1267" s="3"/>
-      <c r="G1267" s="3"/>
-      <c r="H1267" s="3"/>
-    </row>
-    <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1268" s="6" t="s">
+      <c r="G1268" s="31"/>
+      <c r="H1268" s="3"/>
+    </row>
+    <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1269" s="32" t="s">
+        <v>2949</v>
+      </c>
+      <c r="B1269" s="33">
+        <v>79286136662</v>
+      </c>
+      <c r="C1269" s="31"/>
+      <c r="D1269" s="31" t="s">
+        <v>2616</v>
+      </c>
+      <c r="E1269" s="31"/>
+      <c r="F1269" s="31"/>
+      <c r="G1269" s="31"/>
+      <c r="H1269" s="3"/>
+    </row>
+    <row r="1270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1270" s="32" t="s">
         <v>2265</v>
       </c>
-      <c r="B1268" s="17">
-        <v>79181206771</v>
-      </c>
-      <c r="C1268" s="3" t="s">
-        <v>2620</v>
-      </c>
-      <c r="D1268" s="3" t="s">
-        <v>2627</v>
-      </c>
-      <c r="E1268" s="3" t="s">
-        <v>2628</v>
-      </c>
-      <c r="F1268" s="3" t="s">
+      <c r="B1270" s="33"/>
+      <c r="C1270" s="31"/>
+      <c r="D1270" s="31"/>
+      <c r="E1270" s="31"/>
+      <c r="F1270" s="31"/>
+      <c r="G1270" s="31"/>
+      <c r="H1270" s="3"/>
+    </row>
+    <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1271" s="18" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B1271" s="39">
+        <v>375297856891</v>
+      </c>
+      <c r="C1271" s="19"/>
+      <c r="D1271" s="19" t="s">
+        <v>2701</v>
+      </c>
+      <c r="E1271" s="19"/>
+      <c r="F1271" s="19"/>
+      <c r="G1271" s="19"/>
+      <c r="H1271" s="5"/>
+    </row>
+    <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1272" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1272" s="33">
+        <v>79787715371</v>
+      </c>
+      <c r="C1272" s="31" t="s">
+        <v>2611</v>
+      </c>
+      <c r="D1272" s="31" t="s">
+        <v>2615</v>
+      </c>
+      <c r="E1272" s="31"/>
+      <c r="F1272" s="31"/>
+      <c r="G1272" s="31"/>
+      <c r="H1272" s="3"/>
+    </row>
+    <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1273" s="32" t="s">
+        <v>2951</v>
+      </c>
+      <c r="B1273" s="33">
+        <v>79189218545</v>
+      </c>
+      <c r="C1273" s="31"/>
+      <c r="D1273" s="31" t="s">
+        <v>2614</v>
+      </c>
+      <c r="E1273" s="31"/>
+      <c r="F1273" s="31"/>
+      <c r="G1273" s="31"/>
+      <c r="H1273" s="3"/>
+    </row>
+    <row r="1274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1274" s="32" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B1274" s="33"/>
+      <c r="C1274" s="31"/>
+      <c r="D1274" s="31"/>
+      <c r="E1274" s="31"/>
+      <c r="F1274" s="31"/>
+      <c r="G1274" s="31"/>
+      <c r="H1274" s="3"/>
+    </row>
+    <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1275" s="18" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B1275" s="39">
+        <v>79883302117</v>
+      </c>
+      <c r="C1275" s="19" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D1275" s="19" t="s">
+        <v>2829</v>
+      </c>
+      <c r="E1275" s="19"/>
+      <c r="F1275" s="19"/>
+      <c r="G1275" s="19"/>
+      <c r="H1275" s="5"/>
+    </row>
+    <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1276" s="32" t="s">
+        <v>2953</v>
+      </c>
+      <c r="B1276" s="33">
+        <v>79885414599</v>
+      </c>
+      <c r="C1276" s="31" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D1276" s="31"/>
+      <c r="E1276" s="31"/>
+      <c r="F1276" s="31"/>
+      <c r="G1276" s="31"/>
+      <c r="H1276" s="3"/>
+    </row>
+    <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1277" s="32" t="s">
+        <v>2954</v>
+      </c>
+      <c r="B1277" s="33">
+        <v>79606987172</v>
+      </c>
+      <c r="C1277" s="31"/>
+      <c r="D1277" s="31"/>
+      <c r="E1277" s="31" t="s">
+        <v>2619</v>
+      </c>
+      <c r="F1277" s="31" t="s">
+        <v>2268</v>
+      </c>
+      <c r="G1277" s="31"/>
+      <c r="H1277" s="3"/>
+    </row>
+    <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1278" s="32" t="s">
         <v>2267</v>
       </c>
-      <c r="G1268" s="3"/>
-      <c r="H1268" s="3"/>
-    </row>
-    <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1269" s="6" t="s">
-        <v>2266</v>
-      </c>
-      <c r="B1269" s="17">
-        <v>79286136662</v>
-      </c>
-      <c r="C1269" s="3"/>
-      <c r="D1269" s="3" t="s">
-        <v>2626</v>
-      </c>
-      <c r="E1269" s="3"/>
-      <c r="F1269" s="3"/>
-      <c r="G1269" s="3"/>
-      <c r="H1269" s="3"/>
-    </row>
-    <row r="1270" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1270" s="6" t="s">
-        <v>2271</v>
-      </c>
-      <c r="B1270" s="17"/>
-      <c r="C1270" s="3"/>
-      <c r="D1270" s="3"/>
-      <c r="E1270" s="3"/>
-      <c r="F1270" s="3"/>
-      <c r="G1270" s="3"/>
-      <c r="H1270" s="3"/>
-    </row>
-    <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1271" s="8" t="s">
-        <v>2268</v>
-      </c>
-      <c r="B1271" s="42">
-        <v>375297856891</v>
-      </c>
-      <c r="C1271" s="5"/>
-      <c r="D1271" s="5" t="s">
-        <v>2711</v>
-      </c>
-      <c r="E1271" s="5"/>
-      <c r="F1271" s="5"/>
-      <c r="G1271" s="5"/>
-      <c r="H1271" s="5"/>
-    </row>
-    <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1272" s="6" t="s">
-        <v>2269</v>
-      </c>
-      <c r="B1272" s="17">
-        <v>79787715371</v>
-      </c>
-      <c r="C1272" s="3" t="s">
-        <v>2621</v>
-      </c>
-      <c r="D1272" s="3" t="s">
-        <v>2625</v>
-      </c>
-      <c r="E1272" s="3"/>
-      <c r="F1272" s="3"/>
-      <c r="G1272" s="3"/>
-      <c r="H1272" s="3"/>
-    </row>
-    <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1273" s="6" t="s">
-        <v>2270</v>
-      </c>
-      <c r="B1273" s="17">
-        <v>79189218545</v>
-      </c>
-      <c r="C1273" s="3"/>
-      <c r="D1273" s="3" t="s">
-        <v>2624</v>
-      </c>
-      <c r="E1273" s="3"/>
-      <c r="F1273" s="3"/>
-      <c r="G1273" s="3"/>
-      <c r="H1273" s="3"/>
-    </row>
-    <row r="1274" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1274" s="6" t="s">
-        <v>2272</v>
-      </c>
-      <c r="B1274" s="17"/>
-      <c r="C1274" s="3"/>
-      <c r="D1274" s="3"/>
-      <c r="E1274" s="3"/>
-      <c r="F1274" s="3"/>
-      <c r="G1274" s="3"/>
-      <c r="H1274" s="3"/>
-    </row>
-    <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1275" s="8" t="s">
-        <v>2273</v>
-      </c>
-      <c r="B1275" s="42">
-        <v>79883302117</v>
-      </c>
-      <c r="C1275" s="5" t="s">
-        <v>2838</v>
-      </c>
-      <c r="D1275" s="5" t="s">
-        <v>2839</v>
-      </c>
-      <c r="E1275" s="5"/>
-      <c r="F1275" s="5"/>
-      <c r="G1275" s="5"/>
-      <c r="H1275" s="5"/>
-    </row>
-    <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1276" s="6" t="s">
-        <v>2274</v>
-      </c>
-      <c r="B1276" s="17">
-        <v>79885414599</v>
-      </c>
-      <c r="C1276" s="3" t="s">
-        <v>2622</v>
-      </c>
-      <c r="D1276" s="3"/>
-      <c r="E1276" s="3"/>
-      <c r="F1276" s="3"/>
-      <c r="G1276" s="3"/>
-      <c r="H1276" s="3"/>
-    </row>
-    <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1277" s="6" t="s">
-        <v>2275</v>
-      </c>
-      <c r="B1277" s="17">
-        <v>79606987172</v>
-      </c>
-      <c r="C1277" s="3"/>
-      <c r="D1277" s="3"/>
-      <c r="E1277" s="3" t="s">
-        <v>2629</v>
-      </c>
-      <c r="F1277" s="3" t="s">
-        <v>2278</v>
-      </c>
-      <c r="G1277" s="3"/>
-      <c r="H1277" s="3"/>
-    </row>
-    <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1278" s="6" t="s">
-        <v>2277</v>
-      </c>
-      <c r="B1278" s="17"/>
-      <c r="C1278" s="3"/>
-      <c r="D1278" s="3"/>
-      <c r="E1278" s="3"/>
-      <c r="F1278" s="3"/>
-      <c r="G1278" s="3"/>
+      <c r="B1278" s="33"/>
+      <c r="C1278" s="31"/>
+      <c r="D1278" s="31"/>
+      <c r="E1278" s="31"/>
+      <c r="F1278" s="31"/>
+      <c r="G1278" s="31"/>
       <c r="H1278" s="3"/>
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1279" s="6" t="s">
-        <v>2276</v>
-      </c>
-      <c r="B1279" s="17">
+      <c r="A1279" s="32" t="s">
+        <v>2955</v>
+      </c>
+      <c r="B1279" s="33">
         <v>79002702201</v>
       </c>
-      <c r="C1279" s="3" t="s">
-        <v>2623</v>
-      </c>
-      <c r="D1279" s="3"/>
-      <c r="E1279" s="3"/>
-      <c r="F1279" s="3"/>
-      <c r="G1279" s="3"/>
+      <c r="C1279" s="31" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D1279" s="31"/>
+      <c r="E1279" s="31"/>
+      <c r="F1279" s="31"/>
+      <c r="G1279" s="31"/>
       <c r="H1279" s="3"/>
     </row>
     <row r="1280" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1280" s="6"/>
-      <c r="B1280" s="17"/>
-      <c r="C1280" s="3" t="s">
+      <c r="A1280" s="32"/>
+      <c r="B1280" s="33"/>
+      <c r="C1280" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D1280" s="3" t="s">
+      <c r="D1280" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E1280" s="3" t="s">
+      <c r="E1280" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F1280" s="3" t="s">
+      <c r="F1280" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="G1280" s="3"/>
+      <c r="G1280" s="31"/>
       <c r="H1280" s="3"/>
     </row>
     <row r="1281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1281" s="6" t="s">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B1281" s="17"/>
       <c r="C1281" s="3"/>
@@ -32418,13 +32445,13 @@
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1282" s="6" t="s">
-        <v>2341</v>
+        <v>2331</v>
       </c>
       <c r="B1282" s="17">
         <v>79036910787</v>
       </c>
       <c r="C1282" s="3" t="s">
-        <v>2689</v>
+        <v>2679</v>
       </c>
       <c r="D1282" s="3"/>
       <c r="E1282" s="3"/>
@@ -32434,58 +32461,58 @@
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1283" s="6" t="s">
-        <v>2342</v>
+        <v>2332</v>
       </c>
       <c r="B1283" s="17">
         <v>79085097827</v>
       </c>
       <c r="C1283" s="3" t="s">
-        <v>2689</v>
+        <v>2679</v>
       </c>
       <c r="D1283" s="3" t="s">
-        <v>2706</v>
+        <v>2696</v>
       </c>
       <c r="E1283" s="3" t="s">
-        <v>2707</v>
+        <v>2697</v>
       </c>
       <c r="F1283" s="3" t="s">
-        <v>2358</v>
+        <v>2348</v>
       </c>
       <c r="G1283" s="3"/>
       <c r="H1283" s="3"/>
     </row>
     <row r="1284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1284" s="6" t="s">
-        <v>2343</v>
+        <v>2333</v>
       </c>
       <c r="B1284" s="17">
         <v>79786456031</v>
       </c>
       <c r="C1284" s="3" t="s">
-        <v>2689</v>
+        <v>2679</v>
       </c>
       <c r="D1284" s="3" t="s">
-        <v>2705</v>
+        <v>2695</v>
       </c>
       <c r="E1284" s="3" t="s">
-        <v>2707</v>
+        <v>2697</v>
       </c>
       <c r="F1284" s="3" t="s">
-        <v>2359</v>
+        <v>2349</v>
       </c>
       <c r="G1284" s="3"/>
       <c r="H1284" s="3"/>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1285" s="6" t="s">
-        <v>2344</v>
+        <v>2334</v>
       </c>
       <c r="B1285" s="17">
         <v>79180492172</v>
       </c>
       <c r="C1285" s="3"/>
       <c r="D1285" s="3" t="s">
-        <v>2705</v>
+        <v>2695</v>
       </c>
       <c r="E1285" s="3"/>
       <c r="F1285" s="3"/>
@@ -32494,7 +32521,7 @@
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1286" s="6" t="s">
-        <v>2345</v>
+        <v>2335</v>
       </c>
       <c r="B1286" s="17"/>
       <c r="C1286" s="3"/>
@@ -32506,7 +32533,7 @@
     </row>
     <row r="1287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1287" s="6" t="s">
-        <v>2346</v>
+        <v>2336</v>
       </c>
       <c r="B1287" s="17">
         <v>79530708343</v>
@@ -32514,26 +32541,26 @@
       <c r="C1287" s="3"/>
       <c r="D1287" s="3"/>
       <c r="E1287" s="3" t="s">
-        <v>2708</v>
+        <v>2698</v>
       </c>
       <c r="F1287" s="3" t="s">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="G1287" s="3"/>
       <c r="H1287" s="3"/>
     </row>
     <row r="1288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1288" s="6" t="s">
-        <v>2347</v>
+        <v>2337</v>
       </c>
       <c r="B1288" s="17">
         <v>79618588262</v>
       </c>
       <c r="C1288" s="3" t="s">
-        <v>2690</v>
+        <v>2680</v>
       </c>
       <c r="D1288" s="3" t="s">
-        <v>2704</v>
+        <v>2694</v>
       </c>
       <c r="E1288" s="3"/>
       <c r="F1288" s="3"/>
@@ -32542,7 +32569,7 @@
     </row>
     <row r="1289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1289" s="6" t="s">
-        <v>2348</v>
+        <v>2338</v>
       </c>
       <c r="B1289" s="17">
         <v>79990580869</v>
@@ -32550,17 +32577,17 @@
       <c r="C1289" s="3"/>
       <c r="D1289" s="3"/>
       <c r="E1289" s="3" t="s">
-        <v>2708</v>
+        <v>2698</v>
       </c>
       <c r="F1289" s="3" t="s">
-        <v>2361</v>
+        <v>2351</v>
       </c>
       <c r="G1289" s="3"/>
       <c r="H1289" s="3"/>
     </row>
     <row r="1290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1290" s="6" t="s">
-        <v>2349</v>
+        <v>2339</v>
       </c>
       <c r="B1290" s="17">
         <v>79283306686</v>
@@ -32568,23 +32595,23 @@
       <c r="C1290" s="3"/>
       <c r="D1290" s="3"/>
       <c r="E1290" s="3" t="s">
-        <v>2708</v>
+        <v>2698</v>
       </c>
       <c r="F1290" s="3" t="s">
-        <v>2361</v>
+        <v>2351</v>
       </c>
       <c r="G1290" s="3"/>
       <c r="H1290" s="3"/>
     </row>
     <row r="1291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1291" s="6" t="s">
-        <v>2350</v>
+        <v>2340</v>
       </c>
       <c r="B1291" s="17">
         <v>79184803174</v>
       </c>
       <c r="C1291" s="3" t="s">
-        <v>2690</v>
+        <v>2680</v>
       </c>
       <c r="D1291" s="3"/>
       <c r="E1291" s="3"/>
@@ -32594,13 +32621,13 @@
     </row>
     <row r="1292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1292" s="6" t="s">
-        <v>2351</v>
+        <v>2341</v>
       </c>
       <c r="B1292" s="17">
         <v>79186825836</v>
       </c>
       <c r="C1292" s="3" t="s">
-        <v>2690</v>
+        <v>2680</v>
       </c>
       <c r="D1292" s="3"/>
       <c r="E1292" s="3"/>
@@ -32610,13 +32637,13 @@
     </row>
     <row r="1293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1293" s="6" t="s">
-        <v>2352</v>
+        <v>2342</v>
       </c>
       <c r="B1293" s="17">
         <v>79182466940</v>
       </c>
       <c r="C1293" s="3" t="s">
-        <v>2690</v>
+        <v>2680</v>
       </c>
       <c r="D1293" s="3"/>
       <c r="E1293" s="3"/>
@@ -32626,7 +32653,7 @@
     </row>
     <row r="1294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1294" s="6" t="s">
-        <v>2354</v>
+        <v>2344</v>
       </c>
       <c r="B1294" s="17"/>
       <c r="C1294" s="3"/>
@@ -32638,16 +32665,16 @@
     </row>
     <row r="1295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1295" s="6" t="s">
-        <v>2353</v>
+        <v>2343</v>
       </c>
       <c r="B1295" s="17">
         <v>79149202703</v>
       </c>
       <c r="C1295" s="3" t="s">
-        <v>2691</v>
+        <v>2681</v>
       </c>
       <c r="D1295" s="3" t="s">
-        <v>2703</v>
+        <v>2693</v>
       </c>
       <c r="E1295" s="3"/>
       <c r="F1295" s="3"/>
@@ -32656,27 +32683,27 @@
     </row>
     <row r="1296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1296" s="6" t="s">
-        <v>2355</v>
+        <v>2345</v>
       </c>
       <c r="B1296" s="17">
         <v>79885468941</v>
       </c>
       <c r="C1296" s="3" t="s">
-        <v>2691</v>
+        <v>2681</v>
       </c>
       <c r="D1296" s="3"/>
       <c r="E1296" s="3" t="s">
-        <v>2709</v>
+        <v>2699</v>
       </c>
       <c r="F1296" s="3" t="s">
-        <v>2362</v>
+        <v>2352</v>
       </c>
       <c r="G1296" s="3"/>
       <c r="H1296" s="28"/>
     </row>
     <row r="1297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1297" s="6" t="s">
-        <v>2356</v>
+        <v>2346</v>
       </c>
       <c r="B1297" s="17"/>
       <c r="C1297" s="3"/>
@@ -32688,16 +32715,16 @@
     </row>
     <row r="1298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1298" s="6" t="s">
-        <v>2357</v>
+        <v>2347</v>
       </c>
       <c r="B1298" s="17">
         <v>79806633494</v>
       </c>
       <c r="C1298" s="3" t="s">
+        <v>2682</v>
+      </c>
+      <c r="D1298" s="3" t="s">
         <v>2692</v>
-      </c>
-      <c r="D1298" s="3" t="s">
-        <v>2702</v>
       </c>
       <c r="E1298" s="3"/>
       <c r="F1298" s="3"/>
@@ -32724,7 +32751,7 @@
     </row>
     <row r="1300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1300" s="6" t="s">
-        <v>2363</v>
+        <v>2353</v>
       </c>
       <c r="B1300" s="17"/>
       <c r="C1300" s="3"/>
@@ -32736,13 +32763,13 @@
     </row>
     <row r="1301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1301" s="6" t="s">
-        <v>2364</v>
+        <v>2354</v>
       </c>
       <c r="B1301" s="17">
         <v>79525837593</v>
       </c>
       <c r="C1301" s="3" t="s">
-        <v>2693</v>
+        <v>2683</v>
       </c>
       <c r="D1301" s="3"/>
       <c r="E1301" s="3"/>
@@ -32752,16 +32779,16 @@
     </row>
     <row r="1302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1302" s="6" t="s">
-        <v>2365</v>
+        <v>2355</v>
       </c>
       <c r="B1302" s="17">
         <v>79183870112</v>
       </c>
       <c r="C1302" s="3" t="s">
-        <v>2693</v>
+        <v>2683</v>
       </c>
       <c r="D1302" s="3" t="s">
-        <v>2701</v>
+        <v>2691</v>
       </c>
       <c r="E1302" s="3"/>
       <c r="F1302" s="3"/>
@@ -32770,14 +32797,14 @@
     </row>
     <row r="1303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1303" s="6" t="s">
-        <v>2366</v>
+        <v>2356</v>
       </c>
       <c r="B1303" s="17">
         <v>79182842938</v>
       </c>
       <c r="C1303" s="3"/>
       <c r="D1303" s="3" t="s">
-        <v>2700</v>
+        <v>2690</v>
       </c>
       <c r="E1303" s="3"/>
       <c r="F1303" s="3"/>
@@ -32786,7 +32813,7 @@
     </row>
     <row r="1304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1304" s="6" t="s">
-        <v>2367</v>
+        <v>2357</v>
       </c>
       <c r="B1304" s="17"/>
       <c r="C1304" s="3"/>
@@ -32798,29 +32825,29 @@
     </row>
     <row r="1305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1305" s="6" t="s">
-        <v>2368</v>
+        <v>2358</v>
       </c>
       <c r="B1305" s="17">
         <v>79183772137</v>
       </c>
       <c r="C1305" s="3" t="s">
-        <v>2694</v>
+        <v>2684</v>
       </c>
       <c r="D1305" s="3" t="s">
-        <v>2699</v>
+        <v>2689</v>
       </c>
       <c r="E1305" s="3" t="s">
-        <v>2710</v>
+        <v>2700</v>
       </c>
       <c r="F1305" s="3" t="s">
-        <v>2376</v>
+        <v>2366</v>
       </c>
       <c r="G1305" s="3"/>
       <c r="H1305" s="28"/>
     </row>
     <row r="1306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1306" s="6" t="s">
-        <v>2369</v>
+        <v>2359</v>
       </c>
       <c r="B1306" s="17">
         <v>79897201133</v>
@@ -32828,24 +32855,24 @@
       <c r="C1306" s="3"/>
       <c r="D1306" s="3"/>
       <c r="E1306" s="3" t="s">
-        <v>2710</v>
+        <v>2700</v>
       </c>
       <c r="F1306" s="3" t="s">
-        <v>2377</v>
+        <v>2367</v>
       </c>
       <c r="G1306" s="3"/>
       <c r="H1306" s="28"/>
     </row>
     <row r="1307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1307" s="6" t="s">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B1307" s="17">
         <v>79615332857</v>
       </c>
       <c r="C1307" s="3"/>
       <c r="D1307" s="3" t="s">
-        <v>2698</v>
+        <v>2688</v>
       </c>
       <c r="E1307" s="3"/>
       <c r="F1307" s="3"/>
@@ -32854,14 +32881,14 @@
     </row>
     <row r="1308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1308" s="6" t="s">
-        <v>2371</v>
+        <v>2361</v>
       </c>
       <c r="B1308" s="17">
         <v>79184188755</v>
       </c>
       <c r="C1308" s="3"/>
       <c r="D1308" s="3" t="s">
-        <v>2698</v>
+        <v>2688</v>
       </c>
       <c r="E1308" s="3"/>
       <c r="F1308" s="3"/>
@@ -32870,7 +32897,7 @@
     </row>
     <row r="1309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1309" s="6" t="s">
-        <v>2372</v>
+        <v>2362</v>
       </c>
       <c r="B1309" s="17"/>
       <c r="C1309" s="3"/>
@@ -32882,14 +32909,14 @@
     </row>
     <row r="1310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1310" s="6" t="s">
-        <v>2373</v>
+        <v>2363</v>
       </c>
       <c r="B1310" s="17">
         <v>79034550320</v>
       </c>
       <c r="C1310" s="3"/>
       <c r="D1310" s="3" t="s">
-        <v>2697</v>
+        <v>2687</v>
       </c>
       <c r="E1310" s="3"/>
       <c r="F1310" s="3"/>
@@ -32898,13 +32925,13 @@
     </row>
     <row r="1311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1311" s="6" t="s">
-        <v>2374</v>
+        <v>2364</v>
       </c>
       <c r="B1311" s="17">
         <v>79497336125</v>
       </c>
       <c r="C1311" s="3" t="s">
-        <v>2695</v>
+        <v>2685</v>
       </c>
       <c r="D1311" s="3"/>
       <c r="E1311" s="3"/>
@@ -32914,14 +32941,14 @@
     </row>
     <row r="1312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1312" s="6" t="s">
-        <v>2375</v>
+        <v>2365</v>
       </c>
       <c r="B1312" s="17">
         <v>79676739173</v>
       </c>
       <c r="C1312" s="3"/>
       <c r="D1312" s="3" t="s">
-        <v>2696</v>
+        <v>2686</v>
       </c>
       <c r="E1312" s="3"/>
       <c r="F1312" s="3"/>
@@ -32947,7 +32974,7 @@
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1314" s="6" t="s">
-        <v>2378</v>
+        <v>2368</v>
       </c>
       <c r="B1314" s="17"/>
       <c r="C1314" s="3"/>
@@ -32958,26 +32985,26 @@
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1315" s="6" t="s">
-        <v>2379</v>
+        <v>2369</v>
       </c>
       <c r="B1315" s="17">
         <v>79183767815</v>
       </c>
       <c r="C1315" s="3"/>
       <c r="D1315" s="3" t="s">
-        <v>2789</v>
+        <v>2779</v>
       </c>
       <c r="E1315" s="3" t="s">
-        <v>2790</v>
+        <v>2780</v>
       </c>
       <c r="F1315" s="3" t="s">
-        <v>2388</v>
+        <v>2378</v>
       </c>
       <c r="G1315" s="2"/>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1316" s="6" t="s">
-        <v>2383</v>
+        <v>2373</v>
       </c>
       <c r="B1316" s="28"/>
       <c r="C1316" s="3"/>
@@ -32988,13 +33015,13 @@
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1317" s="6" t="s">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B1317" s="17">
         <v>79528700394</v>
       </c>
       <c r="C1317" s="3" t="s">
-        <v>2772</v>
+        <v>2762</v>
       </c>
       <c r="D1317" s="3"/>
       <c r="E1317" s="3"/>
@@ -33003,13 +33030,13 @@
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1318" s="6" t="s">
-        <v>2381</v>
+        <v>2371</v>
       </c>
       <c r="B1318" s="17">
         <v>79054305403</v>
       </c>
       <c r="C1318" s="3" t="s">
-        <v>2772</v>
+        <v>2762</v>
       </c>
       <c r="D1318" s="3"/>
       <c r="E1318" s="3"/>
@@ -33018,14 +33045,14 @@
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1319" s="6" t="s">
-        <v>2382</v>
+        <v>2372</v>
       </c>
       <c r="B1319" s="17">
         <v>79064046088</v>
       </c>
       <c r="C1319" s="3"/>
       <c r="D1319" s="3" t="s">
-        <v>2788</v>
+        <v>2778</v>
       </c>
       <c r="E1319" s="3"/>
       <c r="F1319" s="3"/>
@@ -33033,16 +33060,16 @@
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1320" s="6" t="s">
-        <v>2384</v>
+        <v>2374</v>
       </c>
       <c r="B1320" s="17">
         <v>79284483258</v>
       </c>
       <c r="C1320" s="3" t="s">
-        <v>2772</v>
+        <v>2762</v>
       </c>
       <c r="D1320" s="3" t="s">
-        <v>2788</v>
+        <v>2778</v>
       </c>
       <c r="E1320" s="3"/>
       <c r="F1320" s="3"/>
@@ -33050,7 +33077,7 @@
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1321" s="6" t="s">
-        <v>2385</v>
+        <v>2375</v>
       </c>
       <c r="B1321" s="17"/>
       <c r="C1321" s="3"/>
@@ -33061,13 +33088,13 @@
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1322" s="6" t="s">
-        <v>2386</v>
+        <v>2376</v>
       </c>
       <c r="B1322" s="28">
         <v>79081817570</v>
       </c>
       <c r="C1322" s="17" t="s">
-        <v>2773</v>
+        <v>2763</v>
       </c>
       <c r="D1322" s="3"/>
       <c r="E1322" s="3"/>
@@ -33076,7 +33103,7 @@
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1323" s="6" t="s">
-        <v>2387</v>
+        <v>2377</v>
       </c>
       <c r="B1323" s="28">
         <v>79045033313</v>
@@ -33084,16 +33111,16 @@
       <c r="C1323" s="28"/>
       <c r="D1323" s="3"/>
       <c r="E1323" s="3" t="s">
-        <v>2791</v>
+        <v>2781</v>
       </c>
       <c r="F1323" s="3" t="s">
-        <v>2389</v>
+        <v>2379</v>
       </c>
       <c r="G1323" s="2"/>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1324" s="6" t="s">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B1324" s="28"/>
       <c r="C1324" s="28"/>
@@ -33104,52 +33131,52 @@
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1325" s="6" t="s">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="B1325" s="17">
         <v>79186195666</v>
       </c>
       <c r="C1325" s="3" t="s">
-        <v>2923</v>
+        <v>2913</v>
       </c>
       <c r="D1325" s="3"/>
       <c r="E1325" s="3" t="s">
-        <v>2924</v>
+        <v>2914</v>
       </c>
       <c r="F1325" s="3" t="s">
-        <v>2489</v>
+        <v>2479</v>
       </c>
       <c r="G1325" s="2"/>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1326" s="6" t="s">
-        <v>2392</v>
+        <v>2382</v>
       </c>
       <c r="B1326" s="17">
         <v>79780648554</v>
       </c>
       <c r="C1326" s="3"/>
       <c r="D1326" s="3" t="s">
-        <v>2787</v>
+        <v>2777</v>
       </c>
       <c r="E1326" s="3" t="s">
-        <v>2792</v>
+        <v>2782</v>
       </c>
       <c r="F1326" s="3" t="s">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="G1326" s="2"/>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1327" s="6" t="s">
-        <v>2393</v>
+        <v>2383</v>
       </c>
       <c r="B1327" s="17">
         <v>79493022752</v>
       </c>
       <c r="C1327" s="3"/>
       <c r="D1327" s="3" t="s">
-        <v>2787</v>
+        <v>2777</v>
       </c>
       <c r="E1327" s="3"/>
       <c r="F1327" s="3"/>
@@ -33157,7 +33184,7 @@
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1328" s="6" t="s">
-        <v>2394</v>
+        <v>2384</v>
       </c>
       <c r="B1328" s="17"/>
       <c r="C1328" s="3"/>
@@ -33168,7 +33195,7 @@
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1329" s="6" t="s">
-        <v>2395</v>
+        <v>2385</v>
       </c>
       <c r="B1329" s="17">
         <v>79085033991</v>
@@ -33181,14 +33208,14 @@
     </row>
     <row r="1330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1330" s="6" t="s">
-        <v>2396</v>
+        <v>2386</v>
       </c>
       <c r="B1330" s="17">
         <v>79282576368</v>
       </c>
       <c r="C1330" s="3"/>
       <c r="D1330" s="3" t="s">
-        <v>2786</v>
+        <v>2776</v>
       </c>
       <c r="E1330" s="3"/>
       <c r="F1330" s="3"/>
@@ -33196,7 +33223,7 @@
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1331" s="6" t="s">
-        <v>2397</v>
+        <v>2387</v>
       </c>
       <c r="B1331" s="17"/>
       <c r="C1331" s="3"/>
@@ -33207,13 +33234,13 @@
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1332" s="6" t="s">
-        <v>2398</v>
+        <v>2388</v>
       </c>
       <c r="B1332" s="17">
         <v>79054871997</v>
       </c>
       <c r="C1332" s="3" t="s">
-        <v>2774</v>
+        <v>2764</v>
       </c>
       <c r="D1332" s="3"/>
       <c r="E1332" s="3"/>
@@ -33222,14 +33249,14 @@
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1333" s="6" t="s">
-        <v>2399</v>
+        <v>2389</v>
       </c>
       <c r="B1333" s="17">
         <v>79193683714</v>
       </c>
       <c r="C1333" s="3"/>
       <c r="D1333" s="3" t="s">
-        <v>2785</v>
+        <v>2775</v>
       </c>
       <c r="E1333" s="3"/>
       <c r="F1333" s="3"/>
@@ -33237,14 +33264,14 @@
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1334" s="6" t="s">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B1334" s="17">
         <v>79586493944</v>
       </c>
       <c r="C1334" s="3"/>
       <c r="D1334" s="3" t="s">
-        <v>2784</v>
+        <v>2774</v>
       </c>
       <c r="E1334" s="3"/>
       <c r="F1334" s="3"/>
@@ -33252,13 +33279,13 @@
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1335" s="6" t="s">
-        <v>2401</v>
+        <v>2391</v>
       </c>
       <c r="B1335" s="17">
         <v>79780045546</v>
       </c>
       <c r="C1335" s="3" t="s">
-        <v>2774</v>
+        <v>2764</v>
       </c>
       <c r="D1335" s="3"/>
       <c r="E1335" s="3"/>
@@ -33284,7 +33311,7 @@
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1337" s="6" t="s">
-        <v>2508</v>
+        <v>2498</v>
       </c>
       <c r="B1337" s="17"/>
       <c r="C1337" s="3"/>
@@ -33295,16 +33322,16 @@
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1338" s="8" t="s">
-        <v>2509</v>
+        <v>2499</v>
       </c>
       <c r="B1338" s="42">
         <v>79782640332</v>
       </c>
       <c r="C1338" s="5" t="s">
-        <v>2836</v>
+        <v>2826</v>
       </c>
       <c r="D1338" s="5" t="s">
-        <v>2837</v>
+        <v>2827</v>
       </c>
       <c r="E1338" s="5"/>
       <c r="F1338" s="5"/>
@@ -33312,7 +33339,7 @@
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1339" s="6" t="s">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="B1339" s="17"/>
       <c r="C1339" s="3"/>
@@ -33323,16 +33350,16 @@
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1340" s="6" t="s">
-        <v>2511</v>
+        <v>2501</v>
       </c>
       <c r="B1340" s="17">
         <v>79530977713</v>
       </c>
       <c r="C1340" s="3" t="s">
-        <v>2775</v>
+        <v>2765</v>
       </c>
       <c r="D1340" s="3" t="s">
-        <v>2783</v>
+        <v>2773</v>
       </c>
       <c r="E1340" s="3"/>
       <c r="F1340" s="3"/>
@@ -33340,14 +33367,14 @@
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1341" s="6" t="s">
-        <v>2512</v>
+        <v>2502</v>
       </c>
       <c r="B1341" s="17">
         <v>79896279922</v>
       </c>
       <c r="C1341" s="3"/>
       <c r="D1341" s="3" t="s">
-        <v>2782</v>
+        <v>2772</v>
       </c>
       <c r="E1341" s="3"/>
       <c r="F1341" s="3"/>
@@ -33355,7 +33382,7 @@
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1342" s="8" t="s">
-        <v>2513</v>
+        <v>2503</v>
       </c>
       <c r="B1342" s="42">
         <v>79064327871</v>
@@ -33387,7 +33414,7 @@
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1344" s="6" t="s">
-        <v>2520</v>
+        <v>2510</v>
       </c>
       <c r="B1344" s="17"/>
       <c r="C1344" s="3"/>
@@ -33398,7 +33425,7 @@
     </row>
     <row r="1345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1345" s="6" t="s">
-        <v>2517</v>
+        <v>2507</v>
       </c>
       <c r="B1345" s="17">
         <v>79184743700</v>
@@ -33406,23 +33433,23 @@
       <c r="C1345" s="3"/>
       <c r="D1345" s="3"/>
       <c r="E1345" s="3" t="s">
-        <v>2793</v>
+        <v>2783</v>
       </c>
       <c r="F1345" s="3" t="s">
-        <v>2550</v>
+        <v>2540</v>
       </c>
       <c r="G1345" s="2"/>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1346" s="6" t="s">
-        <v>2518</v>
+        <v>2508</v>
       </c>
       <c r="B1346" s="17">
         <v>79186353503</v>
       </c>
       <c r="C1346" s="3"/>
       <c r="D1346" s="3" t="s">
-        <v>2781</v>
+        <v>2771</v>
       </c>
       <c r="E1346" s="3"/>
       <c r="F1346" s="3"/>
@@ -33430,70 +33457,70 @@
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1347" s="6" t="s">
-        <v>2519</v>
+        <v>2509</v>
       </c>
       <c r="B1347" s="17">
         <v>79676684446</v>
       </c>
       <c r="C1347" s="3" t="s">
-        <v>2523</v>
+        <v>2513</v>
       </c>
       <c r="D1347" s="3" t="s">
-        <v>2780</v>
+        <v>2770</v>
       </c>
       <c r="E1347" s="3" t="s">
-        <v>2551</v>
+        <v>2541</v>
       </c>
       <c r="F1347" s="3" t="s">
-        <v>2548</v>
+        <v>2538</v>
       </c>
       <c r="G1347" s="2"/>
     </row>
     <row r="1348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1348" s="6" t="s">
-        <v>2521</v>
+        <v>2511</v>
       </c>
       <c r="B1348" s="17">
         <v>79183887841</v>
       </c>
       <c r="C1348" s="3" t="s">
-        <v>2776</v>
+        <v>2766</v>
       </c>
       <c r="D1348" s="3" t="s">
-        <v>2780</v>
+        <v>2770</v>
       </c>
       <c r="E1348" s="3" t="s">
-        <v>2551</v>
+        <v>2541</v>
       </c>
       <c r="F1348" s="3" t="s">
-        <v>2548</v>
+        <v>2538</v>
       </c>
       <c r="G1348" s="2"/>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1349" s="6" t="s">
-        <v>2522</v>
+        <v>2512</v>
       </c>
       <c r="B1349" s="17">
         <v>79198880562</v>
       </c>
       <c r="C1349" s="3" t="s">
-        <v>2776</v>
+        <v>2766</v>
       </c>
       <c r="D1349" s="3" t="s">
-        <v>2780</v>
+        <v>2770</v>
       </c>
       <c r="E1349" s="3" t="s">
-        <v>2793</v>
+        <v>2783</v>
       </c>
       <c r="F1349" s="3" t="s">
-        <v>2549</v>
+        <v>2539</v>
       </c>
       <c r="G1349" s="2"/>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1350" s="6" t="s">
-        <v>2524</v>
+        <v>2514</v>
       </c>
       <c r="B1350" s="17"/>
       <c r="C1350" s="3"/>
@@ -33504,16 +33531,16 @@
     </row>
     <row r="1351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1351" s="6" t="s">
-        <v>2525</v>
+        <v>2515</v>
       </c>
       <c r="B1351" s="17">
         <v>79882440037</v>
       </c>
       <c r="C1351" s="3" t="s">
-        <v>2777</v>
+        <v>2767</v>
       </c>
       <c r="D1351" s="3" t="s">
-        <v>2779</v>
+        <v>2769</v>
       </c>
       <c r="E1351" s="3"/>
       <c r="F1351" s="3"/>
@@ -33521,16 +33548,16 @@
     </row>
     <row r="1352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1352" s="6" t="s">
-        <v>2526</v>
+        <v>2516</v>
       </c>
       <c r="B1352" s="17">
         <v>79187698925</v>
       </c>
       <c r="C1352" s="3" t="s">
-        <v>2777</v>
+        <v>2767</v>
       </c>
       <c r="D1352" s="3" t="s">
-        <v>2778</v>
+        <v>2768</v>
       </c>
       <c r="E1352" s="3"/>
       <c r="F1352" s="3"/>
@@ -33538,7 +33565,7 @@
     </row>
     <row r="1353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1353" s="6" t="s">
-        <v>2552</v>
+        <v>2542</v>
       </c>
       <c r="B1353" s="17"/>
       <c r="C1353" s="3"/>
@@ -33549,13 +33576,13 @@
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1354" s="6" t="s">
-        <v>2553</v>
+        <v>2543</v>
       </c>
       <c r="B1354" s="17">
         <v>79189831000</v>
       </c>
       <c r="C1354" s="3" t="s">
-        <v>2840</v>
+        <v>2830</v>
       </c>
       <c r="D1354" s="3"/>
       <c r="E1354" s="3"/>
@@ -33564,7 +33591,7 @@
     </row>
     <row r="1355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1355" s="6" t="s">
-        <v>2554</v>
+        <v>2544</v>
       </c>
       <c r="B1355" s="17"/>
       <c r="C1355" s="3"/>
@@ -33575,7 +33602,7 @@
     </row>
     <row r="1356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1356" s="6" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="B1356" s="17">
         <v>79787158378</v>
@@ -33583,10 +33610,10 @@
       <c r="C1356" s="3"/>
       <c r="D1356" s="3"/>
       <c r="E1356" s="3" t="s">
-        <v>2851</v>
+        <v>2841</v>
       </c>
       <c r="F1356" s="3" t="s">
-        <v>2556</v>
+        <v>2546</v>
       </c>
       <c r="G1356" s="2"/>
     </row>
@@ -33609,7 +33636,7 @@
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1358" s="6" t="s">
-        <v>2557</v>
+        <v>2547</v>
       </c>
       <c r="B1358" s="17"/>
       <c r="C1358" s="3"/>
@@ -33620,16 +33647,16 @@
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1359" s="6" t="s">
-        <v>2558</v>
+        <v>2548</v>
       </c>
       <c r="B1359" s="17">
         <v>79381366868</v>
       </c>
       <c r="C1359" s="3" t="s">
-        <v>2841</v>
+        <v>2831</v>
       </c>
       <c r="D1359" s="3" t="s">
-        <v>2850</v>
+        <v>2840</v>
       </c>
       <c r="E1359" s="3"/>
       <c r="F1359" s="3"/>
@@ -33637,28 +33664,28 @@
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1360" s="6" t="s">
-        <v>2559</v>
+        <v>2549</v>
       </c>
       <c r="B1360" s="17">
         <v>79636924737</v>
       </c>
       <c r="C1360" s="3" t="s">
-        <v>2841</v>
+        <v>2831</v>
       </c>
       <c r="D1360" s="3" t="s">
-        <v>2850</v>
+        <v>2840</v>
       </c>
       <c r="E1360" s="3" t="s">
-        <v>2852</v>
+        <v>2842</v>
       </c>
       <c r="F1360" s="3" t="s">
-        <v>2565</v>
+        <v>2555</v>
       </c>
       <c r="G1360" s="2"/>
     </row>
     <row r="1361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1361" s="6" t="s">
-        <v>2560</v>
+        <v>2550</v>
       </c>
       <c r="B1361" s="17"/>
       <c r="C1361" s="3"/>
@@ -33669,26 +33696,26 @@
     </row>
     <row r="1362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1362" s="6" t="s">
-        <v>2561</v>
+        <v>2551</v>
       </c>
       <c r="B1362" s="17">
         <v>79265224303</v>
       </c>
       <c r="C1362" s="3" t="s">
-        <v>2842</v>
+        <v>2832</v>
       </c>
       <c r="D1362" s="3"/>
       <c r="E1362" s="3" t="s">
-        <v>2853</v>
+        <v>2843</v>
       </c>
       <c r="F1362" s="3" t="s">
-        <v>2566</v>
+        <v>2556</v>
       </c>
       <c r="G1362" s="2"/>
     </row>
     <row r="1363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1363" s="6" t="s">
-        <v>2562</v>
+        <v>2552</v>
       </c>
       <c r="B1363" s="17"/>
       <c r="C1363" s="3"/>
@@ -33699,16 +33726,16 @@
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1364" s="6" t="s">
-        <v>2563</v>
+        <v>2553</v>
       </c>
       <c r="B1364" s="17">
         <v>79064147502</v>
       </c>
       <c r="C1364" s="3" t="s">
-        <v>2843</v>
+        <v>2833</v>
       </c>
       <c r="D1364" s="3" t="s">
-        <v>2849</v>
+        <v>2839</v>
       </c>
       <c r="E1364" s="3"/>
       <c r="F1364" s="3"/>
@@ -33716,7 +33743,7 @@
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1365" s="6" t="s">
-        <v>2564</v>
+        <v>2554</v>
       </c>
       <c r="B1365" s="17">
         <v>79628802828</v>
@@ -33724,16 +33751,16 @@
       <c r="C1365" s="3"/>
       <c r="D1365" s="3"/>
       <c r="E1365" s="3" t="s">
-        <v>2854</v>
+        <v>2844</v>
       </c>
       <c r="F1365" s="3" t="s">
-        <v>2567</v>
+        <v>2557</v>
       </c>
       <c r="G1365" s="2"/>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1366" s="6" t="s">
-        <v>2614</v>
+        <v>2604</v>
       </c>
       <c r="B1366" s="17"/>
       <c r="C1366" s="3"/>
@@ -33744,13 +33771,13 @@
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1367" s="6" t="s">
-        <v>2615</v>
+        <v>2605</v>
       </c>
       <c r="B1367" s="17">
         <v>79324167398</v>
       </c>
       <c r="C1367" s="3" t="s">
-        <v>2844</v>
+        <v>2834</v>
       </c>
       <c r="D1367" s="3"/>
       <c r="E1367" s="3"/>
@@ -33759,26 +33786,26 @@
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1368" s="6" t="s">
-        <v>2616</v>
+        <v>2606</v>
       </c>
       <c r="B1368" s="17">
         <v>79056181271</v>
       </c>
       <c r="C1368" s="3" t="s">
-        <v>2844</v>
+        <v>2834</v>
       </c>
       <c r="D1368" s="3"/>
       <c r="E1368" s="3" t="s">
-        <v>2855</v>
+        <v>2845</v>
       </c>
       <c r="F1368" s="3" t="s">
-        <v>2617</v>
+        <v>2607</v>
       </c>
       <c r="G1368" s="2"/>
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1369" s="6" t="s">
-        <v>2618</v>
+        <v>2608</v>
       </c>
       <c r="B1369" s="17"/>
       <c r="C1369" s="3"/>
@@ -33789,16 +33816,16 @@
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1370" s="6" t="s">
-        <v>2619</v>
+        <v>2609</v>
       </c>
       <c r="B1370" s="17">
         <v>79276629955</v>
       </c>
       <c r="C1370" s="3" t="s">
-        <v>2845</v>
+        <v>2835</v>
       </c>
       <c r="D1370" s="3" t="s">
-        <v>2848</v>
+        <v>2838</v>
       </c>
       <c r="E1370" s="3"/>
       <c r="F1370" s="3"/>
@@ -33823,7 +33850,7 @@
     </row>
     <row r="1372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1372" s="6" t="s">
-        <v>2658</v>
+        <v>2648</v>
       </c>
       <c r="B1372" s="17"/>
       <c r="C1372" s="3"/>
@@ -33834,16 +33861,16 @@
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1373" s="6" t="s">
-        <v>2659</v>
+        <v>2649</v>
       </c>
       <c r="B1373" s="17">
         <v>79496106569</v>
       </c>
       <c r="C1373" s="3" t="s">
-        <v>2846</v>
+        <v>2836</v>
       </c>
       <c r="D1373" s="3" t="s">
-        <v>2847</v>
+        <v>2837</v>
       </c>
       <c r="E1373" s="3"/>
       <c r="F1373" s="3"/>
@@ -33851,7 +33878,7 @@
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1374" s="6" t="s">
-        <v>2660</v>
+        <v>2650</v>
       </c>
       <c r="B1374" s="17"/>
       <c r="C1374" s="3"/>
@@ -33862,16 +33889,16 @@
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1375" s="6" t="s">
-        <v>2661</v>
+        <v>2651</v>
       </c>
       <c r="B1375" s="17">
         <v>79287390768</v>
       </c>
       <c r="C1375" s="3" t="s">
-        <v>2898</v>
+        <v>2888</v>
       </c>
       <c r="D1375" s="3" t="s">
-        <v>2912</v>
+        <v>2902</v>
       </c>
       <c r="E1375" s="3"/>
       <c r="F1375" s="3"/>
@@ -33879,13 +33906,13 @@
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1376" s="6" t="s">
-        <v>2662</v>
+        <v>2652</v>
       </c>
       <c r="B1376" s="17">
         <v>79085216412</v>
       </c>
       <c r="C1376" s="3" t="s">
-        <v>2898</v>
+        <v>2888</v>
       </c>
       <c r="D1376" s="3"/>
       <c r="E1376" s="3"/>
@@ -33894,7 +33921,7 @@
     </row>
     <row r="1377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1377" s="6" t="s">
-        <v>2663</v>
+        <v>2653</v>
       </c>
       <c r="B1377" s="17"/>
       <c r="C1377" s="3"/>
@@ -33905,20 +33932,20 @@
     </row>
     <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1378" s="6" t="s">
-        <v>2664</v>
+        <v>2654</v>
       </c>
       <c r="B1378" s="17">
         <v>79803218503</v>
       </c>
       <c r="C1378" s="3" t="s">
-        <v>2899</v>
+        <v>2889</v>
       </c>
       <c r="D1378" s="3"/>
       <c r="E1378" s="3" t="s">
-        <v>2913</v>
+        <v>2903</v>
       </c>
       <c r="F1378" s="3" t="s">
-        <v>2665</v>
+        <v>2655</v>
       </c>
       <c r="G1378" s="2"/>
     </row>
@@ -33941,7 +33968,7 @@
     </row>
     <row r="1380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1380" s="6" t="s">
-        <v>2712</v>
+        <v>2702</v>
       </c>
       <c r="B1380" s="17"/>
       <c r="C1380" s="3"/>
@@ -33952,14 +33979,14 @@
     </row>
     <row r="1381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1381" s="6" t="s">
-        <v>2713</v>
+        <v>2703</v>
       </c>
       <c r="B1381" s="17">
         <v>79000072332</v>
       </c>
       <c r="C1381" s="3"/>
       <c r="D1381" s="3" t="s">
-        <v>2911</v>
+        <v>2901</v>
       </c>
       <c r="E1381" s="3"/>
       <c r="F1381" s="3"/>
@@ -33967,16 +33994,16 @@
     </row>
     <row r="1382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1382" s="6" t="s">
-        <v>2714</v>
+        <v>2704</v>
       </c>
       <c r="B1382" s="17">
         <v>79381241749</v>
       </c>
       <c r="C1382" s="3" t="s">
+        <v>2890</v>
+      </c>
+      <c r="D1382" s="3" t="s">
         <v>2900</v>
-      </c>
-      <c r="D1382" s="3" t="s">
-        <v>2910</v>
       </c>
       <c r="E1382" s="3"/>
       <c r="F1382" s="3"/>
@@ -33984,13 +34011,13 @@
     </row>
     <row r="1383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1383" s="6" t="s">
-        <v>2715</v>
+        <v>2705</v>
       </c>
       <c r="B1383" s="17">
         <v>79183931723</v>
       </c>
       <c r="C1383" s="3" t="s">
-        <v>2900</v>
+        <v>2890</v>
       </c>
       <c r="D1383" s="3"/>
       <c r="E1383" s="3"/>
@@ -34000,7 +34027,7 @@
     </row>
     <row r="1384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1384" s="6" t="s">
-        <v>2716</v>
+        <v>2706</v>
       </c>
       <c r="B1384" s="17"/>
       <c r="C1384" s="3"/>
@@ -34012,35 +34039,35 @@
     </row>
     <row r="1385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1385" s="6" t="s">
-        <v>2717</v>
+        <v>2707</v>
       </c>
       <c r="B1385" s="17">
         <v>79895207444</v>
       </c>
       <c r="C1385" s="3" t="s">
-        <v>2900</v>
+        <v>2890</v>
       </c>
       <c r="D1385" s="3" t="s">
-        <v>2909</v>
+        <v>2899</v>
       </c>
       <c r="E1385" s="3" t="s">
-        <v>2914</v>
+        <v>2904</v>
       </c>
       <c r="F1385" s="3" t="s">
-        <v>2727</v>
+        <v>2717</v>
       </c>
       <c r="G1385" s="2"/>
       <c r="H1385" s="2"/>
     </row>
     <row r="1386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1386" s="6" t="s">
-        <v>2718</v>
+        <v>2708</v>
       </c>
       <c r="B1386" s="17">
         <v>79054396611</v>
       </c>
       <c r="C1386" s="3" t="s">
-        <v>2901</v>
+        <v>2891</v>
       </c>
       <c r="D1386" s="3"/>
       <c r="E1386" s="3"/>
@@ -34050,13 +34077,13 @@
     </row>
     <row r="1387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1387" s="6" t="s">
-        <v>2719</v>
+        <v>2709</v>
       </c>
       <c r="B1387" s="17">
         <v>79189914636</v>
       </c>
       <c r="C1387" s="3" t="s">
-        <v>2901</v>
+        <v>2891</v>
       </c>
       <c r="D1387" s="3"/>
       <c r="E1387" s="3"/>
@@ -34066,16 +34093,16 @@
     </row>
     <row r="1388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1388" s="6" t="s">
-        <v>2720</v>
+        <v>2710</v>
       </c>
       <c r="B1388" s="17">
         <v>79281644488</v>
       </c>
       <c r="C1388" s="3" t="s">
-        <v>2901</v>
+        <v>2891</v>
       </c>
       <c r="D1388" s="3" t="s">
-        <v>2908</v>
+        <v>2898</v>
       </c>
       <c r="E1388" s="3"/>
       <c r="F1388" s="3"/>
@@ -34084,7 +34111,7 @@
     </row>
     <row r="1389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1389" s="6" t="s">
-        <v>2721</v>
+        <v>2711</v>
       </c>
       <c r="B1389" s="17"/>
       <c r="C1389" s="3"/>
@@ -34096,14 +34123,14 @@
     </row>
     <row r="1390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1390" s="6" t="s">
-        <v>2722</v>
+        <v>2712</v>
       </c>
       <c r="B1390" s="17">
         <v>79969140482</v>
       </c>
       <c r="C1390" s="3"/>
       <c r="D1390" s="3" t="s">
-        <v>2906</v>
+        <v>2896</v>
       </c>
       <c r="E1390" s="3"/>
       <c r="F1390" s="3"/>
@@ -34112,16 +34139,16 @@
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1391" s="6" t="s">
-        <v>2723</v>
+        <v>2713</v>
       </c>
       <c r="B1391" s="17">
         <v>79034655195</v>
       </c>
       <c r="C1391" s="3" t="s">
-        <v>2902</v>
+        <v>2892</v>
       </c>
       <c r="D1391" s="3" t="s">
-        <v>2906</v>
+        <v>2896</v>
       </c>
       <c r="E1391" s="3"/>
       <c r="F1391" s="3"/>
@@ -34130,13 +34157,13 @@
     </row>
     <row r="1392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1392" s="6" t="s">
-        <v>2724</v>
+        <v>2714</v>
       </c>
       <c r="B1392" s="17">
         <v>79181891524</v>
       </c>
       <c r="C1392" s="3" t="s">
-        <v>2902</v>
+        <v>2892</v>
       </c>
       <c r="D1392" s="3"/>
       <c r="E1392" s="3"/>
@@ -34146,16 +34173,16 @@
     </row>
     <row r="1393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1393" s="6" t="s">
-        <v>2725</v>
+        <v>2715</v>
       </c>
       <c r="B1393" s="17">
         <v>79197527391</v>
       </c>
       <c r="C1393" s="3" t="s">
-        <v>2902</v>
+        <v>2892</v>
       </c>
       <c r="D1393" s="3" t="s">
-        <v>2907</v>
+        <v>2897</v>
       </c>
       <c r="E1393" s="3"/>
       <c r="F1393" s="3"/>
@@ -34164,14 +34191,14 @@
     </row>
     <row r="1394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1394" s="6" t="s">
-        <v>2726</v>
+        <v>2716</v>
       </c>
       <c r="B1394" s="17">
         <v>79032888829</v>
       </c>
       <c r="C1394" s="3"/>
       <c r="D1394" s="3" t="s">
-        <v>2906</v>
+        <v>2896</v>
       </c>
       <c r="E1394" s="3"/>
       <c r="F1394" s="3"/>
@@ -34198,7 +34225,7 @@
     </row>
     <row r="1396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1396" s="6" t="s">
-        <v>2729</v>
+        <v>2719</v>
       </c>
       <c r="B1396" s="17"/>
       <c r="C1396" s="3"/>
@@ -34210,7 +34237,7 @@
     </row>
     <row r="1397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1397" s="6" t="s">
-        <v>2730</v>
+        <v>2720</v>
       </c>
       <c r="B1397" s="17">
         <v>79282292956</v>
@@ -34218,17 +34245,17 @@
       <c r="C1397" s="3"/>
       <c r="D1397" s="3"/>
       <c r="E1397" s="3" t="s">
-        <v>2915</v>
+        <v>2905</v>
       </c>
       <c r="F1397" s="3" t="s">
-        <v>2736</v>
+        <v>2726</v>
       </c>
       <c r="G1397" s="2"/>
       <c r="H1397" s="2"/>
     </row>
     <row r="1398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1398" s="6" t="s">
-        <v>2731</v>
+        <v>2721</v>
       </c>
       <c r="B1398" s="17"/>
       <c r="C1398" s="3"/>
@@ -34240,16 +34267,16 @@
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1399" s="6" t="s">
-        <v>2732</v>
+        <v>2722</v>
       </c>
       <c r="B1399" s="17">
         <v>79892315277</v>
       </c>
       <c r="C1399" s="3" t="s">
-        <v>2903</v>
+        <v>2893</v>
       </c>
       <c r="D1399" s="3" t="s">
-        <v>2905</v>
+        <v>2895</v>
       </c>
       <c r="E1399" s="3"/>
       <c r="F1399" s="3"/>
@@ -34258,27 +34285,27 @@
     </row>
     <row r="1400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1400" s="6" t="s">
-        <v>2733</v>
+        <v>2723</v>
       </c>
       <c r="B1400" s="17">
         <v>79182323366</v>
       </c>
       <c r="C1400" s="3" t="s">
-        <v>2903</v>
+        <v>2893</v>
       </c>
       <c r="D1400" s="3"/>
       <c r="E1400" s="3" t="s">
-        <v>2916</v>
+        <v>2906</v>
       </c>
       <c r="F1400" s="3" t="s">
-        <v>2737</v>
+        <v>2727</v>
       </c>
       <c r="G1400" s="2"/>
       <c r="H1400" s="2"/>
     </row>
     <row r="1401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1401" s="6" t="s">
-        <v>2734</v>
+        <v>2724</v>
       </c>
       <c r="B1401" s="17"/>
       <c r="C1401" s="3"/>
@@ -34290,13 +34317,13 @@
     </row>
     <row r="1402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1402" s="6" t="s">
-        <v>2735</v>
+        <v>2725</v>
       </c>
       <c r="B1402" s="17">
         <v>79937726026</v>
       </c>
       <c r="C1402" s="3" t="s">
-        <v>2904</v>
+        <v>2894</v>
       </c>
       <c r="D1402" s="3"/>
       <c r="E1402" s="3"/>
@@ -34306,7 +34333,7 @@
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1403" s="7" t="s">
-        <v>2738</v>
+        <v>2728</v>
       </c>
       <c r="B1403" s="16"/>
       <c r="C1403" s="2"/>
@@ -34318,16 +34345,16 @@
     </row>
     <row r="1404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1404" s="7" t="s">
-        <v>2739</v>
+        <v>2729</v>
       </c>
       <c r="B1404" s="16">
         <v>79508496243</v>
       </c>
       <c r="C1404" s="2" t="s">
-        <v>2741</v>
+        <v>2731</v>
       </c>
       <c r="D1404" s="2" t="s">
-        <v>2740</v>
+        <v>2730</v>
       </c>
       <c r="E1404" s="2"/>
       <c r="F1404" s="2"/>
@@ -34336,7 +34363,7 @@
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1405" s="37" t="s">
-        <v>2794</v>
+        <v>2784</v>
       </c>
       <c r="B1405" s="16"/>
       <c r="C1405" s="2"/>
@@ -34348,38 +34375,38 @@
     </row>
     <row r="1406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1406" s="7" t="s">
-        <v>2795</v>
+        <v>2785</v>
       </c>
       <c r="B1406" s="16">
         <v>79045010358</v>
       </c>
       <c r="C1406" s="2" t="s">
-        <v>2801</v>
+        <v>2791</v>
       </c>
       <c r="D1406" s="2" t="s">
-        <v>2798</v>
+        <v>2788</v>
       </c>
       <c r="E1406" s="2" t="s">
-        <v>2803</v>
+        <v>2793</v>
       </c>
       <c r="F1406" s="2" t="s">
-        <v>2802</v>
+        <v>2792</v>
       </c>
       <c r="G1406" s="2" t="s">
-        <v>2800</v>
+        <v>2790</v>
       </c>
       <c r="H1406" s="2"/>
     </row>
     <row r="1407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1407" s="7" t="s">
-        <v>2796</v>
+        <v>2786</v>
       </c>
       <c r="B1407" s="16">
         <v>79155232799</v>
       </c>
       <c r="C1407" s="2"/>
       <c r="D1407" s="2" t="s">
-        <v>2799</v>
+        <v>2789</v>
       </c>
       <c r="E1407" s="2"/>
       <c r="F1407" s="2"/>
@@ -34388,13 +34415,13 @@
     </row>
     <row r="1408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1408" s="7" t="s">
-        <v>2797</v>
+        <v>2787</v>
       </c>
       <c r="B1408" s="16">
         <v>79281777077</v>
       </c>
       <c r="C1408" s="2" t="s">
-        <v>2801</v>
+        <v>2791</v>
       </c>
       <c r="D1408" s="2"/>
       <c r="E1408" s="2"/>
@@ -34422,7 +34449,7 @@
     </row>
     <row r="1410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1410" s="37" t="s">
-        <v>2804</v>
+        <v>2794</v>
       </c>
       <c r="B1410" s="16"/>
       <c r="C1410" s="2"/>
@@ -34434,38 +34461,38 @@
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1411" s="7" t="s">
-        <v>2805</v>
+        <v>2795</v>
       </c>
       <c r="B1411" s="16">
         <v>79034731643</v>
       </c>
       <c r="C1411" s="2" t="s">
-        <v>2814</v>
+        <v>2804</v>
       </c>
       <c r="D1411" s="2" t="s">
-        <v>2815</v>
+        <v>2805</v>
       </c>
       <c r="E1411" s="2" t="s">
-        <v>2823</v>
+        <v>2813</v>
       </c>
       <c r="F1411" s="2" t="s">
-        <v>2821</v>
+        <v>2811</v>
       </c>
       <c r="G1411" s="2"/>
       <c r="H1411" s="2"/>
     </row>
     <row r="1412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1412" s="7" t="s">
-        <v>2806</v>
+        <v>2796</v>
       </c>
       <c r="B1412" s="16">
         <v>79288803988</v>
       </c>
       <c r="C1412" s="2" t="s">
-        <v>2814</v>
+        <v>2804</v>
       </c>
       <c r="D1412" s="2" t="s">
-        <v>2816</v>
+        <v>2806</v>
       </c>
       <c r="E1412" s="2"/>
       <c r="F1412" s="2"/>
@@ -34474,7 +34501,7 @@
     </row>
     <row r="1413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1413" s="37" t="s">
-        <v>2807</v>
+        <v>2797</v>
       </c>
       <c r="B1413" s="16"/>
       <c r="C1413" s="2"/>
@@ -34486,16 +34513,16 @@
     </row>
     <row r="1414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1414" s="7" t="s">
-        <v>2808</v>
+        <v>2798</v>
       </c>
       <c r="B1414" s="16">
         <v>79184775008</v>
       </c>
       <c r="C1414" s="2" t="s">
-        <v>2817</v>
+        <v>2807</v>
       </c>
       <c r="D1414" s="2" t="s">
-        <v>2818</v>
+        <v>2808</v>
       </c>
       <c r="E1414" s="2"/>
       <c r="F1414" s="2"/>
@@ -34504,16 +34531,16 @@
     </row>
     <row r="1415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1415" s="7" t="s">
-        <v>2809</v>
+        <v>2799</v>
       </c>
       <c r="B1415" s="16">
         <v>79185810505</v>
       </c>
       <c r="C1415" s="2" t="s">
-        <v>2817</v>
+        <v>2807</v>
       </c>
       <c r="D1415" s="2" t="s">
-        <v>2820</v>
+        <v>2810</v>
       </c>
       <c r="E1415" s="2"/>
       <c r="F1415" s="2"/>
@@ -34522,7 +34549,7 @@
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1416" s="37" t="s">
-        <v>2810</v>
+        <v>2800</v>
       </c>
       <c r="B1416" s="16"/>
       <c r="C1416" s="2"/>
@@ -34534,7 +34561,7 @@
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1417" s="7" t="s">
-        <v>2811</v>
+        <v>2801</v>
       </c>
       <c r="B1417" s="16">
         <v>79876274373</v>
@@ -34542,24 +34569,24 @@
       <c r="C1417" s="2"/>
       <c r="D1417" s="2"/>
       <c r="E1417" s="2" t="s">
-        <v>2824</v>
+        <v>2814</v>
       </c>
       <c r="F1417" s="2" t="s">
-        <v>2822</v>
+        <v>2812</v>
       </c>
       <c r="G1417" s="2"/>
       <c r="H1417" s="2"/>
     </row>
     <row r="1418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1418" s="7" t="s">
-        <v>2812</v>
+        <v>2802</v>
       </c>
       <c r="B1418" s="16">
         <v>79186355444</v>
       </c>
       <c r="C1418" s="2"/>
       <c r="D1418" s="2" t="s">
-        <v>2819</v>
+        <v>2809</v>
       </c>
       <c r="E1418" s="2"/>
       <c r="F1418" s="2"/>
@@ -34568,14 +34595,14 @@
     </row>
     <row r="1419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1419" s="7" t="s">
-        <v>2813</v>
+        <v>2803</v>
       </c>
       <c r="B1419" s="16">
         <v>79184115068</v>
       </c>
       <c r="C1419" s="2"/>
       <c r="D1419" s="2" t="s">
-        <v>2819</v>
+        <v>2809</v>
       </c>
       <c r="E1419" s="2"/>
       <c r="F1419" s="2"/>
@@ -34584,7 +34611,7 @@
     </row>
     <row r="1420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1420" s="37" t="s">
-        <v>2828</v>
+        <v>2818</v>
       </c>
       <c r="B1420" s="16"/>
       <c r="C1420" s="2"/>
@@ -34596,13 +34623,13 @@
     </row>
     <row r="1421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1421" s="7" t="s">
-        <v>2825</v>
+        <v>2815</v>
       </c>
       <c r="B1421" s="16">
         <v>79287641001</v>
       </c>
       <c r="C1421" s="2" t="s">
-        <v>2832</v>
+        <v>2822</v>
       </c>
       <c r="D1421" s="2"/>
       <c r="E1421" s="2"/>
@@ -34612,16 +34639,16 @@
     </row>
     <row r="1422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1422" s="7" t="s">
-        <v>2826</v>
+        <v>2816</v>
       </c>
       <c r="B1422" s="16">
         <v>79384046645</v>
       </c>
       <c r="C1422" s="2" t="s">
-        <v>2832</v>
+        <v>2822</v>
       </c>
       <c r="D1422" s="2" t="s">
-        <v>2833</v>
+        <v>2823</v>
       </c>
       <c r="E1422" s="2"/>
       <c r="F1422" s="2"/>
@@ -34630,13 +34657,13 @@
     </row>
     <row r="1423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1423" s="7" t="s">
-        <v>2827</v>
+        <v>2817</v>
       </c>
       <c r="B1423" s="16">
         <v>79525762953</v>
       </c>
       <c r="C1423" s="2" t="s">
-        <v>2832</v>
+        <v>2822</v>
       </c>
       <c r="D1423" s="2"/>
       <c r="E1423" s="2"/>
@@ -34646,7 +34673,7 @@
     </row>
     <row r="1424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1424" s="37" t="s">
-        <v>2829</v>
+        <v>2819</v>
       </c>
       <c r="B1424" s="16"/>
       <c r="C1424" s="2"/>
@@ -34658,14 +34685,14 @@
     </row>
     <row r="1425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1425" s="7" t="s">
-        <v>2830</v>
+        <v>2820</v>
       </c>
       <c r="B1425" s="16">
         <v>79873945838</v>
       </c>
       <c r="C1425" s="2"/>
       <c r="D1425" s="2" t="s">
-        <v>2834</v>
+        <v>2824</v>
       </c>
       <c r="E1425" s="2"/>
       <c r="F1425" s="2"/>
@@ -34674,14 +34701,14 @@
     </row>
     <row r="1426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1426" s="7" t="s">
-        <v>2831</v>
+        <v>2821</v>
       </c>
       <c r="B1426" s="16">
         <v>79515080763</v>
       </c>
       <c r="C1426" s="2"/>
       <c r="D1426" s="2" t="s">
-        <v>2835</v>
+        <v>2825</v>
       </c>
       <c r="E1426" s="2"/>
       <c r="F1426" s="2"/>
@@ -34690,7 +34717,7 @@
     </row>
     <row r="1427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1427" s="37" t="s">
-        <v>2870</v>
+        <v>2860</v>
       </c>
       <c r="B1427" s="16"/>
       <c r="C1427" s="2"/>
@@ -34702,14 +34729,14 @@
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1428" s="7" t="s">
-        <v>2871</v>
+        <v>2861</v>
       </c>
       <c r="B1428" s="16">
         <v>79588660254</v>
       </c>
       <c r="C1428" s="2"/>
       <c r="D1428" s="2" t="s">
-        <v>2872</v>
+        <v>2862</v>
       </c>
       <c r="E1428" s="2"/>
       <c r="F1428" s="2"/>
@@ -34736,7 +34763,7 @@
     </row>
     <row r="1430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1430" s="37" t="s">
-        <v>2873</v>
+        <v>2863</v>
       </c>
       <c r="B1430" s="16"/>
       <c r="C1430" s="2"/>
@@ -34748,27 +34775,27 @@
     </row>
     <row r="1431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1431" s="7" t="s">
-        <v>2874</v>
+        <v>2864</v>
       </c>
       <c r="B1431" s="16">
         <v>79023891506</v>
       </c>
       <c r="C1431" s="2"/>
       <c r="D1431" s="2" t="s">
-        <v>2877</v>
+        <v>2867</v>
       </c>
       <c r="E1431" s="2"/>
       <c r="F1431" s="2"/>
     </row>
     <row r="1432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1432" s="7" t="s">
-        <v>2875</v>
+        <v>2865</v>
       </c>
       <c r="B1432" s="16">
         <v>79184377062</v>
       </c>
       <c r="C1432" s="2" t="s">
-        <v>2876</v>
+        <v>2866</v>
       </c>
       <c r="D1432" s="2"/>
       <c r="E1432" s="2"/>
@@ -34776,7 +34803,7 @@
     </row>
     <row r="1433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1433" s="37" t="s">
-        <v>2873</v>
+        <v>2863</v>
       </c>
       <c r="B1433" s="16"/>
       <c r="C1433" s="2"/>
@@ -34786,35 +34813,35 @@
     </row>
     <row r="1434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1434" s="7" t="s">
-        <v>2892</v>
+        <v>2882</v>
       </c>
       <c r="B1434" s="16">
         <v>79066122888</v>
       </c>
       <c r="C1434" s="2"/>
       <c r="D1434" s="2" t="s">
-        <v>2895</v>
+        <v>2885</v>
       </c>
       <c r="E1434" s="2"/>
       <c r="F1434" s="2"/>
     </row>
     <row r="1435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1435" s="7" t="s">
-        <v>2893</v>
+        <v>2883</v>
       </c>
       <c r="B1435" s="16">
         <v>79959416136</v>
       </c>
       <c r="C1435" s="2"/>
       <c r="D1435" s="2" t="s">
-        <v>2895</v>
+        <v>2885</v>
       </c>
       <c r="E1435" s="2"/>
       <c r="F1435" s="2"/>
     </row>
     <row r="1436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1436" s="7" t="s">
-        <v>2894</v>
+        <v>2884</v>
       </c>
       <c r="B1436" s="16">
         <v>79628779270</v>
@@ -34822,15 +34849,15 @@
       <c r="C1436" s="2"/>
       <c r="D1436" s="2"/>
       <c r="E1436" s="2" t="s">
-        <v>2897</v>
+        <v>2887</v>
       </c>
       <c r="F1436" s="2" t="s">
-        <v>2896</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="1437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1437" s="37" t="s">
-        <v>2917</v>
+        <v>2907</v>
       </c>
       <c r="B1437" s="16"/>
       <c r="C1437" s="2"/>
@@ -34840,7 +34867,7 @@
     </row>
     <row r="1438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1438" s="7" t="s">
-        <v>2918</v>
+        <v>2908</v>
       </c>
       <c r="B1438" s="16">
         <v>79034397172</v>
@@ -34848,15 +34875,15 @@
       <c r="C1438" s="2"/>
       <c r="D1438" s="2"/>
       <c r="E1438" s="2" t="s">
-        <v>2926</v>
+        <v>2916</v>
       </c>
       <c r="F1438" s="2" t="s">
-        <v>2925</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="1439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1439" s="37" t="s">
-        <v>2920</v>
+        <v>2910</v>
       </c>
       <c r="C1439" s="2"/>
       <c r="D1439" s="2"/>
@@ -34865,21 +34892,21 @@
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1440" s="7" t="s">
-        <v>2919</v>
+        <v>2909</v>
       </c>
       <c r="B1440" s="16">
         <v>79493830457</v>
       </c>
       <c r="C1440" s="2"/>
       <c r="D1440" s="2" t="s">
-        <v>2927</v>
+        <v>2917</v>
       </c>
       <c r="E1440" s="2"/>
       <c r="F1440" s="2"/>
     </row>
     <row r="1441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1441" s="37" t="s">
-        <v>2921</v>
+        <v>2911</v>
       </c>
       <c r="B1441" s="16"/>
       <c r="C1441" s="2"/>
@@ -34889,14 +34916,14 @@
     </row>
     <row r="1442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1442" s="7" t="s">
-        <v>2922</v>
+        <v>2912</v>
       </c>
       <c r="B1442" s="16">
         <v>79030000959</v>
       </c>
       <c r="C1442" s="2"/>
       <c r="D1442" s="2" t="s">
-        <v>2928</v>
+        <v>2918</v>
       </c>
       <c r="E1442" s="2"/>
       <c r="F1442" s="2"/>
@@ -34919,7 +34946,7 @@
     </row>
     <row r="1444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1444" s="37" t="s">
-        <v>2929</v>
+        <v>2919</v>
       </c>
       <c r="B1444" s="16"/>
       <c r="C1444" s="2"/>
@@ -34929,29 +34956,29 @@
     </row>
     <row r="1445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1445" s="7" t="s">
-        <v>2930</v>
+        <v>2920</v>
       </c>
       <c r="B1445" s="16">
         <v>79181311990</v>
       </c>
       <c r="C1445" s="2" t="s">
-        <v>2945</v>
+        <v>2936</v>
       </c>
       <c r="D1445" s="2" t="s">
-        <v>2946</v>
+        <v>2937</v>
       </c>
       <c r="E1445" s="2"/>
       <c r="F1445" s="2"/>
     </row>
     <row r="1446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1446" s="7" t="s">
-        <v>2931</v>
+        <v>2921</v>
       </c>
       <c r="B1446" s="16">
         <v>79221892567</v>
       </c>
       <c r="C1446" s="2" t="s">
-        <v>2945</v>
+        <v>2936</v>
       </c>
       <c r="D1446" s="2"/>
       <c r="E1446" s="2"/>
@@ -34959,13 +34986,13 @@
     </row>
     <row r="1447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1447" s="7" t="s">
-        <v>2932</v>
+        <v>2922</v>
       </c>
       <c r="B1447" s="16">
         <v>79189219714</v>
       </c>
       <c r="C1447" s="2" t="s">
-        <v>2945</v>
+        <v>2936</v>
       </c>
       <c r="D1447" s="2"/>
       <c r="E1447" s="2"/>
@@ -34973,7 +35000,7 @@
     </row>
     <row r="1448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1448" s="37" t="s">
-        <v>2933</v>
+        <v>2923</v>
       </c>
       <c r="B1448" s="16"/>
       <c r="C1448" s="2"/>
@@ -34983,13 +35010,13 @@
     </row>
     <row r="1449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1449" s="7" t="s">
-        <v>2934</v>
+        <v>2924</v>
       </c>
       <c r="B1449" s="16">
         <v>79898382391</v>
       </c>
       <c r="C1449" s="2" t="s">
-        <v>2943</v>
+        <v>2934</v>
       </c>
       <c r="D1449" s="2"/>
       <c r="E1449" s="2"/>
@@ -34997,53 +35024,53 @@
     </row>
     <row r="1450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1450" s="7" t="s">
-        <v>2942</v>
+        <v>2932</v>
       </c>
       <c r="B1450" s="16">
         <v>79867392843</v>
       </c>
       <c r="C1450" s="2"/>
       <c r="D1450" s="2" t="s">
-        <v>2948</v>
+        <v>2939</v>
       </c>
       <c r="E1450" s="2"/>
       <c r="F1450" s="2"/>
     </row>
     <row r="1451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1451" s="7" t="s">
-        <v>2935</v>
+        <v>2925</v>
       </c>
       <c r="B1451" s="16">
         <v>79515340206</v>
       </c>
       <c r="C1451" s="2"/>
       <c r="D1451" s="2" t="s">
-        <v>2949</v>
+        <v>2940</v>
       </c>
       <c r="E1451" s="2"/>
       <c r="F1451" s="2"/>
     </row>
     <row r="1452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1452" s="7" t="s">
-        <v>2936</v>
+        <v>2926</v>
       </c>
       <c r="B1452" s="16">
         <v>79181058985</v>
       </c>
       <c r="C1452" s="2" t="s">
-        <v>2943</v>
+        <v>2934</v>
       </c>
       <c r="D1452" s="2" t="s">
-        <v>2947</v>
+        <v>2938</v>
       </c>
       <c r="E1452" s="2" t="s">
-        <v>2953</v>
+        <v>2944</v>
       </c>
       <c r="F1452" s="2"/>
     </row>
     <row r="1453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1453" s="37" t="s">
-        <v>2937</v>
+        <v>2927</v>
       </c>
       <c r="B1453" s="16"/>
       <c r="C1453" s="2"/>
@@ -35053,7 +35080,7 @@
     </row>
     <row r="1454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1454" s="7" t="s">
-        <v>2938</v>
+        <v>2928</v>
       </c>
       <c r="B1454" s="16">
         <v>79094330806</v>
@@ -35061,52 +35088,52 @@
       <c r="C1454" s="2"/>
       <c r="D1454" s="2"/>
       <c r="E1454" s="2" t="s">
-        <v>2955</v>
+        <v>2946</v>
       </c>
       <c r="F1454" s="2" t="s">
-        <v>2954</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="1455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1455" s="7" t="s">
-        <v>2939</v>
+        <v>2929</v>
       </c>
       <c r="B1455" s="16">
         <v>79892969812</v>
       </c>
       <c r="C1455" s="2"/>
       <c r="D1455" s="2" t="s">
-        <v>2951</v>
+        <v>2942</v>
       </c>
       <c r="E1455" s="2"/>
       <c r="F1455" s="2"/>
     </row>
     <row r="1456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1456" s="7" t="s">
-        <v>2940</v>
+        <v>2930</v>
       </c>
       <c r="B1456" s="16">
         <v>79038276326</v>
       </c>
       <c r="C1456" s="2" t="s">
-        <v>2944</v>
+        <v>2935</v>
       </c>
       <c r="D1456" s="2" t="s">
-        <v>2952</v>
+        <v>2943</v>
       </c>
       <c r="E1456" s="2"/>
       <c r="F1456" s="2"/>
     </row>
     <row r="1457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1457" s="7" t="s">
-        <v>2941</v>
+        <v>2931</v>
       </c>
       <c r="B1457" s="16">
         <v>79612832854</v>
       </c>
       <c r="C1457" s="2"/>
       <c r="D1457" s="2" t="s">
-        <v>2950</v>
+        <v>2941</v>
       </c>
       <c r="E1457" s="2"/>
       <c r="F1457" s="2"/>
@@ -35114,13 +35141,23 @@
     <row r="1458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1458" s="7"/>
       <c r="B1458" s="16"/>
-      <c r="C1458" s="2"/>
-      <c r="D1458" s="2"/>
-      <c r="E1458" s="2"/>
-      <c r="F1458" s="2"/>
+      <c r="C1458" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1458" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1458" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1458" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="1459" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1459" s="7"/>
+      <c r="A1459" s="37" t="s">
+        <v>2956</v>
+      </c>
       <c r="B1459" s="16"/>
       <c r="C1459" s="2"/>
       <c r="D1459" s="2"/>
@@ -35128,47 +35165,80 @@
       <c r="F1459" s="2"/>
     </row>
     <row r="1460" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1460" s="7"/>
-      <c r="B1460" s="16"/>
-      <c r="C1460" s="2"/>
-      <c r="D1460" s="2"/>
-      <c r="E1460" s="2"/>
+      <c r="A1460" s="7" t="s">
+        <v>2957</v>
+      </c>
+      <c r="B1460" s="16">
+        <v>79204054783</v>
+      </c>
+      <c r="C1460" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1460" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="E1460" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="F1460" s="2"/>
     </row>
     <row r="1461" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1461" s="7"/>
-      <c r="B1461" s="16"/>
+      <c r="A1461" s="37" t="s">
+        <v>2961</v>
+      </c>
       <c r="C1461" s="2"/>
       <c r="D1461" s="2"/>
       <c r="E1461" s="2"/>
       <c r="F1461" s="2"/>
     </row>
     <row r="1462" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1462" s="7"/>
-      <c r="B1462" s="16"/>
+      <c r="A1462" s="7" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B1462" s="16">
+        <v>79054008128</v>
+      </c>
       <c r="C1462" s="2"/>
-      <c r="D1462" s="2"/>
+      <c r="D1462" s="2" t="s">
+        <v>2933</v>
+      </c>
       <c r="E1462" s="2"/>
       <c r="F1462" s="2"/>
     </row>
     <row r="1463" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1463" s="7"/>
-      <c r="B1463" s="16"/>
+      <c r="A1463" s="7" t="s">
+        <v>2959</v>
+      </c>
+      <c r="B1463" s="16">
+        <v>79788069407</v>
+      </c>
       <c r="C1463" s="2"/>
       <c r="D1463" s="2"/>
-      <c r="E1463" s="2"/>
-      <c r="F1463" s="2"/>
+      <c r="E1463" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1463" s="2" t="s">
+        <v>731</v>
+      </c>
     </row>
     <row r="1464" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1464" s="7"/>
-      <c r="B1464" s="16"/>
+      <c r="A1464" s="7" t="s">
+        <v>2960</v>
+      </c>
+      <c r="B1464" s="16">
+        <v>79054079005</v>
+      </c>
       <c r="C1464" s="2"/>
-      <c r="D1464" s="2"/>
+      <c r="D1464" s="2" t="s">
+        <v>2964</v>
+      </c>
       <c r="E1464" s="2"/>
       <c r="F1464" s="2"/>
     </row>
     <row r="1465" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1465" s="7"/>
+      <c r="A1465" s="37" t="s">
+        <v>2962</v>
+      </c>
       <c r="B1465" s="16"/>
       <c r="C1465" s="2"/>
       <c r="D1465" s="2"/>
@@ -35176,11 +35246,21 @@
       <c r="F1465" s="2"/>
     </row>
     <row r="1466" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1466" s="7"/>
-      <c r="B1466" s="16"/>
-      <c r="C1466" s="2"/>
-      <c r="D1466" s="2"/>
-      <c r="E1466" s="2"/>
+      <c r="A1466" s="7" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B1466" s="16">
+        <v>79530998771</v>
+      </c>
+      <c r="C1466" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1466" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="E1466" s="2" t="s">
+        <v>731</v>
+      </c>
       <c r="F1466" s="2"/>
     </row>
     <row r="1467" spans="1:6" x14ac:dyDescent="0.25">
@@ -35192,24 +35272,18 @@
       <c r="F1467" s="2"/>
     </row>
     <row r="1468" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1468" s="7"/>
-      <c r="B1468" s="16"/>
       <c r="C1468" s="2"/>
       <c r="D1468" s="2"/>
       <c r="E1468" s="2"/>
       <c r="F1468" s="2"/>
     </row>
     <row r="1469" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1469" s="7"/>
-      <c r="B1469" s="16"/>
       <c r="C1469" s="2"/>
       <c r="D1469" s="2"/>
       <c r="E1469" s="2"/>
       <c r="F1469" s="2"/>
     </row>
     <row r="1470" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1470" s="7"/>
-      <c r="B1470" s="16"/>
       <c r="C1470" s="2"/>
       <c r="D1470" s="2"/>
       <c r="E1470" s="2"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817CFFCF-6ED3-44FC-B6B3-00710819BCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2795598D-26A2-456F-BE5A-947BB503D2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4526" uniqueCount="2965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4528" uniqueCount="2975">
   <si>
     <t>Пароль</t>
   </si>
@@ -8835,9 +8835,6 @@
     <t>92843</t>
   </si>
   <si>
-    <t>* Дима</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/d/3OGg5RUkUpblwQ</t>
   </si>
   <si>
@@ -8928,7 +8925,40 @@
     <t>98771</t>
   </si>
   <si>
-    <t>* ДимМа</t>
+    <t>https://disk.yandex.ru/d/nUZjfmRlOrssDQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/R671pNVRFeacSA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/EGnYGPjjiu5HyQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Gl7BBd9yx20a8w</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/lHv24Py8FR11hg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/YzSh339129nqnA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/odRMAiHFC03irg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/bnKXaSaQTFsqrg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/xyPGJZ9XAylTwg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/lfkHzln5xOGfIA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/NLKgRWjKz5GowA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/O31Ssebkwuspgw</t>
   </si>
 </sst>
 </file>
@@ -32177,7 +32207,7 @@
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1265" s="32" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="B1265" s="33">
         <v>79787819232</v>
@@ -32223,7 +32253,7 @@
     </row>
     <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1268" s="32" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="B1268" s="33">
         <v>79181206771</v>
@@ -32245,7 +32275,7 @@
     </row>
     <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1269" s="32" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="B1269" s="33">
         <v>79286136662</v>
@@ -32273,7 +32303,7 @@
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1271" s="18" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="B1271" s="39">
         <v>375297856891</v>
@@ -32307,7 +32337,7 @@
     </row>
     <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1273" s="32" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="B1273" s="33">
         <v>79189218545</v>
@@ -32335,7 +32365,7 @@
     </row>
     <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1275" s="18" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="B1275" s="39">
         <v>79883302117</v>
@@ -32353,7 +32383,7 @@
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1276" s="32" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="B1276" s="33">
         <v>79885414599</v>
@@ -32369,7 +32399,7 @@
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1277" s="32" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="B1277" s="33">
         <v>79606987172</v>
@@ -32399,7 +32429,7 @@
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1279" s="32" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="B1279" s="33">
         <v>79002702201</v>
@@ -34962,10 +34992,10 @@
         <v>79181311990</v>
       </c>
       <c r="C1445" s="2" t="s">
+        <v>2935</v>
+      </c>
+      <c r="D1445" s="2" t="s">
         <v>2936</v>
-      </c>
-      <c r="D1445" s="2" t="s">
-        <v>2937</v>
       </c>
       <c r="E1445" s="2"/>
       <c r="F1445" s="2"/>
@@ -34978,7 +35008,7 @@
         <v>79221892567</v>
       </c>
       <c r="C1446" s="2" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="D1446" s="2"/>
       <c r="E1446" s="2"/>
@@ -34992,7 +35022,7 @@
         <v>79189219714</v>
       </c>
       <c r="C1447" s="2" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="D1447" s="2"/>
       <c r="E1447" s="2"/>
@@ -35016,7 +35046,7 @@
         <v>79898382391</v>
       </c>
       <c r="C1449" s="2" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="D1449" s="2"/>
       <c r="E1449" s="2"/>
@@ -35031,7 +35061,7 @@
       </c>
       <c r="C1450" s="2"/>
       <c r="D1450" s="2" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="E1450" s="2"/>
       <c r="F1450" s="2"/>
@@ -35045,7 +35075,7 @@
       </c>
       <c r="C1451" s="2"/>
       <c r="D1451" s="2" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="E1451" s="2"/>
       <c r="F1451" s="2"/>
@@ -35058,13 +35088,13 @@
         <v>79181058985</v>
       </c>
       <c r="C1452" s="2" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="D1452" s="2" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="E1452" s="2" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="F1452" s="2"/>
     </row>
@@ -35088,10 +35118,10 @@
       <c r="C1454" s="2"/>
       <c r="D1454" s="2"/>
       <c r="E1454" s="2" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="F1454" s="2" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="1455" spans="1:6" x14ac:dyDescent="0.25">
@@ -35103,7 +35133,7 @@
       </c>
       <c r="C1455" s="2"/>
       <c r="D1455" s="2" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="E1455" s="2"/>
       <c r="F1455" s="2"/>
@@ -35116,10 +35146,10 @@
         <v>79038276326</v>
       </c>
       <c r="C1456" s="2" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="D1456" s="2" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="E1456" s="2"/>
       <c r="F1456" s="2"/>
@@ -35133,7 +35163,7 @@
       </c>
       <c r="C1457" s="2"/>
       <c r="D1457" s="2" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="E1457" s="2"/>
       <c r="F1457" s="2"/>
@@ -35156,7 +35186,7 @@
     </row>
     <row r="1459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1459" s="37" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="B1459" s="16"/>
       <c r="C1459" s="2"/>
@@ -35166,25 +35196,27 @@
     </row>
     <row r="1460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1460" s="7" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="B1460" s="16">
         <v>79204054783</v>
       </c>
       <c r="C1460" s="2" t="s">
-        <v>731</v>
+        <v>2963</v>
       </c>
       <c r="D1460" s="2" t="s">
-        <v>731</v>
+        <v>2964</v>
       </c>
       <c r="E1460" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="F1460" s="2"/>
+        <v>2970</v>
+      </c>
+      <c r="F1460" s="2" t="s">
+        <v>2969</v>
+      </c>
     </row>
     <row r="1461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1461" s="37" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="C1461" s="2"/>
       <c r="D1461" s="2"/>
@@ -35193,21 +35225,21 @@
     </row>
     <row r="1462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1462" s="7" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="B1462" s="16">
         <v>79054008128</v>
       </c>
       <c r="C1462" s="2"/>
       <c r="D1462" s="2" t="s">
-        <v>2933</v>
+        <v>2965</v>
       </c>
       <c r="E1462" s="2"/>
       <c r="F1462" s="2"/>
     </row>
     <row r="1463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1463" s="7" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B1463" s="16">
         <v>79788069407</v>
@@ -35215,29 +35247,29 @@
       <c r="C1463" s="2"/>
       <c r="D1463" s="2"/>
       <c r="E1463" s="2" t="s">
-        <v>731</v>
+        <v>2972</v>
       </c>
       <c r="F1463" s="2" t="s">
-        <v>731</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="1464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1464" s="7" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="B1464" s="16">
         <v>79054079005</v>
       </c>
       <c r="C1464" s="2"/>
       <c r="D1464" s="2" t="s">
-        <v>2964</v>
+        <v>2966</v>
       </c>
       <c r="E1464" s="2"/>
       <c r="F1464" s="2"/>
     </row>
     <row r="1465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1465" s="37" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="B1465" s="16"/>
       <c r="C1465" s="2"/>
@@ -35247,21 +35279,23 @@
     </row>
     <row r="1466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1466" s="7" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="B1466" s="16">
         <v>79530998771</v>
       </c>
       <c r="C1466" s="2" t="s">
-        <v>731</v>
+        <v>2968</v>
       </c>
       <c r="D1466" s="2" t="s">
-        <v>731</v>
+        <v>2967</v>
       </c>
       <c r="E1466" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="F1466" s="2"/>
+        <v>2974</v>
+      </c>
+      <c r="F1466" s="2" t="s">
+        <v>2973</v>
+      </c>
     </row>
     <row r="1467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1467" s="7"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401C598B-5DB5-4C28-B6BE-7DD450004326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC341514-4A60-4DAE-8678-EB65DB146E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4543" uniqueCount="2984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4545" uniqueCount="2984">
   <si>
     <t>Пароль</t>
   </si>
@@ -35387,8 +35387,12 @@
       <c r="D1470" s="43" t="s">
         <v>2981</v>
       </c>
-      <c r="E1470" s="43"/>
-      <c r="F1470" s="43"/>
+      <c r="E1470" s="43" t="s">
+        <v>2983</v>
+      </c>
+      <c r="F1470" s="43" t="s">
+        <v>2982</v>
+      </c>
       <c r="G1470" s="7"/>
     </row>
     <row r="1471" spans="1:7" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC341514-4A60-4DAE-8678-EB65DB146E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BBA97A-51C7-4218-8324-68EA7669A789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4545" uniqueCount="2984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4562" uniqueCount="2994">
   <si>
     <t>Пароль</t>
   </si>
@@ -8986,6 +8986,36 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/5h6hg13REgxhtw</t>
+  </si>
+  <si>
+    <t>15/10/26/10:00</t>
+  </si>
+  <si>
+    <t>80634</t>
+  </si>
+  <si>
+    <t>+79042880634</t>
+  </si>
+  <si>
+    <t>00159</t>
+  </si>
+  <si>
+    <t>+79184400159</t>
+  </si>
+  <si>
+    <t>15/10/26/12:30</t>
+  </si>
+  <si>
+    <t>97039</t>
+  </si>
+  <si>
+    <t>+79525697039</t>
+  </si>
+  <si>
+    <t>?https://disk.yandex.ru/d/OGLB4SbQGg8ETw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/YmP6upvE3Fqq-Q</t>
   </si>
 </sst>
 </file>
@@ -35419,14 +35449,24 @@
     <row r="1472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1472" s="7"/>
       <c r="B1472" s="7"/>
-      <c r="C1472" s="43"/>
-      <c r="D1472" s="43"/>
-      <c r="E1472" s="43"/>
-      <c r="F1472" s="43"/>
+      <c r="C1472" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1472" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1472" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1472" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1472" s="7"/>
     </row>
     <row r="1473" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1473" s="7"/>
+      <c r="A1473" s="37" t="s">
+        <v>2984</v>
+      </c>
       <c r="B1473" s="7"/>
       <c r="C1473" s="43"/>
       <c r="D1473" s="43"/>
@@ -35435,25 +35475,43 @@
       <c r="G1473" s="7"/>
     </row>
     <row r="1474" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1474" s="7"/>
-      <c r="B1474" s="7"/>
-      <c r="C1474" s="43"/>
-      <c r="D1474" s="43"/>
+      <c r="A1474" s="7" t="s">
+        <v>2985</v>
+      </c>
+      <c r="B1474" s="7" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C1474" s="43" t="s">
+        <v>2992</v>
+      </c>
+      <c r="D1474" s="43" t="s">
+        <v>2993</v>
+      </c>
       <c r="E1474" s="43"/>
       <c r="F1474" s="43"/>
       <c r="G1474" s="7"/>
     </row>
     <row r="1475" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1475" s="7"/>
-      <c r="B1475" s="7"/>
-      <c r="C1475" s="43"/>
-      <c r="D1475" s="43"/>
+      <c r="A1475" s="7" t="s">
+        <v>2987</v>
+      </c>
+      <c r="B1475" s="7" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C1475" s="43" t="s">
+        <v>2992</v>
+      </c>
+      <c r="D1475" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="E1475" s="43"/>
       <c r="F1475" s="43"/>
       <c r="G1475" s="7"/>
     </row>
     <row r="1476" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1476" s="7"/>
+      <c r="A1476" s="37" t="s">
+        <v>2989</v>
+      </c>
       <c r="B1476" s="7"/>
       <c r="C1476" s="43"/>
       <c r="D1476" s="43"/>
@@ -35462,10 +35520,16 @@
       <c r="G1476" s="7"/>
     </row>
     <row r="1477" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1477" s="7"/>
-      <c r="B1477" s="7"/>
+      <c r="A1477" s="7" t="s">
+        <v>2990</v>
+      </c>
+      <c r="B1477" s="7" t="s">
+        <v>2991</v>
+      </c>
       <c r="C1477" s="43"/>
-      <c r="D1477" s="43"/>
+      <c r="D1477" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="E1477" s="43"/>
       <c r="F1477" s="43"/>
       <c r="G1477" s="7"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BBA97A-51C7-4218-8324-68EA7669A789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDECAA3-55A6-4559-8527-85CAFBF60BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4562" uniqueCount="2994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4562" uniqueCount="2996">
   <si>
     <t>Пароль</t>
   </si>
@@ -9016,6 +9016,12 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/YmP6upvE3Fqq-Q</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/-tGj-sQP-WHLlw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/P96eCoZihduJ1w</t>
   </si>
 </sst>
 </file>
@@ -35502,7 +35508,7 @@
         <v>2992</v>
       </c>
       <c r="D1475" s="43" t="s">
-        <v>731</v>
+        <v>2994</v>
       </c>
       <c r="E1475" s="43"/>
       <c r="F1475" s="43"/>
@@ -35528,7 +35534,7 @@
       </c>
       <c r="C1477" s="43"/>
       <c r="D1477" s="43" t="s">
-        <v>731</v>
+        <v>2995</v>
       </c>
       <c r="E1477" s="43"/>
       <c r="F1477" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDECAA3-55A6-4559-8527-85CAFBF60BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EEA3DF-AA59-421D-98A3-CE8BBB6C60C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4562" uniqueCount="2996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4572" uniqueCount="3002">
   <si>
     <t>Пароль</t>
   </si>
@@ -9022,6 +9022,24 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/P96eCoZihduJ1w</t>
+  </si>
+  <si>
+    <t>16/10/26/10:00</t>
+  </si>
+  <si>
+    <t>62677</t>
+  </si>
+  <si>
+    <t>+79277062677</t>
+  </si>
+  <si>
+    <t>+79782640332</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/wYgqI98OttzaJw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/NkpSPXMC57XnwQ</t>
   </si>
 </sst>
 </file>
@@ -35541,7 +35559,9 @@
       <c r="G1477" s="7"/>
     </row>
     <row r="1478" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1478" s="7"/>
+      <c r="A1478" s="37" t="s">
+        <v>2996</v>
+      </c>
       <c r="B1478" s="7"/>
       <c r="C1478" s="43"/>
       <c r="D1478" s="43"/>
@@ -35550,19 +35570,37 @@
       <c r="G1478" s="7"/>
     </row>
     <row r="1479" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1479" s="7"/>
-      <c r="B1479" s="7"/>
-      <c r="C1479" s="43"/>
+      <c r="A1479" s="7" t="s">
+        <v>2997</v>
+      </c>
+      <c r="B1479" s="7" t="s">
+        <v>2998</v>
+      </c>
+      <c r="C1479" s="43" t="s">
+        <v>3000</v>
+      </c>
       <c r="D1479" s="43"/>
-      <c r="E1479" s="43"/>
-      <c r="F1479" s="43"/>
+      <c r="E1479" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1479" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1479" s="7"/>
     </row>
     <row r="1480" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1480" s="7"/>
-      <c r="B1480" s="7"/>
-      <c r="C1480" s="43"/>
-      <c r="D1480" s="43"/>
+      <c r="A1480" s="7" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B1480" s="7" t="s">
+        <v>2999</v>
+      </c>
+      <c r="C1480" s="43" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1480" s="43" t="s">
+        <v>3001</v>
+      </c>
       <c r="E1480" s="43"/>
       <c r="F1480" s="43"/>
       <c r="G1480" s="7"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EEA3DF-AA59-421D-98A3-CE8BBB6C60C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5AB5CB-AAAD-4195-AE41-A1EF8A6F8548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4572" uniqueCount="3002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4572" uniqueCount="3004">
   <si>
     <t>Пароль</t>
   </si>
@@ -9040,6 +9040,12 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/NkpSPXMC57XnwQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/nnkHEAd8YtM5-A</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/60IWHCtJ1tPHlQ</t>
   </si>
 </sst>
 </file>
@@ -35581,10 +35587,10 @@
       </c>
       <c r="D1479" s="43"/>
       <c r="E1479" s="43" t="s">
-        <v>731</v>
+        <v>3003</v>
       </c>
       <c r="F1479" s="43" t="s">
-        <v>731</v>
+        <v>3002</v>
       </c>
       <c r="G1479" s="7"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5AB5CB-AAAD-4195-AE41-A1EF8A6F8548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944B8614-46FE-48BD-89FF-C9F9B2DDDBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4572" uniqueCount="3004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4592" uniqueCount="3016">
   <si>
     <t>Пароль</t>
   </si>
@@ -9046,6 +9046,42 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/60IWHCtJ1tPHlQ</t>
+  </si>
+  <si>
+    <t>17/10/26/12:30</t>
+  </si>
+  <si>
+    <t>47214</t>
+  </si>
+  <si>
+    <t>+79187947214</t>
+  </si>
+  <si>
+    <t>36222</t>
+  </si>
+  <si>
+    <t>+79034836222</t>
+  </si>
+  <si>
+    <t>49955</t>
+  </si>
+  <si>
+    <t>+79184649955</t>
+  </si>
+  <si>
+    <t>17658</t>
+  </si>
+  <si>
+    <t>+79996917658</t>
+  </si>
+  <si>
+    <t>* Дима/ДанНя</t>
+  </si>
+  <si>
+    <t>* ДимМа</t>
+  </si>
+  <si>
+    <t>* Sheff</t>
   </si>
 </sst>
 </file>
@@ -35612,7 +35648,9 @@
       <c r="G1480" s="7"/>
     </row>
     <row r="1481" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1481" s="7"/>
+      <c r="A1481" s="37" t="s">
+        <v>3004</v>
+      </c>
       <c r="B1481" s="7"/>
       <c r="C1481" s="43"/>
       <c r="D1481" s="43"/>
@@ -35621,37 +35659,75 @@
       <c r="G1481" s="7"/>
     </row>
     <row r="1482" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1482" s="7"/>
-      <c r="B1482" s="7"/>
-      <c r="C1482" s="43"/>
-      <c r="D1482" s="43"/>
-      <c r="E1482" s="43"/>
-      <c r="F1482" s="43"/>
+      <c r="A1482" s="7" t="s">
+        <v>3005</v>
+      </c>
+      <c r="B1482" s="7" t="s">
+        <v>3006</v>
+      </c>
+      <c r="C1482" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1482" s="43" t="s">
+        <v>3013</v>
+      </c>
+      <c r="E1482" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1482" s="43" t="s">
+        <v>3013</v>
+      </c>
       <c r="G1482" s="7"/>
     </row>
     <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1483" s="7"/>
-      <c r="B1483" s="7"/>
-      <c r="C1483" s="43"/>
-      <c r="D1483" s="43"/>
-      <c r="E1483" s="43"/>
-      <c r="F1483" s="43"/>
+      <c r="A1483" s="7" t="s">
+        <v>3007</v>
+      </c>
+      <c r="B1483" s="7" t="s">
+        <v>3008</v>
+      </c>
+      <c r="C1483" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1483" s="43" t="s">
+        <v>3014</v>
+      </c>
+      <c r="E1483" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1483" s="43" t="s">
+        <v>3014</v>
+      </c>
       <c r="G1483" s="7"/>
     </row>
     <row r="1484" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1484" s="7"/>
-      <c r="B1484" s="7"/>
+      <c r="A1484" s="7" t="s">
+        <v>3009</v>
+      </c>
+      <c r="B1484" s="7" t="s">
+        <v>3010</v>
+      </c>
       <c r="C1484" s="43"/>
-      <c r="D1484" s="43"/>
+      <c r="D1484" s="43" t="s">
+        <v>3014</v>
+      </c>
       <c r="E1484" s="43"/>
       <c r="F1484" s="43"/>
       <c r="G1484" s="7"/>
     </row>
     <row r="1485" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1485" s="7"/>
-      <c r="B1485" s="7"/>
-      <c r="C1485" s="43"/>
-      <c r="D1485" s="43"/>
+      <c r="A1485" s="7" t="s">
+        <v>3011</v>
+      </c>
+      <c r="B1485" s="7" t="s">
+        <v>3012</v>
+      </c>
+      <c r="C1485" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1485" s="43" t="s">
+        <v>3015</v>
+      </c>
       <c r="E1485" s="43"/>
       <c r="F1485" s="43"/>
       <c r="G1485" s="7"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944B8614-46FE-48BD-89FF-C9F9B2DDDBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A59CE1-0D48-4F6B-A59C-4BB0F8C09BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4592" uniqueCount="3016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="3017">
   <si>
     <t>Пароль</t>
   </si>
@@ -9082,6 +9082,9 @@
   </si>
   <si>
     <t>* Sheff</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -35707,11 +35710,15 @@
       <c r="B1484" s="7" t="s">
         <v>3010</v>
       </c>
-      <c r="C1484" s="43"/>
+      <c r="C1484" s="43" t="s">
+        <v>3016</v>
+      </c>
       <c r="D1484" s="43" t="s">
         <v>3014</v>
       </c>
-      <c r="E1484" s="43"/>
+      <c r="E1484" s="43" t="s">
+        <v>3016</v>
+      </c>
       <c r="F1484" s="43"/>
       <c r="G1484" s="7"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A59CE1-0D48-4F6B-A59C-4BB0F8C09BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD31A86-D26B-46F6-B664-7E7C1D949B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="3017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="3018">
   <si>
     <t>Пароль</t>
   </si>
@@ -9085,6 +9085,9 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Y9K86Gl45XwCTw</t>
   </si>
 </sst>
 </file>
@@ -35669,7 +35672,7 @@
         <v>3006</v>
       </c>
       <c r="C1482" s="43" t="s">
-        <v>731</v>
+        <v>3017</v>
       </c>
       <c r="D1482" s="43" t="s">
         <v>3013</v>
@@ -35690,7 +35693,7 @@
         <v>3008</v>
       </c>
       <c r="C1483" s="43" t="s">
-        <v>731</v>
+        <v>3017</v>
       </c>
       <c r="D1483" s="43" t="s">
         <v>3014</v>
@@ -35730,7 +35733,7 @@
         <v>3012</v>
       </c>
       <c r="C1485" s="43" t="s">
-        <v>731</v>
+        <v>3017</v>
       </c>
       <c r="D1485" s="43" t="s">
         <v>3015</v>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD31A86-D26B-46F6-B664-7E7C1D949B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E4B593-2C31-4E22-A166-F3C19E72DB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9057,12 +9057,6 @@
     <t>+79187947214</t>
   </si>
   <si>
-    <t>36222</t>
-  </si>
-  <si>
-    <t>+79034836222</t>
-  </si>
-  <si>
     <t>49955</t>
   </si>
   <si>
@@ -9088,6 +9082,12 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/Y9K86Gl45XwCTw</t>
+  </si>
+  <si>
+    <t>96222</t>
+  </si>
+  <si>
+    <t>+79034896222</t>
   </si>
 </sst>
 </file>
@@ -35672,71 +35672,71 @@
         <v>3006</v>
       </c>
       <c r="C1482" s="43" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="D1482" s="43" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="E1482" s="43" t="s">
         <v>731</v>
       </c>
       <c r="F1482" s="43" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="G1482" s="7"/>
     </row>
     <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1483" s="7" t="s">
-        <v>3007</v>
+        <v>3016</v>
       </c>
       <c r="B1483" s="7" t="s">
-        <v>3008</v>
+        <v>3017</v>
       </c>
       <c r="C1483" s="43" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="D1483" s="43" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="E1483" s="43" t="s">
         <v>731</v>
       </c>
       <c r="F1483" s="43" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G1483" s="7"/>
     </row>
     <row r="1484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1484" s="7" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="B1484" s="7" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="C1484" s="43" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="D1484" s="43" t="s">
+        <v>3012</v>
+      </c>
+      <c r="E1484" s="43" t="s">
         <v>3014</v>
-      </c>
-      <c r="E1484" s="43" t="s">
-        <v>3016</v>
       </c>
       <c r="F1484" s="43"/>
       <c r="G1484" s="7"/>
     </row>
     <row r="1485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1485" s="7" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="B1485" s="7" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C1485" s="43" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="D1485" s="43" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="E1485" s="43"/>
       <c r="F1485" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E4B593-2C31-4E22-A166-F3C19E72DB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94630B7-A698-408C-BFF2-804B34416C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="3018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="3021">
   <si>
     <t>Пароль</t>
   </si>
@@ -9069,9 +9069,6 @@
     <t>+79996917658</t>
   </si>
   <si>
-    <t>* Дима/ДанНя</t>
-  </si>
-  <si>
     <t>* ДимМа</t>
   </si>
   <si>
@@ -9088,6 +9085,18 @@
   </si>
   <si>
     <t>+79034896222</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/IlNNHtFhaAKItw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/QSlHLoiLMAnulw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/8P53TbS1Vo0aFA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/16LZnrUSKaGGIg</t>
   </si>
 </sst>
 </file>
@@ -35672,37 +35681,37 @@
         <v>3006</v>
       </c>
       <c r="C1482" s="43" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="D1482" s="43" t="s">
-        <v>3011</v>
+        <v>3017</v>
       </c>
       <c r="E1482" s="43" t="s">
-        <v>731</v>
+        <v>3018</v>
       </c>
       <c r="F1482" s="43" t="s">
-        <v>3011</v>
+        <v>3019</v>
       </c>
       <c r="G1482" s="7"/>
     </row>
     <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1483" s="7" t="s">
+        <v>3015</v>
+      </c>
+      <c r="B1483" s="7" t="s">
         <v>3016</v>
       </c>
-      <c r="B1483" s="7" t="s">
-        <v>3017</v>
-      </c>
       <c r="C1483" s="43" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="D1483" s="43" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="E1483" s="43" t="s">
-        <v>731</v>
+        <v>3018</v>
       </c>
       <c r="F1483" s="43" t="s">
-        <v>3012</v>
+        <v>3020</v>
       </c>
       <c r="G1483" s="7"/>
     </row>
@@ -35714,13 +35723,13 @@
         <v>3008</v>
       </c>
       <c r="C1484" s="43" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="D1484" s="43" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="E1484" s="43" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="F1484" s="43"/>
       <c r="G1484" s="7"/>
@@ -35733,10 +35742,10 @@
         <v>3010</v>
       </c>
       <c r="C1485" s="43" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="D1485" s="43" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="E1485" s="43"/>
       <c r="F1485" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94630B7-A698-408C-BFF2-804B34416C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D582518E-71F8-44C2-9DAE-B64C7730C967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9072,9 +9072,6 @@
     <t>* ДимМа</t>
   </si>
   <si>
-    <t>* Sheff</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
@@ -9097,6 +9094,9 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/i/16LZnrUSKaGGIg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/XPToMghn4tAkCA</t>
   </si>
 </sst>
 </file>
@@ -35681,37 +35681,37 @@
         <v>3006</v>
       </c>
       <c r="C1482" s="43" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="D1482" s="43" t="s">
+        <v>3016</v>
+      </c>
+      <c r="E1482" s="43" t="s">
         <v>3017</v>
       </c>
-      <c r="E1482" s="43" t="s">
+      <c r="F1482" s="43" t="s">
         <v>3018</v>
-      </c>
-      <c r="F1482" s="43" t="s">
-        <v>3019</v>
       </c>
       <c r="G1482" s="7"/>
     </row>
     <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1483" s="7" t="s">
+        <v>3014</v>
+      </c>
+      <c r="B1483" s="7" t="s">
         <v>3015</v>
       </c>
-      <c r="B1483" s="7" t="s">
-        <v>3016</v>
-      </c>
       <c r="C1483" s="43" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="D1483" s="43" t="s">
         <v>3011</v>
       </c>
       <c r="E1483" s="43" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="F1483" s="43" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="G1483" s="7"/>
     </row>
@@ -35723,13 +35723,13 @@
         <v>3008</v>
       </c>
       <c r="C1484" s="43" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="D1484" s="43" t="s">
         <v>3011</v>
       </c>
       <c r="E1484" s="43" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="F1484" s="43"/>
       <c r="G1484" s="7"/>
@@ -35742,10 +35742,10 @@
         <v>3010</v>
       </c>
       <c r="C1485" s="43" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="D1485" s="43" t="s">
-        <v>3012</v>
+        <v>3020</v>
       </c>
       <c r="E1485" s="43"/>
       <c r="F1485" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D582518E-71F8-44C2-9DAE-B64C7730C967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439EDD4B-49B9-4398-945E-74D1B2942A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9069,15 +9069,9 @@
     <t>+79996917658</t>
   </si>
   <si>
-    <t>* ДимМа</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/Y9K86Gl45XwCTw</t>
-  </si>
-  <si>
     <t>96222</t>
   </si>
   <si>
@@ -9097,6 +9091,12 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/XPToMghn4tAkCA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/spDXPD5sV0sefQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/GgfTLa15Zmiz3w</t>
   </si>
 </sst>
 </file>
@@ -35681,37 +35681,37 @@
         <v>3006</v>
       </c>
       <c r="C1482" s="43" t="s">
-        <v>3013</v>
+        <v>3020</v>
       </c>
       <c r="D1482" s="43" t="s">
+        <v>3014</v>
+      </c>
+      <c r="E1482" s="43" t="s">
+        <v>3015</v>
+      </c>
+      <c r="F1482" s="43" t="s">
         <v>3016</v>
-      </c>
-      <c r="E1482" s="43" t="s">
-        <v>3017</v>
-      </c>
-      <c r="F1482" s="43" t="s">
-        <v>3018</v>
       </c>
       <c r="G1482" s="7"/>
     </row>
     <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1483" s="7" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="B1483" s="7" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C1483" s="43" t="s">
+        <v>3020</v>
+      </c>
+      <c r="D1483" s="43" t="s">
+        <v>3019</v>
+      </c>
+      <c r="E1483" s="43" t="s">
         <v>3015</v>
       </c>
-      <c r="C1483" s="43" t="s">
-        <v>3013</v>
-      </c>
-      <c r="D1483" s="43" t="s">
-        <v>3011</v>
-      </c>
-      <c r="E1483" s="43" t="s">
+      <c r="F1483" s="43" t="s">
         <v>3017</v>
-      </c>
-      <c r="F1483" s="43" t="s">
-        <v>3019</v>
       </c>
       <c r="G1483" s="7"/>
     </row>
@@ -35723,13 +35723,13 @@
         <v>3008</v>
       </c>
       <c r="C1484" s="43" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="D1484" s="43" t="s">
+        <v>3019</v>
+      </c>
+      <c r="E1484" s="43" t="s">
         <v>3011</v>
-      </c>
-      <c r="E1484" s="43" t="s">
-        <v>3012</v>
       </c>
       <c r="F1484" s="43"/>
       <c r="G1484" s="7"/>
@@ -35742,10 +35742,10 @@
         <v>3010</v>
       </c>
       <c r="C1485" s="43" t="s">
-        <v>3013</v>
+        <v>3020</v>
       </c>
       <c r="D1485" s="43" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="E1485" s="43"/>
       <c r="F1485" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439EDD4B-49B9-4398-945E-74D1B2942A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2698B91-4714-4C5E-B3D5-9C7B11B745EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="3021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="3026">
   <si>
     <t>Пароль</t>
   </si>
@@ -9097,6 +9097,21 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/GgfTLa15Zmiz3w</t>
+  </si>
+  <si>
+    <t>18/10/26/12:30</t>
+  </si>
+  <si>
+    <t>60883</t>
+  </si>
+  <si>
+    <t>+79066060883</t>
+  </si>
+  <si>
+    <t>48035</t>
+  </si>
+  <si>
+    <t>+79224548035</t>
   </si>
 </sst>
 </file>
@@ -35752,7 +35767,9 @@
       <c r="G1485" s="7"/>
     </row>
     <row r="1486" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1486" s="7"/>
+      <c r="A1486" s="37" t="s">
+        <v>3021</v>
+      </c>
       <c r="B1486" s="7"/>
       <c r="C1486" s="43"/>
       <c r="D1486" s="43"/>
@@ -35761,19 +35778,35 @@
       <c r="G1486" s="7"/>
     </row>
     <row r="1487" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1487" s="7"/>
-      <c r="B1487" s="7"/>
+      <c r="A1487" s="7" t="s">
+        <v>3022</v>
+      </c>
+      <c r="B1487" s="7" t="s">
+        <v>3023</v>
+      </c>
       <c r="C1487" s="43"/>
       <c r="D1487" s="43"/>
-      <c r="E1487" s="43"/>
-      <c r="F1487" s="43"/>
+      <c r="E1487" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1487" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1487" s="7"/>
     </row>
     <row r="1488" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1488" s="7"/>
-      <c r="B1488" s="7"/>
-      <c r="C1488" s="43"/>
-      <c r="D1488" s="43"/>
+      <c r="A1488" s="7" t="s">
+        <v>3024</v>
+      </c>
+      <c r="B1488" s="7" t="s">
+        <v>3025</v>
+      </c>
+      <c r="C1488" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1488" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="E1488" s="43"/>
       <c r="F1488" s="43"/>
       <c r="G1488" s="7"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2698B91-4714-4C5E-B3D5-9C7B11B745EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286CAB37-BA4F-4661-90B7-9E307B151CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="3026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="3030">
   <si>
     <t>Пароль</t>
   </si>
@@ -9112,6 +9112,18 @@
   </si>
   <si>
     <t>+79224548035</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/okcR_HZIHudX9w</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Vfctie4JBaSYHQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/mux0bNdJeD6vwQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/8U96XkcaRTBaLg</t>
   </si>
 </sst>
 </file>
@@ -35787,10 +35799,10 @@
       <c r="C1487" s="43"/>
       <c r="D1487" s="43"/>
       <c r="E1487" s="43" t="s">
-        <v>731</v>
+        <v>3027</v>
       </c>
       <c r="F1487" s="43" t="s">
-        <v>731</v>
+        <v>3026</v>
       </c>
       <c r="G1487" s="7"/>
     </row>
@@ -35802,10 +35814,10 @@
         <v>3025</v>
       </c>
       <c r="C1488" s="43" t="s">
-        <v>731</v>
+        <v>3029</v>
       </c>
       <c r="D1488" s="43" t="s">
-        <v>731</v>
+        <v>3028</v>
       </c>
       <c r="E1488" s="43"/>
       <c r="F1488" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286CAB37-BA4F-4661-90B7-9E307B151CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A61205F-4FEB-4458-94CD-1F585C8488D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="3030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4610" uniqueCount="3035">
   <si>
     <t>Пароль</t>
   </si>
@@ -9124,6 +9124,21 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/8U96XkcaRTBaLg</t>
+  </si>
+  <si>
+    <t>20/10/26/16:00</t>
+  </si>
+  <si>
+    <t>51918</t>
+  </si>
+  <si>
+    <t>+79186751918</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/PLYI9ni_OtC3gA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/fEQgpB8NuxEnWg</t>
   </si>
 </sst>
 </file>
@@ -35824,7 +35839,9 @@
       <c r="G1488" s="7"/>
     </row>
     <row r="1489" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1489" s="7"/>
+      <c r="A1489" s="37" t="s">
+        <v>3030</v>
+      </c>
       <c r="B1489" s="7"/>
       <c r="C1489" s="43"/>
       <c r="D1489" s="43"/>
@@ -35833,12 +35850,24 @@
       <c r="G1489" s="7"/>
     </row>
     <row r="1490" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1490" s="7"/>
-      <c r="B1490" s="7"/>
-      <c r="C1490" s="43"/>
-      <c r="D1490" s="43"/>
-      <c r="E1490" s="43"/>
-      <c r="F1490" s="43"/>
+      <c r="A1490" s="7" t="s">
+        <v>3031</v>
+      </c>
+      <c r="B1490" s="7" t="s">
+        <v>3032</v>
+      </c>
+      <c r="C1490" s="43" t="s">
+        <v>3034</v>
+      </c>
+      <c r="D1490" s="43" t="s">
+        <v>3033</v>
+      </c>
+      <c r="E1490" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1490" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1490" s="7"/>
     </row>
     <row r="1491" spans="1:7" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A61205F-4FEB-4458-94CD-1F585C8488D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693C4403-40F9-4D33-A048-0057E0219E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4610" uniqueCount="3035">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4610" uniqueCount="3037">
   <si>
     <t>Пароль</t>
   </si>
@@ -9139,6 +9139,12 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/fEQgpB8NuxEnWg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/bgt3VSnMKfUPpA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/oF2wb-dZ2K5kFQ</t>
   </si>
 </sst>
 </file>
@@ -35863,10 +35869,10 @@
         <v>3033</v>
       </c>
       <c r="E1490" s="43" t="s">
-        <v>731</v>
+        <v>3036</v>
       </c>
       <c r="F1490" s="43" t="s">
-        <v>731</v>
+        <v>3035</v>
       </c>
       <c r="G1490" s="7"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693C4403-40F9-4D33-A048-0057E0219E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560A5C80-89AE-452C-88D8-704552590001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4610" uniqueCount="3037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="3041">
   <si>
     <t>Пароль</t>
   </si>
@@ -9145,6 +9145,18 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/oF2wb-dZ2K5kFQ</t>
+  </si>
+  <si>
+    <t>23/10/26/12:00</t>
+  </si>
+  <si>
+    <t>49444</t>
+  </si>
+  <si>
+    <t>+79183449444</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/NB32X53SBNnsLQ</t>
   </si>
 </sst>
 </file>
@@ -35877,7 +35889,9 @@
       <c r="G1490" s="7"/>
     </row>
     <row r="1491" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1491" s="7"/>
+      <c r="A1491" s="37" t="s">
+        <v>3037</v>
+      </c>
       <c r="B1491" s="7"/>
       <c r="C1491" s="43"/>
       <c r="D1491" s="43"/>
@@ -35886,10 +35900,16 @@
       <c r="G1491" s="7"/>
     </row>
     <row r="1492" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1492" s="7"/>
-      <c r="B1492" s="7"/>
+      <c r="A1492" s="7" t="s">
+        <v>3038</v>
+      </c>
+      <c r="B1492" s="7" t="s">
+        <v>3039</v>
+      </c>
       <c r="C1492" s="43"/>
-      <c r="D1492" s="43"/>
+      <c r="D1492" s="43" t="s">
+        <v>3040</v>
+      </c>
       <c r="E1492" s="43"/>
       <c r="F1492" s="43"/>
       <c r="G1492" s="7"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560A5C80-89AE-452C-88D8-704552590001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD7CF52-C6AD-4F96-9E8C-59AAA161F499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="3041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="3070">
   <si>
     <t>Пароль</t>
   </si>
@@ -9157,6 +9157,93 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/NB32X53SBNnsLQ</t>
+  </si>
+  <si>
+    <t>24/10/26/10:00</t>
+  </si>
+  <si>
+    <t>90399</t>
+  </si>
+  <si>
+    <t>+79281390399</t>
+  </si>
+  <si>
+    <t>67349</t>
+  </si>
+  <si>
+    <t>+79092967349</t>
+  </si>
+  <si>
+    <t>24/10/26/15:00</t>
+  </si>
+  <si>
+    <t>77792</t>
+  </si>
+  <si>
+    <t>+79649177792</t>
+  </si>
+  <si>
+    <t>57853</t>
+  </si>
+  <si>
+    <t>+79528357853</t>
+  </si>
+  <si>
+    <t>26366</t>
+  </si>
+  <si>
+    <t>+79054726366</t>
+  </si>
+  <si>
+    <t>31213</t>
+  </si>
+  <si>
+    <t>+79894331213</t>
+  </si>
+  <si>
+    <t>*  ДимМа</t>
+  </si>
+  <si>
+    <t>? ДимМа</t>
+  </si>
+  <si>
+    <t>* ДимМа</t>
+  </si>
+  <si>
+    <t>25/10/26/11:00</t>
+  </si>
+  <si>
+    <t>09296</t>
+  </si>
+  <si>
+    <t>+79892409296</t>
+  </si>
+  <si>
+    <t>25/10/26/12:30</t>
+  </si>
+  <si>
+    <t>09503</t>
+  </si>
+  <si>
+    <t>+79182309503</t>
+  </si>
+  <si>
+    <t>83797</t>
+  </si>
+  <si>
+    <t>+79788583797</t>
+  </si>
+  <si>
+    <t>00041</t>
+  </si>
+  <si>
+    <t>+79275000041</t>
+  </si>
+  <si>
+    <t>24507</t>
+  </si>
+  <si>
+    <t>+79045024507</t>
   </si>
 </sst>
 </file>
@@ -35917,14 +36004,24 @@
     <row r="1493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1493" s="7"/>
       <c r="B1493" s="7"/>
-      <c r="C1493" s="43"/>
-      <c r="D1493" s="43"/>
-      <c r="E1493" s="43"/>
-      <c r="F1493" s="43"/>
+      <c r="C1493" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1493" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1493" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1493" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1493" s="7"/>
     </row>
     <row r="1494" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1494" s="7"/>
+      <c r="A1494" s="37" t="s">
+        <v>3041</v>
+      </c>
       <c r="B1494" s="7"/>
       <c r="C1494" s="43"/>
       <c r="D1494" s="43"/>
@@ -35933,25 +36030,49 @@
       <c r="G1494" s="7"/>
     </row>
     <row r="1495" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1495" s="7"/>
-      <c r="B1495" s="7"/>
+      <c r="A1495" s="7" t="s">
+        <v>3042</v>
+      </c>
+      <c r="B1495" s="7" t="s">
+        <v>3043</v>
+      </c>
       <c r="C1495" s="43"/>
-      <c r="D1495" s="43"/>
-      <c r="E1495" s="43"/>
-      <c r="F1495" s="43"/>
+      <c r="D1495" s="43" t="s">
+        <v>3055</v>
+      </c>
+      <c r="E1495" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1495" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1495" s="7"/>
     </row>
     <row r="1496" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1496" s="7"/>
-      <c r="B1496" s="7"/>
-      <c r="C1496" s="43"/>
-      <c r="D1496" s="43"/>
-      <c r="E1496" s="43"/>
-      <c r="F1496" s="43"/>
+      <c r="A1496" s="7" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B1496" s="7" t="s">
+        <v>3045</v>
+      </c>
+      <c r="C1496" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1496" s="43" t="s">
+        <v>3056</v>
+      </c>
+      <c r="E1496" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1496" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1496" s="7"/>
     </row>
     <row r="1497" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1497" s="7"/>
+      <c r="A1497" s="37" t="s">
+        <v>3046</v>
+      </c>
       <c r="B1497" s="7"/>
       <c r="C1497" s="43"/>
       <c r="D1497" s="43"/>
@@ -35960,43 +36081,69 @@
       <c r="G1497" s="7"/>
     </row>
     <row r="1498" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1498" s="7"/>
-      <c r="B1498" s="7"/>
-      <c r="C1498" s="43"/>
+      <c r="A1498" s="7" t="s">
+        <v>3047</v>
+      </c>
+      <c r="B1498" s="7" t="s">
+        <v>3048</v>
+      </c>
+      <c r="C1498" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1498" s="43"/>
       <c r="E1498" s="43"/>
       <c r="F1498" s="43"/>
       <c r="G1498" s="7"/>
     </row>
     <row r="1499" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1499" s="7"/>
-      <c r="B1499" s="7"/>
-      <c r="C1499" s="43"/>
+      <c r="A1499" s="7" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B1499" s="7" t="s">
+        <v>3050</v>
+      </c>
+      <c r="C1499" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1499" s="43"/>
       <c r="E1499" s="43"/>
       <c r="F1499" s="43"/>
       <c r="G1499" s="7"/>
     </row>
     <row r="1500" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1500" s="7"/>
-      <c r="B1500" s="7"/>
+      <c r="A1500" s="7" t="s">
+        <v>3051</v>
+      </c>
+      <c r="B1500" s="7" t="s">
+        <v>3052</v>
+      </c>
       <c r="C1500" s="43"/>
-      <c r="D1500" s="43"/>
+      <c r="D1500" s="43" t="s">
+        <v>3057</v>
+      </c>
       <c r="E1500" s="43"/>
       <c r="F1500" s="43"/>
       <c r="G1500" s="7"/>
     </row>
     <row r="1501" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1501" s="7"/>
-      <c r="B1501" s="7"/>
+      <c r="A1501" s="7" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B1501" s="7" t="s">
+        <v>3054</v>
+      </c>
       <c r="C1501" s="43"/>
-      <c r="D1501" s="43"/>
+      <c r="D1501" s="43" t="s">
+        <v>3057</v>
+      </c>
       <c r="E1501" s="43"/>
       <c r="F1501" s="43"/>
       <c r="G1501" s="7"/>
     </row>
     <row r="1502" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1502" s="7"/>
+      <c r="A1502" s="37" t="s">
+        <v>3058</v>
+      </c>
       <c r="B1502" s="7"/>
       <c r="C1502" s="43"/>
       <c r="D1502" s="43"/>
@@ -36005,16 +36152,26 @@
       <c r="G1502" s="7"/>
     </row>
     <row r="1503" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1503" s="7"/>
-      <c r="B1503" s="7"/>
+      <c r="A1503" s="7" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B1503" s="7" t="s">
+        <v>3060</v>
+      </c>
       <c r="C1503" s="43"/>
       <c r="D1503" s="43"/>
-      <c r="E1503" s="43"/>
-      <c r="F1503" s="43"/>
+      <c r="E1503" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1503" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1503" s="7"/>
     </row>
     <row r="1504" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1504" s="7"/>
+      <c r="A1504" s="37" t="s">
+        <v>3061</v>
+      </c>
       <c r="B1504" s="7"/>
       <c r="C1504" s="43"/>
       <c r="D1504" s="43"/>
@@ -36023,39 +36180,69 @@
       <c r="G1504" s="7"/>
     </row>
     <row r="1505" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1505" s="7"/>
-      <c r="B1505" s="7"/>
-      <c r="C1505" s="43"/>
+      <c r="A1505" s="7" t="s">
+        <v>3062</v>
+      </c>
+      <c r="B1505" s="7" t="s">
+        <v>3063</v>
+      </c>
+      <c r="C1505" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1505" s="43"/>
       <c r="E1505" s="43"/>
       <c r="F1505" s="43"/>
       <c r="G1505" s="7"/>
     </row>
     <row r="1506" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1506" s="7"/>
-      <c r="B1506" s="7"/>
+      <c r="A1506" s="7" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B1506" s="7" t="s">
+        <v>3065</v>
+      </c>
       <c r="C1506" s="43"/>
       <c r="D1506" s="43"/>
-      <c r="E1506" s="43"/>
-      <c r="F1506" s="43"/>
+      <c r="E1506" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1506" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1506" s="7"/>
     </row>
     <row r="1507" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1507" s="7"/>
-      <c r="B1507" s="7"/>
+      <c r="A1507" s="7" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B1507" s="7" t="s">
+        <v>3067</v>
+      </c>
       <c r="C1507" s="43"/>
       <c r="D1507" s="43"/>
-      <c r="E1507" s="43"/>
-      <c r="F1507" s="43"/>
+      <c r="E1507" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1507" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1507" s="7"/>
     </row>
     <row r="1508" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1508" s="7"/>
-      <c r="B1508" s="7"/>
+      <c r="A1508" s="7" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B1508" s="7" t="s">
+        <v>3069</v>
+      </c>
       <c r="C1508" s="43"/>
       <c r="D1508" s="43"/>
-      <c r="E1508" s="43"/>
-      <c r="F1508" s="43"/>
+      <c r="E1508" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1508" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1508" s="7"/>
     </row>
     <row r="1509" spans="1:7" x14ac:dyDescent="0.25">

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD7CF52-C6AD-4F96-9E8C-59AAA161F499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940A7CBC-333A-4554-A9B7-4E618767AF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="3070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="3073">
   <si>
     <t>Пароль</t>
   </si>
@@ -9201,9 +9201,6 @@
     <t>+79894331213</t>
   </si>
   <si>
-    <t>*  ДимМа</t>
-  </si>
-  <si>
     <t>? ДимМа</t>
   </si>
   <si>
@@ -9244,6 +9241,18 @@
   </si>
   <si>
     <t>+79045024507</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/HnrlReyfW2FYgQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/XMNHBU_XwumXYw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Lee-pTtY3a9gpA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/rkVRMFIJi1d_JA</t>
   </si>
 </sst>
 </file>
@@ -36038,7 +36047,7 @@
       </c>
       <c r="C1495" s="43"/>
       <c r="D1495" s="43" t="s">
-        <v>3055</v>
+        <v>3071</v>
       </c>
       <c r="E1495" s="43" t="s">
         <v>731</v>
@@ -36056,10 +36065,10 @@
         <v>3045</v>
       </c>
       <c r="C1496" s="43" t="s">
-        <v>731</v>
+        <v>3069</v>
       </c>
       <c r="D1496" s="43" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="E1496" s="43" t="s">
         <v>731</v>
@@ -36088,7 +36097,7 @@
         <v>3048</v>
       </c>
       <c r="C1498" s="43" t="s">
-        <v>731</v>
+        <v>3070</v>
       </c>
       <c r="D1498" s="43"/>
       <c r="E1498" s="43"/>
@@ -36103,7 +36112,7 @@
         <v>3050</v>
       </c>
       <c r="C1499" s="43" t="s">
-        <v>731</v>
+        <v>3070</v>
       </c>
       <c r="D1499" s="43"/>
       <c r="E1499" s="43"/>
@@ -36119,7 +36128,7 @@
       </c>
       <c r="C1500" s="43"/>
       <c r="D1500" s="43" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="E1500" s="43"/>
       <c r="F1500" s="43"/>
@@ -36134,7 +36143,7 @@
       </c>
       <c r="C1501" s="43"/>
       <c r="D1501" s="43" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="E1501" s="43"/>
       <c r="F1501" s="43"/>
@@ -36142,7 +36151,7 @@
     </row>
     <row r="1502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1502" s="37" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="B1502" s="7"/>
       <c r="C1502" s="43"/>
@@ -36153,10 +36162,10 @@
     </row>
     <row r="1503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1503" s="7" t="s">
+        <v>3058</v>
+      </c>
+      <c r="B1503" s="7" t="s">
         <v>3059</v>
-      </c>
-      <c r="B1503" s="7" t="s">
-        <v>3060</v>
       </c>
       <c r="C1503" s="43"/>
       <c r="D1503" s="43"/>
@@ -36170,7 +36179,7 @@
     </row>
     <row r="1504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1504" s="37" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1504" s="7"/>
       <c r="C1504" s="43"/>
@@ -36181,13 +36190,13 @@
     </row>
     <row r="1505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1505" s="7" t="s">
+        <v>3061</v>
+      </c>
+      <c r="B1505" s="7" t="s">
         <v>3062</v>
       </c>
-      <c r="B1505" s="7" t="s">
-        <v>3063</v>
-      </c>
       <c r="C1505" s="43" t="s">
-        <v>731</v>
+        <v>3072</v>
       </c>
       <c r="D1505" s="43"/>
       <c r="E1505" s="43"/>
@@ -36196,10 +36205,10 @@
     </row>
     <row r="1506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1506" s="7" t="s">
+        <v>3063</v>
+      </c>
+      <c r="B1506" s="7" t="s">
         <v>3064</v>
-      </c>
-      <c r="B1506" s="7" t="s">
-        <v>3065</v>
       </c>
       <c r="C1506" s="43"/>
       <c r="D1506" s="43"/>
@@ -36213,10 +36222,10 @@
     </row>
     <row r="1507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1507" s="7" t="s">
+        <v>3065</v>
+      </c>
+      <c r="B1507" s="7" t="s">
         <v>3066</v>
-      </c>
-      <c r="B1507" s="7" t="s">
-        <v>3067</v>
       </c>
       <c r="C1507" s="43"/>
       <c r="D1507" s="43"/>
@@ -36230,10 +36239,10 @@
     </row>
     <row r="1508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1508" s="7" t="s">
+        <v>3067</v>
+      </c>
+      <c r="B1508" s="7" t="s">
         <v>3068</v>
-      </c>
-      <c r="B1508" s="7" t="s">
-        <v>3069</v>
       </c>
       <c r="C1508" s="43"/>
       <c r="D1508" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940A7CBC-333A-4554-A9B7-4E618767AF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF79607-4058-4643-B11F-81469B029F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="3073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="3080">
   <si>
     <t>Пароль</t>
   </si>
@@ -9204,9 +9204,6 @@
     <t>? ДимМа</t>
   </si>
   <si>
-    <t>* ДимМа</t>
-  </si>
-  <si>
     <t>25/10/26/11:00</t>
   </si>
   <si>
@@ -9253,6 +9250,30 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/rkVRMFIJi1d_JA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/yuu1Ou4Cgtl39Q</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/PRmt2fALxCoQnA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/992h-b-qYjAFqg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/bMv3qOF3q-d8zg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/KnEwFYTBTQAIJA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/aRgsOJ4Z_89Ldw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/oCXafH6Yd1DqrQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/JnMeR6tm70UAsw</t>
   </si>
 </sst>
 </file>
@@ -36047,13 +36068,13 @@
       </c>
       <c r="C1495" s="43"/>
       <c r="D1495" s="43" t="s">
-        <v>3071</v>
+        <v>3079</v>
       </c>
       <c r="E1495" s="43" t="s">
-        <v>731</v>
+        <v>3073</v>
       </c>
       <c r="F1495" s="43" t="s">
-        <v>731</v>
+        <v>3072</v>
       </c>
       <c r="G1495" s="7"/>
     </row>
@@ -36065,16 +36086,16 @@
         <v>3045</v>
       </c>
       <c r="C1496" s="43" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="D1496" s="43" t="s">
         <v>3055</v>
       </c>
       <c r="E1496" s="43" t="s">
-        <v>731</v>
+        <v>3073</v>
       </c>
       <c r="F1496" s="43" t="s">
-        <v>731</v>
+        <v>3072</v>
       </c>
       <c r="G1496" s="7"/>
     </row>
@@ -36097,7 +36118,7 @@
         <v>3048</v>
       </c>
       <c r="C1498" s="43" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="D1498" s="43"/>
       <c r="E1498" s="43"/>
@@ -36112,7 +36133,7 @@
         <v>3050</v>
       </c>
       <c r="C1499" s="43" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="D1499" s="43"/>
       <c r="E1499" s="43"/>
@@ -36128,7 +36149,7 @@
       </c>
       <c r="C1500" s="43"/>
       <c r="D1500" s="43" t="s">
-        <v>3056</v>
+        <v>3070</v>
       </c>
       <c r="E1500" s="43"/>
       <c r="F1500" s="43"/>
@@ -36143,7 +36164,7 @@
       </c>
       <c r="C1501" s="43"/>
       <c r="D1501" s="43" t="s">
-        <v>3056</v>
+        <v>3070</v>
       </c>
       <c r="E1501" s="43"/>
       <c r="F1501" s="43"/>
@@ -36151,7 +36172,7 @@
     </row>
     <row r="1502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1502" s="37" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="B1502" s="7"/>
       <c r="C1502" s="43"/>
@@ -36162,24 +36183,24 @@
     </row>
     <row r="1503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1503" s="7" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B1503" s="7" t="s">
         <v>3058</v>
-      </c>
-      <c r="B1503" s="7" t="s">
-        <v>3059</v>
       </c>
       <c r="C1503" s="43"/>
       <c r="D1503" s="43"/>
       <c r="E1503" s="43" t="s">
-        <v>731</v>
+        <v>3074</v>
       </c>
       <c r="F1503" s="43" t="s">
-        <v>731</v>
+        <v>3076</v>
       </c>
       <c r="G1503" s="7"/>
     </row>
     <row r="1504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1504" s="37" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B1504" s="7"/>
       <c r="C1504" s="43"/>
@@ -36190,13 +36211,13 @@
     </row>
     <row r="1505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1505" s="7" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B1505" s="7" t="s">
         <v>3061</v>
       </c>
-      <c r="B1505" s="7" t="s">
-        <v>3062</v>
-      </c>
       <c r="C1505" s="43" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="D1505" s="43"/>
       <c r="E1505" s="43"/>
@@ -36205,52 +36226,52 @@
     </row>
     <row r="1506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1506" s="7" t="s">
+        <v>3062</v>
+      </c>
+      <c r="B1506" s="7" t="s">
         <v>3063</v>
-      </c>
-      <c r="B1506" s="7" t="s">
-        <v>3064</v>
       </c>
       <c r="C1506" s="43"/>
       <c r="D1506" s="43"/>
       <c r="E1506" s="43" t="s">
-        <v>731</v>
+        <v>3075</v>
       </c>
       <c r="F1506" s="43" t="s">
-        <v>731</v>
+        <v>3078</v>
       </c>
       <c r="G1506" s="7"/>
     </row>
     <row r="1507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1507" s="7" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B1507" s="7" t="s">
         <v>3065</v>
-      </c>
-      <c r="B1507" s="7" t="s">
-        <v>3066</v>
       </c>
       <c r="C1507" s="43"/>
       <c r="D1507" s="43"/>
       <c r="E1507" s="43" t="s">
-        <v>731</v>
+        <v>3075</v>
       </c>
       <c r="F1507" s="43" t="s">
-        <v>731</v>
+        <v>3077</v>
       </c>
       <c r="G1507" s="7"/>
     </row>
     <row r="1508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1508" s="7" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B1508" s="7" t="s">
         <v>3067</v>
-      </c>
-      <c r="B1508" s="7" t="s">
-        <v>3068</v>
       </c>
       <c r="C1508" s="43"/>
       <c r="D1508" s="43"/>
       <c r="E1508" s="43" t="s">
-        <v>731</v>
+        <v>3075</v>
       </c>
       <c r="F1508" s="43" t="s">
-        <v>731</v>
+        <v>3077</v>
       </c>
       <c r="G1508" s="7"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF79607-4058-4643-B11F-81469B029F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E658B339-FCB3-4E13-A2C8-2DC1E2CF264C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8703,9 +8703,6 @@
     <t>!https://disk.yandex.ru/d/w8_g3g1dKVk9Bg</t>
   </si>
   <si>
-    <t>!https://disk.yandex.ru/d/Xlj5JdmGvFsPIA</t>
-  </si>
-  <si>
     <t>!https://disk.yandex.ru/d/tC9K-oTdrp79lw</t>
   </si>
   <si>
@@ -8745,9 +8742,6 @@
     <t>!https://disk.yandex.ru/d/7yOPZjleeyUa5w</t>
   </si>
   <si>
-    <t>!https://disk.yandex.ru/d/-H5lAKsT8SR4eg</t>
-  </si>
-  <si>
     <t>!https://disk.yandex.ru/d/oaSt3Co4L92WRQ</t>
   </si>
   <si>
@@ -9274,6 +9268,12 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/JnMeR6tm70UAsw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/-H5lAKsT8SR4eg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Xlj5JdmGvFsPIA</t>
   </si>
 </sst>
 </file>
@@ -32525,7 +32525,7 @@
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1265" s="32" t="s">
-        <v>2946</v>
+        <v>2944</v>
       </c>
       <c r="B1265" s="33">
         <v>79787819232</v>
@@ -32571,7 +32571,7 @@
     </row>
     <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1268" s="32" t="s">
-        <v>2947</v>
+        <v>2945</v>
       </c>
       <c r="B1268" s="33">
         <v>79181206771</v>
@@ -32593,7 +32593,7 @@
     </row>
     <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1269" s="32" t="s">
-        <v>2948</v>
+        <v>2946</v>
       </c>
       <c r="B1269" s="33">
         <v>79286136662</v>
@@ -32621,7 +32621,7 @@
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1271" s="18" t="s">
-        <v>2949</v>
+        <v>2947</v>
       </c>
       <c r="B1271" s="39">
         <v>375297856891</v>
@@ -32655,7 +32655,7 @@
     </row>
     <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1273" s="32" t="s">
-        <v>2950</v>
+        <v>2948</v>
       </c>
       <c r="B1273" s="33">
         <v>79189218545</v>
@@ -32683,7 +32683,7 @@
     </row>
     <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1275" s="18" t="s">
-        <v>2951</v>
+        <v>2949</v>
       </c>
       <c r="B1275" s="39">
         <v>79883302117</v>
@@ -32701,7 +32701,7 @@
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1276" s="32" t="s">
-        <v>2952</v>
+        <v>2950</v>
       </c>
       <c r="B1276" s="33">
         <v>79885414599</v>
@@ -32717,7 +32717,7 @@
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1277" s="32" t="s">
-        <v>2953</v>
+        <v>2951</v>
       </c>
       <c r="B1277" s="33">
         <v>79606987172</v>
@@ -32747,7 +32747,7 @@
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1279" s="32" t="s">
-        <v>2954</v>
+        <v>2952</v>
       </c>
       <c r="B1279" s="33">
         <v>79002702201</v>
@@ -33485,11 +33485,11 @@
         <v>79186195666</v>
       </c>
       <c r="C1325" s="3" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="D1325" s="3"/>
       <c r="E1325" s="3" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="F1325" s="3" t="s">
         <v>2479</v>
@@ -34246,7 +34246,7 @@
         <v>2888</v>
       </c>
       <c r="D1375" s="3" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="E1375" s="3"/>
       <c r="F1375" s="3"/>
@@ -34279,20 +34279,20 @@
       <c r="G1377" s="2"/>
     </row>
     <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1378" s="6" t="s">
+      <c r="A1378" s="8" t="s">
         <v>2654</v>
       </c>
-      <c r="B1378" s="17">
+      <c r="B1378" s="42">
         <v>79803218503</v>
       </c>
-      <c r="C1378" s="3" t="s">
-        <v>2889</v>
-      </c>
-      <c r="D1378" s="3"/>
-      <c r="E1378" s="3" t="s">
-        <v>2903</v>
-      </c>
-      <c r="F1378" s="3" t="s">
+      <c r="C1378" s="5" t="s">
+        <v>3079</v>
+      </c>
+      <c r="D1378" s="5"/>
+      <c r="E1378" s="5" t="s">
+        <v>3078</v>
+      </c>
+      <c r="F1378" s="5" t="s">
         <v>2655</v>
       </c>
       <c r="G1378" s="2"/>
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C1381" s="3"/>
       <c r="D1381" s="3" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="E1381" s="3"/>
       <c r="F1381" s="3"/>
@@ -34348,10 +34348,10 @@
         <v>79381241749</v>
       </c>
       <c r="C1382" s="3" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="D1382" s="3" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="E1382" s="3"/>
       <c r="F1382" s="3"/>
@@ -34365,7 +34365,7 @@
         <v>79183931723</v>
       </c>
       <c r="C1383" s="3" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="D1383" s="3"/>
       <c r="E1383" s="3"/>
@@ -34393,13 +34393,13 @@
         <v>79895207444</v>
       </c>
       <c r="C1385" s="3" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="D1385" s="3" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="E1385" s="3" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="F1385" s="3" t="s">
         <v>2717</v>
@@ -34415,7 +34415,7 @@
         <v>79054396611</v>
       </c>
       <c r="C1386" s="3" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="D1386" s="3"/>
       <c r="E1386" s="3"/>
@@ -34431,7 +34431,7 @@
         <v>79189914636</v>
       </c>
       <c r="C1387" s="3" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="D1387" s="3"/>
       <c r="E1387" s="3"/>
@@ -34447,10 +34447,10 @@
         <v>79281644488</v>
       </c>
       <c r="C1388" s="3" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="D1388" s="3" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="E1388" s="3"/>
       <c r="F1388" s="3"/>
@@ -34478,7 +34478,7 @@
       </c>
       <c r="C1390" s="3"/>
       <c r="D1390" s="3" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="E1390" s="3"/>
       <c r="F1390" s="3"/>
@@ -34493,10 +34493,10 @@
         <v>79034655195</v>
       </c>
       <c r="C1391" s="3" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="D1391" s="3" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="E1391" s="3"/>
       <c r="F1391" s="3"/>
@@ -34511,7 +34511,7 @@
         <v>79181891524</v>
       </c>
       <c r="C1392" s="3" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="D1392" s="3"/>
       <c r="E1392" s="3"/>
@@ -34527,10 +34527,10 @@
         <v>79197527391</v>
       </c>
       <c r="C1393" s="3" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="D1393" s="3" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="E1393" s="3"/>
       <c r="F1393" s="3"/>
@@ -34546,7 +34546,7 @@
       </c>
       <c r="C1394" s="3"/>
       <c r="D1394" s="3" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="E1394" s="3"/>
       <c r="F1394" s="3"/>
@@ -34593,7 +34593,7 @@
       <c r="C1397" s="3"/>
       <c r="D1397" s="3"/>
       <c r="E1397" s="3" t="s">
-        <v>2905</v>
+        <v>2903</v>
       </c>
       <c r="F1397" s="3" t="s">
         <v>2726</v>
@@ -34621,10 +34621,10 @@
         <v>79892315277</v>
       </c>
       <c r="C1399" s="3" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="D1399" s="3" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="E1399" s="3"/>
       <c r="F1399" s="3"/>
@@ -34639,11 +34639,11 @@
         <v>79182323366</v>
       </c>
       <c r="C1400" s="3" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="D1400" s="3"/>
       <c r="E1400" s="3" t="s">
-        <v>2906</v>
+        <v>2904</v>
       </c>
       <c r="F1400" s="3" t="s">
         <v>2727</v>
@@ -34671,7 +34671,7 @@
         <v>79937726026</v>
       </c>
       <c r="C1402" s="3" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="D1402" s="3"/>
       <c r="E1402" s="3"/>
@@ -35205,7 +35205,7 @@
     </row>
     <row r="1437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1437" s="37" t="s">
-        <v>2907</v>
+        <v>2905</v>
       </c>
       <c r="B1437" s="16"/>
       <c r="C1437" s="2"/>
@@ -35215,7 +35215,7 @@
     </row>
     <row r="1438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1438" s="7" t="s">
-        <v>2908</v>
+        <v>2906</v>
       </c>
       <c r="B1438" s="16">
         <v>79034397172</v>
@@ -35223,15 +35223,15 @@
       <c r="C1438" s="2"/>
       <c r="D1438" s="2"/>
       <c r="E1438" s="2" t="s">
-        <v>2916</v>
+        <v>2914</v>
       </c>
       <c r="F1438" s="2" t="s">
-        <v>2915</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="1439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1439" s="37" t="s">
-        <v>2910</v>
+        <v>2908</v>
       </c>
       <c r="C1439" s="2"/>
       <c r="D1439" s="2"/>
@@ -35240,21 +35240,21 @@
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1440" s="7" t="s">
-        <v>2909</v>
+        <v>2907</v>
       </c>
       <c r="B1440" s="16">
         <v>79493830457</v>
       </c>
       <c r="C1440" s="2"/>
       <c r="D1440" s="2" t="s">
-        <v>2917</v>
+        <v>2915</v>
       </c>
       <c r="E1440" s="2"/>
       <c r="F1440" s="2"/>
     </row>
     <row r="1441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1441" s="37" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="B1441" s="16"/>
       <c r="C1441" s="2"/>
@@ -35264,14 +35264,14 @@
     </row>
     <row r="1442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1442" s="7" t="s">
-        <v>2912</v>
+        <v>2910</v>
       </c>
       <c r="B1442" s="16">
         <v>79030000959</v>
       </c>
       <c r="C1442" s="2"/>
       <c r="D1442" s="2" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="E1442" s="2"/>
       <c r="F1442" s="2"/>
@@ -35294,7 +35294,7 @@
     </row>
     <row r="1444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1444" s="37" t="s">
-        <v>2919</v>
+        <v>2917</v>
       </c>
       <c r="B1444" s="16"/>
       <c r="C1444" s="2"/>
@@ -35304,29 +35304,29 @@
     </row>
     <row r="1445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1445" s="7" t="s">
-        <v>2920</v>
+        <v>2918</v>
       </c>
       <c r="B1445" s="16">
         <v>79181311990</v>
       </c>
       <c r="C1445" s="2" t="s">
-        <v>2935</v>
+        <v>2933</v>
       </c>
       <c r="D1445" s="2" t="s">
-        <v>2936</v>
+        <v>2934</v>
       </c>
       <c r="E1445" s="2"/>
       <c r="F1445" s="2"/>
     </row>
     <row r="1446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1446" s="7" t="s">
-        <v>2921</v>
+        <v>2919</v>
       </c>
       <c r="B1446" s="16">
         <v>79221892567</v>
       </c>
       <c r="C1446" s="2" t="s">
-        <v>2935</v>
+        <v>2933</v>
       </c>
       <c r="D1446" s="2"/>
       <c r="E1446" s="2"/>
@@ -35334,13 +35334,13 @@
     </row>
     <row r="1447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1447" s="7" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="B1447" s="16">
         <v>79189219714</v>
       </c>
       <c r="C1447" s="2" t="s">
-        <v>2935</v>
+        <v>2933</v>
       </c>
       <c r="D1447" s="2"/>
       <c r="E1447" s="2"/>
@@ -35348,7 +35348,7 @@
     </row>
     <row r="1448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1448" s="37" t="s">
-        <v>2923</v>
+        <v>2921</v>
       </c>
       <c r="B1448" s="16"/>
       <c r="C1448" s="2"/>
@@ -35358,13 +35358,13 @@
     </row>
     <row r="1449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1449" s="7" t="s">
-        <v>2924</v>
+        <v>2922</v>
       </c>
       <c r="B1449" s="16">
         <v>79898382391</v>
       </c>
       <c r="C1449" s="2" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
       <c r="D1449" s="2"/>
       <c r="E1449" s="2"/>
@@ -35372,53 +35372,53 @@
     </row>
     <row r="1450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1450" s="7" t="s">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="B1450" s="16">
         <v>79867392843</v>
       </c>
       <c r="C1450" s="2"/>
       <c r="D1450" s="2" t="s">
-        <v>2938</v>
+        <v>2936</v>
       </c>
       <c r="E1450" s="2"/>
       <c r="F1450" s="2"/>
     </row>
     <row r="1451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1451" s="7" t="s">
-        <v>2925</v>
+        <v>2923</v>
       </c>
       <c r="B1451" s="16">
         <v>79515340206</v>
       </c>
       <c r="C1451" s="2"/>
       <c r="D1451" s="2" t="s">
-        <v>2939</v>
+        <v>2937</v>
       </c>
       <c r="E1451" s="2"/>
       <c r="F1451" s="2"/>
     </row>
     <row r="1452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1452" s="7" t="s">
-        <v>2926</v>
+        <v>2924</v>
       </c>
       <c r="B1452" s="16">
         <v>79181058985</v>
       </c>
       <c r="C1452" s="2" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
       <c r="D1452" s="2" t="s">
-        <v>2937</v>
+        <v>2935</v>
       </c>
       <c r="E1452" s="2" t="s">
-        <v>2943</v>
+        <v>2941</v>
       </c>
       <c r="F1452" s="2"/>
     </row>
     <row r="1453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1453" s="37" t="s">
-        <v>2927</v>
+        <v>2925</v>
       </c>
       <c r="B1453" s="16"/>
       <c r="C1453" s="2"/>
@@ -35428,7 +35428,7 @@
     </row>
     <row r="1454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1454" s="7" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="B1454" s="16">
         <v>79094330806</v>
@@ -35436,52 +35436,52 @@
       <c r="C1454" s="2"/>
       <c r="D1454" s="2"/>
       <c r="E1454" s="2" t="s">
-        <v>2945</v>
+        <v>2943</v>
       </c>
       <c r="F1454" s="2" t="s">
-        <v>2944</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="1455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1455" s="7" t="s">
-        <v>2929</v>
+        <v>2927</v>
       </c>
       <c r="B1455" s="16">
         <v>79892969812</v>
       </c>
       <c r="C1455" s="2"/>
       <c r="D1455" s="2" t="s">
-        <v>2941</v>
+        <v>2939</v>
       </c>
       <c r="E1455" s="2"/>
       <c r="F1455" s="2"/>
     </row>
     <row r="1456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1456" s="7" t="s">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="B1456" s="16">
         <v>79038276326</v>
       </c>
       <c r="C1456" s="2" t="s">
-        <v>2934</v>
+        <v>2932</v>
       </c>
       <c r="D1456" s="2" t="s">
-        <v>2942</v>
+        <v>2940</v>
       </c>
       <c r="E1456" s="2"/>
       <c r="F1456" s="2"/>
     </row>
     <row r="1457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1457" s="7" t="s">
-        <v>2931</v>
+        <v>2929</v>
       </c>
       <c r="B1457" s="16">
         <v>79612832854</v>
       </c>
       <c r="C1457" s="2"/>
       <c r="D1457" s="2" t="s">
-        <v>2940</v>
+        <v>2938</v>
       </c>
       <c r="E1457" s="2"/>
       <c r="F1457" s="2"/>
@@ -35504,7 +35504,7 @@
     </row>
     <row r="1459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1459" s="37" t="s">
-        <v>2955</v>
+        <v>2953</v>
       </c>
       <c r="B1459" s="16"/>
       <c r="C1459" s="2"/>
@@ -35514,27 +35514,27 @@
     </row>
     <row r="1460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1460" s="7" t="s">
-        <v>2956</v>
+        <v>2954</v>
       </c>
       <c r="B1460" s="16">
         <v>79204054783</v>
       </c>
       <c r="C1460" s="2" t="s">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="D1460" s="2" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="E1460" s="2" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="F1460" s="2" t="s">
-        <v>2969</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="1461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1461" s="37" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="C1461" s="2"/>
       <c r="D1461" s="2"/>
@@ -35543,21 +35543,21 @@
     </row>
     <row r="1462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1462" s="7" t="s">
-        <v>2957</v>
+        <v>2955</v>
       </c>
       <c r="B1462" s="16">
         <v>79054008128</v>
       </c>
       <c r="C1462" s="2"/>
       <c r="D1462" s="2" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
       <c r="E1462" s="2"/>
       <c r="F1462" s="2"/>
     </row>
     <row r="1463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1463" s="7" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="B1463" s="16">
         <v>79788069407</v>
@@ -35565,29 +35565,29 @@
       <c r="C1463" s="2"/>
       <c r="D1463" s="2"/>
       <c r="E1463" s="2" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="F1463" s="2" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="1464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1464" s="7" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="B1464" s="16">
         <v>79054079005</v>
       </c>
       <c r="C1464" s="2"/>
       <c r="D1464" s="2" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
       <c r="E1464" s="2"/>
       <c r="F1464" s="2"/>
     </row>
     <row r="1465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1465" s="37" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="B1465" s="16"/>
       <c r="C1465" s="2"/>
@@ -35597,27 +35597,27 @@
     </row>
     <row r="1466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1466" s="7" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="B1466" s="16">
         <v>79530998771</v>
       </c>
       <c r="C1466" s="2" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="D1466" s="2" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="E1466" s="2" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="F1466" s="2" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="1467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1467" s="37" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
       <c r="B1467" s="16"/>
       <c r="C1467" s="16"/>
@@ -35634,16 +35634,16 @@
         <v>79282812167</v>
       </c>
       <c r="C1468" s="43" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="D1468" s="43" t="s">
+        <v>2978</v>
+      </c>
+      <c r="E1468" s="43" t="s">
+        <v>2981</v>
+      </c>
+      <c r="F1468" s="43" t="s">
         <v>2980</v>
-      </c>
-      <c r="E1468" s="43" t="s">
-        <v>2983</v>
-      </c>
-      <c r="F1468" s="43" t="s">
-        <v>2982</v>
       </c>
       <c r="G1468" s="7"/>
     </row>
@@ -35655,10 +35655,10 @@
         <v>79490875530</v>
       </c>
       <c r="C1469" s="43" t="s">
+        <v>2977</v>
+      </c>
+      <c r="D1469" s="43" t="s">
         <v>2979</v>
-      </c>
-      <c r="D1469" s="43" t="s">
-        <v>2981</v>
       </c>
       <c r="E1469" s="43"/>
       <c r="F1469" s="43"/>
@@ -35666,41 +35666,41 @@
     </row>
     <row r="1470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1470" s="7" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B1470" s="7">
         <v>79518401534</v>
       </c>
       <c r="C1470" s="43"/>
       <c r="D1470" s="43" t="s">
+        <v>2979</v>
+      </c>
+      <c r="E1470" s="43" t="s">
         <v>2981</v>
       </c>
-      <c r="E1470" s="43" t="s">
-        <v>2983</v>
-      </c>
       <c r="F1470" s="43" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="G1470" s="7"/>
     </row>
     <row r="1471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1471" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="B1471" s="7" t="s">
+        <v>2976</v>
+      </c>
+      <c r="C1471" s="43" t="s">
         <v>2977</v>
       </c>
-      <c r="B1471" s="7" t="s">
+      <c r="D1471" s="43" t="s">
         <v>2978</v>
       </c>
-      <c r="C1471" s="43" t="s">
-        <v>2979</v>
-      </c>
-      <c r="D1471" s="43" t="s">
+      <c r="E1471" s="43" t="s">
+        <v>2981</v>
+      </c>
+      <c r="F1471" s="43" t="s">
         <v>2980</v>
-      </c>
-      <c r="E1471" s="43" t="s">
-        <v>2983</v>
-      </c>
-      <c r="F1471" s="43" t="s">
-        <v>2982</v>
       </c>
       <c r="G1471" s="7"/>
     </row>
@@ -35723,7 +35723,7 @@
     </row>
     <row r="1473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1473" s="37" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
       <c r="B1473" s="7"/>
       <c r="C1473" s="43"/>
@@ -35734,16 +35734,16 @@
     </row>
     <row r="1474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1474" s="7" t="s">
-        <v>2985</v>
+        <v>2983</v>
       </c>
       <c r="B1474" s="7" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="C1474" s="43" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
       <c r="D1474" s="43" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="E1474" s="43"/>
       <c r="F1474" s="43"/>
@@ -35751,16 +35751,16 @@
     </row>
     <row r="1475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1475" s="7" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B1475" s="7" t="s">
-        <v>2988</v>
+        <v>2986</v>
       </c>
       <c r="C1475" s="43" t="s">
+        <v>2990</v>
+      </c>
+      <c r="D1475" s="43" t="s">
         <v>2992</v>
-      </c>
-      <c r="D1475" s="43" t="s">
-        <v>2994</v>
       </c>
       <c r="E1475" s="43"/>
       <c r="F1475" s="43"/>
@@ -35768,7 +35768,7 @@
     </row>
     <row r="1476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1476" s="37" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="B1476" s="7"/>
       <c r="C1476" s="43"/>
@@ -35779,14 +35779,14 @@
     </row>
     <row r="1477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1477" s="7" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B1477" s="7" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="C1477" s="43"/>
       <c r="D1477" s="43" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
       <c r="E1477" s="43"/>
       <c r="F1477" s="43"/>
@@ -35794,7 +35794,7 @@
     </row>
     <row r="1478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1478" s="37" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="B1478" s="7"/>
       <c r="C1478" s="43"/>
@@ -35805,20 +35805,20 @@
     </row>
     <row r="1479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1479" s="7" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="B1479" s="7" t="s">
+        <v>2996</v>
+      </c>
+      <c r="C1479" s="43" t="s">
         <v>2998</v>
-      </c>
-      <c r="C1479" s="43" t="s">
-        <v>3000</v>
       </c>
       <c r="D1479" s="43"/>
       <c r="E1479" s="43" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="F1479" s="43" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="G1479" s="7"/>
     </row>
@@ -35827,13 +35827,13 @@
         <v>2499</v>
       </c>
       <c r="B1480" s="7" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C1480" s="43" t="s">
+        <v>2998</v>
+      </c>
+      <c r="D1480" s="43" t="s">
         <v>2999</v>
-      </c>
-      <c r="C1480" s="43" t="s">
-        <v>3000</v>
-      </c>
-      <c r="D1480" s="43" t="s">
-        <v>3001</v>
       </c>
       <c r="E1480" s="43"/>
       <c r="F1480" s="43"/>
@@ -35841,7 +35841,7 @@
     </row>
     <row r="1481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1481" s="37" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="B1481" s="7"/>
       <c r="C1481" s="43"/>
@@ -35852,77 +35852,77 @@
     </row>
     <row r="1482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1482" s="7" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="B1482" s="7" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="C1482" s="43" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="D1482" s="43" t="s">
+        <v>3012</v>
+      </c>
+      <c r="E1482" s="43" t="s">
+        <v>3013</v>
+      </c>
+      <c r="F1482" s="43" t="s">
         <v>3014</v>
-      </c>
-      <c r="E1482" s="43" t="s">
-        <v>3015</v>
-      </c>
-      <c r="F1482" s="43" t="s">
-        <v>3016</v>
       </c>
       <c r="G1482" s="7"/>
     </row>
     <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1483" s="7" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="B1483" s="7" t="s">
+        <v>3011</v>
+      </c>
+      <c r="C1483" s="43" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D1483" s="43" t="s">
+        <v>3017</v>
+      </c>
+      <c r="E1483" s="43" t="s">
         <v>3013</v>
       </c>
-      <c r="C1483" s="43" t="s">
-        <v>3020</v>
-      </c>
-      <c r="D1483" s="43" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E1483" s="43" t="s">
+      <c r="F1483" s="43" t="s">
         <v>3015</v>
-      </c>
-      <c r="F1483" s="43" t="s">
-        <v>3017</v>
       </c>
       <c r="G1483" s="7"/>
     </row>
     <row r="1484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1484" s="7" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="B1484" s="7" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="C1484" s="43" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="D1484" s="43" t="s">
-        <v>3019</v>
+        <v>3017</v>
       </c>
       <c r="E1484" s="43" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="F1484" s="43"/>
       <c r="G1484" s="7"/>
     </row>
     <row r="1485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1485" s="7" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="B1485" s="7" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="C1485" s="43" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="D1485" s="43" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="E1485" s="43"/>
       <c r="F1485" s="43"/>
@@ -35930,7 +35930,7 @@
     </row>
     <row r="1486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1486" s="37" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="B1486" s="7"/>
       <c r="C1486" s="43"/>
@@ -35941,33 +35941,33 @@
     </row>
     <row r="1487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1487" s="7" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="B1487" s="7" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
       <c r="C1487" s="43"/>
       <c r="D1487" s="43"/>
       <c r="E1487" s="43" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="F1487" s="43" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="G1487" s="7"/>
     </row>
     <row r="1488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1488" s="7" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
       <c r="B1488" s="7" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="C1488" s="43" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
       <c r="D1488" s="43" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="E1488" s="43"/>
       <c r="F1488" s="43"/>
@@ -35975,7 +35975,7 @@
     </row>
     <row r="1489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1489" s="37" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
       <c r="B1489" s="7"/>
       <c r="C1489" s="43"/>
@@ -35986,28 +35986,28 @@
     </row>
     <row r="1490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1490" s="7" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B1490" s="7" t="s">
+        <v>3030</v>
+      </c>
+      <c r="C1490" s="43" t="s">
+        <v>3032</v>
+      </c>
+      <c r="D1490" s="43" t="s">
         <v>3031</v>
       </c>
-      <c r="B1490" s="7" t="s">
-        <v>3032</v>
-      </c>
-      <c r="C1490" s="43" t="s">
+      <c r="E1490" s="43" t="s">
         <v>3034</v>
       </c>
-      <c r="D1490" s="43" t="s">
+      <c r="F1490" s="43" t="s">
         <v>3033</v>
-      </c>
-      <c r="E1490" s="43" t="s">
-        <v>3036</v>
-      </c>
-      <c r="F1490" s="43" t="s">
-        <v>3035</v>
       </c>
       <c r="G1490" s="7"/>
     </row>
     <row r="1491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1491" s="37" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="B1491" s="7"/>
       <c r="C1491" s="43"/>
@@ -36018,14 +36018,14 @@
     </row>
     <row r="1492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1492" s="7" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="B1492" s="7" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="C1492" s="43"/>
       <c r="D1492" s="43" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
       <c r="E1492" s="43"/>
       <c r="F1492" s="43"/>
@@ -36050,7 +36050,7 @@
     </row>
     <row r="1494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1494" s="37" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="B1494" s="7"/>
       <c r="C1494" s="43"/>
@@ -36061,47 +36061,47 @@
     </row>
     <row r="1495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1495" s="7" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
       <c r="B1495" s="7" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="C1495" s="43"/>
       <c r="D1495" s="43" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="E1495" s="43" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="F1495" s="43" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
       <c r="G1495" s="7"/>
     </row>
     <row r="1496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1496" s="7" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="B1496" s="7" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="C1496" s="43" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
       <c r="D1496" s="43" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="E1496" s="43" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="F1496" s="43" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
       <c r="G1496" s="7"/>
     </row>
     <row r="1497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1497" s="37" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="B1497" s="7"/>
       <c r="C1497" s="43"/>
@@ -36112,13 +36112,13 @@
     </row>
     <row r="1498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1498" s="7" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="B1498" s="7" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
       <c r="C1498" s="43" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="D1498" s="43"/>
       <c r="E1498" s="43"/>
@@ -36127,13 +36127,13 @@
     </row>
     <row r="1499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1499" s="7" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="B1499" s="7" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
       <c r="C1499" s="43" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="D1499" s="43"/>
       <c r="E1499" s="43"/>
@@ -36142,14 +36142,14 @@
     </row>
     <row r="1500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1500" s="7" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="B1500" s="7" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="C1500" s="43"/>
       <c r="D1500" s="43" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
       <c r="E1500" s="43"/>
       <c r="F1500" s="43"/>
@@ -36157,14 +36157,14 @@
     </row>
     <row r="1501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1501" s="7" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="B1501" s="7" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="C1501" s="43"/>
       <c r="D1501" s="43" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
       <c r="E1501" s="43"/>
       <c r="F1501" s="43"/>
@@ -36172,7 +36172,7 @@
     </row>
     <row r="1502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1502" s="37" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="B1502" s="7"/>
       <c r="C1502" s="43"/>
@@ -36183,24 +36183,24 @@
     </row>
     <row r="1503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1503" s="7" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="B1503" s="7" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="C1503" s="43"/>
       <c r="D1503" s="43"/>
       <c r="E1503" s="43" t="s">
+        <v>3072</v>
+      </c>
+      <c r="F1503" s="43" t="s">
         <v>3074</v>
-      </c>
-      <c r="F1503" s="43" t="s">
-        <v>3076</v>
       </c>
       <c r="G1503" s="7"/>
     </row>
     <row r="1504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1504" s="37" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="B1504" s="7"/>
       <c r="C1504" s="43"/>
@@ -36211,13 +36211,13 @@
     </row>
     <row r="1505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1505" s="7" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
       <c r="B1505" s="7" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="C1505" s="43" t="s">
-        <v>3071</v>
+        <v>3069</v>
       </c>
       <c r="D1505" s="43"/>
       <c r="E1505" s="43"/>
@@ -36226,52 +36226,52 @@
     </row>
     <row r="1506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1506" s="7" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="B1506" s="7" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
       <c r="C1506" s="43"/>
       <c r="D1506" s="43"/>
       <c r="E1506" s="43" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
       <c r="F1506" s="43" t="s">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="G1506" s="7"/>
     </row>
     <row r="1507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1507" s="7" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="B1507" s="7" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="C1507" s="43"/>
       <c r="D1507" s="43"/>
       <c r="E1507" s="43" t="s">
+        <v>3073</v>
+      </c>
+      <c r="F1507" s="43" t="s">
         <v>3075</v>
-      </c>
-      <c r="F1507" s="43" t="s">
-        <v>3077</v>
       </c>
       <c r="G1507" s="7"/>
     </row>
     <row r="1508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1508" s="7" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
       <c r="B1508" s="7" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="C1508" s="43"/>
       <c r="D1508" s="43"/>
       <c r="E1508" s="43" t="s">
+        <v>3073</v>
+      </c>
+      <c r="F1508" s="43" t="s">
         <v>3075</v>
-      </c>
-      <c r="F1508" s="43" t="s">
-        <v>3077</v>
       </c>
       <c r="G1508" s="7"/>
     </row>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E658B339-FCB3-4E13-A2C8-2DC1E2CF264C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DCCBD5-5BB9-4300-ABD4-FDC41600F1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="3080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4682" uniqueCount="3091">
   <si>
     <t>Пароль</t>
   </si>
@@ -9274,6 +9274,39 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/Xlj5JdmGvFsPIA</t>
+  </si>
+  <si>
+    <t>26/10/26/11:00</t>
+  </si>
+  <si>
+    <t>34051</t>
+  </si>
+  <si>
+    <t>+79892134051</t>
+  </si>
+  <si>
+    <t>74107</t>
+  </si>
+  <si>
+    <t>+79182574107</t>
+  </si>
+  <si>
+    <t>15454</t>
+  </si>
+  <si>
+    <t>+79888915454</t>
+  </si>
+  <si>
+    <t>26/10/26/14:00</t>
+  </si>
+  <si>
+    <t>33111</t>
+  </si>
+  <si>
+    <t>+79180933111</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/9Ux122IKU_eUow</t>
   </si>
 </sst>
 </file>
@@ -36278,14 +36311,24 @@
     <row r="1509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1509" s="7"/>
       <c r="B1509" s="7"/>
-      <c r="C1509" s="43"/>
-      <c r="D1509" s="43"/>
-      <c r="E1509" s="43"/>
-      <c r="F1509" s="43"/>
+      <c r="C1509" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1509" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1509" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1509" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1509" s="7"/>
     </row>
     <row r="1510" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1510" s="7"/>
+      <c r="A1510" s="37" t="s">
+        <v>3080</v>
+      </c>
       <c r="B1510" s="7"/>
       <c r="C1510" s="43"/>
       <c r="D1510" s="43"/>
@@ -36294,34 +36337,54 @@
       <c r="G1510" s="7"/>
     </row>
     <row r="1511" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1511" s="7"/>
-      <c r="B1511" s="7"/>
-      <c r="C1511" s="43"/>
+      <c r="A1511" s="7" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B1511" s="7" t="s">
+        <v>3082</v>
+      </c>
+      <c r="C1511" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1511" s="43"/>
       <c r="E1511" s="43"/>
       <c r="F1511" s="43"/>
       <c r="G1511" s="7"/>
     </row>
     <row r="1512" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1512" s="7"/>
-      <c r="B1512" s="7"/>
-      <c r="C1512" s="43"/>
+      <c r="A1512" s="7" t="s">
+        <v>3083</v>
+      </c>
+      <c r="B1512" s="7" t="s">
+        <v>3084</v>
+      </c>
+      <c r="C1512" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1512" s="43"/>
       <c r="E1512" s="43"/>
       <c r="F1512" s="43"/>
       <c r="G1512" s="7"/>
     </row>
     <row r="1513" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1513" s="7"/>
-      <c r="B1513" s="7"/>
-      <c r="C1513" s="43"/>
+      <c r="A1513" s="7" t="s">
+        <v>3085</v>
+      </c>
+      <c r="B1513" s="7" t="s">
+        <v>3086</v>
+      </c>
+      <c r="C1513" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1513" s="43"/>
       <c r="E1513" s="43"/>
       <c r="F1513" s="43"/>
       <c r="G1513" s="7"/>
     </row>
     <row r="1514" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1514" s="7"/>
+      <c r="A1514" s="37" t="s">
+        <v>3087</v>
+      </c>
       <c r="B1514" s="7"/>
       <c r="C1514" s="43"/>
       <c r="D1514" s="43"/>
@@ -36330,10 +36393,16 @@
       <c r="G1514" s="7"/>
     </row>
     <row r="1515" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1515" s="7"/>
-      <c r="B1515" s="7"/>
+      <c r="A1515" s="7" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B1515" s="7" t="s">
+        <v>3089</v>
+      </c>
       <c r="C1515" s="43"/>
-      <c r="D1515" s="43"/>
+      <c r="D1515" s="43" t="s">
+        <v>3090</v>
+      </c>
       <c r="E1515" s="43"/>
       <c r="F1515" s="43"/>
       <c r="G1515" s="7"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DCCBD5-5BB9-4300-ABD4-FDC41600F1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D90B79-1102-43E1-88D2-3862E2B8A4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4682" uniqueCount="3091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4682" uniqueCount="3092">
   <si>
     <t>Пароль</t>
   </si>
@@ -9307,6 +9307,9 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/9Ux122IKU_eUow</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/N6VV0wmme07ewQ</t>
   </si>
 </sst>
 </file>
@@ -36344,7 +36347,7 @@
         <v>3082</v>
       </c>
       <c r="C1511" s="43" t="s">
-        <v>731</v>
+        <v>3091</v>
       </c>
       <c r="D1511" s="43"/>
       <c r="E1511" s="43"/>
@@ -36359,7 +36362,7 @@
         <v>3084</v>
       </c>
       <c r="C1512" s="43" t="s">
-        <v>731</v>
+        <v>3091</v>
       </c>
       <c r="D1512" s="43"/>
       <c r="E1512" s="43"/>
@@ -36374,7 +36377,7 @@
         <v>3086</v>
       </c>
       <c r="C1513" s="43" t="s">
-        <v>731</v>
+        <v>3091</v>
       </c>
       <c r="D1513" s="43"/>
       <c r="E1513" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D90B79-1102-43E1-88D2-3862E2B8A4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56A0335-D464-4A64-9FFA-2F45DD68DF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4682" uniqueCount="3092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4710" uniqueCount="3118">
   <si>
     <t>Пароль</t>
   </si>
@@ -9310,6 +9310,84 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/N6VV0wmme07ewQ</t>
+  </si>
+  <si>
+    <t>27/10/26/10:00</t>
+  </si>
+  <si>
+    <t>18905</t>
+  </si>
+  <si>
+    <t>+79787118905</t>
+  </si>
+  <si>
+    <t>49343</t>
+  </si>
+  <si>
+    <t>+79628949343</t>
+  </si>
+  <si>
+    <t>27/10/26/12:30</t>
+  </si>
+  <si>
+    <t>23634</t>
+  </si>
+  <si>
+    <t>+79280123634</t>
+  </si>
+  <si>
+    <t>62999</t>
+  </si>
+  <si>
+    <t>+79788462999</t>
+  </si>
+  <si>
+    <t>87638</t>
+  </si>
+  <si>
+    <t>+79515387638</t>
+  </si>
+  <si>
+    <t>38330</t>
+  </si>
+  <si>
+    <t>+79614238330</t>
+  </si>
+  <si>
+    <t>27/10/26/15:00</t>
+  </si>
+  <si>
+    <t>26646</t>
+  </si>
+  <si>
+    <t>+79895126646</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Cal-s-tjMGxmjA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/I8tQEZVd7ri1aA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/06J0OqE0Sq_ImA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Sh3eD-Etkfmeqw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/rpnecIkWCIx_Sg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/vJ6Ne8u9SrmFyw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/01kZTw9mHRFcGw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/dZYl_W2-uzBszg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/5nLdECEs5J_nlw</t>
   </si>
 </sst>
 </file>
@@ -36411,7 +36489,9 @@
       <c r="G1515" s="7"/>
     </row>
     <row r="1516" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1516" s="7"/>
+      <c r="A1516" s="37" t="s">
+        <v>3092</v>
+      </c>
       <c r="B1516" s="7"/>
       <c r="C1516" s="43"/>
       <c r="D1516" s="43"/>
@@ -36420,25 +36500,45 @@
       <c r="G1516" s="7"/>
     </row>
     <row r="1517" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1517" s="7"/>
-      <c r="B1517" s="7"/>
-      <c r="C1517" s="43"/>
+      <c r="A1517" s="7" t="s">
+        <v>3093</v>
+      </c>
+      <c r="B1517" s="7" t="s">
+        <v>3094</v>
+      </c>
+      <c r="C1517" s="43" t="s">
+        <v>3109</v>
+      </c>
       <c r="D1517" s="43"/>
       <c r="E1517" s="43"/>
       <c r="F1517" s="43"/>
       <c r="G1517" s="7"/>
     </row>
     <row r="1518" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1518" s="7"/>
-      <c r="B1518" s="7"/>
-      <c r="C1518" s="43"/>
-      <c r="D1518" s="43"/>
-      <c r="E1518" s="43"/>
-      <c r="F1518" s="43"/>
+      <c r="A1518" s="7" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B1518" s="7" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C1518" s="43" t="s">
+        <v>3109</v>
+      </c>
+      <c r="D1518" s="43" t="s">
+        <v>3113</v>
+      </c>
+      <c r="E1518" s="43" t="s">
+        <v>3117</v>
+      </c>
+      <c r="F1518" s="43" t="s">
+        <v>3116</v>
+      </c>
       <c r="G1518" s="7"/>
     </row>
     <row r="1519" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1519" s="7"/>
+      <c r="A1519" s="37" t="s">
+        <v>3097</v>
+      </c>
       <c r="B1519" s="7"/>
       <c r="C1519" s="43"/>
       <c r="D1519" s="43"/>
@@ -36447,494 +36547,528 @@
       <c r="G1519" s="7"/>
     </row>
     <row r="1520" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1520" s="7"/>
-      <c r="B1520" s="7"/>
+      <c r="A1520" s="7" t="s">
+        <v>3098</v>
+      </c>
+      <c r="B1520" s="7" t="s">
+        <v>3099</v>
+      </c>
       <c r="C1520" s="7"/>
-      <c r="D1520" s="7"/>
+      <c r="D1520" s="43" t="s">
+        <v>3114</v>
+      </c>
       <c r="E1520" s="7"/>
       <c r="F1520" s="7"/>
       <c r="G1520" s="7"/>
     </row>
     <row r="1521" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1521" s="7"/>
-      <c r="B1521" s="7"/>
+      <c r="A1521" s="7" t="s">
+        <v>3100</v>
+      </c>
+      <c r="B1521" s="7" t="s">
+        <v>3101</v>
+      </c>
       <c r="C1521" s="1"/>
-      <c r="D1521" s="1"/>
+      <c r="D1521" s="43" t="s">
+        <v>3115</v>
+      </c>
       <c r="E1521" s="1"/>
       <c r="F1521" s="1"/>
       <c r="G1521" s="1"/>
     </row>
     <row r="1522" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1522" s="1"/>
-      <c r="B1522" s="1"/>
-      <c r="C1522" s="1"/>
-      <c r="D1522" s="1"/>
-      <c r="E1522" s="1"/>
-      <c r="F1522" s="1"/>
-      <c r="G1522" s="1"/>
+      <c r="A1522" s="7" t="s">
+        <v>3102</v>
+      </c>
+      <c r="B1522" s="7" t="s">
+        <v>3103</v>
+      </c>
+      <c r="C1522" s="43" t="s">
+        <v>3110</v>
+      </c>
+      <c r="D1522" s="43"/>
+      <c r="E1522" s="43"/>
+      <c r="F1522" s="43"/>
+      <c r="G1522" s="43"/>
     </row>
     <row r="1523" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1523" s="1"/>
-      <c r="B1523" s="1"/>
-      <c r="C1523" s="1"/>
-      <c r="D1523" s="1"/>
-      <c r="E1523" s="1"/>
-      <c r="F1523" s="1"/>
-      <c r="G1523" s="1"/>
+      <c r="A1523" s="7" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B1523" s="7" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C1523" s="43" t="s">
+        <v>3110</v>
+      </c>
+      <c r="D1523" s="43"/>
+      <c r="E1523" s="43"/>
+      <c r="F1523" s="43"/>
+      <c r="G1523" s="43"/>
     </row>
     <row r="1524" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1524" s="1"/>
-      <c r="B1524" s="1"/>
-      <c r="C1524" s="1"/>
-      <c r="D1524" s="1"/>
-      <c r="E1524" s="1"/>
-      <c r="F1524" s="1"/>
-      <c r="G1524" s="1"/>
+      <c r="A1524" s="37" t="s">
+        <v>3106</v>
+      </c>
+      <c r="B1524" s="7"/>
+      <c r="C1524" s="43"/>
+      <c r="D1524" s="43"/>
+      <c r="E1524" s="43"/>
+      <c r="F1524" s="43"/>
+      <c r="G1524" s="43"/>
     </row>
     <row r="1525" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1525" s="1"/>
-      <c r="B1525" s="1"/>
-      <c r="C1525" s="1"/>
-      <c r="D1525" s="1"/>
-      <c r="E1525" s="1"/>
-      <c r="F1525" s="1"/>
-      <c r="G1525" s="1"/>
+      <c r="A1525" s="7" t="s">
+        <v>3107</v>
+      </c>
+      <c r="B1525" s="7" t="s">
+        <v>3108</v>
+      </c>
+      <c r="C1525" s="43" t="s">
+        <v>3111</v>
+      </c>
+      <c r="D1525" s="43" t="s">
+        <v>3112</v>
+      </c>
+      <c r="E1525" s="43"/>
+      <c r="F1525" s="43"/>
+      <c r="G1525" s="43"/>
     </row>
     <row r="1526" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1526" s="1"/>
-      <c r="B1526" s="1"/>
-      <c r="C1526" s="1"/>
-      <c r="D1526" s="1"/>
-      <c r="E1526" s="1"/>
-      <c r="F1526" s="1"/>
-      <c r="G1526" s="1"/>
+      <c r="A1526" s="7"/>
+      <c r="B1526" s="7"/>
+      <c r="C1526" s="43"/>
+      <c r="D1526" s="43"/>
+      <c r="E1526" s="43"/>
+      <c r="F1526" s="43"/>
+      <c r="G1526" s="43"/>
     </row>
     <row r="1527" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1527" s="1"/>
-      <c r="B1527" s="1"/>
-      <c r="C1527" s="1"/>
-      <c r="D1527" s="1"/>
-      <c r="E1527" s="1"/>
-      <c r="F1527" s="1"/>
-      <c r="G1527" s="1"/>
+      <c r="A1527" s="7"/>
+      <c r="B1527" s="7"/>
+      <c r="C1527" s="43"/>
+      <c r="D1527" s="43"/>
+      <c r="E1527" s="43"/>
+      <c r="F1527" s="43"/>
+      <c r="G1527" s="43"/>
     </row>
     <row r="1528" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1528" s="1"/>
-      <c r="B1528" s="1"/>
-      <c r="C1528" s="1"/>
-      <c r="D1528" s="1"/>
-      <c r="E1528" s="1"/>
-      <c r="F1528" s="1"/>
-      <c r="G1528" s="1"/>
+      <c r="A1528" s="7"/>
+      <c r="B1528" s="7"/>
+      <c r="C1528" s="43"/>
+      <c r="D1528" s="43"/>
+      <c r="E1528" s="43"/>
+      <c r="F1528" s="43"/>
+      <c r="G1528" s="43"/>
     </row>
     <row r="1529" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1529" s="1"/>
-      <c r="B1529" s="1"/>
-      <c r="C1529" s="1"/>
-      <c r="D1529" s="1"/>
-      <c r="E1529" s="1"/>
-      <c r="F1529" s="1"/>
-      <c r="G1529" s="1"/>
+      <c r="A1529" s="7"/>
+      <c r="B1529" s="7"/>
+      <c r="C1529" s="43"/>
+      <c r="D1529" s="43"/>
+      <c r="E1529" s="43"/>
+      <c r="F1529" s="43"/>
+      <c r="G1529" s="43"/>
     </row>
     <row r="1530" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1530" s="1"/>
-      <c r="B1530" s="1"/>
-      <c r="C1530" s="1"/>
-      <c r="D1530" s="1"/>
-      <c r="E1530" s="1"/>
-      <c r="F1530" s="1"/>
-      <c r="G1530" s="1"/>
+      <c r="A1530" s="7"/>
+      <c r="B1530" s="7"/>
+      <c r="C1530" s="43"/>
+      <c r="D1530" s="43"/>
+      <c r="E1530" s="43"/>
+      <c r="F1530" s="43"/>
+      <c r="G1530" s="43"/>
     </row>
     <row r="1531" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1531" s="1"/>
-      <c r="B1531" s="1"/>
-      <c r="C1531" s="1"/>
-      <c r="D1531" s="1"/>
-      <c r="E1531" s="1"/>
-      <c r="F1531" s="1"/>
-      <c r="G1531" s="1"/>
+      <c r="A1531" s="7"/>
+      <c r="B1531" s="7"/>
+      <c r="C1531" s="43"/>
+      <c r="D1531" s="43"/>
+      <c r="E1531" s="43"/>
+      <c r="F1531" s="43"/>
+      <c r="G1531" s="43"/>
     </row>
     <row r="1532" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1532" s="1"/>
-      <c r="B1532" s="1"/>
-      <c r="C1532" s="1"/>
-      <c r="D1532" s="1"/>
-      <c r="E1532" s="1"/>
-      <c r="F1532" s="1"/>
-      <c r="G1532" s="1"/>
+      <c r="A1532" s="7"/>
+      <c r="B1532" s="7"/>
+      <c r="C1532" s="43"/>
+      <c r="D1532" s="43"/>
+      <c r="E1532" s="43"/>
+      <c r="F1532" s="43"/>
+      <c r="G1532" s="43"/>
     </row>
     <row r="1533" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1533" s="1"/>
-      <c r="B1533" s="1"/>
-      <c r="C1533" s="1"/>
-      <c r="D1533" s="1"/>
-      <c r="E1533" s="1"/>
-      <c r="F1533" s="1"/>
-      <c r="G1533" s="1"/>
+      <c r="A1533" s="7"/>
+      <c r="B1533" s="7"/>
+      <c r="C1533" s="43"/>
+      <c r="D1533" s="43"/>
+      <c r="E1533" s="43"/>
+      <c r="F1533" s="43"/>
+      <c r="G1533" s="43"/>
     </row>
     <row r="1534" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1534" s="1"/>
-      <c r="B1534" s="1"/>
-      <c r="C1534" s="1"/>
-      <c r="D1534" s="1"/>
-      <c r="E1534" s="1"/>
-      <c r="F1534" s="1"/>
-      <c r="G1534" s="1"/>
+      <c r="A1534" s="7"/>
+      <c r="B1534" s="7"/>
+      <c r="C1534" s="43"/>
+      <c r="D1534" s="43"/>
+      <c r="E1534" s="43"/>
+      <c r="F1534" s="43"/>
+      <c r="G1534" s="43"/>
     </row>
     <row r="1535" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1535" s="1"/>
-      <c r="B1535" s="1"/>
-      <c r="C1535" s="1"/>
-      <c r="D1535" s="1"/>
-      <c r="E1535" s="1"/>
-      <c r="F1535" s="1"/>
-      <c r="G1535" s="1"/>
+      <c r="A1535" s="7"/>
+      <c r="B1535" s="7"/>
+      <c r="C1535" s="43"/>
+      <c r="D1535" s="43"/>
+      <c r="E1535" s="43"/>
+      <c r="F1535" s="43"/>
+      <c r="G1535" s="43"/>
     </row>
     <row r="1536" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1536" s="1"/>
-      <c r="B1536" s="1"/>
-      <c r="C1536" s="1"/>
-      <c r="D1536" s="1"/>
-      <c r="E1536" s="1"/>
-      <c r="F1536" s="1"/>
-      <c r="G1536" s="1"/>
+      <c r="A1536" s="7"/>
+      <c r="B1536" s="7"/>
+      <c r="C1536" s="43"/>
+      <c r="D1536" s="43"/>
+      <c r="E1536" s="43"/>
+      <c r="F1536" s="43"/>
+      <c r="G1536" s="43"/>
     </row>
     <row r="1537" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1537" s="1"/>
-      <c r="B1537" s="1"/>
-      <c r="C1537" s="1"/>
-      <c r="D1537" s="1"/>
-      <c r="E1537" s="1"/>
-      <c r="F1537" s="1"/>
-      <c r="G1537" s="1"/>
+      <c r="A1537" s="7"/>
+      <c r="B1537" s="7"/>
+      <c r="C1537" s="43"/>
+      <c r="D1537" s="43"/>
+      <c r="E1537" s="43"/>
+      <c r="F1537" s="43"/>
+      <c r="G1537" s="43"/>
     </row>
     <row r="1538" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1538" s="1"/>
-      <c r="B1538" s="1"/>
-      <c r="C1538" s="1"/>
-      <c r="D1538" s="1"/>
-      <c r="E1538" s="1"/>
-      <c r="F1538" s="1"/>
-      <c r="G1538" s="1"/>
+      <c r="A1538" s="7"/>
+      <c r="B1538" s="7"/>
+      <c r="C1538" s="43"/>
+      <c r="D1538" s="43"/>
+      <c r="E1538" s="43"/>
+      <c r="F1538" s="43"/>
+      <c r="G1538" s="43"/>
     </row>
     <row r="1539" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1539" s="1"/>
-      <c r="B1539" s="1"/>
-      <c r="C1539" s="1"/>
-      <c r="D1539" s="1"/>
-      <c r="E1539" s="1"/>
-      <c r="F1539" s="1"/>
-      <c r="G1539" s="1"/>
+      <c r="A1539" s="7"/>
+      <c r="B1539" s="7"/>
+      <c r="C1539" s="43"/>
+      <c r="D1539" s="43"/>
+      <c r="E1539" s="43"/>
+      <c r="F1539" s="43"/>
+      <c r="G1539" s="43"/>
     </row>
     <row r="1540" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1540" s="1"/>
-      <c r="B1540" s="1"/>
-      <c r="C1540" s="1"/>
-      <c r="D1540" s="1"/>
-      <c r="E1540" s="1"/>
-      <c r="F1540" s="1"/>
-      <c r="G1540" s="1"/>
+      <c r="A1540" s="7"/>
+      <c r="B1540" s="7"/>
+      <c r="C1540" s="43"/>
+      <c r="D1540" s="43"/>
+      <c r="E1540" s="43"/>
+      <c r="F1540" s="43"/>
+      <c r="G1540" s="43"/>
     </row>
     <row r="1541" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1541" s="1"/>
-      <c r="B1541" s="1"/>
-      <c r="C1541" s="1"/>
-      <c r="D1541" s="1"/>
-      <c r="E1541" s="1"/>
-      <c r="F1541" s="1"/>
-      <c r="G1541" s="1"/>
+      <c r="A1541" s="7"/>
+      <c r="B1541" s="7"/>
+      <c r="C1541" s="43"/>
+      <c r="D1541" s="43"/>
+      <c r="E1541" s="43"/>
+      <c r="F1541" s="43"/>
+      <c r="G1541" s="43"/>
     </row>
     <row r="1542" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1542" s="1"/>
-      <c r="B1542" s="1"/>
-      <c r="C1542" s="1"/>
-      <c r="D1542" s="1"/>
-      <c r="E1542" s="1"/>
-      <c r="F1542" s="1"/>
-      <c r="G1542" s="1"/>
+      <c r="A1542" s="7"/>
+      <c r="B1542" s="7"/>
+      <c r="C1542" s="43"/>
+      <c r="D1542" s="43"/>
+      <c r="E1542" s="43"/>
+      <c r="F1542" s="43"/>
+      <c r="G1542" s="43"/>
     </row>
     <row r="1543" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1543" s="1"/>
-      <c r="B1543" s="1"/>
-      <c r="C1543" s="1"/>
-      <c r="D1543" s="1"/>
-      <c r="E1543" s="1"/>
-      <c r="F1543" s="1"/>
-      <c r="G1543" s="1"/>
+      <c r="A1543" s="7"/>
+      <c r="B1543" s="7"/>
+      <c r="C1543" s="43"/>
+      <c r="D1543" s="43"/>
+      <c r="E1543" s="43"/>
+      <c r="F1543" s="43"/>
+      <c r="G1543" s="43"/>
     </row>
     <row r="1544" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1544" s="1"/>
-      <c r="B1544" s="1"/>
-      <c r="C1544" s="1"/>
-      <c r="D1544" s="1"/>
-      <c r="E1544" s="1"/>
-      <c r="F1544" s="1"/>
-      <c r="G1544" s="1"/>
+      <c r="A1544" s="7"/>
+      <c r="B1544" s="7"/>
+      <c r="C1544" s="43"/>
+      <c r="D1544" s="43"/>
+      <c r="E1544" s="43"/>
+      <c r="F1544" s="43"/>
+      <c r="G1544" s="43"/>
     </row>
     <row r="1545" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1545" s="1"/>
-      <c r="B1545" s="1"/>
-      <c r="C1545" s="1"/>
-      <c r="D1545" s="1"/>
-      <c r="E1545" s="1"/>
-      <c r="F1545" s="1"/>
-      <c r="G1545" s="1"/>
+      <c r="A1545" s="7"/>
+      <c r="B1545" s="7"/>
+      <c r="C1545" s="43"/>
+      <c r="D1545" s="43"/>
+      <c r="E1545" s="43"/>
+      <c r="F1545" s="43"/>
+      <c r="G1545" s="43"/>
     </row>
     <row r="1546" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1546" s="1"/>
-      <c r="B1546" s="1"/>
-      <c r="C1546" s="1"/>
-      <c r="D1546" s="1"/>
-      <c r="E1546" s="1"/>
-      <c r="F1546" s="1"/>
-      <c r="G1546" s="1"/>
+      <c r="A1546" s="7"/>
+      <c r="B1546" s="7"/>
+      <c r="C1546" s="43"/>
+      <c r="D1546" s="43"/>
+      <c r="E1546" s="43"/>
+      <c r="F1546" s="43"/>
+      <c r="G1546" s="43"/>
     </row>
     <row r="1547" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1547" s="1"/>
-      <c r="B1547" s="1"/>
-      <c r="C1547" s="1"/>
-      <c r="D1547" s="1"/>
-      <c r="E1547" s="1"/>
-      <c r="F1547" s="1"/>
-      <c r="G1547" s="1"/>
+      <c r="A1547" s="7"/>
+      <c r="B1547" s="7"/>
+      <c r="C1547" s="43"/>
+      <c r="D1547" s="43"/>
+      <c r="E1547" s="43"/>
+      <c r="F1547" s="43"/>
+      <c r="G1547" s="43"/>
     </row>
     <row r="1548" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1548" s="1"/>
-      <c r="B1548" s="1"/>
-      <c r="C1548" s="1"/>
-      <c r="D1548" s="1"/>
-      <c r="E1548" s="1"/>
-      <c r="F1548" s="1"/>
-      <c r="G1548" s="1"/>
+      <c r="A1548" s="7"/>
+      <c r="B1548" s="7"/>
+      <c r="C1548" s="43"/>
+      <c r="D1548" s="43"/>
+      <c r="E1548" s="43"/>
+      <c r="F1548" s="43"/>
+      <c r="G1548" s="43"/>
     </row>
     <row r="1549" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1549" s="1"/>
-      <c r="B1549" s="1"/>
-      <c r="C1549" s="1"/>
-      <c r="D1549" s="1"/>
-      <c r="E1549" s="1"/>
-      <c r="F1549" s="1"/>
-      <c r="G1549" s="1"/>
+      <c r="A1549" s="7"/>
+      <c r="B1549" s="7"/>
+      <c r="C1549" s="43"/>
+      <c r="D1549" s="43"/>
+      <c r="E1549" s="43"/>
+      <c r="F1549" s="43"/>
+      <c r="G1549" s="43"/>
     </row>
     <row r="1550" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1550" s="1"/>
-      <c r="B1550" s="1"/>
-      <c r="C1550" s="1"/>
-      <c r="D1550" s="1"/>
-      <c r="E1550" s="1"/>
-      <c r="F1550" s="1"/>
-      <c r="G1550" s="1"/>
+      <c r="A1550" s="7"/>
+      <c r="B1550" s="7"/>
+      <c r="C1550" s="43"/>
+      <c r="D1550" s="43"/>
+      <c r="E1550" s="43"/>
+      <c r="F1550" s="43"/>
+      <c r="G1550" s="43"/>
     </row>
     <row r="1551" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1551" s="1"/>
-      <c r="B1551" s="1"/>
-      <c r="C1551" s="1"/>
-      <c r="D1551" s="1"/>
-      <c r="E1551" s="1"/>
-      <c r="F1551" s="1"/>
-      <c r="G1551" s="1"/>
+      <c r="A1551" s="7"/>
+      <c r="B1551" s="7"/>
+      <c r="C1551" s="43"/>
+      <c r="D1551" s="43"/>
+      <c r="E1551" s="43"/>
+      <c r="F1551" s="43"/>
+      <c r="G1551" s="43"/>
     </row>
     <row r="1552" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1552" s="1"/>
-      <c r="B1552" s="1"/>
-      <c r="C1552" s="1"/>
-      <c r="D1552" s="1"/>
-      <c r="E1552" s="1"/>
-      <c r="F1552" s="1"/>
-      <c r="G1552" s="1"/>
+      <c r="A1552" s="7"/>
+      <c r="B1552" s="7"/>
+      <c r="C1552" s="43"/>
+      <c r="D1552" s="43"/>
+      <c r="E1552" s="43"/>
+      <c r="F1552" s="43"/>
+      <c r="G1552" s="43"/>
     </row>
     <row r="1553" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1553" s="1"/>
-      <c r="B1553" s="1"/>
-      <c r="C1553" s="1"/>
-      <c r="D1553" s="1"/>
-      <c r="E1553" s="1"/>
-      <c r="F1553" s="1"/>
-      <c r="G1553" s="1"/>
+      <c r="A1553" s="7"/>
+      <c r="B1553" s="7"/>
+      <c r="C1553" s="43"/>
+      <c r="D1553" s="43"/>
+      <c r="E1553" s="43"/>
+      <c r="F1553" s="43"/>
+      <c r="G1553" s="43"/>
     </row>
     <row r="1554" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1554" s="1"/>
-      <c r="B1554" s="1"/>
-      <c r="C1554" s="1"/>
-      <c r="D1554" s="1"/>
-      <c r="E1554" s="1"/>
-      <c r="F1554" s="1"/>
-      <c r="G1554" s="1"/>
+      <c r="A1554" s="7"/>
+      <c r="B1554" s="7"/>
+      <c r="C1554" s="43"/>
+      <c r="D1554" s="43"/>
+      <c r="E1554" s="43"/>
+      <c r="F1554" s="43"/>
+      <c r="G1554" s="43"/>
     </row>
     <row r="1555" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1555" s="1"/>
-      <c r="B1555" s="1"/>
-      <c r="C1555" s="1"/>
-      <c r="D1555" s="1"/>
-      <c r="E1555" s="1"/>
-      <c r="F1555" s="1"/>
-      <c r="G1555" s="1"/>
+      <c r="A1555" s="7"/>
+      <c r="B1555" s="7"/>
+      <c r="C1555" s="43"/>
+      <c r="D1555" s="43"/>
+      <c r="E1555" s="43"/>
+      <c r="F1555" s="43"/>
+      <c r="G1555" s="43"/>
     </row>
     <row r="1556" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1556" s="1"/>
-      <c r="B1556" s="1"/>
-      <c r="C1556" s="1"/>
-      <c r="D1556" s="1"/>
-      <c r="E1556" s="1"/>
-      <c r="F1556" s="1"/>
-      <c r="G1556" s="1"/>
+      <c r="A1556" s="7"/>
+      <c r="B1556" s="7"/>
+      <c r="C1556" s="43"/>
+      <c r="D1556" s="43"/>
+      <c r="E1556" s="43"/>
+      <c r="F1556" s="43"/>
+      <c r="G1556" s="43"/>
     </row>
     <row r="1557" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1557" s="1"/>
-      <c r="B1557" s="1"/>
-      <c r="C1557" s="1"/>
-      <c r="D1557" s="1"/>
-      <c r="E1557" s="1"/>
-      <c r="F1557" s="1"/>
-      <c r="G1557" s="1"/>
+      <c r="A1557" s="7"/>
+      <c r="B1557" s="7"/>
+      <c r="C1557" s="43"/>
+      <c r="D1557" s="43"/>
+      <c r="E1557" s="43"/>
+      <c r="F1557" s="43"/>
+      <c r="G1557" s="43"/>
     </row>
     <row r="1558" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1558" s="1"/>
-      <c r="B1558" s="1"/>
-      <c r="C1558" s="1"/>
-      <c r="D1558" s="1"/>
-      <c r="E1558" s="1"/>
-      <c r="F1558" s="1"/>
-      <c r="G1558" s="1"/>
+      <c r="A1558" s="7"/>
+      <c r="B1558" s="7"/>
+      <c r="C1558" s="43"/>
+      <c r="D1558" s="43"/>
+      <c r="E1558" s="43"/>
+      <c r="F1558" s="43"/>
+      <c r="G1558" s="43"/>
     </row>
     <row r="1559" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1559" s="1"/>
-      <c r="B1559" s="1"/>
-      <c r="C1559" s="1"/>
-      <c r="D1559" s="1"/>
-      <c r="E1559" s="1"/>
-      <c r="F1559" s="1"/>
-      <c r="G1559" s="1"/>
+      <c r="A1559" s="7"/>
+      <c r="B1559" s="7"/>
+      <c r="C1559" s="43"/>
+      <c r="D1559" s="43"/>
+      <c r="E1559" s="43"/>
+      <c r="F1559" s="43"/>
+      <c r="G1559" s="43"/>
     </row>
     <row r="1560" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1560" s="1"/>
-      <c r="B1560" s="1"/>
-      <c r="C1560" s="1"/>
-      <c r="D1560" s="1"/>
-      <c r="E1560" s="1"/>
-      <c r="F1560" s="1"/>
-      <c r="G1560" s="1"/>
+      <c r="A1560" s="7"/>
+      <c r="B1560" s="7"/>
+      <c r="C1560" s="43"/>
+      <c r="D1560" s="43"/>
+      <c r="E1560" s="43"/>
+      <c r="F1560" s="43"/>
+      <c r="G1560" s="43"/>
     </row>
     <row r="1561" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1561" s="1"/>
-      <c r="B1561" s="1"/>
-      <c r="C1561" s="1"/>
-      <c r="D1561" s="1"/>
-      <c r="E1561" s="1"/>
-      <c r="F1561" s="1"/>
-      <c r="G1561" s="1"/>
+      <c r="A1561" s="7"/>
+      <c r="B1561" s="7"/>
+      <c r="C1561" s="43"/>
+      <c r="D1561" s="43"/>
+      <c r="E1561" s="43"/>
+      <c r="F1561" s="43"/>
+      <c r="G1561" s="43"/>
     </row>
     <row r="1562" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1562" s="1"/>
-      <c r="B1562" s="1"/>
-      <c r="C1562" s="1"/>
-      <c r="D1562" s="1"/>
-      <c r="E1562" s="1"/>
-      <c r="F1562" s="1"/>
-      <c r="G1562" s="1"/>
+      <c r="A1562" s="7"/>
+      <c r="B1562" s="7"/>
+      <c r="C1562" s="43"/>
+      <c r="D1562" s="43"/>
+      <c r="E1562" s="43"/>
+      <c r="F1562" s="43"/>
+      <c r="G1562" s="43"/>
     </row>
     <row r="1563" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1563" s="1"/>
-      <c r="B1563" s="1"/>
-      <c r="C1563" s="1"/>
-      <c r="D1563" s="1"/>
-      <c r="E1563" s="1"/>
-      <c r="F1563" s="1"/>
-      <c r="G1563" s="1"/>
+      <c r="A1563" s="7"/>
+      <c r="B1563" s="7"/>
+      <c r="C1563" s="43"/>
+      <c r="D1563" s="43"/>
+      <c r="E1563" s="43"/>
+      <c r="F1563" s="43"/>
+      <c r="G1563" s="43"/>
     </row>
     <row r="1564" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1564" s="1"/>
-      <c r="B1564" s="1"/>
-      <c r="C1564" s="1"/>
-      <c r="D1564" s="1"/>
-      <c r="E1564" s="1"/>
-      <c r="F1564" s="1"/>
-      <c r="G1564" s="1"/>
+      <c r="A1564" s="7"/>
+      <c r="B1564" s="7"/>
+      <c r="C1564" s="43"/>
+      <c r="D1564" s="43"/>
+      <c r="E1564" s="43"/>
+      <c r="F1564" s="43"/>
+      <c r="G1564" s="43"/>
     </row>
     <row r="1565" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1565" s="1"/>
-      <c r="B1565" s="1"/>
-      <c r="C1565" s="1"/>
-      <c r="D1565" s="1"/>
-      <c r="E1565" s="1"/>
-      <c r="F1565" s="1"/>
-      <c r="G1565" s="1"/>
+      <c r="A1565" s="7"/>
+      <c r="B1565" s="7"/>
+      <c r="C1565" s="43"/>
+      <c r="D1565" s="43"/>
+      <c r="E1565" s="43"/>
+      <c r="F1565" s="43"/>
+      <c r="G1565" s="43"/>
     </row>
     <row r="1566" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1566" s="1"/>
-      <c r="B1566" s="1"/>
-      <c r="C1566" s="1"/>
-      <c r="D1566" s="1"/>
-      <c r="E1566" s="1"/>
-      <c r="F1566" s="1"/>
-      <c r="G1566" s="1"/>
+      <c r="A1566" s="7"/>
+      <c r="B1566" s="7"/>
+      <c r="C1566" s="43"/>
+      <c r="D1566" s="43"/>
+      <c r="E1566" s="43"/>
+      <c r="F1566" s="43"/>
+      <c r="G1566" s="43"/>
     </row>
     <row r="1567" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1567" s="1"/>
-      <c r="B1567" s="1"/>
-      <c r="C1567" s="1"/>
-      <c r="D1567" s="1"/>
-      <c r="E1567" s="1"/>
-      <c r="F1567" s="1"/>
-      <c r="G1567" s="1"/>
+      <c r="A1567" s="7"/>
+      <c r="B1567" s="7"/>
+      <c r="C1567" s="43"/>
+      <c r="D1567" s="43"/>
+      <c r="E1567" s="43"/>
+      <c r="F1567" s="43"/>
+      <c r="G1567" s="43"/>
     </row>
     <row r="1568" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1568" s="1"/>
-      <c r="B1568" s="1"/>
-      <c r="C1568" s="1"/>
-      <c r="D1568" s="1"/>
-      <c r="E1568" s="1"/>
-      <c r="F1568" s="1"/>
-      <c r="G1568" s="1"/>
+      <c r="A1568" s="7"/>
+      <c r="B1568" s="7"/>
+      <c r="C1568" s="43"/>
+      <c r="D1568" s="43"/>
+      <c r="E1568" s="43"/>
+      <c r="F1568" s="43"/>
+      <c r="G1568" s="43"/>
     </row>
     <row r="1569" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1569" s="1"/>
-      <c r="B1569" s="1"/>
-      <c r="C1569" s="1"/>
-      <c r="D1569" s="1"/>
-      <c r="E1569" s="1"/>
-      <c r="F1569" s="1"/>
-      <c r="G1569" s="1"/>
+      <c r="A1569" s="7"/>
+      <c r="B1569" s="7"/>
+      <c r="C1569" s="43"/>
+      <c r="D1569" s="43"/>
+      <c r="E1569" s="43"/>
+      <c r="F1569" s="43"/>
+      <c r="G1569" s="43"/>
     </row>
     <row r="1570" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1570" s="1"/>
-      <c r="B1570" s="1"/>
-      <c r="C1570" s="1"/>
-      <c r="D1570" s="1"/>
-      <c r="E1570" s="1"/>
-      <c r="F1570" s="1"/>
-      <c r="G1570" s="1"/>
+      <c r="A1570" s="7"/>
+      <c r="B1570" s="7"/>
+      <c r="C1570" s="43"/>
+      <c r="D1570" s="43"/>
+      <c r="E1570" s="43"/>
+      <c r="F1570" s="43"/>
+      <c r="G1570" s="43"/>
     </row>
     <row r="1571" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1571" s="1"/>
-      <c r="B1571" s="1"/>
-      <c r="C1571" s="1"/>
-      <c r="D1571" s="1"/>
-      <c r="E1571" s="1"/>
-      <c r="F1571" s="1"/>
-      <c r="G1571" s="1"/>
+      <c r="A1571" s="7"/>
+      <c r="B1571" s="7"/>
+      <c r="C1571" s="43"/>
+      <c r="D1571" s="43"/>
+      <c r="E1571" s="43"/>
+      <c r="F1571" s="43"/>
+      <c r="G1571" s="43"/>
     </row>
     <row r="1572" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1572" s="1"/>
-      <c r="B1572" s="1"/>
-      <c r="C1572" s="1"/>
-      <c r="D1572" s="1"/>
-      <c r="E1572" s="1"/>
-      <c r="F1572" s="1"/>
-      <c r="G1572" s="1"/>
+      <c r="A1572" s="7"/>
+      <c r="B1572" s="7"/>
+      <c r="C1572" s="43"/>
+      <c r="D1572" s="43"/>
+      <c r="E1572" s="43"/>
+      <c r="F1572" s="43"/>
+      <c r="G1572" s="43"/>
     </row>
     <row r="1573" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1573" s="1"/>
-      <c r="B1573" s="1"/>
-      <c r="C1573" s="1"/>
-      <c r="D1573" s="1"/>
-      <c r="E1573" s="1"/>
-      <c r="F1573" s="1"/>
-      <c r="G1573" s="1"/>
+      <c r="A1573" s="7"/>
+      <c r="B1573" s="7"/>
+      <c r="C1573" s="43"/>
+      <c r="D1573" s="43"/>
+      <c r="E1573" s="43"/>
+      <c r="F1573" s="43"/>
+      <c r="G1573" s="43"/>
     </row>
     <row r="1574" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1574" s="1"/>
-      <c r="B1574" s="1"/>
+      <c r="A1574" s="7"/>
+      <c r="B1574" s="7"/>
       <c r="C1574" s="1"/>
       <c r="D1574" s="1"/>
       <c r="E1574" s="1"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56A0335-D464-4A64-9FFA-2F45DD68DF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF558F1-2F11-4405-A378-885B8939A948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4710" uniqueCount="3118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4710" uniqueCount="3115">
   <si>
     <t>Пароль</t>
   </si>
@@ -9372,22 +9372,13 @@
     <t>https://disk.yandex.ru/d/06J0OqE0Sq_ImA</t>
   </si>
   <si>
-    <t>https://disk.yandex.ru/d/Sh3eD-Etkfmeqw</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/rpnecIkWCIx_Sg</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/vJ6Ne8u9SrmFyw</t>
-  </si>
-  <si>
-    <t>https://disk.yandex.ru/d/01kZTw9mHRFcGw</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/i/dZYl_W2-uzBszg</t>
   </si>
   <si>
     <t>https://disk.yandex.ru/d/5nLdECEs5J_nlw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/CIzBNS4FpTenbQ</t>
   </si>
 </sst>
 </file>
@@ -36525,13 +36516,13 @@
         <v>3109</v>
       </c>
       <c r="D1518" s="43" t="s">
+        <v>3114</v>
+      </c>
+      <c r="E1518" s="43" t="s">
         <v>3113</v>
       </c>
-      <c r="E1518" s="43" t="s">
-        <v>3117</v>
-      </c>
       <c r="F1518" s="43" t="s">
-        <v>3116</v>
+        <v>3112</v>
       </c>
       <c r="G1518" s="7"/>
     </row>
@@ -36570,7 +36561,7 @@
       </c>
       <c r="C1521" s="1"/>
       <c r="D1521" s="43" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="E1521" s="1"/>
       <c r="F1521" s="1"/>
@@ -36628,7 +36619,7 @@
         <v>3111</v>
       </c>
       <c r="D1525" s="43" t="s">
-        <v>3112</v>
+        <v>3114</v>
       </c>
       <c r="E1525" s="43"/>
       <c r="F1525" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF558F1-2F11-4405-A378-885B8939A948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A841ABB4-89E0-4849-B709-A6529404B761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="600" windowWidth="38700" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4710" uniqueCount="3115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4739" uniqueCount="3136">
   <si>
     <t>Пароль</t>
   </si>
@@ -9379,6 +9379,69 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/CIzBNS4FpTenbQ</t>
+  </si>
+  <si>
+    <t>28/10/26/09:00</t>
+  </si>
+  <si>
+    <t>09068</t>
+  </si>
+  <si>
+    <t>+79054509068</t>
+  </si>
+  <si>
+    <t>82171</t>
+  </si>
+  <si>
+    <t>+79385082171</t>
+  </si>
+  <si>
+    <t>28/10/26/11:00</t>
+  </si>
+  <si>
+    <t>+79155232799</t>
+  </si>
+  <si>
+    <t>11133</t>
+  </si>
+  <si>
+    <t>+79021111133</t>
+  </si>
+  <si>
+    <t>69826</t>
+  </si>
+  <si>
+    <t>+79497469826</t>
+  </si>
+  <si>
+    <t>60128</t>
+  </si>
+  <si>
+    <t>+79183360128</t>
+  </si>
+  <si>
+    <t>28/10/26/14:30</t>
+  </si>
+  <si>
+    <t>73608</t>
+  </si>
+  <si>
+    <t>+7903573608</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/GHeOyYC8TQXX5A</t>
+  </si>
+  <si>
+    <t>? https://disk.yandex.ru/d/GHeOyYC8TQXX5A</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Jgl2x5B5LuJcjw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/cvDMpASpSlIcgA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/v3JdI8ictOfUJQ</t>
   </si>
 </sst>
 </file>
@@ -36626,7 +36689,9 @@
       <c r="G1525" s="43"/>
     </row>
     <row r="1526" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1526" s="7"/>
+      <c r="A1526" s="37" t="s">
+        <v>3115</v>
+      </c>
       <c r="B1526" s="7"/>
       <c r="C1526" s="43"/>
       <c r="D1526" s="43"/>
@@ -36635,25 +36700,43 @@
       <c r="G1526" s="43"/>
     </row>
     <row r="1527" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1527" s="7"/>
-      <c r="B1527" s="7"/>
-      <c r="C1527" s="43"/>
-      <c r="D1527" s="43"/>
+      <c r="A1527" s="7" t="s">
+        <v>3116</v>
+      </c>
+      <c r="B1527" s="7" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C1527" s="43" t="s">
+        <v>3132</v>
+      </c>
+      <c r="D1527" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="E1527" s="43"/>
       <c r="F1527" s="43"/>
       <c r="G1527" s="43"/>
     </row>
     <row r="1528" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1528" s="7"/>
-      <c r="B1528" s="7"/>
-      <c r="C1528" s="43"/>
-      <c r="D1528" s="43"/>
+      <c r="A1528" s="7" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B1528" s="7" t="s">
+        <v>3119</v>
+      </c>
+      <c r="C1528" s="43" t="s">
+        <v>3131</v>
+      </c>
+      <c r="D1528" s="43" t="s">
+        <v>3009</v>
+      </c>
       <c r="E1528" s="43"/>
       <c r="F1528" s="43"/>
       <c r="G1528" s="43"/>
     </row>
     <row r="1529" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1529" s="7"/>
+      <c r="A1529" s="37" t="s">
+        <v>3120</v>
+      </c>
       <c r="B1529" s="7"/>
       <c r="C1529" s="43"/>
       <c r="D1529" s="43"/>
@@ -36662,43 +36745,73 @@
       <c r="G1529" s="43"/>
     </row>
     <row r="1530" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1530" s="7"/>
-      <c r="B1530" s="7"/>
+      <c r="A1530" s="7" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B1530" s="7" t="s">
+        <v>3121</v>
+      </c>
       <c r="C1530" s="43"/>
-      <c r="D1530" s="43"/>
-      <c r="E1530" s="43"/>
-      <c r="F1530" s="43"/>
+      <c r="D1530" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="E1530" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1530" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="G1530" s="43"/>
     </row>
     <row r="1531" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1531" s="7"/>
-      <c r="B1531" s="7"/>
-      <c r="C1531" s="43"/>
+      <c r="A1531" s="7" t="s">
+        <v>3122</v>
+      </c>
+      <c r="B1531" s="7" t="s">
+        <v>3123</v>
+      </c>
+      <c r="C1531" s="43" t="s">
+        <v>3133</v>
+      </c>
       <c r="D1531" s="43"/>
       <c r="E1531" s="43"/>
       <c r="F1531" s="43"/>
       <c r="G1531" s="43"/>
     </row>
     <row r="1532" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1532" s="7"/>
-      <c r="B1532" s="7"/>
-      <c r="C1532" s="43"/>
+      <c r="A1532" s="7" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B1532" s="7" t="s">
+        <v>3125</v>
+      </c>
+      <c r="C1532" s="43" t="s">
+        <v>3133</v>
+      </c>
       <c r="D1532" s="43"/>
       <c r="E1532" s="43"/>
       <c r="F1532" s="43"/>
       <c r="G1532" s="43"/>
     </row>
     <row r="1533" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1533" s="7"/>
-      <c r="B1533" s="7"/>
-      <c r="C1533" s="43"/>
+      <c r="A1533" s="7" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1533" s="7" t="s">
+        <v>3127</v>
+      </c>
+      <c r="C1533" s="43" t="s">
+        <v>3133</v>
+      </c>
       <c r="D1533" s="43"/>
       <c r="E1533" s="43"/>
       <c r="F1533" s="43"/>
       <c r="G1533" s="43"/>
     </row>
     <row r="1534" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1534" s="7"/>
+      <c r="A1534" s="37" t="s">
+        <v>3128</v>
+      </c>
       <c r="B1534" s="7"/>
       <c r="C1534" s="43"/>
       <c r="D1534" s="43"/>
@@ -36707,10 +36820,18 @@
       <c r="G1534" s="43"/>
     </row>
     <row r="1535" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1535" s="7"/>
-      <c r="B1535" s="7"/>
-      <c r="C1535" s="43"/>
-      <c r="D1535" s="43"/>
+      <c r="A1535" s="7" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B1535" s="7" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1535" s="43" t="s">
+        <v>3135</v>
+      </c>
+      <c r="D1535" s="43" t="s">
+        <v>3134</v>
+      </c>
       <c r="E1535" s="43"/>
       <c r="F1535" s="43"/>
       <c r="G1535" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A841ABB4-89E0-4849-B709-A6529404B761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A279607F-813A-4E03-BC4F-73D276875D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4739" uniqueCount="3136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4738" uniqueCount="3139">
   <si>
     <t>Пароль</t>
   </si>
@@ -9426,9 +9426,6 @@
     <t>73608</t>
   </si>
   <si>
-    <t>+7903573608</t>
-  </si>
-  <si>
     <t>https://disk.yandex.ru/d/GHeOyYC8TQXX5A</t>
   </si>
   <si>
@@ -9442,6 +9439,18 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/v3JdI8ictOfUJQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/Rmz36k3Z3dG_DA</t>
+  </si>
+  <si>
+    <t>? https://disk.yandex.ru/d/Rmz36k3Z3dG_DA</t>
+  </si>
+  <si>
+    <t>+79038573608</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/4JCxONWWHfWtlQ</t>
   </si>
 </sst>
 </file>
@@ -36707,10 +36716,10 @@
         <v>3117</v>
       </c>
       <c r="C1527" s="43" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="D1527" s="43" t="s">
-        <v>731</v>
+        <v>3135</v>
       </c>
       <c r="E1527" s="43"/>
       <c r="F1527" s="43"/>
@@ -36724,10 +36733,10 @@
         <v>3119</v>
       </c>
       <c r="C1528" s="43" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="D1528" s="43" t="s">
-        <v>3009</v>
+        <v>3136</v>
       </c>
       <c r="E1528" s="43"/>
       <c r="F1528" s="43"/>
@@ -36753,14 +36762,12 @@
       </c>
       <c r="C1530" s="43"/>
       <c r="D1530" s="43" t="s">
-        <v>731</v>
+        <v>3135</v>
       </c>
       <c r="E1530" s="43" t="s">
-        <v>731</v>
-      </c>
-      <c r="F1530" s="43" t="s">
-        <v>731</v>
-      </c>
+        <v>3138</v>
+      </c>
+      <c r="F1530" s="43"/>
       <c r="G1530" s="43"/>
     </row>
     <row r="1531" spans="1:7" x14ac:dyDescent="0.25">
@@ -36771,7 +36778,7 @@
         <v>3123</v>
       </c>
       <c r="C1531" s="43" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="D1531" s="43"/>
       <c r="E1531" s="43"/>
@@ -36786,7 +36793,7 @@
         <v>3125</v>
       </c>
       <c r="C1532" s="43" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="D1532" s="43"/>
       <c r="E1532" s="43"/>
@@ -36801,7 +36808,7 @@
         <v>3127</v>
       </c>
       <c r="C1533" s="43" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="D1533" s="43"/>
       <c r="E1533" s="43"/>
@@ -36824,13 +36831,13 @@
         <v>3129</v>
       </c>
       <c r="B1535" s="7" t="s">
-        <v>3130</v>
+        <v>3137</v>
       </c>
       <c r="C1535" s="43" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="D1535" s="43" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="E1535" s="43"/>
       <c r="F1535" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A279607F-813A-4E03-BC4F-73D276875D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D43749F-9937-4E1F-8A01-3DEC9BD0FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4738" uniqueCount="3139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4745" uniqueCount="3146">
   <si>
     <t>Пароль</t>
   </si>
@@ -9451,6 +9451,27 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/4JCxONWWHfWtlQ</t>
+  </si>
+  <si>
+    <t>29/10/26/12:30</t>
+  </si>
+  <si>
+    <t>64455</t>
+  </si>
+  <si>
+    <t>+79181364455</t>
+  </si>
+  <si>
+    <t>50190</t>
+  </si>
+  <si>
+    <t>+79858850190</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/tkaIW_EKkfPVsA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/GXGEZ4ak8imzpQ</t>
   </si>
 </sst>
 </file>
@@ -36844,7 +36865,9 @@
       <c r="G1535" s="43"/>
     </row>
     <row r="1536" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1536" s="7"/>
+      <c r="A1536" s="37" t="s">
+        <v>3139</v>
+      </c>
       <c r="B1536" s="7"/>
       <c r="C1536" s="43"/>
       <c r="D1536" s="43"/>
@@ -36853,18 +36876,30 @@
       <c r="G1536" s="43"/>
     </row>
     <row r="1537" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1537" s="7"/>
-      <c r="B1537" s="7"/>
-      <c r="C1537" s="43"/>
+      <c r="A1537" s="7" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B1537" s="7" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1537" s="43" t="s">
+        <v>3144</v>
+      </c>
       <c r="D1537" s="43"/>
       <c r="E1537" s="43"/>
       <c r="F1537" s="43"/>
       <c r="G1537" s="43"/>
     </row>
     <row r="1538" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1538" s="7"/>
-      <c r="B1538" s="7"/>
-      <c r="C1538" s="43"/>
+      <c r="A1538" s="7" t="s">
+        <v>3142</v>
+      </c>
+      <c r="B1538" s="7" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1538" s="43" t="s">
+        <v>3145</v>
+      </c>
       <c r="D1538" s="43"/>
       <c r="E1538" s="43"/>
       <c r="F1538" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D43749F-9937-4E1F-8A01-3DEC9BD0FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49434D9-C1FE-477E-BBF9-1B6B4CA8C9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4745" uniqueCount="3146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4780" uniqueCount="3166">
   <si>
     <t>Пароль</t>
   </si>
@@ -9472,6 +9472,66 @@
   </si>
   <si>
     <t>https://disk.yandex.ru/d/GXGEZ4ak8imzpQ</t>
+  </si>
+  <si>
+    <t>52046</t>
+  </si>
+  <si>
+    <t>+79268252046</t>
+  </si>
+  <si>
+    <t>30/10/26/10:00</t>
+  </si>
+  <si>
+    <t>30/10/26/12:30</t>
+  </si>
+  <si>
+    <t>16968</t>
+  </si>
+  <si>
+    <t>+79001216968</t>
+  </si>
+  <si>
+    <t>94849</t>
+  </si>
+  <si>
+    <t>+79281494849</t>
+  </si>
+  <si>
+    <t>98681</t>
+  </si>
+  <si>
+    <t>+79067998681</t>
+  </si>
+  <si>
+    <t>03892</t>
+  </si>
+  <si>
+    <t>+79197303892</t>
+  </si>
+  <si>
+    <t>30/10/26/14:30</t>
+  </si>
+  <si>
+    <t>21274</t>
+  </si>
+  <si>
+    <t>+79189421274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* </t>
+  </si>
+  <si>
+    <t>* ДимМа</t>
+  </si>
+  <si>
+    <t>* Рамиль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">? </t>
+  </si>
+  <si>
+    <t>* Олег</t>
   </si>
 </sst>
 </file>
@@ -36908,14 +36968,24 @@
     <row r="1539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1539" s="7"/>
       <c r="B1539" s="7"/>
-      <c r="C1539" s="43"/>
-      <c r="D1539" s="43"/>
-      <c r="E1539" s="43"/>
-      <c r="F1539" s="43"/>
+      <c r="C1539" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1539" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1539" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1539" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1539" s="43"/>
     </row>
     <row r="1540" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1540" s="7"/>
+      <c r="A1540" s="37" t="s">
+        <v>3148</v>
+      </c>
       <c r="B1540" s="7"/>
       <c r="C1540" s="43"/>
       <c r="D1540" s="43"/>
@@ -36924,16 +36994,28 @@
       <c r="G1540" s="43"/>
     </row>
     <row r="1541" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1541" s="7"/>
-      <c r="B1541" s="7"/>
-      <c r="C1541" s="43"/>
+      <c r="A1541" s="7" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B1541" s="7" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C1541" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1541" s="43"/>
-      <c r="E1541" s="43"/>
-      <c r="F1541" s="43"/>
+      <c r="E1541" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1541" s="43" t="s">
+        <v>3161</v>
+      </c>
       <c r="G1541" s="43"/>
     </row>
     <row r="1542" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1542" s="7"/>
+      <c r="A1542" s="37" t="s">
+        <v>3149</v>
+      </c>
       <c r="B1542" s="7"/>
       <c r="C1542" s="43"/>
       <c r="D1542" s="43"/>
@@ -36942,43 +37024,85 @@
       <c r="G1542" s="43"/>
     </row>
     <row r="1543" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1543" s="7"/>
-      <c r="B1543" s="7"/>
-      <c r="C1543" s="43"/>
+      <c r="A1543" s="7" t="s">
+        <v>3150</v>
+      </c>
+      <c r="B1543" s="7" t="s">
+        <v>3151</v>
+      </c>
+      <c r="C1543" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1543" s="43"/>
-      <c r="E1543" s="43"/>
-      <c r="F1543" s="43"/>
+      <c r="E1543" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1543" s="43" t="s">
+        <v>3162</v>
+      </c>
       <c r="G1543" s="43"/>
     </row>
     <row r="1544" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1544" s="7"/>
-      <c r="B1544" s="7"/>
-      <c r="C1544" s="43"/>
+      <c r="A1544" s="7" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B1544" s="7" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C1544" s="43" t="s">
+        <v>3164</v>
+      </c>
       <c r="D1544" s="43"/>
-      <c r="E1544" s="43"/>
-      <c r="F1544" s="43"/>
+      <c r="E1544" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1544" s="43" t="s">
+        <v>3163</v>
+      </c>
       <c r="G1544" s="43"/>
     </row>
     <row r="1545" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1545" s="7"/>
-      <c r="B1545" s="7"/>
-      <c r="C1545" s="43"/>
+      <c r="A1545" s="7" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B1545" s="7" t="s">
+        <v>3155</v>
+      </c>
+      <c r="C1545" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1545" s="43"/>
-      <c r="E1545" s="43"/>
-      <c r="F1545" s="43"/>
+      <c r="E1545" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1545" s="43" t="s">
+        <v>3163</v>
+      </c>
       <c r="G1545" s="43"/>
     </row>
     <row r="1546" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1546" s="7"/>
-      <c r="B1546" s="7"/>
-      <c r="C1546" s="43"/>
+      <c r="A1546" s="7" t="s">
+        <v>3156</v>
+      </c>
+      <c r="B1546" s="7" t="s">
+        <v>3157</v>
+      </c>
+      <c r="C1546" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="D1546" s="43"/>
-      <c r="E1546" s="43"/>
-      <c r="F1546" s="43"/>
+      <c r="E1546" s="43" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1546" s="43" t="s">
+        <v>3165</v>
+      </c>
       <c r="G1546" s="43"/>
     </row>
     <row r="1547" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1547" s="7"/>
+      <c r="A1547" s="37" t="s">
+        <v>3158</v>
+      </c>
       <c r="B1547" s="7"/>
       <c r="C1547" s="43"/>
       <c r="D1547" s="43"/>
@@ -36987,10 +37111,16 @@
       <c r="G1547" s="43"/>
     </row>
     <row r="1548" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1548" s="7"/>
-      <c r="B1548" s="7"/>
+      <c r="A1548" s="7" t="s">
+        <v>3159</v>
+      </c>
+      <c r="B1548" s="7" t="s">
+        <v>3160</v>
+      </c>
       <c r="C1548" s="43"/>
-      <c r="D1548" s="43"/>
+      <c r="D1548" s="43" t="s">
+        <v>731</v>
+      </c>
       <c r="E1548" s="43"/>
       <c r="F1548" s="43"/>
       <c r="G1548" s="43"/>

--- a/ФОТО дрон яндекс ссылки.xlsx
+++ b/ФОТО дрон яндекс ссылки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\РАФТИНГ бланки\QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49434D9-C1FE-477E-BBF9-1B6B4CA8C9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5073C6E6-7410-4782-9C5A-A1F5852D85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4780" uniqueCount="3166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4780" uniqueCount="3170">
   <si>
     <t>Пароль</t>
   </si>
@@ -9519,26 +9519,38 @@
     <t>+79189421274</t>
   </si>
   <si>
-    <t xml:space="preserve">* </t>
-  </si>
-  <si>
-    <t>* ДимМа</t>
-  </si>
-  <si>
-    <t>* Рамиль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">? </t>
-  </si>
-  <si>
-    <t>* Олег</t>
+    <t>https://disk.yandex.ru/d/itfbguGkKnt8Sw</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/qMWeazTCv11lFA</t>
+  </si>
+  <si>
+    <t>? https://disk.yandex.ru/d/qMWeazTCv11lFA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/XINEQ4zKUXhd7g</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/vvLfk2nKuCZcrg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/NieKaplAR44lNQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/U0izZL-CufiHbA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/ZBkbH6Zs8MhuZg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/d/XPjcCFw0jLOUFg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9552,6 +9564,15 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -9642,7 +9663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9751,6 +9772,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -37001,14 +37025,14 @@
         <v>3147</v>
       </c>
       <c r="C1541" s="43" t="s">
-        <v>731</v>
+        <v>3161</v>
       </c>
       <c r="D1541" s="43"/>
       <c r="E1541" s="43" t="s">
-        <v>731</v>
+        <v>3168</v>
       </c>
       <c r="F1541" s="43" t="s">
-        <v>3161</v>
+        <v>3164</v>
       </c>
       <c r="G1541" s="43"/>
     </row>
@@ -37031,14 +37055,14 @@
         <v>3151</v>
       </c>
       <c r="C1543" s="43" t="s">
-        <v>731</v>
+        <v>3162</v>
       </c>
       <c r="D1543" s="43"/>
       <c r="E1543" s="43" t="s">
-        <v>731</v>
+        <v>3169</v>
       </c>
       <c r="F1543" s="43" t="s">
-        <v>3162</v>
+        <v>3165</v>
       </c>
       <c r="G1543" s="43"/>
     </row>
@@ -37050,14 +37074,14 @@
         <v>3153</v>
       </c>
       <c r="C1544" s="43" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="D1544" s="43"/>
       <c r="E1544" s="43" t="s">
-        <v>731</v>
+        <v>3169</v>
       </c>
       <c r="F1544" s="43" t="s">
-        <v>3163</v>
+        <v>3167</v>
       </c>
       <c r="G1544" s="43"/>
     </row>
@@ -37068,15 +37092,15 @@
       <c r="B1545" s="7" t="s">
         <v>3155</v>
       </c>
-      <c r="C1545" s="43" t="s">
-        <v>731</v>
+      <c r="C1545" s="44" t="s">
+        <v>3162</v>
       </c>
       <c r="D1545" s="43"/>
       <c r="E1545" s="43" t="s">
-        <v>731</v>
+        <v>3169</v>
       </c>
       <c r="F1545" s="43" t="s">
-        <v>3163</v>
+        <v>3167</v>
       </c>
       <c r="G1545" s="43"/>
     </row>
@@ -37088,14 +37112,14 @@
         <v>3157</v>
       </c>
       <c r="C1546" s="43" t="s">
-        <v>731</v>
+        <v>3162</v>
       </c>
       <c r="D1546" s="43"/>
       <c r="E1546" s="43" t="s">
-        <v>731</v>
+        <v>3169</v>
       </c>
       <c r="F1546" s="43" t="s">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="G1546" s="43"/>
     </row>
